--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="575" uniqueCount="575">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="576" uniqueCount="576">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,64 +38,64 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02345728874207</t>
+    <t xml:space="preserve">3.02345752716064</t>
   </si>
   <si>
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519899368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88901519775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98013710975647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97266840934753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94577980041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95773029327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9622118473053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9353232383728</t>
+    <t xml:space="preserve">2.96519923210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88901543617249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98013734817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97266817092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94578003883362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9577305316925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96221160888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93532347679138</t>
   </si>
   <si>
     <t xml:space="preserve">2.91291642189026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9786434173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98611235618591</t>
+    <t xml:space="preserve">2.97864365577698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98611259460449</t>
   </si>
   <si>
     <t xml:space="preserve">3.03540802001953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.056321144104</t>
+    <t xml:space="preserve">3.05632138252258</t>
   </si>
   <si>
     <t xml:space="preserve">3.0593090057373</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05034613609314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98760652542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95026135444641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01598882675171</t>
+    <t xml:space="preserve">3.05034589767456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98760628700256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95026159286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01598858833313</t>
   </si>
   <si>
     <t xml:space="preserve">3.01001334190369</t>
@@ -104,34 +104,34 @@
     <t xml:space="preserve">3.02495145797729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01748204231262</t>
+    <t xml:space="preserve">3.01748251914978</t>
   </si>
   <si>
     <t xml:space="preserve">3.03092670440674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99955654144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0443708896637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.959223985672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00254416465759</t>
+    <t xml:space="preserve">2.99955677986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04437112808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95922422409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00254464149475</t>
   </si>
   <si>
     <t xml:space="preserve">2.92785429954529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90843462944031</t>
+    <t xml:space="preserve">2.90843510627747</t>
   </si>
   <si>
     <t xml:space="preserve">2.896484375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91889142990112</t>
+    <t xml:space="preserve">2.91889119148254</t>
   </si>
   <si>
     <t xml:space="preserve">2.9159038066864</t>
@@ -140,25 +140,25 @@
     <t xml:space="preserve">2.92038512229919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90544724464417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90992879867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9233729839325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8382260799408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8606333732605</t>
+    <t xml:space="preserve">2.90544700622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90992856025696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92337274551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83822560310364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86063313484192</t>
   </si>
   <si>
     <t xml:space="preserve">2.82627558708191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77996778488159</t>
+    <t xml:space="preserve">2.77996754646301</t>
   </si>
   <si>
     <t xml:space="preserve">2.84569501876831</t>
@@ -167,16 +167,16 @@
     <t xml:space="preserve">2.86810207366943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88303971290588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79639959335327</t>
+    <t xml:space="preserve">2.88303995132446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79639935493469</t>
   </si>
   <si>
     <t xml:space="preserve">2.87557101249695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89797806739807</t>
+    <t xml:space="preserve">2.89797830581665</t>
   </si>
   <si>
     <t xml:space="preserve">2.80088090896606</t>
@@ -185,10 +185,10 @@
     <t xml:space="preserve">2.74262237548828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82179427146912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75009155273438</t>
+    <t xml:space="preserve">2.82179403305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75009179115295</t>
   </si>
   <si>
     <t xml:space="preserve">2.76353597640991</t>
@@ -197,22 +197,22 @@
     <t xml:space="preserve">2.77847409248352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78594279289246</t>
+    <t xml:space="preserve">2.78594303131104</t>
   </si>
   <si>
     <t xml:space="preserve">2.79341197013855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69631505012512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65150046348572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6216242313385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5394651889801</t>
+    <t xml:space="preserve">2.69631481170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6515007019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62162470817566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53946542739868</t>
   </si>
   <si>
     <t xml:space="preserve">2.56934142112732</t>
@@ -221,7 +221,7 @@
     <t xml:space="preserve">2.61415553092957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65896940231323</t>
+    <t xml:space="preserve">2.65896964073181</t>
   </si>
   <si>
     <t xml:space="preserve">2.68884563446045</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">2.70378375053406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77100491523743</t>
+    <t xml:space="preserve">2.77100443840027</t>
   </si>
   <si>
     <t xml:space="preserve">2.81581902503967</t>
@@ -239,7 +239,7 @@
     <t xml:space="preserve">2.7336597442627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66643834114075</t>
+    <t xml:space="preserve">2.66643857955933</t>
   </si>
   <si>
     <t xml:space="preserve">2.68137645721436</t>
@@ -251,16 +251,16 @@
     <t xml:space="preserve">2.72619080543518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8307569026947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89315104484558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69871854782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83870983123779</t>
+    <t xml:space="preserve">2.83075714111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.893150806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69871830940247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83870959281921</t>
   </si>
   <si>
     <t xml:space="preserve">2.93203711509705</t>
@@ -275,55 +275,55 @@
     <t xml:space="preserve">2.81537771224976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84648704528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79982304573059</t>
+    <t xml:space="preserve">2.84648680686951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79982328414917</t>
   </si>
   <si>
     <t xml:space="preserve">2.73760485649109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76093649864197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80760073661804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00980997085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9553689956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90870523452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88537335395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82315516471863</t>
+    <t xml:space="preserve">2.76093673706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80760049819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00980973243713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95536875724792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90870547294617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88537311553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82315492630005</t>
   </si>
   <si>
     <t xml:space="preserve">2.86204171180725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00203227996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9164822101593</t>
+    <t xml:space="preserve">3.00203251838684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91648244857788</t>
   </si>
   <si>
     <t xml:space="preserve">2.85426449775696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72982740402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68316388130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7220504283905</t>
+    <t xml:space="preserve">2.72982788085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68316411972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72205018997192</t>
   </si>
   <si>
     <t xml:space="preserve">2.75315952301025</t>
@@ -332,19 +332,19 @@
     <t xml:space="preserve">2.70649576187134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93981456756592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99425530433655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97870111465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86981892585754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94759154319763</t>
+    <t xml:space="preserve">2.93981432914734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99425554275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97870087623596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86981868743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94759178161621</t>
   </si>
   <si>
     <t xml:space="preserve">2.98647809028625</t>
@@ -353,19 +353,19 @@
     <t xml:space="preserve">2.63650035858154</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55095028877258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51984071731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41095876693726</t>
+    <t xml:space="preserve">2.550950050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51984095573425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41095900535583</t>
   </si>
   <si>
     <t xml:space="preserve">2.34096336364746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34874033927917</t>
+    <t xml:space="preserve">2.34874081611633</t>
   </si>
   <si>
     <t xml:space="preserve">2.36429500579834</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">2.24763584136963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3254086971283</t>
+    <t xml:space="preserve">2.32540893554688</t>
   </si>
   <si>
     <t xml:space="preserve">2.23208093643188</t>
@@ -401,7 +401,7 @@
     <t xml:space="preserve">2.1465311050415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10764479637146</t>
+    <t xml:space="preserve">2.10764455795288</t>
   </si>
   <si>
     <t xml:space="preserve">2.15430855751038</t>
@@ -410,73 +410,73 @@
     <t xml:space="preserve">2.17764019966125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22430419921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35651779174805</t>
+    <t xml:space="preserve">2.22430396080017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35651755332947</t>
   </si>
   <si>
     <t xml:space="preserve">2.4887318611145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52761840820312</t>
+    <t xml:space="preserve">2.52761816978455</t>
   </si>
   <si>
     <t xml:space="preserve">2.43429064750671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44206809997559</t>
+    <t xml:space="preserve">2.44206786155701</t>
   </si>
   <si>
     <t xml:space="preserve">2.5587272644043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44984531402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37207221984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33318591117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29429960250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3798496723175</t>
+    <t xml:space="preserve">2.44984555244446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37207245826721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33318614959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29429936408997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37984991073608</t>
   </si>
   <si>
     <t xml:space="preserve">2.71427321434021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58205938339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62872314453125</t>
+    <t xml:space="preserve">2.58205890655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62872290611267</t>
   </si>
   <si>
     <t xml:space="preserve">2.659832239151</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57428193092346</t>
+    <t xml:space="preserve">2.57428169250488</t>
   </si>
   <si>
     <t xml:space="preserve">2.67538666725159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64427733421326</t>
+    <t xml:space="preserve">2.64427781105042</t>
   </si>
   <si>
     <t xml:space="preserve">2.69094109535217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76871371269226</t>
+    <t xml:space="preserve">2.76871418952942</t>
   </si>
   <si>
     <t xml:space="preserve">2.90092802047729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9631462097168</t>
+    <t xml:space="preserve">2.96314597129822</t>
   </si>
   <si>
     <t xml:space="preserve">2.92426013946533</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">3.03314185142517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0642511844635</t>
+    <t xml:space="preserve">3.06425094604492</t>
   </si>
   <si>
     <t xml:space="preserve">3.07980561256409</t>
@@ -509,25 +509,25 @@
     <t xml:space="preserve">3.01191973686218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1090784072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09288501739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1252715587616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0766921043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99572682380676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30339598655701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41674733161926</t>
+    <t xml:space="preserve">3.10907816886902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0928852558136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12527132034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07669186592102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99572658538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30339574813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41674757003784</t>
   </si>
   <si>
     <t xml:space="preserve">3.35197520256042</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">3.36816835403442</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23862338066101</t>
+    <t xml:space="preserve">3.23862314224243</t>
   </si>
   <si>
     <t xml:space="preserve">3.31958889961243</t>
@@ -551,37 +551,37 @@
     <t xml:space="preserve">3.28720235824585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22242999076843</t>
+    <t xml:space="preserve">3.22243022918701</t>
   </si>
   <si>
     <t xml:space="preserve">3.17385101318359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20623707771301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1414647102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40055441856384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49771356582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38436102867126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25481629371643</t>
+    <t xml:space="preserve">3.20623731613159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14146494865417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40055418014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49771332740784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38436126708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25481653213501</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004416465759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96334052085876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97953343391418</t>
+    <t xml:space="preserve">2.96334028244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97953367233276</t>
   </si>
   <si>
     <t xml:space="preserve">2.80140924453735</t>
@@ -599,34 +599,34 @@
     <t xml:space="preserve">2.78521609306335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75282979011536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72044348716736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83379554748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76902294158936</t>
+    <t xml:space="preserve">2.75283002853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72044372558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83379530906677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76902318000793</t>
   </si>
   <si>
     <t xml:space="preserve">2.73663687705994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81760215759277</t>
+    <t xml:space="preserve">2.81760239601135</t>
   </si>
   <si>
     <t xml:space="preserve">2.89856767654419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91476106643677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63947796821594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67186427116394</t>
+    <t xml:space="preserve">2.91476082801819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63947772979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67186403274536</t>
   </si>
   <si>
     <t xml:space="preserve">2.62328481674194</t>
@@ -635,13 +635,13 @@
     <t xml:space="preserve">2.68805718421936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70425033569336</t>
+    <t xml:space="preserve">2.70425057411194</t>
   </si>
   <si>
     <t xml:space="preserve">2.60709190368652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59089851379395</t>
+    <t xml:space="preserve">2.59089875221252</t>
   </si>
   <si>
     <t xml:space="preserve">2.42896747589111</t>
@@ -653,25 +653,25 @@
     <t xml:space="preserve">2.46135354042053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31561541557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29942226409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35488176345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40607452392578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28662443161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1330451965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08185172080994</t>
+    <t xml:space="preserve">2.3156156539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29942274093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35488152503967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40607476234436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28662419319153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13304495811462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08185195922852</t>
   </si>
   <si>
     <t xml:space="preserve">2.06478762626648</t>
@@ -686,22 +686,22 @@
     <t xml:space="preserve">2.09891629219055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26955962181091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2183666229248</t>
+    <t xml:space="preserve">2.26956009864807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21836686134338</t>
   </si>
   <si>
     <t xml:space="preserve">2.32075309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55965399742126</t>
+    <t xml:space="preserve">2.55965423583984</t>
   </si>
   <si>
     <t xml:space="preserve">2.54258990287781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45726776123047</t>
+    <t xml:space="preserve">2.45726799964905</t>
   </si>
   <si>
     <t xml:space="preserve">2.5767183303833</t>
@@ -716,37 +716,37 @@
     <t xml:space="preserve">2.64497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59378266334534</t>
+    <t xml:space="preserve">2.59378290176392</t>
   </si>
   <si>
     <t xml:space="preserve">2.69616913795471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71323347091675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44020318984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4231390953064</t>
+    <t xml:space="preserve">2.71323323249817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44020342826843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42313933372498</t>
   </si>
   <si>
     <t xml:space="preserve">2.47433233261108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15010952949524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33781743049622</t>
+    <t xml:space="preserve">2.15010929107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33781719207764</t>
   </si>
   <si>
     <t xml:space="preserve">2.30368876457214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25249552726746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23543119430542</t>
+    <t xml:space="preserve">2.25249576568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23543095588684</t>
   </si>
   <si>
     <t xml:space="preserve">2.37194633483887</t>
@@ -758,10 +758,10 @@
     <t xml:space="preserve">2.20130252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18423819541931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01359438896179</t>
+    <t xml:space="preserve">2.18423795700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01359415054321</t>
   </si>
   <si>
     <t xml:space="preserve">2.04772329330444</t>
@@ -770,31 +770,31 @@
     <t xml:space="preserve">2.11598062515259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91120851039886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87707948684692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84295105934143</t>
+    <t xml:space="preserve">1.91120839118958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87707984447479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84295094013214</t>
   </si>
   <si>
     <t xml:space="preserve">1.97946584224701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86001539230347</t>
+    <t xml:space="preserve">1.86001515388489</t>
   </si>
   <si>
     <t xml:space="preserve">1.94533693790436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96240139007568</t>
+    <t xml:space="preserve">1.96240127086639</t>
   </si>
   <si>
     <t xml:space="preserve">1.99652993679047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81561946868896</t>
+    <t xml:space="preserve">2.81561923027039</t>
   </si>
   <si>
     <t xml:space="preserve">2.90094137191772</t>
@@ -803,13 +803,13 @@
     <t xml:space="preserve">2.88387703895569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76442646980286</t>
+    <t xml:space="preserve">2.76442623138428</t>
   </si>
   <si>
     <t xml:space="preserve">2.73029756546021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6791045665741</t>
+    <t xml:space="preserve">2.67910432815552</t>
   </si>
   <si>
     <t xml:space="preserve">2.74736189842224</t>
@@ -836,10 +836,10 @@
     <t xml:space="preserve">3.02039170265198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00332736968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03745603561401</t>
+    <t xml:space="preserve">3.00332713127136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03745627403259</t>
   </si>
   <si>
     <t xml:space="preserve">2.98626303672791</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.13131022453308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06305241584778</t>
+    <t xml:space="preserve">3.06305265426636</t>
   </si>
   <si>
     <t xml:space="preserve">3.16543889045715</t>
@@ -869,13 +869,13 @@
     <t xml:space="preserve">3.19956755638123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15690684318542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23369598388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2763569355011</t>
+    <t xml:space="preserve">3.15690660476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23369646072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27635717391968</t>
   </si>
   <si>
     <t xml:space="preserve">3.24222826957703</t>
@@ -887,43 +887,43 @@
     <t xml:space="preserve">3.31048607826233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3446147441864</t>
+    <t xml:space="preserve">3.34461450576782</t>
   </si>
   <si>
     <t xml:space="preserve">3.32755041122437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28488922119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18250322341919</t>
+    <t xml:space="preserve">3.28488945960999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18250346183777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29342126846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33710074424744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32836484909058</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342150688171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33710074424744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32836484909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29342174530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24974226951599</t>
+    <t xml:space="preserve">3.24974250793457</t>
   </si>
   <si>
     <t xml:space="preserve">3.20606303215027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15364766120911</t>
+    <t xml:space="preserve">3.15364742279053</t>
   </si>
   <si>
     <t xml:space="preserve">3.21479892730713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17111968994141</t>
+    <t xml:space="preserve">3.17111945152283</t>
   </si>
   <si>
     <t xml:space="preserve">3.26721405982971</t>
@@ -950,13 +950,13 @@
     <t xml:space="preserve">3.51181817054749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54676151275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63412046432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62538480758667</t>
+    <t xml:space="preserve">3.54676175117493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63412022590637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62538456916809</t>
   </si>
   <si>
     <t xml:space="preserve">3.74768662452698</t>
@@ -965,34 +965,34 @@
     <t xml:space="preserve">3.69527125358582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66906356811523</t>
+    <t xml:space="preserve">3.66906332969666</t>
   </si>
   <si>
     <t xml:space="preserve">3.60791301727295</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55549764633179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66032791137695</t>
+    <t xml:space="preserve">3.55549788475037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66032767295837</t>
   </si>
   <si>
     <t xml:space="preserve">3.65159177780151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68653535842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70400714874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75642251968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57296967506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53802585601807</t>
+    <t xml:space="preserve">3.68653512001038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7040069103241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75642275810242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57296943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53802609443665</t>
   </si>
   <si>
     <t xml:space="preserve">3.3458366394043</t>
@@ -1004,7 +1004,7 @@
     <t xml:space="preserve">3.42445969581604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45066738128662</t>
+    <t xml:space="preserve">3.45066714286804</t>
   </si>
   <si>
     <t xml:space="preserve">3.44193148612976</t>
@@ -1019,10 +1019,10 @@
     <t xml:space="preserve">3.35457253456116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45940327644348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52928972244263</t>
+    <t xml:space="preserve">3.4594030380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52928996086121</t>
   </si>
   <si>
     <t xml:space="preserve">3.46813893318176</t>
@@ -1031,10 +1031,10 @@
     <t xml:space="preserve">3.47687458992004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79136633872986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7214789390564</t>
+    <t xml:space="preserve">3.79136610031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72147917747498</t>
   </si>
   <si>
     <t xml:space="preserve">3.8787248134613</t>
@@ -1049,13 +1049,13 @@
     <t xml:space="preserve">4.35046148300171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18447971343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20195150375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25436687469482</t>
+    <t xml:space="preserve">4.1844801902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20195198059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25436639785767</t>
   </si>
   <si>
     <t xml:space="preserve">4.14080047607422</t>
@@ -1067,10 +1067,10 @@
     <t xml:space="preserve">3.98355484008789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94861197471619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93114018440247</t>
+    <t xml:space="preserve">3.94861149787903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93113970756531</t>
   </si>
   <si>
     <t xml:space="preserve">4.08838510513306</t>
@@ -1088,31 +1088,31 @@
     <t xml:space="preserve">4.00976276397705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93987607955933</t>
+    <t xml:space="preserve">3.93987560272217</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2106876373291</t>
+    <t xml:space="preserve">4.21068811416626</t>
   </si>
   <si>
     <t xml:space="preserve">4.29804611206055</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28931045532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21942329406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19321584701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1495361328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16700792312622</t>
+    <t xml:space="preserve">4.28930997848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21942377090454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19321632385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14953660964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16700839996338</t>
   </si>
   <si>
     <t xml:space="preserve">4.11459302902222</t>
@@ -1121,19 +1121,19 @@
     <t xml:space="preserve">4.06217813491821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78262996673584</t>
+    <t xml:space="preserve">3.78263020515442</t>
   </si>
   <si>
     <t xml:space="preserve">3.80010175704956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82630968093872</t>
+    <t xml:space="preserve">3.82630944252014</t>
   </si>
   <si>
     <t xml:space="preserve">3.83504509925842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84378099441528</t>
+    <t xml:space="preserve">3.84378123283386</t>
   </si>
   <si>
     <t xml:space="preserve">3.77389454841614</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734786987305</t>
+    <t xml:space="preserve">3.95734739303589</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">3.86125302314758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76515865325928</t>
+    <t xml:space="preserve">3.7651584148407</t>
   </si>
   <si>
     <t xml:space="preserve">3.8175733089447</t>
@@ -1160,13 +1160,13 @@
     <t xml:space="preserve">3.64285612106323</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67779970169067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73895072937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85251665115356</t>
+    <t xml:space="preserve">3.67779946327209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7389509677887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85251712799072</t>
   </si>
   <si>
     <t xml:space="preserve">3.71274304389954</t>
@@ -1196,7 +1196,7 @@
     <t xml:space="preserve">2.91777920722961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90904331207275</t>
+    <t xml:space="preserve">2.90904355049133</t>
   </si>
   <si>
     <t xml:space="preserve">3.37204432487488</t>
@@ -1205,7 +1205,7 @@
     <t xml:space="preserve">3.38078022003174</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41572380065918</t>
+    <t xml:space="preserve">3.41572403907776</t>
   </si>
   <si>
     <t xml:space="preserve">3.31962895393372</t>
@@ -1214,7 +1214,7 @@
     <t xml:space="preserve">3.27594995498657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28468585014343</t>
+    <t xml:space="preserve">3.28468561172485</t>
   </si>
   <si>
     <t xml:space="preserve">3.50245499610901</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">3.32098078727722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26653838157654</t>
+    <t xml:space="preserve">3.26653814315796</t>
   </si>
   <si>
     <t xml:space="preserve">3.39357042312622</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">3.23024344444275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19394850730896</t>
+    <t xml:space="preserve">3.19394874572754</t>
   </si>
   <si>
     <t xml:space="preserve">3.25746440887451</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">3.2211697101593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10321164131165</t>
+    <t xml:space="preserve">3.10321140289307</t>
   </si>
   <si>
     <t xml:space="preserve">2.99432682991028</t>
@@ -1286,13 +1286,13 @@
     <t xml:space="preserve">2.95803189277649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85822129249573</t>
+    <t xml:space="preserve">2.85822105407715</t>
   </si>
   <si>
     <t xml:space="preserve">2.89451599121094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86729502677917</t>
+    <t xml:space="preserve">2.8672947883606</t>
   </si>
   <si>
     <t xml:space="preserve">2.81285238265991</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">2.75841021537781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7039680480957</t>
+    <t xml:space="preserve">2.70396780967712</t>
   </si>
   <si>
     <t xml:space="preserve">2.72211527824402</t>
@@ -1313,16 +1313,16 @@
     <t xml:space="preserve">2.64952564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79470491409302</t>
+    <t xml:space="preserve">2.7947051525116</t>
   </si>
   <si>
     <t xml:space="preserve">2.92173719406128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05784296989441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02154779434204</t>
+    <t xml:space="preserve">3.05784273147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02154803276062</t>
   </si>
   <si>
     <t xml:space="preserve">3.13950634002686</t>
@@ -1352,46 +1352,46 @@
     <t xml:space="preserve">3.08506417274475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01247406005859</t>
+    <t xml:space="preserve">3.01247429847717</t>
   </si>
   <si>
     <t xml:space="preserve">2.88544225692749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77655744552612</t>
+    <t xml:space="preserve">2.7765576839447</t>
   </si>
   <si>
     <t xml:space="preserve">2.71304154396057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63137817382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68582057952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66767311096191</t>
+    <t xml:space="preserve">2.6313784122467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68582034111023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66767287254333</t>
   </si>
   <si>
     <t xml:space="preserve">2.55878829956055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52249360084534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67674684524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64045190811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87636876106262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83099961280823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6041567325592</t>
+    <t xml:space="preserve">2.52249336242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67674660682678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64045214653015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87636852264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83099985122681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60415697097778</t>
   </si>
   <si>
     <t xml:space="preserve">2.73118901252747</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">2.91266345977783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12135910987854</t>
+    <t xml:space="preserve">3.12135887145996</t>
   </si>
   <si>
     <t xml:space="preserve">3.0759904384613</t>
@@ -1427,46 +1427,46 @@
     <t xml:space="preserve">3.0941379070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38449668884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41171789169312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37542295455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42079162597656</t>
+    <t xml:space="preserve">3.38449692726135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41171765327454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37542319297791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42079138755798</t>
   </si>
   <si>
     <t xml:space="preserve">3.43893885612488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36634922027588</t>
+    <t xml:space="preserve">3.36634945869446</t>
   </si>
   <si>
     <t xml:space="preserve">3.35727572441101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20302224159241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27561211585999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29375982284546</t>
+    <t xml:space="preserve">3.20302248001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27561187744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29375958442688</t>
   </si>
   <si>
     <t xml:space="preserve">3.1667275428772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11228537559509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78563117980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84007358551025</t>
+    <t xml:space="preserve">3.11228513717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78563141822815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84007382392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.82192611694336</t>
@@ -1737,6 +1737,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.22000002861023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16000008583069</t>
   </si>
 </sst>
 </file>
@@ -55219,7 +55222,7 @@
     </row>
     <row r="2045">
       <c r="A2045" s="1" t="n">
-        <v>45943.6494675926</v>
+        <v>45943.2916666667</v>
       </c>
       <c r="B2045" t="n">
         <v>8941</v>
@@ -55240,6 +55243,32 @@
         <v>574</v>
       </c>
       <c r="H2045" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2046">
+      <c r="A2046" s="1" t="n">
+        <v>45944.5968518518</v>
+      </c>
+      <c r="B2046" t="n">
+        <v>7126</v>
+      </c>
+      <c r="C2046" t="n">
+        <v>3.22000002861023</v>
+      </c>
+      <c r="D2046" t="n">
+        <v>3.16000008583069</v>
+      </c>
+      <c r="E2046" t="n">
+        <v>3.22000002861023</v>
+      </c>
+      <c r="F2046" t="n">
+        <v>3.16000008583069</v>
+      </c>
+      <c r="G2046" t="s">
+        <v>575</v>
+      </c>
+      <c r="H2046" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -44,46 +44,46 @@
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519923210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88901567459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98013758659363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97266793251038</t>
+    <t xml:space="preserve">2.96519947052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88901543617249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98013734817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97266840934753</t>
   </si>
   <si>
     <t xml:space="preserve">2.94578003883362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95773005485535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96221160888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93532347679138</t>
+    <t xml:space="preserve">2.95773029327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96221137046814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9353232383728</t>
   </si>
   <si>
     <t xml:space="preserve">2.91291618347168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9786434173584</t>
+    <t xml:space="preserve">2.97864365577698</t>
   </si>
   <si>
     <t xml:space="preserve">2.98611259460449</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03540825843811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05632138252258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0593090057373</t>
+    <t xml:space="preserve">3.03540802001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.056321144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05930924415588</t>
   </si>
   <si>
     <t xml:space="preserve">3.05034637451172</t>
@@ -92,73 +92,73 @@
     <t xml:space="preserve">2.98760604858398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95026159286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01598858833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01001358032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02495145797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01748251914978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03092670440674</t>
+    <t xml:space="preserve">2.95026135444641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01598882675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01001334190369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02495169639587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0174822807312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03092646598816</t>
   </si>
   <si>
     <t xml:space="preserve">2.99955677986145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04437112808228</t>
+    <t xml:space="preserve">3.0443708896637</t>
   </si>
   <si>
     <t xml:space="preserve">2.959223985672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00254464149475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92785406112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90843462944031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9188916683197</t>
+    <t xml:space="preserve">3.00254440307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92785429954529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90843486785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89648461341858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91889142990112</t>
   </si>
   <si>
     <t xml:space="preserve">2.9159038066864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92038559913635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90544724464417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90992879867554</t>
+    <t xml:space="preserve">2.92038536071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90544748306274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90992856025696</t>
   </si>
   <si>
     <t xml:space="preserve">2.9233729839325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8382260799408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86063289642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82627534866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77996778488159</t>
+    <t xml:space="preserve">2.83822584152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86063313484192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82627558708191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77996754646301</t>
   </si>
   <si>
     <t xml:space="preserve">2.84569501876831</t>
@@ -167,22 +167,22 @@
     <t xml:space="preserve">2.86810207366943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88304018974304</t>
+    <t xml:space="preserve">2.88303971290588</t>
   </si>
   <si>
     <t xml:space="preserve">2.79639959335327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87557101249695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89797830581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80088090896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74262261390686</t>
+    <t xml:space="preserve">2.87557125091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89797806739807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80088114738464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74262237548828</t>
   </si>
   <si>
     <t xml:space="preserve">2.82179427146912</t>
@@ -203,10 +203,10 @@
     <t xml:space="preserve">2.79341173171997</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69631457328796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65150046348572</t>
+    <t xml:space="preserve">2.69631481170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6515007019043</t>
   </si>
   <si>
     <t xml:space="preserve">2.62162446975708</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">2.5693416595459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61415576934814</t>
+    <t xml:space="preserve">2.61415553092957</t>
   </si>
   <si>
     <t xml:space="preserve">2.65896964073181</t>
@@ -227,16 +227,16 @@
     <t xml:space="preserve">2.68884563446045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70378375053406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77100467681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81581878662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7336597442627</t>
+    <t xml:space="preserve">2.70378351211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77100491523743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81581902503967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73365950584412</t>
   </si>
   <si>
     <t xml:space="preserve">2.66643857955933</t>
@@ -254,40 +254,40 @@
     <t xml:space="preserve">2.8307569026947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89315056800842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69871854782104</t>
+    <t xml:space="preserve">2.893150806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69871878623962</t>
   </si>
   <si>
     <t xml:space="preserve">2.83870959281921</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93203711509705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87759613990784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8309326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81537771224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84648656845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79982304573059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73760509490967</t>
+    <t xml:space="preserve">2.93203687667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87759590148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83093237876892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81537795066833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84648680686951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79982328414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73760485649109</t>
   </si>
   <si>
     <t xml:space="preserve">2.76093673706055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80760049819946</t>
+    <t xml:space="preserve">2.80760025978088</t>
   </si>
   <si>
     <t xml:space="preserve">3.00980973243713</t>
@@ -296,13 +296,13 @@
     <t xml:space="preserve">2.9553689956665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90870523452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88537335395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82315540313721</t>
+    <t xml:space="preserve">2.90870499610901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88537359237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82315516471863</t>
   </si>
   <si>
     <t xml:space="preserve">2.86204171180725</t>
@@ -314,49 +314,49 @@
     <t xml:space="preserve">2.91648268699646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8542640209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7298276424408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68316388130188</t>
+    <t xml:space="preserve">2.85426425933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72982740402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68316411972046</t>
   </si>
   <si>
     <t xml:space="preserve">2.72205066680908</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75315928459167</t>
+    <t xml:space="preserve">2.75315976142883</t>
   </si>
   <si>
     <t xml:space="preserve">2.70649576187134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93981432914734</t>
+    <t xml:space="preserve">2.93981456756592</t>
   </si>
   <si>
     <t xml:space="preserve">2.99425530433655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97870063781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86981868743896</t>
+    <t xml:space="preserve">2.9787003993988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86981892585754</t>
   </si>
   <si>
     <t xml:space="preserve">2.94759154319763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98647785186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63650035858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55094981193542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51984095573425</t>
+    <t xml:space="preserve">2.98647809028625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63650012016296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55095028877258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51984119415283</t>
   </si>
   <si>
     <t xml:space="preserve">2.41095876693726</t>
@@ -365,10 +365,10 @@
     <t xml:space="preserve">2.34096312522888</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34874081611633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36429500579834</t>
+    <t xml:space="preserve">2.34874105453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36429524421692</t>
   </si>
   <si>
     <t xml:space="preserve">2.2554132938385</t>
@@ -377,13 +377,13 @@
     <t xml:space="preserve">2.24763607978821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32540893554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23208141326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18541741371155</t>
+    <t xml:space="preserve">2.3254086971283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23208117485046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18541765213013</t>
   </si>
   <si>
     <t xml:space="preserve">2.27874493598938</t>
@@ -392,22 +392,22 @@
     <t xml:space="preserve">2.26319026947021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21652674674988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06875824928284</t>
+    <t xml:space="preserve">2.21652698516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06875848770142</t>
   </si>
   <si>
     <t xml:space="preserve">2.14653134346008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10764503479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15430855751038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17763996124268</t>
+    <t xml:space="preserve">2.10764479637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1543083190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17764019966125</t>
   </si>
   <si>
     <t xml:space="preserve">2.22430396080017</t>
@@ -416,7 +416,7 @@
     <t xml:space="preserve">2.35651779174805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4887318611145</t>
+    <t xml:space="preserve">2.48873209953308</t>
   </si>
   <si>
     <t xml:space="preserve">2.52761793136597</t>
@@ -431,10 +431,10 @@
     <t xml:space="preserve">2.5587272644043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44984531402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37207245826721</t>
+    <t xml:space="preserve">2.44984555244446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37207221984863</t>
   </si>
   <si>
     <t xml:space="preserve">2.33318614959717</t>
@@ -443,13 +443,13 @@
     <t xml:space="preserve">2.29429960250854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37984991073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71427321434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58205914497375</t>
+    <t xml:space="preserve">2.3798496723175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71427297592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58205938339233</t>
   </si>
   <si>
     <t xml:space="preserve">2.62872290611267</t>
@@ -470,55 +470,55 @@
     <t xml:space="preserve">2.69094133377075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76871371269226</t>
+    <t xml:space="preserve">2.76871418952942</t>
   </si>
   <si>
     <t xml:space="preserve">2.90092802047729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9631462097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92426013946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97092342376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01758742332458</t>
+    <t xml:space="preserve">2.96314597129822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92425990104675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97092366218567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01758766174316</t>
   </si>
   <si>
     <t xml:space="preserve">3.04869651794434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03314161300659</t>
+    <t xml:space="preserve">3.03314208984375</t>
   </si>
   <si>
     <t xml:space="preserve">3.06425094604492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07980561256409</t>
+    <t xml:space="preserve">3.07980537414551</t>
   </si>
   <si>
     <t xml:space="preserve">3.06049919128418</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0281126499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01191973686218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10907816886902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09288501739502</t>
+    <t xml:space="preserve">3.02811288833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01191997528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1090784072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0928852558136</t>
   </si>
   <si>
     <t xml:space="preserve">3.1252715587616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07669234275818</t>
+    <t xml:space="preserve">3.0766921043396</t>
   </si>
   <si>
     <t xml:space="preserve">2.99572658538818</t>
@@ -527,64 +527,64 @@
     <t xml:space="preserve">3.30339574813843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41674733161926</t>
+    <t xml:space="preserve">3.41674709320068</t>
   </si>
   <si>
     <t xml:space="preserve">3.35197496414185</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33578157424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36816787719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23862314224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31958913803101</t>
+    <t xml:space="preserve">3.33578181266785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36816811561584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23862338066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31958889961243</t>
   </si>
   <si>
     <t xml:space="preserve">3.27100944519043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28720259666443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22242999076843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17385101318359</t>
+    <t xml:space="preserve">3.28720283508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22243022918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17385077476501</t>
   </si>
   <si>
     <t xml:space="preserve">3.20623707771301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1414647102356</t>
+    <t xml:space="preserve">3.14146494865417</t>
   </si>
   <si>
     <t xml:space="preserve">3.40055441856384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49771356582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38436126708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25481677055359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19004416465759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96334004402161</t>
+    <t xml:space="preserve">3.497713804245</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38436150550842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25481653213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19004392623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96334052085876</t>
   </si>
   <si>
     <t xml:space="preserve">2.97953367233276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80140924453735</t>
+    <t xml:space="preserve">2.80140900611877</t>
   </si>
   <si>
     <t xml:space="preserve">2.88237452507019</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">2.75283002853394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72044348716736</t>
+    <t xml:space="preserve">2.72044324874878</t>
   </si>
   <si>
     <t xml:space="preserve">2.83379554748535</t>
@@ -614,31 +614,31 @@
     <t xml:space="preserve">2.73663663864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81760239601135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89856791496277</t>
+    <t xml:space="preserve">2.81760215759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89856767654419</t>
   </si>
   <si>
     <t xml:space="preserve">2.91476082801819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63947820663452</t>
+    <t xml:space="preserve">2.63947796821594</t>
   </si>
   <si>
     <t xml:space="preserve">2.67186427116394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62328505516052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68805742263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70425057411194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60709142684937</t>
+    <t xml:space="preserve">2.62328481674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68805718421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70425033569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60709166526794</t>
   </si>
   <si>
     <t xml:space="preserve">2.59089875221252</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">2.54231929779053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46135354042053</t>
+    <t xml:space="preserve">2.46135377883911</t>
   </si>
   <si>
     <t xml:space="preserve">2.3156156539917</t>
@@ -668,7 +668,7 @@
     <t xml:space="preserve">2.28662443161011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13304495811462</t>
+    <t xml:space="preserve">2.13304471969604</t>
   </si>
   <si>
     <t xml:space="preserve">2.08185195922852</t>
@@ -683,19 +683,19 @@
     <t xml:space="preserve">2.1671736240387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09891653060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26955986022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2183666229248</t>
+    <t xml:space="preserve">2.09891629219055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26956009864807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21836686134338</t>
   </si>
   <si>
     <t xml:space="preserve">2.32075309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55965399742126</t>
+    <t xml:space="preserve">2.55965423583984</t>
   </si>
   <si>
     <t xml:space="preserve">2.54258966445923</t>
@@ -710,19 +710,19 @@
     <t xml:space="preserve">2.62791132926941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61084723472595</t>
+    <t xml:space="preserve">2.61084699630737</t>
   </si>
   <si>
     <t xml:space="preserve">2.64497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59378266334534</t>
+    <t xml:space="preserve">2.59378290176392</t>
   </si>
   <si>
     <t xml:space="preserve">2.69616913795471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71323347091675</t>
+    <t xml:space="preserve">2.71323323249817</t>
   </si>
   <si>
     <t xml:space="preserve">2.44020342826843</t>
@@ -731,7 +731,7 @@
     <t xml:space="preserve">2.4231390953064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47433257102966</t>
+    <t xml:space="preserve">2.47433233261108</t>
   </si>
   <si>
     <t xml:space="preserve">2.15010929107666</t>
@@ -740,58 +740,58 @@
     <t xml:space="preserve">2.33781743049622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30368852615356</t>
+    <t xml:space="preserve">2.30368876457214</t>
   </si>
   <si>
     <t xml:space="preserve">2.25249576568604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23543095588684</t>
+    <t xml:space="preserve">2.23543119430542</t>
   </si>
   <si>
     <t xml:space="preserve">2.37194609642029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38901019096375</t>
+    <t xml:space="preserve">2.38901042938232</t>
   </si>
   <si>
     <t xml:space="preserve">2.20130252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18423819541931</t>
+    <t xml:space="preserve">2.18423795700073</t>
   </si>
   <si>
     <t xml:space="preserve">2.01359415054321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04772353172302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11598062515259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91120839118958</t>
+    <t xml:space="preserve">2.04772329330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11598038673401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91120827198029</t>
   </si>
   <si>
     <t xml:space="preserve">1.87707960605621</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84295105934143</t>
+    <t xml:space="preserve">1.84295117855072</t>
   </si>
   <si>
     <t xml:space="preserve">1.97946560382843</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86001539230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94533705711365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96240162849426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99652993679047</t>
+    <t xml:space="preserve">1.86001515388489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94533693790436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96240139007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99653005599976</t>
   </si>
   <si>
     <t xml:space="preserve">2.81561946868896</t>
@@ -812,16 +812,16 @@
     <t xml:space="preserve">2.6791045665741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74736166000366</t>
+    <t xml:space="preserve">2.74736189842224</t>
   </si>
   <si>
     <t xml:space="preserve">2.832683801651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86681246757507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79855489730835</t>
+    <t xml:space="preserve">2.86681222915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79855513572693</t>
   </si>
   <si>
     <t xml:space="preserve">2.78149080276489</t>
@@ -839,16 +839,16 @@
     <t xml:space="preserve">3.00332736968994</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03745579719543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98626327514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05452060699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07158470153809</t>
+    <t xml:space="preserve">3.03745603561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98626303672791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05452036857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07158493995667</t>
   </si>
   <si>
     <t xml:space="preserve">3.13984251022339</t>
@@ -857,16 +857,16 @@
     <t xml:space="preserve">3.11424589157104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1313099861145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06305241584778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16543889045715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19956755638123</t>
+    <t xml:space="preserve">3.13131022453308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06305265426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16543912887573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1995677947998</t>
   </si>
   <si>
     <t xml:space="preserve">3.15690660476685</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">3.2336962223053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2763569355011</t>
+    <t xml:space="preserve">3.27635717391968</t>
   </si>
   <si>
     <t xml:space="preserve">3.24222850799561</t>
@@ -884,13 +884,13 @@
     <t xml:space="preserve">3.26782488822937</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31048607826233</t>
+    <t xml:space="preserve">3.31048631668091</t>
   </si>
   <si>
     <t xml:space="preserve">3.3446147441864</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32755017280579</t>
+    <t xml:space="preserve">3.32755041122437</t>
   </si>
   <si>
     <t xml:space="preserve">3.28488922119141</t>
@@ -55271,7 +55271,7 @@
     </row>
     <row r="2047">
       <c r="A2047" s="1" t="n">
-        <v>45945.6452777778</v>
+        <v>45945.2916666667</v>
       </c>
       <c r="B2047" t="n">
         <v>5325</v>
@@ -55292,6 +55292,32 @@
         <v>571</v>
       </c>
       <c r="H2047" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2048">
+      <c r="A2048" s="1" t="n">
+        <v>45946.6376041667</v>
+      </c>
+      <c r="B2048" t="n">
+        <v>10711</v>
+      </c>
+      <c r="C2048" t="n">
+        <v>3.27999997138977</v>
+      </c>
+      <c r="D2048" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="E2048" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="F2048" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="G2048" t="s">
+        <v>568</v>
+      </c>
+      <c r="H2048" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -47,22 +47,22 @@
     <t xml:space="preserve">2.96519947052002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88901543617249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98013734817505</t>
+    <t xml:space="preserve">2.88901519775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98013758659363</t>
   </si>
   <si>
     <t xml:space="preserve">2.97266840934753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94578003883362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95773029327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96221137046814</t>
+    <t xml:space="preserve">2.94577980041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95773005485535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9622118473053</t>
   </si>
   <si>
     <t xml:space="preserve">2.9353232383728</t>
@@ -77,19 +77,19 @@
     <t xml:space="preserve">2.98611259460449</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03540802001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.056321144104</t>
+    <t xml:space="preserve">3.03540825843811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05632138252258</t>
   </si>
   <si>
     <t xml:space="preserve">3.05930924415588</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05034637451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98760604858398</t>
+    <t xml:space="preserve">3.05034589767456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98760652542114</t>
   </si>
   <si>
     <t xml:space="preserve">2.95026135444641</t>
@@ -98,19 +98,19 @@
     <t xml:space="preserve">3.01598882675171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01001334190369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02495169639587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0174822807312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03092646598816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99955677986145</t>
+    <t xml:space="preserve">3.01001358032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02495145797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01748251914978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03092694282532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99955654144287</t>
   </si>
   <si>
     <t xml:space="preserve">3.0443708896637</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">2.92785429954529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90843486785889</t>
+    <t xml:space="preserve">2.90843510627747</t>
   </si>
   <si>
     <t xml:space="preserve">2.89648461341858</t>
@@ -134,25 +134,25 @@
     <t xml:space="preserve">2.91889142990112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9159038066864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92038536071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90544748306274</t>
+    <t xml:space="preserve">2.91590404510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92038512229919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90544724464417</t>
   </si>
   <si>
     <t xml:space="preserve">2.90992856025696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9233729839325</t>
+    <t xml:space="preserve">2.92337274551392</t>
   </si>
   <si>
     <t xml:space="preserve">2.83822584152222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86063313484192</t>
+    <t xml:space="preserve">2.8606333732605</t>
   </si>
   <si>
     <t xml:space="preserve">2.82627558708191</t>
@@ -161,28 +161,28 @@
     <t xml:space="preserve">2.77996754646301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84569501876831</t>
+    <t xml:space="preserve">2.84569525718689</t>
   </si>
   <si>
     <t xml:space="preserve">2.86810207366943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88303971290588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79639959335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87557125091553</t>
+    <t xml:space="preserve">2.88304018974304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79639983177185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87557101249695</t>
   </si>
   <si>
     <t xml:space="preserve">2.89797806739807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80088114738464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74262237548828</t>
+    <t xml:space="preserve">2.80088090896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74262261390686</t>
   </si>
   <si>
     <t xml:space="preserve">2.82179427146912</t>
@@ -191,7 +191,7 @@
     <t xml:space="preserve">2.75009155273438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76353597640991</t>
+    <t xml:space="preserve">2.76353573799133</t>
   </si>
   <si>
     <t xml:space="preserve">2.77847385406494</t>
@@ -218,25 +218,25 @@
     <t xml:space="preserve">2.5693416595459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61415553092957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65896964073181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68884563446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70378351211548</t>
+    <t xml:space="preserve">2.61415600776672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65896940231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68884539604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70378375053406</t>
   </si>
   <si>
     <t xml:space="preserve">2.77100491523743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81581902503967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73365950584412</t>
+    <t xml:space="preserve">2.81581878662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7336597442627</t>
   </si>
   <si>
     <t xml:space="preserve">2.66643857955933</t>
@@ -245,13 +245,13 @@
     <t xml:space="preserve">2.68137645721436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74112868309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72619104385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8307569026947</t>
+    <t xml:space="preserve">2.74112892150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72619080543518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83075714111328</t>
   </si>
   <si>
     <t xml:space="preserve">2.893150806427</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">2.69871878623962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83870959281921</t>
+    <t xml:space="preserve">2.83870983123779</t>
   </si>
   <si>
     <t xml:space="preserve">2.93203687667847</t>
@@ -269,109 +269,109 @@
     <t xml:space="preserve">2.87759590148926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83093237876892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81537795066833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84648680686951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79982328414917</t>
+    <t xml:space="preserve">2.8309326171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81537747383118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84648704528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79982304573059</t>
   </si>
   <si>
     <t xml:space="preserve">2.73760485649109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76093673706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80760025978088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00980973243713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9553689956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90870499610901</t>
+    <t xml:space="preserve">2.76093649864197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80760073661804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00980997085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95536875724792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90870523452759</t>
   </si>
   <si>
     <t xml:space="preserve">2.88537359237671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82315516471863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86204171180725</t>
+    <t xml:space="preserve">2.82315492630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86204147338867</t>
   </si>
   <si>
     <t xml:space="preserve">3.00203275680542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91648268699646</t>
+    <t xml:space="preserve">2.91648244857788</t>
   </si>
   <si>
     <t xml:space="preserve">2.85426425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72982740402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68316411972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72205066680908</t>
+    <t xml:space="preserve">2.72982788085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68316388130188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7220504283905</t>
   </si>
   <si>
     <t xml:space="preserve">2.75315976142883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70649576187134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93981456756592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99425530433655</t>
+    <t xml:space="preserve">2.70649552345276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93981432914734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99425506591797</t>
   </si>
   <si>
     <t xml:space="preserve">2.9787003993988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86981892585754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94759154319763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98647809028625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63650012016296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55095028877258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51984119415283</t>
+    <t xml:space="preserve">2.86981868743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94759178161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98647785186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63650035858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55094981193542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51984071731567</t>
   </si>
   <si>
     <t xml:space="preserve">2.41095876693726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34096312522888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34874105453491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36429524421692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2554132938385</t>
+    <t xml:space="preserve">2.34096336364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34874081611633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36429500579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25541305541992</t>
   </si>
   <si>
     <t xml:space="preserve">2.24763607978821</t>
@@ -386,13 +386,13 @@
     <t xml:space="preserve">2.18541765213013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27874493598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26319026947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21652698516846</t>
+    <t xml:space="preserve">2.27874517440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26319050788879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2165265083313</t>
   </si>
   <si>
     <t xml:space="preserve">2.06875848770142</t>
@@ -413,34 +413,34 @@
     <t xml:space="preserve">2.22430396080017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35651779174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48873209953308</t>
+    <t xml:space="preserve">2.35651803016663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48873162269592</t>
   </si>
   <si>
     <t xml:space="preserve">2.52761793136597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43429088592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44206809997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5587272644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44984555244446</t>
+    <t xml:space="preserve">2.43429064750671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44206786155701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55872750282288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44984531402588</t>
   </si>
   <si>
     <t xml:space="preserve">2.37207221984863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33318614959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29429960250854</t>
+    <t xml:space="preserve">2.33318591117859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29429984092712</t>
   </si>
   <si>
     <t xml:space="preserve">2.3798496723175</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">2.71427297592163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58205938339233</t>
+    <t xml:space="preserve">2.58205914497375</t>
   </si>
   <si>
     <t xml:space="preserve">2.62872290611267</t>
@@ -458,67 +458,67 @@
     <t xml:space="preserve">2.65983200073242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57428169250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67538666725159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64427757263184</t>
+    <t xml:space="preserve">2.57428193092346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67538714408875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64427781105042</t>
   </si>
   <si>
     <t xml:space="preserve">2.69094133377075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76871418952942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90092802047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96314597129822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92425990104675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97092366218567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01758766174316</t>
+    <t xml:space="preserve">2.76871395111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90092778205872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9631462097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92425966262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97092342376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01758742332458</t>
   </si>
   <si>
     <t xml:space="preserve">3.04869651794434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03314208984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06425094604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07980537414551</t>
+    <t xml:space="preserve">3.03314185142517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0642511844635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07980561256409</t>
   </si>
   <si>
     <t xml:space="preserve">3.06049919128418</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02811288833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01191997528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1090784072876</t>
+    <t xml:space="preserve">3.0281126499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01191973686218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10907816886902</t>
   </si>
   <si>
     <t xml:space="preserve">3.0928852558136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1252715587616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0766921043396</t>
+    <t xml:space="preserve">3.12527132034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07669186592102</t>
   </si>
   <si>
     <t xml:space="preserve">2.99572658538818</t>
@@ -527,16 +527,16 @@
     <t xml:space="preserve">3.30339574813843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41674709320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35197496414185</t>
+    <t xml:space="preserve">3.41674733161926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35197520256042</t>
   </si>
   <si>
     <t xml:space="preserve">3.33578181266785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36816811561584</t>
+    <t xml:space="preserve">3.36816787719727</t>
   </si>
   <si>
     <t xml:space="preserve">3.23862338066101</t>
@@ -548,16 +548,16 @@
     <t xml:space="preserve">3.27100944519043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28720283508301</t>
+    <t xml:space="preserve">3.28720259666443</t>
   </si>
   <si>
     <t xml:space="preserve">3.22243022918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17385077476501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20623707771301</t>
+    <t xml:space="preserve">3.17385101318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20623731613159</t>
   </si>
   <si>
     <t xml:space="preserve">3.14146494865417</t>
@@ -566,43 +566,43 @@
     <t xml:space="preserve">3.40055441856384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.497713804245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38436150550842</t>
+    <t xml:space="preserve">3.49771356582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38436126708984</t>
   </si>
   <si>
     <t xml:space="preserve">3.25481653213501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19004392623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96334052085876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97953367233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80140900611877</t>
+    <t xml:space="preserve">3.19004416465759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96334028244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97953343391418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80140924453735</t>
   </si>
   <si>
     <t xml:space="preserve">2.88237452507019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86618161201477</t>
+    <t xml:space="preserve">2.86618185043335</t>
   </si>
   <si>
     <t xml:space="preserve">2.84998846054077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78521609306335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75283002853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72044324874878</t>
+    <t xml:space="preserve">2.78521633148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75283026695251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72044348716736</t>
   </si>
   <si>
     <t xml:space="preserve">2.83379554748535</t>
@@ -611,31 +611,31 @@
     <t xml:space="preserve">2.76902294158936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73663663864136</t>
+    <t xml:space="preserve">2.73663687705994</t>
   </si>
   <si>
     <t xml:space="preserve">2.81760215759277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89856767654419</t>
+    <t xml:space="preserve">2.89856791496277</t>
   </si>
   <si>
     <t xml:space="preserve">2.91476082801819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63947796821594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67186427116394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62328481674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68805718421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70425033569336</t>
+    <t xml:space="preserve">2.63947820663452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67186450958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62328457832336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68805742263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70425057411194</t>
   </si>
   <si>
     <t xml:space="preserve">2.60709166526794</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">2.54231929779053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46135377883911</t>
+    <t xml:space="preserve">2.46135354042053</t>
   </si>
   <si>
     <t xml:space="preserve">2.3156156539917</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">2.40607476234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28662443161011</t>
+    <t xml:space="preserve">2.28662419319153</t>
   </si>
   <si>
     <t xml:space="preserve">2.13304471969604</t>
@@ -686,22 +686,22 @@
     <t xml:space="preserve">2.09891629219055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26956009864807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21836686134338</t>
+    <t xml:space="preserve">2.26955986022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2183666229248</t>
   </si>
   <si>
     <t xml:space="preserve">2.32075309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55965423583984</t>
+    <t xml:space="preserve">2.55965399742126</t>
   </si>
   <si>
     <t xml:space="preserve">2.54258966445923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45726799964905</t>
+    <t xml:space="preserve">2.45726823806763</t>
   </si>
   <si>
     <t xml:space="preserve">2.57671856880188</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">2.64497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59378290176392</t>
+    <t xml:space="preserve">2.59378266334534</t>
   </si>
   <si>
     <t xml:space="preserve">2.69616913795471</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">2.30368876457214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25249576568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23543119430542</t>
+    <t xml:space="preserve">2.25249552726746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23543095588684</t>
   </si>
   <si>
     <t xml:space="preserve">2.37194609642029</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">2.38901042938232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20130252838135</t>
+    <t xml:space="preserve">2.20130228996277</t>
   </si>
   <si>
     <t xml:space="preserve">2.18423795700073</t>
@@ -767,25 +767,25 @@
     <t xml:space="preserve">2.04772329330444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11598038673401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91120827198029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87707960605621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84295117855072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97946560382843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86001515388489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94533693790436</t>
+    <t xml:space="preserve">2.11598062515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91120839118958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8770797252655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84295094013214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97946572303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86001527309418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94533705711365</t>
   </si>
   <si>
     <t xml:space="preserve">1.96240139007568</t>
@@ -794,19 +794,19 @@
     <t xml:space="preserve">1.99653005599976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81561946868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90094137191772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88387680053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76442646980286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73029780387878</t>
+    <t xml:space="preserve">2.81561970710754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9009416103363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88387703895569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76442623138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73029756546021</t>
   </si>
   <si>
     <t xml:space="preserve">2.6791045665741</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">2.832683801651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86681222915649</t>
+    <t xml:space="preserve">2.86681246757507</t>
   </si>
   <si>
     <t xml:space="preserve">2.79855513572693</t>
@@ -827,13 +827,13 @@
     <t xml:space="preserve">2.78149080276489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9350700378418</t>
+    <t xml:space="preserve">2.93507027626038</t>
   </si>
   <si>
     <t xml:space="preserve">2.96919870376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02039170265198</t>
+    <t xml:space="preserve">3.02039194107056</t>
   </si>
   <si>
     <t xml:space="preserve">3.00332736968994</t>
@@ -842,13 +842,13 @@
     <t xml:space="preserve">3.03745603561401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98626303672791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05452036857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07158493995667</t>
+    <t xml:space="preserve">2.98626327514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05452060699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07158470153809</t>
   </si>
   <si>
     <t xml:space="preserve">3.13984251022339</t>
@@ -857,16 +857,16 @@
     <t xml:space="preserve">3.11424589157104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13131022453308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06305265426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16543912887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1995677947998</t>
+    <t xml:space="preserve">3.1313099861145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06305241584778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16543889045715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19956755638123</t>
   </si>
   <si>
     <t xml:space="preserve">3.15690660476685</t>
@@ -875,19 +875,19 @@
     <t xml:space="preserve">3.2336962223053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27635717391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24222850799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26782488822937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31048631668091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3446147441864</t>
+    <t xml:space="preserve">3.2763569355011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24222826957703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26782464981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31048607826233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34461498260498</t>
   </si>
   <si>
     <t xml:space="preserve">3.32755041122437</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">3.28488922119141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18250322341919</t>
+    <t xml:space="preserve">3.18250298500061</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342150688171</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">3.33710074424744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32836508750916</t>
+    <t xml:space="preserve">3.32836484909058</t>
   </si>
   <si>
     <t xml:space="preserve">3.24974226951599</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">3.21479892730713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17111968994141</t>
+    <t xml:space="preserve">3.17111945152283</t>
   </si>
   <si>
     <t xml:space="preserve">3.26721382141113</t>
@@ -929,16 +929,16 @@
     <t xml:space="preserve">3.36330842971802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49434638023376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58170533180237</t>
+    <t xml:space="preserve">3.49434661865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58170509338379</t>
   </si>
   <si>
     <t xml:space="preserve">3.56423330307007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59044098854065</t>
+    <t xml:space="preserve">3.59044122695923</t>
   </si>
   <si>
     <t xml:space="preserve">3.5030825138092</t>
@@ -959,13 +959,13 @@
     <t xml:space="preserve">3.7476863861084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69527149200439</t>
+    <t xml:space="preserve">3.69527125358582</t>
   </si>
   <si>
     <t xml:space="preserve">3.66906380653381</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60791277885437</t>
+    <t xml:space="preserve">3.60791301727295</t>
   </si>
   <si>
     <t xml:space="preserve">3.55549788475037</t>
@@ -989,16 +989,16 @@
     <t xml:space="preserve">3.57296967506409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53802585601807</t>
+    <t xml:space="preserve">3.53802609443665</t>
   </si>
   <si>
     <t xml:space="preserve">3.3458366394043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38951635360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42445969581604</t>
+    <t xml:space="preserve">3.3895161151886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42445993423462</t>
   </si>
   <si>
     <t xml:space="preserve">3.45066738128662</t>
@@ -1010,13 +1010,13 @@
     <t xml:space="preserve">3.48561072349548</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40698790550232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35457253456116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4594030380249</t>
+    <t xml:space="preserve">3.4069881439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35457229614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45940327644348</t>
   </si>
   <si>
     <t xml:space="preserve">3.52928996086121</t>
@@ -1025,13 +1025,13 @@
     <t xml:space="preserve">3.46813893318176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47687458992004</t>
+    <t xml:space="preserve">3.47687482833862</t>
   </si>
   <si>
     <t xml:space="preserve">3.79136610031128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72147917747498</t>
+    <t xml:space="preserve">3.72147941589355</t>
   </si>
   <si>
     <t xml:space="preserve">3.87872457504272</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">4.31551790237427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35046100616455</t>
+    <t xml:space="preserve">4.35046148300171</t>
   </si>
   <si>
     <t xml:space="preserve">4.18447971343994</t>
@@ -1070,22 +1070,22 @@
     <t xml:space="preserve">3.93113970756531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08838510513306</t>
+    <t xml:space="preserve">4.08838558197021</t>
   </si>
   <si>
     <t xml:space="preserve">4.07091379165649</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12332820892334</t>
+    <t xml:space="preserve">4.1233286857605</t>
   </si>
   <si>
     <t xml:space="preserve">4.00102663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00976276397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93987560272217</t>
+    <t xml:space="preserve">4.00976324081421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93987584114075</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">4.2106876373291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29804658889771</t>
+    <t xml:space="preserve">4.29804611206055</t>
   </si>
   <si>
     <t xml:space="preserve">4.28930997848511</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">4.14953660964966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16700839996338</t>
+    <t xml:space="preserve">4.16700792312622</t>
   </si>
   <si>
     <t xml:space="preserve">4.11459302902222</t>
@@ -1118,19 +1118,19 @@
     <t xml:space="preserve">4.06217765808105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78263020515442</t>
+    <t xml:space="preserve">3.78262996673584</t>
   </si>
   <si>
     <t xml:space="preserve">3.80010175704956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82630968093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.835045337677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84378123283386</t>
+    <t xml:space="preserve">3.8263099193573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83504557609558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84378147125244</t>
   </si>
   <si>
     <t xml:space="preserve">3.77389454841614</t>
@@ -1139,19 +1139,19 @@
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734763145447</t>
+    <t xml:space="preserve">3.95734786987305</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.861252784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76515817642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8175733089447</t>
+    <t xml:space="preserve">3.86125302314758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76515793800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81757354736328</t>
   </si>
   <si>
     <t xml:space="preserve">3.64285612106323</t>
@@ -1169,25 +1169,25 @@
     <t xml:space="preserve">3.71274328231812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92240357398987</t>
+    <t xml:space="preserve">3.92240381240845</t>
   </si>
   <si>
     <t xml:space="preserve">3.61664843559265</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39825224876404</t>
+    <t xml:space="preserve">3.39825201034546</t>
   </si>
   <si>
     <t xml:space="preserve">3.23227047920227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05755352973938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97019457817078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95272278785706</t>
+    <t xml:space="preserve">3.0575532913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97019481658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95272302627563</t>
   </si>
   <si>
     <t xml:space="preserve">2.91777944564819</t>
@@ -1196,22 +1196,22 @@
     <t xml:space="preserve">2.90904355049133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37204432487488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38077998161316</t>
+    <t xml:space="preserve">3.3720440864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38078022003174</t>
   </si>
   <si>
     <t xml:space="preserve">3.41572380065918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31962919235229</t>
+    <t xml:space="preserve">3.31962895393372</t>
   </si>
   <si>
     <t xml:space="preserve">3.27594995498657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28468585014343</t>
+    <t xml:space="preserve">3.28468561172485</t>
   </si>
   <si>
     <t xml:space="preserve">3.50245499610901</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">3.32098078727722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26653838157654</t>
+    <t xml:space="preserve">3.26653814315796</t>
   </si>
   <si>
     <t xml:space="preserve">3.39357042312622</t>
@@ -1256,7 +1256,7 @@
     <t xml:space="preserve">3.23024344444275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19394850730896</t>
+    <t xml:space="preserve">3.19394874572754</t>
   </si>
   <si>
     <t xml:space="preserve">3.25746440887451</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">3.2211697101593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10321164131165</t>
+    <t xml:space="preserve">3.10321140289307</t>
   </si>
   <si>
     <t xml:space="preserve">2.99432682991028</t>
@@ -1283,13 +1283,13 @@
     <t xml:space="preserve">2.95803189277649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85822129249573</t>
+    <t xml:space="preserve">2.85822105407715</t>
   </si>
   <si>
     <t xml:space="preserve">2.89451599121094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86729502677917</t>
+    <t xml:space="preserve">2.8672947883606</t>
   </si>
   <si>
     <t xml:space="preserve">2.81285238265991</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">2.75841021537781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7039680480957</t>
+    <t xml:space="preserve">2.70396780967712</t>
   </si>
   <si>
     <t xml:space="preserve">2.72211527824402</t>
@@ -1310,16 +1310,16 @@
     <t xml:space="preserve">2.64952564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79470491409302</t>
+    <t xml:space="preserve">2.7947051525116</t>
   </si>
   <si>
     <t xml:space="preserve">2.92173719406128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05784296989441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02154779434204</t>
+    <t xml:space="preserve">3.05784273147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02154803276062</t>
   </si>
   <si>
     <t xml:space="preserve">3.13950634002686</t>
@@ -1349,46 +1349,46 @@
     <t xml:space="preserve">3.08506417274475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01247406005859</t>
+    <t xml:space="preserve">3.01247429847717</t>
   </si>
   <si>
     <t xml:space="preserve">2.88544225692749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77655744552612</t>
+    <t xml:space="preserve">2.7765576839447</t>
   </si>
   <si>
     <t xml:space="preserve">2.71304154396057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63137817382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68582057952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66767311096191</t>
+    <t xml:space="preserve">2.6313784122467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68582034111023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66767287254333</t>
   </si>
   <si>
     <t xml:space="preserve">2.55878829956055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52249360084534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67674684524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64045190811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87636876106262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83099961280823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6041567325592</t>
+    <t xml:space="preserve">2.52249336242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67674660682678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64045214653015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87636852264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83099985122681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60415697097778</t>
   </si>
   <si>
     <t xml:space="preserve">2.73118901252747</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">2.91266345977783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12135910987854</t>
+    <t xml:space="preserve">3.12135887145996</t>
   </si>
   <si>
     <t xml:space="preserve">3.0759904384613</t>
@@ -1424,46 +1424,46 @@
     <t xml:space="preserve">3.0941379070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38449668884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41171789169312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37542295455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42079162597656</t>
+    <t xml:space="preserve">3.38449692726135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41171765327454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37542319297791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42079138755798</t>
   </si>
   <si>
     <t xml:space="preserve">3.43893885612488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36634922027588</t>
+    <t xml:space="preserve">3.36634945869446</t>
   </si>
   <si>
     <t xml:space="preserve">3.35727572441101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20302224159241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27561211585999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29375982284546</t>
+    <t xml:space="preserve">3.20302248001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27561187744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29375958442688</t>
   </si>
   <si>
     <t xml:space="preserve">3.1667275428772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11228537559509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78563117980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84007358551025</t>
+    <t xml:space="preserve">3.11228513717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78563141822815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84007382392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.82192611694336</t>
@@ -55297,7 +55297,7 @@
     </row>
     <row r="2048">
       <c r="A2048" s="1" t="n">
-        <v>45946.6376041667</v>
+        <v>45946.2916666667</v>
       </c>
       <c r="B2048" t="n">
         <v>10711</v>
@@ -55318,6 +55318,32 @@
         <v>568</v>
       </c>
       <c r="H2048" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2049">
+      <c r="A2049" s="1" t="n">
+        <v>45947.520150463</v>
+      </c>
+      <c r="B2049" t="n">
+        <v>4984</v>
+      </c>
+      <c r="C2049" t="n">
+        <v>3.22000002861023</v>
+      </c>
+      <c r="D2049" t="n">
+        <v>3.16000008583069</v>
+      </c>
+      <c r="E2049" t="n">
+        <v>3.22000002861023</v>
+      </c>
+      <c r="F2049" t="n">
+        <v>3.16000008583069</v>
+      </c>
+      <c r="G2049" t="s">
+        <v>574</v>
+      </c>
+      <c r="H2049" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -44,19 +44,19 @@
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519947052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88901519775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98013758659363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97266840934753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94577980041504</t>
+    <t xml:space="preserve">2.96519923210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88901543617249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98013734817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97266817092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94578003883362</t>
   </si>
   <si>
     <t xml:space="preserve">2.95773005485535</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">2.9622118473053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9353232383728</t>
+    <t xml:space="preserve">2.93532299995422</t>
   </si>
   <si>
     <t xml:space="preserve">2.91291618347168</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">2.98611259460449</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03540825843811</t>
+    <t xml:space="preserve">3.03540802001953</t>
   </si>
   <si>
     <t xml:space="preserve">3.05632138252258</t>
@@ -86,58 +86,58 @@
     <t xml:space="preserve">3.05930924415588</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05034589767456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98760652542114</t>
+    <t xml:space="preserve">3.05034637451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98760628700256</t>
   </si>
   <si>
     <t xml:space="preserve">2.95026135444641</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01598882675171</t>
+    <t xml:space="preserve">3.01598858833313</t>
   </si>
   <si>
     <t xml:space="preserve">3.01001358032227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02495145797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01748251914978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03092694282532</t>
+    <t xml:space="preserve">3.02495121955872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0174822807312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03092646598816</t>
   </si>
   <si>
     <t xml:space="preserve">2.99955654144287</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0443708896637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.959223985672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00254440307617</t>
+    <t xml:space="preserve">3.04437112808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95922422409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00254464149475</t>
   </si>
   <si>
     <t xml:space="preserve">2.92785429954529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90843510627747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89648461341858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91889142990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91590404510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92038512229919</t>
+    <t xml:space="preserve">2.90843462944031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89648485183716</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91889119148254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9159038066864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92038536071777</t>
   </si>
   <si>
     <t xml:space="preserve">2.90544724464417</t>
@@ -146,37 +146,37 @@
     <t xml:space="preserve">2.90992856025696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92337274551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83822584152222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8606333732605</t>
+    <t xml:space="preserve">2.9233729839325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8382260799408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86063289642334</t>
   </si>
   <si>
     <t xml:space="preserve">2.82627558708191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77996754646301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84569525718689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86810207366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88304018974304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79639983177185</t>
+    <t xml:space="preserve">2.77996730804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84569478034973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86810183525085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88303995132446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79639935493469</t>
   </si>
   <si>
     <t xml:space="preserve">2.87557101249695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89797806739807</t>
+    <t xml:space="preserve">2.89797830581665</t>
   </si>
   <si>
     <t xml:space="preserve">2.80088090896606</t>
@@ -191,16 +191,16 @@
     <t xml:space="preserve">2.75009155273438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76353573799133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77847385406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78594303131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79341173171997</t>
+    <t xml:space="preserve">2.76353597640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77847409248352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78594279289246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79341197013855</t>
   </si>
   <si>
     <t xml:space="preserve">2.69631481170654</t>
@@ -212,19 +212,19 @@
     <t xml:space="preserve">2.62162446975708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53946542739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5693416595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61415600776672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65896940231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68884539604187</t>
+    <t xml:space="preserve">2.53946566581726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56934142112732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61415576934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65896964073181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68884563446045</t>
   </si>
   <si>
     <t xml:space="preserve">2.70378375053406</t>
@@ -233,22 +233,22 @@
     <t xml:space="preserve">2.77100491523743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81581878662109</t>
+    <t xml:space="preserve">2.81581902503967</t>
   </si>
   <si>
     <t xml:space="preserve">2.7336597442627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66643857955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68137645721436</t>
+    <t xml:space="preserve">2.66643881797791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68137669563293</t>
   </si>
   <si>
     <t xml:space="preserve">2.74112892150879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72619080543518</t>
+    <t xml:space="preserve">2.72619104385376</t>
   </si>
   <si>
     <t xml:space="preserve">2.83075714111328</t>
@@ -257,25 +257,25 @@
     <t xml:space="preserve">2.893150806427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69871878623962</t>
+    <t xml:space="preserve">2.69871854782104</t>
   </si>
   <si>
     <t xml:space="preserve">2.83870983123779</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93203687667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87759590148926</t>
+    <t xml:space="preserve">2.93203711509705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87759613990784</t>
   </si>
   <si>
     <t xml:space="preserve">2.8309326171875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81537747383118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84648704528809</t>
+    <t xml:space="preserve">2.81537771224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84648680686951</t>
   </si>
   <si>
     <t xml:space="preserve">2.79982304573059</t>
@@ -284,31 +284,31 @@
     <t xml:space="preserve">2.73760485649109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76093649864197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80760073661804</t>
+    <t xml:space="preserve">2.76093697547913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80760049819946</t>
   </si>
   <si>
     <t xml:space="preserve">3.00980997085571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95536875724792</t>
+    <t xml:space="preserve">2.9553689956665</t>
   </si>
   <si>
     <t xml:space="preserve">2.90870523452759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88537359237671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82315492630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86204147338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00203275680542</t>
+    <t xml:space="preserve">2.88537335395813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82315516471863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86204171180725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00203251838684</t>
   </si>
   <si>
     <t xml:space="preserve">2.91648244857788</t>
@@ -317,28 +317,28 @@
     <t xml:space="preserve">2.85426425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72982788085938</t>
+    <t xml:space="preserve">2.7298276424408</t>
   </si>
   <si>
     <t xml:space="preserve">2.68316388130188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7220504283905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75315976142883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70649552345276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93981432914734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99425506591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9787003993988</t>
+    <t xml:space="preserve">2.72205066680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75315952301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70649576187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93981456756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99425530433655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97870063781738</t>
   </si>
   <si>
     <t xml:space="preserve">2.86981868743896</t>
@@ -350,13 +350,13 @@
     <t xml:space="preserve">2.98647785186768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63650035858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55094981193542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51984071731567</t>
+    <t xml:space="preserve">2.63650012016296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.550950050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51984095573425</t>
   </si>
   <si>
     <t xml:space="preserve">2.41095876693726</t>
@@ -368,10 +368,10 @@
     <t xml:space="preserve">2.34874081611633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36429500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25541305541992</t>
+    <t xml:space="preserve">2.36429524421692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25541353225708</t>
   </si>
   <si>
     <t xml:space="preserve">2.24763607978821</t>
@@ -383,28 +383,28 @@
     <t xml:space="preserve">2.23208117485046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18541765213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27874517440796</t>
+    <t xml:space="preserve">2.18541741371155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27874493598938</t>
   </si>
   <si>
     <t xml:space="preserve">2.26319050788879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2165265083313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06875848770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14653134346008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10764479637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1543083190918</t>
+    <t xml:space="preserve">2.21652674674988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06875824928284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1465311050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10764503479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15430808067322</t>
   </si>
   <si>
     <t xml:space="preserve">2.17764019966125</t>
@@ -413,40 +413,40 @@
     <t xml:space="preserve">2.22430396080017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35651803016663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48873162269592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52761793136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43429064750671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44206786155701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55872750282288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44984531402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37207221984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33318591117859</t>
+    <t xml:space="preserve">2.35651779174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4887318611145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52761816978455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43429088592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44206809997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5587272644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44984555244446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37207269668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33318614959717</t>
   </si>
   <si>
     <t xml:space="preserve">2.29429984092712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3798496723175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71427297592163</t>
+    <t xml:space="preserve">2.37984991073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71427321434021</t>
   </si>
   <si>
     <t xml:space="preserve">2.58205914497375</t>
@@ -455,19 +455,19 @@
     <t xml:space="preserve">2.62872290611267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65983200073242</t>
+    <t xml:space="preserve">2.659832239151</t>
   </si>
   <si>
     <t xml:space="preserve">2.57428193092346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67538714408875</t>
+    <t xml:space="preserve">2.67538666725159</t>
   </si>
   <si>
     <t xml:space="preserve">2.64427781105042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69094133377075</t>
+    <t xml:space="preserve">2.69094109535217</t>
   </si>
   <si>
     <t xml:space="preserve">2.76871395111084</t>
@@ -476,10 +476,10 @@
     <t xml:space="preserve">2.90092778205872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9631462097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92425966262817</t>
+    <t xml:space="preserve">2.96314597129822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92425990104675</t>
   </si>
   <si>
     <t xml:space="preserve">2.97092342376709</t>
@@ -494,46 +494,46 @@
     <t xml:space="preserve">3.03314185142517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0642511844635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07980561256409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06049919128418</t>
+    <t xml:space="preserve">3.06425094604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07980537414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0604989528656</t>
   </si>
   <si>
     <t xml:space="preserve">3.0281126499176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01191973686218</t>
+    <t xml:space="preserve">3.0119194984436</t>
   </si>
   <si>
     <t xml:space="preserve">3.10907816886902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0928852558136</t>
+    <t xml:space="preserve">3.09288501739502</t>
   </si>
   <si>
     <t xml:space="preserve">3.12527132034302</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07669186592102</t>
+    <t xml:space="preserve">3.0766921043396</t>
   </si>
   <si>
     <t xml:space="preserve">2.99572658538818</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30339574813843</t>
+    <t xml:space="preserve">3.30339550971985</t>
   </si>
   <si>
     <t xml:space="preserve">3.41674733161926</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35197520256042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33578181266785</t>
+    <t xml:space="preserve">3.35197496414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33578157424927</t>
   </si>
   <si>
     <t xml:space="preserve">3.36816787719727</t>
@@ -551,31 +551,31 @@
     <t xml:space="preserve">3.28720259666443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22243022918701</t>
+    <t xml:space="preserve">3.22242999076843</t>
   </si>
   <si>
     <t xml:space="preserve">3.17385101318359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20623731613159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14146494865417</t>
+    <t xml:space="preserve">3.20623683929443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1414647102356</t>
   </si>
   <si>
     <t xml:space="preserve">3.40055441856384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49771356582642</t>
+    <t xml:space="preserve">3.49771332740784</t>
   </si>
   <si>
     <t xml:space="preserve">3.38436126708984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25481653213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19004416465759</t>
+    <t xml:space="preserve">3.25481629371643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19004392623901</t>
   </si>
   <si>
     <t xml:space="preserve">2.96334028244019</t>
@@ -587,19 +587,19 @@
     <t xml:space="preserve">2.80140924453735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88237452507019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86618185043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84998846054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78521633148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75283026695251</t>
+    <t xml:space="preserve">2.88237476348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86618161201477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84998822212219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78521609306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75283002853394</t>
   </si>
   <si>
     <t xml:space="preserve">2.72044348716736</t>
@@ -608,16 +608,16 @@
     <t xml:space="preserve">2.83379554748535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76902294158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73663687705994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81760215759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89856791496277</t>
+    <t xml:space="preserve">2.76902270317078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73663663864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81760239601135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89856767654419</t>
   </si>
   <si>
     <t xml:space="preserve">2.91476082801819</t>
@@ -626,10 +626,10 @@
     <t xml:space="preserve">2.63947820663452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67186450958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62328457832336</t>
+    <t xml:space="preserve">2.67186427116394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62328481674194</t>
   </si>
   <si>
     <t xml:space="preserve">2.68805742263794</t>
@@ -650,13 +650,13 @@
     <t xml:space="preserve">2.54231929779053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46135354042053</t>
+    <t xml:space="preserve">2.46135377883911</t>
   </si>
   <si>
     <t xml:space="preserve">2.3156156539917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2994225025177</t>
+    <t xml:space="preserve">2.29942226409912</t>
   </si>
   <si>
     <t xml:space="preserve">2.35488176345825</t>
@@ -665,10 +665,10 @@
     <t xml:space="preserve">2.40607476234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28662419319153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13304471969604</t>
+    <t xml:space="preserve">2.28662443161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13304495811462</t>
   </si>
   <si>
     <t xml:space="preserve">2.08185195922852</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">2.1671736240387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09891629219055</t>
+    <t xml:space="preserve">2.09891653060913</t>
   </si>
   <si>
     <t xml:space="preserve">2.26955986022949</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">2.54258966445923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45726823806763</t>
+    <t xml:space="preserve">2.45726799964905</t>
   </si>
   <si>
     <t xml:space="preserve">2.57671856880188</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">2.62791132926941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61084699630737</t>
+    <t xml:space="preserve">2.61084723472595</t>
   </si>
   <si>
     <t xml:space="preserve">2.64497566223145</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">2.69616913795471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71323323249817</t>
+    <t xml:space="preserve">2.71323347091675</t>
   </si>
   <si>
     <t xml:space="preserve">2.44020342826843</t>
@@ -731,7 +731,7 @@
     <t xml:space="preserve">2.4231390953064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47433233261108</t>
+    <t xml:space="preserve">2.47433257102966</t>
   </si>
   <si>
     <t xml:space="preserve">2.15010929107666</t>
@@ -740,10 +740,10 @@
     <t xml:space="preserve">2.33781743049622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30368876457214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25249552726746</t>
+    <t xml:space="preserve">2.30368852615356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25249576568604</t>
   </si>
   <si>
     <t xml:space="preserve">2.23543095588684</t>
@@ -752,19 +752,19 @@
     <t xml:space="preserve">2.37194609642029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38901042938232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20130228996277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18423795700073</t>
+    <t xml:space="preserve">2.38901019096375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20130252838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18423819541931</t>
   </si>
   <si>
     <t xml:space="preserve">2.01359415054321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04772329330444</t>
+    <t xml:space="preserve">2.04772353172302</t>
   </si>
   <si>
     <t xml:space="preserve">2.11598062515259</t>
@@ -773,46 +773,46 @@
     <t xml:space="preserve">1.91120839118958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8770797252655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84295094013214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97946572303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86001527309418</t>
+    <t xml:space="preserve">1.87707960605621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84295105934143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97946560382843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86001539230347</t>
   </si>
   <si>
     <t xml:space="preserve">1.94533705711365</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96240139007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99653005599976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81561970710754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9009416103363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88387703895569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76442623138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73029756546021</t>
+    <t xml:space="preserve">1.96240162849426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99652993679047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81561946868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90094137191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88387680053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76442646980286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73029780387878</t>
   </si>
   <si>
     <t xml:space="preserve">2.6791045665741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74736189842224</t>
+    <t xml:space="preserve">2.74736166000366</t>
   </si>
   <si>
     <t xml:space="preserve">2.832683801651</t>
@@ -821,25 +821,25 @@
     <t xml:space="preserve">2.86681246757507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79855513572693</t>
+    <t xml:space="preserve">2.79855489730835</t>
   </si>
   <si>
     <t xml:space="preserve">2.78149080276489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93507027626038</t>
+    <t xml:space="preserve">2.9350700378418</t>
   </si>
   <si>
     <t xml:space="preserve">2.96919870376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02039194107056</t>
+    <t xml:space="preserve">3.02039170265198</t>
   </si>
   <si>
     <t xml:space="preserve">3.00332736968994</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03745603561401</t>
+    <t xml:space="preserve">3.03745579719543</t>
   </si>
   <si>
     <t xml:space="preserve">2.98626327514648</t>
@@ -878,25 +878,25 @@
     <t xml:space="preserve">3.2763569355011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24222826957703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26782464981079</t>
+    <t xml:space="preserve">3.24222850799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26782488822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.31048607826233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34461498260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32755041122437</t>
+    <t xml:space="preserve">3.3446147441864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32755017280579</t>
   </si>
   <si>
     <t xml:space="preserve">3.28488922119141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18250298500061</t>
+    <t xml:space="preserve">3.18250322341919</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342150688171</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">3.33710074424744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32836484909058</t>
+    <t xml:space="preserve">3.32836508750916</t>
   </si>
   <si>
     <t xml:space="preserve">3.24974226951599</t>
@@ -920,7 +920,7 @@
     <t xml:space="preserve">3.21479892730713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17111945152283</t>
+    <t xml:space="preserve">3.17111968994141</t>
   </si>
   <si>
     <t xml:space="preserve">3.26721382141113</t>
@@ -929,16 +929,16 @@
     <t xml:space="preserve">3.36330842971802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49434661865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58170509338379</t>
+    <t xml:space="preserve">3.49434638023376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58170533180237</t>
   </si>
   <si>
     <t xml:space="preserve">3.56423330307007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59044122695923</t>
+    <t xml:space="preserve">3.59044098854065</t>
   </si>
   <si>
     <t xml:space="preserve">3.5030825138092</t>
@@ -959,13 +959,13 @@
     <t xml:space="preserve">3.7476863861084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69527125358582</t>
+    <t xml:space="preserve">3.69527149200439</t>
   </si>
   <si>
     <t xml:space="preserve">3.66906380653381</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60791301727295</t>
+    <t xml:space="preserve">3.60791277885437</t>
   </si>
   <si>
     <t xml:space="preserve">3.55549788475037</t>
@@ -989,16 +989,16 @@
     <t xml:space="preserve">3.57296967506409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53802609443665</t>
+    <t xml:space="preserve">3.53802585601807</t>
   </si>
   <si>
     <t xml:space="preserve">3.3458366394043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3895161151886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42445993423462</t>
+    <t xml:space="preserve">3.38951635360718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42445969581604</t>
   </si>
   <si>
     <t xml:space="preserve">3.45066738128662</t>
@@ -1010,13 +1010,13 @@
     <t xml:space="preserve">3.48561072349548</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4069881439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35457229614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45940327644348</t>
+    <t xml:space="preserve">3.40698790550232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35457253456116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4594030380249</t>
   </si>
   <si>
     <t xml:space="preserve">3.52928996086121</t>
@@ -1025,13 +1025,13 @@
     <t xml:space="preserve">3.46813893318176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47687482833862</t>
+    <t xml:space="preserve">3.47687458992004</t>
   </si>
   <si>
     <t xml:space="preserve">3.79136610031128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72147941589355</t>
+    <t xml:space="preserve">3.72147917747498</t>
   </si>
   <si>
     <t xml:space="preserve">3.87872457504272</t>
@@ -1043,7 +1043,7 @@
     <t xml:space="preserve">4.31551790237427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35046148300171</t>
+    <t xml:space="preserve">4.35046100616455</t>
   </si>
   <si>
     <t xml:space="preserve">4.18447971343994</t>
@@ -1070,22 +1070,22 @@
     <t xml:space="preserve">3.93113970756531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08838558197021</t>
+    <t xml:space="preserve">4.08838510513306</t>
   </si>
   <si>
     <t xml:space="preserve">4.07091379165649</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1233286857605</t>
+    <t xml:space="preserve">4.12332820892334</t>
   </si>
   <si>
     <t xml:space="preserve">4.00102663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00976324081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93987584114075</t>
+    <t xml:space="preserve">4.00976276397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93987560272217</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
@@ -1094,7 +1094,7 @@
     <t xml:space="preserve">4.2106876373291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29804611206055</t>
+    <t xml:space="preserve">4.29804658889771</t>
   </si>
   <si>
     <t xml:space="preserve">4.28930997848511</t>
@@ -1109,7 +1109,7 @@
     <t xml:space="preserve">4.14953660964966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16700792312622</t>
+    <t xml:space="preserve">4.16700839996338</t>
   </si>
   <si>
     <t xml:space="preserve">4.11459302902222</t>
@@ -1118,19 +1118,19 @@
     <t xml:space="preserve">4.06217765808105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78262996673584</t>
+    <t xml:space="preserve">3.78263020515442</t>
   </si>
   <si>
     <t xml:space="preserve">3.80010175704956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8263099193573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83504557609558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84378147125244</t>
+    <t xml:space="preserve">3.82630968093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.835045337677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84378123283386</t>
   </si>
   <si>
     <t xml:space="preserve">3.77389454841614</t>
@@ -1139,19 +1139,19 @@
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734786987305</t>
+    <t xml:space="preserve">3.95734763145447</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86125302314758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76515793800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81757354736328</t>
+    <t xml:space="preserve">3.861252784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76515817642212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8175733089447</t>
   </si>
   <si>
     <t xml:space="preserve">3.64285612106323</t>
@@ -1169,25 +1169,25 @@
     <t xml:space="preserve">3.71274328231812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92240381240845</t>
+    <t xml:space="preserve">3.92240357398987</t>
   </si>
   <si>
     <t xml:space="preserve">3.61664843559265</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39825201034546</t>
+    <t xml:space="preserve">3.39825224876404</t>
   </si>
   <si>
     <t xml:space="preserve">3.23227047920227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0575532913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97019481658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95272302627563</t>
+    <t xml:space="preserve">3.05755352973938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97019457817078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95272278785706</t>
   </si>
   <si>
     <t xml:space="preserve">2.91777944564819</t>
@@ -1196,22 +1196,22 @@
     <t xml:space="preserve">2.90904355049133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3720440864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38078022003174</t>
+    <t xml:space="preserve">3.37204432487488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38077998161316</t>
   </si>
   <si>
     <t xml:space="preserve">3.41572380065918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31962895393372</t>
+    <t xml:space="preserve">3.31962919235229</t>
   </si>
   <si>
     <t xml:space="preserve">3.27594995498657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28468561172485</t>
+    <t xml:space="preserve">3.28468585014343</t>
   </si>
   <si>
     <t xml:space="preserve">3.50245499610901</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">3.32098078727722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26653814315796</t>
+    <t xml:space="preserve">3.26653838157654</t>
   </si>
   <si>
     <t xml:space="preserve">3.39357042312622</t>
@@ -1256,7 +1256,7 @@
     <t xml:space="preserve">3.23024344444275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19394874572754</t>
+    <t xml:space="preserve">3.19394850730896</t>
   </si>
   <si>
     <t xml:space="preserve">3.25746440887451</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">3.2211697101593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10321140289307</t>
+    <t xml:space="preserve">3.10321164131165</t>
   </si>
   <si>
     <t xml:space="preserve">2.99432682991028</t>
@@ -1283,13 +1283,13 @@
     <t xml:space="preserve">2.95803189277649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85822105407715</t>
+    <t xml:space="preserve">2.85822129249573</t>
   </si>
   <si>
     <t xml:space="preserve">2.89451599121094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8672947883606</t>
+    <t xml:space="preserve">2.86729502677917</t>
   </si>
   <si>
     <t xml:space="preserve">2.81285238265991</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">2.75841021537781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70396780967712</t>
+    <t xml:space="preserve">2.7039680480957</t>
   </si>
   <si>
     <t xml:space="preserve">2.72211527824402</t>
@@ -1310,16 +1310,16 @@
     <t xml:space="preserve">2.64952564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7947051525116</t>
+    <t xml:space="preserve">2.79470491409302</t>
   </si>
   <si>
     <t xml:space="preserve">2.92173719406128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05784273147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02154803276062</t>
+    <t xml:space="preserve">3.05784296989441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02154779434204</t>
   </si>
   <si>
     <t xml:space="preserve">3.13950634002686</t>
@@ -1349,46 +1349,46 @@
     <t xml:space="preserve">3.08506417274475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01247429847717</t>
+    <t xml:space="preserve">3.01247406005859</t>
   </si>
   <si>
     <t xml:space="preserve">2.88544225692749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7765576839447</t>
+    <t xml:space="preserve">2.77655744552612</t>
   </si>
   <si>
     <t xml:space="preserve">2.71304154396057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6313784122467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68582034111023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66767287254333</t>
+    <t xml:space="preserve">2.63137817382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68582057952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66767311096191</t>
   </si>
   <si>
     <t xml:space="preserve">2.55878829956055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52249336242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67674660682678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64045214653015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87636852264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83099985122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60415697097778</t>
+    <t xml:space="preserve">2.52249360084534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67674684524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64045190811157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87636876106262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83099961280823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6041567325592</t>
   </si>
   <si>
     <t xml:space="preserve">2.73118901252747</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">2.91266345977783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12135887145996</t>
+    <t xml:space="preserve">3.12135910987854</t>
   </si>
   <si>
     <t xml:space="preserve">3.0759904384613</t>
@@ -1424,46 +1424,46 @@
     <t xml:space="preserve">3.0941379070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38449692726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41171765327454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37542319297791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42079138755798</t>
+    <t xml:space="preserve">3.38449668884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41171789169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37542295455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42079162597656</t>
   </si>
   <si>
     <t xml:space="preserve">3.43893885612488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36634945869446</t>
+    <t xml:space="preserve">3.36634922027588</t>
   </si>
   <si>
     <t xml:space="preserve">3.35727572441101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20302248001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27561187744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29375958442688</t>
+    <t xml:space="preserve">3.20302224159241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27561211585999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29375982284546</t>
   </si>
   <si>
     <t xml:space="preserve">3.1667275428772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11228513717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78563141822815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84007382392883</t>
+    <t xml:space="preserve">3.11228537559509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78563117980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84007358551025</t>
   </si>
   <si>
     <t xml:space="preserve">2.82192611694336</t>
@@ -55323,7 +55323,7 @@
     </row>
     <row r="2049">
       <c r="A2049" s="1" t="n">
-        <v>45947.520150463</v>
+        <v>45947.2916666667</v>
       </c>
       <c r="B2049" t="n">
         <v>4984</v>
@@ -55344,6 +55344,32 @@
         <v>574</v>
       </c>
       <c r="H2049" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2050">
+      <c r="A2050" s="1" t="n">
+        <v>45950.5779282407</v>
+      </c>
+      <c r="B2050" t="n">
+        <v>19392</v>
+      </c>
+      <c r="C2050" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="D2050" t="n">
+        <v>3.16000008583069</v>
+      </c>
+      <c r="E2050" t="n">
+        <v>3.16000008583069</v>
+      </c>
+      <c r="F2050" t="n">
+        <v>3.22000002861023</v>
+      </c>
+      <c r="G2050" t="s">
+        <v>573</v>
+      </c>
+      <c r="H2050" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02345728874207</t>
+    <t xml:space="preserve">3.02345752716064</t>
   </si>
   <si>
     <t xml:space="preserve">NDT.MI</t>
@@ -47,58 +47,58 @@
     <t xml:space="preserve">2.96519923210144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88901543617249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98013758659363</t>
+    <t xml:space="preserve">2.88901567459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98013710975647</t>
   </si>
   <si>
     <t xml:space="preserve">2.97266817092896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94578003883362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9577305316925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9622118473053</t>
+    <t xml:space="preserve">2.94577980041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95773005485535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96221160888672</t>
   </si>
   <si>
     <t xml:space="preserve">2.93532347679138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91291618347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97864365577698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98611283302307</t>
+    <t xml:space="preserve">2.91291642189026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9786434173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98611235618591</t>
   </si>
   <si>
     <t xml:space="preserve">3.03540802001953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05632138252258</t>
+    <t xml:space="preserve">3.056321144104</t>
   </si>
   <si>
     <t xml:space="preserve">3.0593090057373</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05034613609314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98760628700256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95026135444641</t>
+    <t xml:space="preserve">3.05034589767456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98760604858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95026111602783</t>
   </si>
   <si>
     <t xml:space="preserve">3.01598882675171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01001358032227</t>
+    <t xml:space="preserve">3.01001334190369</t>
   </si>
   <si>
     <t xml:space="preserve">3.02495145797729</t>
@@ -107,46 +107,46 @@
     <t xml:space="preserve">3.0174822807312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03092694282532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99955654144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04437112808228</t>
+    <t xml:space="preserve">3.03092670440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99955677986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04437065124512</t>
   </si>
   <si>
     <t xml:space="preserve">2.959223985672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00254464149475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92785453796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90843486785889</t>
+    <t xml:space="preserve">3.00254416465759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92785429954529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90843462944031</t>
   </si>
   <si>
     <t xml:space="preserve">2.896484375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91889119148254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9159038066864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92038512229919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90544724464417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90992879867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92337274551392</t>
+    <t xml:space="preserve">2.9188916683197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91590356826782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92038536071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90544748306274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90992856025696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9233729839325</t>
   </si>
   <si>
     <t xml:space="preserve">2.8382260799408</t>
@@ -167,10 +167,10 @@
     <t xml:space="preserve">2.86810207366943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88303995132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79639959335327</t>
+    <t xml:space="preserve">2.88304018974304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79639935493469</t>
   </si>
   <si>
     <t xml:space="preserve">2.87557101249695</t>
@@ -185,10 +185,10 @@
     <t xml:space="preserve">2.74262261390686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82179403305054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75009155273438</t>
+    <t xml:space="preserve">2.82179427146912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7500913143158</t>
   </si>
   <si>
     <t xml:space="preserve">2.76353573799133</t>
@@ -203,16 +203,16 @@
     <t xml:space="preserve">2.79341197013855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69631481170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65150094032288</t>
+    <t xml:space="preserve">2.69631457328796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6515007019043</t>
   </si>
   <si>
     <t xml:space="preserve">2.62162446975708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53946542739868</t>
+    <t xml:space="preserve">2.53946566581726</t>
   </si>
   <si>
     <t xml:space="preserve">2.56934142112732</t>
@@ -221,13 +221,13 @@
     <t xml:space="preserve">2.61415529251099</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65896964073181</t>
+    <t xml:space="preserve">2.65896987915039</t>
   </si>
   <si>
     <t xml:space="preserve">2.68884563446045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70378375053406</t>
+    <t xml:space="preserve">2.70378351211548</t>
   </si>
   <si>
     <t xml:space="preserve">2.77100467681885</t>
@@ -236,13 +236,13 @@
     <t xml:space="preserve">2.81581902503967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73365998268127</t>
+    <t xml:space="preserve">2.7336597442627</t>
   </si>
   <si>
     <t xml:space="preserve">2.66643857955933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68137669563293</t>
+    <t xml:space="preserve">2.68137645721436</t>
   </si>
   <si>
     <t xml:space="preserve">2.74112868309021</t>
@@ -257,22 +257,22 @@
     <t xml:space="preserve">2.89315104484558</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69871854782104</t>
+    <t xml:space="preserve">2.69871830940247</t>
   </si>
   <si>
     <t xml:space="preserve">2.83870959281921</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93203735351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87759637832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8309326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81537795066833</t>
+    <t xml:space="preserve">2.93203687667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87759613990784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83093237876892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81537771224976</t>
   </si>
   <si>
     <t xml:space="preserve">2.84648704528809</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">2.79982304573059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73760461807251</t>
+    <t xml:space="preserve">2.73760485649109</t>
   </si>
   <si>
     <t xml:space="preserve">2.76093697547913</t>
@@ -290,16 +290,16 @@
     <t xml:space="preserve">2.80760049819946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00980997085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95536923408508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90870523452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88537335395813</t>
+    <t xml:space="preserve">3.00980973243713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9553689956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90870547294617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88537311553955</t>
   </si>
   <si>
     <t xml:space="preserve">2.82315516471863</t>
@@ -311,13 +311,13 @@
     <t xml:space="preserve">3.00203275680542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91648244857788</t>
+    <t xml:space="preserve">2.91648268699646</t>
   </si>
   <si>
     <t xml:space="preserve">2.8542640209198</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72982740402222</t>
+    <t xml:space="preserve">2.7298276424408</t>
   </si>
   <si>
     <t xml:space="preserve">2.68316388130188</t>
@@ -335,28 +335,28 @@
     <t xml:space="preserve">2.93981456756592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99425554275513</t>
+    <t xml:space="preserve">2.99425506591797</t>
   </si>
   <si>
     <t xml:space="preserve">2.97870063781738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86981892585754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94759178161621</t>
+    <t xml:space="preserve">2.86981868743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94759130477905</t>
   </si>
   <si>
     <t xml:space="preserve">2.98647809028625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63650035858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55094981193542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51984071731567</t>
+    <t xml:space="preserve">2.63650012016296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.550950050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51984095573425</t>
   </si>
   <si>
     <t xml:space="preserve">2.41095876693726</t>
@@ -365,10 +365,10 @@
     <t xml:space="preserve">2.34096336364746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34874081611633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36429500579834</t>
+    <t xml:space="preserve">2.34874057769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36429524421692</t>
   </si>
   <si>
     <t xml:space="preserve">2.2554132938385</t>
@@ -377,25 +377,25 @@
     <t xml:space="preserve">2.24763584136963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32540893554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23208141326904</t>
+    <t xml:space="preserve">2.3254086971283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23208117485046</t>
   </si>
   <si>
     <t xml:space="preserve">2.18541741371155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27874493598938</t>
+    <t xml:space="preserve">2.27874517440796</t>
   </si>
   <si>
     <t xml:space="preserve">2.26319050788879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2165265083313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06875824928284</t>
+    <t xml:space="preserve">2.21652674674988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06875848770142</t>
   </si>
   <si>
     <t xml:space="preserve">2.1465311050415</t>
@@ -407,16 +407,16 @@
     <t xml:space="preserve">2.15430855751038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17764067649841</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22430396080017</t>
+    <t xml:space="preserve">2.17764019966125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22430372238159</t>
   </si>
   <si>
     <t xml:space="preserve">2.35651803016663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48873162269592</t>
+    <t xml:space="preserve">2.4887318611145</t>
   </si>
   <si>
     <t xml:space="preserve">2.52761816978455</t>
@@ -425,7 +425,7 @@
     <t xml:space="preserve">2.43429064750671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44206809997559</t>
+    <t xml:space="preserve">2.44206833839417</t>
   </si>
   <si>
     <t xml:space="preserve">2.5587272644043</t>
@@ -437,31 +437,31 @@
     <t xml:space="preserve">2.37207245826721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33318591117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29429984092712</t>
+    <t xml:space="preserve">2.33318614959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29429960250854</t>
   </si>
   <si>
     <t xml:space="preserve">2.3798496723175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71427297592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58205890655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62872314453125</t>
+    <t xml:space="preserve">2.71427321434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58205938339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62872290611267</t>
   </si>
   <si>
     <t xml:space="preserve">2.65983200073242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57428193092346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67538666725159</t>
+    <t xml:space="preserve">2.57428169250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67538642883301</t>
   </si>
   <si>
     <t xml:space="preserve">2.64427757263184</t>
@@ -479,7 +479,7 @@
     <t xml:space="preserve">2.9631462097168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92425990104675</t>
+    <t xml:space="preserve">2.92425966262817</t>
   </si>
   <si>
     <t xml:space="preserve">2.97092342376709</t>
@@ -488,13 +488,13 @@
     <t xml:space="preserve">3.01758742332458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04869651794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03314185142517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06425094604492</t>
+    <t xml:space="preserve">3.04869675636292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03314208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0642511844635</t>
   </si>
   <si>
     <t xml:space="preserve">3.07980561256409</t>
@@ -503,7 +503,7 @@
     <t xml:space="preserve">3.06049919128418</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02811288833618</t>
+    <t xml:space="preserve">3.02811312675476</t>
   </si>
   <si>
     <t xml:space="preserve">3.01191997528076</t>
@@ -512,49 +512,49 @@
     <t xml:space="preserve">3.1090784072876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0928852558136</t>
+    <t xml:space="preserve">3.09288501739502</t>
   </si>
   <si>
     <t xml:space="preserve">3.1252715587616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07669234275818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99572682380676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30339550971985</t>
+    <t xml:space="preserve">3.0766921043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9957263469696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30339574813843</t>
   </si>
   <si>
     <t xml:space="preserve">3.41674733161926</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35197496414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33578181266785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36816811561584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23862314224243</t>
+    <t xml:space="preserve">3.35197520256042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33578205108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36816835403442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23862338066101</t>
   </si>
   <si>
     <t xml:space="preserve">3.31958889961243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27100920677185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28720235824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22242999076843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17385101318359</t>
+    <t xml:space="preserve">3.27100944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28720259666443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22243022918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17385077476501</t>
   </si>
   <si>
     <t xml:space="preserve">3.20623707771301</t>
@@ -563,10 +563,10 @@
     <t xml:space="preserve">3.1414647102356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40055418014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49771332740784</t>
+    <t xml:space="preserve">3.40055441856384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49771308898926</t>
   </si>
   <si>
     <t xml:space="preserve">3.38436126708984</t>
@@ -575,10 +575,10 @@
     <t xml:space="preserve">3.25481629371643</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19004392623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96334052085876</t>
+    <t xml:space="preserve">3.19004416465759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96334028244019</t>
   </si>
   <si>
     <t xml:space="preserve">2.97953343391418</t>
@@ -587,13 +587,13 @@
     <t xml:space="preserve">2.80140924453735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88237476348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86618185043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84998822212219</t>
+    <t xml:space="preserve">2.88237452507019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86618161201477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84998846054077</t>
   </si>
   <si>
     <t xml:space="preserve">2.78521609306335</t>
@@ -602,13 +602,13 @@
     <t xml:space="preserve">2.75283002853394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72044348716736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83379530906677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76902294158936</t>
+    <t xml:space="preserve">2.72044372558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83379554748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76902318000793</t>
   </si>
   <si>
     <t xml:space="preserve">2.73663687705994</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">2.81760215759277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89856791496277</t>
+    <t xml:space="preserve">2.89856767654419</t>
   </si>
   <si>
     <t xml:space="preserve">2.91476082801819</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">2.63947796821594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67186403274536</t>
+    <t xml:space="preserve">2.67186427116394</t>
   </si>
   <si>
     <t xml:space="preserve">2.62328481674194</t>
@@ -635,19 +635,19 @@
     <t xml:space="preserve">2.68805718421936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70425057411194</t>
+    <t xml:space="preserve">2.70425033569336</t>
   </si>
   <si>
     <t xml:space="preserve">2.60709166526794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59089851379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42896747589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54231929779053</t>
+    <t xml:space="preserve">2.59089875221252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42896771430969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54231905937195</t>
   </si>
   <si>
     <t xml:space="preserve">2.46135354042053</t>
@@ -656,7 +656,7 @@
     <t xml:space="preserve">2.3156156539917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29942274093628</t>
+    <t xml:space="preserve">2.2994225025177</t>
   </si>
   <si>
     <t xml:space="preserve">2.35488176345825</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">2.40607476234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28662443161011</t>
+    <t xml:space="preserve">2.28662419319153</t>
   </si>
   <si>
     <t xml:space="preserve">2.13304495811462</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">2.09891629219055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26955986022949</t>
+    <t xml:space="preserve">2.26956009864807</t>
   </si>
   <si>
     <t xml:space="preserve">2.21836686134338</t>
@@ -695,19 +695,19 @@
     <t xml:space="preserve">2.32075309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55965399742126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54258990287781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45726823806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57671856880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62791132926941</t>
+    <t xml:space="preserve">2.55965423583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54258966445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45726799964905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5767183303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62791156768799</t>
   </si>
   <si>
     <t xml:space="preserve">2.61084699630737</t>
@@ -716,13 +716,13 @@
     <t xml:space="preserve">2.64497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59378266334534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69616889953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71323323249817</t>
+    <t xml:space="preserve">2.59378290176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69616913795471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71323347091675</t>
   </si>
   <si>
     <t xml:space="preserve">2.44020342826843</t>
@@ -737,10 +737,10 @@
     <t xml:space="preserve">2.15010929107666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33781719207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30368852615356</t>
+    <t xml:space="preserve">2.33781743049622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30368876457214</t>
   </si>
   <si>
     <t xml:space="preserve">2.25249576568604</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">2.37194609642029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3890106678009</t>
+    <t xml:space="preserve">2.38901042938232</t>
   </si>
   <si>
     <t xml:space="preserve">2.20130252838135</t>
@@ -761,16 +761,16 @@
     <t xml:space="preserve">2.18423795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01359438896179</t>
+    <t xml:space="preserve">2.01359415054321</t>
   </si>
   <si>
     <t xml:space="preserve">2.04772329330444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11598062515259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91120851039886</t>
+    <t xml:space="preserve">2.11598038673401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91120827198029</t>
   </si>
   <si>
     <t xml:space="preserve">1.87707984447479</t>
@@ -779,19 +779,19 @@
     <t xml:space="preserve">1.84295094013214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97946584224701</t>
+    <t xml:space="preserve">1.97946560382843</t>
   </si>
   <si>
     <t xml:space="preserve">1.86001515388489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94533717632294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96240127086639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99652993679047</t>
+    <t xml:space="preserve">1.94533693790436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96240139007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99653005599976</t>
   </si>
   <si>
     <t xml:space="preserve">2.81561923027039</t>
@@ -803,10 +803,10 @@
     <t xml:space="preserve">2.88387703895569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76442623138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73029756546021</t>
+    <t xml:space="preserve">2.76442646980286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73029780387878</t>
   </si>
   <si>
     <t xml:space="preserve">2.6791045665741</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">2.86681246757507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79855489730835</t>
+    <t xml:space="preserve">2.79855513572693</t>
   </si>
   <si>
     <t xml:space="preserve">2.78149056434631</t>
@@ -830,10 +830,10 @@
     <t xml:space="preserve">2.9350700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96919846534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02039194107056</t>
+    <t xml:space="preserve">2.96919870376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02039170265198</t>
   </si>
   <si>
     <t xml:space="preserve">3.00332713127136</t>
@@ -842,34 +842,34 @@
     <t xml:space="preserve">3.03745603561401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98626303672791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05452060699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07158470153809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13984227180481</t>
+    <t xml:space="preserve">2.98626279830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05452036857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07158493995667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13984251022339</t>
   </si>
   <si>
     <t xml:space="preserve">3.11424589157104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1313099861145</t>
+    <t xml:space="preserve">3.13131022453308</t>
   </si>
   <si>
     <t xml:space="preserve">3.06305265426636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16543865203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19956755638123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15690684318542</t>
+    <t xml:space="preserve">3.16543889045715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1995677947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15690660476685</t>
   </si>
   <si>
     <t xml:space="preserve">3.2336962223053</t>
@@ -887,34 +887,34 @@
     <t xml:space="preserve">3.31048607826233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3446147441864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32755041122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28488945960999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18250346183777</t>
+    <t xml:space="preserve">3.34461498260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32755017280579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28488922119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18250322341919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29342126846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33710074424744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32836508750916</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342150688171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33710074424744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32836484909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29342174530029</t>
-  </si>
-  <si>
     <t xml:space="preserve">3.24974226951599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20606303215027</t>
+    <t xml:space="preserve">3.20606279373169</t>
   </si>
   <si>
     <t xml:space="preserve">3.15364766120911</t>
@@ -926,7 +926,7 @@
     <t xml:space="preserve">3.17111968994141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26721405982971</t>
+    <t xml:space="preserve">3.26721382141113</t>
   </si>
   <si>
     <t xml:space="preserve">3.36330842971802</t>
@@ -935,55 +935,55 @@
     <t xml:space="preserve">3.49434638023376</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58170509338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56423354148865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59044122695923</t>
+    <t xml:space="preserve">3.58170533180237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56423330307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59044098854065</t>
   </si>
   <si>
     <t xml:space="preserve">3.5030825138092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51181817054749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54676151275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63412046432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62538480758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74768662452698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69527125358582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66906356811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60791301727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55549764633179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66032791137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65159177780151</t>
+    <t xml:space="preserve">3.51181840896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54676175117493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63411998748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62538456916809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7476863861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69527149200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66906380653381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60791277885437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55549788475037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66032814979553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65159201622009</t>
   </si>
   <si>
     <t xml:space="preserve">3.68653535842896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70400714874268</t>
+    <t xml:space="preserve">3.7040069103241</t>
   </si>
   <si>
     <t xml:space="preserve">3.75642251968384</t>
@@ -1010,19 +1010,19 @@
     <t xml:space="preserve">3.44193148612976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4856104850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4069881439209</t>
+    <t xml:space="preserve">3.48561072349548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40698790550232</t>
   </si>
   <si>
     <t xml:space="preserve">3.35457253456116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45940327644348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52928972244263</t>
+    <t xml:space="preserve">3.4594030380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52928996086121</t>
   </si>
   <si>
     <t xml:space="preserve">3.46813893318176</t>
@@ -1031,22 +1031,22 @@
     <t xml:space="preserve">3.47687458992004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79136633872986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7214789390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8787248134613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17574453353882</t>
+    <t xml:space="preserve">3.79136610031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72147917747498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87872457504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17574405670166</t>
   </si>
   <si>
     <t xml:space="preserve">4.31551790237427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35046148300171</t>
+    <t xml:space="preserve">4.35046100616455</t>
   </si>
   <si>
     <t xml:space="preserve">4.18447971343994</t>
@@ -1061,25 +1061,25 @@
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493202209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98355484008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94861197471619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93114018440247</t>
+    <t xml:space="preserve">3.90493226051331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98355507850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94861173629761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93113970756531</t>
   </si>
   <si>
     <t xml:space="preserve">4.08838510513306</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07091331481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1233286857605</t>
+    <t xml:space="preserve">4.07091379165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12332820892334</t>
   </si>
   <si>
     <t xml:space="preserve">4.00102663040161</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">4.00976276397705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93987607955933</t>
+    <t xml:space="preserve">3.93987560272217</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
@@ -1097,31 +1097,31 @@
     <t xml:space="preserve">4.2106876373291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29804611206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28931045532227</t>
+    <t xml:space="preserve">4.29804658889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28930997848511</t>
   </si>
   <si>
     <t xml:space="preserve">4.21942329406738</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19321584701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1495361328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16700792312622</t>
+    <t xml:space="preserve">4.19321632385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14953660964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16700839996338</t>
   </si>
   <si>
     <t xml:space="preserve">4.11459302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06217813491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78262996673584</t>
+    <t xml:space="preserve">4.06217765808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78263020515442</t>
   </si>
   <si>
     <t xml:space="preserve">3.80010175704956</t>
@@ -1130,10 +1130,10 @@
     <t xml:space="preserve">3.82630968093872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83504509925842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84378099441528</t>
+    <t xml:space="preserve">3.835045337677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84378123283386</t>
   </si>
   <si>
     <t xml:space="preserve">3.77389454841614</t>
@@ -1142,16 +1142,16 @@
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734786987305</t>
+    <t xml:space="preserve">3.95734763145447</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86125302314758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76515865325928</t>
+    <t xml:space="preserve">3.861252784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76515817642212</t>
   </si>
   <si>
     <t xml:space="preserve">3.8175733089447</t>
@@ -1163,52 +1163,52 @@
     <t xml:space="preserve">3.67779970169067</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73895072937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85251665115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71274304389954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92240381240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61664867401123</t>
+    <t xml:space="preserve">3.7389509677887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85251712799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71274328231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92240357398987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61664843559265</t>
   </si>
   <si>
     <t xml:space="preserve">3.39825224876404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23227071762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0575532913208</t>
+    <t xml:space="preserve">3.23227047920227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05755352973938</t>
   </si>
   <si>
     <t xml:space="preserve">2.97019457817078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95272302627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91777920722961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90904331207275</t>
+    <t xml:space="preserve">2.95272278785706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91777944564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90904355049133</t>
   </si>
   <si>
     <t xml:space="preserve">3.37204432487488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38078022003174</t>
+    <t xml:space="preserve">3.38077998161316</t>
   </si>
   <si>
     <t xml:space="preserve">3.41572380065918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31962895393372</t>
+    <t xml:space="preserve">3.31962919235229</t>
   </si>
   <si>
     <t xml:space="preserve">3.27594995498657</t>
@@ -55378,7 +55378,7 @@
     </row>
     <row r="2051">
       <c r="A2051" s="1" t="n">
-        <v>45951.6431134259</v>
+        <v>45951.2916666667</v>
       </c>
       <c r="B2051" t="n">
         <v>6364</v>
@@ -55399,6 +55399,32 @@
         <v>570</v>
       </c>
       <c r="H2051" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2052">
+      <c r="A2052" s="1" t="n">
+        <v>45952.5842361111</v>
+      </c>
+      <c r="B2052" t="n">
+        <v>7189</v>
+      </c>
+      <c r="C2052" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="D2052" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E2052" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="F2052" t="n">
+        <v>3.22000002861023</v>
+      </c>
+      <c r="G2052" t="s">
+        <v>574</v>
+      </c>
+      <c r="H2052" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02345728874207</t>
+    <t xml:space="preserve">3.02345776557922</t>
   </si>
   <si>
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519923210144</t>
+    <t xml:space="preserve">2.96519947052002</t>
   </si>
   <si>
     <t xml:space="preserve">2.88901543617249</t>
@@ -56,31 +56,31 @@
     <t xml:space="preserve">2.97266840934753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94578003883362</t>
+    <t xml:space="preserve">2.94577980041504</t>
   </si>
   <si>
     <t xml:space="preserve">2.95773029327393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96221160888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93532299995422</t>
+    <t xml:space="preserve">2.96221137046814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93532347679138</t>
   </si>
   <si>
     <t xml:space="preserve">2.91291618347168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9786434173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98611235618591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03540802001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05632162094116</t>
+    <t xml:space="preserve">2.97864365577698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98611259460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03540849685669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05632138252258</t>
   </si>
   <si>
     <t xml:space="preserve">3.0593090057373</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">3.05034637451172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98760652542114</t>
+    <t xml:space="preserve">2.98760628700256</t>
   </si>
   <si>
     <t xml:space="preserve">2.95026135444641</t>
@@ -101,13 +101,13 @@
     <t xml:space="preserve">3.01001358032227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02495145797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01748204231262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03092670440674</t>
+    <t xml:space="preserve">3.02495121955872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0174822807312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03092646598816</t>
   </si>
   <si>
     <t xml:space="preserve">2.99955677986145</t>
@@ -119,31 +119,31 @@
     <t xml:space="preserve">2.959223985672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00254440307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92785406112671</t>
+    <t xml:space="preserve">3.00254416465759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92785453796387</t>
   </si>
   <si>
     <t xml:space="preserve">2.90843486785889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89648461341858</t>
+    <t xml:space="preserve">2.896484375</t>
   </si>
   <si>
     <t xml:space="preserve">2.91889119148254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9159038066864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92038559913635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90544724464417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90992832183838</t>
+    <t xml:space="preserve">2.91590404510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92038512229919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90544700622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90992856025696</t>
   </si>
   <si>
     <t xml:space="preserve">2.9233729839325</t>
@@ -152,22 +152,22 @@
     <t xml:space="preserve">2.8382260799408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86063289642334</t>
+    <t xml:space="preserve">2.86063313484192</t>
   </si>
   <si>
     <t xml:space="preserve">2.82627534866333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77996754646301</t>
+    <t xml:space="preserve">2.77996778488159</t>
   </si>
   <si>
     <t xml:space="preserve">2.84569501876831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86810231208801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88304018974304</t>
+    <t xml:space="preserve">2.86810183525085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88303995132446</t>
   </si>
   <si>
     <t xml:space="preserve">2.79639959335327</t>
@@ -176,34 +176,34 @@
     <t xml:space="preserve">2.87557101249695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89797806739807</t>
+    <t xml:space="preserve">2.89797830581665</t>
   </si>
   <si>
     <t xml:space="preserve">2.80088090896606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74262261390686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8217945098877</t>
+    <t xml:space="preserve">2.7426221370697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82179427146912</t>
   </si>
   <si>
     <t xml:space="preserve">2.75009155273438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76353621482849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77847409248352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78594303131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79341197013855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69631457328796</t>
+    <t xml:space="preserve">2.76353597640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77847385406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78594279289246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79341173171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69631481170654</t>
   </si>
   <si>
     <t xml:space="preserve">2.65150046348572</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">2.5693416595459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61415529251099</t>
+    <t xml:space="preserve">2.61415576934814</t>
   </si>
   <si>
     <t xml:space="preserve">2.65896964073181</t>
@@ -233,40 +233,40 @@
     <t xml:space="preserve">2.77100491523743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81581878662109</t>
+    <t xml:space="preserve">2.81581926345825</t>
   </si>
   <si>
     <t xml:space="preserve">2.7336597442627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66643857955933</t>
+    <t xml:space="preserve">2.66643834114075</t>
   </si>
   <si>
     <t xml:space="preserve">2.68137645721436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74112868309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7261905670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8307569026947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89315056800842</t>
+    <t xml:space="preserve">2.74112892150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72619080543518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83075714111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.893150806427</t>
   </si>
   <si>
     <t xml:space="preserve">2.69871854782104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83870959281921</t>
+    <t xml:space="preserve">2.83870983123779</t>
   </si>
   <si>
     <t xml:space="preserve">2.93203711509705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87759637832642</t>
+    <t xml:space="preserve">2.87759590148926</t>
   </si>
   <si>
     <t xml:space="preserve">2.83093237876892</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">2.84648680686951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79982304573059</t>
+    <t xml:space="preserve">2.79982328414917</t>
   </si>
   <si>
     <t xml:space="preserve">2.73760509490967</t>
@@ -287,16 +287,16 @@
     <t xml:space="preserve">2.76093673706055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80760025978088</t>
+    <t xml:space="preserve">2.80760049819946</t>
   </si>
   <si>
     <t xml:space="preserve">3.00980997085571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95536875724792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90870547294617</t>
+    <t xml:space="preserve">2.9553689956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90870523452759</t>
   </si>
   <si>
     <t xml:space="preserve">2.88537335395813</t>
@@ -305,58 +305,58 @@
     <t xml:space="preserve">2.82315540313721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86204147338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00203275680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91648268699646</t>
+    <t xml:space="preserve">2.86204171180725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00203251838684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91648244857788</t>
   </si>
   <si>
     <t xml:space="preserve">2.85426425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72982788085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6831636428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72205018997192</t>
+    <t xml:space="preserve">2.7298276424408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68316411972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7220504283905</t>
   </si>
   <si>
     <t xml:space="preserve">2.75315928459167</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70649600028992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93981409072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99425530433655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9787003993988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86981892585754</t>
+    <t xml:space="preserve">2.70649576187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93981432914734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99425554275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97870063781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86981868743896</t>
   </si>
   <si>
     <t xml:space="preserve">2.94759154319763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98647832870483</t>
+    <t xml:space="preserve">2.98647809028625</t>
   </si>
   <si>
     <t xml:space="preserve">2.63650035858154</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55094981193542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51984095573425</t>
+    <t xml:space="preserve">2.550950050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51984071731567</t>
   </si>
   <si>
     <t xml:space="preserve">2.41095876693726</t>
@@ -368,13 +368,13 @@
     <t xml:space="preserve">2.34874057769775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36429524421692</t>
+    <t xml:space="preserve">2.36429500579834</t>
   </si>
   <si>
     <t xml:space="preserve">2.2554132938385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24763631820679</t>
+    <t xml:space="preserve">2.24763607978821</t>
   </si>
   <si>
     <t xml:space="preserve">2.32540893554688</t>
@@ -383,13 +383,13 @@
     <t xml:space="preserve">2.23208117485046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18541717529297</t>
+    <t xml:space="preserve">2.18541765213013</t>
   </si>
   <si>
     <t xml:space="preserve">2.27874493598938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26319050788879</t>
+    <t xml:space="preserve">2.26319026947021</t>
   </si>
   <si>
     <t xml:space="preserve">2.2165265083313</t>
@@ -398,7 +398,7 @@
     <t xml:space="preserve">2.06875824928284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14653086662292</t>
+    <t xml:space="preserve">2.14653134346008</t>
   </si>
   <si>
     <t xml:space="preserve">2.10764455795288</t>
@@ -407,7 +407,7 @@
     <t xml:space="preserve">2.15430855751038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17764019966125</t>
+    <t xml:space="preserve">2.17763996124268</t>
   </si>
   <si>
     <t xml:space="preserve">2.22430396080017</t>
@@ -419,10 +419,10 @@
     <t xml:space="preserve">2.4887318611145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52761816978455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43429088592529</t>
+    <t xml:space="preserve">2.52761840820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43429112434387</t>
   </si>
   <si>
     <t xml:space="preserve">2.44206809997559</t>
@@ -434,19 +434,19 @@
     <t xml:space="preserve">2.44984531402588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37207245826721</t>
+    <t xml:space="preserve">2.37207221984863</t>
   </si>
   <si>
     <t xml:space="preserve">2.33318614959717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29429936408997</t>
+    <t xml:space="preserve">2.29429960250854</t>
   </si>
   <si>
     <t xml:space="preserve">2.3798496723175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71427321434021</t>
+    <t xml:space="preserve">2.71427297592163</t>
   </si>
   <si>
     <t xml:space="preserve">2.58205914497375</t>
@@ -455,22 +455,22 @@
     <t xml:space="preserve">2.62872314453125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65983176231384</t>
+    <t xml:space="preserve">2.659832239151</t>
   </si>
   <si>
     <t xml:space="preserve">2.57428169250488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67538666725159</t>
+    <t xml:space="preserve">2.67538642883301</t>
   </si>
   <si>
     <t xml:space="preserve">2.64427757263184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69094109535217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76871418952942</t>
+    <t xml:space="preserve">2.69094133377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76871371269226</t>
   </si>
   <si>
     <t xml:space="preserve">2.90092802047729</t>
@@ -485,19 +485,19 @@
     <t xml:space="preserve">2.97092342376709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01758742332458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04869627952576</t>
+    <t xml:space="preserve">3.01758718490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04869651794434</t>
   </si>
   <si>
     <t xml:space="preserve">3.03314185142517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06425070762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07980561256409</t>
+    <t xml:space="preserve">3.06425094604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07980537414551</t>
   </si>
   <si>
     <t xml:space="preserve">3.0604989528656</t>
@@ -506,13 +506,13 @@
     <t xml:space="preserve">3.02811288833618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01191973686218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10907816886902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09288501739502</t>
+    <t xml:space="preserve">3.01191997528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1090784072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0928852558136</t>
   </si>
   <si>
     <t xml:space="preserve">3.1252715587616</t>
@@ -524,43 +524,43 @@
     <t xml:space="preserve">2.99572682380676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30339598655701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41674733161926</t>
+    <t xml:space="preserve">3.30339574813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41674757003784</t>
   </si>
   <si>
     <t xml:space="preserve">3.35197496414185</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33578157424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36816811561584</t>
+    <t xml:space="preserve">3.33578181266785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36816835403442</t>
   </si>
   <si>
     <t xml:space="preserve">3.23862338066101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31958866119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27100944519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28720259666443</t>
+    <t xml:space="preserve">3.31958889961243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27100968360901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28720283508301</t>
   </si>
   <si>
     <t xml:space="preserve">3.22243022918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17385101318359</t>
+    <t xml:space="preserve">3.17385077476501</t>
   </si>
   <si>
     <t xml:space="preserve">3.20623707771301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1414647102356</t>
+    <t xml:space="preserve">3.14146494865417</t>
   </si>
   <si>
     <t xml:space="preserve">3.40055418014526</t>
@@ -569,13 +569,13 @@
     <t xml:space="preserve">3.49771332740784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38436126708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25481653213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19004416465759</t>
+    <t xml:space="preserve">3.38436150550842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25481677055359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19004392623901</t>
   </si>
   <si>
     <t xml:space="preserve">2.96334028244019</t>
@@ -584,19 +584,19 @@
     <t xml:space="preserve">2.97953367233276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80140924453735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88237476348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86618161201477</t>
+    <t xml:space="preserve">2.80140900611877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88237500190735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86618185043335</t>
   </si>
   <si>
     <t xml:space="preserve">2.84998846054077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78521585464478</t>
+    <t xml:space="preserve">2.78521609306335</t>
   </si>
   <si>
     <t xml:space="preserve">2.75283026695251</t>
@@ -626,28 +626,28 @@
     <t xml:space="preserve">2.63947820663452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67186427116394</t>
+    <t xml:space="preserve">2.67186403274536</t>
   </si>
   <si>
     <t xml:space="preserve">2.62328505516052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68805742263794</t>
+    <t xml:space="preserve">2.68805718421936</t>
   </si>
   <si>
     <t xml:space="preserve">2.70425057411194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60709166526794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59089851379395</t>
+    <t xml:space="preserve">2.60709190368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59089875221252</t>
   </si>
   <si>
     <t xml:space="preserve">2.42896747589111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54231929779053</t>
+    <t xml:space="preserve">2.54231953620911</t>
   </si>
   <si>
     <t xml:space="preserve">2.46135354042053</t>
@@ -656,25 +656,25 @@
     <t xml:space="preserve">2.3156156539917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2994225025177</t>
+    <t xml:space="preserve">2.29942226409912</t>
   </si>
   <si>
     <t xml:space="preserve">2.35488152503967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40607452392578</t>
+    <t xml:space="preserve">2.40607476234436</t>
   </si>
   <si>
     <t xml:space="preserve">2.28662443161011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1330451965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08185172080994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06478762626648</t>
+    <t xml:space="preserve">2.13304495811462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08185195922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0647873878479</t>
   </si>
   <si>
     <t xml:space="preserve">2.03065896034241</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">2.26956009864807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21836638450623</t>
+    <t xml:space="preserve">2.2183666229248</t>
   </si>
   <si>
     <t xml:space="preserve">2.32075309753418</t>
@@ -704,7 +704,7 @@
     <t xml:space="preserve">2.45726799964905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57671856880188</t>
+    <t xml:space="preserve">2.5767183303833</t>
   </si>
   <si>
     <t xml:space="preserve">2.62791156768799</t>
@@ -722,25 +722,25 @@
     <t xml:space="preserve">2.69616889953613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71323347091675</t>
+    <t xml:space="preserve">2.71323323249817</t>
   </si>
   <si>
     <t xml:space="preserve">2.44020342826843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4231390953064</t>
+    <t xml:space="preserve">2.42313885688782</t>
   </si>
   <si>
     <t xml:space="preserve">2.47433233261108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15010929107666</t>
+    <t xml:space="preserve">2.15010952949524</t>
   </si>
   <si>
     <t xml:space="preserve">2.33781743049622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30368876457214</t>
+    <t xml:space="preserve">2.30368852615356</t>
   </si>
   <si>
     <t xml:space="preserve">2.25249552726746</t>
@@ -758,13 +758,13 @@
     <t xml:space="preserve">2.20130252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18423819541931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01359462738037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04772353172302</t>
+    <t xml:space="preserve">2.18423795700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01359438896179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04772329330444</t>
   </si>
   <si>
     <t xml:space="preserve">2.11598062515259</t>
@@ -779,22 +779,22 @@
     <t xml:space="preserve">1.84295094013214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97946560382843</t>
+    <t xml:space="preserve">1.97946572303772</t>
   </si>
   <si>
     <t xml:space="preserve">1.86001539230347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94533705711365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9624011516571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99653017520905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81561946868896</t>
+    <t xml:space="preserve">1.94533681869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96240139007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99653005599976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81561923027039</t>
   </si>
   <si>
     <t xml:space="preserve">2.9009416103363</t>
@@ -806,43 +806,43 @@
     <t xml:space="preserve">2.76442646980286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73029756546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6791045665741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74736189842224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.832683801651</t>
+    <t xml:space="preserve">2.73029780387878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67910480499268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74736213684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83268356323242</t>
   </si>
   <si>
     <t xml:space="preserve">2.86681246757507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79855489730835</t>
+    <t xml:space="preserve">2.79855513572693</t>
   </si>
   <si>
     <t xml:space="preserve">2.78149080276489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93506979942322</t>
+    <t xml:space="preserve">2.9350700378418</t>
   </si>
   <si>
     <t xml:space="preserve">2.96919870376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02039170265198</t>
+    <t xml:space="preserve">3.02039194107056</t>
   </si>
   <si>
     <t xml:space="preserve">3.00332736968994</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03745603561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98626279830933</t>
+    <t xml:space="preserve">3.03745627403259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98626303672791</t>
   </si>
   <si>
     <t xml:space="preserve">3.05452060699463</t>
@@ -854,10 +854,10 @@
     <t xml:space="preserve">3.13984251022339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11424589157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13131022453308</t>
+    <t xml:space="preserve">3.11424565315247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1313099861145</t>
   </si>
   <si>
     <t xml:space="preserve">3.06305241584778</t>
@@ -872,10 +872,10 @@
     <t xml:space="preserve">3.15690684318542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2336962223053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2763569355011</t>
+    <t xml:space="preserve">3.23369598388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27635717391968</t>
   </si>
   <si>
     <t xml:space="preserve">3.24222826957703</t>
@@ -884,13 +884,13 @@
     <t xml:space="preserve">3.26782488822937</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31048583984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3446147441864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32755041122437</t>
+    <t xml:space="preserve">3.31048631668091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34461450576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32755064964294</t>
   </si>
   <si>
     <t xml:space="preserve">3.28488922119141</t>
@@ -55427,7 +55427,7 @@
     </row>
     <row r="2053">
       <c r="A2053" s="1" t="n">
-        <v>45953.6121180556</v>
+        <v>45953.2916666667</v>
       </c>
       <c r="B2053" t="n">
         <v>2702</v>
@@ -55448,6 +55448,32 @@
         <v>573</v>
       </c>
       <c r="H2053" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2054">
+      <c r="A2054" s="1" t="n">
+        <v>45954.5892592593</v>
+      </c>
+      <c r="B2054" t="n">
+        <v>3623</v>
+      </c>
+      <c r="C2054" t="n">
+        <v>3.24000000953674</v>
+      </c>
+      <c r="D2054" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="E2054" t="n">
+        <v>3.22000002861023</v>
+      </c>
+      <c r="F2054" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="G2054" t="s">
+        <v>568</v>
+      </c>
+      <c r="H2054" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">2.96519947052002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88901543617249</t>
+    <t xml:space="preserve">2.88901519775391</t>
   </si>
   <si>
     <t xml:space="preserve">2.98013734817505</t>
@@ -56,28 +56,28 @@
     <t xml:space="preserve">2.97266840934753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94577980041504</t>
+    <t xml:space="preserve">2.94578003883362</t>
   </si>
   <si>
     <t xml:space="preserve">2.95773029327393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96221137046814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93532347679138</t>
+    <t xml:space="preserve">2.9622118473053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9353232383728</t>
   </si>
   <si>
     <t xml:space="preserve">2.91291618347168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97864365577698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98611259460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03540849685669</t>
+    <t xml:space="preserve">2.97864389419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98611235618591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03540802001953</t>
   </si>
   <si>
     <t xml:space="preserve">3.05632138252258</t>
@@ -86,7 +86,7 @@
     <t xml:space="preserve">3.0593090057373</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05034637451172</t>
+    <t xml:space="preserve">3.05034613609314</t>
   </si>
   <si>
     <t xml:space="preserve">2.98760628700256</t>
@@ -101,37 +101,37 @@
     <t xml:space="preserve">3.01001358032227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02495121955872</t>
+    <t xml:space="preserve">3.02495145797729</t>
   </si>
   <si>
     <t xml:space="preserve">3.0174822807312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03092646598816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99955677986145</t>
+    <t xml:space="preserve">3.03092670440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99955654144287</t>
   </si>
   <si>
     <t xml:space="preserve">3.0443708896637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.959223985672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00254416465759</t>
+    <t xml:space="preserve">2.95922422409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00254440307617</t>
   </si>
   <si>
     <t xml:space="preserve">2.92785453796387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90843486785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91889119148254</t>
+    <t xml:space="preserve">2.90843510627747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89648461341858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91889142990112</t>
   </si>
   <si>
     <t xml:space="preserve">2.91590404510498</t>
@@ -143,46 +143,46 @@
     <t xml:space="preserve">2.90544700622559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90992856025696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9233729839325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8382260799408</t>
+    <t xml:space="preserve">2.90992879867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92337274551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83822584152222</t>
   </si>
   <si>
     <t xml:space="preserve">2.86063313484192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82627534866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77996778488159</t>
+    <t xml:space="preserve">2.82627558708191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77996802330017</t>
   </si>
   <si>
     <t xml:space="preserve">2.84569501876831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86810183525085</t>
+    <t xml:space="preserve">2.86810207366943</t>
   </si>
   <si>
     <t xml:space="preserve">2.88303995132446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79639959335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87557101249695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89797830581665</t>
+    <t xml:space="preserve">2.79639983177185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87557125091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89797854423523</t>
   </si>
   <si>
     <t xml:space="preserve">2.80088090896606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7426221370697</t>
+    <t xml:space="preserve">2.74262285232544</t>
   </si>
   <si>
     <t xml:space="preserve">2.82179427146912</t>
@@ -191,34 +191,34 @@
     <t xml:space="preserve">2.75009155273438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76353597640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77847385406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78594279289246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79341173171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69631481170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65150046348572</t>
+    <t xml:space="preserve">2.76353573799133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7784743309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78594303131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79341197013855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69631505012512</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6515007019043</t>
   </si>
   <si>
     <t xml:space="preserve">2.62162470817566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53946542739868</t>
+    <t xml:space="preserve">2.53946566581726</t>
   </si>
   <si>
     <t xml:space="preserve">2.5693416595459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61415576934814</t>
+    <t xml:space="preserve">2.61415600776672</t>
   </si>
   <si>
     <t xml:space="preserve">2.65896964073181</t>
@@ -227,25 +227,25 @@
     <t xml:space="preserve">2.68884563446045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70378351211548</t>
+    <t xml:space="preserve">2.70378375053406</t>
   </si>
   <si>
     <t xml:space="preserve">2.77100491523743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81581926345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7336597442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66643834114075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68137645721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74112892150879</t>
+    <t xml:space="preserve">2.81581902503967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73365998268127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66643905639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68137669563293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74112868309021</t>
   </si>
   <si>
     <t xml:space="preserve">2.72619080543518</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">2.69871854782104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83870983123779</t>
+    <t xml:space="preserve">2.83870959281921</t>
   </si>
   <si>
     <t xml:space="preserve">2.93203711509705</t>
@@ -269,16 +269,16 @@
     <t xml:space="preserve">2.87759590148926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83093237876892</t>
+    <t xml:space="preserve">2.8309326171875</t>
   </si>
   <si>
     <t xml:space="preserve">2.81537771224976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84648680686951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79982328414917</t>
+    <t xml:space="preserve">2.84648728370667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79982304573059</t>
   </si>
   <si>
     <t xml:space="preserve">2.73760509490967</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">2.80760049819946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00980997085571</t>
+    <t xml:space="preserve">3.00980973243713</t>
   </si>
   <si>
     <t xml:space="preserve">2.9553689956665</t>
@@ -299,19 +299,19 @@
     <t xml:space="preserve">2.90870523452759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88537335395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82315540313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86204171180725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00203251838684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91648244857788</t>
+    <t xml:space="preserve">2.88537359237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82315492630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86204147338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00203275680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91648268699646</t>
   </si>
   <si>
     <t xml:space="preserve">2.85426425933838</t>
@@ -326,25 +326,25 @@
     <t xml:space="preserve">2.7220504283905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75315928459167</t>
+    <t xml:space="preserve">2.75315952301025</t>
   </si>
   <si>
     <t xml:space="preserve">2.70649576187134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93981432914734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99425554275513</t>
+    <t xml:space="preserve">2.93981409072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99425530433655</t>
   </si>
   <si>
     <t xml:space="preserve">2.97870063781738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86981868743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94759154319763</t>
+    <t xml:space="preserve">2.86981892585754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94759178161621</t>
   </si>
   <si>
     <t xml:space="preserve">2.98647809028625</t>
@@ -353,19 +353,19 @@
     <t xml:space="preserve">2.63650035858154</t>
   </si>
   <si>
-    <t xml:space="preserve">2.550950050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51984071731567</t>
+    <t xml:space="preserve">2.55094981193542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51984095573425</t>
   </si>
   <si>
     <t xml:space="preserve">2.41095876693726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34096336364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34874057769775</t>
+    <t xml:space="preserve">2.34096360206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34874081611633</t>
   </si>
   <si>
     <t xml:space="preserve">2.36429500579834</t>
@@ -377,7 +377,7 @@
     <t xml:space="preserve">2.24763607978821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32540893554688</t>
+    <t xml:space="preserve">2.3254086971283</t>
   </si>
   <si>
     <t xml:space="preserve">2.23208117485046</t>
@@ -389,43 +389,43 @@
     <t xml:space="preserve">2.27874493598938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26319026947021</t>
+    <t xml:space="preserve">2.26319050788879</t>
   </si>
   <si>
     <t xml:space="preserve">2.2165265083313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06875824928284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14653134346008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10764455795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15430855751038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17763996124268</t>
+    <t xml:space="preserve">2.06875848770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1465311050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10764479637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1543083190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17764019966125</t>
   </si>
   <si>
     <t xml:space="preserve">2.22430396080017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35651779174805</t>
+    <t xml:space="preserve">2.35651803016663</t>
   </si>
   <si>
     <t xml:space="preserve">2.4887318611145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52761840820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43429112434387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44206809997559</t>
+    <t xml:space="preserve">2.52761793136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43429088592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44206786155701</t>
   </si>
   <si>
     <t xml:space="preserve">2.5587272644043</t>
@@ -434,10 +434,10 @@
     <t xml:space="preserve">2.44984531402588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37207221984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33318614959717</t>
+    <t xml:space="preserve">2.37207245826721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33318567276001</t>
   </si>
   <si>
     <t xml:space="preserve">2.29429960250854</t>
@@ -452,25 +452,25 @@
     <t xml:space="preserve">2.58205914497375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62872314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.659832239151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57428169250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67538642883301</t>
+    <t xml:space="preserve">2.62872290611267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65983200073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57428193092346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67538666725159</t>
   </si>
   <si>
     <t xml:space="preserve">2.64427757263184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69094133377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76871371269226</t>
+    <t xml:space="preserve">2.69094109535217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76871418952942</t>
   </si>
   <si>
     <t xml:space="preserve">2.90092802047729</t>
@@ -479,13 +479,13 @@
     <t xml:space="preserve">2.9631462097168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92425990104675</t>
+    <t xml:space="preserve">2.92425966262817</t>
   </si>
   <si>
     <t xml:space="preserve">2.97092342376709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01758718490601</t>
+    <t xml:space="preserve">3.01758766174316</t>
   </si>
   <si>
     <t xml:space="preserve">3.04869651794434</t>
@@ -497,16 +497,16 @@
     <t xml:space="preserve">3.06425094604492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07980537414551</t>
+    <t xml:space="preserve">3.07980561256409</t>
   </si>
   <si>
     <t xml:space="preserve">3.0604989528656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02811288833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01191997528076</t>
+    <t xml:space="preserve">3.0281126499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01191973686218</t>
   </si>
   <si>
     <t xml:space="preserve">3.1090784072876</t>
@@ -515,19 +515,19 @@
     <t xml:space="preserve">3.0928852558136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1252715587616</t>
+    <t xml:space="preserve">3.12527132034302</t>
   </si>
   <si>
     <t xml:space="preserve">3.0766921043396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99572682380676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30339574813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41674757003784</t>
+    <t xml:space="preserve">2.99572658538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30339550971985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41674733161926</t>
   </si>
   <si>
     <t xml:space="preserve">3.35197496414185</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">3.33578181266785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36816835403442</t>
+    <t xml:space="preserve">3.36816787719727</t>
   </si>
   <si>
     <t xml:space="preserve">3.23862338066101</t>
@@ -545,64 +545,64 @@
     <t xml:space="preserve">3.31958889961243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27100968360901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28720283508301</t>
+    <t xml:space="preserve">3.27100944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28720259666443</t>
   </si>
   <si>
     <t xml:space="preserve">3.22243022918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17385077476501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20623707771301</t>
+    <t xml:space="preserve">3.17385101318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20623731613159</t>
   </si>
   <si>
     <t xml:space="preserve">3.14146494865417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40055418014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49771332740784</t>
+    <t xml:space="preserve">3.40055465698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49771356582642</t>
   </si>
   <si>
     <t xml:space="preserve">3.38436150550842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25481677055359</t>
+    <t xml:space="preserve">3.25481653213501</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004392623901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96334028244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97953367233276</t>
+    <t xml:space="preserve">2.96334052085876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97953343391418</t>
   </si>
   <si>
     <t xml:space="preserve">2.80140900611877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88237500190735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86618185043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84998846054077</t>
+    <t xml:space="preserve">2.88237476348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86618161201477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84998869895935</t>
   </si>
   <si>
     <t xml:space="preserve">2.78521609306335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75283026695251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72044348716736</t>
+    <t xml:space="preserve">2.75283002853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72044324874878</t>
   </si>
   <si>
     <t xml:space="preserve">2.83379530906677</t>
@@ -623,31 +623,31 @@
     <t xml:space="preserve">2.91476082801819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63947820663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67186403274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62328505516052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68805718421936</t>
+    <t xml:space="preserve">2.6394784450531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67186427116394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62328481674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68805742263794</t>
   </si>
   <si>
     <t xml:space="preserve">2.70425057411194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60709190368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59089875221252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42896747589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54231953620911</t>
+    <t xml:space="preserve">2.60709166526794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5908989906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42896723747253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54231929779053</t>
   </si>
   <si>
     <t xml:space="preserve">2.46135354042053</t>
@@ -656,25 +656,25 @@
     <t xml:space="preserve">2.3156156539917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29942226409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35488152503967</t>
+    <t xml:space="preserve">2.2994225025177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35488176345825</t>
   </si>
   <si>
     <t xml:space="preserve">2.40607476234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28662443161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13304495811462</t>
+    <t xml:space="preserve">2.28662419319153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13304471969604</t>
   </si>
   <si>
     <t xml:space="preserve">2.08185195922852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0647873878479</t>
+    <t xml:space="preserve">2.06478762626648</t>
   </si>
   <si>
     <t xml:space="preserve">2.03065896034241</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">2.09891629219055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26956009864807</t>
+    <t xml:space="preserve">2.26955986022949</t>
   </si>
   <si>
     <t xml:space="preserve">2.2183666229248</t>
@@ -701,16 +701,16 @@
     <t xml:space="preserve">2.54258966445923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45726799964905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5767183303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62791156768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61084723472595</t>
+    <t xml:space="preserve">2.45726823806763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57671856880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62791132926941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61084699630737</t>
   </si>
   <si>
     <t xml:space="preserve">2.64497566223145</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">2.59378266334534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69616889953613</t>
+    <t xml:space="preserve">2.69616913795471</t>
   </si>
   <si>
     <t xml:space="preserve">2.71323323249817</t>
@@ -728,19 +728,19 @@
     <t xml:space="preserve">2.44020342826843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42313885688782</t>
+    <t xml:space="preserve">2.4231390953064</t>
   </si>
   <si>
     <t xml:space="preserve">2.47433233261108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15010952949524</t>
+    <t xml:space="preserve">2.15010929107666</t>
   </si>
   <si>
     <t xml:space="preserve">2.33781743049622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30368852615356</t>
+    <t xml:space="preserve">2.30368876457214</t>
   </si>
   <si>
     <t xml:space="preserve">2.25249552726746</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">2.38901042938232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20130252838135</t>
+    <t xml:space="preserve">2.20130228996277</t>
   </si>
   <si>
     <t xml:space="preserve">2.18423795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01359438896179</t>
+    <t xml:space="preserve">2.01359415054321</t>
   </si>
   <si>
     <t xml:space="preserve">2.04772329330444</t>
@@ -782,10 +782,10 @@
     <t xml:space="preserve">1.97946572303772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86001539230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94533681869507</t>
+    <t xml:space="preserve">1.86001527309418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94533705711365</t>
   </si>
   <si>
     <t xml:space="preserve">1.96240139007568</t>
@@ -794,7 +794,7 @@
     <t xml:space="preserve">1.99653005599976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81561923027039</t>
+    <t xml:space="preserve">2.81561970710754</t>
   </si>
   <si>
     <t xml:space="preserve">2.9009416103363</t>
@@ -803,19 +803,19 @@
     <t xml:space="preserve">2.88387703895569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76442646980286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73029780387878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67910480499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74736213684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83268356323242</t>
+    <t xml:space="preserve">2.76442623138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73029756546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6791045665741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74736189842224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.832683801651</t>
   </si>
   <si>
     <t xml:space="preserve">2.86681246757507</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">2.78149080276489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9350700378418</t>
+    <t xml:space="preserve">2.93507027626038</t>
   </si>
   <si>
     <t xml:space="preserve">2.96919870376587</t>
@@ -839,10 +839,10 @@
     <t xml:space="preserve">3.00332736968994</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03745627403259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98626303672791</t>
+    <t xml:space="preserve">3.03745603561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98626327514648</t>
   </si>
   <si>
     <t xml:space="preserve">3.05452060699463</t>
@@ -854,7 +854,7 @@
     <t xml:space="preserve">3.13984251022339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11424565315247</t>
+    <t xml:space="preserve">3.11424589157104</t>
   </si>
   <si>
     <t xml:space="preserve">3.1313099861145</t>
@@ -866,37 +866,37 @@
     <t xml:space="preserve">3.16543889045715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1995677947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15690684318542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23369598388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27635717391968</t>
+    <t xml:space="preserve">3.19956755638123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15690660476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2336962223053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2763569355011</t>
   </si>
   <si>
     <t xml:space="preserve">3.24222826957703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26782488822937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31048631668091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34461450576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32755064964294</t>
+    <t xml:space="preserve">3.26782464981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31048607826233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34461498260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32755041122437</t>
   </si>
   <si>
     <t xml:space="preserve">3.28488922119141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18250322341919</t>
+    <t xml:space="preserve">3.18250298500061</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342150688171</t>
@@ -905,16 +905,16 @@
     <t xml:space="preserve">3.33710074424744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32836508750916</t>
+    <t xml:space="preserve">3.32836484909058</t>
   </si>
   <si>
     <t xml:space="preserve">3.24974226951599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20606303215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15364742279053</t>
+    <t xml:space="preserve">3.20606279373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15364766120911</t>
   </si>
   <si>
     <t xml:space="preserve">3.21479892730713</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">3.17111945152283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26721405982971</t>
+    <t xml:space="preserve">3.26721382141113</t>
   </si>
   <si>
     <t xml:space="preserve">3.36330842971802</t>
@@ -932,10 +932,10 @@
     <t xml:space="preserve">3.49434661865234</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58170485496521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56423354148865</t>
+    <t xml:space="preserve">3.58170509338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56423330307007</t>
   </si>
   <si>
     <t xml:space="preserve">3.59044122695923</t>
@@ -944,13 +944,13 @@
     <t xml:space="preserve">3.5030825138092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51181817054749</t>
+    <t xml:space="preserve">3.51181840896606</t>
   </si>
   <si>
     <t xml:space="preserve">3.54676175117493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63412022590637</t>
+    <t xml:space="preserve">3.63411998748779</t>
   </si>
   <si>
     <t xml:space="preserve">3.62538456916809</t>
@@ -962,16 +962,16 @@
     <t xml:space="preserve">3.69527125358582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66906356811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60791277885437</t>
+    <t xml:space="preserve">3.66906380653381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60791301727295</t>
   </si>
   <si>
     <t xml:space="preserve">3.55549788475037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66032791137695</t>
+    <t xml:space="preserve">3.66032814979553</t>
   </si>
   <si>
     <t xml:space="preserve">3.65159201622009</t>
@@ -980,13 +980,13 @@
     <t xml:space="preserve">3.68653535842896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70400714874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75642275810242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57296943664551</t>
+    <t xml:space="preserve">3.7040069103241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75642251968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57296967506409</t>
   </si>
   <si>
     <t xml:space="preserve">3.53802609443665</t>
@@ -998,25 +998,25 @@
     <t xml:space="preserve">3.3895161151886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42445969581604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45066714286804</t>
+    <t xml:space="preserve">3.42445993423462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45066738128662</t>
   </si>
   <si>
     <t xml:space="preserve">3.44193148612976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4856104850769</t>
+    <t xml:space="preserve">3.48561072349548</t>
   </si>
   <si>
     <t xml:space="preserve">3.4069881439209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35457253456116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4594030380249</t>
+    <t xml:space="preserve">3.35457229614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45940327644348</t>
   </si>
   <si>
     <t xml:space="preserve">3.52928996086121</t>
@@ -1031,13 +1031,13 @@
     <t xml:space="preserve">3.79136610031128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72147917747498</t>
+    <t xml:space="preserve">3.72147941589355</t>
   </si>
   <si>
     <t xml:space="preserve">3.87872457504272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17574453353882</t>
+    <t xml:space="preserve">4.17574405670166</t>
   </si>
   <si>
     <t xml:space="preserve">4.31551790237427</t>
@@ -1046,13 +1046,13 @@
     <t xml:space="preserve">4.35046148300171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1844801902771</t>
+    <t xml:space="preserve">4.18447971343994</t>
   </si>
   <si>
     <t xml:space="preserve">4.20195150375366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25436639785767</t>
+    <t xml:space="preserve">4.25436687469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.14080047607422</t>
@@ -1064,7 +1064,7 @@
     <t xml:space="preserve">3.98355507850647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94861149787903</t>
+    <t xml:space="preserve">3.94861173629761</t>
   </si>
   <si>
     <t xml:space="preserve">3.93113970756531</t>
@@ -1073,16 +1073,16 @@
     <t xml:space="preserve">4.08838558197021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07091331481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12332916259766</t>
+    <t xml:space="preserve">4.07091379165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1233286857605</t>
   </si>
   <si>
     <t xml:space="preserve">4.00102663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00976276397705</t>
+    <t xml:space="preserve">4.00976324081421</t>
   </si>
   <si>
     <t xml:space="preserve">3.93987584114075</t>
@@ -1100,7 +1100,7 @@
     <t xml:space="preserve">4.28930997848511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21942377090454</t>
+    <t xml:space="preserve">4.21942329406738</t>
   </si>
   <si>
     <t xml:space="preserve">4.19321632385254</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">3.80010175704956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82630944252014</t>
+    <t xml:space="preserve">3.8263099193573</t>
   </si>
   <si>
     <t xml:space="preserve">3.83504557609558</t>
@@ -1133,13 +1133,13 @@
     <t xml:space="preserve">3.84378147125244</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77389430999756</t>
+    <t xml:space="preserve">3.77389454841614</t>
   </si>
   <si>
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734739303589</t>
+    <t xml:space="preserve">3.95734786987305</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
@@ -1148,16 +1148,16 @@
     <t xml:space="preserve">3.86125302314758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76515817642212</t>
+    <t xml:space="preserve">3.76515793800354</t>
   </si>
   <si>
     <t xml:space="preserve">3.81757354736328</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64285635948181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67779946327209</t>
+    <t xml:space="preserve">3.64285612106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67779970169067</t>
   </si>
   <si>
     <t xml:space="preserve">3.7389509677887</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">3.85251712799072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71274304389954</t>
+    <t xml:space="preserve">3.71274328231812</t>
   </si>
   <si>
     <t xml:space="preserve">3.92240381240845</t>
@@ -1175,13 +1175,13 @@
     <t xml:space="preserve">3.61664843559265</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39825224876404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23227071762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05755305290222</t>
+    <t xml:space="preserve">3.39825201034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23227047920227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0575532913208</t>
   </si>
   <si>
     <t xml:space="preserve">2.97019481658936</t>
@@ -1193,10 +1193,10 @@
     <t xml:space="preserve">2.91777944564819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90904331207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37204432487488</t>
+    <t xml:space="preserve">2.90904355049133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3720440864563</t>
   </si>
   <si>
     <t xml:space="preserve">3.38078022003174</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">3.31962895393372</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27595019340515</t>
+    <t xml:space="preserve">3.27594995498657</t>
   </si>
   <si>
     <t xml:space="preserve">3.28468561172485</t>
@@ -55453,7 +55453,7 @@
     </row>
     <row r="2054">
       <c r="A2054" s="1" t="n">
-        <v>45954.5892592593</v>
+        <v>45954.2916666667</v>
       </c>
       <c r="B2054" t="n">
         <v>3623</v>
@@ -55474,6 +55474,32 @@
         <v>568</v>
       </c>
       <c r="H2054" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2055">
+      <c r="A2055" s="1" t="n">
+        <v>45957.5839236111</v>
+      </c>
+      <c r="B2055" t="n">
+        <v>4172</v>
+      </c>
+      <c r="C2055" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="D2055" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="E2055" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="F2055" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="G2055" t="s">
+        <v>568</v>
+      </c>
+      <c r="H2055" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02345728874207</t>
+    <t xml:space="preserve">3.02345752716064</t>
   </si>
   <si>
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519947052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88901519775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98013734817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97266840934753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94577980041504</t>
+    <t xml:space="preserve">2.96519923210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88901543617249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98013758659363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97266817092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94578003883362</t>
   </si>
   <si>
     <t xml:space="preserve">2.95773029327393</t>
@@ -68,22 +68,22 @@
     <t xml:space="preserve">2.9353232383728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91291618347168</t>
+    <t xml:space="preserve">2.91291642189026</t>
   </si>
   <si>
     <t xml:space="preserve">2.97864365577698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98611235618591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03540849685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05632162094116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05930924415588</t>
+    <t xml:space="preserve">2.98611259460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03540802001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05632138252258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05930876731873</t>
   </si>
   <si>
     <t xml:space="preserve">3.05034613609314</t>
@@ -92,13 +92,13 @@
     <t xml:space="preserve">2.98760628700256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95026111602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01598858833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01001381874084</t>
+    <t xml:space="preserve">2.95026159286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01598882675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01001358032227</t>
   </si>
   <si>
     <t xml:space="preserve">3.02495145797729</t>
@@ -113,10 +113,10 @@
     <t xml:space="preserve">2.99955654144287</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0443708896637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95922446250916</t>
+    <t xml:space="preserve">3.04437112808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95922374725342</t>
   </si>
   <si>
     <t xml:space="preserve">3.00254440307617</t>
@@ -125,10 +125,10 @@
     <t xml:space="preserve">2.92785429954529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90843462944031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89648485183716</t>
+    <t xml:space="preserve">2.90843486785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.896484375</t>
   </si>
   <si>
     <t xml:space="preserve">2.91889142990112</t>
@@ -137,7 +137,7 @@
     <t xml:space="preserve">2.9159038066864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92038512229919</t>
+    <t xml:space="preserve">2.92038536071777</t>
   </si>
   <si>
     <t xml:space="preserve">2.90544700622559</t>
@@ -146,7 +146,7 @@
     <t xml:space="preserve">2.90992856025696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9233729839325</t>
+    <t xml:space="preserve">2.92337274551392</t>
   </si>
   <si>
     <t xml:space="preserve">2.83822584152222</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">2.82627558708191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77996802330017</t>
+    <t xml:space="preserve">2.77996754646301</t>
   </si>
   <si>
     <t xml:space="preserve">2.84569501876831</t>
@@ -167,73 +167,73 @@
     <t xml:space="preserve">2.86810183525085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88303995132446</t>
+    <t xml:space="preserve">2.88304018974304</t>
   </si>
   <si>
     <t xml:space="preserve">2.79639935493469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87557077407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89797830581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80088090896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74262237548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82179427146912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7500913143158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76353597640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7784743309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78594279289246</t>
+    <t xml:space="preserve">2.87557101249695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89797806739807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80088114738464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74262261390686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8217945098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75009155273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76353621482849</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77847409248352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78594303131104</t>
   </si>
   <si>
     <t xml:space="preserve">2.79341197013855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69631481170654</t>
+    <t xml:space="preserve">2.69631457328796</t>
   </si>
   <si>
     <t xml:space="preserve">2.6515007019043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62162446975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53946566581726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5693416595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61415600776672</t>
+    <t xml:space="preserve">2.6216242313385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53946542739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56934142112732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61415576934814</t>
   </si>
   <si>
     <t xml:space="preserve">2.65896964073181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68884587287903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70378351211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77100515365601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81581926345825</t>
+    <t xml:space="preserve">2.68884539604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70378398895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77100467681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81581902503967</t>
   </si>
   <si>
     <t xml:space="preserve">2.73366022109985</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">2.66643857955933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68137669563293</t>
+    <t xml:space="preserve">2.68137693405151</t>
   </si>
   <si>
     <t xml:space="preserve">2.74112868309021</t>
@@ -251,19 +251,19 @@
     <t xml:space="preserve">2.72619080543518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8307569026947</t>
+    <t xml:space="preserve">2.83075714111328</t>
   </si>
   <si>
     <t xml:space="preserve">2.893150806427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69871830940247</t>
+    <t xml:space="preserve">2.69871854782104</t>
   </si>
   <si>
     <t xml:space="preserve">2.83870983123779</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93203735351562</t>
+    <t xml:space="preserve">2.93203711509705</t>
   </si>
   <si>
     <t xml:space="preserve">2.87759637832642</t>
@@ -272,16 +272,16 @@
     <t xml:space="preserve">2.83093237876892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81537771224976</t>
+    <t xml:space="preserve">2.81537795066833</t>
   </si>
   <si>
     <t xml:space="preserve">2.84648728370667</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79982304573059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73760509490967</t>
+    <t xml:space="preserve">2.79982328414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73760461807251</t>
   </si>
   <si>
     <t xml:space="preserve">2.76093673706055</t>
@@ -293,91 +293,91 @@
     <t xml:space="preserve">3.00980973243713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9553689956665</t>
+    <t xml:space="preserve">2.95536875724792</t>
   </si>
   <si>
     <t xml:space="preserve">2.90870547294617</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88537335395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82315492630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86204195022583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00203251838684</t>
+    <t xml:space="preserve">2.88537311553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82315516471863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86204147338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00203275680542</t>
   </si>
   <si>
     <t xml:space="preserve">2.91648244857788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85426449775696</t>
+    <t xml:space="preserve">2.85426425933838</t>
   </si>
   <si>
     <t xml:space="preserve">2.7298276424408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68316411972046</t>
+    <t xml:space="preserve">2.68316388130188</t>
   </si>
   <si>
     <t xml:space="preserve">2.7220504283905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75315928459167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70649576187134</t>
+    <t xml:space="preserve">2.75315952301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70649552345276</t>
   </si>
   <si>
     <t xml:space="preserve">2.93981432914734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99425506591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97870063781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86981892585754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94759178161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9864776134491</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63650012016296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.550950050354</t>
+    <t xml:space="preserve">2.99425554275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97870087623596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86981868743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94759154319763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98647809028625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63650035858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55094981193542</t>
   </si>
   <si>
     <t xml:space="preserve">2.51984095573425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41095900535583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34096360206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34874081611633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36429524421692</t>
+    <t xml:space="preserve">2.41095876693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34096336364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34874057769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36429500579834</t>
   </si>
   <si>
     <t xml:space="preserve">2.25541305541992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24763584136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3254086971283</t>
+    <t xml:space="preserve">2.24763560295105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32540917396545</t>
   </si>
   <si>
     <t xml:space="preserve">2.23208117485046</t>
@@ -392,28 +392,28 @@
     <t xml:space="preserve">2.26319050788879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21652674674988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06875824928284</t>
+    <t xml:space="preserve">2.2165265083313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06875801086426</t>
   </si>
   <si>
     <t xml:space="preserve">2.14653134346008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10764455795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1543083190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17764019966125</t>
+    <t xml:space="preserve">2.10764479637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15430855751038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17764043807983</t>
   </si>
   <si>
     <t xml:space="preserve">2.22430372238159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35651779174805</t>
+    <t xml:space="preserve">2.35651803016663</t>
   </si>
   <si>
     <t xml:space="preserve">2.4887318611145</t>
@@ -422,13 +422,13 @@
     <t xml:space="preserve">2.52761816978455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43429088592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44206786155701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55872702598572</t>
+    <t xml:space="preserve">2.43429064750671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44206809997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5587272644043</t>
   </si>
   <si>
     <t xml:space="preserve">2.44984555244446</t>
@@ -437,10 +437,10 @@
     <t xml:space="preserve">2.37207221984863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33318614959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29429960250854</t>
+    <t xml:space="preserve">2.33318591117859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29429984092712</t>
   </si>
   <si>
     <t xml:space="preserve">2.3798496723175</t>
@@ -452,22 +452,22 @@
     <t xml:space="preserve">2.58205890655518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62872266769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65983200073242</t>
+    <t xml:space="preserve">2.62872314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.659832239151</t>
   </si>
   <si>
     <t xml:space="preserve">2.57428193092346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67538690567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64427733421326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69094133377075</t>
+    <t xml:space="preserve">2.67538666725159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64427781105042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69094109535217</t>
   </si>
   <si>
     <t xml:space="preserve">2.76871395111084</t>
@@ -476,25 +476,25 @@
     <t xml:space="preserve">2.90092802047729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96314597129822</t>
+    <t xml:space="preserve">2.9631462097168</t>
   </si>
   <si>
     <t xml:space="preserve">2.92425990104675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97092318534851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01758718490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04869651794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03314185142517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0642511844635</t>
+    <t xml:space="preserve">2.97092342376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01758742332458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04869675636292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03314208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06425094604492</t>
   </si>
   <si>
     <t xml:space="preserve">3.07980561256409</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">3.01191973686218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10907816886902</t>
+    <t xml:space="preserve">3.1090784072876</t>
   </si>
   <si>
     <t xml:space="preserve">3.0928852558136</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">3.30339574813843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41674733161926</t>
+    <t xml:space="preserve">3.41674757003784</t>
   </si>
   <si>
     <t xml:space="preserve">3.35197520256042</t>
@@ -539,16 +539,16 @@
     <t xml:space="preserve">3.36816811561584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23862338066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31958866119385</t>
+    <t xml:space="preserve">3.23862314224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31958889961243</t>
   </si>
   <si>
     <t xml:space="preserve">3.27100944519043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28720259666443</t>
+    <t xml:space="preserve">3.28720235824585</t>
   </si>
   <si>
     <t xml:space="preserve">3.22243022918701</t>
@@ -557,22 +557,22 @@
     <t xml:space="preserve">3.17385101318359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20623707771301</t>
+    <t xml:space="preserve">3.20623731613159</t>
   </si>
   <si>
     <t xml:space="preserve">3.1414647102356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40055465698242</t>
+    <t xml:space="preserve">3.40055418014526</t>
   </si>
   <si>
     <t xml:space="preserve">3.49771332740784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38436102867126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25481653213501</t>
+    <t xml:space="preserve">3.38436126708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25481629371643</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004416465759</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">2.96334052085876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97953367233276</t>
+    <t xml:space="preserve">2.97953343391418</t>
   </si>
   <si>
     <t xml:space="preserve">2.80140924453735</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">2.86618161201477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84998869895935</t>
+    <t xml:space="preserve">2.84998822212219</t>
   </si>
   <si>
     <t xml:space="preserve">2.78521609306335</t>
@@ -602,19 +602,19 @@
     <t xml:space="preserve">2.75282979011536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72044324874878</t>
+    <t xml:space="preserve">2.72044372558594</t>
   </si>
   <si>
     <t xml:space="preserve">2.83379554748535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76902294158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73663663864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81760239601135</t>
+    <t xml:space="preserve">2.76902318000793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73663687705994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81760215759277</t>
   </si>
   <si>
     <t xml:space="preserve">2.89856791496277</t>
@@ -641,43 +641,43 @@
     <t xml:space="preserve">2.60709190368652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5908989906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42896747589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54231953620911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46135377883911</t>
+    <t xml:space="preserve">2.59089851379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42896723747253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54231929779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46135354042053</t>
   </si>
   <si>
     <t xml:space="preserve">2.31561541557312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2994225025177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35488152503967</t>
+    <t xml:space="preserve">2.29942274093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35488176345825</t>
   </si>
   <si>
     <t xml:space="preserve">2.40607476234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28662419319153</t>
+    <t xml:space="preserve">2.28662443161011</t>
   </si>
   <si>
     <t xml:space="preserve">2.13304495811462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08185219764709</t>
+    <t xml:space="preserve">2.08185195922852</t>
   </si>
   <si>
     <t xml:space="preserve">2.06478762626648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03065896034241</t>
+    <t xml:space="preserve">2.03065872192383</t>
   </si>
   <si>
     <t xml:space="preserve">2.1671736240387</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">2.09891629219055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26956009864807</t>
+    <t xml:space="preserve">2.26955986022949</t>
   </si>
   <si>
     <t xml:space="preserve">2.21836686134338</t>
@@ -695,22 +695,22 @@
     <t xml:space="preserve">2.32075309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55965423583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54258966445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45726799964905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5767183303833</t>
+    <t xml:space="preserve">2.55965399742126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54258990287781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45726823806763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57671856880188</t>
   </si>
   <si>
     <t xml:space="preserve">2.62791132926941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61084723472595</t>
+    <t xml:space="preserve">2.61084699630737</t>
   </si>
   <si>
     <t xml:space="preserve">2.64497566223145</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">2.59378266334534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69616913795471</t>
+    <t xml:space="preserve">2.69616889953613</t>
   </si>
   <si>
     <t xml:space="preserve">2.71323323249817</t>
@@ -728,10 +728,10 @@
     <t xml:space="preserve">2.44020342826843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4231390953064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4743320941925</t>
+    <t xml:space="preserve">2.42313933372498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47433233261108</t>
   </si>
   <si>
     <t xml:space="preserve">2.15010929107666</t>
@@ -743,16 +743,16 @@
     <t xml:space="preserve">2.30368852615356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25249552726746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23543095588684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37194633483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38901042938232</t>
+    <t xml:space="preserve">2.25249576568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23543119430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37194609642029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3890106678009</t>
   </si>
   <si>
     <t xml:space="preserve">2.20130252838135</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">2.18423795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01359415054321</t>
+    <t xml:space="preserve">2.01359438896179</t>
   </si>
   <si>
     <t xml:space="preserve">2.04772329330444</t>
@@ -770,34 +770,34 @@
     <t xml:space="preserve">2.11598062515259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91120839118958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8770797252655</t>
+    <t xml:space="preserve">1.91120851039886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87707984447479</t>
   </si>
   <si>
     <t xml:space="preserve">1.84295094013214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97946572303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86001527309418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94533681869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96240139007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99652981758118</t>
+    <t xml:space="preserve">1.97946584224701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86001515388489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94533717632294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96240127086639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99652993679047</t>
   </si>
   <si>
     <t xml:space="preserve">2.81561923027039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9009416103363</t>
+    <t xml:space="preserve">2.90094137191772</t>
   </si>
   <si>
     <t xml:space="preserve">2.88387703895569</t>
@@ -806,13 +806,13 @@
     <t xml:space="preserve">2.76442623138428</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73029780387878</t>
+    <t xml:space="preserve">2.73029756546021</t>
   </si>
   <si>
     <t xml:space="preserve">2.6791045665741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74736213684082</t>
+    <t xml:space="preserve">2.74736189842224</t>
   </si>
   <si>
     <t xml:space="preserve">2.83268356323242</t>
@@ -821,16 +821,16 @@
     <t xml:space="preserve">2.86681246757507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79855513572693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78149080276489</t>
+    <t xml:space="preserve">2.79855489730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78149056434631</t>
   </si>
   <si>
     <t xml:space="preserve">2.9350700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96919870376587</t>
+    <t xml:space="preserve">2.96919846534729</t>
   </si>
   <si>
     <t xml:space="preserve">3.02039194107056</t>
@@ -839,28 +839,28 @@
     <t xml:space="preserve">3.00332713127136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03745627403259</t>
+    <t xml:space="preserve">3.03745603561401</t>
   </si>
   <si>
     <t xml:space="preserve">2.98626303672791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05452036857605</t>
+    <t xml:space="preserve">3.05452060699463</t>
   </si>
   <si>
     <t xml:space="preserve">3.07158470153809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13984251022339</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11424565315247</t>
+    <t xml:space="preserve">3.13984227180481</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11424589157104</t>
   </si>
   <si>
     <t xml:space="preserve">3.1313099861145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06305241584778</t>
+    <t xml:space="preserve">3.06305265426636</t>
   </si>
   <si>
     <t xml:space="preserve">3.16543865203857</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">3.19956755638123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15690660476685</t>
+    <t xml:space="preserve">3.15690684318542</t>
   </si>
   <si>
     <t xml:space="preserve">3.2336962223053</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">3.27635717391968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24222826957703</t>
+    <t xml:space="preserve">3.24222850799561</t>
   </si>
   <si>
     <t xml:space="preserve">3.26782488822937</t>
@@ -893,22 +893,22 @@
     <t xml:space="preserve">3.32755041122437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28488922119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18250322341919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29342126846313</t>
+    <t xml:space="preserve">3.28488945960999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18250346183777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29342150688171</t>
   </si>
   <si>
     <t xml:space="preserve">3.33710074424744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32836508750916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29342150688171</t>
+    <t xml:space="preserve">3.32836484909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29342174530029</t>
   </si>
   <si>
     <t xml:space="preserve">3.24974226951599</t>
@@ -917,13 +917,13 @@
     <t xml:space="preserve">3.20606303215027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15364742279053</t>
+    <t xml:space="preserve">3.15364766120911</t>
   </si>
   <si>
     <t xml:space="preserve">3.21479892730713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17111945152283</t>
+    <t xml:space="preserve">3.17111968994141</t>
   </si>
   <si>
     <t xml:space="preserve">3.26721405982971</t>
@@ -932,10 +932,10 @@
     <t xml:space="preserve">3.36330842971802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49434661865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58170485496521</t>
+    <t xml:space="preserve">3.49434638023376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58170509338379</t>
   </si>
   <si>
     <t xml:space="preserve">3.56423354148865</t>
@@ -950,16 +950,16 @@
     <t xml:space="preserve">3.51181817054749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54676175117493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63412022590637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62538456916809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7476863861084</t>
+    <t xml:space="preserve">3.54676151275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63412046432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62538480758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74768662452698</t>
   </si>
   <si>
     <t xml:space="preserve">3.69527125358582</t>
@@ -968,16 +968,16 @@
     <t xml:space="preserve">3.66906356811523</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60791277885437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55549788475037</t>
+    <t xml:space="preserve">3.60791301727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55549764633179</t>
   </si>
   <si>
     <t xml:space="preserve">3.66032791137695</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65159201622009</t>
+    <t xml:space="preserve">3.65159177780151</t>
   </si>
   <si>
     <t xml:space="preserve">3.68653535842896</t>
@@ -986,25 +986,25 @@
     <t xml:space="preserve">3.70400714874268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75642275810242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57296943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53802609443665</t>
+    <t xml:space="preserve">3.75642251968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57296967506409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53802585601807</t>
   </si>
   <si>
     <t xml:space="preserve">3.3458366394043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3895161151886</t>
+    <t xml:space="preserve">3.38951635360718</t>
   </si>
   <si>
     <t xml:space="preserve">3.42445969581604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45066714286804</t>
+    <t xml:space="preserve">3.45066738128662</t>
   </si>
   <si>
     <t xml:space="preserve">3.44193148612976</t>
@@ -1019,25 +1019,25 @@
     <t xml:space="preserve">3.35457253456116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4594030380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52928996086121</t>
+    <t xml:space="preserve">3.45940327644348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52928972244263</t>
   </si>
   <si>
     <t xml:space="preserve">3.46813893318176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47687482833862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79136610031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72147917747498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87872457504272</t>
+    <t xml:space="preserve">3.47687458992004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79136633872986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7214789390564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8787248134613</t>
   </si>
   <si>
     <t xml:space="preserve">4.17574453353882</t>
@@ -1049,37 +1049,37 @@
     <t xml:space="preserve">4.35046148300171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1844801902771</t>
+    <t xml:space="preserve">4.18447971343994</t>
   </si>
   <si>
     <t xml:space="preserve">4.20195150375366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25436639785767</t>
+    <t xml:space="preserve">4.25436687469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493226051331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98355507850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94861149787903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93113970756531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08838558197021</t>
+    <t xml:space="preserve">3.90493202209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98355484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94861197471619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93114018440247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08838510513306</t>
   </si>
   <si>
     <t xml:space="preserve">4.07091331481934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12332916259766</t>
+    <t xml:space="preserve">4.1233286857605</t>
   </si>
   <si>
     <t xml:space="preserve">4.00102663040161</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">4.00976276397705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93987584114075</t>
+    <t xml:space="preserve">3.93987607955933</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
@@ -1100,16 +1100,16 @@
     <t xml:space="preserve">4.29804611206055</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28930997848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21942377090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19321632385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14953660964966</t>
+    <t xml:space="preserve">4.28931045532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21942329406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19321584701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1495361328125</t>
   </si>
   <si>
     <t xml:space="preserve">4.16700792312622</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">4.11459302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06217765808105</t>
+    <t xml:space="preserve">4.06217813491821</t>
   </si>
   <si>
     <t xml:space="preserve">3.78262996673584</t>
@@ -1127,22 +1127,22 @@
     <t xml:space="preserve">3.80010175704956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82630944252014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83504557609558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84378147125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77389430999756</t>
+    <t xml:space="preserve">3.82630968093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83504509925842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84378099441528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77389454841614</t>
   </si>
   <si>
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734739303589</t>
+    <t xml:space="preserve">3.95734786987305</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
@@ -1151,22 +1151,22 @@
     <t xml:space="preserve">3.86125302314758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76515817642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81757354736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64285635948181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67779946327209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7389509677887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85251712799072</t>
+    <t xml:space="preserve">3.76515865325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8175733089447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64285612106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67779970169067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73895072937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85251665115356</t>
   </si>
   <si>
     <t xml:space="preserve">3.71274304389954</t>
@@ -1175,7 +1175,7 @@
     <t xml:space="preserve">3.92240381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61664843559265</t>
+    <t xml:space="preserve">3.61664867401123</t>
   </si>
   <si>
     <t xml:space="preserve">3.39825224876404</t>
@@ -1184,16 +1184,16 @@
     <t xml:space="preserve">3.23227071762085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05755305290222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97019481658936</t>
+    <t xml:space="preserve">3.0575532913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97019457817078</t>
   </si>
   <si>
     <t xml:space="preserve">2.95272302627563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91777944564819</t>
+    <t xml:space="preserve">2.91777920722961</t>
   </si>
   <si>
     <t xml:space="preserve">2.90904331207275</t>
@@ -1211,10 +1211,10 @@
     <t xml:space="preserve">3.31962895393372</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27595019340515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28468561172485</t>
+    <t xml:space="preserve">3.27594995498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28468585014343</t>
   </si>
   <si>
     <t xml:space="preserve">3.50245499610901</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">3.32098078727722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26653814315796</t>
+    <t xml:space="preserve">3.26653838157654</t>
   </si>
   <si>
     <t xml:space="preserve">3.39357042312622</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">3.23024344444275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19394874572754</t>
+    <t xml:space="preserve">3.19394850730896</t>
   </si>
   <si>
     <t xml:space="preserve">3.25746440887451</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">3.2211697101593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10321140289307</t>
+    <t xml:space="preserve">3.10321164131165</t>
   </si>
   <si>
     <t xml:space="preserve">2.99432682991028</t>
@@ -1286,13 +1286,13 @@
     <t xml:space="preserve">2.95803189277649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85822105407715</t>
+    <t xml:space="preserve">2.85822129249573</t>
   </si>
   <si>
     <t xml:space="preserve">2.89451599121094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8672947883606</t>
+    <t xml:space="preserve">2.86729502677917</t>
   </si>
   <si>
     <t xml:space="preserve">2.81285238265991</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">2.75841021537781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70396780967712</t>
+    <t xml:space="preserve">2.7039680480957</t>
   </si>
   <si>
     <t xml:space="preserve">2.72211527824402</t>
@@ -1313,16 +1313,16 @@
     <t xml:space="preserve">2.64952564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7947051525116</t>
+    <t xml:space="preserve">2.79470491409302</t>
   </si>
   <si>
     <t xml:space="preserve">2.92173719406128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05784273147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02154803276062</t>
+    <t xml:space="preserve">3.05784296989441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02154779434204</t>
   </si>
   <si>
     <t xml:space="preserve">3.13950634002686</t>
@@ -1352,46 +1352,46 @@
     <t xml:space="preserve">3.08506417274475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01247429847717</t>
+    <t xml:space="preserve">3.01247406005859</t>
   </si>
   <si>
     <t xml:space="preserve">2.88544225692749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7765576839447</t>
+    <t xml:space="preserve">2.77655744552612</t>
   </si>
   <si>
     <t xml:space="preserve">2.71304154396057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6313784122467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68582034111023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66767287254333</t>
+    <t xml:space="preserve">2.63137817382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68582057952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66767311096191</t>
   </si>
   <si>
     <t xml:space="preserve">2.55878829956055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52249336242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67674660682678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64045214653015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87636852264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83099985122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60415697097778</t>
+    <t xml:space="preserve">2.52249360084534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67674684524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64045190811157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87636876106262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83099961280823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6041567325592</t>
   </si>
   <si>
     <t xml:space="preserve">2.73118901252747</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">2.91266345977783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12135887145996</t>
+    <t xml:space="preserve">3.12135910987854</t>
   </si>
   <si>
     <t xml:space="preserve">3.0759904384613</t>
@@ -1427,46 +1427,46 @@
     <t xml:space="preserve">3.0941379070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38449692726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41171765327454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37542319297791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42079138755798</t>
+    <t xml:space="preserve">3.38449668884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41171789169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37542295455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42079162597656</t>
   </si>
   <si>
     <t xml:space="preserve">3.43893885612488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36634945869446</t>
+    <t xml:space="preserve">3.36634922027588</t>
   </si>
   <si>
     <t xml:space="preserve">3.35727572441101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20302248001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27561187744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29375958442688</t>
+    <t xml:space="preserve">3.20302224159241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27561211585999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29375982284546</t>
   </si>
   <si>
     <t xml:space="preserve">3.1667275428772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11228513717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78563141822815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84007382392883</t>
+    <t xml:space="preserve">3.11228537559509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78563117980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84007358551025</t>
   </si>
   <si>
     <t xml:space="preserve">2.82192611694336</t>
@@ -55560,7 +55560,7 @@
     </row>
     <row r="2058">
       <c r="A2058" s="1" t="n">
-        <v>45960.6832060185</v>
+        <v>45960.3333333333</v>
       </c>
       <c r="B2058" t="n">
         <v>25562</v>
@@ -55581,6 +55581,32 @@
         <v>554</v>
       </c>
       <c r="H2058" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2059">
+      <c r="A2059" s="1" t="n">
+        <v>45961.6833449074</v>
+      </c>
+      <c r="B2059" t="n">
+        <v>4392</v>
+      </c>
+      <c r="C2059" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="D2059" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="E2059" t="n">
+        <v>3.05999994277954</v>
+      </c>
+      <c r="F2059" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="G2059" t="s">
+        <v>555</v>
+      </c>
+      <c r="H2059" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -38,31 +38,31 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02345728874207</t>
+    <t xml:space="preserve">3.02345752716064</t>
   </si>
   <si>
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519923210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88901519775391</t>
+    <t xml:space="preserve">2.96519947052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88901543617249</t>
   </si>
   <si>
     <t xml:space="preserve">2.98013734817505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97266817092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94577980041504</t>
+    <t xml:space="preserve">2.97266840934753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94578003883362</t>
   </si>
   <si>
     <t xml:space="preserve">2.95773029327393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9622118473053</t>
+    <t xml:space="preserve">2.96221160888672</t>
   </si>
   <si>
     <t xml:space="preserve">2.93532347679138</t>
@@ -71,22 +71,22 @@
     <t xml:space="preserve">2.91291618347168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97864365577698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98611235618591</t>
+    <t xml:space="preserve">2.9786434173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98611259460449</t>
   </si>
   <si>
     <t xml:space="preserve">3.03540802001953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05632162094116</t>
+    <t xml:space="preserve">3.056321144104</t>
   </si>
   <si>
     <t xml:space="preserve">3.0593090057373</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05034637451172</t>
+    <t xml:space="preserve">3.05034613609314</t>
   </si>
   <si>
     <t xml:space="preserve">2.98760628700256</t>
@@ -101,46 +101,46 @@
     <t xml:space="preserve">3.01001358032227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02495145797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0174822807312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03092670440674</t>
+    <t xml:space="preserve">3.02495169639587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01748251914978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03092646598816</t>
   </si>
   <si>
     <t xml:space="preserve">2.99955677986145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0443708896637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95922422409058</t>
+    <t xml:space="preserve">3.04437112808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.959223985672</t>
   </si>
   <si>
     <t xml:space="preserve">3.00254440307617</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92785406112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90843486785889</t>
+    <t xml:space="preserve">2.92785429954529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90843462944031</t>
   </si>
   <si>
     <t xml:space="preserve">2.89648461341858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91889119148254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91590356826782</t>
+    <t xml:space="preserve">2.91889142990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9159038066864</t>
   </si>
   <si>
     <t xml:space="preserve">2.92038536071777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90544748306274</t>
+    <t xml:space="preserve">2.90544724464417</t>
   </si>
   <si>
     <t xml:space="preserve">2.90992856025696</t>
@@ -152,49 +152,49 @@
     <t xml:space="preserve">2.8382260799408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86063289642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82627534866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77996754646301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84569501876831</t>
+    <t xml:space="preserve">2.86063313484192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82627558708191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77996778488159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84569525718689</t>
   </si>
   <si>
     <t xml:space="preserve">2.86810207366943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88304018974304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79639959335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87557077407837</t>
+    <t xml:space="preserve">2.88303995132446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79639935493469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87557101249695</t>
   </si>
   <si>
     <t xml:space="preserve">2.89797806739807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80088090896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74262237548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82179403305054</t>
+    <t xml:space="preserve">2.80088114738464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74262285232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82179427146912</t>
   </si>
   <si>
     <t xml:space="preserve">2.75009155273438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76353597640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77847385406494</t>
+    <t xml:space="preserve">2.76353573799133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77847361564636</t>
   </si>
   <si>
     <t xml:space="preserve">2.78594303131104</t>
@@ -209,28 +209,28 @@
     <t xml:space="preserve">2.6515007019043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62162446975708</t>
+    <t xml:space="preserve">2.62162470817566</t>
   </si>
   <si>
     <t xml:space="preserve">2.5394651889801</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56934142112732</t>
+    <t xml:space="preserve">2.5693416595459</t>
   </si>
   <si>
     <t xml:space="preserve">2.61415553092957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65896964073181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68884587287903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70378375053406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77100491523743</t>
+    <t xml:space="preserve">2.65896940231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68884563446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70378351211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77100515365601</t>
   </si>
   <si>
     <t xml:space="preserve">2.81581902503967</t>
@@ -239,25 +239,25 @@
     <t xml:space="preserve">2.7336597442627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66643834114075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68137669563293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74112868309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7261905670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83075666427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89315056800842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69871878623962</t>
+    <t xml:space="preserve">2.66643881797791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68137693405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74112892150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72619104385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83075714111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.893150806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69871854782104</t>
   </si>
   <si>
     <t xml:space="preserve">2.83870959281921</t>
@@ -266,67 +266,67 @@
     <t xml:space="preserve">2.93203711509705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87759590148926</t>
+    <t xml:space="preserve">2.87759613990784</t>
   </si>
   <si>
     <t xml:space="preserve">2.8309326171875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81537795066833</t>
+    <t xml:space="preserve">2.81537771224976</t>
   </si>
   <si>
     <t xml:space="preserve">2.84648680686951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79982328414917</t>
+    <t xml:space="preserve">2.79982304573059</t>
   </si>
   <si>
     <t xml:space="preserve">2.73760485649109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76093673706055</t>
+    <t xml:space="preserve">2.76093697547913</t>
   </si>
   <si>
     <t xml:space="preserve">2.80760049819946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00980997085571</t>
+    <t xml:space="preserve">3.00980973243713</t>
   </si>
   <si>
     <t xml:space="preserve">2.95536875724792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90870499610901</t>
+    <t xml:space="preserve">2.90870523452759</t>
   </si>
   <si>
     <t xml:space="preserve">2.88537335395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82315564155579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86204171180725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00203275680542</t>
+    <t xml:space="preserve">2.82315492630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86204147338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00203251838684</t>
   </si>
   <si>
     <t xml:space="preserve">2.91648244857788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85426425933838</t>
+    <t xml:space="preserve">2.85426449775696</t>
   </si>
   <si>
     <t xml:space="preserve">2.7298276424408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68316388130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7220504283905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75315928459167</t>
+    <t xml:space="preserve">2.68316411972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72205018997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75315976142883</t>
   </si>
   <si>
     <t xml:space="preserve">2.70649576187134</t>
@@ -335,37 +335,37 @@
     <t xml:space="preserve">2.93981432914734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99425530433655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97870087623596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86981892585754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94759130477905</t>
+    <t xml:space="preserve">2.99425554275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97870063781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86981868743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94759202003479</t>
   </si>
   <si>
     <t xml:space="preserve">2.98647809028625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63650012016296</t>
+    <t xml:space="preserve">2.63650059700012</t>
   </si>
   <si>
     <t xml:space="preserve">2.550950050354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51984095573425</t>
+    <t xml:space="preserve">2.51984071731567</t>
   </si>
   <si>
     <t xml:space="preserve">2.41095876693726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34096336364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34874081611633</t>
+    <t xml:space="preserve">2.34096312522888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34874057769775</t>
   </si>
   <si>
     <t xml:space="preserve">2.36429500579834</t>
@@ -374,7 +374,7 @@
     <t xml:space="preserve">2.2554132938385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24763607978821</t>
+    <t xml:space="preserve">2.24763584136963</t>
   </si>
   <si>
     <t xml:space="preserve">2.32540893554688</t>
@@ -386,46 +386,46 @@
     <t xml:space="preserve">2.18541765213013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27874493598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26319026947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21652674674988</t>
+    <t xml:space="preserve">2.27874517440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26319003105164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2165265083313</t>
   </si>
   <si>
     <t xml:space="preserve">2.06875824928284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14653134346008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10764455795288</t>
+    <t xml:space="preserve">2.1465311050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10764479637146</t>
   </si>
   <si>
     <t xml:space="preserve">2.15430855751038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17764019966125</t>
+    <t xml:space="preserve">2.17764043807983</t>
   </si>
   <si>
     <t xml:space="preserve">2.22430396080017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35651803016663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4887318611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52761840820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43429088592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44206809997559</t>
+    <t xml:space="preserve">2.35651779174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48873209953308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52761793136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43429064750671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44206833839417</t>
   </si>
   <si>
     <t xml:space="preserve">2.55872750282288</t>
@@ -434,31 +434,31 @@
     <t xml:space="preserve">2.44984531402588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37207221984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33318614959717</t>
+    <t xml:space="preserve">2.37207269668579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33318591117859</t>
   </si>
   <si>
     <t xml:space="preserve">2.29429960250854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37984943389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71427321434021</t>
+    <t xml:space="preserve">2.3798496723175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71427297592163</t>
   </si>
   <si>
     <t xml:space="preserve">2.58205890655518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62872290611267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65983247756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57428169250488</t>
+    <t xml:space="preserve">2.62872314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65983200073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57428193092346</t>
   </si>
   <si>
     <t xml:space="preserve">2.67538666725159</t>
@@ -470,25 +470,25 @@
     <t xml:space="preserve">2.69094133377075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76871395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90092802047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9631462097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92426013946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97092366218567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01758742332458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04869627952576</t>
+    <t xml:space="preserve">2.76871418952942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90092825889587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96314597129822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92425990104675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97092342376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01758766174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04869651794434</t>
   </si>
   <si>
     <t xml:space="preserve">3.03314185142517</t>
@@ -497,16 +497,16 @@
     <t xml:space="preserve">3.0642511844635</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07980561256409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06049919128418</t>
+    <t xml:space="preserve">3.07980585098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0604989528656</t>
   </si>
   <si>
     <t xml:space="preserve">3.02811288833618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01191997528076</t>
+    <t xml:space="preserve">3.01191973686218</t>
   </si>
   <si>
     <t xml:space="preserve">3.1090784072876</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">3.12527132034302</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07669234275818</t>
+    <t xml:space="preserve">3.07669186592102</t>
   </si>
   <si>
     <t xml:space="preserve">2.99572658538818</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">3.30339574813843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41674733161926</t>
+    <t xml:space="preserve">3.41674757003784</t>
   </si>
   <si>
     <t xml:space="preserve">3.35197496414185</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33578205108643</t>
+    <t xml:space="preserve">3.33578181266785</t>
   </si>
   <si>
     <t xml:space="preserve">3.36816811561584</t>
@@ -548,28 +548,28 @@
     <t xml:space="preserve">3.27100944519043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28720235824585</t>
+    <t xml:space="preserve">3.28720259666443</t>
   </si>
   <si>
     <t xml:space="preserve">3.22243022918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17385125160217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20623707771301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1414647102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40055418014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49771332740784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38436126708984</t>
+    <t xml:space="preserve">3.17385101318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20623731613159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14146494865417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40055441856384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49771356582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38436102867126</t>
   </si>
   <si>
     <t xml:space="preserve">3.25481653213501</t>
@@ -581,19 +581,19 @@
     <t xml:space="preserve">2.96334028244019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97953367233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80140900611877</t>
+    <t xml:space="preserve">2.97953343391418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80140924453735</t>
   </si>
   <si>
     <t xml:space="preserve">2.88237476348877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86618161201477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84998822212219</t>
+    <t xml:space="preserve">2.86618185043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84998846054077</t>
   </si>
   <si>
     <t xml:space="preserve">2.78521609306335</t>
@@ -617,10 +617,10 @@
     <t xml:space="preserve">2.81760239601135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89856767654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91476106643677</t>
+    <t xml:space="preserve">2.89856791496277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91476082801819</t>
   </si>
   <si>
     <t xml:space="preserve">2.63947796821594</t>
@@ -629,7 +629,7 @@
     <t xml:space="preserve">2.67186403274536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62328505516052</t>
+    <t xml:space="preserve">2.62328481674194</t>
   </si>
   <si>
     <t xml:space="preserve">2.68805718421936</t>
@@ -638,19 +638,19 @@
     <t xml:space="preserve">2.70425057411194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60709166526794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59089875221252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42896771430969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54231929779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46135377883911</t>
+    <t xml:space="preserve">2.60709190368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5908989906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42896747589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54231953620911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46135354042053</t>
   </si>
   <si>
     <t xml:space="preserve">2.3156156539917</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">2.29942274093628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35488176345825</t>
+    <t xml:space="preserve">2.35488152503967</t>
   </si>
   <si>
     <t xml:space="preserve">2.40607476234436</t>
@@ -671,13 +671,13 @@
     <t xml:space="preserve">2.13304495811462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08185195922852</t>
+    <t xml:space="preserve">2.08185219764709</t>
   </si>
   <si>
     <t xml:space="preserve">2.06478762626648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03065872192383</t>
+    <t xml:space="preserve">2.03065896034241</t>
   </si>
   <si>
     <t xml:space="preserve">2.1671736240387</t>
@@ -707,49 +707,49 @@
     <t xml:space="preserve">2.5767183303833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62791156768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61084699630737</t>
+    <t xml:space="preserve">2.62791132926941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61084723472595</t>
   </si>
   <si>
     <t xml:space="preserve">2.64497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59378290176392</t>
+    <t xml:space="preserve">2.59378266334534</t>
   </si>
   <si>
     <t xml:space="preserve">2.69616913795471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71323347091675</t>
+    <t xml:space="preserve">2.71323323249817</t>
   </si>
   <si>
     <t xml:space="preserve">2.44020342826843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42313933372498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47433233261108</t>
+    <t xml:space="preserve">2.4231390953064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4743320941925</t>
   </si>
   <si>
     <t xml:space="preserve">2.15010929107666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33781743049622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30368876457214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25249576568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23543119430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37194609642029</t>
+    <t xml:space="preserve">2.33781719207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30368852615356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25249552726746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23543095588684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37194633483887</t>
   </si>
   <si>
     <t xml:space="preserve">2.38901042938232</t>
@@ -767,43 +767,43 @@
     <t xml:space="preserve">2.04772329330444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11598038673401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91120827198029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87707984447479</t>
+    <t xml:space="preserve">2.11598062515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91120839118958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8770797252655</t>
   </si>
   <si>
     <t xml:space="preserve">1.84295094013214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97946560382843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86001515388489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94533693790436</t>
+    <t xml:space="preserve">1.97946572303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86001527309418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94533681869507</t>
   </si>
   <si>
     <t xml:space="preserve">1.96240139007568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99653005599976</t>
+    <t xml:space="preserve">1.99652981758118</t>
   </si>
   <si>
     <t xml:space="preserve">2.81561923027039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90094137191772</t>
+    <t xml:space="preserve">2.9009416103363</t>
   </si>
   <si>
     <t xml:space="preserve">2.88387703895569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76442646980286</t>
+    <t xml:space="preserve">2.76442623138428</t>
   </si>
   <si>
     <t xml:space="preserve">2.73029780387878</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">2.6791045665741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74736189842224</t>
+    <t xml:space="preserve">2.74736213684082</t>
   </si>
   <si>
     <t xml:space="preserve">2.83268356323242</t>
@@ -824,7 +824,7 @@
     <t xml:space="preserve">2.79855513572693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78149056434631</t>
+    <t xml:space="preserve">2.78149080276489</t>
   </si>
   <si>
     <t xml:space="preserve">2.9350700378418</t>
@@ -833,40 +833,40 @@
     <t xml:space="preserve">2.96919870376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02039170265198</t>
+    <t xml:space="preserve">3.02039194107056</t>
   </si>
   <si>
     <t xml:space="preserve">3.00332713127136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03745603561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98626279830933</t>
+    <t xml:space="preserve">3.03745627403259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98626303672791</t>
   </si>
   <si>
     <t xml:space="preserve">3.05452036857605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07158493995667</t>
+    <t xml:space="preserve">3.07158470153809</t>
   </si>
   <si>
     <t xml:space="preserve">3.13984251022339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11424589157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13131022453308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06305265426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16543889045715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1995677947998</t>
+    <t xml:space="preserve">3.11424565315247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1313099861145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06305241584778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16543865203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19956755638123</t>
   </si>
   <si>
     <t xml:space="preserve">3.15690660476685</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">3.27635717391968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24222850799561</t>
+    <t xml:space="preserve">3.24222826957703</t>
   </si>
   <si>
     <t xml:space="preserve">3.26782488822937</t>
@@ -887,10 +887,10 @@
     <t xml:space="preserve">3.31048607826233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34461498260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32755017280579</t>
+    <t xml:space="preserve">3.3446147441864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32755041122437</t>
   </si>
   <si>
     <t xml:space="preserve">3.28488922119141</t>
@@ -914,46 +914,46 @@
     <t xml:space="preserve">3.24974226951599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20606279373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15364766120911</t>
+    <t xml:space="preserve">3.20606303215027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15364742279053</t>
   </si>
   <si>
     <t xml:space="preserve">3.21479892730713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17111968994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26721382141113</t>
+    <t xml:space="preserve">3.17111945152283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26721405982971</t>
   </si>
   <si>
     <t xml:space="preserve">3.36330842971802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49434638023376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58170533180237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56423330307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59044098854065</t>
+    <t xml:space="preserve">3.49434661865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58170485496521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56423354148865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59044122695923</t>
   </si>
   <si>
     <t xml:space="preserve">3.5030825138092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51181840896606</t>
+    <t xml:space="preserve">3.51181817054749</t>
   </si>
   <si>
     <t xml:space="preserve">3.54676175117493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63411998748779</t>
+    <t xml:space="preserve">3.63412022590637</t>
   </si>
   <si>
     <t xml:space="preserve">3.62538456916809</t>
@@ -962,10 +962,10 @@
     <t xml:space="preserve">3.7476863861084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69527149200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66906380653381</t>
+    <t xml:space="preserve">3.69527125358582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66906356811523</t>
   </si>
   <si>
     <t xml:space="preserve">3.60791277885437</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">3.55549788475037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66032814979553</t>
+    <t xml:space="preserve">3.66032791137695</t>
   </si>
   <si>
     <t xml:space="preserve">3.65159201622009</t>
@@ -983,37 +983,37 @@
     <t xml:space="preserve">3.68653535842896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7040069103241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75642251968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57296967506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53802585601807</t>
+    <t xml:space="preserve">3.70400714874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75642275810242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57296943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53802609443665</t>
   </si>
   <si>
     <t xml:space="preserve">3.3458366394043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38951635360718</t>
+    <t xml:space="preserve">3.3895161151886</t>
   </si>
   <si>
     <t xml:space="preserve">3.42445969581604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45066738128662</t>
+    <t xml:space="preserve">3.45066714286804</t>
   </si>
   <si>
     <t xml:space="preserve">3.44193148612976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48561072349548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40698790550232</t>
+    <t xml:space="preserve">3.4856104850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4069881439209</t>
   </si>
   <si>
     <t xml:space="preserve">3.35457253456116</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">3.46813893318176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47687458992004</t>
+    <t xml:space="preserve">3.47687482833862</t>
   </si>
   <si>
     <t xml:space="preserve">3.79136610031128</t>
@@ -1040,22 +1040,22 @@
     <t xml:space="preserve">3.87872457504272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17574405670166</t>
+    <t xml:space="preserve">4.17574453353882</t>
   </si>
   <si>
     <t xml:space="preserve">4.31551790237427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35046100616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18447971343994</t>
+    <t xml:space="preserve">4.35046148300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1844801902771</t>
   </si>
   <si>
     <t xml:space="preserve">4.20195150375366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25436687469482</t>
+    <t xml:space="preserve">4.25436639785767</t>
   </si>
   <si>
     <t xml:space="preserve">4.14080047607422</t>
@@ -1067,19 +1067,19 @@
     <t xml:space="preserve">3.98355507850647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94861173629761</t>
+    <t xml:space="preserve">3.94861149787903</t>
   </si>
   <si>
     <t xml:space="preserve">3.93113970756531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08838510513306</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07091379165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12332820892334</t>
+    <t xml:space="preserve">4.08838558197021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07091331481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12332916259766</t>
   </si>
   <si>
     <t xml:space="preserve">4.00102663040161</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">4.00976276397705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93987560272217</t>
+    <t xml:space="preserve">3.93987584114075</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
@@ -1097,13 +1097,13 @@
     <t xml:space="preserve">4.2106876373291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29804658889771</t>
+    <t xml:space="preserve">4.29804611206055</t>
   </si>
   <si>
     <t xml:space="preserve">4.28930997848511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21942329406738</t>
+    <t xml:space="preserve">4.21942377090454</t>
   </si>
   <si>
     <t xml:space="preserve">4.19321632385254</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">4.14953660964966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16700839996338</t>
+    <t xml:space="preserve">4.16700792312622</t>
   </si>
   <si>
     <t xml:space="preserve">4.11459302902222</t>
@@ -1121,46 +1121,46 @@
     <t xml:space="preserve">4.06217765808105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78263020515442</t>
+    <t xml:space="preserve">3.78262996673584</t>
   </si>
   <si>
     <t xml:space="preserve">3.80010175704956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82630968093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.835045337677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84378123283386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77389454841614</t>
+    <t xml:space="preserve">3.82630944252014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83504557609558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84378147125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77389430999756</t>
   </si>
   <si>
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734763145447</t>
+    <t xml:space="preserve">3.95734739303589</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.861252784729</t>
+    <t xml:space="preserve">3.86125302314758</t>
   </si>
   <si>
     <t xml:space="preserve">3.76515817642212</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8175733089447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64285612106323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67779970169067</t>
+    <t xml:space="preserve">3.81757354736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64285635948181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67779946327209</t>
   </si>
   <si>
     <t xml:space="preserve">3.7389509677887</t>
@@ -1169,10 +1169,10 @@
     <t xml:space="preserve">3.85251712799072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71274328231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92240357398987</t>
+    <t xml:space="preserve">3.71274304389954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92240381240845</t>
   </si>
   <si>
     <t xml:space="preserve">3.61664843559265</t>
@@ -1181,40 +1181,40 @@
     <t xml:space="preserve">3.39825224876404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23227047920227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05755352973938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97019457817078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95272278785706</t>
+    <t xml:space="preserve">3.23227071762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05755305290222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97019481658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95272302627563</t>
   </si>
   <si>
     <t xml:space="preserve">2.91777944564819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90904355049133</t>
+    <t xml:space="preserve">2.90904331207275</t>
   </si>
   <si>
     <t xml:space="preserve">3.37204432487488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38077998161316</t>
+    <t xml:space="preserve">3.38078022003174</t>
   </si>
   <si>
     <t xml:space="preserve">3.41572380065918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31962919235229</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27594995498657</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28468585014343</t>
+    <t xml:space="preserve">3.31962895393372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27595019340515</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28468561172485</t>
   </si>
   <si>
     <t xml:space="preserve">3.50245499610901</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">3.32098078727722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26653838157654</t>
+    <t xml:space="preserve">3.26653814315796</t>
   </si>
   <si>
     <t xml:space="preserve">3.39357042312622</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">3.23024344444275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19394850730896</t>
+    <t xml:space="preserve">3.19394874572754</t>
   </si>
   <si>
     <t xml:space="preserve">3.25746440887451</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">3.2211697101593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10321164131165</t>
+    <t xml:space="preserve">3.10321140289307</t>
   </si>
   <si>
     <t xml:space="preserve">2.99432682991028</t>
@@ -1286,13 +1286,13 @@
     <t xml:space="preserve">2.95803189277649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85822129249573</t>
+    <t xml:space="preserve">2.85822105407715</t>
   </si>
   <si>
     <t xml:space="preserve">2.89451599121094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86729502677917</t>
+    <t xml:space="preserve">2.8672947883606</t>
   </si>
   <si>
     <t xml:space="preserve">2.81285238265991</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">2.75841021537781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7039680480957</t>
+    <t xml:space="preserve">2.70396780967712</t>
   </si>
   <si>
     <t xml:space="preserve">2.72211527824402</t>
@@ -1313,16 +1313,16 @@
     <t xml:space="preserve">2.64952564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79470491409302</t>
+    <t xml:space="preserve">2.7947051525116</t>
   </si>
   <si>
     <t xml:space="preserve">2.92173719406128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05784296989441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02154779434204</t>
+    <t xml:space="preserve">3.05784273147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02154803276062</t>
   </si>
   <si>
     <t xml:space="preserve">3.13950634002686</t>
@@ -1352,46 +1352,46 @@
     <t xml:space="preserve">3.08506417274475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01247406005859</t>
+    <t xml:space="preserve">3.01247429847717</t>
   </si>
   <si>
     <t xml:space="preserve">2.88544225692749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77655744552612</t>
+    <t xml:space="preserve">2.7765576839447</t>
   </si>
   <si>
     <t xml:space="preserve">2.71304154396057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63137817382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68582057952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66767311096191</t>
+    <t xml:space="preserve">2.6313784122467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68582034111023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66767287254333</t>
   </si>
   <si>
     <t xml:space="preserve">2.55878829956055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52249360084534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67674684524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64045190811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87636876106262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83099961280823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6041567325592</t>
+    <t xml:space="preserve">2.52249336242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67674660682678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64045214653015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87636852264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83099985122681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60415697097778</t>
   </si>
   <si>
     <t xml:space="preserve">2.73118901252747</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">2.91266345977783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12135910987854</t>
+    <t xml:space="preserve">3.12135887145996</t>
   </si>
   <si>
     <t xml:space="preserve">3.0759904384613</t>
@@ -1427,46 +1427,46 @@
     <t xml:space="preserve">3.0941379070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38449668884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41171789169312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37542295455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42079162597656</t>
+    <t xml:space="preserve">3.38449692726135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41171765327454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37542319297791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42079138755798</t>
   </si>
   <si>
     <t xml:space="preserve">3.43893885612488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36634922027588</t>
+    <t xml:space="preserve">3.36634945869446</t>
   </si>
   <si>
     <t xml:space="preserve">3.35727572441101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20302224159241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27561211585999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29375982284546</t>
+    <t xml:space="preserve">3.20302248001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27561187744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29375958442688</t>
   </si>
   <si>
     <t xml:space="preserve">3.1667275428772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11228537559509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78563117980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84007358551025</t>
+    <t xml:space="preserve">3.11228513717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78563141822815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84007382392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.82192611694336</t>
@@ -55742,7 +55742,7 @@
     </row>
     <row r="2065">
       <c r="A2065" s="1" t="n">
-        <v>45971.6732986111</v>
+        <v>45971.3333333333</v>
       </c>
       <c r="B2065" t="n">
         <v>13298</v>
@@ -55763,6 +55763,32 @@
         <v>568</v>
       </c>
       <c r="H2065" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2066">
+      <c r="A2066" s="1" t="n">
+        <v>45972.6664236111</v>
+      </c>
+      <c r="B2066" t="n">
+        <v>3000</v>
+      </c>
+      <c r="C2066" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="D2066" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="E2066" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="F2066" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="G2066" t="s">
+        <v>568</v>
+      </c>
+      <c r="H2066" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -50,13 +50,13 @@
     <t xml:space="preserve">2.88901543617249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98013734817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97266840934753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94578003883362</t>
+    <t xml:space="preserve">2.98013710975647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97266864776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94577980041504</t>
   </si>
   <si>
     <t xml:space="preserve">2.95773029327393</t>
@@ -68,10 +68,10 @@
     <t xml:space="preserve">2.93532347679138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91291618347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9786434173584</t>
+    <t xml:space="preserve">2.91291642189026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97864365577698</t>
   </si>
   <si>
     <t xml:space="preserve">2.98611259460449</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">3.03540802001953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.056321144104</t>
+    <t xml:space="preserve">3.05632138252258</t>
   </si>
   <si>
     <t xml:space="preserve">3.0593090057373</t>
@@ -89,22 +89,22 @@
     <t xml:space="preserve">3.05034613609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98760628700256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95026135444641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01598858833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01001358032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02495169639587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01748251914978</t>
+    <t xml:space="preserve">2.98760652542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95026111602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01598882675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01001381874084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02495145797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0174822807312</t>
   </si>
   <si>
     <t xml:space="preserve">3.03092646598816</t>
@@ -113,10 +113,10 @@
     <t xml:space="preserve">2.99955677986145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04437112808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.959223985672</t>
+    <t xml:space="preserve">3.0443708896637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95922422409058</t>
   </si>
   <si>
     <t xml:space="preserve">3.00254440307617</t>
@@ -125,34 +125,34 @@
     <t xml:space="preserve">2.92785429954529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90843462944031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89648461341858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91889142990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9159038066864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92038536071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90544724464417</t>
+    <t xml:space="preserve">2.90843486785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91889119148254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91590404510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92038512229919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90544700622559</t>
   </si>
   <si>
     <t xml:space="preserve">2.90992856025696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92337274551392</t>
+    <t xml:space="preserve">2.9233729839325</t>
   </si>
   <si>
     <t xml:space="preserve">2.8382260799408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86063313484192</t>
+    <t xml:space="preserve">2.86063289642334</t>
   </si>
   <si>
     <t xml:space="preserve">2.82627558708191</t>
@@ -164,25 +164,25 @@
     <t xml:space="preserve">2.84569525718689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86810207366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88303995132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79639935493469</t>
+    <t xml:space="preserve">2.86810231208801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88304018974304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79639959335327</t>
   </si>
   <si>
     <t xml:space="preserve">2.87557101249695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89797806739807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80088114738464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74262285232544</t>
+    <t xml:space="preserve">2.89797830581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80088067054749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74262237548828</t>
   </si>
   <si>
     <t xml:space="preserve">2.82179427146912</t>
@@ -194,13 +194,13 @@
     <t xml:space="preserve">2.76353573799133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77847361564636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78594303131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79341173171997</t>
+    <t xml:space="preserve">2.77847409248352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78594279289246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79341197013855</t>
   </si>
   <si>
     <t xml:space="preserve">2.69631457328796</t>
@@ -209,46 +209,46 @@
     <t xml:space="preserve">2.6515007019043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62162470817566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5394651889801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5693416595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61415553092957</t>
+    <t xml:space="preserve">2.62162446975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53946542739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56934142112732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61415576934814</t>
   </si>
   <si>
     <t xml:space="preserve">2.65896940231323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68884563446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70378351211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77100515365601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81581902503967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7336597442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66643881797791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68137693405151</t>
+    <t xml:space="preserve">2.68884587287903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70378375053406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77100491523743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81581926345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73365998268127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66643857955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68137669563293</t>
   </si>
   <si>
     <t xml:space="preserve">2.74112892150879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72619104385376</t>
+    <t xml:space="preserve">2.72619080543518</t>
   </si>
   <si>
     <t xml:space="preserve">2.83075714111328</t>
@@ -257,34 +257,34 @@
     <t xml:space="preserve">2.893150806427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69871854782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83870959281921</t>
+    <t xml:space="preserve">2.69871878623962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83871006965637</t>
   </si>
   <si>
     <t xml:space="preserve">2.93203711509705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87759613990784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8309326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81537771224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84648680686951</t>
+    <t xml:space="preserve">2.87759590148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83093237876892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81537747383118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84648704528809</t>
   </si>
   <si>
     <t xml:space="preserve">2.79982304573059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73760485649109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76093697547913</t>
+    <t xml:space="preserve">2.73760509490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76093649864197</t>
   </si>
   <si>
     <t xml:space="preserve">2.80760049819946</t>
@@ -293,7 +293,7 @@
     <t xml:space="preserve">3.00980973243713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95536875724792</t>
+    <t xml:space="preserve">2.9553689956665</t>
   </si>
   <si>
     <t xml:space="preserve">2.90870523452759</t>
@@ -302,19 +302,19 @@
     <t xml:space="preserve">2.88537335395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82315492630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86204147338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00203251838684</t>
+    <t xml:space="preserve">2.82315516471863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86204171180725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00203275680542</t>
   </si>
   <si>
     <t xml:space="preserve">2.91648244857788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85426449775696</t>
+    <t xml:space="preserve">2.8542640209198</t>
   </si>
   <si>
     <t xml:space="preserve">2.7298276424408</t>
@@ -323,10 +323,10 @@
     <t xml:space="preserve">2.68316411972046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72205018997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75315976142883</t>
+    <t xml:space="preserve">2.7220504283905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75315952301025</t>
   </si>
   <si>
     <t xml:space="preserve">2.70649576187134</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">2.93981432914734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99425554275513</t>
+    <t xml:space="preserve">2.99425506591797</t>
   </si>
   <si>
     <t xml:space="preserve">2.97870063781738</t>
@@ -350,52 +350,52 @@
     <t xml:space="preserve">2.98647809028625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63650059700012</t>
+    <t xml:space="preserve">2.63650035858154</t>
   </si>
   <si>
     <t xml:space="preserve">2.550950050354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51984071731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41095876693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34096312522888</t>
+    <t xml:space="preserve">2.51984047889709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41095900535583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34096336364746</t>
   </si>
   <si>
     <t xml:space="preserve">2.34874057769775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36429500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2554132938385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24763584136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32540893554688</t>
+    <t xml:space="preserve">2.36429524421692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25541305541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24763607978821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32540845870972</t>
   </si>
   <si>
     <t xml:space="preserve">2.23208117485046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18541765213013</t>
+    <t xml:space="preserve">2.18541741371155</t>
   </si>
   <si>
     <t xml:space="preserve">2.27874517440796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26319003105164</t>
+    <t xml:space="preserve">2.26319026947021</t>
   </si>
   <si>
     <t xml:space="preserve">2.2165265083313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06875824928284</t>
+    <t xml:space="preserve">2.06875848770142</t>
   </si>
   <si>
     <t xml:space="preserve">2.1465311050415</t>
@@ -407,52 +407,52 @@
     <t xml:space="preserve">2.15430855751038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17764043807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22430396080017</t>
+    <t xml:space="preserve">2.17764019966125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22430372238159</t>
   </si>
   <si>
     <t xml:space="preserve">2.35651779174805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48873209953308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52761793136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43429064750671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44206833839417</t>
+    <t xml:space="preserve">2.4887318611145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52761840820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43429088592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44206809997559</t>
   </si>
   <si>
     <t xml:space="preserve">2.55872750282288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44984531402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37207269668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33318591117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29429960250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3798496723175</t>
+    <t xml:space="preserve">2.44984555244446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37207221984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33318614959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29429984092712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37984943389893</t>
   </si>
   <si>
     <t xml:space="preserve">2.71427297592163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58205890655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62872314453125</t>
+    <t xml:space="preserve">2.58205938339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62872290611267</t>
   </si>
   <si>
     <t xml:space="preserve">2.65983200073242</t>
@@ -470,34 +470,34 @@
     <t xml:space="preserve">2.69094133377075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76871418952942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90092825889587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96314597129822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92425990104675</t>
+    <t xml:space="preserve">2.76871371269226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90092802047729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9631462097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92425966262817</t>
   </si>
   <si>
     <t xml:space="preserve">2.97092342376709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01758766174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04869651794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03314185142517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0642511844635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07980585098267</t>
+    <t xml:space="preserve">3.01758718490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04869627952576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03314208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06425094604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07980561256409</t>
   </si>
   <si>
     <t xml:space="preserve">3.0604989528656</t>
@@ -518,16 +518,16 @@
     <t xml:space="preserve">3.12527132034302</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07669186592102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99572658538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30339574813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41674757003784</t>
+    <t xml:space="preserve">3.0766921043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99572682380676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30339598655701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41674733161926</t>
   </si>
   <si>
     <t xml:space="preserve">3.35197496414185</t>
@@ -542,10 +542,10 @@
     <t xml:space="preserve">3.23862338066101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31958889961243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27100944519043</t>
+    <t xml:space="preserve">3.31958866119385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27100968360901</t>
   </si>
   <si>
     <t xml:space="preserve">3.28720259666443</t>
@@ -554,25 +554,25 @@
     <t xml:space="preserve">3.22243022918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17385101318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20623731613159</t>
+    <t xml:space="preserve">3.17385077476501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20623707771301</t>
   </si>
   <si>
     <t xml:space="preserve">3.14146494865417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40055441856384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49771356582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38436102867126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25481653213501</t>
+    <t xml:space="preserve">3.40055418014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49771332740784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38436126708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25481629371643</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004416465759</t>
@@ -587,10 +587,10 @@
     <t xml:space="preserve">2.80140924453735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88237476348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86618185043335</t>
+    <t xml:space="preserve">2.88237500190735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86618161201477</t>
   </si>
   <si>
     <t xml:space="preserve">2.84998846054077</t>
@@ -599,7 +599,7 @@
     <t xml:space="preserve">2.78521609306335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75283002853394</t>
+    <t xml:space="preserve">2.75283026695251</t>
   </si>
   <si>
     <t xml:space="preserve">2.72044348716736</t>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">2.91476082801819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63947796821594</t>
+    <t xml:space="preserve">2.63947820663452</t>
   </si>
   <si>
     <t xml:space="preserve">2.67186403274536</t>
@@ -632,7 +632,7 @@
     <t xml:space="preserve">2.62328481674194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68805718421936</t>
+    <t xml:space="preserve">2.68805766105652</t>
   </si>
   <si>
     <t xml:space="preserve">2.70425057411194</t>
@@ -641,13 +641,13 @@
     <t xml:space="preserve">2.60709190368652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5908989906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42896747589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54231953620911</t>
+    <t xml:space="preserve">2.59089875221252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42896723747253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54231929779053</t>
   </si>
   <si>
     <t xml:space="preserve">2.46135354042053</t>
@@ -656,13 +656,13 @@
     <t xml:space="preserve">2.3156156539917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29942274093628</t>
+    <t xml:space="preserve">2.2994225025177</t>
   </si>
   <si>
     <t xml:space="preserve">2.35488152503967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40607476234436</t>
+    <t xml:space="preserve">2.40607452392578</t>
   </si>
   <si>
     <t xml:space="preserve">2.28662419319153</t>
@@ -671,7 +671,7 @@
     <t xml:space="preserve">2.13304495811462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08185219764709</t>
+    <t xml:space="preserve">2.08185172080994</t>
   </si>
   <si>
     <t xml:space="preserve">2.06478762626648</t>
@@ -689,28 +689,28 @@
     <t xml:space="preserve">2.26956009864807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21836686134338</t>
+    <t xml:space="preserve">2.2183666229248</t>
   </si>
   <si>
     <t xml:space="preserve">2.32075309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55965423583984</t>
+    <t xml:space="preserve">2.55965399742126</t>
   </si>
   <si>
     <t xml:space="preserve">2.54258966445923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45726799964905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5767183303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62791132926941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61084723472595</t>
+    <t xml:space="preserve">2.45726823806763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57671856880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62791156768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61084699630737</t>
   </si>
   <si>
     <t xml:space="preserve">2.64497566223145</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">2.69616913795471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71323323249817</t>
+    <t xml:space="preserve">2.71323347091675</t>
   </si>
   <si>
     <t xml:space="preserve">2.44020342826843</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">2.4231390953064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4743320941925</t>
+    <t xml:space="preserve">2.47433233261108</t>
   </si>
   <si>
     <t xml:space="preserve">2.15010929107666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33781719207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30368852615356</t>
+    <t xml:space="preserve">2.33781743049622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30368876457214</t>
   </si>
   <si>
     <t xml:space="preserve">2.25249552726746</t>
@@ -749,7 +749,7 @@
     <t xml:space="preserve">2.23543095588684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37194633483887</t>
+    <t xml:space="preserve">2.37194585800171</t>
   </si>
   <si>
     <t xml:space="preserve">2.38901042938232</t>
@@ -758,10 +758,10 @@
     <t xml:space="preserve">2.20130252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18423795700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01359415054321</t>
+    <t xml:space="preserve">2.18423819541931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01359438896179</t>
   </si>
   <si>
     <t xml:space="preserve">2.04772329330444</t>
@@ -785,16 +785,16 @@
     <t xml:space="preserve">1.86001527309418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94533681869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96240139007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99652981758118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81561923027039</t>
+    <t xml:space="preserve">1.94533705711365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9624011516571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99653005599976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81561946868896</t>
   </si>
   <si>
     <t xml:space="preserve">2.9009416103363</t>
@@ -803,10 +803,10 @@
     <t xml:space="preserve">2.88387703895569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76442623138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73029780387878</t>
+    <t xml:space="preserve">2.76442646980286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73029756546021</t>
   </si>
   <si>
     <t xml:space="preserve">2.6791045665741</t>
@@ -815,13 +815,13 @@
     <t xml:space="preserve">2.74736213684082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83268356323242</t>
+    <t xml:space="preserve">2.832683801651</t>
   </si>
   <si>
     <t xml:space="preserve">2.86681246757507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79855513572693</t>
+    <t xml:space="preserve">2.79855489730835</t>
   </si>
   <si>
     <t xml:space="preserve">2.78149080276489</t>
@@ -836,7 +836,7 @@
     <t xml:space="preserve">3.02039194107056</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00332713127136</t>
+    <t xml:space="preserve">3.00332736968994</t>
   </si>
   <si>
     <t xml:space="preserve">3.03745627403259</t>
@@ -845,7 +845,7 @@
     <t xml:space="preserve">2.98626303672791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05452036857605</t>
+    <t xml:space="preserve">3.05452060699463</t>
   </si>
   <si>
     <t xml:space="preserve">3.07158470153809</t>
@@ -854,22 +854,22 @@
     <t xml:space="preserve">3.13984251022339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11424565315247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1313099861145</t>
+    <t xml:space="preserve">3.11424589157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13131022453308</t>
   </si>
   <si>
     <t xml:space="preserve">3.06305241584778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16543865203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19956755638123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15690660476685</t>
+    <t xml:space="preserve">3.16543889045715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1995677947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15690684318542</t>
   </si>
   <si>
     <t xml:space="preserve">3.2336962223053</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24222826957703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26782488822937</t>
+    <t xml:space="preserve">3.26782464981079</t>
   </si>
   <si>
     <t xml:space="preserve">3.31048607826233</t>
@@ -899,7 +899,7 @@
     <t xml:space="preserve">3.18250322341919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29342126846313</t>
+    <t xml:space="preserve">3.29342174530029</t>
   </si>
   <si>
     <t xml:space="preserve">3.33710074424744</t>
@@ -55768,7 +55768,7 @@
     </row>
     <row r="2066">
       <c r="A2066" s="1" t="n">
-        <v>45972.6664236111</v>
+        <v>45972.3333333333</v>
       </c>
       <c r="B2066" t="n">
         <v>3000</v>
@@ -55789,6 +55789,32 @@
         <v>568</v>
       </c>
       <c r="H2066" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2067">
+      <c r="A2067" s="1" t="n">
+        <v>45973.681724537</v>
+      </c>
+      <c r="B2067" t="n">
+        <v>2850</v>
+      </c>
+      <c r="C2067" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="D2067" t="n">
+        <v>3.01999998092651</v>
+      </c>
+      <c r="E2067" t="n">
+        <v>3.03999996185303</v>
+      </c>
+      <c r="F2067" t="n">
+        <v>3.07999992370605</v>
+      </c>
+      <c r="G2067" t="s">
+        <v>555</v>
+      </c>
+      <c r="H2067" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">2.98013710975647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97266864776611</t>
+    <t xml:space="preserve">2.97266817092896</t>
   </si>
   <si>
     <t xml:space="preserve">2.94577980041504</t>
@@ -62,64 +62,64 @@
     <t xml:space="preserve">2.95773029327393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96221160888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93532347679138</t>
+    <t xml:space="preserve">2.9622118473053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9353232383728</t>
   </si>
   <si>
     <t xml:space="preserve">2.91291642189026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97864365577698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98611259460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03540802001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05632138252258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0593090057373</t>
+    <t xml:space="preserve">2.9786434173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98611235618591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03540825843811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.056321144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05930924415588</t>
   </si>
   <si>
     <t xml:space="preserve">3.05034613609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98760652542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95026111602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01598882675171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01001381874084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02495145797729</t>
+    <t xml:space="preserve">2.98760628700256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95026135444641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01598858833313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01001358032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02495169639587</t>
   </si>
   <si>
     <t xml:space="preserve">3.0174822807312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03092646598816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99955677986145</t>
+    <t xml:space="preserve">3.03092670440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99955654144287</t>
   </si>
   <si>
     <t xml:space="preserve">3.0443708896637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95922422409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00254440307617</t>
+    <t xml:space="preserve">2.959223985672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00254416465759</t>
   </si>
   <si>
     <t xml:space="preserve">2.92785429954529</t>
@@ -131,109 +131,109 @@
     <t xml:space="preserve">2.896484375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91889119148254</t>
+    <t xml:space="preserve">2.91889142990112</t>
   </si>
   <si>
     <t xml:space="preserve">2.91590404510498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92038512229919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90544700622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90992856025696</t>
+    <t xml:space="preserve">2.92038536071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90544748306274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90992879867554</t>
   </si>
   <si>
     <t xml:space="preserve">2.9233729839325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8382260799408</t>
+    <t xml:space="preserve">2.83822584152222</t>
   </si>
   <si>
     <t xml:space="preserve">2.86063289642334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82627558708191</t>
+    <t xml:space="preserve">2.82627511024475</t>
   </si>
   <si>
     <t xml:space="preserve">2.77996778488159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84569525718689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86810231208801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88304018974304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79639959335327</t>
+    <t xml:space="preserve">2.84569501876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86810207366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88303971290588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79639935493469</t>
   </si>
   <si>
     <t xml:space="preserve">2.87557101249695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89797830581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80088067054749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74262237548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82179427146912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75009155273438</t>
+    <t xml:space="preserve">2.89797806739807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80088090896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74262261390686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82179403305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7500913143158</t>
   </si>
   <si>
     <t xml:space="preserve">2.76353573799133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77847409248352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78594279289246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79341197013855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69631457328796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6515007019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62162446975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53946542739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56934142112732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61415576934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65896940231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68884587287903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70378375053406</t>
+    <t xml:space="preserve">2.77847385406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78594303131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79341220855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69631481170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65150046348572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6216242313385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5394651889801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5693416595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61415553092957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65896964073181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68884563446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70378351211548</t>
   </si>
   <si>
     <t xml:space="preserve">2.77100491523743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81581926345825</t>
+    <t xml:space="preserve">2.81581878662109</t>
   </si>
   <si>
     <t xml:space="preserve">2.73365998268127</t>
@@ -242,40 +242,40 @@
     <t xml:space="preserve">2.66643857955933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68137669563293</t>
+    <t xml:space="preserve">2.68137645721436</t>
   </si>
   <si>
     <t xml:space="preserve">2.74112892150879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72619080543518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83075714111328</t>
+    <t xml:space="preserve">2.72619104385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8307569026947</t>
   </si>
   <si>
     <t xml:space="preserve">2.893150806427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69871878623962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83871006965637</t>
+    <t xml:space="preserve">2.69871830940247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83870983123779</t>
   </si>
   <si>
     <t xml:space="preserve">2.93203711509705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87759590148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83093237876892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81537747383118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84648704528809</t>
+    <t xml:space="preserve">2.87759613990784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8309326171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81537795066833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84648728370667</t>
   </si>
   <si>
     <t xml:space="preserve">2.79982304573059</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">2.73760509490967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76093649864197</t>
+    <t xml:space="preserve">2.76093697547913</t>
   </si>
   <si>
     <t xml:space="preserve">2.80760049819946</t>
@@ -296,7 +296,7 @@
     <t xml:space="preserve">2.9553689956665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90870523452759</t>
+    <t xml:space="preserve">2.90870547294617</t>
   </si>
   <si>
     <t xml:space="preserve">2.88537335395813</t>
@@ -308,19 +308,19 @@
     <t xml:space="preserve">2.86204171180725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00203275680542</t>
+    <t xml:space="preserve">3.00203251838684</t>
   </si>
   <si>
     <t xml:space="preserve">2.91648244857788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8542640209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7298276424408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68316411972046</t>
+    <t xml:space="preserve">2.85426425933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72982740402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68316388130188</t>
   </si>
   <si>
     <t xml:space="preserve">2.7220504283905</t>
@@ -332,10 +332,10 @@
     <t xml:space="preserve">2.70649576187134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93981432914734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99425506591797</t>
+    <t xml:space="preserve">2.93981456756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99425530433655</t>
   </si>
   <si>
     <t xml:space="preserve">2.97870063781738</t>
@@ -344,40 +344,40 @@
     <t xml:space="preserve">2.86981868743896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94759202003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98647809028625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63650035858154</t>
+    <t xml:space="preserve">2.94759154319763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98647785186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63650012016296</t>
   </si>
   <si>
     <t xml:space="preserve">2.550950050354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51984047889709</t>
+    <t xml:space="preserve">2.51984095573425</t>
   </si>
   <si>
     <t xml:space="preserve">2.41095900535583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34096336364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34874057769775</t>
+    <t xml:space="preserve">2.34096312522888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34874081611633</t>
   </si>
   <si>
     <t xml:space="preserve">2.36429524421692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25541305541992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24763607978821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32540845870972</t>
+    <t xml:space="preserve">2.2554132938385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24763584136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3254086971283</t>
   </si>
   <si>
     <t xml:space="preserve">2.23208117485046</t>
@@ -395,31 +395,31 @@
     <t xml:space="preserve">2.2165265083313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06875848770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1465311050415</t>
+    <t xml:space="preserve">2.06875824928284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14653134346008</t>
   </si>
   <si>
     <t xml:space="preserve">2.10764479637146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15430855751038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17764019966125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22430372238159</t>
+    <t xml:space="preserve">2.1543083190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17764043807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22430396080017</t>
   </si>
   <si>
     <t xml:space="preserve">2.35651779174805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4887318611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52761840820312</t>
+    <t xml:space="preserve">2.48873209953308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52761793136597</t>
   </si>
   <si>
     <t xml:space="preserve">2.43429088592529</t>
@@ -428,34 +428,34 @@
     <t xml:space="preserve">2.44206809997559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55872750282288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44984555244446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37207221984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33318614959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29429984092712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37984943389893</t>
+    <t xml:space="preserve">2.5587272644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44984531402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37207245826721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33318638801575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29429960250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37984991073608</t>
   </si>
   <si>
     <t xml:space="preserve">2.71427297592163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58205938339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62872290611267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65983200073242</t>
+    <t xml:space="preserve">2.58205914497375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62872314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.659832239151</t>
   </si>
   <si>
     <t xml:space="preserve">2.57428193092346</t>
@@ -464,55 +464,55 @@
     <t xml:space="preserve">2.67538666725159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64427757263184</t>
+    <t xml:space="preserve">2.64427733421326</t>
   </si>
   <si>
     <t xml:space="preserve">2.69094133377075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76871371269226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90092802047729</t>
+    <t xml:space="preserve">2.76871395111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90092778205872</t>
   </si>
   <si>
     <t xml:space="preserve">2.9631462097168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92425966262817</t>
+    <t xml:space="preserve">2.92425990104675</t>
   </si>
   <si>
     <t xml:space="preserve">2.97092342376709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01758718490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04869627952576</t>
+    <t xml:space="preserve">3.01758742332458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04869651794434</t>
   </si>
   <si>
     <t xml:space="preserve">3.03314208984375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06425094604492</t>
+    <t xml:space="preserve">3.0642511844635</t>
   </si>
   <si>
     <t xml:space="preserve">3.07980561256409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0604989528656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02811288833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01191973686218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1090784072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0928852558136</t>
+    <t xml:space="preserve">3.06049919128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02811312675476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01191997528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10907816886902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09288501739502</t>
   </si>
   <si>
     <t xml:space="preserve">3.12527132034302</t>
@@ -521,22 +521,22 @@
     <t xml:space="preserve">3.0766921043396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99572682380676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30339598655701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41674733161926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35197496414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33578181266785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36816811561584</t>
+    <t xml:space="preserve">2.99572658538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30339574813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41674709320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35197520256042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33578205108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36816835403442</t>
   </si>
   <si>
     <t xml:space="preserve">3.23862338066101</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">3.31958866119385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27100968360901</t>
+    <t xml:space="preserve">3.27100944519043</t>
   </si>
   <si>
     <t xml:space="preserve">3.28720259666443</t>
@@ -560,13 +560,13 @@
     <t xml:space="preserve">3.20623707771301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14146494865417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40055418014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49771332740784</t>
+    <t xml:space="preserve">3.1414647102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40055441856384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49771308898926</t>
   </si>
   <si>
     <t xml:space="preserve">3.38436126708984</t>
@@ -578,73 +578,73 @@
     <t xml:space="preserve">3.19004416465759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96334028244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97953343391418</t>
+    <t xml:space="preserve">2.96334052085876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97953367233276</t>
   </si>
   <si>
     <t xml:space="preserve">2.80140924453735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88237500190735</t>
+    <t xml:space="preserve">2.88237452507019</t>
   </si>
   <si>
     <t xml:space="preserve">2.86618161201477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84998846054077</t>
+    <t xml:space="preserve">2.84998869895935</t>
   </si>
   <si>
     <t xml:space="preserve">2.78521609306335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75283026695251</t>
+    <t xml:space="preserve">2.75282979011536</t>
   </si>
   <si>
     <t xml:space="preserve">2.72044348716736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83379530906677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76902294158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73663687705994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81760239601135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89856791496277</t>
+    <t xml:space="preserve">2.83379554748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76902318000793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73663663864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81760215759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89856767654419</t>
   </si>
   <si>
     <t xml:space="preserve">2.91476082801819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63947820663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67186403274536</t>
+    <t xml:space="preserve">2.63947796821594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67186427116394</t>
   </si>
   <si>
     <t xml:space="preserve">2.62328481674194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68805766105652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70425057411194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60709190368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59089875221252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42896723747253</t>
+    <t xml:space="preserve">2.68805718421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70425009727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60709166526794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5908989906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42896771430969</t>
   </si>
   <si>
     <t xml:space="preserve">2.54231929779053</t>
@@ -659,10 +659,10 @@
     <t xml:space="preserve">2.2994225025177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35488152503967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40607452392578</t>
+    <t xml:space="preserve">2.35488176345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40607476234436</t>
   </si>
   <si>
     <t xml:space="preserve">2.28662419319153</t>
@@ -671,13 +671,13 @@
     <t xml:space="preserve">2.13304495811462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08185172080994</t>
+    <t xml:space="preserve">2.08185195922852</t>
   </si>
   <si>
     <t xml:space="preserve">2.06478762626648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03065896034241</t>
+    <t xml:space="preserve">2.03065872192383</t>
   </si>
   <si>
     <t xml:space="preserve">2.1671736240387</t>
@@ -689,22 +689,22 @@
     <t xml:space="preserve">2.26956009864807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2183666229248</t>
+    <t xml:space="preserve">2.21836686134338</t>
   </si>
   <si>
     <t xml:space="preserve">2.32075309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55965399742126</t>
+    <t xml:space="preserve">2.55965423583984</t>
   </si>
   <si>
     <t xml:space="preserve">2.54258966445923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45726823806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57671856880188</t>
+    <t xml:space="preserve">2.45726799964905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5767183303833</t>
   </si>
   <si>
     <t xml:space="preserve">2.62791156768799</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">2.64497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59378266334534</t>
+    <t xml:space="preserve">2.59378290176392</t>
   </si>
   <si>
     <t xml:space="preserve">2.69616913795471</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">2.44020342826843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4231390953064</t>
+    <t xml:space="preserve">2.42313933372498</t>
   </si>
   <si>
     <t xml:space="preserve">2.47433233261108</t>
@@ -743,13 +743,13 @@
     <t xml:space="preserve">2.30368876457214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25249552726746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23543095588684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37194585800171</t>
+    <t xml:space="preserve">2.25249576568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23543119430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37194609642029</t>
   </si>
   <si>
     <t xml:space="preserve">2.38901042938232</t>
@@ -758,46 +758,46 @@
     <t xml:space="preserve">2.20130252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18423819541931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01359438896179</t>
+    <t xml:space="preserve">2.18423795700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01359415054321</t>
   </si>
   <si>
     <t xml:space="preserve">2.04772329330444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11598062515259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91120839118958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8770797252655</t>
+    <t xml:space="preserve">2.11598038673401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91120827198029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87707984447479</t>
   </si>
   <si>
     <t xml:space="preserve">1.84295094013214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97946572303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86001527309418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94533705711365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9624011516571</t>
+    <t xml:space="preserve">1.97946560382843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86001515388489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94533693790436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96240139007568</t>
   </si>
   <si>
     <t xml:space="preserve">1.99653005599976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81561946868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9009416103363</t>
+    <t xml:space="preserve">2.81561923027039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90094137191772</t>
   </si>
   <si>
     <t xml:space="preserve">2.88387703895569</t>
@@ -806,25 +806,25 @@
     <t xml:space="preserve">2.76442646980286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73029756546021</t>
+    <t xml:space="preserve">2.73029780387878</t>
   </si>
   <si>
     <t xml:space="preserve">2.6791045665741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74736213684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.832683801651</t>
+    <t xml:space="preserve">2.74736189842224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83268356323242</t>
   </si>
   <si>
     <t xml:space="preserve">2.86681246757507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79855489730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78149080276489</t>
+    <t xml:space="preserve">2.79855513572693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78149056434631</t>
   </si>
   <si>
     <t xml:space="preserve">2.9350700378418</t>
@@ -833,22 +833,22 @@
     <t xml:space="preserve">2.96919870376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02039194107056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00332736968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03745627403259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98626303672791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05452060699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07158470153809</t>
+    <t xml:space="preserve">3.02039170265198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00332713127136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03745603561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98626279830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05452036857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07158493995667</t>
   </si>
   <si>
     <t xml:space="preserve">3.13984251022339</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.13131022453308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06305241584778</t>
+    <t xml:space="preserve">3.06305265426636</t>
   </si>
   <si>
     <t xml:space="preserve">3.16543889045715</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">3.1995677947998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15690684318542</t>
+    <t xml:space="preserve">3.15690660476685</t>
   </si>
   <si>
     <t xml:space="preserve">3.2336962223053</t>
@@ -878,19 +878,19 @@
     <t xml:space="preserve">3.27635717391968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24222826957703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26782464981079</t>
+    <t xml:space="preserve">3.24222850799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26782488822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.31048607826233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3446147441864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32755041122437</t>
+    <t xml:space="preserve">3.34461498260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32755017280579</t>
   </si>
   <si>
     <t xml:space="preserve">3.28488922119141</t>
@@ -899,7 +899,7 @@
     <t xml:space="preserve">3.18250322341919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29342174530029</t>
+    <t xml:space="preserve">3.29342126846313</t>
   </si>
   <si>
     <t xml:space="preserve">3.33710074424744</t>
@@ -914,46 +914,46 @@
     <t xml:space="preserve">3.24974226951599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20606303215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15364742279053</t>
+    <t xml:space="preserve">3.20606279373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15364766120911</t>
   </si>
   <si>
     <t xml:space="preserve">3.21479892730713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17111945152283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26721405982971</t>
+    <t xml:space="preserve">3.17111968994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26721382141113</t>
   </si>
   <si>
     <t xml:space="preserve">3.36330842971802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49434661865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58170485496521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56423354148865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59044122695923</t>
+    <t xml:space="preserve">3.49434638023376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58170533180237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56423330307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59044098854065</t>
   </si>
   <si>
     <t xml:space="preserve">3.5030825138092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51181817054749</t>
+    <t xml:space="preserve">3.51181840896606</t>
   </si>
   <si>
     <t xml:space="preserve">3.54676175117493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63412022590637</t>
+    <t xml:space="preserve">3.63411998748779</t>
   </si>
   <si>
     <t xml:space="preserve">3.62538456916809</t>
@@ -962,10 +962,10 @@
     <t xml:space="preserve">3.7476863861084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69527125358582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66906356811523</t>
+    <t xml:space="preserve">3.69527149200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66906380653381</t>
   </si>
   <si>
     <t xml:space="preserve">3.60791277885437</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">3.55549788475037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66032791137695</t>
+    <t xml:space="preserve">3.66032814979553</t>
   </si>
   <si>
     <t xml:space="preserve">3.65159201622009</t>
@@ -983,37 +983,37 @@
     <t xml:space="preserve">3.68653535842896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70400714874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75642275810242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57296943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53802609443665</t>
+    <t xml:space="preserve">3.7040069103241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75642251968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57296967506409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53802585601807</t>
   </si>
   <si>
     <t xml:space="preserve">3.3458366394043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3895161151886</t>
+    <t xml:space="preserve">3.38951635360718</t>
   </si>
   <si>
     <t xml:space="preserve">3.42445969581604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45066714286804</t>
+    <t xml:space="preserve">3.45066738128662</t>
   </si>
   <si>
     <t xml:space="preserve">3.44193148612976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4856104850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4069881439209</t>
+    <t xml:space="preserve">3.48561072349548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40698790550232</t>
   </si>
   <si>
     <t xml:space="preserve">3.35457253456116</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">3.46813893318176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47687482833862</t>
+    <t xml:space="preserve">3.47687458992004</t>
   </si>
   <si>
     <t xml:space="preserve">3.79136610031128</t>
@@ -1040,22 +1040,22 @@
     <t xml:space="preserve">3.87872457504272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17574453353882</t>
+    <t xml:space="preserve">4.17574405670166</t>
   </si>
   <si>
     <t xml:space="preserve">4.31551790237427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35046148300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1844801902771</t>
+    <t xml:space="preserve">4.35046100616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18447971343994</t>
   </si>
   <si>
     <t xml:space="preserve">4.20195150375366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25436639785767</t>
+    <t xml:space="preserve">4.25436687469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.14080047607422</t>
@@ -1067,19 +1067,19 @@
     <t xml:space="preserve">3.98355507850647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94861149787903</t>
+    <t xml:space="preserve">3.94861173629761</t>
   </si>
   <si>
     <t xml:space="preserve">3.93113970756531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08838558197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07091331481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12332916259766</t>
+    <t xml:space="preserve">4.08838510513306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07091379165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12332820892334</t>
   </si>
   <si>
     <t xml:space="preserve">4.00102663040161</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">4.00976276397705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93987584114075</t>
+    <t xml:space="preserve">3.93987560272217</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
@@ -1097,13 +1097,13 @@
     <t xml:space="preserve">4.2106876373291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29804611206055</t>
+    <t xml:space="preserve">4.29804658889771</t>
   </si>
   <si>
     <t xml:space="preserve">4.28930997848511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21942377090454</t>
+    <t xml:space="preserve">4.21942329406738</t>
   </si>
   <si>
     <t xml:space="preserve">4.19321632385254</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">4.14953660964966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16700792312622</t>
+    <t xml:space="preserve">4.16700839996338</t>
   </si>
   <si>
     <t xml:space="preserve">4.11459302902222</t>
@@ -1121,46 +1121,46 @@
     <t xml:space="preserve">4.06217765808105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78262996673584</t>
+    <t xml:space="preserve">3.78263020515442</t>
   </si>
   <si>
     <t xml:space="preserve">3.80010175704956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82630944252014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83504557609558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84378147125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77389430999756</t>
+    <t xml:space="preserve">3.82630968093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.835045337677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84378123283386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77389454841614</t>
   </si>
   <si>
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734739303589</t>
+    <t xml:space="preserve">3.95734763145447</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86125302314758</t>
+    <t xml:space="preserve">3.861252784729</t>
   </si>
   <si>
     <t xml:space="preserve">3.76515817642212</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81757354736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64285635948181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67779946327209</t>
+    <t xml:space="preserve">3.8175733089447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64285612106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67779970169067</t>
   </si>
   <si>
     <t xml:space="preserve">3.7389509677887</t>
@@ -1169,10 +1169,10 @@
     <t xml:space="preserve">3.85251712799072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71274304389954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92240381240845</t>
+    <t xml:space="preserve">3.71274328231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92240357398987</t>
   </si>
   <si>
     <t xml:space="preserve">3.61664843559265</t>
@@ -1181,40 +1181,40 @@
     <t xml:space="preserve">3.39825224876404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23227071762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05755305290222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97019481658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95272302627563</t>
+    <t xml:space="preserve">3.23227047920227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05755352973938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97019457817078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95272278785706</t>
   </si>
   <si>
     <t xml:space="preserve">2.91777944564819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90904331207275</t>
+    <t xml:space="preserve">2.90904355049133</t>
   </si>
   <si>
     <t xml:space="preserve">3.37204432487488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38078022003174</t>
+    <t xml:space="preserve">3.38077998161316</t>
   </si>
   <si>
     <t xml:space="preserve">3.41572380065918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31962895393372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27595019340515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28468561172485</t>
+    <t xml:space="preserve">3.31962919235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27594995498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28468585014343</t>
   </si>
   <si>
     <t xml:space="preserve">3.50245499610901</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">3.32098078727722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26653814315796</t>
+    <t xml:space="preserve">3.26653838157654</t>
   </si>
   <si>
     <t xml:space="preserve">3.39357042312622</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">3.23024344444275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19394874572754</t>
+    <t xml:space="preserve">3.19394850730896</t>
   </si>
   <si>
     <t xml:space="preserve">3.25746440887451</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">3.2211697101593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10321140289307</t>
+    <t xml:space="preserve">3.10321164131165</t>
   </si>
   <si>
     <t xml:space="preserve">2.99432682991028</t>
@@ -1286,13 +1286,13 @@
     <t xml:space="preserve">2.95803189277649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85822105407715</t>
+    <t xml:space="preserve">2.85822129249573</t>
   </si>
   <si>
     <t xml:space="preserve">2.89451599121094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8672947883606</t>
+    <t xml:space="preserve">2.86729502677917</t>
   </si>
   <si>
     <t xml:space="preserve">2.81285238265991</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">2.75841021537781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70396780967712</t>
+    <t xml:space="preserve">2.7039680480957</t>
   </si>
   <si>
     <t xml:space="preserve">2.72211527824402</t>
@@ -1313,16 +1313,16 @@
     <t xml:space="preserve">2.64952564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7947051525116</t>
+    <t xml:space="preserve">2.79470491409302</t>
   </si>
   <si>
     <t xml:space="preserve">2.92173719406128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05784273147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02154803276062</t>
+    <t xml:space="preserve">3.05784296989441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02154779434204</t>
   </si>
   <si>
     <t xml:space="preserve">3.13950634002686</t>
@@ -1352,46 +1352,46 @@
     <t xml:space="preserve">3.08506417274475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01247429847717</t>
+    <t xml:space="preserve">3.01247406005859</t>
   </si>
   <si>
     <t xml:space="preserve">2.88544225692749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7765576839447</t>
+    <t xml:space="preserve">2.77655744552612</t>
   </si>
   <si>
     <t xml:space="preserve">2.71304154396057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6313784122467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68582034111023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66767287254333</t>
+    <t xml:space="preserve">2.63137817382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68582057952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66767311096191</t>
   </si>
   <si>
     <t xml:space="preserve">2.55878829956055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52249336242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67674660682678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64045214653015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87636852264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83099985122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60415697097778</t>
+    <t xml:space="preserve">2.52249360084534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67674684524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64045190811157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87636876106262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83099961280823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6041567325592</t>
   </si>
   <si>
     <t xml:space="preserve">2.73118901252747</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">2.91266345977783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12135887145996</t>
+    <t xml:space="preserve">3.12135910987854</t>
   </si>
   <si>
     <t xml:space="preserve">3.0759904384613</t>
@@ -1427,46 +1427,46 @@
     <t xml:space="preserve">3.0941379070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38449692726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41171765327454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37542319297791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42079138755798</t>
+    <t xml:space="preserve">3.38449668884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41171789169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37542295455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42079162597656</t>
   </si>
   <si>
     <t xml:space="preserve">3.43893885612488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36634945869446</t>
+    <t xml:space="preserve">3.36634922027588</t>
   </si>
   <si>
     <t xml:space="preserve">3.35727572441101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20302248001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27561187744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29375958442688</t>
+    <t xml:space="preserve">3.20302224159241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27561211585999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29375982284546</t>
   </si>
   <si>
     <t xml:space="preserve">3.1667275428772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11228513717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78563141822815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84007382392883</t>
+    <t xml:space="preserve">3.11228537559509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78563117980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84007358551025</t>
   </si>
   <si>
     <t xml:space="preserve">2.82192611694336</t>
@@ -55794,7 +55794,7 @@
     </row>
     <row r="2067">
       <c r="A2067" s="1" t="n">
-        <v>45973.681724537</v>
+        <v>45973.3333333333</v>
       </c>
       <c r="B2067" t="n">
         <v>2850</v>
@@ -55815,6 +55815,32 @@
         <v>555</v>
       </c>
       <c r="H2067" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2068">
+      <c r="A2068" s="1" t="n">
+        <v>45974.6321064815</v>
+      </c>
+      <c r="B2068" t="n">
+        <v>4455</v>
+      </c>
+      <c r="C2068" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="D2068" t="n">
+        <v>3.09999990463257</v>
+      </c>
+      <c r="E2068" t="n">
+        <v>3.20000004768372</v>
+      </c>
+      <c r="F2068" t="n">
+        <v>3.11999988555908</v>
+      </c>
+      <c r="G2068" t="s">
+        <v>567</v>
+      </c>
+      <c r="H2068" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -38,40 +38,40 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02345728874207</t>
+    <t xml:space="preserve">3.02345752716064</t>
   </si>
   <si>
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519923210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88901543617249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98013734817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97266840934753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94578003883362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95773005485535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9622118473053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93532299995422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91291618347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97864365577698</t>
+    <t xml:space="preserve">2.96519947052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88901519775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98013758659363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97266817092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94577980041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9577305316925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96221160888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9353232383728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91291642189026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9786434173584</t>
   </si>
   <si>
     <t xml:space="preserve">2.98611235618591</t>
@@ -80,13 +80,13 @@
     <t xml:space="preserve">3.03540825843811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05632138252258</t>
+    <t xml:space="preserve">3.05632162094116</t>
   </si>
   <si>
     <t xml:space="preserve">3.0593090057373</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05034613609314</t>
+    <t xml:space="preserve">3.05034589767456</t>
   </si>
   <si>
     <t xml:space="preserve">2.98760628700256</t>
@@ -95,52 +95,52 @@
     <t xml:space="preserve">2.95026135444641</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01598882675171</t>
+    <t xml:space="preserve">3.01598858833313</t>
   </si>
   <si>
     <t xml:space="preserve">3.01001358032227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02495169639587</t>
+    <t xml:space="preserve">3.02495145797729</t>
   </si>
   <si>
     <t xml:space="preserve">3.0174822807312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03092670440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99955701828003</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0443708896637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95922422409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00254464149475</t>
+    <t xml:space="preserve">3.03092694282532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99955654144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04437112808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.959223985672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00254440307617</t>
   </si>
   <si>
     <t xml:space="preserve">2.92785429954529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90843510627747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89648413658142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9188916683197</t>
+    <t xml:space="preserve">2.90843486785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91889142990112</t>
   </si>
   <si>
     <t xml:space="preserve">2.9159038066864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92038536071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90544724464417</t>
+    <t xml:space="preserve">2.92038512229919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90544748306274</t>
   </si>
   <si>
     <t xml:space="preserve">2.90992832183838</t>
@@ -149,16 +149,16 @@
     <t xml:space="preserve">2.92337274551392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8382260799408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86063313484192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82627558708191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77996730804443</t>
+    <t xml:space="preserve">2.83822560310364</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86063289642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82627582550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77996754646301</t>
   </si>
   <si>
     <t xml:space="preserve">2.84569501876831</t>
@@ -167,25 +167,25 @@
     <t xml:space="preserve">2.86810207366943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88303995132446</t>
+    <t xml:space="preserve">2.88304018974304</t>
   </si>
   <si>
     <t xml:space="preserve">2.79639959335327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87557101249695</t>
+    <t xml:space="preserve">2.87557125091553</t>
   </si>
   <si>
     <t xml:space="preserve">2.89797830581665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80088090896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74262237548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8217945098877</t>
+    <t xml:space="preserve">2.80088114738464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74262261390686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82179474830627</t>
   </si>
   <si>
     <t xml:space="preserve">2.75009155273438</t>
@@ -203,10 +203,10 @@
     <t xml:space="preserve">2.79341197013855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69631457328796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65150094032288</t>
+    <t xml:space="preserve">2.69631433486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6515007019043</t>
   </si>
   <si>
     <t xml:space="preserve">2.62162446975708</t>
@@ -215,19 +215,19 @@
     <t xml:space="preserve">2.53946566581726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56934118270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61415553092957</t>
+    <t xml:space="preserve">2.56934142112732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61415576934814</t>
   </si>
   <si>
     <t xml:space="preserve">2.65896964073181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68884563446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70378351211548</t>
+    <t xml:space="preserve">2.68884539604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70378375053406</t>
   </si>
   <si>
     <t xml:space="preserve">2.77100491523743</t>
@@ -236,10 +236,10 @@
     <t xml:space="preserve">2.81581878662109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7336597442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66643881797791</t>
+    <t xml:space="preserve">2.73365998268127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66643857955933</t>
   </si>
   <si>
     <t xml:space="preserve">2.68137645721436</t>
@@ -260,7 +260,7 @@
     <t xml:space="preserve">2.69871854782104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83870959281921</t>
+    <t xml:space="preserve">2.83870983123779</t>
   </si>
   <si>
     <t xml:space="preserve">2.93203687667847</t>
@@ -272,31 +272,31 @@
     <t xml:space="preserve">2.83093237876892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81537771224976</t>
+    <t xml:space="preserve">2.81537747383118</t>
   </si>
   <si>
     <t xml:space="preserve">2.84648704528809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79982304573059</t>
+    <t xml:space="preserve">2.79982328414917</t>
   </si>
   <si>
     <t xml:space="preserve">2.73760485649109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76093697547913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8076000213623</t>
+    <t xml:space="preserve">2.76093649864197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80760025978088</t>
   </si>
   <si>
     <t xml:space="preserve">3.00980997085571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95536923408508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90870523452759</t>
+    <t xml:space="preserve">2.95536851882935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90870547294617</t>
   </si>
   <si>
     <t xml:space="preserve">2.88537335395813</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">2.86204171180725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00203251838684</t>
+    <t xml:space="preserve">3.00203275680542</t>
   </si>
   <si>
     <t xml:space="preserve">2.91648268699646</t>
@@ -320,25 +320,25 @@
     <t xml:space="preserve">2.7298276424408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68316411972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7220504283905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75315928459167</t>
+    <t xml:space="preserve">2.6831636428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72205018997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75315952301025</t>
   </si>
   <si>
     <t xml:space="preserve">2.70649576187134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93981432914734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99425530433655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97870063781738</t>
+    <t xml:space="preserve">2.93981409072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99425554275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97870087623596</t>
   </si>
   <si>
     <t xml:space="preserve">2.86981892585754</t>
@@ -350,16 +350,16 @@
     <t xml:space="preserve">2.98647809028625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63650012016296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55094981193542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51984095573425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41095852851868</t>
+    <t xml:space="preserve">2.63650059700012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.550950050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51984119415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41095900535583</t>
   </si>
   <si>
     <t xml:space="preserve">2.34096336364746</t>
@@ -374,25 +374,25 @@
     <t xml:space="preserve">2.2554132938385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24763631820679</t>
+    <t xml:space="preserve">2.24763584136963</t>
   </si>
   <si>
     <t xml:space="preserve">2.3254086971283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23208117485046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18541765213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27874493598938</t>
+    <t xml:space="preserve">2.23208093643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18541741371155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27874517440796</t>
   </si>
   <si>
     <t xml:space="preserve">2.26319050788879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2165265083313</t>
+    <t xml:space="preserve">2.21652674674988</t>
   </si>
   <si>
     <t xml:space="preserve">2.06875824928284</t>
@@ -401,7 +401,7 @@
     <t xml:space="preserve">2.1465311050415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10764479637146</t>
+    <t xml:space="preserve">2.10764455795288</t>
   </si>
   <si>
     <t xml:space="preserve">2.1543083190918</t>
@@ -410,10 +410,10 @@
     <t xml:space="preserve">2.17764019966125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22430396080017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35651803016663</t>
+    <t xml:space="preserve">2.22430372238159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35651779174805</t>
   </si>
   <si>
     <t xml:space="preserve">2.4887318611145</t>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">2.52761816978455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43429064750671</t>
+    <t xml:space="preserve">2.43429088592529</t>
   </si>
   <si>
     <t xml:space="preserve">2.44206809997559</t>
@@ -440,13 +440,13 @@
     <t xml:space="preserve">2.33318591117859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29429936408997</t>
+    <t xml:space="preserve">2.29429984092712</t>
   </si>
   <si>
     <t xml:space="preserve">2.3798496723175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71427297592163</t>
+    <t xml:space="preserve">2.71427321434021</t>
   </si>
   <si>
     <t xml:space="preserve">2.58205890655518</t>
@@ -455,10 +455,10 @@
     <t xml:space="preserve">2.62872314453125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65983200073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57428193092346</t>
+    <t xml:space="preserve">2.659832239151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57428169250488</t>
   </si>
   <si>
     <t xml:space="preserve">2.67538666725159</t>
@@ -467,31 +467,31 @@
     <t xml:space="preserve">2.64427781105042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69094109535217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76871395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90092825889587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9631462097168</t>
+    <t xml:space="preserve">2.69094085693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76871418952942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90092802047729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96314597129822</t>
   </si>
   <si>
     <t xml:space="preserve">2.92425966262817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97092342376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01758742332458</t>
+    <t xml:space="preserve">2.97092318534851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01758766174316</t>
   </si>
   <si>
     <t xml:space="preserve">3.04869627952576</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03314185142517</t>
+    <t xml:space="preserve">3.03314208984375</t>
   </si>
   <si>
     <t xml:space="preserve">3.06425094604492</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">3.07980537414551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0604989528656</t>
+    <t xml:space="preserve">3.06049871444702</t>
   </si>
   <si>
     <t xml:space="preserve">3.02811288833618</t>
@@ -524,16 +524,16 @@
     <t xml:space="preserve">2.99572682380676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30339574813843</t>
+    <t xml:space="preserve">3.30339598655701</t>
   </si>
   <si>
     <t xml:space="preserve">3.41674757003784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35197496414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33578181266785</t>
+    <t xml:space="preserve">3.35197520256042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33578157424927</t>
   </si>
   <si>
     <t xml:space="preserve">3.36816811561584</t>
@@ -566,7 +566,7 @@
     <t xml:space="preserve">3.40055418014526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49771356582642</t>
+    <t xml:space="preserve">3.49771332740784</t>
   </si>
   <si>
     <t xml:space="preserve">3.38436126708984</t>
@@ -575,22 +575,22 @@
     <t xml:space="preserve">3.25481653213501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19004392623901</t>
+    <t xml:space="preserve">3.19004416465759</t>
   </si>
   <si>
     <t xml:space="preserve">2.96334028244019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97953343391418</t>
+    <t xml:space="preserve">2.97953367233276</t>
   </si>
   <si>
     <t xml:space="preserve">2.80140900611877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88237476348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86618185043335</t>
+    <t xml:space="preserve">2.88237500190735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86618161201477</t>
   </si>
   <si>
     <t xml:space="preserve">2.84998846054077</t>
@@ -599,22 +599,22 @@
     <t xml:space="preserve">2.78521609306335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75283026695251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72044348716736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83379530906677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76902294158936</t>
+    <t xml:space="preserve">2.75282979011536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72044372558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83379554748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76902318000793</t>
   </si>
   <si>
     <t xml:space="preserve">2.73663687705994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81760215759277</t>
+    <t xml:space="preserve">2.81760239601135</t>
   </si>
   <si>
     <t xml:space="preserve">2.89856791496277</t>
@@ -623,40 +623,40 @@
     <t xml:space="preserve">2.91476082801819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63947820663452</t>
+    <t xml:space="preserve">2.63947796821594</t>
   </si>
   <si>
     <t xml:space="preserve">2.67186403274536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62328481674194</t>
+    <t xml:space="preserve">2.62328505516052</t>
   </si>
   <si>
     <t xml:space="preserve">2.68805718421936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70425057411194</t>
+    <t xml:space="preserve">2.70425009727478</t>
   </si>
   <si>
     <t xml:space="preserve">2.60709190368652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5908989906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42896747589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54231953620911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46135354042053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3156156539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29942226409912</t>
+    <t xml:space="preserve">2.59089851379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42896723747253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54231929779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46135377883911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31561541557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2994225025177</t>
   </si>
   <si>
     <t xml:space="preserve">2.35488152503967</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">2.55965399742126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54258966445923</t>
+    <t xml:space="preserve">2.54258990287781</t>
   </si>
   <si>
     <t xml:space="preserve">2.45726799964905</t>
@@ -707,16 +707,16 @@
     <t xml:space="preserve">2.5767183303833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62791156768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61084723472595</t>
+    <t xml:space="preserve">2.62791132926941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61084699630737</t>
   </si>
   <si>
     <t xml:space="preserve">2.64497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59378266334534</t>
+    <t xml:space="preserve">2.59378290176392</t>
   </si>
   <si>
     <t xml:space="preserve">2.69616889953613</t>
@@ -728,10 +728,10 @@
     <t xml:space="preserve">2.44020342826843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42313885688782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47433233261108</t>
+    <t xml:space="preserve">2.4231390953064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47433257102966</t>
   </si>
   <si>
     <t xml:space="preserve">2.15010952949524</t>
@@ -740,10 +740,10 @@
     <t xml:space="preserve">2.33781743049622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30368852615356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25249552726746</t>
+    <t xml:space="preserve">2.30368876457214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25249576568604</t>
   </si>
   <si>
     <t xml:space="preserve">2.23543095588684</t>
@@ -773,31 +773,31 @@
     <t xml:space="preserve">1.91120839118958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8770797252655</t>
+    <t xml:space="preserve">1.87707984447479</t>
   </si>
   <si>
     <t xml:space="preserve">1.84295094013214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97946572303772</t>
+    <t xml:space="preserve">1.97946584224701</t>
   </si>
   <si>
     <t xml:space="preserve">1.86001539230347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94533681869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96240139007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99653005599976</t>
+    <t xml:space="preserve">1.94533693790436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96240127086639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99653017520905</t>
   </si>
   <si>
     <t xml:space="preserve">2.81561923027039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9009416103363</t>
+    <t xml:space="preserve">2.90094137191772</t>
   </si>
   <si>
     <t xml:space="preserve">2.88387703895569</t>
@@ -806,13 +806,13 @@
     <t xml:space="preserve">2.76442646980286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73029780387878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67910480499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74736213684082</t>
+    <t xml:space="preserve">2.73029756546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6791045665741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74736189842224</t>
   </si>
   <si>
     <t xml:space="preserve">2.83268356323242</t>
@@ -821,10 +821,10 @@
     <t xml:space="preserve">2.86681246757507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79855513572693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78149080276489</t>
+    <t xml:space="preserve">2.79855489730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78149056434631</t>
   </si>
   <si>
     <t xml:space="preserve">2.9350700378418</t>
@@ -833,7 +833,7 @@
     <t xml:space="preserve">2.96919870376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02039194107056</t>
+    <t xml:space="preserve">3.02039170265198</t>
   </si>
   <si>
     <t xml:space="preserve">3.00332736968994</t>
@@ -854,16 +854,16 @@
     <t xml:space="preserve">3.13984251022339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11424565315247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1313099861145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06305241584778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16543889045715</t>
+    <t xml:space="preserve">3.11424589157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13131022453308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06305265426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16543912887573</t>
   </si>
   <si>
     <t xml:space="preserve">3.1995677947998</t>
@@ -872,7 +872,7 @@
     <t xml:space="preserve">3.15690684318542</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23369598388672</t>
+    <t xml:space="preserve">3.2336962223053</t>
   </si>
   <si>
     <t xml:space="preserve">3.27635717391968</t>
@@ -884,19 +884,19 @@
     <t xml:space="preserve">3.26782488822937</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31048631668091</t>
+    <t xml:space="preserve">3.31048607826233</t>
   </si>
   <si>
     <t xml:space="preserve">3.34461450576782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32755064964294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28488922119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18250322341919</t>
+    <t xml:space="preserve">3.32755041122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28488945960999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18250346183777</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342150688171</t>
@@ -905,10 +905,10 @@
     <t xml:space="preserve">3.33710074424744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32836508750916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24974226951599</t>
+    <t xml:space="preserve">3.32836484909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24974250793457</t>
   </si>
   <si>
     <t xml:space="preserve">3.20606303215027</t>
@@ -929,10 +929,10 @@
     <t xml:space="preserve">3.36330842971802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49434661865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58170485496521</t>
+    <t xml:space="preserve">3.49434638023376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58170509338379</t>
   </si>
   <si>
     <t xml:space="preserve">3.56423354148865</t>
@@ -956,31 +956,31 @@
     <t xml:space="preserve">3.62538456916809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7476863861084</t>
+    <t xml:space="preserve">3.74768662452698</t>
   </si>
   <si>
     <t xml:space="preserve">3.69527125358582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66906356811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60791277885437</t>
+    <t xml:space="preserve">3.66906332969666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60791301727295</t>
   </si>
   <si>
     <t xml:space="preserve">3.55549788475037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66032791137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65159201622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68653535842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70400714874268</t>
+    <t xml:space="preserve">3.66032767295837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65159177780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68653512001038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7040069103241</t>
   </si>
   <si>
     <t xml:space="preserve">3.75642275810242</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">3.3458366394043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3895161151886</t>
+    <t xml:space="preserve">3.38951635360718</t>
   </si>
   <si>
     <t xml:space="preserve">3.42445969581604</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">3.46813893318176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47687482833862</t>
+    <t xml:space="preserve">3.47687458992004</t>
   </si>
   <si>
     <t xml:space="preserve">3.79136610031128</t>
@@ -1034,7 +1034,7 @@
     <t xml:space="preserve">3.72147917747498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87872457504272</t>
+    <t xml:space="preserve">3.8787248134613</t>
   </si>
   <si>
     <t xml:space="preserve">4.17574453353882</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">4.1844801902771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20195150375366</t>
+    <t xml:space="preserve">4.20195198059082</t>
   </si>
   <si>
     <t xml:space="preserve">4.25436639785767</t>
@@ -1058,10 +1058,10 @@
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493226051331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98355507850647</t>
+    <t xml:space="preserve">3.90493202209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98355484008789</t>
   </si>
   <si>
     <t xml:space="preserve">3.94861149787903</t>
@@ -1070,13 +1070,13 @@
     <t xml:space="preserve">3.93113970756531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08838558197021</t>
+    <t xml:space="preserve">4.08838510513306</t>
   </si>
   <si>
     <t xml:space="preserve">4.07091331481934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12332916259766</t>
+    <t xml:space="preserve">4.1233286857605</t>
   </si>
   <si>
     <t xml:space="preserve">4.00102663040161</t>
@@ -1085,13 +1085,13 @@
     <t xml:space="preserve">4.00976276397705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93987584114075</t>
+    <t xml:space="preserve">3.93987560272217</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2106876373291</t>
+    <t xml:space="preserve">4.21068811416626</t>
   </si>
   <si>
     <t xml:space="preserve">4.29804611206055</t>
@@ -1109,16 +1109,16 @@
     <t xml:space="preserve">4.14953660964966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16700792312622</t>
+    <t xml:space="preserve">4.16700839996338</t>
   </si>
   <si>
     <t xml:space="preserve">4.11459302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06217765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78262996673584</t>
+    <t xml:space="preserve">4.06217813491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78263020515442</t>
   </si>
   <si>
     <t xml:space="preserve">3.80010175704956</t>
@@ -1127,13 +1127,13 @@
     <t xml:space="preserve">3.82630944252014</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83504557609558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84378147125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77389430999756</t>
+    <t xml:space="preserve">3.83504509925842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84378123283386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77389454841614</t>
   </si>
   <si>
     <t xml:space="preserve">4.03597021102905</t>
@@ -1148,13 +1148,13 @@
     <t xml:space="preserve">3.86125302314758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76515817642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81757354736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64285635948181</t>
+    <t xml:space="preserve">3.7651584148407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8175733089447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64285612106323</t>
   </si>
   <si>
     <t xml:space="preserve">3.67779946327209</t>
@@ -1172,7 +1172,7 @@
     <t xml:space="preserve">3.92240381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61664843559265</t>
+    <t xml:space="preserve">3.61664867401123</t>
   </si>
   <si>
     <t xml:space="preserve">3.39825224876404</t>
@@ -1181,19 +1181,19 @@
     <t xml:space="preserve">3.23227071762085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05755305290222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97019481658936</t>
+    <t xml:space="preserve">3.0575532913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97019457817078</t>
   </si>
   <si>
     <t xml:space="preserve">2.95272302627563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91777944564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90904331207275</t>
+    <t xml:space="preserve">2.91777920722961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90904355049133</t>
   </si>
   <si>
     <t xml:space="preserve">3.37204432487488</t>
@@ -1202,13 +1202,13 @@
     <t xml:space="preserve">3.38078022003174</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41572380065918</t>
+    <t xml:space="preserve">3.41572403907776</t>
   </si>
   <si>
     <t xml:space="preserve">3.31962895393372</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27595019340515</t>
+    <t xml:space="preserve">3.27594995498657</t>
   </si>
   <si>
     <t xml:space="preserve">3.28468561172485</t>
@@ -55843,7 +55843,7 @@
     </row>
     <row r="2069">
       <c r="A2069" s="1" t="n">
-        <v>45975.6375</v>
+        <v>45975.3333333333</v>
       </c>
       <c r="B2069" t="n">
         <v>83593</v>
@@ -55864,6 +55864,32 @@
         <v>568</v>
       </c>
       <c r="H2069" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2070">
+      <c r="A2070" s="1" t="n">
+        <v>45978.6934837963</v>
+      </c>
+      <c r="B2070" t="n">
+        <v>10164</v>
+      </c>
+      <c r="C2070" t="n">
+        <v>3.27999997138977</v>
+      </c>
+      <c r="D2070" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="E2070" t="n">
+        <v>3.24000000953674</v>
+      </c>
+      <c r="F2070" t="n">
+        <v>3.1800000667572</v>
+      </c>
+      <c r="G2070" t="s">
+        <v>570</v>
+      </c>
+      <c r="H2070" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -47,19 +47,19 @@
     <t xml:space="preserve">2.96519947052002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88901519775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98013758659363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97266817092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94577980041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9577305316925</t>
+    <t xml:space="preserve">2.88901567459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98013734817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97266840934753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94577956199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95773029327393</t>
   </si>
   <si>
     <t xml:space="preserve">2.96221160888672</t>
@@ -71,25 +71,25 @@
     <t xml:space="preserve">2.91291642189026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9786434173584</t>
+    <t xml:space="preserve">2.97864365577698</t>
   </si>
   <si>
     <t xml:space="preserve">2.98611235618591</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03540825843811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05632162094116</t>
+    <t xml:space="preserve">3.03540802001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05632138252258</t>
   </si>
   <si>
     <t xml:space="preserve">3.0593090057373</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05034589767456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98760628700256</t>
+    <t xml:space="preserve">3.05034613609314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98760652542114</t>
   </si>
   <si>
     <t xml:space="preserve">2.95026135444641</t>
@@ -107,13 +107,13 @@
     <t xml:space="preserve">3.0174822807312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03092694282532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99955654144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04437112808228</t>
+    <t xml:space="preserve">3.03092670440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99955677986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0443708896637</t>
   </si>
   <si>
     <t xml:space="preserve">2.959223985672</t>
@@ -128,43 +128,43 @@
     <t xml:space="preserve">2.90843486785889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91889142990112</t>
+    <t xml:space="preserve">2.89648461341858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91889119148254</t>
   </si>
   <si>
     <t xml:space="preserve">2.9159038066864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92038512229919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90544748306274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90992832183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92337274551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83822560310364</t>
+    <t xml:space="preserve">2.92038536071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90544700622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90992879867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9233729839325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83822631835938</t>
   </si>
   <si>
     <t xml:space="preserve">2.86063289642334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82627582550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77996754646301</t>
+    <t xml:space="preserve">2.82627534866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77996778488159</t>
   </si>
   <si>
     <t xml:space="preserve">2.84569501876831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86810207366943</t>
+    <t xml:space="preserve">2.86810231208801</t>
   </si>
   <si>
     <t xml:space="preserve">2.88304018974304</t>
@@ -173,19 +173,19 @@
     <t xml:space="preserve">2.79639959335327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87557125091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89797830581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80088114738464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74262261390686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82179474830627</t>
+    <t xml:space="preserve">2.87557101249695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89797806739807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80088067054749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74262237548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82179427146912</t>
   </si>
   <si>
     <t xml:space="preserve">2.75009155273438</t>
@@ -203,28 +203,28 @@
     <t xml:space="preserve">2.79341197013855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69631433486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6515007019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62162446975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53946566581726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56934142112732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61415576934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65896964073181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68884539604187</t>
+    <t xml:space="preserve">2.69631457328796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65150046348572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62162470817566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53946542739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5693416595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61415553092957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65896940231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68884587287903</t>
   </si>
   <si>
     <t xml:space="preserve">2.70378375053406</t>
@@ -233,28 +233,28 @@
     <t xml:space="preserve">2.77100491523743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81581878662109</t>
+    <t xml:space="preserve">2.81581902503967</t>
   </si>
   <si>
     <t xml:space="preserve">2.73365998268127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66643857955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68137645721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74112892150879</t>
+    <t xml:space="preserve">2.66643834114075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68137669563293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74112868309021</t>
   </si>
   <si>
     <t xml:space="preserve">2.72619080543518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8307569026947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.893150806427</t>
+    <t xml:space="preserve">2.83075714111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89315056800842</t>
   </si>
   <si>
     <t xml:space="preserve">2.69871854782104</t>
@@ -263,7 +263,7 @@
     <t xml:space="preserve">2.83870983123779</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93203687667847</t>
+    <t xml:space="preserve">2.93203711509705</t>
   </si>
   <si>
     <t xml:space="preserve">2.87759613990784</t>
@@ -272,16 +272,16 @@
     <t xml:space="preserve">2.83093237876892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81537747383118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84648704528809</t>
+    <t xml:space="preserve">2.81537771224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84648680686951</t>
   </si>
   <si>
     <t xml:space="preserve">2.79982328414917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73760485649109</t>
+    <t xml:space="preserve">2.73760509490967</t>
   </si>
   <si>
     <t xml:space="preserve">2.76093649864197</t>
@@ -293,70 +293,70 @@
     <t xml:space="preserve">3.00980997085571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95536851882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90870547294617</t>
+    <t xml:space="preserve">2.95536875724792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90870523452759</t>
   </si>
   <si>
     <t xml:space="preserve">2.88537335395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82315516471863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86204171180725</t>
+    <t xml:space="preserve">2.82315540313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86204147338867</t>
   </si>
   <si>
     <t xml:space="preserve">3.00203275680542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91648268699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85426449775696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7298276424408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6831636428833</t>
+    <t xml:space="preserve">2.91648244857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85426425933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72982788085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68316388130188</t>
   </si>
   <si>
     <t xml:space="preserve">2.72205018997192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75315952301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70649576187134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93981409072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99425554275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97870087623596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86981892585754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94759154319763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98647809028625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63650059700012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.550950050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51984119415283</t>
+    <t xml:space="preserve">2.75315928459167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70649600028992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93981432914734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99425530433655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9787003993988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86981868743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94759178161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98647832870483</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63650035858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55094981193542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51984071731567</t>
   </si>
   <si>
     <t xml:space="preserve">2.41095900535583</t>
@@ -368,31 +368,31 @@
     <t xml:space="preserve">2.34874057769775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36429524421692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2554132938385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24763584136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3254086971283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23208093643188</t>
+    <t xml:space="preserve">2.36429500579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25541305541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24763607978821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32540893554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23208117485046</t>
   </si>
   <si>
     <t xml:space="preserve">2.18541741371155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27874517440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26319050788879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21652674674988</t>
+    <t xml:space="preserve">2.27874493598938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26319026947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2165265083313</t>
   </si>
   <si>
     <t xml:space="preserve">2.06875824928284</t>
@@ -404,7 +404,7 @@
     <t xml:space="preserve">2.10764455795288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1543083190918</t>
+    <t xml:space="preserve">2.15430879592896</t>
   </si>
   <si>
     <t xml:space="preserve">2.17764019966125</t>
@@ -419,28 +419,28 @@
     <t xml:space="preserve">2.4887318611145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52761816978455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43429088592529</t>
+    <t xml:space="preserve">2.52761840820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43429112434387</t>
   </si>
   <si>
     <t xml:space="preserve">2.44206809997559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55872750282288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44984555244446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37207245826721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33318591117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29429984092712</t>
+    <t xml:space="preserve">2.5587272644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44984531402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37207221984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33318614959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29429960250854</t>
   </si>
   <si>
     <t xml:space="preserve">2.3798496723175</t>
@@ -449,13 +449,13 @@
     <t xml:space="preserve">2.71427321434021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58205890655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62872314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.659832239151</t>
+    <t xml:space="preserve">2.58205938339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62872290611267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65983200073242</t>
   </si>
   <si>
     <t xml:space="preserve">2.57428169250488</t>
@@ -464,43 +464,43 @@
     <t xml:space="preserve">2.67538666725159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64427781105042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69094085693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76871418952942</t>
+    <t xml:space="preserve">2.64427757263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69094133377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76871395111084</t>
   </si>
   <si>
     <t xml:space="preserve">2.90092802047729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96314597129822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92425966262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97092318534851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01758766174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04869627952576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03314208984375</t>
+    <t xml:space="preserve">2.9631462097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92425990104675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97092342376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01758718490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04869651794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03314185142517</t>
   </si>
   <si>
     <t xml:space="preserve">3.06425094604492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07980537414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06049871444702</t>
+    <t xml:space="preserve">3.07980561256409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0604989528656</t>
   </si>
   <si>
     <t xml:space="preserve">3.02811288833618</t>
@@ -509,16 +509,16 @@
     <t xml:space="preserve">3.01191973686218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1090784072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0928852558136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12527132034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07669186592102</t>
+    <t xml:space="preserve">3.10907816886902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09288501739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1252715587616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0766921043396</t>
   </si>
   <si>
     <t xml:space="preserve">2.99572682380676</t>
@@ -527,10 +527,10 @@
     <t xml:space="preserve">3.30339598655701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41674757003784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35197520256042</t>
+    <t xml:space="preserve">3.41674733161926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35197496414185</t>
   </si>
   <si>
     <t xml:space="preserve">3.33578157424927</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">3.31958866119385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27100968360901</t>
+    <t xml:space="preserve">3.27100944519043</t>
   </si>
   <si>
     <t xml:space="preserve">3.28720259666443</t>
@@ -554,13 +554,13 @@
     <t xml:space="preserve">3.22243022918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17385053634644</t>
+    <t xml:space="preserve">3.17385101318359</t>
   </si>
   <si>
     <t xml:space="preserve">3.20623707771301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14146494865417</t>
+    <t xml:space="preserve">3.1414647102356</t>
   </si>
   <si>
     <t xml:space="preserve">3.40055418014526</t>
@@ -584,10 +584,10 @@
     <t xml:space="preserve">2.97953367233276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80140900611877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88237500190735</t>
+    <t xml:space="preserve">2.80140924453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88237476348877</t>
   </si>
   <si>
     <t xml:space="preserve">2.86618161201477</t>
@@ -596,19 +596,19 @@
     <t xml:space="preserve">2.84998846054077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78521609306335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75282979011536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72044372558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83379554748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76902318000793</t>
+    <t xml:space="preserve">2.78521585464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75283026695251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72044348716736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83379530906677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76902294158936</t>
   </si>
   <si>
     <t xml:space="preserve">2.73663687705994</t>
@@ -623,37 +623,37 @@
     <t xml:space="preserve">2.91476082801819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63947796821594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67186403274536</t>
+    <t xml:space="preserve">2.63947820663452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67186427116394</t>
   </si>
   <si>
     <t xml:space="preserve">2.62328505516052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68805718421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70425009727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60709190368652</t>
+    <t xml:space="preserve">2.68805742263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70425057411194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60709166526794</t>
   </si>
   <si>
     <t xml:space="preserve">2.59089851379395</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42896723747253</t>
+    <t xml:space="preserve">2.42896747589111</t>
   </si>
   <si>
     <t xml:space="preserve">2.54231929779053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46135377883911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31561541557312</t>
+    <t xml:space="preserve">2.46135354042053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3156156539917</t>
   </si>
   <si>
     <t xml:space="preserve">2.2994225025177</t>
@@ -662,19 +662,19 @@
     <t xml:space="preserve">2.35488152503967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40607476234436</t>
+    <t xml:space="preserve">2.40607452392578</t>
   </si>
   <si>
     <t xml:space="preserve">2.28662443161011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13304495811462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08185195922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0647873878479</t>
+    <t xml:space="preserve">2.1330451965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08185172080994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06478762626648</t>
   </si>
   <si>
     <t xml:space="preserve">2.03065896034241</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">2.26956009864807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2183666229248</t>
+    <t xml:space="preserve">2.21836638450623</t>
   </si>
   <si>
     <t xml:space="preserve">2.32075309753418</t>
@@ -698,31 +698,31 @@
     <t xml:space="preserve">2.55965399742126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54258990287781</t>
+    <t xml:space="preserve">2.54258966445923</t>
   </si>
   <si>
     <t xml:space="preserve">2.45726799964905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5767183303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62791132926941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61084699630737</t>
+    <t xml:space="preserve">2.57671856880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62791156768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61084723472595</t>
   </si>
   <si>
     <t xml:space="preserve">2.64497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59378290176392</t>
+    <t xml:space="preserve">2.59378266334534</t>
   </si>
   <si>
     <t xml:space="preserve">2.69616889953613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71323323249817</t>
+    <t xml:space="preserve">2.71323347091675</t>
   </si>
   <si>
     <t xml:space="preserve">2.44020342826843</t>
@@ -731,10 +731,10 @@
     <t xml:space="preserve">2.4231390953064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47433257102966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15010952949524</t>
+    <t xml:space="preserve">2.47433233261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15010929107666</t>
   </si>
   <si>
     <t xml:space="preserve">2.33781743049622</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">2.30368876457214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25249576568604</t>
+    <t xml:space="preserve">2.25249552726746</t>
   </si>
   <si>
     <t xml:space="preserve">2.23543095588684</t>
@@ -758,13 +758,13 @@
     <t xml:space="preserve">2.20130252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18423795700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01359438896179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04772329330444</t>
+    <t xml:space="preserve">2.18423819541931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01359462738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04772353172302</t>
   </si>
   <si>
     <t xml:space="preserve">2.11598062515259</t>
@@ -773,31 +773,31 @@
     <t xml:space="preserve">1.91120839118958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87707984447479</t>
+    <t xml:space="preserve">1.8770797252655</t>
   </si>
   <si>
     <t xml:space="preserve">1.84295094013214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97946584224701</t>
+    <t xml:space="preserve">1.97946560382843</t>
   </si>
   <si>
     <t xml:space="preserve">1.86001539230347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94533693790436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96240127086639</t>
+    <t xml:space="preserve">1.94533705711365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9624011516571</t>
   </si>
   <si>
     <t xml:space="preserve">1.99653017520905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81561923027039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90094137191772</t>
+    <t xml:space="preserve">2.81561946868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9009416103363</t>
   </si>
   <si>
     <t xml:space="preserve">2.88387703895569</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">2.74736189842224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83268356323242</t>
+    <t xml:space="preserve">2.832683801651</t>
   </si>
   <si>
     <t xml:space="preserve">2.86681246757507</t>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">2.79855489730835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78149056434631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9350700378418</t>
+    <t xml:space="preserve">2.78149080276489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93506979942322</t>
   </si>
   <si>
     <t xml:space="preserve">2.96919870376587</t>
@@ -839,10 +839,10 @@
     <t xml:space="preserve">3.00332736968994</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03745627403259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98626303672791</t>
+    <t xml:space="preserve">3.03745603561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98626279830933</t>
   </si>
   <si>
     <t xml:space="preserve">3.05452060699463</t>
@@ -860,10 +860,10 @@
     <t xml:space="preserve">3.13131022453308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06305265426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16543912887573</t>
+    <t xml:space="preserve">3.06305241584778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16543889045715</t>
   </si>
   <si>
     <t xml:space="preserve">3.1995677947998</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">3.2336962223053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27635717391968</t>
+    <t xml:space="preserve">3.2763569355011</t>
   </si>
   <si>
     <t xml:space="preserve">3.24222826957703</t>
@@ -884,19 +884,19 @@
     <t xml:space="preserve">3.26782488822937</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31048607826233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34461450576782</t>
+    <t xml:space="preserve">3.31048583984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3446147441864</t>
   </si>
   <si>
     <t xml:space="preserve">3.32755041122437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28488945960999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18250346183777</t>
+    <t xml:space="preserve">3.28488922119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18250322341919</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342150688171</t>
@@ -905,10 +905,10 @@
     <t xml:space="preserve">3.33710074424744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32836484909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24974250793457</t>
+    <t xml:space="preserve">3.32836508750916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24974226951599</t>
   </si>
   <si>
     <t xml:space="preserve">3.20606303215027</t>
@@ -929,10 +929,10 @@
     <t xml:space="preserve">3.36330842971802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49434638023376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58170509338379</t>
+    <t xml:space="preserve">3.49434661865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58170485496521</t>
   </si>
   <si>
     <t xml:space="preserve">3.56423354148865</t>
@@ -956,31 +956,31 @@
     <t xml:space="preserve">3.62538456916809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74768662452698</t>
+    <t xml:space="preserve">3.7476863861084</t>
   </si>
   <si>
     <t xml:space="preserve">3.69527125358582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66906332969666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60791301727295</t>
+    <t xml:space="preserve">3.66906356811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60791277885437</t>
   </si>
   <si>
     <t xml:space="preserve">3.55549788475037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66032767295837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65159177780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68653512001038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7040069103241</t>
+    <t xml:space="preserve">3.66032791137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65159201622009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68653535842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70400714874268</t>
   </si>
   <si>
     <t xml:space="preserve">3.75642275810242</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">3.3458366394043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38951635360718</t>
+    <t xml:space="preserve">3.3895161151886</t>
   </si>
   <si>
     <t xml:space="preserve">3.42445969581604</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">3.46813893318176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47687458992004</t>
+    <t xml:space="preserve">3.47687482833862</t>
   </si>
   <si>
     <t xml:space="preserve">3.79136610031128</t>
@@ -1034,7 +1034,7 @@
     <t xml:space="preserve">3.72147917747498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8787248134613</t>
+    <t xml:space="preserve">3.87872457504272</t>
   </si>
   <si>
     <t xml:space="preserve">4.17574453353882</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">4.1844801902771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20195198059082</t>
+    <t xml:space="preserve">4.20195150375366</t>
   </si>
   <si>
     <t xml:space="preserve">4.25436639785767</t>
@@ -1058,10 +1058,10 @@
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493202209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98355484008789</t>
+    <t xml:space="preserve">3.90493226051331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98355507850647</t>
   </si>
   <si>
     <t xml:space="preserve">3.94861149787903</t>
@@ -1070,13 +1070,13 @@
     <t xml:space="preserve">3.93113970756531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08838510513306</t>
+    <t xml:space="preserve">4.08838558197021</t>
   </si>
   <si>
     <t xml:space="preserve">4.07091331481934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1233286857605</t>
+    <t xml:space="preserve">4.12332916259766</t>
   </si>
   <si>
     <t xml:space="preserve">4.00102663040161</t>
@@ -1085,13 +1085,13 @@
     <t xml:space="preserve">4.00976276397705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93987560272217</t>
+    <t xml:space="preserve">3.93987584114075</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21068811416626</t>
+    <t xml:space="preserve">4.2106876373291</t>
   </si>
   <si>
     <t xml:space="preserve">4.29804611206055</t>
@@ -1109,16 +1109,16 @@
     <t xml:space="preserve">4.14953660964966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16700839996338</t>
+    <t xml:space="preserve">4.16700792312622</t>
   </si>
   <si>
     <t xml:space="preserve">4.11459302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06217813491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78263020515442</t>
+    <t xml:space="preserve">4.06217765808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78262996673584</t>
   </si>
   <si>
     <t xml:space="preserve">3.80010175704956</t>
@@ -1127,13 +1127,13 @@
     <t xml:space="preserve">3.82630944252014</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83504509925842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84378123283386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77389454841614</t>
+    <t xml:space="preserve">3.83504557609558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84378147125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77389430999756</t>
   </si>
   <si>
     <t xml:space="preserve">4.03597021102905</t>
@@ -1148,13 +1148,13 @@
     <t xml:space="preserve">3.86125302314758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7651584148407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8175733089447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64285612106323</t>
+    <t xml:space="preserve">3.76515817642212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81757354736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64285635948181</t>
   </si>
   <si>
     <t xml:space="preserve">3.67779946327209</t>
@@ -1172,7 +1172,7 @@
     <t xml:space="preserve">3.92240381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61664867401123</t>
+    <t xml:space="preserve">3.61664843559265</t>
   </si>
   <si>
     <t xml:space="preserve">3.39825224876404</t>
@@ -1181,19 +1181,19 @@
     <t xml:space="preserve">3.23227071762085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0575532913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97019457817078</t>
+    <t xml:space="preserve">3.05755305290222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97019481658936</t>
   </si>
   <si>
     <t xml:space="preserve">2.95272302627563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91777920722961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90904355049133</t>
+    <t xml:space="preserve">2.91777944564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90904331207275</t>
   </si>
   <si>
     <t xml:space="preserve">3.37204432487488</t>
@@ -1202,13 +1202,13 @@
     <t xml:space="preserve">3.38078022003174</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41572403907776</t>
+    <t xml:space="preserve">3.41572380065918</t>
   </si>
   <si>
     <t xml:space="preserve">3.31962895393372</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27594995498657</t>
+    <t xml:space="preserve">3.27595019340515</t>
   </si>
   <si>
     <t xml:space="preserve">3.28468561172485</t>
@@ -55869,7 +55869,7 @@
     </row>
     <row r="2070">
       <c r="A2070" s="1" t="n">
-        <v>45978.6934837963</v>
+        <v>45978.3333333333</v>
       </c>
       <c r="B2070" t="n">
         <v>10164</v>
@@ -55890,6 +55890,32 @@
         <v>570</v>
       </c>
       <c r="H2070" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2071">
+      <c r="A2071" s="1" t="n">
+        <v>45979.6910763889</v>
+      </c>
+      <c r="B2071" t="n">
+        <v>148452</v>
+      </c>
+      <c r="C2071" t="n">
+        <v>3.3199999332428</v>
+      </c>
+      <c r="D2071" t="n">
+        <v>3.16000008583069</v>
+      </c>
+      <c r="E2071" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="F2071" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="G2071" t="s">
+        <v>571</v>
+      </c>
+      <c r="H2071" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -44,22 +44,22 @@
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519899368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88901519775391</t>
+    <t xml:space="preserve">2.96519947052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88901543617249</t>
   </si>
   <si>
     <t xml:space="preserve">2.98013734817505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97266817092896</t>
+    <t xml:space="preserve">2.97266840934753</t>
   </si>
   <si>
     <t xml:space="preserve">2.94578003883362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95773029327393</t>
+    <t xml:space="preserve">2.95773005485535</t>
   </si>
   <si>
     <t xml:space="preserve">2.96221160888672</t>
@@ -68,37 +68,37 @@
     <t xml:space="preserve">2.9353232383728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91291618347168</t>
+    <t xml:space="preserve">2.9129159450531</t>
   </si>
   <si>
     <t xml:space="preserve">2.97864365577698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98611235618591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03540802001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05632138252258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05930876731873</t>
+    <t xml:space="preserve">2.98611259460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03540778160095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.056321144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05930948257446</t>
   </si>
   <si>
     <t xml:space="preserve">3.05034613609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98760604858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95026135444641</t>
+    <t xml:space="preserve">2.98760628700256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95026159286499</t>
   </si>
   <si>
     <t xml:space="preserve">3.01598882675171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01001358032227</t>
+    <t xml:space="preserve">3.01001334190369</t>
   </si>
   <si>
     <t xml:space="preserve">3.02495145797729</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">3.0174822807312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03092622756958</t>
+    <t xml:space="preserve">3.03092646598816</t>
   </si>
   <si>
     <t xml:space="preserve">2.99955654144287</t>
@@ -116,28 +116,28 @@
     <t xml:space="preserve">3.04437112808228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95922374725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00254440307617</t>
+    <t xml:space="preserve">2.95922422409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00254464149475</t>
   </si>
   <si>
     <t xml:space="preserve">2.92785406112671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90843510627747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89648413658142</t>
+    <t xml:space="preserve">2.90843486785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.896484375</t>
   </si>
   <si>
     <t xml:space="preserve">2.91889142990112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91590404510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92038536071777</t>
+    <t xml:space="preserve">2.9159038066864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92038512229919</t>
   </si>
   <si>
     <t xml:space="preserve">2.90544724464417</t>
@@ -155,10 +155,10 @@
     <t xml:space="preserve">2.86063313484192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82627558708191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77996778488159</t>
+    <t xml:space="preserve">2.82627534866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77996754646301</t>
   </si>
   <si>
     <t xml:space="preserve">2.84569525718689</t>
@@ -167,10 +167,10 @@
     <t xml:space="preserve">2.86810207366943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88304018974304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79639959335327</t>
+    <t xml:space="preserve">2.88303995132446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79639935493469</t>
   </si>
   <si>
     <t xml:space="preserve">2.87557125091553</t>
@@ -191,10 +191,10 @@
     <t xml:space="preserve">2.75009155273438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76353621482849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77847385406494</t>
+    <t xml:space="preserve">2.76353597640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77847409248352</t>
   </si>
   <si>
     <t xml:space="preserve">2.78594303131104</t>
@@ -209,7 +209,7 @@
     <t xml:space="preserve">2.65150046348572</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62162446975708</t>
+    <t xml:space="preserve">2.62162470817566</t>
   </si>
   <si>
     <t xml:space="preserve">2.53946566581726</t>
@@ -221,25 +221,25 @@
     <t xml:space="preserve">2.61415553092957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65896964073181</t>
+    <t xml:space="preserve">2.65896940231323</t>
   </si>
   <si>
     <t xml:space="preserve">2.68884563446045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70378375053406</t>
+    <t xml:space="preserve">2.70378351211548</t>
   </si>
   <si>
     <t xml:space="preserve">2.77100467681885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81581926345825</t>
+    <t xml:space="preserve">2.81581902503967</t>
   </si>
   <si>
     <t xml:space="preserve">2.73365998268127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66643857955933</t>
+    <t xml:space="preserve">2.66643834114075</t>
   </si>
   <si>
     <t xml:space="preserve">2.68137645721436</t>
@@ -248,16 +248,16 @@
     <t xml:space="preserve">2.74112892150879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72619104385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8307569026947</t>
+    <t xml:space="preserve">2.72619080543518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83075714111328</t>
   </si>
   <si>
     <t xml:space="preserve">2.89315056800842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69871854782104</t>
+    <t xml:space="preserve">2.69871878623962</t>
   </si>
   <si>
     <t xml:space="preserve">2.83870959281921</t>
@@ -272,10 +272,10 @@
     <t xml:space="preserve">2.8309326171875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81537795066833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84648704528809</t>
+    <t xml:space="preserve">2.81537771224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84648680686951</t>
   </si>
   <si>
     <t xml:space="preserve">2.79982304573059</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">2.76093673706055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80760049819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00981020927429</t>
+    <t xml:space="preserve">2.80760025978088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00980973243713</t>
   </si>
   <si>
     <t xml:space="preserve">2.9553689956665</t>
@@ -299,7 +299,7 @@
     <t xml:space="preserve">2.90870523452759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88537311553955</t>
+    <t xml:space="preserve">2.88537335395813</t>
   </si>
   <si>
     <t xml:space="preserve">2.82315540313721</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">2.86204171180725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00203275680542</t>
+    <t xml:space="preserve">3.00203251838684</t>
   </si>
   <si>
     <t xml:space="preserve">2.91648268699646</t>
@@ -326,16 +326,16 @@
     <t xml:space="preserve">2.7220504283905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75315928459167</t>
+    <t xml:space="preserve">2.75315952301025</t>
   </si>
   <si>
     <t xml:space="preserve">2.70649576187134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93981409072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99425554275513</t>
+    <t xml:space="preserve">2.93981432914734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99425482749939</t>
   </si>
   <si>
     <t xml:space="preserve">2.97870087623596</t>
@@ -344,22 +344,22 @@
     <t xml:space="preserve">2.86981892585754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94759154319763</t>
+    <t xml:space="preserve">2.94759130477905</t>
   </si>
   <si>
     <t xml:space="preserve">2.98647809028625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63650035858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.550950050354</t>
+    <t xml:space="preserve">2.63650012016296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55095028877258</t>
   </si>
   <si>
     <t xml:space="preserve">2.51984095573425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41095876693726</t>
+    <t xml:space="preserve">2.41095900535583</t>
   </si>
   <si>
     <t xml:space="preserve">2.34096336364746</t>
@@ -371,22 +371,22 @@
     <t xml:space="preserve">2.36429524421692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2554132938385</t>
+    <t xml:space="preserve">2.25541353225708</t>
   </si>
   <si>
     <t xml:space="preserve">2.24763607978821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32540893554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23208141326904</t>
+    <t xml:space="preserve">2.32540845870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23208117485046</t>
   </si>
   <si>
     <t xml:space="preserve">2.18541741371155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27874493598938</t>
+    <t xml:space="preserve">2.27874517440796</t>
   </si>
   <si>
     <t xml:space="preserve">2.26319050788879</t>
@@ -395,7 +395,7 @@
     <t xml:space="preserve">2.21652674674988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06875824928284</t>
+    <t xml:space="preserve">2.06875848770142</t>
   </si>
   <si>
     <t xml:space="preserve">2.14653134346008</t>
@@ -416,25 +416,25 @@
     <t xml:space="preserve">2.35651779174805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48873162269592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52761816978455</t>
+    <t xml:space="preserve">2.4887318611145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52761793136597</t>
   </si>
   <si>
     <t xml:space="preserve">2.43429064750671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44206809997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55872750282288</t>
+    <t xml:space="preserve">2.44206833839417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5587272644043</t>
   </si>
   <si>
     <t xml:space="preserve">2.44984531402588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37207245826721</t>
+    <t xml:space="preserve">2.37207221984863</t>
   </si>
   <si>
     <t xml:space="preserve">2.33318614959717</t>
@@ -446,7 +446,7 @@
     <t xml:space="preserve">2.3798496723175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71427321434021</t>
+    <t xml:space="preserve">2.71427297592163</t>
   </si>
   <si>
     <t xml:space="preserve">2.58205890655518</t>
@@ -455,16 +455,16 @@
     <t xml:space="preserve">2.62872290611267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65983200073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57428169250488</t>
+    <t xml:space="preserve">2.659832239151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57428193092346</t>
   </si>
   <si>
     <t xml:space="preserve">2.67538666725159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64427757263184</t>
+    <t xml:space="preserve">2.64427781105042</t>
   </si>
   <si>
     <t xml:space="preserve">2.69094133377075</t>
@@ -473,10 +473,10 @@
     <t xml:space="preserve">2.76871395111084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90092802047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96314644813538</t>
+    <t xml:space="preserve">2.90092754364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9631462097168</t>
   </si>
   <si>
     <t xml:space="preserve">2.92426013946533</t>
@@ -485,31 +485,31 @@
     <t xml:space="preserve">2.97092366218567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01758742332458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04869627952576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03314185142517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06425070762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07980561256409</t>
+    <t xml:space="preserve">3.01758766174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04869651794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03314208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0642511844635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07980585098267</t>
   </si>
   <si>
     <t xml:space="preserve">3.0604989528656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0281126499176</t>
+    <t xml:space="preserve">3.02811288833618</t>
   </si>
   <si>
     <t xml:space="preserve">3.01191973686218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1090784072876</t>
+    <t xml:space="preserve">3.10907816886902</t>
   </si>
   <si>
     <t xml:space="preserve">3.0928852558136</t>
@@ -518,13 +518,13 @@
     <t xml:space="preserve">3.1252715587616</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07669234275818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99572682380676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30339574813843</t>
+    <t xml:space="preserve">3.0766921043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99572658538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30339598655701</t>
   </si>
   <si>
     <t xml:space="preserve">3.41674757003784</t>
@@ -533,55 +533,55 @@
     <t xml:space="preserve">3.35197496414185</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33578157424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36816811561584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23862314224243</t>
+    <t xml:space="preserve">3.33578181266785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36816835403442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23862338066101</t>
   </si>
   <si>
     <t xml:space="preserve">3.31958866119385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27100920677185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28720259666443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22242999076843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17385077476501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20623707771301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1414647102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40055418014526</t>
+    <t xml:space="preserve">3.27100944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28720283508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22243022918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17385053634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20623731613159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14146494865417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40055441856384</t>
   </si>
   <si>
     <t xml:space="preserve">3.49771332740784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38436126708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25481653213501</t>
+    <t xml:space="preserve">3.38436102867126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25481629371643</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004392623901</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96334052085876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97953367233276</t>
+    <t xml:space="preserve">2.96334028244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97953343391418</t>
   </si>
   <si>
     <t xml:space="preserve">2.80140924453735</t>
@@ -593,19 +593,19 @@
     <t xml:space="preserve">2.86618161201477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84998822212219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78521609306335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75283002853394</t>
+    <t xml:space="preserve">2.84998846054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78521633148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75282979011536</t>
   </si>
   <si>
     <t xml:space="preserve">2.72044348716736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83379530906677</t>
+    <t xml:space="preserve">2.83379554748535</t>
   </si>
   <si>
     <t xml:space="preserve">2.76902294158936</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">2.81760239601135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89856767654419</t>
+    <t xml:space="preserve">2.89856743812561</t>
   </si>
   <si>
     <t xml:space="preserve">2.91476082801819</t>
@@ -626,22 +626,22 @@
     <t xml:space="preserve">2.63947796821594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67186403274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62328505516052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68805718421936</t>
+    <t xml:space="preserve">2.67186450958252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62328481674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68805694580078</t>
   </si>
   <si>
     <t xml:space="preserve">2.70425033569336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60709166526794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59089851379395</t>
+    <t xml:space="preserve">2.60709190368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59089875221252</t>
   </si>
   <si>
     <t xml:space="preserve">2.42896747589111</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">2.40607476234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28662443161011</t>
+    <t xml:space="preserve">2.28662419319153</t>
   </si>
   <si>
     <t xml:space="preserve">2.13304495811462</t>
@@ -689,7 +689,7 @@
     <t xml:space="preserve">2.26955986022949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2183666229248</t>
+    <t xml:space="preserve">2.21836686134338</t>
   </si>
   <si>
     <t xml:space="preserve">2.32075309753418</t>
@@ -698,16 +698,16 @@
     <t xml:space="preserve">2.55965399742126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54258990287781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45726823806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57671856880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62791132926941</t>
+    <t xml:space="preserve">2.54258966445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45726799964905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5767183303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62791156768799</t>
   </si>
   <si>
     <t xml:space="preserve">2.61084699630737</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">2.59378290176392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69616889953613</t>
+    <t xml:space="preserve">2.69616913795471</t>
   </si>
   <si>
     <t xml:space="preserve">2.71323323249817</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">2.30368852615356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25249576568604</t>
+    <t xml:space="preserve">2.25249552726746</t>
   </si>
   <si>
     <t xml:space="preserve">2.23543119430542</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">2.18423795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01359438896179</t>
+    <t xml:space="preserve">2.01359415054321</t>
   </si>
   <si>
     <t xml:space="preserve">2.04772305488586</t>
@@ -788,10 +788,10 @@
     <t xml:space="preserve">1.94533717632294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96240127086639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99652993679047</t>
+    <t xml:space="preserve">1.96240139007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99653005599976</t>
   </si>
   <si>
     <t xml:space="preserve">2.81561923027039</t>
@@ -803,16 +803,16 @@
     <t xml:space="preserve">2.88387680053711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76442646980286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73029756546021</t>
+    <t xml:space="preserve">2.76442670822144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73029780387878</t>
   </si>
   <si>
     <t xml:space="preserve">2.6791045665741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74736189842224</t>
+    <t xml:space="preserve">2.74736213684082</t>
   </si>
   <si>
     <t xml:space="preserve">2.83268356323242</t>
@@ -824,22 +824,22 @@
     <t xml:space="preserve">2.79855513572693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78149056434631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9350700378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96919870376587</t>
+    <t xml:space="preserve">2.78149080276489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93507027626038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96919894218445</t>
   </si>
   <si>
     <t xml:space="preserve">3.02039170265198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00332713127136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03745603561401</t>
+    <t xml:space="preserve">3.00332736968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03745627403259</t>
   </si>
   <si>
     <t xml:space="preserve">2.98626303672791</t>
@@ -854,13 +854,13 @@
     <t xml:space="preserve">3.13984251022339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11424589157104</t>
+    <t xml:space="preserve">3.11424565315247</t>
   </si>
   <si>
     <t xml:space="preserve">3.13131022453308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06305265426636</t>
+    <t xml:space="preserve">3.06305241584778</t>
   </si>
   <si>
     <t xml:space="preserve">3.16543865203857</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">3.19956755638123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15690684318542</t>
+    <t xml:space="preserve">3.15690660476685</t>
   </si>
   <si>
     <t xml:space="preserve">3.2336962223053</t>
@@ -890,13 +890,13 @@
     <t xml:space="preserve">3.34461450576782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32755041122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28488945960999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18250322341919</t>
+    <t xml:space="preserve">3.32755017280579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28488922119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18250298500061</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342150688171</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">3.33710074424744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32836484909058</t>
+    <t xml:space="preserve">3.32836508750916</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342174530029</t>
@@ -926,7 +926,7 @@
     <t xml:space="preserve">3.17111968994141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26721405982971</t>
+    <t xml:space="preserve">3.26721382141113</t>
   </si>
   <si>
     <t xml:space="preserve">3.36330842971802</t>
@@ -938,22 +938,22 @@
     <t xml:space="preserve">3.58170509338379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56423354148865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59044122695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5030825138092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51181817054749</t>
+    <t xml:space="preserve">3.56423330307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59044098854065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50308275222778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51181840896606</t>
   </si>
   <si>
     <t xml:space="preserve">3.54676151275635</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63412046432495</t>
+    <t xml:space="preserve">3.63412022590637</t>
   </si>
   <si>
     <t xml:space="preserve">3.62538480758667</t>
@@ -962,22 +962,22 @@
     <t xml:space="preserve">3.74768662452698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69527125358582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66906356811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60791301727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55549764633179</t>
+    <t xml:space="preserve">3.69527149200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66906380653381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60791277885437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55549788475037</t>
   </si>
   <si>
     <t xml:space="preserve">3.66032791137695</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65159177780151</t>
+    <t xml:space="preserve">3.65159201622009</t>
   </si>
   <si>
     <t xml:space="preserve">3.68653535842896</t>
@@ -995,25 +995,25 @@
     <t xml:space="preserve">3.53802585601807</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3458366394043</t>
+    <t xml:space="preserve">3.34583687782288</t>
   </si>
   <si>
     <t xml:space="preserve">3.38951635360718</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42445969581604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45066738128662</t>
+    <t xml:space="preserve">3.42445945739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45066714286804</t>
   </si>
   <si>
     <t xml:space="preserve">3.44193148612976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4856104850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4069881439209</t>
+    <t xml:space="preserve">3.48561072349548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40698790550232</t>
   </si>
   <si>
     <t xml:space="preserve">3.35457253456116</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">3.45940327644348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52928972244263</t>
+    <t xml:space="preserve">3.52928996086121</t>
   </si>
   <si>
     <t xml:space="preserve">3.46813893318176</t>
@@ -1031,13 +1031,13 @@
     <t xml:space="preserve">3.47687458992004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79136633872986</t>
+    <t xml:space="preserve">3.79136610031128</t>
   </si>
   <si>
     <t xml:space="preserve">3.7214789390564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8787248134613</t>
+    <t xml:space="preserve">3.87872457504272</t>
   </si>
   <si>
     <t xml:space="preserve">4.17574453353882</t>
@@ -1049,34 +1049,34 @@
     <t xml:space="preserve">4.35046148300171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18447971343994</t>
+    <t xml:space="preserve">4.1844801902771</t>
   </si>
   <si>
     <t xml:space="preserve">4.20195150375366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25436687469482</t>
+    <t xml:space="preserve">4.25436639785767</t>
   </si>
   <si>
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493202209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98355484008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94861197471619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93114018440247</t>
+    <t xml:space="preserve">3.90493178367615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98355507850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94861173629761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93113970756531</t>
   </si>
   <si>
     <t xml:space="preserve">4.08838510513306</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07091331481934</t>
+    <t xml:space="preserve">4.07091379165649</t>
   </si>
   <si>
     <t xml:space="preserve">4.1233286857605</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">4.00102663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00976276397705</t>
+    <t xml:space="preserve">4.00976228713989</t>
   </si>
   <si>
     <t xml:space="preserve">3.93987607955933</t>
@@ -1094,16 +1094,16 @@
     <t xml:space="preserve">4.0971212387085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2106876373291</t>
+    <t xml:space="preserve">4.21068716049194</t>
   </si>
   <si>
     <t xml:space="preserve">4.29804611206055</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28931045532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21942329406738</t>
+    <t xml:space="preserve">4.28930997848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21942377090454</t>
   </si>
   <si>
     <t xml:space="preserve">4.19321584701538</t>
@@ -1112,70 +1112,70 @@
     <t xml:space="preserve">4.1495361328125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16700792312622</t>
+    <t xml:space="preserve">4.16700839996338</t>
   </si>
   <si>
     <t xml:space="preserve">4.11459302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06217813491821</t>
+    <t xml:space="preserve">4.06217765808105</t>
   </si>
   <si>
     <t xml:space="preserve">3.78262996673584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80010175704956</t>
+    <t xml:space="preserve">3.80010151863098</t>
   </si>
   <si>
     <t xml:space="preserve">3.82630968093872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83504509925842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84378099441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77389454841614</t>
+    <t xml:space="preserve">3.83504486083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84378123283386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77389430999756</t>
   </si>
   <si>
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734786987305</t>
+    <t xml:space="preserve">3.95734763145447</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86125302314758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76515865325928</t>
+    <t xml:space="preserve">3.861252784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7651584148407</t>
   </si>
   <si>
     <t xml:space="preserve">3.8175733089447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64285612106323</t>
+    <t xml:space="preserve">3.64285635948181</t>
   </si>
   <si>
     <t xml:space="preserve">3.67779970169067</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73895072937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85251665115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71274304389954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92240381240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61664867401123</t>
+    <t xml:space="preserve">3.7389509677887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85251712799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71274328231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92240357398987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61664843559265</t>
   </si>
   <si>
     <t xml:space="preserve">3.39825224876404</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">2.97019457817078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95272302627563</t>
+    <t xml:space="preserve">2.95272278785706</t>
   </si>
   <si>
     <t xml:space="preserve">2.91777920722961</t>
@@ -1202,13 +1202,13 @@
     <t xml:space="preserve">3.37204432487488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38078022003174</t>
+    <t xml:space="preserve">3.38077998161316</t>
   </si>
   <si>
     <t xml:space="preserve">3.41572380065918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31962895393372</t>
+    <t xml:space="preserve">3.31962919235229</t>
   </si>
   <si>
     <t xml:space="preserve">3.27594995498657</t>
@@ -55927,7 +55927,7 @@
     </row>
     <row r="2072">
       <c r="A2072" s="1" t="n">
-        <v>45980.6556134259</v>
+        <v>45980.3333333333</v>
       </c>
       <c r="B2072" t="n">
         <v>41030</v>
@@ -55948,6 +55948,32 @@
         <v>576</v>
       </c>
       <c r="H2072" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2073">
+      <c r="A2073" s="1" t="n">
+        <v>45981.6911921296</v>
+      </c>
+      <c r="B2073" t="n">
+        <v>8081</v>
+      </c>
+      <c r="C2073" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="D2073" t="n">
+        <v>3.24000000953674</v>
+      </c>
+      <c r="E2073" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="F2073" t="n">
+        <v>3.24000000953674</v>
+      </c>
+      <c r="G2073" t="s">
+        <v>570</v>
+      </c>
+      <c r="H2073" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02345752716064</t>
+    <t xml:space="preserve">3.02345728874207</t>
   </si>
   <si>
     <t xml:space="preserve">NDT.MI</t>
@@ -47,16 +47,16 @@
     <t xml:space="preserve">2.96519923210144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88901519775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98013710975647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97266840934753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94577980041504</t>
+    <t xml:space="preserve">2.88901567459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98013758659363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97266817092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94578003883362</t>
   </si>
   <si>
     <t xml:space="preserve">2.9577305316925</t>
@@ -65,70 +65,70 @@
     <t xml:space="preserve">2.96221160888672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9353232383728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91291642189026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9786434173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98611259460449</t>
+    <t xml:space="preserve">2.93532347679138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91291618347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97864317893982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98611235618591</t>
   </si>
   <si>
     <t xml:space="preserve">3.03540825843811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05632138252258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0593090057373</t>
+    <t xml:space="preserve">3.056321144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05930924415588</t>
   </si>
   <si>
     <t xml:space="preserve">3.05034613609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98760652542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95026087760925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01598858833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01001381874084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02495169639587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0174822807312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03092694282532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99955654144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0443708896637</t>
+    <t xml:space="preserve">2.98760628700256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95026135444641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01598834991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01001358032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02495145797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01748251914978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03092670440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99955701828003</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04437136650085</t>
   </si>
   <si>
     <t xml:space="preserve">2.959223985672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00254464149475</t>
+    <t xml:space="preserve">3.00254440307617</t>
   </si>
   <si>
     <t xml:space="preserve">2.92785429954529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90843462944031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89648461341858</t>
+    <t xml:space="preserve">2.90843486785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.896484375</t>
   </si>
   <si>
     <t xml:space="preserve">2.91889142990112</t>
@@ -140,19 +140,19 @@
     <t xml:space="preserve">2.92038536071777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90544724464417</t>
+    <t xml:space="preserve">2.90544700622559</t>
   </si>
   <si>
     <t xml:space="preserve">2.90992832183838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92337274551392</t>
+    <t xml:space="preserve">2.92337322235107</t>
   </si>
   <si>
     <t xml:space="preserve">2.8382260799408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86063313484192</t>
+    <t xml:space="preserve">2.86063289642334</t>
   </si>
   <si>
     <t xml:space="preserve">2.82627558708191</t>
@@ -161,160 +161,160 @@
     <t xml:space="preserve">2.77996778488159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84569525718689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86810207366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88304018974304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79639983177185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87557077407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89797830581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80088067054749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74262261390686</t>
+    <t xml:space="preserve">2.84569478034973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86810183525085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88303971290588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79639959335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87557125091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89797854423523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80088114738464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74262237548828</t>
   </si>
   <si>
     <t xml:space="preserve">2.82179427146912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75009155273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76353573799133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7784743309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78594255447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79341220855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69631457328796</t>
+    <t xml:space="preserve">2.7500913143158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76353597640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77847409248352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78594279289246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79341173171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69631505012512</t>
   </si>
   <si>
     <t xml:space="preserve">2.6515007019043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6216242313385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53946542739868</t>
+    <t xml:space="preserve">2.62162446975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53946566581726</t>
   </si>
   <si>
     <t xml:space="preserve">2.56934142112732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61415576934814</t>
+    <t xml:space="preserve">2.61415553092957</t>
   </si>
   <si>
     <t xml:space="preserve">2.65896964073181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68884587287903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70378375053406</t>
+    <t xml:space="preserve">2.68884563446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70378351211548</t>
   </si>
   <si>
     <t xml:space="preserve">2.77100491523743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81581926345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73365998268127</t>
+    <t xml:space="preserve">2.81581878662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7336597442627</t>
   </si>
   <si>
     <t xml:space="preserve">2.66643857955933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68137669563293</t>
+    <t xml:space="preserve">2.68137645721436</t>
   </si>
   <si>
     <t xml:space="preserve">2.74112892150879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72619104385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8307569026947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89315104484558</t>
+    <t xml:space="preserve">2.72619080543518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83075714111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.893150806427</t>
   </si>
   <si>
     <t xml:space="preserve">2.69871854782104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83870983123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93203711509705</t>
+    <t xml:space="preserve">2.83870959281921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93203687667847</t>
   </si>
   <si>
     <t xml:space="preserve">2.87759613990784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83093214035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81537771224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84648704528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79982328414917</t>
+    <t xml:space="preserve">2.8309326171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81537747383118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84648680686951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79982304573059</t>
   </si>
   <si>
     <t xml:space="preserve">2.73760485649109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76093673706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80760025978088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00980973243713</t>
+    <t xml:space="preserve">2.76093697547913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80760073661804</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00980997085571</t>
   </si>
   <si>
     <t xml:space="preserve">2.9553689956665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90870547294617</t>
+    <t xml:space="preserve">2.90870499610901</t>
   </si>
   <si>
     <t xml:space="preserve">2.88537335395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82315492630005</t>
+    <t xml:space="preserve">2.82315516471863</t>
   </si>
   <si>
     <t xml:space="preserve">2.86204147338867</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00203251838684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9164822101593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85426449775696</t>
+    <t xml:space="preserve">3.00203227996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91648268699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85426425933838</t>
   </si>
   <si>
     <t xml:space="preserve">2.7298276424408</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">2.7220504283905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75315928459167</t>
+    <t xml:space="preserve">2.75315952301025</t>
   </si>
   <si>
     <t xml:space="preserve">2.70649576187134</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">2.93981432914734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99425506591797</t>
+    <t xml:space="preserve">2.99425554275513</t>
   </si>
   <si>
     <t xml:space="preserve">2.97870063781738</t>
@@ -347,100 +347,100 @@
     <t xml:space="preserve">2.94759178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98647809028625</t>
+    <t xml:space="preserve">2.98647785186768</t>
   </si>
   <si>
     <t xml:space="preserve">2.63650035858154</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55094981193542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51984095573425</t>
+    <t xml:space="preserve">2.550950050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51984071731567</t>
   </si>
   <si>
     <t xml:space="preserve">2.41095876693726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34096360206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34874057769775</t>
+    <t xml:space="preserve">2.34096312522888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34874081611633</t>
   </si>
   <si>
     <t xml:space="preserve">2.36429500579834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25541305541992</t>
+    <t xml:space="preserve">2.2554132938385</t>
   </si>
   <si>
     <t xml:space="preserve">2.24763607978821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32540893554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23208141326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18541741371155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27874493598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26319050788879</t>
+    <t xml:space="preserve">2.3254086971283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23208117485046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18541765213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27874517440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26319026947021</t>
   </si>
   <si>
     <t xml:space="preserve">2.2165265083313</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06875848770142</t>
+    <t xml:space="preserve">2.06875824928284</t>
   </si>
   <si>
     <t xml:space="preserve">2.1465311050415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10764455795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15430855751038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17764043807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22430372238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35651803016663</t>
+    <t xml:space="preserve">2.10764479637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1543083190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17764019966125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22430396080017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35651779174805</t>
   </si>
   <si>
     <t xml:space="preserve">2.4887318611145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52761840820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43429088592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44206786155701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5587272644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44984555244446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37207221984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33318591117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29429984092712</t>
+    <t xml:space="preserve">2.52761793136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43429112434387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44206809997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55872750282288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44984531402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37207245826721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33318567276001</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29429960250854</t>
   </si>
   <si>
     <t xml:space="preserve">2.3798496723175</t>
@@ -449,49 +449,49 @@
     <t xml:space="preserve">2.71427297592163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58205914497375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62872290611267</t>
+    <t xml:space="preserve">2.58205938339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62872314453125</t>
   </si>
   <si>
     <t xml:space="preserve">2.65983200073242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57428193092346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67538690567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64427709579468</t>
+    <t xml:space="preserve">2.57428216934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67538666725159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64427781105042</t>
   </si>
   <si>
     <t xml:space="preserve">2.69094133377075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76871371269226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90092802047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9631462097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92425990104675</t>
+    <t xml:space="preserve">2.76871418952942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90092778205872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96314597129822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92425966262817</t>
   </si>
   <si>
     <t xml:space="preserve">2.97092342376709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01758718490601</t>
+    <t xml:space="preserve">3.01758766174316</t>
   </si>
   <si>
     <t xml:space="preserve">3.04869651794434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03314208984375</t>
+    <t xml:space="preserve">3.03314185142517</t>
   </si>
   <si>
     <t xml:space="preserve">3.0642511844635</t>
@@ -503,22 +503,22 @@
     <t xml:space="preserve">3.0604989528656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02811288833618</t>
+    <t xml:space="preserve">3.0281126499176</t>
   </si>
   <si>
     <t xml:space="preserve">3.01191973686218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1090784072876</t>
+    <t xml:space="preserve">3.10907816886902</t>
   </si>
   <si>
     <t xml:space="preserve">3.0928852558136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12527132034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07669186592102</t>
+    <t xml:space="preserve">3.12527108192444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0766921043396</t>
   </si>
   <si>
     <t xml:space="preserve">2.99572658538818</t>
@@ -530,22 +530,22 @@
     <t xml:space="preserve">3.41674733161926</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35197520256042</t>
+    <t xml:space="preserve">3.35197496414185</t>
   </si>
   <si>
     <t xml:space="preserve">3.33578181266785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36816811561584</t>
+    <t xml:space="preserve">3.36816787719727</t>
   </si>
   <si>
     <t xml:space="preserve">3.23862338066101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31958866119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27100944519043</t>
+    <t xml:space="preserve">3.31958889961243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27100968360901</t>
   </si>
   <si>
     <t xml:space="preserve">3.28720259666443</t>
@@ -557,28 +557,28 @@
     <t xml:space="preserve">3.17385101318359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20623707771301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1414647102356</t>
+    <t xml:space="preserve">3.20623731613159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14146494865417</t>
   </si>
   <si>
     <t xml:space="preserve">3.40055441856384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49771332740784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38436102867126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25481629371643</t>
+    <t xml:space="preserve">3.49771356582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38436150550842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25481653213501</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004416465759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96334052085876</t>
+    <t xml:space="preserve">2.96334028244019</t>
   </si>
   <si>
     <t xml:space="preserve">2.97953343391418</t>
@@ -587,31 +587,31 @@
     <t xml:space="preserve">2.80140924453735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88237452507019</t>
+    <t xml:space="preserve">2.88237476348877</t>
   </si>
   <si>
     <t xml:space="preserve">2.86618161201477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84998869895935</t>
+    <t xml:space="preserve">2.84998846054077</t>
   </si>
   <si>
     <t xml:space="preserve">2.78521609306335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75282979011536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72044324874878</t>
+    <t xml:space="preserve">2.75283026695251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72044348716736</t>
   </si>
   <si>
     <t xml:space="preserve">2.83379554748535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76902318000793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73663663864136</t>
+    <t xml:space="preserve">2.76902294158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73663687705994</t>
   </si>
   <si>
     <t xml:space="preserve">2.81760239601135</t>
@@ -626,28 +626,28 @@
     <t xml:space="preserve">2.63947820663452</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67186403274536</t>
+    <t xml:space="preserve">2.67186427116394</t>
   </si>
   <si>
     <t xml:space="preserve">2.62328481674194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68805718421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70425033569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60709190368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5908989906311</t>
+    <t xml:space="preserve">2.68805766105652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70425057411194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60709166526794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59089875221252</t>
   </si>
   <si>
     <t xml:space="preserve">2.42896723747253</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54231953620911</t>
+    <t xml:space="preserve">2.54231929779053</t>
   </si>
   <si>
     <t xml:space="preserve">2.46135354042053</t>
@@ -659,22 +659,22 @@
     <t xml:space="preserve">2.2994225025177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35488152503967</t>
+    <t xml:space="preserve">2.35488176345825</t>
   </si>
   <si>
     <t xml:space="preserve">2.40607476234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28662443161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13304495811462</t>
+    <t xml:space="preserve">2.28662419319153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13304471969604</t>
   </si>
   <si>
     <t xml:space="preserve">2.08185195922852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0647873878479</t>
+    <t xml:space="preserve">2.06478762626648</t>
   </si>
   <si>
     <t xml:space="preserve">2.03065896034241</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">2.09891629219055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26956009864807</t>
+    <t xml:space="preserve">2.26955986022949</t>
   </si>
   <si>
     <t xml:space="preserve">2.2183666229248</t>
@@ -701,16 +701,16 @@
     <t xml:space="preserve">2.54258966445923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45726799964905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5767183303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62791156768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61084723472595</t>
+    <t xml:space="preserve">2.45726823806763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57671856880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62791132926941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61084699630737</t>
   </si>
   <si>
     <t xml:space="preserve">2.64497566223145</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">2.59378266334534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69616889953613</t>
+    <t xml:space="preserve">2.69616913795471</t>
   </si>
   <si>
     <t xml:space="preserve">2.71323323249817</t>
@@ -728,19 +728,19 @@
     <t xml:space="preserve">2.44020342826843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42313885688782</t>
+    <t xml:space="preserve">2.4231390953064</t>
   </si>
   <si>
     <t xml:space="preserve">2.47433233261108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15010952949524</t>
+    <t xml:space="preserve">2.15010929107666</t>
   </si>
   <si>
     <t xml:space="preserve">2.33781743049622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30368852615356</t>
+    <t xml:space="preserve">2.30368876457214</t>
   </si>
   <si>
     <t xml:space="preserve">2.25249552726746</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">2.38901042938232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20130252838135</t>
+    <t xml:space="preserve">2.20130228996277</t>
   </si>
   <si>
     <t xml:space="preserve">2.18423795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01359438896179</t>
+    <t xml:space="preserve">2.01359415054321</t>
   </si>
   <si>
     <t xml:space="preserve">2.04772329330444</t>
@@ -782,10 +782,10 @@
     <t xml:space="preserve">1.97946572303772</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86001539230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94533681869507</t>
+    <t xml:space="preserve">1.86001527309418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94533705711365</t>
   </si>
   <si>
     <t xml:space="preserve">1.96240139007568</t>
@@ -794,7 +794,7 @@
     <t xml:space="preserve">1.99653005599976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81561923027039</t>
+    <t xml:space="preserve">2.81561970710754</t>
   </si>
   <si>
     <t xml:space="preserve">2.9009416103363</t>
@@ -803,19 +803,19 @@
     <t xml:space="preserve">2.88387703895569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76442646980286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73029780387878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67910480499268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74736213684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83268356323242</t>
+    <t xml:space="preserve">2.76442623138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73029756546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6791045665741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74736189842224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.832683801651</t>
   </si>
   <si>
     <t xml:space="preserve">2.86681246757507</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">2.78149080276489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9350700378418</t>
+    <t xml:space="preserve">2.93507027626038</t>
   </si>
   <si>
     <t xml:space="preserve">2.96919870376587</t>
@@ -839,10 +839,10 @@
     <t xml:space="preserve">3.00332736968994</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03745627403259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98626303672791</t>
+    <t xml:space="preserve">3.03745603561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98626327514648</t>
   </si>
   <si>
     <t xml:space="preserve">3.05452060699463</t>
@@ -854,7 +854,7 @@
     <t xml:space="preserve">3.13984251022339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11424565315247</t>
+    <t xml:space="preserve">3.11424589157104</t>
   </si>
   <si>
     <t xml:space="preserve">3.1313099861145</t>
@@ -866,37 +866,37 @@
     <t xml:space="preserve">3.16543889045715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1995677947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15690684318542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23369598388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27635717391968</t>
+    <t xml:space="preserve">3.19956755638123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15690660476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2336962223053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2763569355011</t>
   </si>
   <si>
     <t xml:space="preserve">3.24222826957703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26782488822937</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31048631668091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34461450576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32755064964294</t>
+    <t xml:space="preserve">3.26782464981079</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31048607826233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34461498260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32755041122437</t>
   </si>
   <si>
     <t xml:space="preserve">3.28488922119141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18250322341919</t>
+    <t xml:space="preserve">3.18250298500061</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342150688171</t>
@@ -905,16 +905,16 @@
     <t xml:space="preserve">3.33710074424744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32836508750916</t>
+    <t xml:space="preserve">3.32836484909058</t>
   </si>
   <si>
     <t xml:space="preserve">3.24974226951599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20606303215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15364742279053</t>
+    <t xml:space="preserve">3.20606279373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15364766120911</t>
   </si>
   <si>
     <t xml:space="preserve">3.21479892730713</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">3.17111945152283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26721405982971</t>
+    <t xml:space="preserve">3.26721382141113</t>
   </si>
   <si>
     <t xml:space="preserve">3.36330842971802</t>
@@ -932,10 +932,10 @@
     <t xml:space="preserve">3.49434661865234</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58170485496521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56423354148865</t>
+    <t xml:space="preserve">3.58170509338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56423330307007</t>
   </si>
   <si>
     <t xml:space="preserve">3.59044122695923</t>
@@ -944,13 +944,13 @@
     <t xml:space="preserve">3.5030825138092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51181817054749</t>
+    <t xml:space="preserve">3.51181840896606</t>
   </si>
   <si>
     <t xml:space="preserve">3.54676175117493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63412022590637</t>
+    <t xml:space="preserve">3.63411998748779</t>
   </si>
   <si>
     <t xml:space="preserve">3.62538456916809</t>
@@ -962,16 +962,16 @@
     <t xml:space="preserve">3.69527125358582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66906356811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60791277885437</t>
+    <t xml:space="preserve">3.66906380653381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60791301727295</t>
   </si>
   <si>
     <t xml:space="preserve">3.55549788475037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66032791137695</t>
+    <t xml:space="preserve">3.66032814979553</t>
   </si>
   <si>
     <t xml:space="preserve">3.65159201622009</t>
@@ -980,13 +980,13 @@
     <t xml:space="preserve">3.68653535842896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70400714874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75642275810242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57296943664551</t>
+    <t xml:space="preserve">3.7040069103241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75642251968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57296967506409</t>
   </si>
   <si>
     <t xml:space="preserve">3.53802609443665</t>
@@ -998,25 +998,25 @@
     <t xml:space="preserve">3.3895161151886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42445969581604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45066714286804</t>
+    <t xml:space="preserve">3.42445993423462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45066738128662</t>
   </si>
   <si>
     <t xml:space="preserve">3.44193148612976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4856104850769</t>
+    <t xml:space="preserve">3.48561072349548</t>
   </si>
   <si>
     <t xml:space="preserve">3.4069881439209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35457253456116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4594030380249</t>
+    <t xml:space="preserve">3.35457229614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45940327644348</t>
   </si>
   <si>
     <t xml:space="preserve">3.52928996086121</t>
@@ -1031,13 +1031,13 @@
     <t xml:space="preserve">3.79136610031128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72147917747498</t>
+    <t xml:space="preserve">3.72147941589355</t>
   </si>
   <si>
     <t xml:space="preserve">3.87872457504272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17574453353882</t>
+    <t xml:space="preserve">4.17574405670166</t>
   </si>
   <si>
     <t xml:space="preserve">4.31551790237427</t>
@@ -1046,13 +1046,13 @@
     <t xml:space="preserve">4.35046148300171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1844801902771</t>
+    <t xml:space="preserve">4.18447971343994</t>
   </si>
   <si>
     <t xml:space="preserve">4.20195150375366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25436639785767</t>
+    <t xml:space="preserve">4.25436687469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.14080047607422</t>
@@ -1064,7 +1064,7 @@
     <t xml:space="preserve">3.98355507850647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94861149787903</t>
+    <t xml:space="preserve">3.94861173629761</t>
   </si>
   <si>
     <t xml:space="preserve">3.93113970756531</t>
@@ -1073,16 +1073,16 @@
     <t xml:space="preserve">4.08838558197021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07091331481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12332916259766</t>
+    <t xml:space="preserve">4.07091379165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1233286857605</t>
   </si>
   <si>
     <t xml:space="preserve">4.00102663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00976276397705</t>
+    <t xml:space="preserve">4.00976324081421</t>
   </si>
   <si>
     <t xml:space="preserve">3.93987584114075</t>
@@ -1100,7 +1100,7 @@
     <t xml:space="preserve">4.28930997848511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21942377090454</t>
+    <t xml:space="preserve">4.21942329406738</t>
   </si>
   <si>
     <t xml:space="preserve">4.19321632385254</t>
@@ -1124,7 +1124,7 @@
     <t xml:space="preserve">3.80010175704956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82630944252014</t>
+    <t xml:space="preserve">3.8263099193573</t>
   </si>
   <si>
     <t xml:space="preserve">3.83504557609558</t>
@@ -1133,13 +1133,13 @@
     <t xml:space="preserve">3.84378147125244</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77389430999756</t>
+    <t xml:space="preserve">3.77389454841614</t>
   </si>
   <si>
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734739303589</t>
+    <t xml:space="preserve">3.95734786987305</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
@@ -1148,16 +1148,16 @@
     <t xml:space="preserve">3.86125302314758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76515817642212</t>
+    <t xml:space="preserve">3.76515793800354</t>
   </si>
   <si>
     <t xml:space="preserve">3.81757354736328</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64285635948181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67779946327209</t>
+    <t xml:space="preserve">3.64285612106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67779970169067</t>
   </si>
   <si>
     <t xml:space="preserve">3.7389509677887</t>
@@ -1166,7 +1166,7 @@
     <t xml:space="preserve">3.85251712799072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71274304389954</t>
+    <t xml:space="preserve">3.71274328231812</t>
   </si>
   <si>
     <t xml:space="preserve">3.92240381240845</t>
@@ -1175,13 +1175,13 @@
     <t xml:space="preserve">3.61664843559265</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39825224876404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23227071762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05755305290222</t>
+    <t xml:space="preserve">3.39825201034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23227047920227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0575532913208</t>
   </si>
   <si>
     <t xml:space="preserve">2.97019481658936</t>
@@ -1193,10 +1193,10 @@
     <t xml:space="preserve">2.91777944564819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90904331207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37204432487488</t>
+    <t xml:space="preserve">2.90904355049133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3720440864563</t>
   </si>
   <si>
     <t xml:space="preserve">3.38078022003174</t>
@@ -1208,7 +1208,7 @@
     <t xml:space="preserve">3.31962895393372</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27595019340515</t>
+    <t xml:space="preserve">3.27594995498657</t>
   </si>
   <si>
     <t xml:space="preserve">3.28468561172485</t>
@@ -55976,7 +55976,7 @@
     </row>
     <row r="2074">
       <c r="A2074" s="1" t="n">
-        <v>45982.6680902778</v>
+        <v>45982.3333333333</v>
       </c>
       <c r="B2074" t="n">
         <v>9520</v>
@@ -55997,6 +55997,32 @@
         <v>568</v>
       </c>
       <c r="H2074" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2075">
+      <c r="A2075" s="1" t="n">
+        <v>45985.6771064815</v>
+      </c>
+      <c r="B2075" t="n">
+        <v>11208</v>
+      </c>
+      <c r="C2075" t="n">
+        <v>3.27999997138977</v>
+      </c>
+      <c r="D2075" t="n">
+        <v>3.24000000953674</v>
+      </c>
+      <c r="E2075" t="n">
+        <v>3.24000000953674</v>
+      </c>
+      <c r="F2075" t="n">
+        <v>3.24000000953674</v>
+      </c>
+      <c r="G2075" t="s">
+        <v>569</v>
+      </c>
+      <c r="H2075" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -38,40 +38,40 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02345728874207</t>
+    <t xml:space="preserve">3.02345752716064</t>
   </si>
   <si>
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519923210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88901567459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98013758659363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97266817092896</t>
+    <t xml:space="preserve">2.96519947052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88901543617249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98013734817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97266840934753</t>
   </si>
   <si>
     <t xml:space="preserve">2.94578003883362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9577305316925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96221160888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93532347679138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91291618347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97864317893982</t>
+    <t xml:space="preserve">2.95773029327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9622118473053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9353232383728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91291642189026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97864365577698</t>
   </si>
   <si>
     <t xml:space="preserve">2.98611235618591</t>
@@ -80,13 +80,13 @@
     <t xml:space="preserve">3.03540825843811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.056321144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05930924415588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05034613609314</t>
+    <t xml:space="preserve">3.05632138252258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0593090057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05034589767456</t>
   </si>
   <si>
     <t xml:space="preserve">2.98760628700256</t>
@@ -95,7 +95,7 @@
     <t xml:space="preserve">2.95026135444641</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01598834991455</t>
+    <t xml:space="preserve">3.01598858833313</t>
   </si>
   <si>
     <t xml:space="preserve">3.01001358032227</t>
@@ -113,13 +113,13 @@
     <t xml:space="preserve">2.99955701828003</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04437136650085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.959223985672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00254440307617</t>
+    <t xml:space="preserve">3.0443708896637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95922422409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00254464149475</t>
   </si>
   <si>
     <t xml:space="preserve">2.92785429954529</t>
@@ -131,64 +131,64 @@
     <t xml:space="preserve">2.896484375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91889142990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91590404510498</t>
+    <t xml:space="preserve">2.91889119148254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9159038066864</t>
   </si>
   <si>
     <t xml:space="preserve">2.92038536071777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90544700622559</t>
+    <t xml:space="preserve">2.90544724464417</t>
   </si>
   <si>
     <t xml:space="preserve">2.90992832183838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92337322235107</t>
+    <t xml:space="preserve">2.9233729839325</t>
   </si>
   <si>
     <t xml:space="preserve">2.8382260799408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86063289642334</t>
+    <t xml:space="preserve">2.86063313484192</t>
   </si>
   <si>
     <t xml:space="preserve">2.82627558708191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77996778488159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84569478034973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86810183525085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88303971290588</t>
+    <t xml:space="preserve">2.77996706962585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84569525718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86810231208801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88303995132446</t>
   </si>
   <si>
     <t xml:space="preserve">2.79639959335327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87557125091553</t>
+    <t xml:space="preserve">2.87557101249695</t>
   </si>
   <si>
     <t xml:space="preserve">2.89797854423523</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80088114738464</t>
+    <t xml:space="preserve">2.80088090896606</t>
   </si>
   <si>
     <t xml:space="preserve">2.74262237548828</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82179427146912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7500913143158</t>
+    <t xml:space="preserve">2.8217945098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75009179115295</t>
   </si>
   <si>
     <t xml:space="preserve">2.76353597640991</t>
@@ -197,16 +197,16 @@
     <t xml:space="preserve">2.77847409248352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78594279289246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79341173171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69631505012512</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6515007019043</t>
+    <t xml:space="preserve">2.78594303131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79341197013855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69631433486938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65150094032288</t>
   </si>
   <si>
     <t xml:space="preserve">2.62162446975708</t>
@@ -224,25 +224,25 @@
     <t xml:space="preserve">2.65896964073181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68884563446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70378351211548</t>
+    <t xml:space="preserve">2.68884539604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70378375053406</t>
   </si>
   <si>
     <t xml:space="preserve">2.77100491523743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81581878662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7336597442627</t>
+    <t xml:space="preserve">2.81581902503967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73365998268127</t>
   </si>
   <si>
     <t xml:space="preserve">2.66643857955933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68137645721436</t>
+    <t xml:space="preserve">2.68137669563293</t>
   </si>
   <si>
     <t xml:space="preserve">2.74112892150879</t>
@@ -251,7 +251,7 @@
     <t xml:space="preserve">2.72619080543518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83075714111328</t>
+    <t xml:space="preserve">2.8307569026947</t>
   </si>
   <si>
     <t xml:space="preserve">2.893150806427</t>
@@ -269,13 +269,13 @@
     <t xml:space="preserve">2.87759613990784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8309326171875</t>
+    <t xml:space="preserve">2.83093237876892</t>
   </si>
   <si>
     <t xml:space="preserve">2.81537747383118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84648680686951</t>
+    <t xml:space="preserve">2.84648704528809</t>
   </si>
   <si>
     <t xml:space="preserve">2.79982304573059</t>
@@ -287,7 +287,7 @@
     <t xml:space="preserve">2.76093697547913</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80760073661804</t>
+    <t xml:space="preserve">2.8076000213623</t>
   </si>
   <si>
     <t xml:space="preserve">3.00980997085571</t>
@@ -296,25 +296,25 @@
     <t xml:space="preserve">2.9553689956665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90870499610901</t>
+    <t xml:space="preserve">2.90870547294617</t>
   </si>
   <si>
     <t xml:space="preserve">2.88537335395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82315516471863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86204147338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00203227996826</t>
+    <t xml:space="preserve">2.82315540313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86204171180725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00203251838684</t>
   </si>
   <si>
     <t xml:space="preserve">2.91648268699646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85426425933838</t>
+    <t xml:space="preserve">2.85426449775696</t>
   </si>
   <si>
     <t xml:space="preserve">2.7298276424408</t>
@@ -323,7 +323,7 @@
     <t xml:space="preserve">2.68316411972046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7220504283905</t>
+    <t xml:space="preserve">2.72205018997192</t>
   </si>
   <si>
     <t xml:space="preserve">2.75315952301025</t>
@@ -332,46 +332,46 @@
     <t xml:space="preserve">2.70649576187134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93981432914734</t>
+    <t xml:space="preserve">2.93981409072876</t>
   </si>
   <si>
     <t xml:space="preserve">2.99425554275513</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97870063781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86981892585754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94759178161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98647785186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63650035858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.550950050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51984071731567</t>
+    <t xml:space="preserve">2.97870087623596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86981868743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94759154319763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98647809028625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63650012016296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55094981193542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51984119415283</t>
   </si>
   <si>
     <t xml:space="preserve">2.41095876693726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34096312522888</t>
+    <t xml:space="preserve">2.34096336364746</t>
   </si>
   <si>
     <t xml:space="preserve">2.34874081611633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36429500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2554132938385</t>
+    <t xml:space="preserve">2.36429524421692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25541353225708</t>
   </si>
   <si>
     <t xml:space="preserve">2.24763607978821</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">2.3254086971283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23208117485046</t>
+    <t xml:space="preserve">2.23208093643188</t>
   </si>
   <si>
     <t xml:space="preserve">2.18541765213013</t>
@@ -392,7 +392,7 @@
     <t xml:space="preserve">2.26319026947021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2165265083313</t>
+    <t xml:space="preserve">2.21652674674988</t>
   </si>
   <si>
     <t xml:space="preserve">2.06875824928284</t>
@@ -401,16 +401,16 @@
     <t xml:space="preserve">2.1465311050415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10764479637146</t>
+    <t xml:space="preserve">2.10764455795288</t>
   </si>
   <si>
     <t xml:space="preserve">2.1543083190918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17764019966125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22430396080017</t>
+    <t xml:space="preserve">2.17763996124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22430419921875</t>
   </si>
   <si>
     <t xml:space="preserve">2.35651779174805</t>
@@ -419,46 +419,46 @@
     <t xml:space="preserve">2.4887318611145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52761793136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43429112434387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44206809997559</t>
+    <t xml:space="preserve">2.52761816978455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43429088592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44206786155701</t>
   </si>
   <si>
     <t xml:space="preserve">2.55872750282288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44984531402588</t>
+    <t xml:space="preserve">2.44984555244446</t>
   </si>
   <si>
     <t xml:space="preserve">2.37207245826721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33318567276001</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29429960250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3798496723175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71427297592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58205938339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62872314453125</t>
+    <t xml:space="preserve">2.33318591117859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29429936408997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37984991073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71427321434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58205914497375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62872290611267</t>
   </si>
   <si>
     <t xml:space="preserve">2.65983200073242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57428216934204</t>
+    <t xml:space="preserve">2.57428169250488</t>
   </si>
   <si>
     <t xml:space="preserve">2.67538666725159</t>
@@ -467,7 +467,7 @@
     <t xml:space="preserve">2.64427781105042</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69094133377075</t>
+    <t xml:space="preserve">2.69094109535217</t>
   </si>
   <si>
     <t xml:space="preserve">2.76871418952942</t>
@@ -476,34 +476,34 @@
     <t xml:space="preserve">2.90092778205872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96314597129822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92425966262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97092342376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01758766174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04869651794434</t>
+    <t xml:space="preserve">2.9631462097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92426013946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97092318534851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01758742332458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04869627952576</t>
   </si>
   <si>
     <t xml:space="preserve">3.03314185142517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0642511844635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07980585098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0604989528656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0281126499176</t>
+    <t xml:space="preserve">3.06425094604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07980537414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06049871444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02811288833618</t>
   </si>
   <si>
     <t xml:space="preserve">3.01191973686218</t>
@@ -515,34 +515,34 @@
     <t xml:space="preserve">3.0928852558136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12527108192444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0766921043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99572658538818</t>
+    <t xml:space="preserve">3.1252715587616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07669186592102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99572682380676</t>
   </si>
   <si>
     <t xml:space="preserve">3.30339574813843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41674733161926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35197496414185</t>
+    <t xml:space="preserve">3.41674757003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35197520256042</t>
   </si>
   <si>
     <t xml:space="preserve">3.33578181266785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36816787719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23862338066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31958889961243</t>
+    <t xml:space="preserve">3.36816835403442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23862314224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31958866119385</t>
   </si>
   <si>
     <t xml:space="preserve">3.27100968360901</t>
@@ -554,37 +554,37 @@
     <t xml:space="preserve">3.22243022918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17385101318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20623731613159</t>
+    <t xml:space="preserve">3.17385077476501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20623707771301</t>
   </si>
   <si>
     <t xml:space="preserve">3.14146494865417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40055441856384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49771356582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38436150550842</t>
+    <t xml:space="preserve">3.40055418014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49771332740784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38436126708984</t>
   </si>
   <si>
     <t xml:space="preserve">3.25481653213501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19004416465759</t>
+    <t xml:space="preserve">3.19004392623901</t>
   </si>
   <si>
     <t xml:space="preserve">2.96334028244019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97953343391418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80140924453735</t>
+    <t xml:space="preserve">2.97953367233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80140900611877</t>
   </si>
   <si>
     <t xml:space="preserve">2.88237476348877</t>
@@ -599,16 +599,16 @@
     <t xml:space="preserve">2.78521609306335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75283026695251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72044348716736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83379554748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76902294158936</t>
+    <t xml:space="preserve">2.75283002853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72044372558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83379530906677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76902318000793</t>
   </si>
   <si>
     <t xml:space="preserve">2.73663687705994</t>
@@ -623,22 +623,22 @@
     <t xml:space="preserve">2.91476082801819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63947820663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67186427116394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62328481674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68805766105652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70425057411194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60709166526794</t>
+    <t xml:space="preserve">2.63947772979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67186403274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62328505516052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68805718421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70425033569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60709190368652</t>
   </si>
   <si>
     <t xml:space="preserve">2.59089875221252</t>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">2.42896723747253</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54231929779053</t>
+    <t xml:space="preserve">2.54231953620911</t>
   </si>
   <si>
     <t xml:space="preserve">2.46135354042053</t>
@@ -659,22 +659,22 @@
     <t xml:space="preserve">2.2994225025177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35488176345825</t>
+    <t xml:space="preserve">2.35488152503967</t>
   </si>
   <si>
     <t xml:space="preserve">2.40607476234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28662419319153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13304471969604</t>
+    <t xml:space="preserve">2.28662443161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13304495811462</t>
   </si>
   <si>
     <t xml:space="preserve">2.08185195922852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06478762626648</t>
+    <t xml:space="preserve">2.0647873878479</t>
   </si>
   <si>
     <t xml:space="preserve">2.03065896034241</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">2.09891629219055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26955986022949</t>
+    <t xml:space="preserve">2.26956009864807</t>
   </si>
   <si>
     <t xml:space="preserve">2.2183666229248</t>
@@ -698,13 +698,13 @@
     <t xml:space="preserve">2.55965399742126</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54258966445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45726823806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57671856880188</t>
+    <t xml:space="preserve">2.54258990287781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45726799964905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5767183303833</t>
   </si>
   <si>
     <t xml:space="preserve">2.62791132926941</t>
@@ -716,10 +716,10 @@
     <t xml:space="preserve">2.64497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59378266334534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69616913795471</t>
+    <t xml:space="preserve">2.59378290176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69616889953613</t>
   </si>
   <si>
     <t xml:space="preserve">2.71323323249817</t>
@@ -731,10 +731,10 @@
     <t xml:space="preserve">2.4231390953064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47433233261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15010929107666</t>
+    <t xml:space="preserve">2.47433257102966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15010952949524</t>
   </si>
   <si>
     <t xml:space="preserve">2.33781743049622</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">2.30368876457214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25249552726746</t>
+    <t xml:space="preserve">2.25249576568604</t>
   </si>
   <si>
     <t xml:space="preserve">2.23543095588684</t>
@@ -755,13 +755,13 @@
     <t xml:space="preserve">2.38901042938232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20130228996277</t>
+    <t xml:space="preserve">2.20130252838135</t>
   </si>
   <si>
     <t xml:space="preserve">2.18423795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01359415054321</t>
+    <t xml:space="preserve">2.01359438896179</t>
   </si>
   <si>
     <t xml:space="preserve">2.04772329330444</t>
@@ -773,37 +773,37 @@
     <t xml:space="preserve">1.91120839118958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8770797252655</t>
+    <t xml:space="preserve">1.87707984447479</t>
   </si>
   <si>
     <t xml:space="preserve">1.84295094013214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97946572303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86001527309418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94533705711365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96240139007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99653005599976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81561970710754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9009416103363</t>
+    <t xml:space="preserve">1.97946584224701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86001539230347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94533693790436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96240127086639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99653017520905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81561923027039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90094137191772</t>
   </si>
   <si>
     <t xml:space="preserve">2.88387703895569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76442623138428</t>
+    <t xml:space="preserve">2.76442646980286</t>
   </si>
   <si>
     <t xml:space="preserve">2.73029756546021</t>
@@ -815,34 +815,34 @@
     <t xml:space="preserve">2.74736189842224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.832683801651</t>
+    <t xml:space="preserve">2.83268356323242</t>
   </si>
   <si>
     <t xml:space="preserve">2.86681246757507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79855513572693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78149080276489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93507027626038</t>
+    <t xml:space="preserve">2.79855489730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78149056434631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9350700378418</t>
   </si>
   <si>
     <t xml:space="preserve">2.96919870376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02039194107056</t>
+    <t xml:space="preserve">3.02039170265198</t>
   </si>
   <si>
     <t xml:space="preserve">3.00332736968994</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03745603561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98626327514648</t>
+    <t xml:space="preserve">3.03745627403259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98626303672791</t>
   </si>
   <si>
     <t xml:space="preserve">3.05452060699463</t>
@@ -857,46 +857,46 @@
     <t xml:space="preserve">3.11424589157104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1313099861145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06305241584778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16543889045715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19956755638123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15690660476685</t>
+    <t xml:space="preserve">3.13131022453308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06305265426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16543912887573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1995677947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15690684318542</t>
   </si>
   <si>
     <t xml:space="preserve">3.2336962223053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2763569355011</t>
+    <t xml:space="preserve">3.27635717391968</t>
   </si>
   <si>
     <t xml:space="preserve">3.24222826957703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26782464981079</t>
+    <t xml:space="preserve">3.26782488822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.31048607826233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34461498260498</t>
+    <t xml:space="preserve">3.34461450576782</t>
   </si>
   <si>
     <t xml:space="preserve">3.32755041122437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28488922119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18250298500061</t>
+    <t xml:space="preserve">3.28488945960999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18250346183777</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342150688171</t>
@@ -908,13 +908,13 @@
     <t xml:space="preserve">3.32836484909058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24974226951599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20606279373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15364766120911</t>
+    <t xml:space="preserve">3.24974250793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20606303215027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15364742279053</t>
   </si>
   <si>
     <t xml:space="preserve">3.21479892730713</t>
@@ -923,19 +923,19 @@
     <t xml:space="preserve">3.17111945152283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26721382141113</t>
+    <t xml:space="preserve">3.26721405982971</t>
   </si>
   <si>
     <t xml:space="preserve">3.36330842971802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49434661865234</t>
+    <t xml:space="preserve">3.49434638023376</t>
   </si>
   <si>
     <t xml:space="preserve">3.58170509338379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56423330307007</t>
+    <t xml:space="preserve">3.56423354148865</t>
   </si>
   <si>
     <t xml:space="preserve">3.59044122695923</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">3.5030825138092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51181840896606</t>
+    <t xml:space="preserve">3.51181817054749</t>
   </si>
   <si>
     <t xml:space="preserve">3.54676175117493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63411998748779</t>
+    <t xml:space="preserve">3.63412022590637</t>
   </si>
   <si>
     <t xml:space="preserve">3.62538456916809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7476863861084</t>
+    <t xml:space="preserve">3.74768662452698</t>
   </si>
   <si>
     <t xml:space="preserve">3.69527125358582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66906380653381</t>
+    <t xml:space="preserve">3.66906332969666</t>
   </si>
   <si>
     <t xml:space="preserve">3.60791301727295</t>
@@ -971,22 +971,22 @@
     <t xml:space="preserve">3.55549788475037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66032814979553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65159201622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68653535842896</t>
+    <t xml:space="preserve">3.66032767295837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65159177780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68653512001038</t>
   </si>
   <si>
     <t xml:space="preserve">3.7040069103241</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75642251968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57296967506409</t>
+    <t xml:space="preserve">3.75642275810242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57296943664551</t>
   </si>
   <si>
     <t xml:space="preserve">3.53802609443665</t>
@@ -995,28 +995,28 @@
     <t xml:space="preserve">3.3458366394043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3895161151886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42445993423462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45066738128662</t>
+    <t xml:space="preserve">3.38951635360718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42445969581604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45066714286804</t>
   </si>
   <si>
     <t xml:space="preserve">3.44193148612976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48561072349548</t>
+    <t xml:space="preserve">3.4856104850769</t>
   </si>
   <si>
     <t xml:space="preserve">3.4069881439209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35457229614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45940327644348</t>
+    <t xml:space="preserve">3.35457253456116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4594030380249</t>
   </si>
   <si>
     <t xml:space="preserve">3.52928996086121</t>
@@ -1025,19 +1025,19 @@
     <t xml:space="preserve">3.46813893318176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47687482833862</t>
+    <t xml:space="preserve">3.47687458992004</t>
   </si>
   <si>
     <t xml:space="preserve">3.79136610031128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72147941589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87872457504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17574405670166</t>
+    <t xml:space="preserve">3.72147917747498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8787248134613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17574453353882</t>
   </si>
   <si>
     <t xml:space="preserve">4.31551790237427</t>
@@ -1046,34 +1046,34 @@
     <t xml:space="preserve">4.35046148300171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18447971343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20195150375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25436687469482</t>
+    <t xml:space="preserve">4.1844801902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20195198059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25436639785767</t>
   </si>
   <si>
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493226051331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98355507850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94861173629761</t>
+    <t xml:space="preserve">3.90493202209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98355484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94861149787903</t>
   </si>
   <si>
     <t xml:space="preserve">3.93113970756531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08838558197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07091379165649</t>
+    <t xml:space="preserve">4.08838510513306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07091331481934</t>
   </si>
   <si>
     <t xml:space="preserve">4.1233286857605</t>
@@ -1082,16 +1082,16 @@
     <t xml:space="preserve">4.00102663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00976324081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93987584114075</t>
+    <t xml:space="preserve">4.00976276397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93987560272217</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2106876373291</t>
+    <t xml:space="preserve">4.21068811416626</t>
   </si>
   <si>
     <t xml:space="preserve">4.29804611206055</t>
@@ -1100,7 +1100,7 @@
     <t xml:space="preserve">4.28930997848511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21942329406738</t>
+    <t xml:space="preserve">4.21942377090454</t>
   </si>
   <si>
     <t xml:space="preserve">4.19321632385254</t>
@@ -1109,28 +1109,28 @@
     <t xml:space="preserve">4.14953660964966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16700792312622</t>
+    <t xml:space="preserve">4.16700839996338</t>
   </si>
   <si>
     <t xml:space="preserve">4.11459302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06217765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78262996673584</t>
+    <t xml:space="preserve">4.06217813491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78263020515442</t>
   </si>
   <si>
     <t xml:space="preserve">3.80010175704956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8263099193573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83504557609558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84378147125244</t>
+    <t xml:space="preserve">3.82630944252014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83504509925842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84378123283386</t>
   </si>
   <si>
     <t xml:space="preserve">3.77389454841614</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734786987305</t>
+    <t xml:space="preserve">3.95734739303589</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
@@ -1148,16 +1148,16 @@
     <t xml:space="preserve">3.86125302314758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76515793800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81757354736328</t>
+    <t xml:space="preserve">3.7651584148407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8175733089447</t>
   </si>
   <si>
     <t xml:space="preserve">3.64285612106323</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67779970169067</t>
+    <t xml:space="preserve">3.67779946327209</t>
   </si>
   <si>
     <t xml:space="preserve">3.7389509677887</t>
@@ -1166,43 +1166,43 @@
     <t xml:space="preserve">3.85251712799072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71274328231812</t>
+    <t xml:space="preserve">3.71274304389954</t>
   </si>
   <si>
     <t xml:space="preserve">3.92240381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61664843559265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39825201034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23227047920227</t>
+    <t xml:space="preserve">3.61664867401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39825224876404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23227071762085</t>
   </si>
   <si>
     <t xml:space="preserve">3.0575532913208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97019481658936</t>
+    <t xml:space="preserve">2.97019457817078</t>
   </si>
   <si>
     <t xml:space="preserve">2.95272302627563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91777944564819</t>
+    <t xml:space="preserve">2.91777920722961</t>
   </si>
   <si>
     <t xml:space="preserve">2.90904355049133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3720440864563</t>
+    <t xml:space="preserve">3.37204432487488</t>
   </si>
   <si>
     <t xml:space="preserve">3.38078022003174</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41572380065918</t>
+    <t xml:space="preserve">3.41572403907776</t>
   </si>
   <si>
     <t xml:space="preserve">3.31962895393372</t>
@@ -56002,7 +56002,7 @@
     </row>
     <row r="2075">
       <c r="A2075" s="1" t="n">
-        <v>45985.6771064815</v>
+        <v>45985.3333333333</v>
       </c>
       <c r="B2075" t="n">
         <v>11208</v>
@@ -56023,6 +56023,32 @@
         <v>569</v>
       </c>
       <c r="H2075" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2076">
+      <c r="A2076" s="1" t="n">
+        <v>45986.654375</v>
+      </c>
+      <c r="B2076" t="n">
+        <v>2480</v>
+      </c>
+      <c r="C2076" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="D2076" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="E2076" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="F2076" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="G2076" t="s">
+        <v>571</v>
+      </c>
+      <c r="H2076" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02345752716064</t>
+    <t xml:space="preserve">3.02345776557922</t>
   </si>
   <si>
     <t xml:space="preserve">NDT.MI</t>
@@ -47,22 +47,22 @@
     <t xml:space="preserve">2.96519947052002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88901543617249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98013734817505</t>
+    <t xml:space="preserve">2.88901567459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98013710975647</t>
   </si>
   <si>
     <t xml:space="preserve">2.97266840934753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94578003883362</t>
+    <t xml:space="preserve">2.94577980041504</t>
   </si>
   <si>
     <t xml:space="preserve">2.95773029327393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9622118473053</t>
+    <t xml:space="preserve">2.96221160888672</t>
   </si>
   <si>
     <t xml:space="preserve">2.9353232383728</t>
@@ -71,22 +71,22 @@
     <t xml:space="preserve">2.91291642189026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97864365577698</t>
+    <t xml:space="preserve">2.9786434173584</t>
   </si>
   <si>
     <t xml:space="preserve">2.98611235618591</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03540825843811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05632138252258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0593090057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05034589767456</t>
+    <t xml:space="preserve">3.03540802001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.056321144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05930924415588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05034613609314</t>
   </si>
   <si>
     <t xml:space="preserve">2.98760628700256</t>
@@ -101,16 +101,16 @@
     <t xml:space="preserve">3.01001358032227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02495145797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01748251914978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03092670440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99955701828003</t>
+    <t xml:space="preserve">3.02495169639587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0174822807312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03092694282532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99955677986145</t>
   </si>
   <si>
     <t xml:space="preserve">3.0443708896637</t>
@@ -119,31 +119,31 @@
     <t xml:space="preserve">2.95922422409058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00254464149475</t>
+    <t xml:space="preserve">3.00254416465759</t>
   </si>
   <si>
     <t xml:space="preserve">2.92785429954529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90843486785889</t>
+    <t xml:space="preserve">2.90843462944031</t>
   </si>
   <si>
     <t xml:space="preserve">2.896484375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91889119148254</t>
+    <t xml:space="preserve">2.91889142990112</t>
   </si>
   <si>
     <t xml:space="preserve">2.9159038066864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92038536071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90544724464417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90992832183838</t>
+    <t xml:space="preserve">2.92038512229919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90544748306274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90992856025696</t>
   </si>
   <si>
     <t xml:space="preserve">2.9233729839325</t>
@@ -152,70 +152,70 @@
     <t xml:space="preserve">2.8382260799408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86063313484192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82627558708191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77996706962585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84569525718689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86810231208801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88303995132446</t>
+    <t xml:space="preserve">2.86063289642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82627511024475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77996754646301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84569501876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86810183525085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88304018974304</t>
   </si>
   <si>
     <t xml:space="preserve">2.79639959335327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87557101249695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89797854423523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80088090896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74262237548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8217945098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75009179115295</t>
+    <t xml:space="preserve">2.87557125091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89797806739807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80088067054749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74262261390686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82179427146912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7500913143158</t>
   </si>
   <si>
     <t xml:space="preserve">2.76353597640991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77847409248352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78594303131104</t>
+    <t xml:space="preserve">2.77847385406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78594279289246</t>
   </si>
   <si>
     <t xml:space="preserve">2.79341197013855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69631433486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65150094032288</t>
+    <t xml:space="preserve">2.69631457328796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6515007019043</t>
   </si>
   <si>
     <t xml:space="preserve">2.62162446975708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53946566581726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56934142112732</t>
+    <t xml:space="preserve">2.53946542739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5693416595459</t>
   </si>
   <si>
     <t xml:space="preserve">2.61415553092957</t>
@@ -224,34 +224,34 @@
     <t xml:space="preserve">2.65896964073181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68884539604187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70378375053406</t>
+    <t xml:space="preserve">2.68884563446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70378351211548</t>
   </si>
   <si>
     <t xml:space="preserve">2.77100491523743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81581902503967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73365998268127</t>
+    <t xml:space="preserve">2.81581926345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7336597442627</t>
   </si>
   <si>
     <t xml:space="preserve">2.66643857955933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68137669563293</t>
+    <t xml:space="preserve">2.68137645721436</t>
   </si>
   <si>
     <t xml:space="preserve">2.74112892150879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72619080543518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8307569026947</t>
+    <t xml:space="preserve">2.7261905670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83075714111328</t>
   </si>
   <si>
     <t xml:space="preserve">2.893150806427</t>
@@ -266,7 +266,7 @@
     <t xml:space="preserve">2.93203687667847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87759613990784</t>
+    <t xml:space="preserve">2.87759637832642</t>
   </si>
   <si>
     <t xml:space="preserve">2.83093237876892</t>
@@ -281,13 +281,13 @@
     <t xml:space="preserve">2.79982304573059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73760485649109</t>
+    <t xml:space="preserve">2.73760509490967</t>
   </si>
   <si>
     <t xml:space="preserve">2.76093697547913</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8076000213623</t>
+    <t xml:space="preserve">2.80760049819946</t>
   </si>
   <si>
     <t xml:space="preserve">3.00980997085571</t>
@@ -296,13 +296,13 @@
     <t xml:space="preserve">2.9553689956665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90870547294617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88537335395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82315540313721</t>
+    <t xml:space="preserve">2.90870523452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88537311553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82315516471863</t>
   </si>
   <si>
     <t xml:space="preserve">2.86204171180725</t>
@@ -311,37 +311,37 @@
     <t xml:space="preserve">3.00203251838684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91648268699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85426449775696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7298276424408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68316411972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72205018997192</t>
+    <t xml:space="preserve">2.9164822101593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8542640209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72982740402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68316388130188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7220504283905</t>
   </si>
   <si>
     <t xml:space="preserve">2.75315952301025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70649576187134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93981409072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99425554275513</t>
+    <t xml:space="preserve">2.70649600028992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93981456756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99425530433655</t>
   </si>
   <si>
     <t xml:space="preserve">2.97870087623596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86981868743896</t>
+    <t xml:space="preserve">2.86981844902039</t>
   </si>
   <si>
     <t xml:space="preserve">2.94759154319763</t>
@@ -350,10 +350,10 @@
     <t xml:space="preserve">2.98647809028625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63650012016296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55094981193542</t>
+    <t xml:space="preserve">2.63650035858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.550950050354</t>
   </si>
   <si>
     <t xml:space="preserve">2.51984119415283</t>
@@ -362,7 +362,7 @@
     <t xml:space="preserve">2.41095876693726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34096336364746</t>
+    <t xml:space="preserve">2.34096360206604</t>
   </si>
   <si>
     <t xml:space="preserve">2.34874081611633</t>
@@ -371,31 +371,31 @@
     <t xml:space="preserve">2.36429524421692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25541353225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24763607978821</t>
+    <t xml:space="preserve">2.2554132938385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24763584136963</t>
   </si>
   <si>
     <t xml:space="preserve">2.3254086971283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23208093643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18541765213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27874517440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26319026947021</t>
+    <t xml:space="preserve">2.23208117485046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18541741371155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27874493598938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26319050788879</t>
   </si>
   <si>
     <t xml:space="preserve">2.21652674674988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06875824928284</t>
+    <t xml:space="preserve">2.06875848770142</t>
   </si>
   <si>
     <t xml:space="preserve">2.1465311050415</t>
@@ -407,46 +407,46 @@
     <t xml:space="preserve">2.1543083190918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17763996124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22430419921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35651779174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4887318611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52761816978455</t>
+    <t xml:space="preserve">2.17764019966125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22430396080017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35651803016663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48873209953308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52761793136597</t>
   </si>
   <si>
     <t xml:space="preserve">2.43429088592529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44206786155701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55872750282288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44984555244446</t>
+    <t xml:space="preserve">2.44206833839417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5587272644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44984531402588</t>
   </si>
   <si>
     <t xml:space="preserve">2.37207245826721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33318591117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29429936408997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37984991073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71427321434021</t>
+    <t xml:space="preserve">2.33318614959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29429960250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3798496723175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71427297592163</t>
   </si>
   <si>
     <t xml:space="preserve">2.58205914497375</t>
@@ -455,115 +455,115 @@
     <t xml:space="preserve">2.62872290611267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65983200073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57428169250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67538666725159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64427781105042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69094109535217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76871418952942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90092778205872</t>
+    <t xml:space="preserve">2.65983247756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57428193092346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67538690567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64427733421326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69094133377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76871395111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90092754364014</t>
   </si>
   <si>
     <t xml:space="preserve">2.9631462097168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92426013946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97092318534851</t>
+    <t xml:space="preserve">2.92425990104675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97092366218567</t>
   </si>
   <si>
     <t xml:space="preserve">3.01758742332458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04869627952576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03314185142517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06425094604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07980537414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06049871444702</t>
+    <t xml:space="preserve">3.04869651794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03314208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0642511844635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07980561256409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06049919128418</t>
   </si>
   <si>
     <t xml:space="preserve">3.02811288833618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01191973686218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10907816886902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0928852558136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1252715587616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07669186592102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99572682380676</t>
+    <t xml:space="preserve">3.01191997528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1090784072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09288501739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12527132034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0766921043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99572658538818</t>
   </si>
   <si>
     <t xml:space="preserve">3.30339574813843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41674757003784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35197520256042</t>
+    <t xml:space="preserve">3.41674733161926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35197496414185</t>
   </si>
   <si>
     <t xml:space="preserve">3.33578181266785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36816835403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23862314224243</t>
+    <t xml:space="preserve">3.36816811561584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23862338066101</t>
   </si>
   <si>
     <t xml:space="preserve">3.31958866119385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27100968360901</t>
+    <t xml:space="preserve">3.27100944519043</t>
   </si>
   <si>
     <t xml:space="preserve">3.28720259666443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22243022918701</t>
+    <t xml:space="preserve">3.22243046760559</t>
   </si>
   <si>
     <t xml:space="preserve">3.17385077476501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20623707771301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14146494865417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40055418014526</t>
+    <t xml:space="preserve">3.20623731613159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1414647102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40055441856384</t>
   </si>
   <si>
     <t xml:space="preserve">3.49771332740784</t>
@@ -572,10 +572,10 @@
     <t xml:space="preserve">3.38436126708984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25481653213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19004392623901</t>
+    <t xml:space="preserve">3.25481629371643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19004416465759</t>
   </si>
   <si>
     <t xml:space="preserve">2.96334028244019</t>
@@ -584,70 +584,70 @@
     <t xml:space="preserve">2.97953367233276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80140900611877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88237476348877</t>
+    <t xml:space="preserve">2.80140924453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88237452507019</t>
   </si>
   <si>
     <t xml:space="preserve">2.86618161201477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84998846054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78521609306335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75283002853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72044372558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83379530906677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76902318000793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73663687705994</t>
+    <t xml:space="preserve">2.84998869895935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78521633148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75282979011536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72044324874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83379554748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76902341842651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73663663864136</t>
   </si>
   <si>
     <t xml:space="preserve">2.81760239601135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89856791496277</t>
+    <t xml:space="preserve">2.89856767654419</t>
   </si>
   <si>
     <t xml:space="preserve">2.91476082801819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63947772979736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67186403274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62328505516052</t>
+    <t xml:space="preserve">2.63947796821594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67186427116394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62328481674194</t>
   </si>
   <si>
     <t xml:space="preserve">2.68805718421936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70425033569336</t>
+    <t xml:space="preserve">2.70425009727478</t>
   </si>
   <si>
     <t xml:space="preserve">2.60709190368652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59089875221252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42896723747253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54231953620911</t>
+    <t xml:space="preserve">2.5908989906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42896771430969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54231929779053</t>
   </si>
   <si>
     <t xml:space="preserve">2.46135354042053</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">2.2994225025177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35488152503967</t>
+    <t xml:space="preserve">2.35488176345825</t>
   </si>
   <si>
     <t xml:space="preserve">2.40607476234436</t>
@@ -668,13 +668,13 @@
     <t xml:space="preserve">2.28662443161011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13304495811462</t>
+    <t xml:space="preserve">2.13304471969604</t>
   </si>
   <si>
     <t xml:space="preserve">2.08185195922852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0647873878479</t>
+    <t xml:space="preserve">2.06478762626648</t>
   </si>
   <si>
     <t xml:space="preserve">2.03065896034241</t>
@@ -689,22 +689,22 @@
     <t xml:space="preserve">2.26956009864807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2183666229248</t>
+    <t xml:space="preserve">2.21836686134338</t>
   </si>
   <si>
     <t xml:space="preserve">2.32075309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55965399742126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54258990287781</t>
+    <t xml:space="preserve">2.55965423583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54258966445923</t>
   </si>
   <si>
     <t xml:space="preserve">2.45726799964905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5767183303833</t>
+    <t xml:space="preserve">2.57671856880188</t>
   </si>
   <si>
     <t xml:space="preserve">2.62791132926941</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">2.59378290176392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69616889953613</t>
+    <t xml:space="preserve">2.69616913795471</t>
   </si>
   <si>
     <t xml:space="preserve">2.71323323249817</t>
@@ -731,10 +731,10 @@
     <t xml:space="preserve">2.4231390953064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47433257102966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15010952949524</t>
+    <t xml:space="preserve">2.47433233261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15010929107666</t>
   </si>
   <si>
     <t xml:space="preserve">2.33781743049622</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">2.25249576568604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23543095588684</t>
+    <t xml:space="preserve">2.23543119430542</t>
   </si>
   <si>
     <t xml:space="preserve">2.37194609642029</t>
@@ -761,52 +761,52 @@
     <t xml:space="preserve">2.18423795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01359438896179</t>
+    <t xml:space="preserve">2.01359415054321</t>
   </si>
   <si>
     <t xml:space="preserve">2.04772329330444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11598062515259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91120839118958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87707984447479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84295094013214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97946584224701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86001539230347</t>
+    <t xml:space="preserve">2.11598038673401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91120827198029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87707960605621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84295117855072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97946560382843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86001515388489</t>
   </si>
   <si>
     <t xml:space="preserve">1.94533693790436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96240127086639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99653017520905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81561923027039</t>
+    <t xml:space="preserve">1.96240139007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99653005599976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81561946868896</t>
   </si>
   <si>
     <t xml:space="preserve">2.90094137191772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88387703895569</t>
+    <t xml:space="preserve">2.88387680053711</t>
   </si>
   <si>
     <t xml:space="preserve">2.76442646980286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73029756546021</t>
+    <t xml:space="preserve">2.73029780387878</t>
   </si>
   <si>
     <t xml:space="preserve">2.6791045665741</t>
@@ -815,16 +815,16 @@
     <t xml:space="preserve">2.74736189842224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83268356323242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86681246757507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79855489730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78149056434631</t>
+    <t xml:space="preserve">2.832683801651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86681222915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79855513572693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78149080276489</t>
   </si>
   <si>
     <t xml:space="preserve">2.9350700378418</t>
@@ -839,16 +839,16 @@
     <t xml:space="preserve">3.00332736968994</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03745627403259</t>
+    <t xml:space="preserve">3.03745603561401</t>
   </si>
   <si>
     <t xml:space="preserve">2.98626303672791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05452060699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07158470153809</t>
+    <t xml:space="preserve">3.05452036857605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07158493995667</t>
   </si>
   <si>
     <t xml:space="preserve">3.13984251022339</t>
@@ -869,7 +869,7 @@
     <t xml:space="preserve">3.1995677947998</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15690684318542</t>
+    <t xml:space="preserve">3.15690660476685</t>
   </si>
   <si>
     <t xml:space="preserve">3.2336962223053</t>
@@ -878,25 +878,25 @@
     <t xml:space="preserve">3.27635717391968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24222826957703</t>
+    <t xml:space="preserve">3.24222850799561</t>
   </si>
   <si>
     <t xml:space="preserve">3.26782488822937</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31048607826233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34461450576782</t>
+    <t xml:space="preserve">3.31048631668091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3446147441864</t>
   </si>
   <si>
     <t xml:space="preserve">3.32755041122437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28488945960999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18250346183777</t>
+    <t xml:space="preserve">3.28488922119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18250322341919</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342150688171</t>
@@ -905,25 +905,25 @@
     <t xml:space="preserve">3.33710074424744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32836484909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24974250793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20606303215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15364742279053</t>
+    <t xml:space="preserve">3.32836508750916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24974226951599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20606279373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15364766120911</t>
   </si>
   <si>
     <t xml:space="preserve">3.21479892730713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17111945152283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26721405982971</t>
+    <t xml:space="preserve">3.17111968994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26721382141113</t>
   </si>
   <si>
     <t xml:space="preserve">3.36330842971802</t>
@@ -932,64 +932,64 @@
     <t xml:space="preserve">3.49434638023376</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58170509338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56423354148865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59044122695923</t>
+    <t xml:space="preserve">3.58170533180237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56423330307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59044098854065</t>
   </si>
   <si>
     <t xml:space="preserve">3.5030825138092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51181817054749</t>
+    <t xml:space="preserve">3.51181840896606</t>
   </si>
   <si>
     <t xml:space="preserve">3.54676175117493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63412022590637</t>
+    <t xml:space="preserve">3.63411998748779</t>
   </si>
   <si>
     <t xml:space="preserve">3.62538456916809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74768662452698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69527125358582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66906332969666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60791301727295</t>
+    <t xml:space="preserve">3.7476863861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69527149200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66906380653381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60791277885437</t>
   </si>
   <si>
     <t xml:space="preserve">3.55549788475037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66032767295837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65159177780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68653512001038</t>
+    <t xml:space="preserve">3.66032814979553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65159201622009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68653535842896</t>
   </si>
   <si>
     <t xml:space="preserve">3.7040069103241</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75642275810242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57296943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53802609443665</t>
+    <t xml:space="preserve">3.75642251968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57296967506409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53802585601807</t>
   </si>
   <si>
     <t xml:space="preserve">3.3458366394043</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">3.42445969581604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45066714286804</t>
+    <t xml:space="preserve">3.45066738128662</t>
   </si>
   <si>
     <t xml:space="preserve">3.44193148612976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4856104850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4069881439209</t>
+    <t xml:space="preserve">3.48561072349548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40698790550232</t>
   </si>
   <si>
     <t xml:space="preserve">3.35457253456116</t>
@@ -1034,37 +1034,37 @@
     <t xml:space="preserve">3.72147917747498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8787248134613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17574453353882</t>
+    <t xml:space="preserve">3.87872457504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17574405670166</t>
   </si>
   <si>
     <t xml:space="preserve">4.31551790237427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35046148300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1844801902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20195198059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25436639785767</t>
+    <t xml:space="preserve">4.35046100616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18447971343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20195150375366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25436687469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493202209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98355484008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94861149787903</t>
+    <t xml:space="preserve">3.90493226051331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98355507850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94861173629761</t>
   </si>
   <si>
     <t xml:space="preserve">3.93113970756531</t>
@@ -1073,10 +1073,10 @@
     <t xml:space="preserve">4.08838510513306</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07091331481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1233286857605</t>
+    <t xml:space="preserve">4.07091379165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12332820892334</t>
   </si>
   <si>
     <t xml:space="preserve">4.00102663040161</t>
@@ -1091,16 +1091,16 @@
     <t xml:space="preserve">4.0971212387085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21068811416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29804611206055</t>
+    <t xml:space="preserve">4.2106876373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29804658889771</t>
   </si>
   <si>
     <t xml:space="preserve">4.28930997848511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21942377090454</t>
+    <t xml:space="preserve">4.21942329406738</t>
   </si>
   <si>
     <t xml:space="preserve">4.19321632385254</t>
@@ -1115,7 +1115,7 @@
     <t xml:space="preserve">4.11459302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06217813491821</t>
+    <t xml:space="preserve">4.06217765808105</t>
   </si>
   <si>
     <t xml:space="preserve">3.78263020515442</t>
@@ -1124,10 +1124,10 @@
     <t xml:space="preserve">3.80010175704956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82630944252014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83504509925842</t>
+    <t xml:space="preserve">3.82630968093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.835045337677</t>
   </si>
   <si>
     <t xml:space="preserve">3.84378123283386</t>
@@ -1139,16 +1139,16 @@
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734739303589</t>
+    <t xml:space="preserve">3.95734763145447</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86125302314758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7651584148407</t>
+    <t xml:space="preserve">3.861252784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76515817642212</t>
   </si>
   <si>
     <t xml:space="preserve">3.8175733089447</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">3.64285612106323</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67779946327209</t>
+    <t xml:space="preserve">3.67779970169067</t>
   </si>
   <si>
     <t xml:space="preserve">3.7389509677887</t>
@@ -1166,31 +1166,31 @@
     <t xml:space="preserve">3.85251712799072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71274304389954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92240381240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61664867401123</t>
+    <t xml:space="preserve">3.71274328231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92240357398987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61664843559265</t>
   </si>
   <si>
     <t xml:space="preserve">3.39825224876404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23227071762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0575532913208</t>
+    <t xml:space="preserve">3.23227047920227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05755352973938</t>
   </si>
   <si>
     <t xml:space="preserve">2.97019457817078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95272302627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91777920722961</t>
+    <t xml:space="preserve">2.95272278785706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91777944564819</t>
   </si>
   <si>
     <t xml:space="preserve">2.90904355049133</t>
@@ -1199,19 +1199,19 @@
     <t xml:space="preserve">3.37204432487488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38078022003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41572403907776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31962895393372</t>
+    <t xml:space="preserve">3.38077998161316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41572380065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31962919235229</t>
   </si>
   <si>
     <t xml:space="preserve">3.27594995498657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28468561172485</t>
+    <t xml:space="preserve">3.28468585014343</t>
   </si>
   <si>
     <t xml:space="preserve">3.50245499610901</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">3.32098078727722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26653814315796</t>
+    <t xml:space="preserve">3.26653838157654</t>
   </si>
   <si>
     <t xml:space="preserve">3.39357042312622</t>
@@ -1256,7 +1256,7 @@
     <t xml:space="preserve">3.23024344444275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19394874572754</t>
+    <t xml:space="preserve">3.19394850730896</t>
   </si>
   <si>
     <t xml:space="preserve">3.25746440887451</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">3.2211697101593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10321140289307</t>
+    <t xml:space="preserve">3.10321164131165</t>
   </si>
   <si>
     <t xml:space="preserve">2.99432682991028</t>
@@ -1283,13 +1283,13 @@
     <t xml:space="preserve">2.95803189277649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85822105407715</t>
+    <t xml:space="preserve">2.85822129249573</t>
   </si>
   <si>
     <t xml:space="preserve">2.89451599121094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8672947883606</t>
+    <t xml:space="preserve">2.86729502677917</t>
   </si>
   <si>
     <t xml:space="preserve">2.81285238265991</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">2.75841021537781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70396780967712</t>
+    <t xml:space="preserve">2.7039680480957</t>
   </si>
   <si>
     <t xml:space="preserve">2.72211527824402</t>
@@ -1310,16 +1310,16 @@
     <t xml:space="preserve">2.64952564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7947051525116</t>
+    <t xml:space="preserve">2.79470491409302</t>
   </si>
   <si>
     <t xml:space="preserve">2.92173719406128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05784273147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02154803276062</t>
+    <t xml:space="preserve">3.05784296989441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02154779434204</t>
   </si>
   <si>
     <t xml:space="preserve">3.13950634002686</t>
@@ -1349,46 +1349,46 @@
     <t xml:space="preserve">3.08506417274475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01247429847717</t>
+    <t xml:space="preserve">3.01247406005859</t>
   </si>
   <si>
     <t xml:space="preserve">2.88544225692749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7765576839447</t>
+    <t xml:space="preserve">2.77655744552612</t>
   </si>
   <si>
     <t xml:space="preserve">2.71304154396057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6313784122467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68582034111023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66767287254333</t>
+    <t xml:space="preserve">2.63137817382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68582057952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66767311096191</t>
   </si>
   <si>
     <t xml:space="preserve">2.55878829956055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52249336242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67674660682678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64045214653015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87636852264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83099985122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60415697097778</t>
+    <t xml:space="preserve">2.52249360084534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67674684524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64045190811157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87636876106262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83099961280823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6041567325592</t>
   </si>
   <si>
     <t xml:space="preserve">2.73118901252747</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">2.91266345977783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12135887145996</t>
+    <t xml:space="preserve">3.12135910987854</t>
   </si>
   <si>
     <t xml:space="preserve">3.0759904384613</t>
@@ -1424,46 +1424,46 @@
     <t xml:space="preserve">3.0941379070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38449692726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41171765327454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37542319297791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42079138755798</t>
+    <t xml:space="preserve">3.38449668884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41171789169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37542295455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42079162597656</t>
   </si>
   <si>
     <t xml:space="preserve">3.43893885612488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36634945869446</t>
+    <t xml:space="preserve">3.36634922027588</t>
   </si>
   <si>
     <t xml:space="preserve">3.35727572441101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20302248001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27561187744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29375958442688</t>
+    <t xml:space="preserve">3.20302224159241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27561211585999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29375982284546</t>
   </si>
   <si>
     <t xml:space="preserve">3.1667275428772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11228513717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78563141822815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84007382392883</t>
+    <t xml:space="preserve">3.11228537559509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78563117980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84007358551025</t>
   </si>
   <si>
     <t xml:space="preserve">2.82192611694336</t>
@@ -56028,7 +56028,7 @@
     </row>
     <row r="2076">
       <c r="A2076" s="1" t="n">
-        <v>45986.654375</v>
+        <v>45986.3333333333</v>
       </c>
       <c r="B2076" t="n">
         <v>2480</v>
@@ -56049,6 +56049,32 @@
         <v>571</v>
       </c>
       <c r="H2076" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2077">
+      <c r="A2077" s="1" t="n">
+        <v>45987.6716666667</v>
+      </c>
+      <c r="B2077" t="n">
+        <v>75182</v>
+      </c>
+      <c r="C2077" t="n">
+        <v>3.40000009536743</v>
+      </c>
+      <c r="D2077" t="n">
+        <v>3.24000000953674</v>
+      </c>
+      <c r="E2077" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="F2077" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="G2077" t="s">
+        <v>572</v>
+      </c>
+      <c r="H2077" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="578" uniqueCount="578">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,46 +44,46 @@
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519923210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88901519775391</t>
+    <t xml:space="preserve">2.96519947052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88901543617249</t>
   </si>
   <si>
     <t xml:space="preserve">2.98013734817505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97266817092896</t>
+    <t xml:space="preserve">2.97266840934753</t>
   </si>
   <si>
     <t xml:space="preserve">2.94578003883362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95773029327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9622118473053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93532347679138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91291618347168</t>
+    <t xml:space="preserve">2.95773005485535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96221160888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9353232383728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91291666030884</t>
   </si>
   <si>
     <t xml:space="preserve">2.97864365577698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98611235618591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03540802001953</t>
+    <t xml:space="preserve">2.98611211776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03540825843811</t>
   </si>
   <si>
     <t xml:space="preserve">3.05632138252258</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05930852890015</t>
+    <t xml:space="preserve">3.0593090057373</t>
   </si>
   <si>
     <t xml:space="preserve">3.05034613609314</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">2.98760604858398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95026111602783</t>
+    <t xml:space="preserve">2.95026135444641</t>
   </si>
   <si>
     <t xml:space="preserve">3.01598858833313</t>
@@ -101,28 +101,28 @@
     <t xml:space="preserve">3.01001358032227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02495169639587</t>
+    <t xml:space="preserve">3.02495145797729</t>
   </si>
   <si>
     <t xml:space="preserve">3.0174822807312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03092646598816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99955677986145</t>
+    <t xml:space="preserve">3.03092694282532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99955654144287</t>
   </si>
   <si>
     <t xml:space="preserve">3.04437112808228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.959223985672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00254416465759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92785406112671</t>
+    <t xml:space="preserve">2.95922374725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00254464149475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92785429954529</t>
   </si>
   <si>
     <t xml:space="preserve">2.90843486785889</t>
@@ -131,22 +131,22 @@
     <t xml:space="preserve">2.896484375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91889142990112</t>
+    <t xml:space="preserve">2.91889119148254</t>
   </si>
   <si>
     <t xml:space="preserve">2.9159038066864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92038536071777</t>
+    <t xml:space="preserve">2.92038512229919</t>
   </si>
   <si>
     <t xml:space="preserve">2.90544724464417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90992856025696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9233729839325</t>
+    <t xml:space="preserve">2.9099280834198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92337274551392</t>
   </si>
   <si>
     <t xml:space="preserve">2.8382260799408</t>
@@ -158,28 +158,28 @@
     <t xml:space="preserve">2.82627558708191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77996754646301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84569478034973</t>
+    <t xml:space="preserve">2.77996730804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84569501876831</t>
   </si>
   <si>
     <t xml:space="preserve">2.86810183525085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88304018974304</t>
+    <t xml:space="preserve">2.88303995132446</t>
   </si>
   <si>
     <t xml:space="preserve">2.79639935493469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87557101249695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89797830581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80088114738464</t>
+    <t xml:space="preserve">2.87557077407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89797806739807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80088090896606</t>
   </si>
   <si>
     <t xml:space="preserve">2.74262261390686</t>
@@ -188,13 +188,13 @@
     <t xml:space="preserve">2.8217945098877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7500913143158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76353597640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77847409248352</t>
+    <t xml:space="preserve">2.75009155273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76353645324707</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77847385406494</t>
   </si>
   <si>
     <t xml:space="preserve">2.78594279289246</t>
@@ -203,40 +203,40 @@
     <t xml:space="preserve">2.79341197013855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69631457328796</t>
+    <t xml:space="preserve">2.69631481170654</t>
   </si>
   <si>
     <t xml:space="preserve">2.6515007019043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62162470817566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53946566581726</t>
+    <t xml:space="preserve">2.6216242313385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53946542739868</t>
   </si>
   <si>
     <t xml:space="preserve">2.5693416595459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61415529251099</t>
+    <t xml:space="preserve">2.61415553092957</t>
   </si>
   <si>
     <t xml:space="preserve">2.65896964073181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68884563446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70378375053406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77100467681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81581926345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73365950584412</t>
+    <t xml:space="preserve">2.68884515762329</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70378351211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77100491523743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81581902503967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73366022109985</t>
   </si>
   <si>
     <t xml:space="preserve">2.66643857955933</t>
@@ -248,16 +248,16 @@
     <t xml:space="preserve">2.74112892150879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7261905670166</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83075666427612</t>
+    <t xml:space="preserve">2.72619080543518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83075714111328</t>
   </si>
   <si>
     <t xml:space="preserve">2.893150806427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69871854782104</t>
+    <t xml:space="preserve">2.69871830940247</t>
   </si>
   <si>
     <t xml:space="preserve">2.83870959281921</t>
@@ -266,19 +266,19 @@
     <t xml:space="preserve">2.93203711509705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87759613990784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8309326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81537771224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84648680686951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79982304573059</t>
+    <t xml:space="preserve">2.87759637832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83093214035034</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81537747383118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84648704528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79982328414917</t>
   </si>
   <si>
     <t xml:space="preserve">2.73760485649109</t>
@@ -287,31 +287,31 @@
     <t xml:space="preserve">2.76093673706055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80760073661804</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00980997085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95536875724792</t>
+    <t xml:space="preserve">2.80760049819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00980973243713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9553689956665</t>
   </si>
   <si>
     <t xml:space="preserve">2.90870523452759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88537335395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82315540313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86204147338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00203275680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91648268699646</t>
+    <t xml:space="preserve">2.88537311553955</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82315516471863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86204171180725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00203227996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91648244857788</t>
   </si>
   <si>
     <t xml:space="preserve">2.85426425933838</t>
@@ -323,37 +323,37 @@
     <t xml:space="preserve">2.68316411972046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7220504283905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75315928459167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70649600028992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93981409072876</t>
+    <t xml:space="preserve">2.72205018997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75315952301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70649576187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93981432914734</t>
   </si>
   <si>
     <t xml:space="preserve">2.99425530433655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97870111465454</t>
+    <t xml:space="preserve">2.97870087623596</t>
   </si>
   <si>
     <t xml:space="preserve">2.86981892585754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94759130477905</t>
+    <t xml:space="preserve">2.94759202003479</t>
   </si>
   <si>
     <t xml:space="preserve">2.98647785186768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63650012016296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.550950050354</t>
+    <t xml:space="preserve">2.63650035858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55094981193542</t>
   </si>
   <si>
     <t xml:space="preserve">2.51984119415283</t>
@@ -362,16 +362,16 @@
     <t xml:space="preserve">2.41095876693726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34096360206604</t>
+    <t xml:space="preserve">2.34096336364746</t>
   </si>
   <si>
     <t xml:space="preserve">2.34874081611633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36429500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2554132938385</t>
+    <t xml:space="preserve">2.36429524421692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25541353225708</t>
   </si>
   <si>
     <t xml:space="preserve">2.24763607978821</t>
@@ -386,22 +386,22 @@
     <t xml:space="preserve">2.18541765213013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2787446975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26319050788879</t>
+    <t xml:space="preserve">2.27874517440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26319074630737</t>
   </si>
   <si>
     <t xml:space="preserve">2.21652674674988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06875824928284</t>
+    <t xml:space="preserve">2.06875848770142</t>
   </si>
   <si>
     <t xml:space="preserve">2.1465311050415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10764479637146</t>
+    <t xml:space="preserve">2.10764455795288</t>
   </si>
   <si>
     <t xml:space="preserve">2.1543083190918</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">2.17764019966125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22430396080017</t>
+    <t xml:space="preserve">2.22430372238159</t>
   </si>
   <si>
     <t xml:space="preserve">2.35651779174805</t>
@@ -422,16 +422,16 @@
     <t xml:space="preserve">2.52761816978455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43429112434387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44206809997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55872750282288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44984531402588</t>
+    <t xml:space="preserve">2.43429088592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44206786155701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55872702598572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44984555244446</t>
   </si>
   <si>
     <t xml:space="preserve">2.37207245826721</t>
@@ -443,25 +443,25 @@
     <t xml:space="preserve">2.29429960250854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3798496723175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71427321434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58205914497375</t>
+    <t xml:space="preserve">2.37984991073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71427297592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58205890655518</t>
   </si>
   <si>
     <t xml:space="preserve">2.62872290611267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65983200073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57428169250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67538690567017</t>
+    <t xml:space="preserve">2.65983247756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57428193092346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67538666725159</t>
   </si>
   <si>
     <t xml:space="preserve">2.64427757263184</t>
@@ -476,49 +476,49 @@
     <t xml:space="preserve">2.90092778205872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9631462097168</t>
+    <t xml:space="preserve">2.96314644813538</t>
   </si>
   <si>
     <t xml:space="preserve">2.92425990104675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97092366218567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01758766174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04869627952576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03314185142517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06425094604492</t>
+    <t xml:space="preserve">2.97092342376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01758718490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04869675636292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03314208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0642511844635</t>
   </si>
   <si>
     <t xml:space="preserve">3.07980561256409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0604989528656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0281126499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01191997528076</t>
+    <t xml:space="preserve">3.06049919128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02811288833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01191973686218</t>
   </si>
   <si>
     <t xml:space="preserve">3.10907816886902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09288501739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12527132034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07669234275818</t>
+    <t xml:space="preserve">3.0928852558136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12527108192444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0766921043396</t>
   </si>
   <si>
     <t xml:space="preserve">2.99572682380676</t>
@@ -527,19 +527,19 @@
     <t xml:space="preserve">3.30339574813843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41674733161926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35197472572327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33578181266785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36816835403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23862338066101</t>
+    <t xml:space="preserve">3.41674709320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35197520256042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33578205108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36816811561584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23862314224243</t>
   </si>
   <si>
     <t xml:space="preserve">3.31958866119385</t>
@@ -548,10 +548,10 @@
     <t xml:space="preserve">3.27100944519043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28720235824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22242999076843</t>
+    <t xml:space="preserve">3.28720259666443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22243022918701</t>
   </si>
   <si>
     <t xml:space="preserve">3.17385101318359</t>
@@ -563,7 +563,7 @@
     <t xml:space="preserve">3.1414647102356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40055441856384</t>
+    <t xml:space="preserve">3.40055418014526</t>
   </si>
   <si>
     <t xml:space="preserve">3.49771332740784</t>
@@ -572,22 +572,22 @@
     <t xml:space="preserve">3.38436126708984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25481653213501</t>
+    <t xml:space="preserve">3.25481629371643</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004416465759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96334004402161</t>
+    <t xml:space="preserve">2.96334052085876</t>
   </si>
   <si>
     <t xml:space="preserve">2.97953367233276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80140924453735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88237500190735</t>
+    <t xml:space="preserve">2.80140900611877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88237476348877</t>
   </si>
   <si>
     <t xml:space="preserve">2.86618161201477</t>
@@ -599,7 +599,7 @@
     <t xml:space="preserve">2.78521633148193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75283002853394</t>
+    <t xml:space="preserve">2.75282979011536</t>
   </si>
   <si>
     <t xml:space="preserve">2.72044348716736</t>
@@ -608,16 +608,16 @@
     <t xml:space="preserve">2.83379530906677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76902294158936</t>
+    <t xml:space="preserve">2.76902341842651</t>
   </si>
   <si>
     <t xml:space="preserve">2.73663663864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81760263442993</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89856743812561</t>
+    <t xml:space="preserve">2.81760239601135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89856791496277</t>
   </si>
   <si>
     <t xml:space="preserve">2.91476082801819</t>
@@ -629,25 +629,25 @@
     <t xml:space="preserve">2.67186427116394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6232852935791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68805742263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70425033569336</t>
+    <t xml:space="preserve">2.62328505516052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68805718421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70425009727478</t>
   </si>
   <si>
     <t xml:space="preserve">2.60709190368652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59089875221252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42896771430969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54231929779053</t>
+    <t xml:space="preserve">2.59089851379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42896747589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54231905937195</t>
   </si>
   <si>
     <t xml:space="preserve">2.46135377883911</t>
@@ -656,7 +656,7 @@
     <t xml:space="preserve">2.31561541557312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29942274093628</t>
+    <t xml:space="preserve">2.2994225025177</t>
   </si>
   <si>
     <t xml:space="preserve">2.35488176345825</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">2.40607476234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28662419319153</t>
+    <t xml:space="preserve">2.28662443161011</t>
   </si>
   <si>
     <t xml:space="preserve">2.1330451965332</t>
@@ -674,7 +674,7 @@
     <t xml:space="preserve">2.08185195922852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06478762626648</t>
+    <t xml:space="preserve">2.0647873878479</t>
   </si>
   <si>
     <t xml:space="preserve">2.03065896034241</t>
@@ -683,19 +683,19 @@
     <t xml:space="preserve">2.1671736240387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09891605377197</t>
+    <t xml:space="preserve">2.09891629219055</t>
   </si>
   <si>
     <t xml:space="preserve">2.26955986022949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21836686134338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32075309753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55965423583984</t>
+    <t xml:space="preserve">2.2183666229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32075333595276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55965399742126</t>
   </si>
   <si>
     <t xml:space="preserve">2.54258990287781</t>
@@ -704,10 +704,10 @@
     <t xml:space="preserve">2.45726799964905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5767183303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62791156768799</t>
+    <t xml:space="preserve">2.57671856880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62791132926941</t>
   </si>
   <si>
     <t xml:space="preserve">2.61084699630737</t>
@@ -722,13 +722,13 @@
     <t xml:space="preserve">2.69616913795471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71323299407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44020318984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42313933372498</t>
+    <t xml:space="preserve">2.71323323249817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44020342826843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4231390953064</t>
   </si>
   <si>
     <t xml:space="preserve">2.47433233261108</t>
@@ -740,7 +740,7 @@
     <t xml:space="preserve">2.33781743049622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30368852615356</t>
+    <t xml:space="preserve">2.30368876457214</t>
   </si>
   <si>
     <t xml:space="preserve">2.25249552726746</t>
@@ -767,16 +767,16 @@
     <t xml:space="preserve">2.04772305488586</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11598038673401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91120827198029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8770797252655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84295094013214</t>
+    <t xml:space="preserve">2.11598062515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91120851039886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87707960605621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84295105934143</t>
   </si>
   <si>
     <t xml:space="preserve">1.97946584224701</t>
@@ -785,13 +785,13 @@
     <t xml:space="preserve">1.86001539230347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94533717632294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96240139007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99653005599976</t>
+    <t xml:space="preserve">1.94533693790436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96240150928497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99652993679047</t>
   </si>
   <si>
     <t xml:space="preserve">2.81561946868896</t>
@@ -800,37 +800,37 @@
     <t xml:space="preserve">2.90094137191772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88387680053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76442670822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73029780387878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6791045665741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74736213684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.832683801651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86681246757507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79855513572693</t>
+    <t xml:space="preserve">2.88387703895569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76442646980286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73029756546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67910432815552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74736189842224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83268356323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86681222915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79855489730835</t>
   </si>
   <si>
     <t xml:space="preserve">2.78149056434631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93507027626038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96919894218445</t>
+    <t xml:space="preserve">2.9350700378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96919870376587</t>
   </si>
   <si>
     <t xml:space="preserve">3.02039170265198</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">3.00332736968994</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03745627403259</t>
+    <t xml:space="preserve">3.03745603561401</t>
   </si>
   <si>
     <t xml:space="preserve">2.98626303672791</t>
@@ -848,22 +848,22 @@
     <t xml:space="preserve">3.05452013015747</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07158470153809</t>
+    <t xml:space="preserve">3.07158493995667</t>
   </si>
   <si>
     <t xml:space="preserve">3.13984251022339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11424565315247</t>
+    <t xml:space="preserve">3.11424589157104</t>
   </si>
   <si>
     <t xml:space="preserve">3.13131022453308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06305265426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16543865203857</t>
+    <t xml:space="preserve">3.06305241584778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16543889045715</t>
   </si>
   <si>
     <t xml:space="preserve">3.19956755638123</t>
@@ -875,37 +875,37 @@
     <t xml:space="preserve">3.2336962223053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2763569355011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24222850799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26782512664795</t>
+    <t xml:space="preserve">3.27635717391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24222826957703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26782488822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.31048607826233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3446147441864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32755017280579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28488922119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18250298500061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29342126846313</t>
+    <t xml:space="preserve">3.34461450576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32755041122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28488945960999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18250322341919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29342150688171</t>
   </si>
   <si>
     <t xml:space="preserve">3.33710074424744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32836508750916</t>
+    <t xml:space="preserve">3.32836484909058</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342174530029</t>
@@ -926,7 +926,7 @@
     <t xml:space="preserve">3.17111968994141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26721382141113</t>
+    <t xml:space="preserve">3.26721405982971</t>
   </si>
   <si>
     <t xml:space="preserve">3.36330842971802</t>
@@ -938,22 +938,22 @@
     <t xml:space="preserve">3.58170509338379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56423330307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59044098854065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50308275222778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51181840896606</t>
+    <t xml:space="preserve">3.56423354148865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59044122695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5030825138092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51181817054749</t>
   </si>
   <si>
     <t xml:space="preserve">3.54676151275635</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63412022590637</t>
+    <t xml:space="preserve">3.63412046432495</t>
   </si>
   <si>
     <t xml:space="preserve">3.62538480758667</t>
@@ -962,22 +962,22 @@
     <t xml:space="preserve">3.74768662452698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69527149200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66906380653381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60791277885437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55549788475037</t>
+    <t xml:space="preserve">3.69527125358582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66906356811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60791301727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55549764633179</t>
   </si>
   <si>
     <t xml:space="preserve">3.66032791137695</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65159201622009</t>
+    <t xml:space="preserve">3.65159177780151</t>
   </si>
   <si>
     <t xml:space="preserve">3.68653535842896</t>
@@ -995,25 +995,25 @@
     <t xml:space="preserve">3.53802585601807</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34583687782288</t>
+    <t xml:space="preserve">3.3458366394043</t>
   </si>
   <si>
     <t xml:space="preserve">3.38951635360718</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42445945739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45066714286804</t>
+    <t xml:space="preserve">3.42445969581604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45066738128662</t>
   </si>
   <si>
     <t xml:space="preserve">3.44193148612976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48561072349548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40698790550232</t>
+    <t xml:space="preserve">3.4856104850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4069881439209</t>
   </si>
   <si>
     <t xml:space="preserve">3.35457253456116</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">3.45940327644348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52928996086121</t>
+    <t xml:space="preserve">3.52928972244263</t>
   </si>
   <si>
     <t xml:space="preserve">3.46813893318176</t>
@@ -1031,13 +1031,13 @@
     <t xml:space="preserve">3.47687458992004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79136610031128</t>
+    <t xml:space="preserve">3.79136633872986</t>
   </si>
   <si>
     <t xml:space="preserve">3.7214789390564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87872457504272</t>
+    <t xml:space="preserve">3.8787248134613</t>
   </si>
   <si>
     <t xml:space="preserve">4.17574453353882</t>
@@ -1049,34 +1049,34 @@
     <t xml:space="preserve">4.35046148300171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1844801902771</t>
+    <t xml:space="preserve">4.18447971343994</t>
   </si>
   <si>
     <t xml:space="preserve">4.20195150375366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25436639785767</t>
+    <t xml:space="preserve">4.25436687469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493178367615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98355507850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94861173629761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93113970756531</t>
+    <t xml:space="preserve">3.90493202209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98355484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94861197471619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93114018440247</t>
   </si>
   <si>
     <t xml:space="preserve">4.08838510513306</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07091379165649</t>
+    <t xml:space="preserve">4.07091331481934</t>
   </si>
   <si>
     <t xml:space="preserve">4.1233286857605</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">4.00102663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00976228713989</t>
+    <t xml:space="preserve">4.00976276397705</t>
   </si>
   <si>
     <t xml:space="preserve">3.93987607955933</t>
@@ -1094,16 +1094,16 @@
     <t xml:space="preserve">4.0971212387085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21068716049194</t>
+    <t xml:space="preserve">4.2106876373291</t>
   </si>
   <si>
     <t xml:space="preserve">4.29804611206055</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28930997848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21942377090454</t>
+    <t xml:space="preserve">4.28931045532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21942329406738</t>
   </si>
   <si>
     <t xml:space="preserve">4.19321584701538</t>
@@ -1112,70 +1112,70 @@
     <t xml:space="preserve">4.1495361328125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16700839996338</t>
+    <t xml:space="preserve">4.16700792312622</t>
   </si>
   <si>
     <t xml:space="preserve">4.11459302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06217765808105</t>
+    <t xml:space="preserve">4.06217813491821</t>
   </si>
   <si>
     <t xml:space="preserve">3.78262996673584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80010151863098</t>
+    <t xml:space="preserve">3.80010175704956</t>
   </si>
   <si>
     <t xml:space="preserve">3.82630968093872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83504486083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84378123283386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77389430999756</t>
+    <t xml:space="preserve">3.83504509925842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84378099441528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77389454841614</t>
   </si>
   <si>
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734763145447</t>
+    <t xml:space="preserve">3.95734786987305</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.861252784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7651584148407</t>
+    <t xml:space="preserve">3.86125302314758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76515865325928</t>
   </si>
   <si>
     <t xml:space="preserve">3.8175733089447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64285635948181</t>
+    <t xml:space="preserve">3.64285612106323</t>
   </si>
   <si>
     <t xml:space="preserve">3.67779970169067</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7389509677887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85251712799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71274328231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92240357398987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61664843559265</t>
+    <t xml:space="preserve">3.73895072937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85251665115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71274304389954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92240381240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61664867401123</t>
   </si>
   <si>
     <t xml:space="preserve">3.39825224876404</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">2.97019457817078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95272278785706</t>
+    <t xml:space="preserve">2.95272302627563</t>
   </si>
   <si>
     <t xml:space="preserve">2.91777920722961</t>
@@ -1202,13 +1202,13 @@
     <t xml:space="preserve">3.37204432487488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38077998161316</t>
+    <t xml:space="preserve">3.38078022003174</t>
   </si>
   <si>
     <t xml:space="preserve">3.41572380065918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31962919235229</t>
+    <t xml:space="preserve">3.31962895393372</t>
   </si>
   <si>
     <t xml:space="preserve">3.27594995498657</t>
@@ -1743,6 +1743,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.3199999332428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27999997138977</t>
   </si>
 </sst>
 </file>
@@ -56083,7 +56086,7 @@
     </row>
     <row r="2078">
       <c r="A2078" s="1" t="n">
-        <v>45988.6911458333</v>
+        <v>45988.3333333333</v>
       </c>
       <c r="B2078" t="n">
         <v>22601</v>
@@ -56104,6 +56107,32 @@
         <v>570</v>
       </c>
       <c r="H2078" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2079">
+      <c r="A2079" s="1" t="n">
+        <v>45989.6911458333</v>
+      </c>
+      <c r="B2079" t="n">
+        <v>11244</v>
+      </c>
+      <c r="C2079" t="n">
+        <v>3.38000011444092</v>
+      </c>
+      <c r="D2079" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="E2079" t="n">
+        <v>3.38000011444092</v>
+      </c>
+      <c r="F2079" t="n">
+        <v>3.27999997138977</v>
+      </c>
+      <c r="G2079" t="s">
+        <v>577</v>
+      </c>
+      <c r="H2079" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02345752716064</t>
+    <t xml:space="preserve">3.02345728874207</t>
   </si>
   <si>
     <t xml:space="preserve">NDT.MI</t>
@@ -47,7 +47,7 @@
     <t xml:space="preserve">2.96519947052002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88901543617249</t>
+    <t xml:space="preserve">2.88901519775391</t>
   </si>
   <si>
     <t xml:space="preserve">2.98013734817505</t>
@@ -62,64 +62,64 @@
     <t xml:space="preserve">2.95773005485535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96221160888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9353232383728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91291666030884</t>
+    <t xml:space="preserve">2.9622118473053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93532347679138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91291618347168</t>
   </si>
   <si>
     <t xml:space="preserve">2.97864365577698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98611211776733</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03540825843811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05632138252258</t>
+    <t xml:space="preserve">2.98611259460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03540778160095</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05632162094116</t>
   </si>
   <si>
     <t xml:space="preserve">3.0593090057373</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05034613609314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98760604858398</t>
+    <t xml:space="preserve">3.05034589767456</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98760652542114</t>
   </si>
   <si>
     <t xml:space="preserve">2.95026135444641</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01598858833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01001358032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02495145797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0174822807312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03092694282532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99955654144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04437112808228</t>
+    <t xml:space="preserve">3.01598882675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01001334190369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02495169639587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01748204231262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03092670440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99955677986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0443708896637</t>
   </si>
   <si>
     <t xml:space="preserve">2.95922374725342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00254464149475</t>
+    <t xml:space="preserve">3.00254440307617</t>
   </si>
   <si>
     <t xml:space="preserve">2.92785429954529</t>
@@ -128,43 +128,43 @@
     <t xml:space="preserve">2.90843486785889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91889119148254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9159038066864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92038512229919</t>
+    <t xml:space="preserve">2.89648461341858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91889142990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91590356826782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92038536071777</t>
   </si>
   <si>
     <t xml:space="preserve">2.90544724464417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9099280834198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92337274551392</t>
+    <t xml:space="preserve">2.90992879867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9233729839325</t>
   </si>
   <si>
     <t xml:space="preserve">2.8382260799408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86063313484192</t>
+    <t xml:space="preserve">2.86063289642334</t>
   </si>
   <si>
     <t xml:space="preserve">2.82627558708191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77996730804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84569501876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86810183525085</t>
+    <t xml:space="preserve">2.77996778488159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84569478034973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86810207366943</t>
   </si>
   <si>
     <t xml:space="preserve">2.88303995132446</t>
@@ -173,7 +173,7 @@
     <t xml:space="preserve">2.79639935493469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87557077407837</t>
+    <t xml:space="preserve">2.87557101249695</t>
   </si>
   <si>
     <t xml:space="preserve">2.89797806739807</t>
@@ -185,49 +185,49 @@
     <t xml:space="preserve">2.74262261390686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8217945098877</t>
+    <t xml:space="preserve">2.82179403305054</t>
   </si>
   <si>
     <t xml:space="preserve">2.75009155273438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76353645324707</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77847385406494</t>
+    <t xml:space="preserve">2.76353597640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77847409248352</t>
   </si>
   <si>
     <t xml:space="preserve">2.78594279289246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79341197013855</t>
+    <t xml:space="preserve">2.79341220855713</t>
   </si>
   <si>
     <t xml:space="preserve">2.69631481170654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6515007019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6216242313385</t>
+    <t xml:space="preserve">2.65150046348572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62162470817566</t>
   </si>
   <si>
     <t xml:space="preserve">2.53946542739868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5693416595459</t>
+    <t xml:space="preserve">2.56934142112732</t>
   </si>
   <si>
     <t xml:space="preserve">2.61415553092957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65896964073181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68884515762329</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70378351211548</t>
+    <t xml:space="preserve">2.65896987915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68884563446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70378375053406</t>
   </si>
   <si>
     <t xml:space="preserve">2.77100491523743</t>
@@ -236,22 +236,22 @@
     <t xml:space="preserve">2.81581902503967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73366022109985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66643857955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68137669563293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74112892150879</t>
+    <t xml:space="preserve">2.73365998268127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66643834114075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68137645721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74112868309021</t>
   </si>
   <si>
     <t xml:space="preserve">2.72619080543518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83075714111328</t>
+    <t xml:space="preserve">2.8307569026947</t>
   </si>
   <si>
     <t xml:space="preserve">2.893150806427</t>
@@ -266,64 +266,64 @@
     <t xml:space="preserve">2.93203711509705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87759637832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83093214035034</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81537747383118</t>
+    <t xml:space="preserve">2.87759613990784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83093237876892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81537771224976</t>
   </si>
   <si>
     <t xml:space="preserve">2.84648704528809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79982328414917</t>
+    <t xml:space="preserve">2.79982304573059</t>
   </si>
   <si>
     <t xml:space="preserve">2.73760485649109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76093673706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80760049819946</t>
+    <t xml:space="preserve">2.76093649864197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80760073661804</t>
   </si>
   <si>
     <t xml:space="preserve">3.00980973243713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9553689956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90870523452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88537311553955</t>
+    <t xml:space="preserve">2.95536875724792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90870547294617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88537335395813</t>
   </si>
   <si>
     <t xml:space="preserve">2.82315516471863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86204171180725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00203227996826</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91648244857788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85426425933838</t>
+    <t xml:space="preserve">2.86204147338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00203251838684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91648268699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8542640209198</t>
   </si>
   <si>
     <t xml:space="preserve">2.7298276424408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68316411972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72205018997192</t>
+    <t xml:space="preserve">2.68316388130188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7220504283905</t>
   </si>
   <si>
     <t xml:space="preserve">2.75315952301025</t>
@@ -338,16 +338,16 @@
     <t xml:space="preserve">2.99425530433655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97870087623596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86981892585754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94759202003479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98647785186768</t>
+    <t xml:space="preserve">2.97870063781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86981868743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94759154319763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98647809028625</t>
   </si>
   <si>
     <t xml:space="preserve">2.63650035858154</t>
@@ -356,7 +356,7 @@
     <t xml:space="preserve">2.55094981193542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51984119415283</t>
+    <t xml:space="preserve">2.51984095573425</t>
   </si>
   <si>
     <t xml:space="preserve">2.41095876693726</t>
@@ -365,37 +365,37 @@
     <t xml:space="preserve">2.34096336364746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34874081611633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36429524421692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25541353225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24763607978821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3254086971283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23208117485046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18541765213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27874517440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26319074630737</t>
+    <t xml:space="preserve">2.34874057769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36429500579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2554132938385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24763584136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32540893554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23208141326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18541741371155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2787446975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26319026947021</t>
   </si>
   <si>
     <t xml:space="preserve">2.21652674674988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06875848770142</t>
+    <t xml:space="preserve">2.06875824928284</t>
   </si>
   <si>
     <t xml:space="preserve">2.1465311050415</t>
@@ -404,10 +404,10 @@
     <t xml:space="preserve">2.10764455795288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1543083190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17764019966125</t>
+    <t xml:space="preserve">2.15430855751038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17764043807983</t>
   </si>
   <si>
     <t xml:space="preserve">2.22430372238159</t>
@@ -416,19 +416,19 @@
     <t xml:space="preserve">2.35651779174805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48873162269592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52761816978455</t>
+    <t xml:space="preserve">2.4887318611145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52761793136597</t>
   </si>
   <si>
     <t xml:space="preserve">2.43429088592529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44206786155701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55872702598572</t>
+    <t xml:space="preserve">2.44206809997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5587272644043</t>
   </si>
   <si>
     <t xml:space="preserve">2.44984555244446</t>
@@ -443,19 +443,19 @@
     <t xml:space="preserve">2.29429960250854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37984991073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71427297592163</t>
+    <t xml:space="preserve">2.3798496723175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71427321434021</t>
   </si>
   <si>
     <t xml:space="preserve">2.58205890655518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62872290611267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65983247756958</t>
+    <t xml:space="preserve">2.62872338294983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65983200073242</t>
   </si>
   <si>
     <t xml:space="preserve">2.57428193092346</t>
@@ -467,37 +467,37 @@
     <t xml:space="preserve">2.64427757263184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69094109535217</t>
+    <t xml:space="preserve">2.69094133377075</t>
   </si>
   <si>
     <t xml:space="preserve">2.76871418952942</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90092778205872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96314644813538</t>
+    <t xml:space="preserve">2.90092802047729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96314597129822</t>
   </si>
   <si>
     <t xml:space="preserve">2.92425990104675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97092342376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01758718490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04869675636292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03314208984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0642511844635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07980561256409</t>
+    <t xml:space="preserve">2.97092366218567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01758742332458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04869651794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03314185142517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06425094604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07980537414551</t>
   </si>
   <si>
     <t xml:space="preserve">3.06049919128418</t>
@@ -506,34 +506,34 @@
     <t xml:space="preserve">3.02811288833618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01191973686218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10907816886902</t>
+    <t xml:space="preserve">3.01191997528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1090784072876</t>
   </si>
   <si>
     <t xml:space="preserve">3.0928852558136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12527108192444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0766921043396</t>
+    <t xml:space="preserve">3.1252715587616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07669234275818</t>
   </si>
   <si>
     <t xml:space="preserve">2.99572682380676</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30339574813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41674709320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35197520256042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33578205108643</t>
+    <t xml:space="preserve">3.30339550971985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41674733161926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35197496414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33578181266785</t>
   </si>
   <si>
     <t xml:space="preserve">3.36816811561584</t>
@@ -542,22 +542,22 @@
     <t xml:space="preserve">3.23862314224243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31958866119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27100944519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28720259666443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22243022918701</t>
+    <t xml:space="preserve">3.31958889961243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27100920677185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28720235824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22242999076843</t>
   </si>
   <si>
     <t xml:space="preserve">3.17385101318359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20623731613159</t>
+    <t xml:space="preserve">3.20623707771301</t>
   </si>
   <si>
     <t xml:space="preserve">3.1414647102356</t>
@@ -575,31 +575,31 @@
     <t xml:space="preserve">3.25481629371643</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19004416465759</t>
+    <t xml:space="preserve">3.19004392623901</t>
   </si>
   <si>
     <t xml:space="preserve">2.96334052085876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97953367233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80140900611877</t>
+    <t xml:space="preserve">2.97953343391418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80140924453735</t>
   </si>
   <si>
     <t xml:space="preserve">2.88237476348877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86618161201477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84998846054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78521633148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75282979011536</t>
+    <t xml:space="preserve">2.86618185043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84998822212219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78521609306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75283002853394</t>
   </si>
   <si>
     <t xml:space="preserve">2.72044348716736</t>
@@ -608,13 +608,13 @@
     <t xml:space="preserve">2.83379530906677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76902341842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73663663864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81760239601135</t>
+    <t xml:space="preserve">2.76902294158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73663687705994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81760215759277</t>
   </si>
   <si>
     <t xml:space="preserve">2.89856791496277</t>
@@ -626,19 +626,19 @@
     <t xml:space="preserve">2.63947796821594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67186427116394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62328505516052</t>
+    <t xml:space="preserve">2.67186403274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62328481674194</t>
   </si>
   <si>
     <t xml:space="preserve">2.68805718421936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70425009727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60709190368652</t>
+    <t xml:space="preserve">2.70425057411194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60709166526794</t>
   </si>
   <si>
     <t xml:space="preserve">2.59089851379395</t>
@@ -647,16 +647,16 @@
     <t xml:space="preserve">2.42896747589111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54231905937195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46135377883911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31561541557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2994225025177</t>
+    <t xml:space="preserve">2.54231929779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46135354042053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3156156539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29942274093628</t>
   </si>
   <si>
     <t xml:space="preserve">2.35488176345825</t>
@@ -668,16 +668,16 @@
     <t xml:space="preserve">2.28662443161011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1330451965332</t>
+    <t xml:space="preserve">2.13304495811462</t>
   </si>
   <si>
     <t xml:space="preserve">2.08185195922852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0647873878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03065896034241</t>
+    <t xml:space="preserve">2.06478762626648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03065872192383</t>
   </si>
   <si>
     <t xml:space="preserve">2.1671736240387</t>
@@ -689,10 +689,10 @@
     <t xml:space="preserve">2.26955986022949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2183666229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32075333595276</t>
+    <t xml:space="preserve">2.21836686134338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32075309753418</t>
   </si>
   <si>
     <t xml:space="preserve">2.55965399742126</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">2.54258990287781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45726799964905</t>
+    <t xml:space="preserve">2.45726823806763</t>
   </si>
   <si>
     <t xml:space="preserve">2.57671856880188</t>
@@ -716,10 +716,10 @@
     <t xml:space="preserve">2.64497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59378290176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69616913795471</t>
+    <t xml:space="preserve">2.59378266334534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69616889953613</t>
   </si>
   <si>
     <t xml:space="preserve">2.71323323249817</t>
@@ -728,31 +728,31 @@
     <t xml:space="preserve">2.44020342826843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4231390953064</t>
+    <t xml:space="preserve">2.42313933372498</t>
   </si>
   <si>
     <t xml:space="preserve">2.47433233261108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15010952949524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33781743049622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30368876457214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25249552726746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23543095588684</t>
+    <t xml:space="preserve">2.15010929107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33781719207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30368852615356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25249576568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23543119430542</t>
   </si>
   <si>
     <t xml:space="preserve">2.37194609642029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38901042938232</t>
+    <t xml:space="preserve">2.3890106678009</t>
   </si>
   <si>
     <t xml:space="preserve">2.20130252838135</t>
@@ -764,7 +764,7 @@
     <t xml:space="preserve">2.01359438896179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04772305488586</t>
+    <t xml:space="preserve">2.04772329330444</t>
   </si>
   <si>
     <t xml:space="preserve">2.11598062515259</t>
@@ -773,28 +773,28 @@
     <t xml:space="preserve">1.91120851039886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87707960605621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84295105934143</t>
+    <t xml:space="preserve">1.87707984447479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84295094013214</t>
   </si>
   <si>
     <t xml:space="preserve">1.97946584224701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86001539230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94533693790436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96240150928497</t>
+    <t xml:space="preserve">1.86001515388489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94533717632294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96240127086639</t>
   </si>
   <si>
     <t xml:space="preserve">1.99652993679047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81561946868896</t>
+    <t xml:space="preserve">2.81561923027039</t>
   </si>
   <si>
     <t xml:space="preserve">2.90094137191772</t>
@@ -803,13 +803,13 @@
     <t xml:space="preserve">2.88387703895569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76442646980286</t>
+    <t xml:space="preserve">2.76442623138428</t>
   </si>
   <si>
     <t xml:space="preserve">2.73029756546021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67910432815552</t>
+    <t xml:space="preserve">2.6791045665741</t>
   </si>
   <si>
     <t xml:space="preserve">2.74736189842224</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">2.83268356323242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86681222915649</t>
+    <t xml:space="preserve">2.86681246757507</t>
   </si>
   <si>
     <t xml:space="preserve">2.79855489730835</t>
@@ -830,13 +830,13 @@
     <t xml:space="preserve">2.9350700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96919870376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02039170265198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00332736968994</t>
+    <t xml:space="preserve">2.96919846534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02039194107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00332713127136</t>
   </si>
   <si>
     <t xml:space="preserve">3.03745603561401</t>
@@ -845,25 +845,25 @@
     <t xml:space="preserve">2.98626303672791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05452013015747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07158493995667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13984251022339</t>
+    <t xml:space="preserve">3.05452060699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07158470153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13984227180481</t>
   </si>
   <si>
     <t xml:space="preserve">3.11424589157104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13131022453308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06305241584778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16543889045715</t>
+    <t xml:space="preserve">3.1313099861145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06305265426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16543865203857</t>
   </si>
   <si>
     <t xml:space="preserve">3.19956755638123</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">3.27635717391968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24222826957703</t>
+    <t xml:space="preserve">3.24222850799561</t>
   </si>
   <si>
     <t xml:space="preserve">3.26782488822937</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">3.31048607826233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34461450576782</t>
+    <t xml:space="preserve">3.3446147441864</t>
   </si>
   <si>
     <t xml:space="preserve">3.32755041122437</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">3.28488945960999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18250322341919</t>
+    <t xml:space="preserve">3.18250346183777</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342150688171</t>
@@ -56112,7 +56112,7 @@
     </row>
     <row r="2079">
       <c r="A2079" s="1" t="n">
-        <v>45989.6911458333</v>
+        <v>45989.3333333333</v>
       </c>
       <c r="B2079" t="n">
         <v>11244</v>
@@ -56133,6 +56133,32 @@
         <v>577</v>
       </c>
       <c r="H2079" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2080">
+      <c r="A2080" s="1" t="n">
+        <v>45992.6652893518</v>
+      </c>
+      <c r="B2080" t="n">
+        <v>13652</v>
+      </c>
+      <c r="C2080" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="D2080" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="E2080" t="n">
+        <v>3.27999997138977</v>
+      </c>
+      <c r="F2080" t="n">
+        <v>3.27999997138977</v>
+      </c>
+      <c r="G2080" t="s">
+        <v>577</v>
+      </c>
+      <c r="H2080" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -44,25 +44,25 @@
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519899368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88901543617249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98013710975647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97266817092896</t>
+    <t xml:space="preserve">2.96519923210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88901567459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98013734817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97266840934753</t>
   </si>
   <si>
     <t xml:space="preserve">2.94578003883362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95773005485535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9622118473053</t>
+    <t xml:space="preserve">2.95773029327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96221160888672</t>
   </si>
   <si>
     <t xml:space="preserve">2.9353232383728</t>
@@ -71,7 +71,7 @@
     <t xml:space="preserve">2.91291642189026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97864365577698</t>
+    <t xml:space="preserve">2.9786434173584</t>
   </si>
   <si>
     <t xml:space="preserve">2.98611235618591</t>
@@ -80,10 +80,10 @@
     <t xml:space="preserve">3.03540825843811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05632138252258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0593090057373</t>
+    <t xml:space="preserve">3.056321144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05930924415588</t>
   </si>
   <si>
     <t xml:space="preserve">3.05034637451172</t>
@@ -95,22 +95,22 @@
     <t xml:space="preserve">2.95026111602783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01598882675171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01001334190369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02495193481445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01748251914978</t>
+    <t xml:space="preserve">3.01598906517029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01001358032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02495169639587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0174822807312</t>
   </si>
   <si>
     <t xml:space="preserve">3.03092670440674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99955701828003</t>
+    <t xml:space="preserve">2.99955654144287</t>
   </si>
   <si>
     <t xml:space="preserve">3.04437112808228</t>
@@ -119,7 +119,7 @@
     <t xml:space="preserve">2.959223985672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00254416465759</t>
+    <t xml:space="preserve">3.00254440307617</t>
   </si>
   <si>
     <t xml:space="preserve">2.92785429954529</t>
@@ -131,16 +131,16 @@
     <t xml:space="preserve">2.896484375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91889142990112</t>
+    <t xml:space="preserve">2.91889095306396</t>
   </si>
   <si>
     <t xml:space="preserve">2.91590404510498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92038536071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90544724464417</t>
+    <t xml:space="preserve">2.92038559913635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90544748306274</t>
   </si>
   <si>
     <t xml:space="preserve">2.90992856025696</t>
@@ -149,43 +149,43 @@
     <t xml:space="preserve">2.92337274551392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83822584152222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86063313484192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82627534866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77996730804443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84569525718689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86810183525085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88304018974304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79639911651611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87557077407837</t>
+    <t xml:space="preserve">2.8382260799408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86063289642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82627558708191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77996754646301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84569501876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86810207366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88303995132446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79639959335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87557101249695</t>
   </si>
   <si>
     <t xml:space="preserve">2.89797830581665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80088090896606</t>
+    <t xml:space="preserve">2.80088114738464</t>
   </si>
   <si>
     <t xml:space="preserve">2.74262261390686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82179403305054</t>
+    <t xml:space="preserve">2.82179427146912</t>
   </si>
   <si>
     <t xml:space="preserve">2.75009179115295</t>
@@ -197,43 +197,43 @@
     <t xml:space="preserve">2.77847409248352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78594279289246</t>
+    <t xml:space="preserve">2.78594303131104</t>
   </si>
   <si>
     <t xml:space="preserve">2.79341197013855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69631457328796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65150046348572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6216242313385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53946542739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5693416595459</t>
+    <t xml:space="preserve">2.69631481170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6515007019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62162470817566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53946566581726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56934142112732</t>
   </si>
   <si>
     <t xml:space="preserve">2.61415553092957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65896940231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68884539604187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70378351211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77100491523743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81581926345825</t>
+    <t xml:space="preserve">2.65896964073181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68884563446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70378375053406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77100515365601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81581878662109</t>
   </si>
   <si>
     <t xml:space="preserve">2.7336597442627</t>
@@ -242,7 +242,7 @@
     <t xml:space="preserve">2.66643881797791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68137669563293</t>
+    <t xml:space="preserve">2.68137645721436</t>
   </si>
   <si>
     <t xml:space="preserve">2.74112868309021</t>
@@ -260,19 +260,19 @@
     <t xml:space="preserve">2.69871854782104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83870983123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93203735351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87759613990784</t>
+    <t xml:space="preserve">2.83870959281921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93203687667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87759637832642</t>
   </si>
   <si>
     <t xml:space="preserve">2.83093237876892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81537747383118</t>
+    <t xml:space="preserve">2.81537795066833</t>
   </si>
   <si>
     <t xml:space="preserve">2.84648680686951</t>
@@ -290,37 +290,37 @@
     <t xml:space="preserve">2.80760049819946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00980973243713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95536875724792</t>
+    <t xml:space="preserve">3.00980997085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9553689956665</t>
   </si>
   <si>
     <t xml:space="preserve">2.90870523452759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88537335395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82315540313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86204147338867</t>
+    <t xml:space="preserve">2.88537383079529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82315492630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86204171180725</t>
   </si>
   <si>
     <t xml:space="preserve">3.00203251838684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91648268699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8542640209198</t>
+    <t xml:space="preserve">2.91648244857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85426425933838</t>
   </si>
   <si>
     <t xml:space="preserve">2.7298276424408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68316388130188</t>
+    <t xml:space="preserve">2.68316411972046</t>
   </si>
   <si>
     <t xml:space="preserve">2.7220504283905</t>
@@ -329,7 +329,7 @@
     <t xml:space="preserve">2.75315952301025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70649600028992</t>
+    <t xml:space="preserve">2.70649576187134</t>
   </si>
   <si>
     <t xml:space="preserve">2.93981432914734</t>
@@ -338,10 +338,10 @@
     <t xml:space="preserve">2.99425530433655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97870087623596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86981868743896</t>
+    <t xml:space="preserve">2.9787003993988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86981892585754</t>
   </si>
   <si>
     <t xml:space="preserve">2.94759178161621</t>
@@ -350,7 +350,7 @@
     <t xml:space="preserve">2.98647785186768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63650012016296</t>
+    <t xml:space="preserve">2.63650059700012</t>
   </si>
   <si>
     <t xml:space="preserve">2.550950050354</t>
@@ -362,25 +362,25 @@
     <t xml:space="preserve">2.41095876693726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34096336364746</t>
+    <t xml:space="preserve">2.34096312522888</t>
   </si>
   <si>
     <t xml:space="preserve">2.34874057769775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36429500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2554132938385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24763607978821</t>
+    <t xml:space="preserve">2.36429524421692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25541353225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24763631820679</t>
   </si>
   <si>
     <t xml:space="preserve">2.3254086971283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23208117485046</t>
+    <t xml:space="preserve">2.23208141326904</t>
   </si>
   <si>
     <t xml:space="preserve">2.18541741371155</t>
@@ -395,67 +395,67 @@
     <t xml:space="preserve">2.21652674674988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06875801086426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14653134346008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10764455795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15430855751038</t>
+    <t xml:space="preserve">2.06875824928284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14653086662292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10764479637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15430808067322</t>
   </si>
   <si>
     <t xml:space="preserve">2.17764019966125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22430372238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35651755332947</t>
+    <t xml:space="preserve">2.22430396080017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35651779174805</t>
   </si>
   <si>
     <t xml:space="preserve">2.4887318611145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52761793136597</t>
+    <t xml:space="preserve">2.52761816978455</t>
   </si>
   <si>
     <t xml:space="preserve">2.43429088592529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44206809997559</t>
+    <t xml:space="preserve">2.44206786155701</t>
   </si>
   <si>
     <t xml:space="preserve">2.5587272644043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44984555244446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37207245826721</t>
+    <t xml:space="preserve">2.44984531402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37207269668579</t>
   </si>
   <si>
     <t xml:space="preserve">2.33318591117859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29429960250854</t>
+    <t xml:space="preserve">2.29429936408997</t>
   </si>
   <si>
     <t xml:space="preserve">2.37984991073608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71427321434021</t>
+    <t xml:space="preserve">2.71427297592163</t>
   </si>
   <si>
     <t xml:space="preserve">2.58205890655518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62872266769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65983247756958</t>
+    <t xml:space="preserve">2.62872314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65983200073242</t>
   </si>
   <si>
     <t xml:space="preserve">2.57428193092346</t>
@@ -467,40 +467,40 @@
     <t xml:space="preserve">2.64427757263184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69094133377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76871395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90092778205872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9631462097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92426013946533</t>
+    <t xml:space="preserve">2.69094109535217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76871418952942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90092802047729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96314597129822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92425966262817</t>
   </si>
   <si>
     <t xml:space="preserve">2.97092342376709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01758742332458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04869675636292</t>
+    <t xml:space="preserve">3.01758766174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04869651794434</t>
   </si>
   <si>
     <t xml:space="preserve">3.03314208984375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06425094604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07980537414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06049919128418</t>
+    <t xml:space="preserve">3.0642511844635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07980561256409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0604989528656</t>
   </si>
   <si>
     <t xml:space="preserve">3.02811288833618</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">3.0766921043396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99572658538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30339574813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41674709320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.351975440979</t>
+    <t xml:space="preserve">2.99572682380676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30339598655701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41674733161926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35197520256042</t>
   </si>
   <si>
     <t xml:space="preserve">3.33578205108643</t>
@@ -557,22 +557,22 @@
     <t xml:space="preserve">3.17385101318359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20623731613159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1414647102356</t>
+    <t xml:space="preserve">3.20623707771301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14146494865417</t>
   </si>
   <si>
     <t xml:space="preserve">3.40055418014526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49771332740784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38436126708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25481629371643</t>
+    <t xml:space="preserve">3.49771356582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38436102867126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25481653213501</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004416465759</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">2.97953367233276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80140924453735</t>
+    <t xml:space="preserve">2.80140900611877</t>
   </si>
   <si>
     <t xml:space="preserve">2.88237476348877</t>
@@ -596,10 +596,10 @@
     <t xml:space="preserve">2.84998846054077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78521633148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75282979011536</t>
+    <t xml:space="preserve">2.78521609306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75283002853394</t>
   </si>
   <si>
     <t xml:space="preserve">2.72044348716736</t>
@@ -608,16 +608,16 @@
     <t xml:space="preserve">2.83379554748535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76902341842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73663663864136</t>
+    <t xml:space="preserve">2.76902294158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73663687705994</t>
   </si>
   <si>
     <t xml:space="preserve">2.81760239601135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89856767654419</t>
+    <t xml:space="preserve">2.89856791496277</t>
   </si>
   <si>
     <t xml:space="preserve">2.91476082801819</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">2.63947796821594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67186403274536</t>
+    <t xml:space="preserve">2.67186427116394</t>
   </si>
   <si>
     <t xml:space="preserve">2.62328505516052</t>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">2.42896747589111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54231929779053</t>
+    <t xml:space="preserve">2.54231905937195</t>
   </si>
   <si>
     <t xml:space="preserve">2.46135377883911</t>
@@ -56161,7 +56161,7 @@
     </row>
     <row r="2081">
       <c r="A2081" s="1" t="n">
-        <v>45993.6717361111</v>
+        <v>45993.3333333333</v>
       </c>
       <c r="B2081" t="n">
         <v>6702</v>
@@ -56182,6 +56182,32 @@
         <v>576</v>
       </c>
       <c r="H2081" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2082">
+      <c r="A2082" s="1" t="n">
+        <v>45994.6736921296</v>
+      </c>
+      <c r="B2082" t="n">
+        <v>10701</v>
+      </c>
+      <c r="C2082" t="n">
+        <v>3.3199999332428</v>
+      </c>
+      <c r="D2082" t="n">
+        <v>3.27999997138977</v>
+      </c>
+      <c r="E2082" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="F2082" t="n">
+        <v>3.27999997138977</v>
+      </c>
+      <c r="G2082" t="s">
+        <v>576</v>
+      </c>
+      <c r="H2082" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -38,37 +38,37 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02345776557922</t>
+    <t xml:space="preserve">3.02345752716064</t>
   </si>
   <si>
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519923210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88901567459106</t>
+    <t xml:space="preserve">2.96519947052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88901519775391</t>
   </si>
   <si>
     <t xml:space="preserve">2.98013734817505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97266840934753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94578003883362</t>
+    <t xml:space="preserve">2.97266817092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94577980041504</t>
   </si>
   <si>
     <t xml:space="preserve">2.95773029327393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96221160888672</t>
+    <t xml:space="preserve">2.96221137046814</t>
   </si>
   <si>
     <t xml:space="preserve">2.9353232383728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91291642189026</t>
+    <t xml:space="preserve">2.91291618347168</t>
   </si>
   <si>
     <t xml:space="preserve">2.9786434173584</t>
@@ -77,31 +77,31 @@
     <t xml:space="preserve">2.98611235618591</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03540825843811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.056321144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05930924415588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05034637451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98760628700256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95026111602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01598906517029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01001358032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02495169639587</t>
+    <t xml:space="preserve">3.03540802001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05632138252258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0593090057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05034613609314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98760604858398</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95026135444641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01598858833313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01001334190369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02495145797729</t>
   </si>
   <si>
     <t xml:space="preserve">3.0174822807312</t>
@@ -110,16 +110,16 @@
     <t xml:space="preserve">3.03092670440674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99955654144287</t>
+    <t xml:space="preserve">2.99955677986145</t>
   </si>
   <si>
     <t xml:space="preserve">3.04437112808228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.959223985672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00254440307617</t>
+    <t xml:space="preserve">2.95922422409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00254416465759</t>
   </si>
   <si>
     <t xml:space="preserve">2.92785429954529</t>
@@ -128,49 +128,49 @@
     <t xml:space="preserve">2.90843510627747</t>
   </si>
   <si>
-    <t xml:space="preserve">2.896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91889095306396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91590404510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92038559913635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90544748306274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90992856025696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92337274551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8382260799408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86063289642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82627558708191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77996754646301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84569501876831</t>
+    <t xml:space="preserve">2.89648461341858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91889119148254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9159038066864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92038512229919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90544724464417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90992879867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9233729839325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83822631835938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86063313484192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82627534866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77996778488159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84569525718689</t>
   </si>
   <si>
     <t xml:space="preserve">2.86810207366943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88303995132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79639959335327</t>
+    <t xml:space="preserve">2.88304018974304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79639935493469</t>
   </si>
   <si>
     <t xml:space="preserve">2.87557101249695</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">2.89797830581665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80088114738464</t>
+    <t xml:space="preserve">2.80088067054749</t>
   </si>
   <si>
     <t xml:space="preserve">2.74262261390686</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">2.82179427146912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75009179115295</t>
+    <t xml:space="preserve">2.75009155273438</t>
   </si>
   <si>
     <t xml:space="preserve">2.76353597640991</t>
@@ -197,31 +197,31 @@
     <t xml:space="preserve">2.77847409248352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78594303131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79341197013855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69631481170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6515007019043</t>
+    <t xml:space="preserve">2.78594279289246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79341173171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69631457328796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65150046348572</t>
   </si>
   <si>
     <t xml:space="preserve">2.62162470817566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53946566581726</t>
+    <t xml:space="preserve">2.5394651889801</t>
   </si>
   <si>
     <t xml:space="preserve">2.56934142112732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61415553092957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65896964073181</t>
+    <t xml:space="preserve">2.61415576934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65896940231323</t>
   </si>
   <si>
     <t xml:space="preserve">2.68884563446045</t>
@@ -230,19 +230,19 @@
     <t xml:space="preserve">2.70378375053406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77100515365601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81581878662109</t>
+    <t xml:space="preserve">2.77100467681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81581902503967</t>
   </si>
   <si>
     <t xml:space="preserve">2.7336597442627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66643881797791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68137645721436</t>
+    <t xml:space="preserve">2.66643857955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68137669563293</t>
   </si>
   <si>
     <t xml:space="preserve">2.74112868309021</t>
@@ -254,25 +254,25 @@
     <t xml:space="preserve">2.83075714111328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.893150806427</t>
+    <t xml:space="preserve">2.89315056800842</t>
   </si>
   <si>
     <t xml:space="preserve">2.69871854782104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83870959281921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93203687667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87759637832642</t>
+    <t xml:space="preserve">2.83870983123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93203711509705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87759613990784</t>
   </si>
   <si>
     <t xml:space="preserve">2.83093237876892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81537795066833</t>
+    <t xml:space="preserve">2.81537771224976</t>
   </si>
   <si>
     <t xml:space="preserve">2.84648680686951</t>
@@ -293,22 +293,22 @@
     <t xml:space="preserve">3.00980997085571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9553689956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90870523452759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88537383079529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82315492630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86204171180725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00203251838684</t>
+    <t xml:space="preserve">2.95536875724792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90870499610901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88537335395813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82315540313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86204147338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00203275680542</t>
   </si>
   <si>
     <t xml:space="preserve">2.91648244857788</t>
@@ -320,16 +320,16 @@
     <t xml:space="preserve">2.7298276424408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68316411972046</t>
+    <t xml:space="preserve">2.68316388130188</t>
   </si>
   <si>
     <t xml:space="preserve">2.7220504283905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75315952301025</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70649576187134</t>
+    <t xml:space="preserve">2.75315928459167</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70649600028992</t>
   </si>
   <si>
     <t xml:space="preserve">2.93981432914734</t>
@@ -338,49 +338,49 @@
     <t xml:space="preserve">2.99425530433655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9787003993988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86981892585754</t>
+    <t xml:space="preserve">2.97870063781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86981868743896</t>
   </si>
   <si>
     <t xml:space="preserve">2.94759178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98647785186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63650059700012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.550950050354</t>
+    <t xml:space="preserve">2.98647809028625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63650035858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55094981193542</t>
   </si>
   <si>
     <t xml:space="preserve">2.51984095573425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41095876693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34096312522888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34874057769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36429524421692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25541353225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24763631820679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3254086971283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23208141326904</t>
+    <t xml:space="preserve">2.41095924377441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34096336364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34874081611633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36429500579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2554132938385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24763584136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32540893554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23208117485046</t>
   </si>
   <si>
     <t xml:space="preserve">2.18541741371155</t>
@@ -389,43 +389,43 @@
     <t xml:space="preserve">2.27874493598938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26319050788879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21652674674988</t>
+    <t xml:space="preserve">2.26319026947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2165265083313</t>
   </si>
   <si>
     <t xml:space="preserve">2.06875824928284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14653086662292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10764479637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15430808067322</t>
+    <t xml:space="preserve">2.14653134346008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10764455795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15430879592896</t>
   </si>
   <si>
     <t xml:space="preserve">2.17764019966125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22430396080017</t>
+    <t xml:space="preserve">2.22430419921875</t>
   </si>
   <si>
     <t xml:space="preserve">2.35651779174805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4887318611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52761816978455</t>
+    <t xml:space="preserve">2.48873162269592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52761840820312</t>
   </si>
   <si>
     <t xml:space="preserve">2.43429088592529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44206786155701</t>
+    <t xml:space="preserve">2.44206809997559</t>
   </si>
   <si>
     <t xml:space="preserve">2.5587272644043</t>
@@ -434,76 +434,76 @@
     <t xml:space="preserve">2.44984531402588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37207269668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33318591117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29429936408997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37984991073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71427297592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58205890655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62872314453125</t>
+    <t xml:space="preserve">2.37207221984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33318614959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29429960250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3798496723175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71427321434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58205914497375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62872290611267</t>
   </si>
   <si>
     <t xml:space="preserve">2.65983200073242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57428193092346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67538666725159</t>
+    <t xml:space="preserve">2.57428169250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67538642883301</t>
   </si>
   <si>
     <t xml:space="preserve">2.64427757263184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69094109535217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76871418952942</t>
+    <t xml:space="preserve">2.69094133377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76871395111084</t>
   </si>
   <si>
     <t xml:space="preserve">2.90092802047729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96314597129822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92425966262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97092342376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01758766174316</t>
+    <t xml:space="preserve">2.96314644813538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92425990104675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97092318534851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01758742332458</t>
   </si>
   <si>
     <t xml:space="preserve">3.04869651794434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03314208984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0642511844635</t>
+    <t xml:space="preserve">3.03314161300659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06425094604492</t>
   </si>
   <si>
     <t xml:space="preserve">3.07980561256409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0604989528656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02811288833618</t>
+    <t xml:space="preserve">3.06049919128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0281126499176</t>
   </si>
   <si>
     <t xml:space="preserve">3.01191973686218</t>
@@ -512,37 +512,37 @@
     <t xml:space="preserve">3.10907816886902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0928852558136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12527132034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0766921043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99572682380676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30339598655701</t>
+    <t xml:space="preserve">3.09288501739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1252715587616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07669234275818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99572658538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30339574813843</t>
   </si>
   <si>
     <t xml:space="preserve">3.41674733161926</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35197520256042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33578205108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36816811561584</t>
+    <t xml:space="preserve">3.35197496414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33578157424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36816787719727</t>
   </si>
   <si>
     <t xml:space="preserve">3.23862314224243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31958889961243</t>
+    <t xml:space="preserve">3.31958913803101</t>
   </si>
   <si>
     <t xml:space="preserve">3.27100944519043</t>
@@ -551,7 +551,7 @@
     <t xml:space="preserve">3.28720259666443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22243022918701</t>
+    <t xml:space="preserve">3.22242999076843</t>
   </si>
   <si>
     <t xml:space="preserve">3.17385101318359</t>
@@ -560,34 +560,34 @@
     <t xml:space="preserve">3.20623707771301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14146494865417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40055418014526</t>
+    <t xml:space="preserve">3.1414647102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40055441856384</t>
   </si>
   <si>
     <t xml:space="preserve">3.49771356582642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38436102867126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25481653213501</t>
+    <t xml:space="preserve">3.38436126708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25481677055359</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004416465759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96334028244019</t>
+    <t xml:space="preserve">2.96334004402161</t>
   </si>
   <si>
     <t xml:space="preserve">2.97953367233276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80140900611877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88237476348877</t>
+    <t xml:space="preserve">2.80140924453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88237452507019</t>
   </si>
   <si>
     <t xml:space="preserve">2.86618161201477</t>
@@ -611,7 +611,7 @@
     <t xml:space="preserve">2.76902294158936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73663687705994</t>
+    <t xml:space="preserve">2.73663663864136</t>
   </si>
   <si>
     <t xml:space="preserve">2.81760239601135</t>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">2.91476082801819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63947796821594</t>
+    <t xml:space="preserve">2.63947820663452</t>
   </si>
   <si>
     <t xml:space="preserve">2.67186427116394</t>
@@ -632,13 +632,13 @@
     <t xml:space="preserve">2.62328505516052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68805718421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70425009727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60709190368652</t>
+    <t xml:space="preserve">2.68805742263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70425057411194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60709142684937</t>
   </si>
   <si>
     <t xml:space="preserve">2.59089875221252</t>
@@ -647,10 +647,10 @@
     <t xml:space="preserve">2.42896747589111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54231905937195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46135377883911</t>
+    <t xml:space="preserve">2.54231929779053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46135354042053</t>
   </si>
   <si>
     <t xml:space="preserve">2.3156156539917</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">2.2994225025177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35488152503967</t>
+    <t xml:space="preserve">2.35488176345825</t>
   </si>
   <si>
     <t xml:space="preserve">2.40607476234436</t>
@@ -668,13 +668,13 @@
     <t xml:space="preserve">2.28662443161011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1330451965332</t>
+    <t xml:space="preserve">2.13304495811462</t>
   </si>
   <si>
     <t xml:space="preserve">2.08185195922852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0647873878479</t>
+    <t xml:space="preserve">2.06478762626648</t>
   </si>
   <si>
     <t xml:space="preserve">2.03065896034241</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">2.1671736240387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09891629219055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26956009864807</t>
+    <t xml:space="preserve">2.09891653060913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26955986022949</t>
   </si>
   <si>
     <t xml:space="preserve">2.2183666229248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32075333595276</t>
+    <t xml:space="preserve">2.32075309753418</t>
   </si>
   <si>
     <t xml:space="preserve">2.55965399742126</t>
@@ -701,28 +701,28 @@
     <t xml:space="preserve">2.54258966445923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45726823806763</t>
+    <t xml:space="preserve">2.45726799964905</t>
   </si>
   <si>
     <t xml:space="preserve">2.57671856880188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62791156768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61084699630737</t>
+    <t xml:space="preserve">2.62791132926941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61084723472595</t>
   </si>
   <si>
     <t xml:space="preserve">2.64497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59378290176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69616889953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71323323249817</t>
+    <t xml:space="preserve">2.59378266334534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69616913795471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71323347091675</t>
   </si>
   <si>
     <t xml:space="preserve">2.44020342826843</t>
@@ -734,61 +734,61 @@
     <t xml:space="preserve">2.47433257102966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15010952949524</t>
+    <t xml:space="preserve">2.15010929107666</t>
   </si>
   <si>
     <t xml:space="preserve">2.33781743049622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30368876457214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25249552726746</t>
+    <t xml:space="preserve">2.30368852615356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25249576568604</t>
   </si>
   <si>
     <t xml:space="preserve">2.23543095588684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37194585800171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38901042938232</t>
+    <t xml:space="preserve">2.37194609642029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38901019096375</t>
   </si>
   <si>
     <t xml:space="preserve">2.20130252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18423795700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01359438896179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04772329330444</t>
+    <t xml:space="preserve">2.18423819541931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01359415054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04772353172302</t>
   </si>
   <si>
     <t xml:space="preserve">2.11598062515259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91120851039886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8770797252655</t>
+    <t xml:space="preserve">1.91120839118958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87707960605621</t>
   </si>
   <si>
     <t xml:space="preserve">1.84295105934143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97946584224701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86001527309418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94533693790436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96240150928497</t>
+    <t xml:space="preserve">1.97946560382843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86001539230347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94533705711365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96240162849426</t>
   </si>
   <si>
     <t xml:space="preserve">1.99652993679047</t>
@@ -800,34 +800,34 @@
     <t xml:space="preserve">2.90094137191772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88387703895569</t>
+    <t xml:space="preserve">2.88387680053711</t>
   </si>
   <si>
     <t xml:space="preserve">2.76442646980286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73029756546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67910432815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74736189842224</t>
+    <t xml:space="preserve">2.73029780387878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6791045665741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74736166000366</t>
   </si>
   <si>
     <t xml:space="preserve">2.832683801651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86681222915649</t>
+    <t xml:space="preserve">2.86681246757507</t>
   </si>
   <si>
     <t xml:space="preserve">2.79855489730835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78149056434631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93506979942322</t>
+    <t xml:space="preserve">2.78149080276489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9350700378418</t>
   </si>
   <si>
     <t xml:space="preserve">2.96919870376587</t>
@@ -836,16 +836,16 @@
     <t xml:space="preserve">3.02039170265198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00332760810852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03745603561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98626303672791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05452036857605</t>
+    <t xml:space="preserve">3.00332736968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03745579719543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98626327514648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05452060699463</t>
   </si>
   <si>
     <t xml:space="preserve">3.07158470153809</t>
@@ -857,28 +857,28 @@
     <t xml:space="preserve">3.11424589157104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13131022453308</t>
+    <t xml:space="preserve">3.1313099861145</t>
   </si>
   <si>
     <t xml:space="preserve">3.06305241584778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16543912887573</t>
+    <t xml:space="preserve">3.16543889045715</t>
   </si>
   <si>
     <t xml:space="preserve">3.19956755638123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15690684318542</t>
+    <t xml:space="preserve">3.15690660476685</t>
   </si>
   <si>
     <t xml:space="preserve">3.2336962223053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27635717391968</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24222826957703</t>
+    <t xml:space="preserve">3.2763569355011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24222850799561</t>
   </si>
   <si>
     <t xml:space="preserve">3.26782488822937</t>
@@ -887,16 +887,16 @@
     <t xml:space="preserve">3.31048607826233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34461450576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32755041122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28488945960999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18250346183777</t>
+    <t xml:space="preserve">3.3446147441864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32755017280579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28488922119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18250322341919</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342150688171</t>
@@ -905,25 +905,25 @@
     <t xml:space="preserve">3.33710074424744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32836484909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24974250793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20606303215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15364742279053</t>
+    <t xml:space="preserve">3.32836508750916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24974226951599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20606279373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15364766120911</t>
   </si>
   <si>
     <t xml:space="preserve">3.21479892730713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17111945152283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26721405982971</t>
+    <t xml:space="preserve">3.17111968994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26721382141113</t>
   </si>
   <si>
     <t xml:space="preserve">3.36330842971802</t>
@@ -932,64 +932,64 @@
     <t xml:space="preserve">3.49434638023376</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58170509338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56423354148865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59044122695923</t>
+    <t xml:space="preserve">3.58170533180237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56423330307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59044098854065</t>
   </si>
   <si>
     <t xml:space="preserve">3.5030825138092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51181817054749</t>
+    <t xml:space="preserve">3.51181840896606</t>
   </si>
   <si>
     <t xml:space="preserve">3.54676175117493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63412022590637</t>
+    <t xml:space="preserve">3.63411998748779</t>
   </si>
   <si>
     <t xml:space="preserve">3.62538456916809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74768662452698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69527125358582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66906332969666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60791301727295</t>
+    <t xml:space="preserve">3.7476863861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69527149200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66906380653381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60791277885437</t>
   </si>
   <si>
     <t xml:space="preserve">3.55549788475037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66032767295837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65159177780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68653512001038</t>
+    <t xml:space="preserve">3.66032814979553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65159201622009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68653535842896</t>
   </si>
   <si>
     <t xml:space="preserve">3.7040069103241</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75642275810242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57296943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53802609443665</t>
+    <t xml:space="preserve">3.75642251968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57296967506409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53802585601807</t>
   </si>
   <si>
     <t xml:space="preserve">3.3458366394043</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">3.42445969581604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45066714286804</t>
+    <t xml:space="preserve">3.45066738128662</t>
   </si>
   <si>
     <t xml:space="preserve">3.44193148612976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4856104850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4069881439209</t>
+    <t xml:space="preserve">3.48561072349548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40698790550232</t>
   </si>
   <si>
     <t xml:space="preserve">3.35457253456116</t>
@@ -1034,37 +1034,37 @@
     <t xml:space="preserve">3.72147917747498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8787248134613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17574453353882</t>
+    <t xml:space="preserve">3.87872457504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17574405670166</t>
   </si>
   <si>
     <t xml:space="preserve">4.31551790237427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35046148300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1844801902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20195198059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25436639785767</t>
+    <t xml:space="preserve">4.35046100616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18447971343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20195150375366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25436687469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493202209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98355484008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94861149787903</t>
+    <t xml:space="preserve">3.90493226051331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98355507850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94861173629761</t>
   </si>
   <si>
     <t xml:space="preserve">3.93113970756531</t>
@@ -1073,10 +1073,10 @@
     <t xml:space="preserve">4.08838510513306</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07091331481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1233286857605</t>
+    <t xml:space="preserve">4.07091379165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12332820892334</t>
   </si>
   <si>
     <t xml:space="preserve">4.00102663040161</t>
@@ -1091,16 +1091,16 @@
     <t xml:space="preserve">4.0971212387085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21068811416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29804611206055</t>
+    <t xml:space="preserve">4.2106876373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29804658889771</t>
   </si>
   <si>
     <t xml:space="preserve">4.28930997848511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21942377090454</t>
+    <t xml:space="preserve">4.21942329406738</t>
   </si>
   <si>
     <t xml:space="preserve">4.19321632385254</t>
@@ -1115,7 +1115,7 @@
     <t xml:space="preserve">4.11459302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06217813491821</t>
+    <t xml:space="preserve">4.06217765808105</t>
   </si>
   <si>
     <t xml:space="preserve">3.78263020515442</t>
@@ -1124,10 +1124,10 @@
     <t xml:space="preserve">3.80010175704956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82630944252014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83504509925842</t>
+    <t xml:space="preserve">3.82630968093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.835045337677</t>
   </si>
   <si>
     <t xml:space="preserve">3.84378123283386</t>
@@ -1139,16 +1139,16 @@
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734739303589</t>
+    <t xml:space="preserve">3.95734763145447</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86125302314758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7651584148407</t>
+    <t xml:space="preserve">3.861252784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76515817642212</t>
   </si>
   <si>
     <t xml:space="preserve">3.8175733089447</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">3.64285612106323</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67779946327209</t>
+    <t xml:space="preserve">3.67779970169067</t>
   </si>
   <si>
     <t xml:space="preserve">3.7389509677887</t>
@@ -1166,31 +1166,31 @@
     <t xml:space="preserve">3.85251712799072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71274304389954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92240381240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61664867401123</t>
+    <t xml:space="preserve">3.71274328231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92240357398987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61664843559265</t>
   </si>
   <si>
     <t xml:space="preserve">3.39825224876404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23227071762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0575532913208</t>
+    <t xml:space="preserve">3.23227047920227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05755352973938</t>
   </si>
   <si>
     <t xml:space="preserve">2.97019457817078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95272302627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91777920722961</t>
+    <t xml:space="preserve">2.95272278785706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91777944564819</t>
   </si>
   <si>
     <t xml:space="preserve">2.90904355049133</t>
@@ -1199,19 +1199,19 @@
     <t xml:space="preserve">3.37204432487488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38078022003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41572403907776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31962895393372</t>
+    <t xml:space="preserve">3.38077998161316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41572380065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31962919235229</t>
   </si>
   <si>
     <t xml:space="preserve">3.27594995498657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28468561172485</t>
+    <t xml:space="preserve">3.28468585014343</t>
   </si>
   <si>
     <t xml:space="preserve">3.50245499610901</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">3.32098078727722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26653814315796</t>
+    <t xml:space="preserve">3.26653838157654</t>
   </si>
   <si>
     <t xml:space="preserve">3.39357042312622</t>
@@ -1256,7 +1256,7 @@
     <t xml:space="preserve">3.23024344444275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19394874572754</t>
+    <t xml:space="preserve">3.19394850730896</t>
   </si>
   <si>
     <t xml:space="preserve">3.25746440887451</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">3.2211697101593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10321140289307</t>
+    <t xml:space="preserve">3.10321164131165</t>
   </si>
   <si>
     <t xml:space="preserve">2.99432682991028</t>
@@ -1283,13 +1283,13 @@
     <t xml:space="preserve">2.95803189277649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85822105407715</t>
+    <t xml:space="preserve">2.85822129249573</t>
   </si>
   <si>
     <t xml:space="preserve">2.89451599121094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8672947883606</t>
+    <t xml:space="preserve">2.86729502677917</t>
   </si>
   <si>
     <t xml:space="preserve">2.81285238265991</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">2.75841021537781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70396780967712</t>
+    <t xml:space="preserve">2.7039680480957</t>
   </si>
   <si>
     <t xml:space="preserve">2.72211527824402</t>
@@ -1310,16 +1310,16 @@
     <t xml:space="preserve">2.64952564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7947051525116</t>
+    <t xml:space="preserve">2.79470491409302</t>
   </si>
   <si>
     <t xml:space="preserve">2.92173719406128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05784273147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02154803276062</t>
+    <t xml:space="preserve">3.05784296989441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02154779434204</t>
   </si>
   <si>
     <t xml:space="preserve">3.13950634002686</t>
@@ -1349,46 +1349,46 @@
     <t xml:space="preserve">3.08506417274475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01247429847717</t>
+    <t xml:space="preserve">3.01247406005859</t>
   </si>
   <si>
     <t xml:space="preserve">2.88544225692749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7765576839447</t>
+    <t xml:space="preserve">2.77655744552612</t>
   </si>
   <si>
     <t xml:space="preserve">2.71304154396057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6313784122467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68582034111023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66767287254333</t>
+    <t xml:space="preserve">2.63137817382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68582057952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66767311096191</t>
   </si>
   <si>
     <t xml:space="preserve">2.55878829956055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52249336242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67674660682678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64045214653015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87636852264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83099985122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60415697097778</t>
+    <t xml:space="preserve">2.52249360084534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67674684524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64045190811157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87636876106262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83099961280823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6041567325592</t>
   </si>
   <si>
     <t xml:space="preserve">2.73118901252747</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">2.91266345977783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12135887145996</t>
+    <t xml:space="preserve">3.12135910987854</t>
   </si>
   <si>
     <t xml:space="preserve">3.0759904384613</t>
@@ -1424,46 +1424,46 @@
     <t xml:space="preserve">3.0941379070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38449692726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41171765327454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37542319297791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42079138755798</t>
+    <t xml:space="preserve">3.38449668884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41171789169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37542295455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42079162597656</t>
   </si>
   <si>
     <t xml:space="preserve">3.43893885612488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36634945869446</t>
+    <t xml:space="preserve">3.36634922027588</t>
   </si>
   <si>
     <t xml:space="preserve">3.35727572441101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20302248001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27561187744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29375958442688</t>
+    <t xml:space="preserve">3.20302224159241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27561211585999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29375982284546</t>
   </si>
   <si>
     <t xml:space="preserve">3.1667275428772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11228513717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78563141822815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84007382392883</t>
+    <t xml:space="preserve">3.11228537559509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78563117980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84007358551025</t>
   </si>
   <si>
     <t xml:space="preserve">2.82192611694336</t>
@@ -56187,7 +56187,7 @@
     </row>
     <row r="2082">
       <c r="A2082" s="1" t="n">
-        <v>45994.6736921296</v>
+        <v>45994.3333333333</v>
       </c>
       <c r="B2082" t="n">
         <v>10701</v>
@@ -56208,6 +56208,32 @@
         <v>576</v>
       </c>
       <c r="H2082" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2083">
+      <c r="A2083" s="1" t="n">
+        <v>45995.5678587963</v>
+      </c>
+      <c r="B2083" t="n">
+        <v>12415</v>
+      </c>
+      <c r="C2083" t="n">
+        <v>3.3199999332428</v>
+      </c>
+      <c r="D2083" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="E2083" t="n">
+        <v>3.3199999332428</v>
+      </c>
+      <c r="F2083" t="n">
+        <v>3.25999999046326</v>
+      </c>
+      <c r="G2083" t="s">
+        <v>571</v>
+      </c>
+      <c r="H2083" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -38,25 +38,25 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02345752716064</t>
+    <t xml:space="preserve">3.02345776557922</t>
   </si>
   <si>
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519947052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88901519775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98013734817505</t>
+    <t xml:space="preserve">2.96519923210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88901543617249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98013710975647</t>
   </si>
   <si>
     <t xml:space="preserve">2.97266817092896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94577980041504</t>
+    <t xml:space="preserve">2.94578003883362</t>
   </si>
   <si>
     <t xml:space="preserve">2.95773029327393</t>
@@ -65,10 +65,10 @@
     <t xml:space="preserve">2.96221137046814</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9353232383728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91291618347168</t>
+    <t xml:space="preserve">2.93532299995422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91291642189026</t>
   </si>
   <si>
     <t xml:space="preserve">2.9786434173584</t>
@@ -77,7 +77,7 @@
     <t xml:space="preserve">2.98611235618591</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03540802001953</t>
+    <t xml:space="preserve">3.03540825843811</t>
   </si>
   <si>
     <t xml:space="preserve">3.05632138252258</t>
@@ -92,22 +92,22 @@
     <t xml:space="preserve">2.98760604858398</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95026135444641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01598858833313</t>
+    <t xml:space="preserve">2.95026111602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01598882675171</t>
   </si>
   <si>
     <t xml:space="preserve">3.01001334190369</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02495145797729</t>
+    <t xml:space="preserve">3.02495169639587</t>
   </si>
   <si>
     <t xml:space="preserve">3.0174822807312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03092670440674</t>
+    <t xml:space="preserve">3.03092694282532</t>
   </si>
   <si>
     <t xml:space="preserve">2.99955677986145</t>
@@ -125,31 +125,31 @@
     <t xml:space="preserve">2.92785429954529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90843510627747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89648461341858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91889119148254</t>
+    <t xml:space="preserve">2.90843486785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91889142990112</t>
   </si>
   <si>
     <t xml:space="preserve">2.9159038066864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92038512229919</t>
+    <t xml:space="preserve">2.92038536071777</t>
   </si>
   <si>
     <t xml:space="preserve">2.90544724464417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90992879867554</t>
+    <t xml:space="preserve">2.90992832183838</t>
   </si>
   <si>
     <t xml:space="preserve">2.9233729839325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83822631835938</t>
+    <t xml:space="preserve">2.83822584152222</t>
   </si>
   <si>
     <t xml:space="preserve">2.86063313484192</t>
@@ -158,19 +158,19 @@
     <t xml:space="preserve">2.82627534866333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77996778488159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84569525718689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86810207366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88304018974304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79639935493469</t>
+    <t xml:space="preserve">2.77996754646301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84569501876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86810183525085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88303995132446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79639959335327</t>
   </si>
   <si>
     <t xml:space="preserve">2.87557101249695</t>
@@ -179,7 +179,7 @@
     <t xml:space="preserve">2.89797830581665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80088067054749</t>
+    <t xml:space="preserve">2.80088090896606</t>
   </si>
   <si>
     <t xml:space="preserve">2.74262261390686</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">2.82179427146912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75009155273438</t>
+    <t xml:space="preserve">2.7500913143158</t>
   </si>
   <si>
     <t xml:space="preserve">2.76353597640991</t>
@@ -197,19 +197,19 @@
     <t xml:space="preserve">2.77847409248352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78594279289246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79341173171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69631457328796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65150046348572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62162470817566</t>
+    <t xml:space="preserve">2.78594303131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79341197013855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69631481170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6515007019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62162446975708</t>
   </si>
   <si>
     <t xml:space="preserve">2.5394651889801</t>
@@ -218,19 +218,19 @@
     <t xml:space="preserve">2.56934142112732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61415576934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65896940231323</t>
+    <t xml:space="preserve">2.61415553092957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65896964073181</t>
   </si>
   <si>
     <t xml:space="preserve">2.68884563446045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70378375053406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77100467681885</t>
+    <t xml:space="preserve">2.70378351211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77100491523743</t>
   </si>
   <si>
     <t xml:space="preserve">2.81581902503967</t>
@@ -248,13 +248,13 @@
     <t xml:space="preserve">2.74112868309021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72619080543518</t>
+    <t xml:space="preserve">2.72619104385376</t>
   </si>
   <si>
     <t xml:space="preserve">2.83075714111328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89315056800842</t>
+    <t xml:space="preserve">2.893150806427</t>
   </si>
   <si>
     <t xml:space="preserve">2.69871854782104</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">2.83093237876892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81537771224976</t>
+    <t xml:space="preserve">2.81537747383118</t>
   </si>
   <si>
     <t xml:space="preserve">2.84648680686951</t>
@@ -284,37 +284,37 @@
     <t xml:space="preserve">2.73760485649109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76093673706055</t>
+    <t xml:space="preserve">2.76093697547913</t>
   </si>
   <si>
     <t xml:space="preserve">2.80760049819946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00980997085571</t>
+    <t xml:space="preserve">3.00980973243713</t>
   </si>
   <si>
     <t xml:space="preserve">2.95536875724792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90870499610901</t>
+    <t xml:space="preserve">2.90870523452759</t>
   </si>
   <si>
     <t xml:space="preserve">2.88537335395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82315540313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86204147338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00203275680542</t>
+    <t xml:space="preserve">2.82315516471863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86204171180725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00203251838684</t>
   </si>
   <si>
     <t xml:space="preserve">2.91648244857788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85426425933838</t>
+    <t xml:space="preserve">2.8542640209198</t>
   </si>
   <si>
     <t xml:space="preserve">2.7298276424408</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">2.7220504283905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75315928459167</t>
+    <t xml:space="preserve">2.75315952301025</t>
   </si>
   <si>
     <t xml:space="preserve">2.70649600028992</t>
@@ -338,7 +338,7 @@
     <t xml:space="preserve">2.99425530433655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97870063781738</t>
+    <t xml:space="preserve">2.97870087623596</t>
   </si>
   <si>
     <t xml:space="preserve">2.86981868743896</t>
@@ -347,55 +347,55 @@
     <t xml:space="preserve">2.94759178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98647809028625</t>
+    <t xml:space="preserve">2.98647785186768</t>
   </si>
   <si>
     <t xml:space="preserve">2.63650035858154</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55094981193542</t>
+    <t xml:space="preserve">2.550950050354</t>
   </si>
   <si>
     <t xml:space="preserve">2.51984095573425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41095924377441</t>
+    <t xml:space="preserve">2.41095900535583</t>
   </si>
   <si>
     <t xml:space="preserve">2.34096336364746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34874081611633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36429500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2554132938385</t>
+    <t xml:space="preserve">2.34874057769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36429524421692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25541305541992</t>
   </si>
   <si>
     <t xml:space="preserve">2.24763584136963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32540893554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23208117485046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18541741371155</t>
+    <t xml:space="preserve">2.32540845870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23208141326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18541765213013</t>
   </si>
   <si>
     <t xml:space="preserve">2.27874493598938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26319026947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2165265083313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06875824928284</t>
+    <t xml:space="preserve">2.26319050788879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21652674674988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06875801086426</t>
   </si>
   <si>
     <t xml:space="preserve">2.14653134346008</t>
@@ -404,22 +404,22 @@
     <t xml:space="preserve">2.10764455795288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15430879592896</t>
+    <t xml:space="preserve">2.15430855751038</t>
   </si>
   <si>
     <t xml:space="preserve">2.17764019966125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22430419921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35651779174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48873162269592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52761840820312</t>
+    <t xml:space="preserve">2.22430396080017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35651755332947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4887318611145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52761793136597</t>
   </si>
   <si>
     <t xml:space="preserve">2.43429088592529</t>
@@ -431,58 +431,58 @@
     <t xml:space="preserve">2.5587272644043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44984531402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37207221984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33318614959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29429960250854</t>
+    <t xml:space="preserve">2.44984555244446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37207245826721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33318591117859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29429984092712</t>
   </si>
   <si>
     <t xml:space="preserve">2.3798496723175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71427321434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58205914497375</t>
+    <t xml:space="preserve">2.71427297592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58205890655518</t>
   </si>
   <si>
     <t xml:space="preserve">2.62872290611267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65983200073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57428169250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67538642883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64427757263184</t>
+    <t xml:space="preserve">2.65983247756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57428193092346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67538666725159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64427733421326</t>
   </si>
   <si>
     <t xml:space="preserve">2.69094133377075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76871395111084</t>
+    <t xml:space="preserve">2.76871418952942</t>
   </si>
   <si>
     <t xml:space="preserve">2.90092802047729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96314644813538</t>
+    <t xml:space="preserve">2.9631462097168</t>
   </si>
   <si>
     <t xml:space="preserve">2.92425990104675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97092318534851</t>
+    <t xml:space="preserve">2.97092366218567</t>
   </si>
   <si>
     <t xml:space="preserve">3.01758742332458</t>
@@ -491,7 +491,7 @@
     <t xml:space="preserve">3.04869651794434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03314161300659</t>
+    <t xml:space="preserve">3.03314208984375</t>
   </si>
   <si>
     <t xml:space="preserve">3.06425094604492</t>
@@ -503,7 +503,7 @@
     <t xml:space="preserve">3.06049919128418</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0281126499176</t>
+    <t xml:space="preserve">3.02811288833618</t>
   </si>
   <si>
     <t xml:space="preserve">3.01191973686218</t>
@@ -512,13 +512,13 @@
     <t xml:space="preserve">3.10907816886902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09288501739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1252715587616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07669234275818</t>
+    <t xml:space="preserve">3.0928852558136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12527132034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0766921043396</t>
   </si>
   <si>
     <t xml:space="preserve">2.99572658538818</t>
@@ -527,22 +527,22 @@
     <t xml:space="preserve">3.30339574813843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41674733161926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35197496414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33578157424927</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36816787719727</t>
+    <t xml:space="preserve">3.41674709320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.351975440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33578205108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36816811561584</t>
   </si>
   <si>
     <t xml:space="preserve">3.23862314224243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31958913803101</t>
+    <t xml:space="preserve">3.31958889961243</t>
   </si>
   <si>
     <t xml:space="preserve">3.27100944519043</t>
@@ -551,34 +551,34 @@
     <t xml:space="preserve">3.28720259666443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22242999076843</t>
+    <t xml:space="preserve">3.22243022918701</t>
   </si>
   <si>
     <t xml:space="preserve">3.17385101318359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20623707771301</t>
+    <t xml:space="preserve">3.20623731613159</t>
   </si>
   <si>
     <t xml:space="preserve">3.1414647102356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40055441856384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49771356582642</t>
+    <t xml:space="preserve">3.40055418014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49771332740784</t>
   </si>
   <si>
     <t xml:space="preserve">3.38436126708984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25481677055359</t>
+    <t xml:space="preserve">3.25481629371643</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004416465759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96334004402161</t>
+    <t xml:space="preserve">2.96334028244019</t>
   </si>
   <si>
     <t xml:space="preserve">2.97953367233276</t>
@@ -587,7 +587,7 @@
     <t xml:space="preserve">2.80140924453735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88237452507019</t>
+    <t xml:space="preserve">2.88237476348877</t>
   </si>
   <si>
     <t xml:space="preserve">2.86618161201477</t>
@@ -596,10 +596,10 @@
     <t xml:space="preserve">2.84998846054077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78521609306335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75283002853394</t>
+    <t xml:space="preserve">2.78521633148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75282979011536</t>
   </si>
   <si>
     <t xml:space="preserve">2.72044348716736</t>
@@ -608,7 +608,7 @@
     <t xml:space="preserve">2.83379554748535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76902294158936</t>
+    <t xml:space="preserve">2.76902341842651</t>
   </si>
   <si>
     <t xml:space="preserve">2.73663663864136</t>
@@ -617,28 +617,28 @@
     <t xml:space="preserve">2.81760239601135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89856791496277</t>
+    <t xml:space="preserve">2.89856767654419</t>
   </si>
   <si>
     <t xml:space="preserve">2.91476082801819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63947820663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67186427116394</t>
+    <t xml:space="preserve">2.63947796821594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67186403274536</t>
   </si>
   <si>
     <t xml:space="preserve">2.62328505516052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68805742263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70425057411194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60709142684937</t>
+    <t xml:space="preserve">2.68805718421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70425009727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60709190368652</t>
   </si>
   <si>
     <t xml:space="preserve">2.59089875221252</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">2.54231929779053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46135354042053</t>
+    <t xml:space="preserve">2.46135377883911</t>
   </si>
   <si>
     <t xml:space="preserve">2.3156156539917</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">2.2994225025177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35488176345825</t>
+    <t xml:space="preserve">2.35488152503967</t>
   </si>
   <si>
     <t xml:space="preserve">2.40607476234436</t>
@@ -668,13 +668,13 @@
     <t xml:space="preserve">2.28662443161011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13304495811462</t>
+    <t xml:space="preserve">2.1330451965332</t>
   </si>
   <si>
     <t xml:space="preserve">2.08185195922852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06478762626648</t>
+    <t xml:space="preserve">2.0647873878479</t>
   </si>
   <si>
     <t xml:space="preserve">2.03065896034241</t>
@@ -683,16 +683,16 @@
     <t xml:space="preserve">2.1671736240387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09891653060913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26955986022949</t>
+    <t xml:space="preserve">2.09891629219055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26956009864807</t>
   </si>
   <si>
     <t xml:space="preserve">2.2183666229248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32075309753418</t>
+    <t xml:space="preserve">2.32075333595276</t>
   </si>
   <si>
     <t xml:space="preserve">2.55965399742126</t>
@@ -701,28 +701,28 @@
     <t xml:space="preserve">2.54258966445923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45726799964905</t>
+    <t xml:space="preserve">2.45726823806763</t>
   </si>
   <si>
     <t xml:space="preserve">2.57671856880188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62791132926941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61084723472595</t>
+    <t xml:space="preserve">2.62791156768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61084699630737</t>
   </si>
   <si>
     <t xml:space="preserve">2.64497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59378266334534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69616913795471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71323347091675</t>
+    <t xml:space="preserve">2.59378290176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69616889953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71323323249817</t>
   </si>
   <si>
     <t xml:space="preserve">2.44020342826843</t>
@@ -734,61 +734,61 @@
     <t xml:space="preserve">2.47433257102966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15010929107666</t>
+    <t xml:space="preserve">2.15010952949524</t>
   </si>
   <si>
     <t xml:space="preserve">2.33781743049622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30368852615356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25249576568604</t>
+    <t xml:space="preserve">2.30368876457214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25249552726746</t>
   </si>
   <si>
     <t xml:space="preserve">2.23543095588684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37194609642029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38901019096375</t>
+    <t xml:space="preserve">2.37194585800171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38901042938232</t>
   </si>
   <si>
     <t xml:space="preserve">2.20130252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18423819541931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01359415054321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04772353172302</t>
+    <t xml:space="preserve">2.18423795700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01359438896179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04772329330444</t>
   </si>
   <si>
     <t xml:space="preserve">2.11598062515259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91120839118958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87707960605621</t>
+    <t xml:space="preserve">1.91120851039886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8770797252655</t>
   </si>
   <si>
     <t xml:space="preserve">1.84295105934143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97946560382843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86001539230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94533705711365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96240162849426</t>
+    <t xml:space="preserve">1.97946584224701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86001527309418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94533693790436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96240150928497</t>
   </si>
   <si>
     <t xml:space="preserve">1.99652993679047</t>
@@ -800,34 +800,34 @@
     <t xml:space="preserve">2.90094137191772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88387680053711</t>
+    <t xml:space="preserve">2.88387703895569</t>
   </si>
   <si>
     <t xml:space="preserve">2.76442646980286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73029780387878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6791045665741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74736166000366</t>
+    <t xml:space="preserve">2.73029756546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67910432815552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74736189842224</t>
   </si>
   <si>
     <t xml:space="preserve">2.832683801651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86681246757507</t>
+    <t xml:space="preserve">2.86681222915649</t>
   </si>
   <si>
     <t xml:space="preserve">2.79855489730835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78149080276489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9350700378418</t>
+    <t xml:space="preserve">2.78149056434631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93506979942322</t>
   </si>
   <si>
     <t xml:space="preserve">2.96919870376587</t>
@@ -836,16 +836,16 @@
     <t xml:space="preserve">3.02039170265198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00332736968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03745579719543</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98626327514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05452060699463</t>
+    <t xml:space="preserve">3.00332760810852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03745603561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98626303672791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05452036857605</t>
   </si>
   <si>
     <t xml:space="preserve">3.07158470153809</t>
@@ -857,28 +857,28 @@
     <t xml:space="preserve">3.11424589157104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1313099861145</t>
+    <t xml:space="preserve">3.13131022453308</t>
   </si>
   <si>
     <t xml:space="preserve">3.06305241584778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16543889045715</t>
+    <t xml:space="preserve">3.16543912887573</t>
   </si>
   <si>
     <t xml:space="preserve">3.19956755638123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15690660476685</t>
+    <t xml:space="preserve">3.15690684318542</t>
   </si>
   <si>
     <t xml:space="preserve">3.2336962223053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2763569355011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24222850799561</t>
+    <t xml:space="preserve">3.27635717391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24222826957703</t>
   </si>
   <si>
     <t xml:space="preserve">3.26782488822937</t>
@@ -887,16 +887,16 @@
     <t xml:space="preserve">3.31048607826233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3446147441864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32755017280579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28488922119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18250322341919</t>
+    <t xml:space="preserve">3.34461450576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32755041122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28488945960999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18250346183777</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342150688171</t>
@@ -905,25 +905,25 @@
     <t xml:space="preserve">3.33710074424744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32836508750916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24974226951599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20606279373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15364766120911</t>
+    <t xml:space="preserve">3.32836484909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24974250793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20606303215027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15364742279053</t>
   </si>
   <si>
     <t xml:space="preserve">3.21479892730713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17111968994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26721382141113</t>
+    <t xml:space="preserve">3.17111945152283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26721405982971</t>
   </si>
   <si>
     <t xml:space="preserve">3.36330842971802</t>
@@ -932,64 +932,64 @@
     <t xml:space="preserve">3.49434638023376</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58170533180237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56423330307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59044098854065</t>
+    <t xml:space="preserve">3.58170509338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56423354148865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59044122695923</t>
   </si>
   <si>
     <t xml:space="preserve">3.5030825138092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51181840896606</t>
+    <t xml:space="preserve">3.51181817054749</t>
   </si>
   <si>
     <t xml:space="preserve">3.54676175117493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63411998748779</t>
+    <t xml:space="preserve">3.63412022590637</t>
   </si>
   <si>
     <t xml:space="preserve">3.62538456916809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7476863861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69527149200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66906380653381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60791277885437</t>
+    <t xml:space="preserve">3.74768662452698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69527125358582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66906332969666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60791301727295</t>
   </si>
   <si>
     <t xml:space="preserve">3.55549788475037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66032814979553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65159201622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68653535842896</t>
+    <t xml:space="preserve">3.66032767295837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65159177780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68653512001038</t>
   </si>
   <si>
     <t xml:space="preserve">3.7040069103241</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75642251968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57296967506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53802585601807</t>
+    <t xml:space="preserve">3.75642275810242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57296943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53802609443665</t>
   </si>
   <si>
     <t xml:space="preserve">3.3458366394043</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">3.42445969581604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45066738128662</t>
+    <t xml:space="preserve">3.45066714286804</t>
   </si>
   <si>
     <t xml:space="preserve">3.44193148612976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48561072349548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40698790550232</t>
+    <t xml:space="preserve">3.4856104850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4069881439209</t>
   </si>
   <si>
     <t xml:space="preserve">3.35457253456116</t>
@@ -1034,37 +1034,37 @@
     <t xml:space="preserve">3.72147917747498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87872457504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17574405670166</t>
+    <t xml:space="preserve">3.8787248134613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17574453353882</t>
   </si>
   <si>
     <t xml:space="preserve">4.31551790237427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35046100616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18447971343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20195150375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25436687469482</t>
+    <t xml:space="preserve">4.35046148300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1844801902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20195198059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25436639785767</t>
   </si>
   <si>
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493226051331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98355507850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94861173629761</t>
+    <t xml:space="preserve">3.90493202209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98355484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94861149787903</t>
   </si>
   <si>
     <t xml:space="preserve">3.93113970756531</t>
@@ -1073,10 +1073,10 @@
     <t xml:space="preserve">4.08838510513306</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07091379165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12332820892334</t>
+    <t xml:space="preserve">4.07091331481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1233286857605</t>
   </si>
   <si>
     <t xml:space="preserve">4.00102663040161</t>
@@ -1091,16 +1091,16 @@
     <t xml:space="preserve">4.0971212387085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2106876373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29804658889771</t>
+    <t xml:space="preserve">4.21068811416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29804611206055</t>
   </si>
   <si>
     <t xml:space="preserve">4.28930997848511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21942329406738</t>
+    <t xml:space="preserve">4.21942377090454</t>
   </si>
   <si>
     <t xml:space="preserve">4.19321632385254</t>
@@ -1115,7 +1115,7 @@
     <t xml:space="preserve">4.11459302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06217765808105</t>
+    <t xml:space="preserve">4.06217813491821</t>
   </si>
   <si>
     <t xml:space="preserve">3.78263020515442</t>
@@ -1124,10 +1124,10 @@
     <t xml:space="preserve">3.80010175704956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82630968093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.835045337677</t>
+    <t xml:space="preserve">3.82630944252014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83504509925842</t>
   </si>
   <si>
     <t xml:space="preserve">3.84378123283386</t>
@@ -1139,16 +1139,16 @@
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734763145447</t>
+    <t xml:space="preserve">3.95734739303589</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.861252784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76515817642212</t>
+    <t xml:space="preserve">3.86125302314758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7651584148407</t>
   </si>
   <si>
     <t xml:space="preserve">3.8175733089447</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">3.64285612106323</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67779970169067</t>
+    <t xml:space="preserve">3.67779946327209</t>
   </si>
   <si>
     <t xml:space="preserve">3.7389509677887</t>
@@ -1166,31 +1166,31 @@
     <t xml:space="preserve">3.85251712799072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71274328231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92240357398987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61664843559265</t>
+    <t xml:space="preserve">3.71274304389954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92240381240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61664867401123</t>
   </si>
   <si>
     <t xml:space="preserve">3.39825224876404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23227047920227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05755352973938</t>
+    <t xml:space="preserve">3.23227071762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0575532913208</t>
   </si>
   <si>
     <t xml:space="preserve">2.97019457817078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95272278785706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91777944564819</t>
+    <t xml:space="preserve">2.95272302627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91777920722961</t>
   </si>
   <si>
     <t xml:space="preserve">2.90904355049133</t>
@@ -1199,19 +1199,19 @@
     <t xml:space="preserve">3.37204432487488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38077998161316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41572380065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31962919235229</t>
+    <t xml:space="preserve">3.38078022003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41572403907776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31962895393372</t>
   </si>
   <si>
     <t xml:space="preserve">3.27594995498657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28468585014343</t>
+    <t xml:space="preserve">3.28468561172485</t>
   </si>
   <si>
     <t xml:space="preserve">3.50245499610901</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">3.32098078727722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26653838157654</t>
+    <t xml:space="preserve">3.26653814315796</t>
   </si>
   <si>
     <t xml:space="preserve">3.39357042312622</t>
@@ -1256,7 +1256,7 @@
     <t xml:space="preserve">3.23024344444275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19394850730896</t>
+    <t xml:space="preserve">3.19394874572754</t>
   </si>
   <si>
     <t xml:space="preserve">3.25746440887451</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">3.2211697101593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10321164131165</t>
+    <t xml:space="preserve">3.10321140289307</t>
   </si>
   <si>
     <t xml:space="preserve">2.99432682991028</t>
@@ -1283,13 +1283,13 @@
     <t xml:space="preserve">2.95803189277649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85822129249573</t>
+    <t xml:space="preserve">2.85822105407715</t>
   </si>
   <si>
     <t xml:space="preserve">2.89451599121094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86729502677917</t>
+    <t xml:space="preserve">2.8672947883606</t>
   </si>
   <si>
     <t xml:space="preserve">2.81285238265991</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">2.75841021537781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7039680480957</t>
+    <t xml:space="preserve">2.70396780967712</t>
   </si>
   <si>
     <t xml:space="preserve">2.72211527824402</t>
@@ -1310,16 +1310,16 @@
     <t xml:space="preserve">2.64952564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79470491409302</t>
+    <t xml:space="preserve">2.7947051525116</t>
   </si>
   <si>
     <t xml:space="preserve">2.92173719406128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05784296989441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02154779434204</t>
+    <t xml:space="preserve">3.05784273147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02154803276062</t>
   </si>
   <si>
     <t xml:space="preserve">3.13950634002686</t>
@@ -1349,46 +1349,46 @@
     <t xml:space="preserve">3.08506417274475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01247406005859</t>
+    <t xml:space="preserve">3.01247429847717</t>
   </si>
   <si>
     <t xml:space="preserve">2.88544225692749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77655744552612</t>
+    <t xml:space="preserve">2.7765576839447</t>
   </si>
   <si>
     <t xml:space="preserve">2.71304154396057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63137817382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68582057952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66767311096191</t>
+    <t xml:space="preserve">2.6313784122467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68582034111023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66767287254333</t>
   </si>
   <si>
     <t xml:space="preserve">2.55878829956055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52249360084534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67674684524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64045190811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87636876106262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83099961280823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6041567325592</t>
+    <t xml:space="preserve">2.52249336242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67674660682678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64045214653015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87636852264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83099985122681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60415697097778</t>
   </si>
   <si>
     <t xml:space="preserve">2.73118901252747</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">2.91266345977783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12135910987854</t>
+    <t xml:space="preserve">3.12135887145996</t>
   </si>
   <si>
     <t xml:space="preserve">3.0759904384613</t>
@@ -1424,46 +1424,46 @@
     <t xml:space="preserve">3.0941379070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38449668884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41171789169312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37542295455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42079162597656</t>
+    <t xml:space="preserve">3.38449692726135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41171765327454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37542319297791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42079138755798</t>
   </si>
   <si>
     <t xml:space="preserve">3.43893885612488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36634922027588</t>
+    <t xml:space="preserve">3.36634945869446</t>
   </si>
   <si>
     <t xml:space="preserve">3.35727572441101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20302224159241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27561211585999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29375982284546</t>
+    <t xml:space="preserve">3.20302248001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27561187744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29375958442688</t>
   </si>
   <si>
     <t xml:space="preserve">3.1667275428772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11228537559509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78563117980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84007358551025</t>
+    <t xml:space="preserve">3.11228513717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78563141822815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84007382392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.82192611694336</t>
@@ -56213,7 +56213,7 @@
     </row>
     <row r="2083">
       <c r="A2083" s="1" t="n">
-        <v>45995.5678587963</v>
+        <v>45995.3333333333</v>
       </c>
       <c r="B2083" t="n">
         <v>12415</v>
@@ -56234,6 +56234,32 @@
         <v>571</v>
       </c>
       <c r="H2083" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2084">
+      <c r="A2084" s="1" t="n">
+        <v>45996.6748958333</v>
+      </c>
+      <c r="B2084" t="n">
+        <v>14100</v>
+      </c>
+      <c r="C2084" t="n">
+        <v>3.33999991416931</v>
+      </c>
+      <c r="D2084" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="E2084" t="n">
+        <v>3.3199999332428</v>
+      </c>
+      <c r="F2084" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="G2084" t="s">
+        <v>572</v>
+      </c>
+      <c r="H2084" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02345776557922</t>
+    <t xml:space="preserve">3.02345752716064</t>
   </si>
   <si>
     <t xml:space="preserve">NDT.MI</t>
@@ -50,37 +50,37 @@
     <t xml:space="preserve">2.88901543617249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98013710975647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97266817092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94578003883362</t>
+    <t xml:space="preserve">2.98013758659363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97266840934753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94577980041504</t>
   </si>
   <si>
     <t xml:space="preserve">2.95773029327393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96221137046814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93532299995422</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91291642189026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9786434173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98611235618591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03540825843811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05632138252258</t>
+    <t xml:space="preserve">2.9622118473053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93532371520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91291618347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97864317893982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98611259460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03540802001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.056321144104</t>
   </si>
   <si>
     <t xml:space="preserve">3.0593090057373</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">3.05034613609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98760604858398</t>
+    <t xml:space="preserve">2.98760652542114</t>
   </si>
   <si>
     <t xml:space="preserve">2.95026111602783</t>
@@ -101,16 +101,16 @@
     <t xml:space="preserve">3.01001334190369</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02495169639587</t>
+    <t xml:space="preserve">3.02495145797729</t>
   </si>
   <si>
     <t xml:space="preserve">3.0174822807312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03092694282532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99955677986145</t>
+    <t xml:space="preserve">3.03092646598816</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99955654144287</t>
   </si>
   <si>
     <t xml:space="preserve">3.04437112808228</t>
@@ -140,10 +140,10 @@
     <t xml:space="preserve">2.92038536071777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90544724464417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90992832183838</t>
+    <t xml:space="preserve">2.90544700622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90992856025696</t>
   </si>
   <si>
     <t xml:space="preserve">2.9233729839325</t>
@@ -152,13 +152,13 @@
     <t xml:space="preserve">2.83822584152222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86063313484192</t>
+    <t xml:space="preserve">2.8606333732605</t>
   </si>
   <si>
     <t xml:space="preserve">2.82627534866333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77996754646301</t>
+    <t xml:space="preserve">2.77996778488159</t>
   </si>
   <si>
     <t xml:space="preserve">2.84569501876831</t>
@@ -176,10 +176,10 @@
     <t xml:space="preserve">2.87557101249695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89797830581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80088090896606</t>
+    <t xml:space="preserve">2.89797854423523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80088138580322</t>
   </si>
   <si>
     <t xml:space="preserve">2.74262261390686</t>
@@ -188,49 +188,49 @@
     <t xml:space="preserve">2.82179427146912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7500913143158</t>
+    <t xml:space="preserve">2.75009155273438</t>
   </si>
   <si>
     <t xml:space="preserve">2.76353597640991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77847409248352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78594303131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79341197013855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69631481170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6515007019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62162446975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5394651889801</t>
+    <t xml:space="preserve">2.77847385406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78594255447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79341173171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69631457328796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65150046348572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62162470817566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53946566581726</t>
   </si>
   <si>
     <t xml:space="preserve">2.56934142112732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61415553092957</t>
+    <t xml:space="preserve">2.61415576934814</t>
   </si>
   <si>
     <t xml:space="preserve">2.65896964073181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68884563446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70378351211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77100491523743</t>
+    <t xml:space="preserve">2.68884539604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70378375053406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77100515365601</t>
   </si>
   <si>
     <t xml:space="preserve">2.81581902503967</t>
@@ -248,10 +248,10 @@
     <t xml:space="preserve">2.74112868309021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72619104385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83075714111328</t>
+    <t xml:space="preserve">2.72619080543518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8307569026947</t>
   </si>
   <si>
     <t xml:space="preserve">2.893150806427</t>
@@ -263,10 +263,10 @@
     <t xml:space="preserve">2.83870983123779</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93203711509705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87759613990784</t>
+    <t xml:space="preserve">2.93203735351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87759590148926</t>
   </si>
   <si>
     <t xml:space="preserve">2.83093237876892</t>
@@ -275,28 +275,28 @@
     <t xml:space="preserve">2.81537747383118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84648680686951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79982304573059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73760485649109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76093697547913</t>
+    <t xml:space="preserve">2.84648728370667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79982328414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73760509490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76093649864197</t>
   </si>
   <si>
     <t xml:space="preserve">2.80760049819946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00980973243713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95536875724792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90870523452759</t>
+    <t xml:space="preserve">3.00980997085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9553689956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90870499610901</t>
   </si>
   <si>
     <t xml:space="preserve">2.88537335395813</t>
@@ -305,34 +305,34 @@
     <t xml:space="preserve">2.82315516471863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86204171180725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00203251838684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91648244857788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8542640209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7298276424408</t>
+    <t xml:space="preserve">2.86204147338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00203227996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9164822101593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85426425933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72982788085938</t>
   </si>
   <si>
     <t xml:space="preserve">2.68316388130188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7220504283905</t>
+    <t xml:space="preserve">2.72205018997192</t>
   </si>
   <si>
     <t xml:space="preserve">2.75315952301025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70649600028992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93981432914734</t>
+    <t xml:space="preserve">2.70649576187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93981456756592</t>
   </si>
   <si>
     <t xml:space="preserve">2.99425530433655</t>
@@ -344,22 +344,22 @@
     <t xml:space="preserve">2.86981868743896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94759178161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98647785186768</t>
+    <t xml:space="preserve">2.94759154319763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98647832870483</t>
   </si>
   <si>
     <t xml:space="preserve">2.63650035858154</t>
   </si>
   <si>
-    <t xml:space="preserve">2.550950050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51984095573425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41095900535583</t>
+    <t xml:space="preserve">2.55095028877258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51984071731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41095876693726</t>
   </si>
   <si>
     <t xml:space="preserve">2.34096336364746</t>
@@ -371,7 +371,7 @@
     <t xml:space="preserve">2.36429524421692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25541305541992</t>
+    <t xml:space="preserve">2.2554132938385</t>
   </si>
   <si>
     <t xml:space="preserve">2.24763584136963</t>
@@ -386,16 +386,16 @@
     <t xml:space="preserve">2.18541765213013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27874493598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26319050788879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21652674674988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06875801086426</t>
+    <t xml:space="preserve">2.27874517440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26319026947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2165265083313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06875848770142</t>
   </si>
   <si>
     <t xml:space="preserve">2.14653134346008</t>
@@ -404,13 +404,13 @@
     <t xml:space="preserve">2.10764455795288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15430855751038</t>
+    <t xml:space="preserve">2.1543083190918</t>
   </si>
   <si>
     <t xml:space="preserve">2.17764019966125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22430396080017</t>
+    <t xml:space="preserve">2.22430372238159</t>
   </si>
   <si>
     <t xml:space="preserve">2.35651755332947</t>
@@ -419,13 +419,13 @@
     <t xml:space="preserve">2.4887318611145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52761793136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43429088592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44206809997559</t>
+    <t xml:space="preserve">2.52761816978455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43429112434387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44206833839417</t>
   </si>
   <si>
     <t xml:space="preserve">2.5587272644043</t>
@@ -434,43 +434,43 @@
     <t xml:space="preserve">2.44984555244446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37207245826721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33318591117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29429984092712</t>
+    <t xml:space="preserve">2.37207221984863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33318638801575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29429960250854</t>
   </si>
   <si>
     <t xml:space="preserve">2.3798496723175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71427297592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58205890655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62872290611267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65983247756958</t>
+    <t xml:space="preserve">2.71427321434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58205938339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62872314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.659832239151</t>
   </si>
   <si>
     <t xml:space="preserve">2.57428193092346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67538666725159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64427733421326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69094133377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76871418952942</t>
+    <t xml:space="preserve">2.67538642883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64427757263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69094157218933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76871371269226</t>
   </si>
   <si>
     <t xml:space="preserve">2.90092802047729</t>
@@ -479,19 +479,19 @@
     <t xml:space="preserve">2.9631462097168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92425990104675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97092366218567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01758742332458</t>
+    <t xml:space="preserve">2.92425966262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97092318534851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01758718490601</t>
   </si>
   <si>
     <t xml:space="preserve">3.04869651794434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03314208984375</t>
+    <t xml:space="preserve">3.03314185142517</t>
   </si>
   <si>
     <t xml:space="preserve">3.06425094604492</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">3.07980561256409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06049919128418</t>
+    <t xml:space="preserve">3.0604989528656</t>
   </si>
   <si>
     <t xml:space="preserve">3.02811288833618</t>
@@ -512,10 +512,10 @@
     <t xml:space="preserve">3.10907816886902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0928852558136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12527132034302</t>
+    <t xml:space="preserve">3.09288501739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1252715587616</t>
   </si>
   <si>
     <t xml:space="preserve">3.0766921043396</t>
@@ -530,22 +530,22 @@
     <t xml:space="preserve">3.41674709320068</t>
   </si>
   <si>
-    <t xml:space="preserve">3.351975440979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33578205108643</t>
+    <t xml:space="preserve">3.35197496414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33578181266785</t>
   </si>
   <si>
     <t xml:space="preserve">3.36816811561584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23862314224243</t>
+    <t xml:space="preserve">3.23862338066101</t>
   </si>
   <si>
     <t xml:space="preserve">3.31958889961243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27100944519043</t>
+    <t xml:space="preserve">3.27100968360901</t>
   </si>
   <si>
     <t xml:space="preserve">3.28720259666443</t>
@@ -554,10 +554,10 @@
     <t xml:space="preserve">3.22243022918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17385101318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20623731613159</t>
+    <t xml:space="preserve">3.17385053634644</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20623707771301</t>
   </si>
   <si>
     <t xml:space="preserve">3.1414647102356</t>
@@ -572,82 +572,82 @@
     <t xml:space="preserve">3.38436126708984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25481629371643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19004416465759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96334028244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97953367233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80140924453735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88237476348877</t>
+    <t xml:space="preserve">3.25481653213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19004392623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96334052085876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97953343391418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80140900611877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88237500190735</t>
   </si>
   <si>
     <t xml:space="preserve">2.86618161201477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84998846054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78521633148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75282979011536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72044348716736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83379554748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76902341842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73663663864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81760239601135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89856767654419</t>
+    <t xml:space="preserve">2.84998822212219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78521585464478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75283002853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72044372558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83379530906677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76902294158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73663687705994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81760191917419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89856791496277</t>
   </si>
   <si>
     <t xml:space="preserve">2.91476082801819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63947796821594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67186403274536</t>
+    <t xml:space="preserve">2.63947820663452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67186427116394</t>
   </si>
   <si>
     <t xml:space="preserve">2.62328505516052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68805718421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70425009727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60709190368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59089875221252</t>
+    <t xml:space="preserve">2.68805742263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70425057411194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6070921421051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5908989906311</t>
   </si>
   <si>
     <t xml:space="preserve">2.42896747589111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54231929779053</t>
+    <t xml:space="preserve">2.54231953620911</t>
   </si>
   <si>
     <t xml:space="preserve">2.46135377883911</t>
@@ -662,7 +662,7 @@
     <t xml:space="preserve">2.35488152503967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40607476234436</t>
+    <t xml:space="preserve">2.40607452392578</t>
   </si>
   <si>
     <t xml:space="preserve">2.28662443161011</t>
@@ -671,10 +671,10 @@
     <t xml:space="preserve">2.1330451965332</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08185195922852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.0647873878479</t>
+    <t xml:space="preserve">2.08185172080994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06478762626648</t>
   </si>
   <si>
     <t xml:space="preserve">2.03065896034241</t>
@@ -689,10 +689,10 @@
     <t xml:space="preserve">2.26956009864807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2183666229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32075333595276</t>
+    <t xml:space="preserve">2.21836638450623</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32075309753418</t>
   </si>
   <si>
     <t xml:space="preserve">2.55965399742126</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">2.54258966445923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45726823806763</t>
+    <t xml:space="preserve">2.45726799964905</t>
   </si>
   <si>
     <t xml:space="preserve">2.57671856880188</t>
@@ -710,19 +710,19 @@
     <t xml:space="preserve">2.62791156768799</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61084699630737</t>
+    <t xml:space="preserve">2.61084723472595</t>
   </si>
   <si>
     <t xml:space="preserve">2.64497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59378290176392</t>
+    <t xml:space="preserve">2.59378266334534</t>
   </si>
   <si>
     <t xml:space="preserve">2.69616889953613</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71323323249817</t>
+    <t xml:space="preserve">2.71323347091675</t>
   </si>
   <si>
     <t xml:space="preserve">2.44020342826843</t>
@@ -731,10 +731,10 @@
     <t xml:space="preserve">2.4231390953064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47433257102966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15010952949524</t>
+    <t xml:space="preserve">2.47433233261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15010929107666</t>
   </si>
   <si>
     <t xml:space="preserve">2.33781743049622</t>
@@ -749,7 +749,7 @@
     <t xml:space="preserve">2.23543095588684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37194585800171</t>
+    <t xml:space="preserve">2.37194609642029</t>
   </si>
   <si>
     <t xml:space="preserve">2.38901042938232</t>
@@ -758,46 +758,46 @@
     <t xml:space="preserve">2.20130252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18423795700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01359438896179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04772329330444</t>
+    <t xml:space="preserve">2.18423819541931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01359462738037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04772353172302</t>
   </si>
   <si>
     <t xml:space="preserve">2.11598062515259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91120851039886</t>
+    <t xml:space="preserve">1.91120839118958</t>
   </si>
   <si>
     <t xml:space="preserve">1.8770797252655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84295105934143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97946584224701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86001527309418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94533693790436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96240150928497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99652993679047</t>
+    <t xml:space="preserve">1.84295094013214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97946560382843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86001539230347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94533705711365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9624011516571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99653017520905</t>
   </si>
   <si>
     <t xml:space="preserve">2.81561946868896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90094137191772</t>
+    <t xml:space="preserve">2.9009416103363</t>
   </si>
   <si>
     <t xml:space="preserve">2.88387703895569</t>
@@ -809,7 +809,7 @@
     <t xml:space="preserve">2.73029756546021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67910432815552</t>
+    <t xml:space="preserve">2.6791045665741</t>
   </si>
   <si>
     <t xml:space="preserve">2.74736189842224</t>
@@ -818,13 +818,13 @@
     <t xml:space="preserve">2.832683801651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86681222915649</t>
+    <t xml:space="preserve">2.86681246757507</t>
   </si>
   <si>
     <t xml:space="preserve">2.79855489730835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78149056434631</t>
+    <t xml:space="preserve">2.78149080276489</t>
   </si>
   <si>
     <t xml:space="preserve">2.93506979942322</t>
@@ -836,16 +836,16 @@
     <t xml:space="preserve">3.02039170265198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00332760810852</t>
+    <t xml:space="preserve">3.00332736968994</t>
   </si>
   <si>
     <t xml:space="preserve">3.03745603561401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98626303672791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05452036857605</t>
+    <t xml:space="preserve">2.98626279830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05452060699463</t>
   </si>
   <si>
     <t xml:space="preserve">3.07158470153809</t>
@@ -863,10 +863,10 @@
     <t xml:space="preserve">3.06305241584778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16543912887573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19956755638123</t>
+    <t xml:space="preserve">3.16543889045715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1995677947998</t>
   </si>
   <si>
     <t xml:space="preserve">3.15690684318542</t>
@@ -875,7 +875,7 @@
     <t xml:space="preserve">3.2336962223053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27635717391968</t>
+    <t xml:space="preserve">3.2763569355011</t>
   </si>
   <si>
     <t xml:space="preserve">3.24222826957703</t>
@@ -884,19 +884,19 @@
     <t xml:space="preserve">3.26782488822937</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31048607826233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34461450576782</t>
+    <t xml:space="preserve">3.31048583984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3446147441864</t>
   </si>
   <si>
     <t xml:space="preserve">3.32755041122437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28488945960999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18250346183777</t>
+    <t xml:space="preserve">3.28488922119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18250322341919</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342150688171</t>
@@ -905,10 +905,10 @@
     <t xml:space="preserve">3.33710074424744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32836484909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24974250793457</t>
+    <t xml:space="preserve">3.32836508750916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24974226951599</t>
   </si>
   <si>
     <t xml:space="preserve">3.20606303215027</t>
@@ -929,10 +929,10 @@
     <t xml:space="preserve">3.36330842971802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49434638023376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58170509338379</t>
+    <t xml:space="preserve">3.49434661865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58170485496521</t>
   </si>
   <si>
     <t xml:space="preserve">3.56423354148865</t>
@@ -956,31 +956,31 @@
     <t xml:space="preserve">3.62538456916809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74768662452698</t>
+    <t xml:space="preserve">3.7476863861084</t>
   </si>
   <si>
     <t xml:space="preserve">3.69527125358582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66906332969666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60791301727295</t>
+    <t xml:space="preserve">3.66906356811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60791277885437</t>
   </si>
   <si>
     <t xml:space="preserve">3.55549788475037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66032767295837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65159177780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68653512001038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7040069103241</t>
+    <t xml:space="preserve">3.66032791137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65159201622009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68653535842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70400714874268</t>
   </si>
   <si>
     <t xml:space="preserve">3.75642275810242</t>
@@ -995,7 +995,7 @@
     <t xml:space="preserve">3.3458366394043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38951635360718</t>
+    <t xml:space="preserve">3.3895161151886</t>
   </si>
   <si>
     <t xml:space="preserve">3.42445969581604</t>
@@ -1025,7 +1025,7 @@
     <t xml:space="preserve">3.46813893318176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47687458992004</t>
+    <t xml:space="preserve">3.47687482833862</t>
   </si>
   <si>
     <t xml:space="preserve">3.79136610031128</t>
@@ -1034,7 +1034,7 @@
     <t xml:space="preserve">3.72147917747498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8787248134613</t>
+    <t xml:space="preserve">3.87872457504272</t>
   </si>
   <si>
     <t xml:space="preserve">4.17574453353882</t>
@@ -1049,7 +1049,7 @@
     <t xml:space="preserve">4.1844801902771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20195198059082</t>
+    <t xml:space="preserve">4.20195150375366</t>
   </si>
   <si>
     <t xml:space="preserve">4.25436639785767</t>
@@ -1058,10 +1058,10 @@
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493202209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98355484008789</t>
+    <t xml:space="preserve">3.90493226051331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98355507850647</t>
   </si>
   <si>
     <t xml:space="preserve">3.94861149787903</t>
@@ -1070,13 +1070,13 @@
     <t xml:space="preserve">3.93113970756531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08838510513306</t>
+    <t xml:space="preserve">4.08838558197021</t>
   </si>
   <si>
     <t xml:space="preserve">4.07091331481934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1233286857605</t>
+    <t xml:space="preserve">4.12332916259766</t>
   </si>
   <si>
     <t xml:space="preserve">4.00102663040161</t>
@@ -1085,13 +1085,13 @@
     <t xml:space="preserve">4.00976276397705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93987560272217</t>
+    <t xml:space="preserve">3.93987584114075</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21068811416626</t>
+    <t xml:space="preserve">4.2106876373291</t>
   </si>
   <si>
     <t xml:space="preserve">4.29804611206055</t>
@@ -1109,16 +1109,16 @@
     <t xml:space="preserve">4.14953660964966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16700839996338</t>
+    <t xml:space="preserve">4.16700792312622</t>
   </si>
   <si>
     <t xml:space="preserve">4.11459302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06217813491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78263020515442</t>
+    <t xml:space="preserve">4.06217765808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78262996673584</t>
   </si>
   <si>
     <t xml:space="preserve">3.80010175704956</t>
@@ -1127,13 +1127,13 @@
     <t xml:space="preserve">3.82630944252014</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83504509925842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84378123283386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77389454841614</t>
+    <t xml:space="preserve">3.83504557609558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84378147125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77389430999756</t>
   </si>
   <si>
     <t xml:space="preserve">4.03597021102905</t>
@@ -1148,13 +1148,13 @@
     <t xml:space="preserve">3.86125302314758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7651584148407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8175733089447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64285612106323</t>
+    <t xml:space="preserve">3.76515817642212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81757354736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64285635948181</t>
   </si>
   <si>
     <t xml:space="preserve">3.67779946327209</t>
@@ -1172,7 +1172,7 @@
     <t xml:space="preserve">3.92240381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61664867401123</t>
+    <t xml:space="preserve">3.61664843559265</t>
   </si>
   <si>
     <t xml:space="preserve">3.39825224876404</t>
@@ -1181,19 +1181,19 @@
     <t xml:space="preserve">3.23227071762085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0575532913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97019457817078</t>
+    <t xml:space="preserve">3.05755305290222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97019481658936</t>
   </si>
   <si>
     <t xml:space="preserve">2.95272302627563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91777920722961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90904355049133</t>
+    <t xml:space="preserve">2.91777944564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90904331207275</t>
   </si>
   <si>
     <t xml:space="preserve">3.37204432487488</t>
@@ -1202,13 +1202,13 @@
     <t xml:space="preserve">3.38078022003174</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41572403907776</t>
+    <t xml:space="preserve">3.41572380065918</t>
   </si>
   <si>
     <t xml:space="preserve">3.31962895393372</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27594995498657</t>
+    <t xml:space="preserve">3.27595019340515</t>
   </si>
   <si>
     <t xml:space="preserve">3.28468561172485</t>
@@ -56239,7 +56239,7 @@
     </row>
     <row r="2084">
       <c r="A2084" s="1" t="n">
-        <v>45996.6748958333</v>
+        <v>45996.3333333333</v>
       </c>
       <c r="B2084" t="n">
         <v>14100</v>
@@ -56260,6 +56260,32 @@
         <v>572</v>
       </c>
       <c r="H2084" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2085">
+      <c r="A2085" s="1" t="n">
+        <v>45999.6911805556</v>
+      </c>
+      <c r="B2085" t="n">
+        <v>17636</v>
+      </c>
+      <c r="C2085" t="n">
+        <v>3.38000011444092</v>
+      </c>
+      <c r="D2085" t="n">
+        <v>3.27999997138977</v>
+      </c>
+      <c r="E2085" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="F2085" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="G2085" t="s">
+        <v>572</v>
+      </c>
+      <c r="H2085" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02345752716064</t>
+    <t xml:space="preserve">3.02345776557922</t>
   </si>
   <si>
     <t xml:space="preserve">NDT.MI</t>
@@ -47,19 +47,19 @@
     <t xml:space="preserve">2.96519923210144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88901543617249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98013734817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97266793251038</t>
+    <t xml:space="preserve">2.88901519775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98013710975647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97266817092896</t>
   </si>
   <si>
     <t xml:space="preserve">2.94578003883362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95773005485535</t>
+    <t xml:space="preserve">2.95773029327393</t>
   </si>
   <si>
     <t xml:space="preserve">2.96221160888672</t>
@@ -68,40 +68,40 @@
     <t xml:space="preserve">2.9353232383728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91291618347168</t>
+    <t xml:space="preserve">2.91291642189026</t>
   </si>
   <si>
     <t xml:space="preserve">2.9786434173584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98611259460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03540825843811</t>
+    <t xml:space="preserve">2.98611235618591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03540802001953</t>
   </si>
   <si>
     <t xml:space="preserve">3.05632138252258</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05930924415588</t>
+    <t xml:space="preserve">3.05930876731873</t>
   </si>
   <si>
     <t xml:space="preserve">3.05034589767456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98760604858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95026159286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01598858833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01001334190369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02495145797729</t>
+    <t xml:space="preserve">2.98760628700256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95026135444641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01598882675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01001310348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02495121955872</t>
   </si>
   <si>
     <t xml:space="preserve">3.0174822807312</t>
@@ -116,70 +116,70 @@
     <t xml:space="preserve">3.04437112808228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.959223985672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00254416465759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92785406112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90843510627747</t>
+    <t xml:space="preserve">2.95922374725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00254440307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92785429954529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90843486785889</t>
   </si>
   <si>
     <t xml:space="preserve">2.896484375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91889142990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9159038066864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92038536071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90544724464417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90992856025696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9233729839325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8382260799408</t>
+    <t xml:space="preserve">2.91889119148254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91590404510498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92038512229919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90544748306274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9099280834198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92337274551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83822560310364</t>
   </si>
   <si>
     <t xml:space="preserve">2.86063313484192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82627558708191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77996778488159</t>
+    <t xml:space="preserve">2.82627582550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77996730804443</t>
   </si>
   <si>
     <t xml:space="preserve">2.84569501876831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86810231208801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88304018974304</t>
+    <t xml:space="preserve">2.86810183525085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88303995132446</t>
   </si>
   <si>
     <t xml:space="preserve">2.79639959335327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87557125091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89797806739807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80088090896606</t>
+    <t xml:space="preserve">2.87557101249695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89797830581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80088114738464</t>
   </si>
   <si>
     <t xml:space="preserve">2.74262261390686</t>
@@ -188,37 +188,37 @@
     <t xml:space="preserve">2.8217945098877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75009179115295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76353597640991</t>
+    <t xml:space="preserve">2.75009155273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76353621482849</t>
   </si>
   <si>
     <t xml:space="preserve">2.77847385406494</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78594303131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79341220855713</t>
+    <t xml:space="preserve">2.78594279289246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79341197013855</t>
   </si>
   <si>
     <t xml:space="preserve">2.69631481170654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65150046348572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62162470817566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53946566581726</t>
+    <t xml:space="preserve">2.6515007019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62162446975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53946542739868</t>
   </si>
   <si>
     <t xml:space="preserve">2.5693416595459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61415553092957</t>
+    <t xml:space="preserve">2.61415576934814</t>
   </si>
   <si>
     <t xml:space="preserve">2.65896964073181</t>
@@ -227,34 +227,34 @@
     <t xml:space="preserve">2.68884563446045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70378375053406</t>
+    <t xml:space="preserve">2.70378398895264</t>
   </si>
   <si>
     <t xml:space="preserve">2.77100467681885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81581902503967</t>
+    <t xml:space="preserve">2.81581926345825</t>
   </si>
   <si>
     <t xml:space="preserve">2.73365998268127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66643881797791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68137669563293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74112892150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72619104385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83075714111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.893150806427</t>
+    <t xml:space="preserve">2.66643857955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68137645721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74112868309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72619080543518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8307569026947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89315056800842</t>
   </si>
   <si>
     <t xml:space="preserve">2.69871854782104</t>
@@ -263,43 +263,43 @@
     <t xml:space="preserve">2.83870959281921</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93203687667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87759613990784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8309326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81537771224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84648656845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79982304573059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73760509490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76093649864197</t>
+    <t xml:space="preserve">2.93203735351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87759637832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83093237876892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81537795066833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84648704528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79982328414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73760485649109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76093673706055</t>
   </si>
   <si>
     <t xml:space="preserve">2.80760049819946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00980997085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9553689956665</t>
+    <t xml:space="preserve">3.00980973243713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95536851882935</t>
   </si>
   <si>
     <t xml:space="preserve">2.90870523452759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88537335395813</t>
+    <t xml:space="preserve">2.88537311553955</t>
   </si>
   <si>
     <t xml:space="preserve">2.82315540313721</t>
@@ -314,7 +314,7 @@
     <t xml:space="preserve">2.91648268699646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8542640209198</t>
+    <t xml:space="preserve">2.85426425933838</t>
   </si>
   <si>
     <t xml:space="preserve">2.7298276424408</t>
@@ -323,22 +323,22 @@
     <t xml:space="preserve">2.68316388130188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72205066680908</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75315928459167</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70649600028992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93981432914734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99425530433655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97870063781738</t>
+    <t xml:space="preserve">2.7220504283905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75315952301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70649576187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93981409072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99425554275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97870087623596</t>
   </si>
   <si>
     <t xml:space="preserve">2.86981868743896</t>
@@ -356,16 +356,16 @@
     <t xml:space="preserve">2.550950050354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51984095573425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41095876693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34096312522888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34874081611633</t>
+    <t xml:space="preserve">2.51984119415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41095900535583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34096360206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34874057769775</t>
   </si>
   <si>
     <t xml:space="preserve">2.36429524421692</t>
@@ -374,19 +374,19 @@
     <t xml:space="preserve">2.2554132938385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24763607978821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32540893554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23208141326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18541717529297</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27874493598938</t>
+    <t xml:space="preserve">2.24763584136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3254086971283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23208093643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18541765213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27874517440796</t>
   </si>
   <si>
     <t xml:space="preserve">2.26319050788879</t>
@@ -395,13 +395,13 @@
     <t xml:space="preserve">2.21652674674988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06875824928284</t>
+    <t xml:space="preserve">2.06875801086426</t>
   </si>
   <si>
     <t xml:space="preserve">2.14653134346008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10764503479004</t>
+    <t xml:space="preserve">2.10764479637146</t>
   </si>
   <si>
     <t xml:space="preserve">2.1543083190918</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">2.17764019966125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22430396080017</t>
+    <t xml:space="preserve">2.22430372238159</t>
   </si>
   <si>
     <t xml:space="preserve">2.35651779174805</t>
@@ -422,55 +422,55 @@
     <t xml:space="preserve">2.52761793136597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43429088592529</t>
+    <t xml:space="preserve">2.43429064750671</t>
   </si>
   <si>
     <t xml:space="preserve">2.44206809997559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55872702598572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44984531402588</t>
+    <t xml:space="preserve">2.5587272644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44984555244446</t>
   </si>
   <si>
     <t xml:space="preserve">2.37207221984863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33318638801575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29429960250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37984991073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71427297592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58205914497375</t>
+    <t xml:space="preserve">2.33318591117859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29429984092712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37984943389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71427321434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58205890655518</t>
   </si>
   <si>
     <t xml:space="preserve">2.62872290611267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65983176231384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57428169250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67538690567017</t>
+    <t xml:space="preserve">2.659832239151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57428193092346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67538666725159</t>
   </si>
   <si>
     <t xml:space="preserve">2.64427757263184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69094133377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76871395111084</t>
+    <t xml:space="preserve">2.69094085693359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76871418952942</t>
   </si>
   <si>
     <t xml:space="preserve">2.90092778205872</t>
@@ -479,7 +479,7 @@
     <t xml:space="preserve">2.9631462097168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92426013946533</t>
+    <t xml:space="preserve">2.92425990104675</t>
   </si>
   <si>
     <t xml:space="preserve">2.97092342376709</t>
@@ -488,10 +488,10 @@
     <t xml:space="preserve">3.01758742332458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04869675636292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03314161300659</t>
+    <t xml:space="preserve">3.04869651794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03314208984375</t>
   </si>
   <si>
     <t xml:space="preserve">3.06425094604492</t>
@@ -500,76 +500,76 @@
     <t xml:space="preserve">3.07980561256409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06049919128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0281126499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01191997528076</t>
+    <t xml:space="preserve">3.0604989528656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02811288833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01191973686218</t>
   </si>
   <si>
     <t xml:space="preserve">3.10907816886902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09288501739502</t>
+    <t xml:space="preserve">3.0928852558136</t>
   </si>
   <si>
     <t xml:space="preserve">3.12527132034302</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07669234275818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99572658538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30339574813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41674733161926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35197472572327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33578157424927</t>
+    <t xml:space="preserve">3.0766921043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99572682380676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30339598655701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41674757003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35197520256042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33578205108643</t>
   </si>
   <si>
     <t xml:space="preserve">3.36816811561584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23862338066101</t>
+    <t xml:space="preserve">3.23862314224243</t>
   </si>
   <si>
     <t xml:space="preserve">3.31958889961243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27100944519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28720259666443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22242999076843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17385125160217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20623707771301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1414647102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40055441856384</t>
+    <t xml:space="preserve">3.27100920677185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28720235824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22243022918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17385101318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20623731613159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14146494865417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40055418014526</t>
   </si>
   <si>
     <t xml:space="preserve">3.49771356582642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38436150550842</t>
+    <t xml:space="preserve">3.38436102867126</t>
   </si>
   <si>
     <t xml:space="preserve">3.25481653213501</t>
@@ -578,13 +578,13 @@
     <t xml:space="preserve">3.19004416465759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96334004402161</t>
+    <t xml:space="preserve">2.96334028244019</t>
   </si>
   <si>
     <t xml:space="preserve">2.97953367233276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80140924453735</t>
+    <t xml:space="preserve">2.80140900611877</t>
   </si>
   <si>
     <t xml:space="preserve">2.88237476348877</t>
@@ -608,22 +608,22 @@
     <t xml:space="preserve">2.83379554748535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76902294158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73663663864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81760263442993</t>
+    <t xml:space="preserve">2.76902318000793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73663687705994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81760239601135</t>
   </si>
   <si>
     <t xml:space="preserve">2.89856767654419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91476082801819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63947820663452</t>
+    <t xml:space="preserve">2.91476106643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63947796821594</t>
   </si>
   <si>
     <t xml:space="preserve">2.67186427116394</t>
@@ -632,28 +632,28 @@
     <t xml:space="preserve">2.62328505516052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68805742263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70425057411194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60709166526794</t>
+    <t xml:space="preserve">2.68805694580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70425009727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60709190368652</t>
   </si>
   <si>
     <t xml:space="preserve">2.59089875221252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42896771430969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54231929779053</t>
+    <t xml:space="preserve">2.42896747589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54231905937195</t>
   </si>
   <si>
     <t xml:space="preserve">2.46135377883911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3156156539917</t>
+    <t xml:space="preserve">2.31561541557312</t>
   </si>
   <si>
     <t xml:space="preserve">2.2994225025177</t>
@@ -665,22 +665,22 @@
     <t xml:space="preserve">2.40607476234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28662419319153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13304495811462</t>
+    <t xml:space="preserve">2.28662443161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1330451965332</t>
   </si>
   <si>
     <t xml:space="preserve">2.08185195922852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06478762626648</t>
+    <t xml:space="preserve">2.0647873878479</t>
   </si>
   <si>
     <t xml:space="preserve">2.03065896034241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16717386245728</t>
+    <t xml:space="preserve">2.1671736240387</t>
   </si>
   <si>
     <t xml:space="preserve">2.09891629219055</t>
@@ -689,16 +689,16 @@
     <t xml:space="preserve">2.26955986022949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21836686134338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32075309753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55965423583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54258966445923</t>
+    <t xml:space="preserve">2.2183666229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32075333595276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55965399742126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54258990287781</t>
   </si>
   <si>
     <t xml:space="preserve">2.45726799964905</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">2.62791132926941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61084723472595</t>
+    <t xml:space="preserve">2.61084699630737</t>
   </si>
   <si>
     <t xml:space="preserve">2.64497566223145</t>
@@ -734,13 +734,13 @@
     <t xml:space="preserve">2.47433233261108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15010929107666</t>
+    <t xml:space="preserve">2.15010952949524</t>
   </si>
   <si>
     <t xml:space="preserve">2.33781743049622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30368852615356</t>
+    <t xml:space="preserve">2.30368876457214</t>
   </si>
   <si>
     <t xml:space="preserve">2.25249552726746</t>
@@ -761,37 +761,37 @@
     <t xml:space="preserve">2.18423795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01359415054321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04772329330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11598038673401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91120827198029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8770797252655</t>
+    <t xml:space="preserve">2.01359438896179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04772305488586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11598062515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91120851039886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87707960605621</t>
   </si>
   <si>
     <t xml:space="preserve">1.84295105934143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97946560382843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86001527309418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94533717632294</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96240162849426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99653005599976</t>
+    <t xml:space="preserve">1.97946584224701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86001539230347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94533693790436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96240150928497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99652993679047</t>
   </si>
   <si>
     <t xml:space="preserve">2.81561946868896</t>
@@ -800,37 +800,37 @@
     <t xml:space="preserve">2.90094137191772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88387680053711</t>
+    <t xml:space="preserve">2.88387703895569</t>
   </si>
   <si>
     <t xml:space="preserve">2.76442646980286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73029780387878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6791045665741</t>
+    <t xml:space="preserve">2.73029756546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67910432815552</t>
   </si>
   <si>
     <t xml:space="preserve">2.74736189842224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.832683801651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86681246757507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79855513572693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78149080276489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93507027626038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96919894218445</t>
+    <t xml:space="preserve">2.83268356323242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86681222915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79855489730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78149056434631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9350700378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96919870376587</t>
   </si>
   <si>
     <t xml:space="preserve">3.02039170265198</t>
@@ -842,13 +842,13 @@
     <t xml:space="preserve">3.03745603561401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98626327514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05452036857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07158470153809</t>
+    <t xml:space="preserve">2.98626303672791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05452013015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07158493995667</t>
   </si>
   <si>
     <t xml:space="preserve">3.13984251022339</t>
@@ -857,10 +857,10 @@
     <t xml:space="preserve">3.11424589157104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1313099861145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06305265426636</t>
+    <t xml:space="preserve">3.13131022453308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06305241584778</t>
   </si>
   <si>
     <t xml:space="preserve">3.16543889045715</t>
@@ -869,16 +869,16 @@
     <t xml:space="preserve">3.19956755638123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15690660476685</t>
+    <t xml:space="preserve">3.15690684318542</t>
   </si>
   <si>
     <t xml:space="preserve">3.2336962223053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2763569355011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24222850799561</t>
+    <t xml:space="preserve">3.27635717391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24222826957703</t>
   </si>
   <si>
     <t xml:space="preserve">3.26782488822937</t>
@@ -887,34 +887,34 @@
     <t xml:space="preserve">3.31048607826233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34461498260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32755017280579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28488922119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18250298500061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29342126846313</t>
+    <t xml:space="preserve">3.34461450576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32755041122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28488945960999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18250322341919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29342150688171</t>
   </si>
   <si>
     <t xml:space="preserve">3.33710074424744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32836508750916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29342150688171</t>
+    <t xml:space="preserve">3.32836484909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29342174530029</t>
   </si>
   <si>
     <t xml:space="preserve">3.24974226951599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20606279373169</t>
+    <t xml:space="preserve">3.20606303215027</t>
   </si>
   <si>
     <t xml:space="preserve">3.15364766120911</t>
@@ -926,7 +926,7 @@
     <t xml:space="preserve">3.17111968994141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26721382141113</t>
+    <t xml:space="preserve">3.26721405982971</t>
   </si>
   <si>
     <t xml:space="preserve">3.36330842971802</t>
@@ -935,55 +935,55 @@
     <t xml:space="preserve">3.49434638023376</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58170533180237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56423330307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59044098854065</t>
+    <t xml:space="preserve">3.58170509338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56423354148865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59044122695923</t>
   </si>
   <si>
     <t xml:space="preserve">3.5030825138092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51181840896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54676175117493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63411998748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62538456916809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7476863861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69527149200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66906380653381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60791277885437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55549788475037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66032814979553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65159201622009</t>
+    <t xml:space="preserve">3.51181817054749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54676151275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63412046432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62538480758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74768662452698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69527125358582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66906356811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60791301727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55549764633179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66032791137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65159177780151</t>
   </si>
   <si>
     <t xml:space="preserve">3.68653535842896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7040069103241</t>
+    <t xml:space="preserve">3.70400714874268</t>
   </si>
   <si>
     <t xml:space="preserve">3.75642251968384</t>
@@ -1010,19 +1010,19 @@
     <t xml:space="preserve">3.44193148612976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48561072349548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40698790550232</t>
+    <t xml:space="preserve">3.4856104850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4069881439209</t>
   </si>
   <si>
     <t xml:space="preserve">3.35457253456116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4594030380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52928996086121</t>
+    <t xml:space="preserve">3.45940327644348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52928972244263</t>
   </si>
   <si>
     <t xml:space="preserve">3.46813893318176</t>
@@ -1031,22 +1031,22 @@
     <t xml:space="preserve">3.47687458992004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79136610031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72147917747498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87872457504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17574405670166</t>
+    <t xml:space="preserve">3.79136633872986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7214789390564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8787248134613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17574453353882</t>
   </si>
   <si>
     <t xml:space="preserve">4.31551790237427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35046100616455</t>
+    <t xml:space="preserve">4.35046148300171</t>
   </si>
   <si>
     <t xml:space="preserve">4.18447971343994</t>
@@ -1061,25 +1061,25 @@
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493226051331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98355507850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94861173629761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93113970756531</t>
+    <t xml:space="preserve">3.90493202209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98355484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94861197471619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93114018440247</t>
   </si>
   <si>
     <t xml:space="preserve">4.08838510513306</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07091379165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12332820892334</t>
+    <t xml:space="preserve">4.07091331481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1233286857605</t>
   </si>
   <si>
     <t xml:space="preserve">4.00102663040161</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">4.00976276397705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93987560272217</t>
+    <t xml:space="preserve">3.93987607955933</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
@@ -1097,31 +1097,31 @@
     <t xml:space="preserve">4.2106876373291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29804658889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28930997848511</t>
+    <t xml:space="preserve">4.29804611206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28931045532227</t>
   </si>
   <si>
     <t xml:space="preserve">4.21942329406738</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19321632385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14953660964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16700839996338</t>
+    <t xml:space="preserve">4.19321584701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1495361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16700792312622</t>
   </si>
   <si>
     <t xml:space="preserve">4.11459302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06217765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78263020515442</t>
+    <t xml:space="preserve">4.06217813491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78262996673584</t>
   </si>
   <si>
     <t xml:space="preserve">3.80010175704956</t>
@@ -1130,10 +1130,10 @@
     <t xml:space="preserve">3.82630968093872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.835045337677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84378123283386</t>
+    <t xml:space="preserve">3.83504509925842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84378099441528</t>
   </si>
   <si>
     <t xml:space="preserve">3.77389454841614</t>
@@ -1142,16 +1142,16 @@
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734763145447</t>
+    <t xml:space="preserve">3.95734786987305</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.861252784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76515817642212</t>
+    <t xml:space="preserve">3.86125302314758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76515865325928</t>
   </si>
   <si>
     <t xml:space="preserve">3.8175733089447</t>
@@ -1163,52 +1163,52 @@
     <t xml:space="preserve">3.67779970169067</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7389509677887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85251712799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71274328231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92240357398987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61664843559265</t>
+    <t xml:space="preserve">3.73895072937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85251665115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71274304389954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92240381240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61664867401123</t>
   </si>
   <si>
     <t xml:space="preserve">3.39825224876404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23227047920227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05755352973938</t>
+    <t xml:space="preserve">3.23227071762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0575532913208</t>
   </si>
   <si>
     <t xml:space="preserve">2.97019457817078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95272278785706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91777944564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90904355049133</t>
+    <t xml:space="preserve">2.95272302627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91777920722961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90904331207275</t>
   </si>
   <si>
     <t xml:space="preserve">3.37204432487488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38077998161316</t>
+    <t xml:space="preserve">3.38078022003174</t>
   </si>
   <si>
     <t xml:space="preserve">3.41572380065918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31962919235229</t>
+    <t xml:space="preserve">3.31962895393372</t>
   </si>
   <si>
     <t xml:space="preserve">3.27594995498657</t>
@@ -56297,7 +56297,7 @@
     </row>
     <row r="2086">
       <c r="A2086" s="1" t="n">
-        <v>46000.6912615741</v>
+        <v>46000.3333333333</v>
       </c>
       <c r="B2086" t="n">
         <v>58276</v>
@@ -56318,6 +56318,32 @@
         <v>578</v>
       </c>
       <c r="H2086" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2087">
+      <c r="A2087" s="1" t="n">
+        <v>46001.6913078704</v>
+      </c>
+      <c r="B2087" t="n">
+        <v>56746</v>
+      </c>
+      <c r="C2087" t="n">
+        <v>3.44000005722046</v>
+      </c>
+      <c r="D2087" t="n">
+        <v>3.35999989509583</v>
+      </c>
+      <c r="E2087" t="n">
+        <v>3.44000005722046</v>
+      </c>
+      <c r="F2087" t="n">
+        <v>3.40000009536743</v>
+      </c>
+      <c r="G2087" t="s">
+        <v>578</v>
+      </c>
+      <c r="H2087" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="579" uniqueCount="579">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="580">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,10 +44,10 @@
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519923210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88901519775391</t>
+    <t xml:space="preserve">2.96519947052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88901543617249</t>
   </si>
   <si>
     <t xml:space="preserve">2.98013710975647</t>
@@ -62,16 +62,16 @@
     <t xml:space="preserve">2.95773029327393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96221160888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9353232383728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91291642189026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9786434173584</t>
+    <t xml:space="preserve">2.96221137046814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93532371520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91291618347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97864365577698</t>
   </si>
   <si>
     <t xml:space="preserve">2.98611235618591</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">3.03540802001953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05632138252258</t>
+    <t xml:space="preserve">3.056321144104</t>
   </si>
   <si>
     <t xml:space="preserve">3.05930876731873</t>
@@ -98,109 +98,109 @@
     <t xml:space="preserve">3.01598882675171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01001310348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02495121955872</t>
+    <t xml:space="preserve">3.01001334190369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02495145797729</t>
   </si>
   <si>
     <t xml:space="preserve">3.0174822807312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03092646598816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99955654144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04437112808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95922374725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00254440307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92785429954529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90843486785889</t>
+    <t xml:space="preserve">3.03092670440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99955677986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0443708896637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.959223985672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00254416465759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92785406112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90843462944031</t>
   </si>
   <si>
     <t xml:space="preserve">2.896484375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91889119148254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91590404510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92038512229919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90544748306274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9099280834198</t>
+    <t xml:space="preserve">2.91889142990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91590356826782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92038536071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90544724464417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90992879867554</t>
   </si>
   <si>
     <t xml:space="preserve">2.92337274551392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83822560310364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86063313484192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82627582550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77996730804443</t>
+    <t xml:space="preserve">2.8382260799408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86063289642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82627534866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77996754646301</t>
   </si>
   <si>
     <t xml:space="preserve">2.84569501876831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86810183525085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88303995132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79639959335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87557101249695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89797830581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80088114738464</t>
+    <t xml:space="preserve">2.86810207366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88304018974304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79639935493469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87557125091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89797806739807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80088090896606</t>
   </si>
   <si>
     <t xml:space="preserve">2.74262261390686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8217945098877</t>
+    <t xml:space="preserve">2.82179403305054</t>
   </si>
   <si>
     <t xml:space="preserve">2.75009155273438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76353621482849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77847385406494</t>
+    <t xml:space="preserve">2.76353549957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77847409248352</t>
   </si>
   <si>
     <t xml:space="preserve">2.78594279289246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79341197013855</t>
+    <t xml:space="preserve">2.79341220855713</t>
   </si>
   <si>
     <t xml:space="preserve">2.69631481170654</t>
@@ -209,16 +209,16 @@
     <t xml:space="preserve">2.6515007019043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62162446975708</t>
+    <t xml:space="preserve">2.6216242313385</t>
   </si>
   <si>
     <t xml:space="preserve">2.53946542739868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5693416595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61415576934814</t>
+    <t xml:space="preserve">2.56934142112732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61415553092957</t>
   </si>
   <si>
     <t xml:space="preserve">2.65896964073181</t>
@@ -227,49 +227,49 @@
     <t xml:space="preserve">2.68884563446045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70378398895264</t>
+    <t xml:space="preserve">2.70378375053406</t>
   </si>
   <si>
     <t xml:space="preserve">2.77100467681885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81581926345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73365998268127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66643857955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68137645721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74112868309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72619080543518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8307569026947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89315056800842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69871854782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83870959281921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93203735351562</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87759637832642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83093237876892</t>
+    <t xml:space="preserve">2.81581878662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7336597442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66643881797791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68137669563293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74112892150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72619104385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83075666427612</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.893150806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69871830940247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83870983123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93203687667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87759590148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8309326171875</t>
   </si>
   <si>
     <t xml:space="preserve">2.81537795066833</t>
@@ -278,13 +278,13 @@
     <t xml:space="preserve">2.84648704528809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79982328414917</t>
+    <t xml:space="preserve">2.79982304573059</t>
   </si>
   <si>
     <t xml:space="preserve">2.73760485649109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76093673706055</t>
+    <t xml:space="preserve">2.76093697547913</t>
   </si>
   <si>
     <t xml:space="preserve">2.80760049819946</t>
@@ -293,31 +293,31 @@
     <t xml:space="preserve">3.00980973243713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95536851882935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90870523452759</t>
+    <t xml:space="preserve">2.9553689956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90870547294617</t>
   </si>
   <si>
     <t xml:space="preserve">2.88537311553955</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82315540313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86204171180725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00203251838684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91648268699646</t>
+    <t xml:space="preserve">2.82315516471863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86204147338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00203275680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91648244857788</t>
   </si>
   <si>
     <t xml:space="preserve">2.85426425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7298276424408</t>
+    <t xml:space="preserve">2.72982740402222</t>
   </si>
   <si>
     <t xml:space="preserve">2.68316388130188</t>
@@ -332,40 +332,40 @@
     <t xml:space="preserve">2.70649576187134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93981409072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99425554275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97870087623596</t>
+    <t xml:space="preserve">2.93981456756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99425530433655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97870063781738</t>
   </si>
   <si>
     <t xml:space="preserve">2.86981868743896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94759154319763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98647785186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63650035858154</t>
+    <t xml:space="preserve">2.94759130477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98647809028625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63650012016296</t>
   </si>
   <si>
     <t xml:space="preserve">2.550950050354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51984119415283</t>
+    <t xml:space="preserve">2.51984095573425</t>
   </si>
   <si>
     <t xml:space="preserve">2.41095900535583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34096360206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34874057769775</t>
+    <t xml:space="preserve">2.34096312522888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34874081611633</t>
   </si>
   <si>
     <t xml:space="preserve">2.36429524421692</t>
@@ -380,7 +380,7 @@
     <t xml:space="preserve">2.3254086971283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23208093643188</t>
+    <t xml:space="preserve">2.23208117485046</t>
   </si>
   <si>
     <t xml:space="preserve">2.18541765213013</t>
@@ -389,13 +389,13 @@
     <t xml:space="preserve">2.27874517440796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26319050788879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21652674674988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06875801086426</t>
+    <t xml:space="preserve">2.26319026947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2165265083313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06875848770142</t>
   </si>
   <si>
     <t xml:space="preserve">2.14653134346008</t>
@@ -404,13 +404,13 @@
     <t xml:space="preserve">2.10764479637146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1543083190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17764019966125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22430372238159</t>
+    <t xml:space="preserve">2.15430855751038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17764043807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22430396080017</t>
   </si>
   <si>
     <t xml:space="preserve">2.35651779174805</t>
@@ -419,40 +419,40 @@
     <t xml:space="preserve">2.4887318611145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52761793136597</t>
+    <t xml:space="preserve">2.52761816978455</t>
   </si>
   <si>
     <t xml:space="preserve">2.43429064750671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44206809997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5587272644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44984555244446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37207221984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33318591117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29429984092712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37984943389893</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71427321434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58205890655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62872290611267</t>
+    <t xml:space="preserve">2.44206786155701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55872750282288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44984531402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37207245826721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33318638801575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29429960250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37984991073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71427297592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58205914497375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62872314453125</t>
   </si>
   <si>
     <t xml:space="preserve">2.659832239151</t>
@@ -467,10 +467,10 @@
     <t xml:space="preserve">2.64427757263184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69094085693359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76871418952942</t>
+    <t xml:space="preserve">2.69094133377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76871395111084</t>
   </si>
   <si>
     <t xml:space="preserve">2.90092778205872</t>
@@ -491,43 +491,43 @@
     <t xml:space="preserve">3.04869651794434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03314208984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06425094604492</t>
+    <t xml:space="preserve">3.03314185142517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0642511844635</t>
   </si>
   <si>
     <t xml:space="preserve">3.07980561256409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0604989528656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02811288833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01191973686218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10907816886902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0928852558136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12527132034302</t>
+    <t xml:space="preserve">3.06049919128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02811312675476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01191997528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1090784072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09288501739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1252715587616</t>
   </si>
   <si>
     <t xml:space="preserve">3.0766921043396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99572682380676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30339598655701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41674757003784</t>
+    <t xml:space="preserve">2.9957263469696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30339574813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41674733161926</t>
   </si>
   <si>
     <t xml:space="preserve">3.35197520256042</t>
@@ -536,43 +536,43 @@
     <t xml:space="preserve">3.33578205108643</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36816811561584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23862314224243</t>
+    <t xml:space="preserve">3.36816835403442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23862338066101</t>
   </si>
   <si>
     <t xml:space="preserve">3.31958889961243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27100920677185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28720235824585</t>
+    <t xml:space="preserve">3.27100944519043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28720259666443</t>
   </si>
   <si>
     <t xml:space="preserve">3.22243022918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17385101318359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20623731613159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14146494865417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40055418014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49771356582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38436102867126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25481653213501</t>
+    <t xml:space="preserve">3.17385077476501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20623707771301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1414647102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40055441856384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49771308898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38436126708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25481629371643</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004416465759</t>
@@ -581,13 +581,13 @@
     <t xml:space="preserve">2.96334028244019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97953367233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80140900611877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88237476348877</t>
+    <t xml:space="preserve">2.97953343391418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80140924453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88237452507019</t>
   </si>
   <si>
     <t xml:space="preserve">2.86618161201477</t>
@@ -596,13 +596,13 @@
     <t xml:space="preserve">2.84998846054077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78521633148193</t>
+    <t xml:space="preserve">2.78521609306335</t>
   </si>
   <si>
     <t xml:space="preserve">2.75283002853394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72044348716736</t>
+    <t xml:space="preserve">2.72044372558594</t>
   </si>
   <si>
     <t xml:space="preserve">2.83379554748535</t>
@@ -614,13 +614,13 @@
     <t xml:space="preserve">2.73663687705994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81760239601135</t>
+    <t xml:space="preserve">2.81760215759277</t>
   </si>
   <si>
     <t xml:space="preserve">2.89856767654419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91476106643677</t>
+    <t xml:space="preserve">2.91476082801819</t>
   </si>
   <si>
     <t xml:space="preserve">2.63947796821594</t>
@@ -629,31 +629,31 @@
     <t xml:space="preserve">2.67186427116394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62328505516052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68805694580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70425009727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60709190368652</t>
+    <t xml:space="preserve">2.62328481674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68805718421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70425033569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60709166526794</t>
   </si>
   <si>
     <t xml:space="preserve">2.59089875221252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42896747589111</t>
+    <t xml:space="preserve">2.42896771430969</t>
   </si>
   <si>
     <t xml:space="preserve">2.54231905937195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46135377883911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31561541557312</t>
+    <t xml:space="preserve">2.46135354042053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3156156539917</t>
   </si>
   <si>
     <t xml:space="preserve">2.2994225025177</t>
@@ -665,19 +665,19 @@
     <t xml:space="preserve">2.40607476234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28662443161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1330451965332</t>
+    <t xml:space="preserve">2.28662419319153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13304495811462</t>
   </si>
   <si>
     <t xml:space="preserve">2.08185195922852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0647873878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03065896034241</t>
+    <t xml:space="preserve">2.06478762626648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03065872192383</t>
   </si>
   <si>
     <t xml:space="preserve">2.1671736240387</t>
@@ -686,28 +686,28 @@
     <t xml:space="preserve">2.09891629219055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26955986022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2183666229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32075333595276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55965399742126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54258990287781</t>
+    <t xml:space="preserve">2.26956009864807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21836686134338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32075309753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55965423583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54258966445923</t>
   </si>
   <si>
     <t xml:space="preserve">2.45726799964905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57671856880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62791132926941</t>
+    <t xml:space="preserve">2.5767183303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62791156768799</t>
   </si>
   <si>
     <t xml:space="preserve">2.61084699630737</t>
@@ -722,19 +722,19 @@
     <t xml:space="preserve">2.69616913795471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71323323249817</t>
+    <t xml:space="preserve">2.71323347091675</t>
   </si>
   <si>
     <t xml:space="preserve">2.44020342826843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4231390953064</t>
+    <t xml:space="preserve">2.42313933372498</t>
   </si>
   <si>
     <t xml:space="preserve">2.47433233261108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15010952949524</t>
+    <t xml:space="preserve">2.15010929107666</t>
   </si>
   <si>
     <t xml:space="preserve">2.33781743049622</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">2.30368876457214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25249552726746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23543095588684</t>
+    <t xml:space="preserve">2.25249576568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23543119430542</t>
   </si>
   <si>
     <t xml:space="preserve">2.37194609642029</t>
@@ -761,40 +761,40 @@
     <t xml:space="preserve">2.18423795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01359438896179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04772305488586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11598062515259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91120851039886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87707960605621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84295105934143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97946584224701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86001539230347</t>
+    <t xml:space="preserve">2.01359415054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04772329330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11598038673401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91120827198029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87707984447479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84295094013214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97946560382843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86001515388489</t>
   </si>
   <si>
     <t xml:space="preserve">1.94533693790436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96240150928497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99652993679047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81561946868896</t>
+    <t xml:space="preserve">1.96240139007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99653005599976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81561923027039</t>
   </si>
   <si>
     <t xml:space="preserve">2.90094137191772</t>
@@ -806,10 +806,10 @@
     <t xml:space="preserve">2.76442646980286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73029756546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67910432815552</t>
+    <t xml:space="preserve">2.73029780387878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6791045665741</t>
   </si>
   <si>
     <t xml:space="preserve">2.74736189842224</t>
@@ -818,10 +818,10 @@
     <t xml:space="preserve">2.83268356323242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86681222915649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79855489730835</t>
+    <t xml:space="preserve">2.86681246757507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79855513572693</t>
   </si>
   <si>
     <t xml:space="preserve">2.78149056434631</t>
@@ -836,16 +836,16 @@
     <t xml:space="preserve">3.02039170265198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00332736968994</t>
+    <t xml:space="preserve">3.00332713127136</t>
   </si>
   <si>
     <t xml:space="preserve">3.03745603561401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98626303672791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05452013015747</t>
+    <t xml:space="preserve">2.98626279830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05452036857605</t>
   </si>
   <si>
     <t xml:space="preserve">3.07158493995667</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.13131022453308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06305241584778</t>
+    <t xml:space="preserve">3.06305265426636</t>
   </si>
   <si>
     <t xml:space="preserve">3.16543889045715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19956755638123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15690684318542</t>
+    <t xml:space="preserve">3.1995677947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15690660476685</t>
   </si>
   <si>
     <t xml:space="preserve">3.2336962223053</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">3.27635717391968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24222826957703</t>
+    <t xml:space="preserve">3.24222850799561</t>
   </si>
   <si>
     <t xml:space="preserve">3.26782488822937</t>
@@ -887,34 +887,34 @@
     <t xml:space="preserve">3.31048607826233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34461450576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32755041122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28488945960999</t>
+    <t xml:space="preserve">3.34461498260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32755017280579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28488922119141</t>
   </si>
   <si>
     <t xml:space="preserve">3.18250322341919</t>
   </si>
   <si>
+    <t xml:space="preserve">3.29342126846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33710074424744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32836508750916</t>
+  </si>
+  <si>
     <t xml:space="preserve">3.29342150688171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33710074424744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32836484909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29342174530029</t>
-  </si>
-  <si>
     <t xml:space="preserve">3.24974226951599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20606303215027</t>
+    <t xml:space="preserve">3.20606279373169</t>
   </si>
   <si>
     <t xml:space="preserve">3.15364766120911</t>
@@ -926,7 +926,7 @@
     <t xml:space="preserve">3.17111968994141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26721405982971</t>
+    <t xml:space="preserve">3.26721382141113</t>
   </si>
   <si>
     <t xml:space="preserve">3.36330842971802</t>
@@ -935,55 +935,55 @@
     <t xml:space="preserve">3.49434638023376</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58170509338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56423354148865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59044122695923</t>
+    <t xml:space="preserve">3.58170533180237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56423330307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59044098854065</t>
   </si>
   <si>
     <t xml:space="preserve">3.5030825138092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51181817054749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54676151275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63412046432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62538480758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74768662452698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69527125358582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66906356811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60791301727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55549764633179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66032791137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65159177780151</t>
+    <t xml:space="preserve">3.51181840896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54676175117493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63411998748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62538456916809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7476863861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69527149200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66906380653381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60791277885437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55549788475037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66032814979553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65159201622009</t>
   </si>
   <si>
     <t xml:space="preserve">3.68653535842896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70400714874268</t>
+    <t xml:space="preserve">3.7040069103241</t>
   </si>
   <si>
     <t xml:space="preserve">3.75642251968384</t>
@@ -1010,19 +1010,19 @@
     <t xml:space="preserve">3.44193148612976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4856104850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4069881439209</t>
+    <t xml:space="preserve">3.48561072349548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40698790550232</t>
   </si>
   <si>
     <t xml:space="preserve">3.35457253456116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45940327644348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52928972244263</t>
+    <t xml:space="preserve">3.4594030380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52928996086121</t>
   </si>
   <si>
     <t xml:space="preserve">3.46813893318176</t>
@@ -1031,22 +1031,22 @@
     <t xml:space="preserve">3.47687458992004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79136633872986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7214789390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8787248134613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17574453353882</t>
+    <t xml:space="preserve">3.79136610031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72147917747498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87872457504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17574405670166</t>
   </si>
   <si>
     <t xml:space="preserve">4.31551790237427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35046148300171</t>
+    <t xml:space="preserve">4.35046100616455</t>
   </si>
   <si>
     <t xml:space="preserve">4.18447971343994</t>
@@ -1061,25 +1061,25 @@
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493202209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98355484008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94861197471619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93114018440247</t>
+    <t xml:space="preserve">3.90493226051331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98355507850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94861173629761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93113970756531</t>
   </si>
   <si>
     <t xml:space="preserve">4.08838510513306</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07091331481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1233286857605</t>
+    <t xml:space="preserve">4.07091379165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12332820892334</t>
   </si>
   <si>
     <t xml:space="preserve">4.00102663040161</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">4.00976276397705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93987607955933</t>
+    <t xml:space="preserve">3.93987560272217</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
@@ -1097,31 +1097,31 @@
     <t xml:space="preserve">4.2106876373291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29804611206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28931045532227</t>
+    <t xml:space="preserve">4.29804658889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28930997848511</t>
   </si>
   <si>
     <t xml:space="preserve">4.21942329406738</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19321584701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1495361328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16700792312622</t>
+    <t xml:space="preserve">4.19321632385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14953660964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16700839996338</t>
   </si>
   <si>
     <t xml:space="preserve">4.11459302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06217813491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78262996673584</t>
+    <t xml:space="preserve">4.06217765808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78263020515442</t>
   </si>
   <si>
     <t xml:space="preserve">3.80010175704956</t>
@@ -1130,10 +1130,10 @@
     <t xml:space="preserve">3.82630968093872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83504509925842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84378099441528</t>
+    <t xml:space="preserve">3.835045337677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84378123283386</t>
   </si>
   <si>
     <t xml:space="preserve">3.77389454841614</t>
@@ -1142,16 +1142,16 @@
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734786987305</t>
+    <t xml:space="preserve">3.95734763145447</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86125302314758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76515865325928</t>
+    <t xml:space="preserve">3.861252784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76515817642212</t>
   </si>
   <si>
     <t xml:space="preserve">3.8175733089447</t>
@@ -1163,52 +1163,52 @@
     <t xml:space="preserve">3.67779970169067</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73895072937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85251665115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71274304389954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92240381240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61664867401123</t>
+    <t xml:space="preserve">3.7389509677887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85251712799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71274328231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92240357398987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61664843559265</t>
   </si>
   <si>
     <t xml:space="preserve">3.39825224876404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23227071762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0575532913208</t>
+    <t xml:space="preserve">3.23227047920227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05755352973938</t>
   </si>
   <si>
     <t xml:space="preserve">2.97019457817078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95272302627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91777920722961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90904331207275</t>
+    <t xml:space="preserve">2.95272278785706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91777944564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90904355049133</t>
   </si>
   <si>
     <t xml:space="preserve">3.37204432487488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38078022003174</t>
+    <t xml:space="preserve">3.38077998161316</t>
   </si>
   <si>
     <t xml:space="preserve">3.41572380065918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31962895393372</t>
+    <t xml:space="preserve">3.31962919235229</t>
   </si>
   <si>
     <t xml:space="preserve">3.27594995498657</t>
@@ -1749,6 +1749,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.40000009536743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.46000003814697</t>
   </si>
 </sst>
 </file>
@@ -56323,7 +56326,7 @@
     </row>
     <row r="2087">
       <c r="A2087" s="1" t="n">
-        <v>46001.6913078704</v>
+        <v>46001.3333333333</v>
       </c>
       <c r="B2087" t="n">
         <v>56746</v>
@@ -56344,6 +56347,32 @@
         <v>578</v>
       </c>
       <c r="H2087" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2088">
+      <c r="A2088" s="1" t="n">
+        <v>46002.6913078704</v>
+      </c>
+      <c r="B2088" t="n">
+        <v>54855</v>
+      </c>
+      <c r="C2088" t="n">
+        <v>3.55999994277954</v>
+      </c>
+      <c r="D2088" t="n">
+        <v>3.40000009536743</v>
+      </c>
+      <c r="E2088" t="n">
+        <v>3.40000009536743</v>
+      </c>
+      <c r="F2088" t="n">
+        <v>3.46000003814697</v>
+      </c>
+      <c r="G2088" t="s">
+        <v>579</v>
+      </c>
+      <c r="H2088" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="580" uniqueCount="580">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="581">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,31 +47,31 @@
     <t xml:space="preserve">2.96519947052002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88901543617249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98013710975647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97266817092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94578003883362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95773029327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96221137046814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93532371520996</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91291618347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97864365577698</t>
+    <t xml:space="preserve">2.88901519775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98013734817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97266864776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94577980041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95773005485535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96221160888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93532347679138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9129159450531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9786434173584</t>
   </si>
   <si>
     <t xml:space="preserve">2.98611235618591</t>
@@ -83,10 +83,10 @@
     <t xml:space="preserve">3.056321144104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05930876731873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05034589767456</t>
+    <t xml:space="preserve">3.0593090057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05034613609314</t>
   </si>
   <si>
     <t xml:space="preserve">2.98760628700256</t>
@@ -98,7 +98,7 @@
     <t xml:space="preserve">3.01598882675171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01001334190369</t>
+    <t xml:space="preserve">3.01001358032227</t>
   </si>
   <si>
     <t xml:space="preserve">3.02495145797729</t>
@@ -113,94 +113,94 @@
     <t xml:space="preserve">2.99955677986145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0443708896637</t>
+    <t xml:space="preserve">3.04437112808228</t>
   </si>
   <si>
     <t xml:space="preserve">2.959223985672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00254416465759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92785406112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90843462944031</t>
+    <t xml:space="preserve">3.00254464149475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92785453796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90843486785889</t>
   </si>
   <si>
     <t xml:space="preserve">2.896484375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91889142990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91590356826782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92038536071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90544724464417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90992879867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92337274551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8382260799408</t>
+    <t xml:space="preserve">2.91889119148254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9159038066864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92038512229919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90544700622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90992856025696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9233729839325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83822584152222</t>
   </si>
   <si>
     <t xml:space="preserve">2.86063289642334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82627534866333</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77996754646301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84569501876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86810207366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88304018974304</t>
+    <t xml:space="preserve">2.82627558708191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77996730804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84569525718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86810183525085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88303995132446</t>
   </si>
   <si>
     <t xml:space="preserve">2.79639935493469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87557125091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89797806739807</t>
+    <t xml:space="preserve">2.87557101249695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89797830581665</t>
   </si>
   <si>
     <t xml:space="preserve">2.80088090896606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74262261390686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82179403305054</t>
+    <t xml:space="preserve">2.74262285232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8217945098877</t>
   </si>
   <si>
     <t xml:space="preserve">2.75009155273438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76353549957275</t>
+    <t xml:space="preserve">2.76353573799133</t>
   </si>
   <si>
     <t xml:space="preserve">2.77847409248352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78594279289246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79341220855713</t>
+    <t xml:space="preserve">2.78594303131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79341197013855</t>
   </si>
   <si>
     <t xml:space="preserve">2.69631481170654</t>
@@ -212,7 +212,7 @@
     <t xml:space="preserve">2.6216242313385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53946542739868</t>
+    <t xml:space="preserve">2.53946566581726</t>
   </si>
   <si>
     <t xml:space="preserve">2.56934142112732</t>
@@ -230,28 +230,28 @@
     <t xml:space="preserve">2.70378375053406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77100467681885</t>
+    <t xml:space="preserve">2.77100491523743</t>
   </si>
   <si>
     <t xml:space="preserve">2.81581878662109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7336597442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66643881797791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68137669563293</t>
+    <t xml:space="preserve">2.73365998268127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66643857955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68137645721436</t>
   </si>
   <si>
     <t xml:space="preserve">2.74112892150879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72619104385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83075666427612</t>
+    <t xml:space="preserve">2.72619080543518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8307569026947</t>
   </si>
   <si>
     <t xml:space="preserve">2.893150806427</t>
@@ -269,10 +269,10 @@
     <t xml:space="preserve">2.87759590148926</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8309326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81537795066833</t>
+    <t xml:space="preserve">2.83093237876892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81537771224976</t>
   </si>
   <si>
     <t xml:space="preserve">2.84648704528809</t>
@@ -281,16 +281,16 @@
     <t xml:space="preserve">2.79982304573059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73760485649109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76093697547913</t>
+    <t xml:space="preserve">2.73760461807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76093673706055</t>
   </si>
   <si>
     <t xml:space="preserve">2.80760049819946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00980973243713</t>
+    <t xml:space="preserve">3.00980997085571</t>
   </si>
   <si>
     <t xml:space="preserve">2.9553689956665</t>
@@ -302,16 +302,16 @@
     <t xml:space="preserve">2.88537311553955</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82315516471863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86204147338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00203275680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91648244857788</t>
+    <t xml:space="preserve">2.82315492630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86204171180725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00203251838684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91648268699646</t>
   </si>
   <si>
     <t xml:space="preserve">2.85426425933838</t>
@@ -320,19 +320,19 @@
     <t xml:space="preserve">2.72982740402222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68316388130188</t>
+    <t xml:space="preserve">2.68316411972046</t>
   </si>
   <si>
     <t xml:space="preserve">2.7220504283905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75315952301025</t>
+    <t xml:space="preserve">2.75315976142883</t>
   </si>
   <si>
     <t xml:space="preserve">2.70649576187134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93981456756592</t>
+    <t xml:space="preserve">2.93981432914734</t>
   </si>
   <si>
     <t xml:space="preserve">2.99425530433655</t>
@@ -344,10 +344,10 @@
     <t xml:space="preserve">2.86981868743896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94759130477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98647809028625</t>
+    <t xml:space="preserve">2.94759178161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98647785186768</t>
   </si>
   <si>
     <t xml:space="preserve">2.63650012016296</t>
@@ -362,22 +362,22 @@
     <t xml:space="preserve">2.41095900535583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34096312522888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34874081611633</t>
+    <t xml:space="preserve">2.34096360206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34874057769775</t>
   </si>
   <si>
     <t xml:space="preserve">2.36429524421692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2554132938385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24763584136963</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3254086971283</t>
+    <t xml:space="preserve">2.25541305541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24763607978821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32540845870972</t>
   </si>
   <si>
     <t xml:space="preserve">2.23208117485046</t>
@@ -386,19 +386,19 @@
     <t xml:space="preserve">2.18541765213013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27874517440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26319026947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2165265083313</t>
+    <t xml:space="preserve">2.27874493598938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26319050788879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21652674674988</t>
   </si>
   <si>
     <t xml:space="preserve">2.06875848770142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14653134346008</t>
+    <t xml:space="preserve">2.1465311050415</t>
   </si>
   <si>
     <t xml:space="preserve">2.10764479637146</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">2.17764043807983</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22430396080017</t>
+    <t xml:space="preserve">2.22430372238159</t>
   </si>
   <si>
     <t xml:space="preserve">2.35651779174805</t>
@@ -419,46 +419,46 @@
     <t xml:space="preserve">2.4887318611145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52761816978455</t>
+    <t xml:space="preserve">2.52761793136597</t>
   </si>
   <si>
     <t xml:space="preserve">2.43429064750671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44206786155701</t>
+    <t xml:space="preserve">2.44206809997559</t>
   </si>
   <si>
     <t xml:space="preserve">2.55872750282288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44984531402588</t>
+    <t xml:space="preserve">2.44984555244446</t>
   </si>
   <si>
     <t xml:space="preserve">2.37207245826721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33318638801575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29429960250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37984991073608</t>
+    <t xml:space="preserve">2.33318591117859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29429936408997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3798496723175</t>
   </si>
   <si>
     <t xml:space="preserve">2.71427297592163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58205914497375</t>
+    <t xml:space="preserve">2.58205890655518</t>
   </si>
   <si>
     <t xml:space="preserve">2.62872314453125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.659832239151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57428193092346</t>
+    <t xml:space="preserve">2.65983200073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57428169250488</t>
   </si>
   <si>
     <t xml:space="preserve">2.67538666725159</t>
@@ -473,13 +473,13 @@
     <t xml:space="preserve">2.76871395111084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90092778205872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9631462097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92425990104675</t>
+    <t xml:space="preserve">2.90092802047729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96314644813538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92425966262817</t>
   </si>
   <si>
     <t xml:space="preserve">2.97092342376709</t>
@@ -491,37 +491,37 @@
     <t xml:space="preserve">3.04869651794434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03314185142517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0642511844635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07980561256409</t>
+    <t xml:space="preserve">3.03314161300659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06425142288208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07980537414551</t>
   </si>
   <si>
     <t xml:space="preserve">3.06049919128418</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02811312675476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01191997528076</t>
+    <t xml:space="preserve">3.0281126499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01191973686218</t>
   </si>
   <si>
     <t xml:space="preserve">3.1090784072876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09288501739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1252715587616</t>
+    <t xml:space="preserve">3.0928852558136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12527132034302</t>
   </si>
   <si>
     <t xml:space="preserve">3.0766921043396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9957263469696</t>
+    <t xml:space="preserve">2.99572658538818</t>
   </si>
   <si>
     <t xml:space="preserve">3.30339574813843</t>
@@ -530,13 +530,13 @@
     <t xml:space="preserve">3.41674733161926</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35197520256042</t>
+    <t xml:space="preserve">3.35197496414185</t>
   </si>
   <si>
     <t xml:space="preserve">3.33578205108643</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36816835403442</t>
+    <t xml:space="preserve">3.36816787719727</t>
   </si>
   <si>
     <t xml:space="preserve">3.23862338066101</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">3.22243022918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17385077476501</t>
+    <t xml:space="preserve">3.17385101318359</t>
   </si>
   <si>
     <t xml:space="preserve">3.20623707771301</t>
@@ -566,13 +566,13 @@
     <t xml:space="preserve">3.40055441856384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49771308898926</t>
+    <t xml:space="preserve">3.49771332740784</t>
   </si>
   <si>
     <t xml:space="preserve">3.38436126708984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25481629371643</t>
+    <t xml:space="preserve">3.25481653213501</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004416465759</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">2.88237452507019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86618161201477</t>
+    <t xml:space="preserve">2.86618185043335</t>
   </si>
   <si>
     <t xml:space="preserve">2.84998846054077</t>
@@ -602,13 +602,13 @@
     <t xml:space="preserve">2.75283002853394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72044372558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83379554748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76902318000793</t>
+    <t xml:space="preserve">2.72044348716736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83379530906677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76902270317078</t>
   </si>
   <si>
     <t xml:space="preserve">2.73663687705994</t>
@@ -617,16 +617,16 @@
     <t xml:space="preserve">2.81760215759277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89856767654419</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91476082801819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63947796821594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67186427116394</t>
+    <t xml:space="preserve">2.89856791496277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91476106643677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63947820663452</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67186403274536</t>
   </si>
   <si>
     <t xml:space="preserve">2.62328481674194</t>
@@ -635,22 +635,22 @@
     <t xml:space="preserve">2.68805718421936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70425033569336</t>
+    <t xml:space="preserve">2.70425057411194</t>
   </si>
   <si>
     <t xml:space="preserve">2.60709166526794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59089875221252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42896771430969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54231905937195</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46135354042053</t>
+    <t xml:space="preserve">2.5908989906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42896747589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54231953620911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46135377883911</t>
   </si>
   <si>
     <t xml:space="preserve">2.3156156539917</t>
@@ -659,7 +659,7 @@
     <t xml:space="preserve">2.2994225025177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35488176345825</t>
+    <t xml:space="preserve">2.35488152503967</t>
   </si>
   <si>
     <t xml:space="preserve">2.40607476234436</t>
@@ -671,7 +671,7 @@
     <t xml:space="preserve">2.13304495811462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08185195922852</t>
+    <t xml:space="preserve">2.08185219764709</t>
   </si>
   <si>
     <t xml:space="preserve">2.06478762626648</t>
@@ -686,13 +686,13 @@
     <t xml:space="preserve">2.09891629219055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26956009864807</t>
+    <t xml:space="preserve">2.26955986022949</t>
   </si>
   <si>
     <t xml:space="preserve">2.21836686134338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32075309753418</t>
+    <t xml:space="preserve">2.3207528591156</t>
   </si>
   <si>
     <t xml:space="preserve">2.55965423583984</t>
@@ -701,7 +701,7 @@
     <t xml:space="preserve">2.54258966445923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45726799964905</t>
+    <t xml:space="preserve">2.45726776123047</t>
   </si>
   <si>
     <t xml:space="preserve">2.5767183303833</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">2.44020342826843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42313933372498</t>
+    <t xml:space="preserve">2.4231390953064</t>
   </si>
   <si>
     <t xml:space="preserve">2.47433233261108</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">2.25249576568604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23543119430542</t>
+    <t xml:space="preserve">2.23543095588684</t>
   </si>
   <si>
     <t xml:space="preserve">2.37194609642029</t>
@@ -755,22 +755,22 @@
     <t xml:space="preserve">2.38901042938232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20130252838135</t>
+    <t xml:space="preserve">2.20130228996277</t>
   </si>
   <si>
     <t xml:space="preserve">2.18423795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01359415054321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04772329330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11598038673401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91120827198029</t>
+    <t xml:space="preserve">2.01359438896179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04772353172302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11598062515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.911208152771</t>
   </si>
   <si>
     <t xml:space="preserve">1.87707984447479</t>
@@ -779,13 +779,13 @@
     <t xml:space="preserve">1.84295094013214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97946560382843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86001515388489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94533693790436</t>
+    <t xml:space="preserve">1.97946572303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86001527309418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94533681869507</t>
   </si>
   <si>
     <t xml:space="preserve">1.96240139007568</t>
@@ -794,13 +794,13 @@
     <t xml:space="preserve">1.99653005599976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81561923027039</t>
+    <t xml:space="preserve">2.81561946868896</t>
   </si>
   <si>
     <t xml:space="preserve">2.90094137191772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88387703895569</t>
+    <t xml:space="preserve">2.88387727737427</t>
   </si>
   <si>
     <t xml:space="preserve">2.76442646980286</t>
@@ -833,7 +833,7 @@
     <t xml:space="preserve">2.96919870376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02039170265198</t>
+    <t xml:space="preserve">3.02039194107056</t>
   </si>
   <si>
     <t xml:space="preserve">3.00332713127136</t>
@@ -842,13 +842,13 @@
     <t xml:space="preserve">3.03745603561401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98626279830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05452036857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07158493995667</t>
+    <t xml:space="preserve">2.98626303672791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05452060699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07158470153809</t>
   </si>
   <si>
     <t xml:space="preserve">3.13984251022339</t>
@@ -857,22 +857,22 @@
     <t xml:space="preserve">3.11424589157104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13131022453308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06305265426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16543889045715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1995677947998</t>
+    <t xml:space="preserve">3.1313099861145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06305241584778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16543865203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19956755638123</t>
   </si>
   <si>
     <t xml:space="preserve">3.15690660476685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2336962223053</t>
+    <t xml:space="preserve">3.23369598388672</t>
   </si>
   <si>
     <t xml:space="preserve">3.27635717391968</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">3.33710074424744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32836508750916</t>
+    <t xml:space="preserve">3.32836484909058</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342150688171</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">3.21479892730713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17111968994141</t>
+    <t xml:space="preserve">3.17111945152283</t>
   </si>
   <si>
     <t xml:space="preserve">3.26721382141113</t>
@@ -932,16 +932,16 @@
     <t xml:space="preserve">3.36330842971802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49434638023376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58170533180237</t>
+    <t xml:space="preserve">3.49434661865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58170509338379</t>
   </si>
   <si>
     <t xml:space="preserve">3.56423330307007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59044098854065</t>
+    <t xml:space="preserve">3.59044122695923</t>
   </si>
   <si>
     <t xml:space="preserve">3.5030825138092</t>
@@ -962,13 +962,13 @@
     <t xml:space="preserve">3.7476863861084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69527149200439</t>
+    <t xml:space="preserve">3.69527125358582</t>
   </si>
   <si>
     <t xml:space="preserve">3.66906380653381</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60791277885437</t>
+    <t xml:space="preserve">3.60791301727295</t>
   </si>
   <si>
     <t xml:space="preserve">3.55549788475037</t>
@@ -992,16 +992,16 @@
     <t xml:space="preserve">3.57296967506409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53802585601807</t>
+    <t xml:space="preserve">3.53802609443665</t>
   </si>
   <si>
     <t xml:space="preserve">3.3458366394043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38951635360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42445969581604</t>
+    <t xml:space="preserve">3.3895161151886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42445993423462</t>
   </si>
   <si>
     <t xml:space="preserve">3.45066738128662</t>
@@ -1013,13 +1013,13 @@
     <t xml:space="preserve">3.48561072349548</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40698790550232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35457253456116</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4594030380249</t>
+    <t xml:space="preserve">3.4069881439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35457229614258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45940327644348</t>
   </si>
   <si>
     <t xml:space="preserve">3.52928996086121</t>
@@ -1028,13 +1028,13 @@
     <t xml:space="preserve">3.46813893318176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47687458992004</t>
+    <t xml:space="preserve">3.47687482833862</t>
   </si>
   <si>
     <t xml:space="preserve">3.79136610031128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72147917747498</t>
+    <t xml:space="preserve">3.72147941589355</t>
   </si>
   <si>
     <t xml:space="preserve">3.87872457504272</t>
@@ -1046,7 +1046,7 @@
     <t xml:space="preserve">4.31551790237427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35046100616455</t>
+    <t xml:space="preserve">4.35046148300171</t>
   </si>
   <si>
     <t xml:space="preserve">4.18447971343994</t>
@@ -1073,22 +1073,22 @@
     <t xml:space="preserve">3.93113970756531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08838510513306</t>
+    <t xml:space="preserve">4.08838558197021</t>
   </si>
   <si>
     <t xml:space="preserve">4.07091379165649</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12332820892334</t>
+    <t xml:space="preserve">4.1233286857605</t>
   </si>
   <si>
     <t xml:space="preserve">4.00102663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00976276397705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93987560272217</t>
+    <t xml:space="preserve">4.00976324081421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93987584114075</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
@@ -1097,7 +1097,7 @@
     <t xml:space="preserve">4.2106876373291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29804658889771</t>
+    <t xml:space="preserve">4.29804611206055</t>
   </si>
   <si>
     <t xml:space="preserve">4.28930997848511</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">4.14953660964966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16700839996338</t>
+    <t xml:space="preserve">4.16700792312622</t>
   </si>
   <si>
     <t xml:space="preserve">4.11459302902222</t>
@@ -1121,19 +1121,19 @@
     <t xml:space="preserve">4.06217765808105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78263020515442</t>
+    <t xml:space="preserve">3.78262996673584</t>
   </si>
   <si>
     <t xml:space="preserve">3.80010175704956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82630968093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.835045337677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84378123283386</t>
+    <t xml:space="preserve">3.8263099193573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83504557609558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84378147125244</t>
   </si>
   <si>
     <t xml:space="preserve">3.77389454841614</t>
@@ -1142,19 +1142,19 @@
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734763145447</t>
+    <t xml:space="preserve">3.95734786987305</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.861252784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76515817642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8175733089447</t>
+    <t xml:space="preserve">3.86125302314758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76515793800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81757354736328</t>
   </si>
   <si>
     <t xml:space="preserve">3.64285612106323</t>
@@ -1172,25 +1172,25 @@
     <t xml:space="preserve">3.71274328231812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92240357398987</t>
+    <t xml:space="preserve">3.92240381240845</t>
   </si>
   <si>
     <t xml:space="preserve">3.61664843559265</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39825224876404</t>
+    <t xml:space="preserve">3.39825201034546</t>
   </si>
   <si>
     <t xml:space="preserve">3.23227047920227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05755352973938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97019457817078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95272278785706</t>
+    <t xml:space="preserve">3.0575532913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97019481658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95272302627563</t>
   </si>
   <si>
     <t xml:space="preserve">2.91777944564819</t>
@@ -1199,22 +1199,22 @@
     <t xml:space="preserve">2.90904355049133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.37204432487488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38077998161316</t>
+    <t xml:space="preserve">3.3720440864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38078022003174</t>
   </si>
   <si>
     <t xml:space="preserve">3.41572380065918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31962919235229</t>
+    <t xml:space="preserve">3.31962895393372</t>
   </si>
   <si>
     <t xml:space="preserve">3.27594995498657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28468585014343</t>
+    <t xml:space="preserve">3.28468561172485</t>
   </si>
   <si>
     <t xml:space="preserve">3.50245499610901</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">3.32098078727722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26653838157654</t>
+    <t xml:space="preserve">3.26653814315796</t>
   </si>
   <si>
     <t xml:space="preserve">3.39357042312622</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">3.23024344444275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19394850730896</t>
+    <t xml:space="preserve">3.19394874572754</t>
   </si>
   <si>
     <t xml:space="preserve">3.25746440887451</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">3.2211697101593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10321164131165</t>
+    <t xml:space="preserve">3.10321140289307</t>
   </si>
   <si>
     <t xml:space="preserve">2.99432682991028</t>
@@ -1286,13 +1286,13 @@
     <t xml:space="preserve">2.95803189277649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85822129249573</t>
+    <t xml:space="preserve">2.85822105407715</t>
   </si>
   <si>
     <t xml:space="preserve">2.89451599121094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86729502677917</t>
+    <t xml:space="preserve">2.8672947883606</t>
   </si>
   <si>
     <t xml:space="preserve">2.81285238265991</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">2.75841021537781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7039680480957</t>
+    <t xml:space="preserve">2.70396780967712</t>
   </si>
   <si>
     <t xml:space="preserve">2.72211527824402</t>
@@ -1313,16 +1313,16 @@
     <t xml:space="preserve">2.64952564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79470491409302</t>
+    <t xml:space="preserve">2.7947051525116</t>
   </si>
   <si>
     <t xml:space="preserve">2.92173719406128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05784296989441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02154779434204</t>
+    <t xml:space="preserve">3.05784273147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02154803276062</t>
   </si>
   <si>
     <t xml:space="preserve">3.13950634002686</t>
@@ -1352,46 +1352,46 @@
     <t xml:space="preserve">3.08506417274475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01247406005859</t>
+    <t xml:space="preserve">3.01247429847717</t>
   </si>
   <si>
     <t xml:space="preserve">2.88544225692749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77655744552612</t>
+    <t xml:space="preserve">2.7765576839447</t>
   </si>
   <si>
     <t xml:space="preserve">2.71304154396057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63137817382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68582057952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66767311096191</t>
+    <t xml:space="preserve">2.6313784122467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68582034111023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66767287254333</t>
   </si>
   <si>
     <t xml:space="preserve">2.55878829956055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52249360084534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67674684524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64045190811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87636876106262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83099961280823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6041567325592</t>
+    <t xml:space="preserve">2.52249336242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67674660682678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64045214653015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87636852264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83099985122681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60415697097778</t>
   </si>
   <si>
     <t xml:space="preserve">2.73118901252747</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">2.91266345977783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12135910987854</t>
+    <t xml:space="preserve">3.12135887145996</t>
   </si>
   <si>
     <t xml:space="preserve">3.0759904384613</t>
@@ -1427,46 +1427,46 @@
     <t xml:space="preserve">3.0941379070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38449668884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41171789169312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37542295455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42079162597656</t>
+    <t xml:space="preserve">3.38449692726135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41171765327454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37542319297791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42079138755798</t>
   </si>
   <si>
     <t xml:space="preserve">3.43893885612488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36634922027588</t>
+    <t xml:space="preserve">3.36634945869446</t>
   </si>
   <si>
     <t xml:space="preserve">3.35727572441101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20302224159241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27561211585999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29375982284546</t>
+    <t xml:space="preserve">3.20302248001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27561187744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29375958442688</t>
   </si>
   <si>
     <t xml:space="preserve">3.1667275428772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11228537559509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78563117980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84007358551025</t>
+    <t xml:space="preserve">3.11228513717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78563141822815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84007382392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.82192611694336</t>
@@ -1752,6 +1752,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.46000003814697</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59999990463257</t>
   </si>
 </sst>
 </file>
@@ -56352,7 +56355,7 @@
     </row>
     <row r="2088">
       <c r="A2088" s="1" t="n">
-        <v>46002.6913078704</v>
+        <v>46002.3333333333</v>
       </c>
       <c r="B2088" t="n">
         <v>54855</v>
@@ -56373,6 +56376,32 @@
         <v>579</v>
       </c>
       <c r="H2088" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2089">
+      <c r="A2089" s="1" t="n">
+        <v>46003.6910069444</v>
+      </c>
+      <c r="B2089" t="n">
+        <v>99801</v>
+      </c>
+      <c r="C2089" t="n">
+        <v>3.72000002861023</v>
+      </c>
+      <c r="D2089" t="n">
+        <v>3.46000003814697</v>
+      </c>
+      <c r="E2089" t="n">
+        <v>3.53999996185303</v>
+      </c>
+      <c r="F2089" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="G2089" t="s">
+        <v>580</v>
+      </c>
+      <c r="H2089" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="581" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="582" uniqueCount="582">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02345776557922</t>
+    <t xml:space="preserve">3.02345728874207</t>
   </si>
   <si>
     <t xml:space="preserve">NDT.MI</t>
@@ -53,37 +53,37 @@
     <t xml:space="preserve">2.98013734817505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97266864776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94577980041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95773005485535</t>
+    <t xml:space="preserve">2.97266817092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94578003883362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95773029327393</t>
   </si>
   <si>
     <t xml:space="preserve">2.96221160888672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93532347679138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9129159450531</t>
+    <t xml:space="preserve">2.93532371520996</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91291618347168</t>
   </si>
   <si>
     <t xml:space="preserve">2.9786434173584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98611235618591</t>
+    <t xml:space="preserve">2.98611259460449</t>
   </si>
   <si>
     <t xml:space="preserve">3.03540802001953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.056321144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0593090057373</t>
+    <t xml:space="preserve">3.05632138252258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05930924415588</t>
   </si>
   <si>
     <t xml:space="preserve">3.05034613609314</t>
@@ -92,7 +92,7 @@
     <t xml:space="preserve">2.98760628700256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95026135444641</t>
+    <t xml:space="preserve">2.95026087760925</t>
   </si>
   <si>
     <t xml:space="preserve">3.01598882675171</t>
@@ -107,46 +107,46 @@
     <t xml:space="preserve">3.0174822807312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03092670440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99955677986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04437112808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.959223985672</t>
+    <t xml:space="preserve">3.03092694282532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99955654144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0443708896637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95922422409058</t>
   </si>
   <si>
     <t xml:space="preserve">3.00254464149475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92785453796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90843486785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91889119148254</t>
+    <t xml:space="preserve">2.92785429954529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90843510627747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89648461341858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9188916683197</t>
   </si>
   <si>
     <t xml:space="preserve">2.9159038066864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92038512229919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90544700622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90992856025696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9233729839325</t>
+    <t xml:space="preserve">2.92038536071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90544724464417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90992832183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92337274551392</t>
   </si>
   <si>
     <t xml:space="preserve">2.83822584152222</t>
@@ -158,22 +158,22 @@
     <t xml:space="preserve">2.82627558708191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77996730804443</t>
+    <t xml:space="preserve">2.77996778488159</t>
   </si>
   <si>
     <t xml:space="preserve">2.84569525718689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86810183525085</t>
+    <t xml:space="preserve">2.86810207366943</t>
   </si>
   <si>
     <t xml:space="preserve">2.88303995132446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79639935493469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87557101249695</t>
+    <t xml:space="preserve">2.79639983177185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87557077407837</t>
   </si>
   <si>
     <t xml:space="preserve">2.89797830581665</t>
@@ -182,10 +182,10 @@
     <t xml:space="preserve">2.80088090896606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74262285232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8217945098877</t>
+    <t xml:space="preserve">2.74262237548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82179427146912</t>
   </si>
   <si>
     <t xml:space="preserve">2.75009155273438</t>
@@ -197,37 +197,37 @@
     <t xml:space="preserve">2.77847409248352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78594303131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79341197013855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69631481170654</t>
+    <t xml:space="preserve">2.78594279289246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79341173171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69631457328796</t>
   </si>
   <si>
     <t xml:space="preserve">2.6515007019043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6216242313385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53946566581726</t>
+    <t xml:space="preserve">2.62162446975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5394651889801</t>
   </si>
   <si>
     <t xml:space="preserve">2.56934142112732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61415553092957</t>
+    <t xml:space="preserve">2.61415576934814</t>
   </si>
   <si>
     <t xml:space="preserve">2.65896964073181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68884563446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70378375053406</t>
+    <t xml:space="preserve">2.68884587287903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70378351211548</t>
   </si>
   <si>
     <t xml:space="preserve">2.77100491523743</t>
@@ -251,13 +251,13 @@
     <t xml:space="preserve">2.72619080543518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8307569026947</t>
+    <t xml:space="preserve">2.83075666427612</t>
   </si>
   <si>
     <t xml:space="preserve">2.893150806427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69871830940247</t>
+    <t xml:space="preserve">2.69871878623962</t>
   </si>
   <si>
     <t xml:space="preserve">2.83870983123779</t>
@@ -266,13 +266,13 @@
     <t xml:space="preserve">2.93203687667847</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87759590148926</t>
+    <t xml:space="preserve">2.87759613990784</t>
   </si>
   <si>
     <t xml:space="preserve">2.83093237876892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81537771224976</t>
+    <t xml:space="preserve">2.81537747383118</t>
   </si>
   <si>
     <t xml:space="preserve">2.84648704528809</t>
@@ -281,28 +281,28 @@
     <t xml:space="preserve">2.79982304573059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73760461807251</t>
+    <t xml:space="preserve">2.73760509490967</t>
   </si>
   <si>
     <t xml:space="preserve">2.76093673706055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80760049819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00980997085571</t>
+    <t xml:space="preserve">2.80760025978088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00980973243713</t>
   </si>
   <si>
     <t xml:space="preserve">2.9553689956665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90870547294617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88537311553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82315492630005</t>
+    <t xml:space="preserve">2.90870523452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88537335395813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82315516471863</t>
   </si>
   <si>
     <t xml:space="preserve">2.86204171180725</t>
@@ -311,13 +311,13 @@
     <t xml:space="preserve">3.00203251838684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91648268699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85426425933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72982740402222</t>
+    <t xml:space="preserve">2.91648244857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85426449775696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7298276424408</t>
   </si>
   <si>
     <t xml:space="preserve">2.68316411972046</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">2.7220504283905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75315976142883</t>
+    <t xml:space="preserve">2.75315952301025</t>
   </si>
   <si>
     <t xml:space="preserve">2.70649576187134</t>
@@ -335,16 +335,16 @@
     <t xml:space="preserve">2.93981432914734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99425530433655</t>
+    <t xml:space="preserve">2.99425506591797</t>
   </si>
   <si>
     <t xml:space="preserve">2.97870063781738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86981868743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94759178161621</t>
+    <t xml:space="preserve">2.86981892585754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94759154319763</t>
   </si>
   <si>
     <t xml:space="preserve">2.98647785186768</t>
@@ -362,52 +362,52 @@
     <t xml:space="preserve">2.41095900535583</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34096360206604</t>
+    <t xml:space="preserve">2.34096336364746</t>
   </si>
   <si>
     <t xml:space="preserve">2.34874057769775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36429524421692</t>
+    <t xml:space="preserve">2.36429500579834</t>
   </si>
   <si>
     <t xml:space="preserve">2.25541305541992</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24763607978821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32540845870972</t>
+    <t xml:space="preserve">2.24763584136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3254086971283</t>
   </si>
   <si>
     <t xml:space="preserve">2.23208117485046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18541765213013</t>
+    <t xml:space="preserve">2.18541741371155</t>
   </si>
   <si>
     <t xml:space="preserve">2.27874493598938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26319050788879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21652674674988</t>
+    <t xml:space="preserve">2.26319026947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2165265083313</t>
   </si>
   <si>
     <t xml:space="preserve">2.06875848770142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1465311050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10764479637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15430855751038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17764043807983</t>
+    <t xml:space="preserve">2.14653134346008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10764455795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15430879592896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17764019966125</t>
   </si>
   <si>
     <t xml:space="preserve">2.22430372238159</t>
@@ -416,16 +416,16 @@
     <t xml:space="preserve">2.35651779174805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4887318611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52761793136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43429064750671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44206809997559</t>
+    <t xml:space="preserve">2.48873162269592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52761816978455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43429088592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44206786155701</t>
   </si>
   <si>
     <t xml:space="preserve">2.55872750282288</t>
@@ -434,37 +434,37 @@
     <t xml:space="preserve">2.44984555244446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37207245826721</t>
+    <t xml:space="preserve">2.37207221984863</t>
   </si>
   <si>
     <t xml:space="preserve">2.33318591117859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29429936408997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3798496723175</t>
+    <t xml:space="preserve">2.29429984092712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37984943389893</t>
   </si>
   <si>
     <t xml:space="preserve">2.71427297592163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58205890655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62872314453125</t>
+    <t xml:space="preserve">2.58205914497375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62872266769409</t>
   </si>
   <si>
     <t xml:space="preserve">2.65983200073242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57428169250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67538666725159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64427757263184</t>
+    <t xml:space="preserve">2.57428193092346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67538690567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64427709579468</t>
   </si>
   <si>
     <t xml:space="preserve">2.69094133377075</t>
@@ -476,34 +476,34 @@
     <t xml:space="preserve">2.90092802047729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96314644813538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92425966262817</t>
+    <t xml:space="preserve">2.9631462097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92425990104675</t>
   </si>
   <si>
     <t xml:space="preserve">2.97092342376709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01758742332458</t>
+    <t xml:space="preserve">3.01758718490601</t>
   </si>
   <si>
     <t xml:space="preserve">3.04869651794434</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03314161300659</t>
+    <t xml:space="preserve">3.03314185142517</t>
   </si>
   <si>
     <t xml:space="preserve">3.06425142288208</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07980537414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06049919128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0281126499176</t>
+    <t xml:space="preserve">3.07980561256409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0604989528656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02811288833618</t>
   </si>
   <si>
     <t xml:space="preserve">3.01191973686218</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">3.0928852558136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12527132034302</t>
+    <t xml:space="preserve">3.1252715587616</t>
   </si>
   <si>
     <t xml:space="preserve">3.0766921043396</t>
@@ -527,16 +527,16 @@
     <t xml:space="preserve">3.30339574813843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41674733161926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35197496414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33578205108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36816787719727</t>
+    <t xml:space="preserve">3.41674757003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35197520256042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33578181266785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36816811561584</t>
   </si>
   <si>
     <t xml:space="preserve">3.23862338066101</t>
@@ -563,13 +563,13 @@
     <t xml:space="preserve">3.1414647102356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40055441856384</t>
+    <t xml:space="preserve">3.40055465698242</t>
   </si>
   <si>
     <t xml:space="preserve">3.49771332740784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38436126708984</t>
+    <t xml:space="preserve">3.38436102867126</t>
   </si>
   <si>
     <t xml:space="preserve">3.25481653213501</t>
@@ -587,10 +587,10 @@
     <t xml:space="preserve">2.80140924453735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88237452507019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86618185043335</t>
+    <t xml:space="preserve">2.88237476348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86618161201477</t>
   </si>
   <si>
     <t xml:space="preserve">2.84998846054077</t>
@@ -605,25 +605,25 @@
     <t xml:space="preserve">2.72044348716736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83379530906677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76902270317078</t>
+    <t xml:space="preserve">2.83379554748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76902294158936</t>
   </si>
   <si>
     <t xml:space="preserve">2.73663687705994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81760215759277</t>
+    <t xml:space="preserve">2.81760239601135</t>
   </si>
   <si>
     <t xml:space="preserve">2.89856791496277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91476106643677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63947820663452</t>
+    <t xml:space="preserve">2.91476082801819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63947796821594</t>
   </si>
   <si>
     <t xml:space="preserve">2.67186403274536</t>
@@ -638,22 +638,22 @@
     <t xml:space="preserve">2.70425057411194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60709166526794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5908989906311</t>
+    <t xml:space="preserve">2.60709190368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59089875221252</t>
   </si>
   <si>
     <t xml:space="preserve">2.42896747589111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54231953620911</t>
+    <t xml:space="preserve">2.54231929779053</t>
   </si>
   <si>
     <t xml:space="preserve">2.46135377883911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3156156539917</t>
+    <t xml:space="preserve">2.31561541557312</t>
   </si>
   <si>
     <t xml:space="preserve">2.2994225025177</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">2.06478762626648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03065872192383</t>
+    <t xml:space="preserve">2.03065896034241</t>
   </si>
   <si>
     <t xml:space="preserve">2.1671736240387</t>
@@ -686,13 +686,13 @@
     <t xml:space="preserve">2.09891629219055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26955986022949</t>
+    <t xml:space="preserve">2.26956009864807</t>
   </si>
   <si>
     <t xml:space="preserve">2.21836686134338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3207528591156</t>
+    <t xml:space="preserve">2.32075309753418</t>
   </si>
   <si>
     <t xml:space="preserve">2.55965423583984</t>
@@ -701,28 +701,28 @@
     <t xml:space="preserve">2.54258966445923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45726776123047</t>
+    <t xml:space="preserve">2.45726799964905</t>
   </si>
   <si>
     <t xml:space="preserve">2.5767183303833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62791156768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61084699630737</t>
+    <t xml:space="preserve">2.62791132926941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61084723472595</t>
   </si>
   <si>
     <t xml:space="preserve">2.64497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59378290176392</t>
+    <t xml:space="preserve">2.59378266334534</t>
   </si>
   <si>
     <t xml:space="preserve">2.69616913795471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71323347091675</t>
+    <t xml:space="preserve">2.71323323249817</t>
   </si>
   <si>
     <t xml:space="preserve">2.44020342826843</t>
@@ -731,49 +731,49 @@
     <t xml:space="preserve">2.4231390953064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47433233261108</t>
+    <t xml:space="preserve">2.4743320941925</t>
   </si>
   <si>
     <t xml:space="preserve">2.15010929107666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33781743049622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30368876457214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25249576568604</t>
+    <t xml:space="preserve">2.33781719207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30368852615356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25249552726746</t>
   </si>
   <si>
     <t xml:space="preserve">2.23543095588684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37194609642029</t>
+    <t xml:space="preserve">2.37194633483887</t>
   </si>
   <si>
     <t xml:space="preserve">2.38901042938232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20130228996277</t>
+    <t xml:space="preserve">2.20130252838135</t>
   </si>
   <si>
     <t xml:space="preserve">2.18423795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01359438896179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04772353172302</t>
+    <t xml:space="preserve">2.01359415054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04772329330444</t>
   </si>
   <si>
     <t xml:space="preserve">2.11598062515259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.911208152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87707984447479</t>
+    <t xml:space="preserve">1.91120839118958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8770797252655</t>
   </si>
   <si>
     <t xml:space="preserve">1.84295094013214</t>
@@ -791,19 +791,19 @@
     <t xml:space="preserve">1.96240139007568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99653005599976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81561946868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90094137191772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88387727737427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76442646980286</t>
+    <t xml:space="preserve">1.99652981758118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81561923027039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9009416103363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88387703895569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76442623138428</t>
   </si>
   <si>
     <t xml:space="preserve">2.73029780387878</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">2.6791045665741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74736189842224</t>
+    <t xml:space="preserve">2.74736213684082</t>
   </si>
   <si>
     <t xml:space="preserve">2.83268356323242</t>
@@ -824,7 +824,7 @@
     <t xml:space="preserve">2.79855513572693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78149056434631</t>
+    <t xml:space="preserve">2.78149080276489</t>
   </si>
   <si>
     <t xml:space="preserve">2.9350700378418</t>
@@ -839,13 +839,13 @@
     <t xml:space="preserve">3.00332713127136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03745603561401</t>
+    <t xml:space="preserve">3.03745627403259</t>
   </si>
   <si>
     <t xml:space="preserve">2.98626303672791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05452060699463</t>
+    <t xml:space="preserve">3.05452036857605</t>
   </si>
   <si>
     <t xml:space="preserve">3.07158470153809</t>
@@ -854,7 +854,7 @@
     <t xml:space="preserve">3.13984251022339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11424589157104</t>
+    <t xml:space="preserve">3.11424565315247</t>
   </si>
   <si>
     <t xml:space="preserve">3.1313099861145</t>
@@ -872,13 +872,13 @@
     <t xml:space="preserve">3.15690660476685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23369598388672</t>
+    <t xml:space="preserve">3.2336962223053</t>
   </si>
   <si>
     <t xml:space="preserve">3.27635717391968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24222850799561</t>
+    <t xml:space="preserve">3.24222826957703</t>
   </si>
   <si>
     <t xml:space="preserve">3.26782488822937</t>
@@ -887,10 +887,10 @@
     <t xml:space="preserve">3.31048607826233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34461498260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32755017280579</t>
+    <t xml:space="preserve">3.3446147441864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32755041122437</t>
   </si>
   <si>
     <t xml:space="preserve">3.28488922119141</t>
@@ -905,7 +905,7 @@
     <t xml:space="preserve">3.33710074424744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32836484909058</t>
+    <t xml:space="preserve">3.32836508750916</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342150688171</t>
@@ -914,10 +914,10 @@
     <t xml:space="preserve">3.24974226951599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20606279373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15364766120911</t>
+    <t xml:space="preserve">3.20606303215027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15364742279053</t>
   </si>
   <si>
     <t xml:space="preserve">3.21479892730713</t>
@@ -926,7 +926,7 @@
     <t xml:space="preserve">3.17111945152283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26721382141113</t>
+    <t xml:space="preserve">3.26721405982971</t>
   </si>
   <si>
     <t xml:space="preserve">3.36330842971802</t>
@@ -935,10 +935,10 @@
     <t xml:space="preserve">3.49434661865234</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58170509338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56423330307007</t>
+    <t xml:space="preserve">3.58170485496521</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56423354148865</t>
   </si>
   <si>
     <t xml:space="preserve">3.59044122695923</t>
@@ -947,13 +947,13 @@
     <t xml:space="preserve">3.5030825138092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51181840896606</t>
+    <t xml:space="preserve">3.51181817054749</t>
   </si>
   <si>
     <t xml:space="preserve">3.54676175117493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63411998748779</t>
+    <t xml:space="preserve">3.63412022590637</t>
   </si>
   <si>
     <t xml:space="preserve">3.62538456916809</t>
@@ -965,16 +965,16 @@
     <t xml:space="preserve">3.69527125358582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66906380653381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60791301727295</t>
+    <t xml:space="preserve">3.66906356811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60791277885437</t>
   </si>
   <si>
     <t xml:space="preserve">3.55549788475037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66032814979553</t>
+    <t xml:space="preserve">3.66032791137695</t>
   </si>
   <si>
     <t xml:space="preserve">3.65159201622009</t>
@@ -983,13 +983,13 @@
     <t xml:space="preserve">3.68653535842896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7040069103241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75642251968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57296967506409</t>
+    <t xml:space="preserve">3.70400714874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75642275810242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57296943664551</t>
   </si>
   <si>
     <t xml:space="preserve">3.53802609443665</t>
@@ -1001,25 +1001,25 @@
     <t xml:space="preserve">3.3895161151886</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42445993423462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45066738128662</t>
+    <t xml:space="preserve">3.42445969581604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45066714286804</t>
   </si>
   <si>
     <t xml:space="preserve">3.44193148612976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48561072349548</t>
+    <t xml:space="preserve">3.4856104850769</t>
   </si>
   <si>
     <t xml:space="preserve">3.4069881439209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35457229614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45940327644348</t>
+    <t xml:space="preserve">3.35457253456116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4594030380249</t>
   </si>
   <si>
     <t xml:space="preserve">3.52928996086121</t>
@@ -1034,13 +1034,13 @@
     <t xml:space="preserve">3.79136610031128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72147941589355</t>
+    <t xml:space="preserve">3.72147917747498</t>
   </si>
   <si>
     <t xml:space="preserve">3.87872457504272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17574405670166</t>
+    <t xml:space="preserve">4.17574453353882</t>
   </si>
   <si>
     <t xml:space="preserve">4.31551790237427</t>
@@ -1049,13 +1049,13 @@
     <t xml:space="preserve">4.35046148300171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18447971343994</t>
+    <t xml:space="preserve">4.1844801902771</t>
   </si>
   <si>
     <t xml:space="preserve">4.20195150375366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25436687469482</t>
+    <t xml:space="preserve">4.25436639785767</t>
   </si>
   <si>
     <t xml:space="preserve">4.14080047607422</t>
@@ -1067,7 +1067,7 @@
     <t xml:space="preserve">3.98355507850647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94861173629761</t>
+    <t xml:space="preserve">3.94861149787903</t>
   </si>
   <si>
     <t xml:space="preserve">3.93113970756531</t>
@@ -1076,16 +1076,16 @@
     <t xml:space="preserve">4.08838558197021</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07091379165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1233286857605</t>
+    <t xml:space="preserve">4.07091331481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12332916259766</t>
   </si>
   <si>
     <t xml:space="preserve">4.00102663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00976324081421</t>
+    <t xml:space="preserve">4.00976276397705</t>
   </si>
   <si>
     <t xml:space="preserve">3.93987584114075</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">4.28930997848511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21942329406738</t>
+    <t xml:space="preserve">4.21942377090454</t>
   </si>
   <si>
     <t xml:space="preserve">4.19321632385254</t>
@@ -1127,7 +1127,7 @@
     <t xml:space="preserve">3.80010175704956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8263099193573</t>
+    <t xml:space="preserve">3.82630944252014</t>
   </si>
   <si>
     <t xml:space="preserve">3.83504557609558</t>
@@ -1136,13 +1136,13 @@
     <t xml:space="preserve">3.84378147125244</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77389454841614</t>
+    <t xml:space="preserve">3.77389430999756</t>
   </si>
   <si>
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734786987305</t>
+    <t xml:space="preserve">3.95734739303589</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
@@ -1151,16 +1151,16 @@
     <t xml:space="preserve">3.86125302314758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76515793800354</t>
+    <t xml:space="preserve">3.76515817642212</t>
   </si>
   <si>
     <t xml:space="preserve">3.81757354736328</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64285612106323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67779970169067</t>
+    <t xml:space="preserve">3.64285635948181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67779946327209</t>
   </si>
   <si>
     <t xml:space="preserve">3.7389509677887</t>
@@ -1169,7 +1169,7 @@
     <t xml:space="preserve">3.85251712799072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71274328231812</t>
+    <t xml:space="preserve">3.71274304389954</t>
   </si>
   <si>
     <t xml:space="preserve">3.92240381240845</t>
@@ -1178,13 +1178,13 @@
     <t xml:space="preserve">3.61664843559265</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39825201034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23227047920227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0575532913208</t>
+    <t xml:space="preserve">3.39825224876404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23227071762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05755305290222</t>
   </si>
   <si>
     <t xml:space="preserve">2.97019481658936</t>
@@ -1196,10 +1196,10 @@
     <t xml:space="preserve">2.91777944564819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90904355049133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3720440864563</t>
+    <t xml:space="preserve">2.90904331207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37204432487488</t>
   </si>
   <si>
     <t xml:space="preserve">3.38078022003174</t>
@@ -1211,7 +1211,7 @@
     <t xml:space="preserve">3.31962895393372</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27594995498657</t>
+    <t xml:space="preserve">3.27595019340515</t>
   </si>
   <si>
     <t xml:space="preserve">3.28468561172485</t>
@@ -1755,6 +1755,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.59999990463257</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75999999046326</t>
   </si>
 </sst>
 </file>
@@ -56381,7 +56384,7 @@
     </row>
     <row r="2089">
       <c r="A2089" s="1" t="n">
-        <v>46003.6910069444</v>
+        <v>46003.3333333333</v>
       </c>
       <c r="B2089" t="n">
         <v>99801</v>
@@ -56402,6 +56405,32 @@
         <v>580</v>
       </c>
       <c r="H2089" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2090">
+      <c r="A2090" s="1" t="n">
+        <v>46006.6909953704</v>
+      </c>
+      <c r="B2090" t="n">
+        <v>60484</v>
+      </c>
+      <c r="C2090" t="n">
+        <v>3.83999991416931</v>
+      </c>
+      <c r="D2090" t="n">
+        <v>3.61999988555908</v>
+      </c>
+      <c r="E2090" t="n">
+        <v>3.77999997138977</v>
+      </c>
+      <c r="F2090" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="G2090" t="s">
+        <v>581</v>
+      </c>
+      <c r="H2090" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02345728874207</t>
+    <t xml:space="preserve">3.02345752716064</t>
   </si>
   <si>
     <t xml:space="preserve">NDT.MI</t>
@@ -47,25 +47,25 @@
     <t xml:space="preserve">2.96519947052002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88901519775391</t>
+    <t xml:space="preserve">2.88901567459106</t>
   </si>
   <si>
     <t xml:space="preserve">2.98013734817505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97266817092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94578003883362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95773029327393</t>
+    <t xml:space="preserve">2.97266840934753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94577980041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95773005485535</t>
   </si>
   <si>
     <t xml:space="preserve">2.96221160888672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93532371520996</t>
+    <t xml:space="preserve">2.93532347679138</t>
   </si>
   <si>
     <t xml:space="preserve">2.91291618347168</t>
@@ -83,7 +83,7 @@
     <t xml:space="preserve">3.05632138252258</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05930924415588</t>
+    <t xml:space="preserve">3.0593090057373</t>
   </si>
   <si>
     <t xml:space="preserve">3.05034613609314</t>
@@ -92,16 +92,16 @@
     <t xml:space="preserve">2.98760628700256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95026087760925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01598882675171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01001358032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02495145797729</t>
+    <t xml:space="preserve">2.95026135444641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01598858833313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01001334190369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02495169639587</t>
   </si>
   <si>
     <t xml:space="preserve">3.0174822807312</t>
@@ -113,130 +113,130 @@
     <t xml:space="preserve">2.99955654144287</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0443708896637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95922422409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00254464149475</t>
+    <t xml:space="preserve">3.04437112808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.959223985672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00254416465759</t>
   </si>
   <si>
     <t xml:space="preserve">2.92785429954529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90843510627747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89648461341858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9188916683197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9159038066864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92038536071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90544724464417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90992832183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92337274551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83822584152222</t>
+    <t xml:space="preserve">2.90843486785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91889142990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91590356826782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92038512229919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90544748306274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90992856025696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9233729839325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8382260799408</t>
   </si>
   <si>
     <t xml:space="preserve">2.86063289642334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82627558708191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77996778488159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84569525718689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86810207366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88303995132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79639983177185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87557077407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89797830581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80088090896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74262237548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82179427146912</t>
+    <t xml:space="preserve">2.82627534866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77996754646301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84569501876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86810183525085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88304018974304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79639935493469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87557101249695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89797806739807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80088114738464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74262261390686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82179403305054</t>
   </si>
   <si>
     <t xml:space="preserve">2.75009155273438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76353573799133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77847409248352</t>
+    <t xml:space="preserve">2.76353597640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77847385406494</t>
   </si>
   <si>
     <t xml:space="preserve">2.78594279289246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79341173171997</t>
+    <t xml:space="preserve">2.79341197013855</t>
   </si>
   <si>
     <t xml:space="preserve">2.69631457328796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6515007019043</t>
+    <t xml:space="preserve">2.65150046348572</t>
   </si>
   <si>
     <t xml:space="preserve">2.62162446975708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5394651889801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56934142112732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61415576934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65896964073181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68884587287903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70378351211548</t>
+    <t xml:space="preserve">2.53946566581726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5693416595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61415553092957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65896987915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68884563446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70378375053406</t>
   </si>
   <si>
     <t xml:space="preserve">2.77100491523743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81581878662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73365998268127</t>
+    <t xml:space="preserve">2.81581902503967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7336597442627</t>
   </si>
   <si>
     <t xml:space="preserve">2.66643857955933</t>
@@ -245,31 +245,31 @@
     <t xml:space="preserve">2.68137645721436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74112892150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72619080543518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83075666427612</t>
+    <t xml:space="preserve">2.74112868309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7261905670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8307569026947</t>
   </si>
   <si>
     <t xml:space="preserve">2.893150806427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69871878623962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83870983123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93203687667847</t>
+    <t xml:space="preserve">2.69871854782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83870959281921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93203711509705</t>
   </si>
   <si>
     <t xml:space="preserve">2.87759613990784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83093237876892</t>
+    <t xml:space="preserve">2.8309326171875</t>
   </si>
   <si>
     <t xml:space="preserve">2.81537747383118</t>
@@ -278,16 +278,16 @@
     <t xml:space="preserve">2.84648704528809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79982304573059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73760509490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76093673706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80760025978088</t>
+    <t xml:space="preserve">2.79982328414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73760485649109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76093697547913</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80760049819946</t>
   </si>
   <si>
     <t xml:space="preserve">3.00980973243713</t>
@@ -299,13 +299,13 @@
     <t xml:space="preserve">2.90870523452759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88537335395813</t>
+    <t xml:space="preserve">2.88537311553955</t>
   </si>
   <si>
     <t xml:space="preserve">2.82315516471863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86204171180725</t>
+    <t xml:space="preserve">2.86204147338867</t>
   </si>
   <si>
     <t xml:space="preserve">3.00203251838684</t>
@@ -314,25 +314,25 @@
     <t xml:space="preserve">2.91648244857788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85426449775696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7298276424408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68316411972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7220504283905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75315952301025</t>
+    <t xml:space="preserve">2.8542640209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72982740402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68316388130188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72205018997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75315976142883</t>
   </si>
   <si>
     <t xml:space="preserve">2.70649576187134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93981432914734</t>
+    <t xml:space="preserve">2.93981456756592</t>
   </si>
   <si>
     <t xml:space="preserve">2.99425506591797</t>
@@ -341,13 +341,13 @@
     <t xml:space="preserve">2.97870063781738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86981892585754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94759154319763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98647785186768</t>
+    <t xml:space="preserve">2.86981844902039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94759130477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98647809028625</t>
   </si>
   <si>
     <t xml:space="preserve">2.63650012016296</t>
@@ -356,22 +356,22 @@
     <t xml:space="preserve">2.550950050354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51984095573425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41095900535583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34096336364746</t>
+    <t xml:space="preserve">2.51984119415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41095876693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34096360206604</t>
   </si>
   <si>
     <t xml:space="preserve">2.34874057769775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36429500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25541305541992</t>
+    <t xml:space="preserve">2.36429524421692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2554132938385</t>
   </si>
   <si>
     <t xml:space="preserve">2.24763584136963</t>
@@ -383,13 +383,13 @@
     <t xml:space="preserve">2.23208117485046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18541741371155</t>
+    <t xml:space="preserve">2.18541765213013</t>
   </si>
   <si>
     <t xml:space="preserve">2.27874493598938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26319026947021</t>
+    <t xml:space="preserve">2.26319074630737</t>
   </si>
   <si>
     <t xml:space="preserve">2.2165265083313</t>
@@ -398,52 +398,52 @@
     <t xml:space="preserve">2.06875848770142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14653134346008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10764455795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15430879592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17764019966125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22430372238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35651779174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48873162269592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52761816978455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43429088592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44206786155701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55872750282288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44984555244446</t>
+    <t xml:space="preserve">2.1465311050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10764479637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15430855751038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17764043807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22430396080017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35651803016663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48873209953308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52761793136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43429064750671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44206833839417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5587272644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44984531402588</t>
   </si>
   <si>
     <t xml:space="preserve">2.37207221984863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33318591117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29429984092712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37984943389893</t>
+    <t xml:space="preserve">2.33318614959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29429960250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3798496723175</t>
   </si>
   <si>
     <t xml:space="preserve">2.71427297592163</t>
@@ -452,7 +452,7 @@
     <t xml:space="preserve">2.58205914497375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62872266769409</t>
+    <t xml:space="preserve">2.62872314453125</t>
   </si>
   <si>
     <t xml:space="preserve">2.65983200073242</t>
@@ -461,19 +461,19 @@
     <t xml:space="preserve">2.57428193092346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67538690567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64427709579468</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69094133377075</t>
+    <t xml:space="preserve">2.67538666725159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64427757263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69094109535217</t>
   </si>
   <si>
     <t xml:space="preserve">2.76871395111084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90092802047729</t>
+    <t xml:space="preserve">2.90092778205872</t>
   </si>
   <si>
     <t xml:space="preserve">2.9631462097168</t>
@@ -482,58 +482,58 @@
     <t xml:space="preserve">2.92425990104675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97092342376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01758718490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04869651794434</t>
+    <t xml:space="preserve">2.97092366218567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01758742332458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04869675636292</t>
   </si>
   <si>
     <t xml:space="preserve">3.03314185142517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06425142288208</t>
+    <t xml:space="preserve">3.0642511844635</t>
   </si>
   <si>
     <t xml:space="preserve">3.07980561256409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0604989528656</t>
+    <t xml:space="preserve">3.06049919128418</t>
   </si>
   <si>
     <t xml:space="preserve">3.02811288833618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01191973686218</t>
+    <t xml:space="preserve">3.01191997528076</t>
   </si>
   <si>
     <t xml:space="preserve">3.1090784072876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0928852558136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1252715587616</t>
+    <t xml:space="preserve">3.09288501739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12527132034302</t>
   </si>
   <si>
     <t xml:space="preserve">3.0766921043396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99572658538818</t>
+    <t xml:space="preserve">2.9957263469696</t>
   </si>
   <si>
     <t xml:space="preserve">3.30339574813843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41674757003784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35197520256042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33578181266785</t>
+    <t xml:space="preserve">3.41674733161926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35197496414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33578205108643</t>
   </si>
   <si>
     <t xml:space="preserve">3.36816811561584</t>
@@ -551,7 +551,7 @@
     <t xml:space="preserve">3.28720259666443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22243022918701</t>
+    <t xml:space="preserve">3.22243046760559</t>
   </si>
   <si>
     <t xml:space="preserve">3.17385101318359</t>
@@ -563,16 +563,16 @@
     <t xml:space="preserve">3.1414647102356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40055465698242</t>
+    <t xml:space="preserve">3.40055441856384</t>
   </si>
   <si>
     <t xml:space="preserve">3.49771332740784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38436102867126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25481653213501</t>
+    <t xml:space="preserve">3.38436126708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25481629371643</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004416465759</t>
@@ -587,10 +587,10 @@
     <t xml:space="preserve">2.80140924453735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88237476348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86618161201477</t>
+    <t xml:space="preserve">2.88237452507019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86618185043335</t>
   </si>
   <si>
     <t xml:space="preserve">2.84998846054077</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">2.72044348716736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83379554748535</t>
+    <t xml:space="preserve">2.83379530906677</t>
   </si>
   <si>
     <t xml:space="preserve">2.76902294158936</t>
@@ -614,7 +614,7 @@
     <t xml:space="preserve">2.73663687705994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81760239601135</t>
+    <t xml:space="preserve">2.81760215759277</t>
   </si>
   <si>
     <t xml:space="preserve">2.89856791496277</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">2.63947796821594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67186403274536</t>
+    <t xml:space="preserve">2.67186427116394</t>
   </si>
   <si>
     <t xml:space="preserve">2.62328481674194</t>
@@ -638,28 +638,28 @@
     <t xml:space="preserve">2.70425057411194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60709190368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59089875221252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42896747589111</t>
+    <t xml:space="preserve">2.60709166526794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5908989906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42896771430969</t>
   </si>
   <si>
     <t xml:space="preserve">2.54231929779053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46135377883911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.31561541557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2994225025177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35488152503967</t>
+    <t xml:space="preserve">2.46135354042053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3156156539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29942274093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35488176345825</t>
   </si>
   <si>
     <t xml:space="preserve">2.40607476234436</t>
@@ -671,13 +671,13 @@
     <t xml:space="preserve">2.13304495811462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08185219764709</t>
+    <t xml:space="preserve">2.08185195922852</t>
   </si>
   <si>
     <t xml:space="preserve">2.06478762626648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03065896034241</t>
+    <t xml:space="preserve">2.03065872192383</t>
   </si>
   <si>
     <t xml:space="preserve">2.1671736240387</t>
@@ -707,49 +707,49 @@
     <t xml:space="preserve">2.5767183303833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62791132926941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61084723472595</t>
+    <t xml:space="preserve">2.62791156768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61084699630737</t>
   </si>
   <si>
     <t xml:space="preserve">2.64497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59378266334534</t>
+    <t xml:space="preserve">2.59378290176392</t>
   </si>
   <si>
     <t xml:space="preserve">2.69616913795471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71323323249817</t>
+    <t xml:space="preserve">2.71323347091675</t>
   </si>
   <si>
     <t xml:space="preserve">2.44020342826843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4231390953064</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4743320941925</t>
+    <t xml:space="preserve">2.42313933372498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47433233261108</t>
   </si>
   <si>
     <t xml:space="preserve">2.15010929107666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33781719207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30368852615356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25249552726746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23543095588684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37194633483887</t>
+    <t xml:space="preserve">2.33781743049622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30368876457214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25249576568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23543119430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37194609642029</t>
   </si>
   <si>
     <t xml:space="preserve">2.38901042938232</t>
@@ -767,43 +767,43 @@
     <t xml:space="preserve">2.04772329330444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11598062515259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91120839118958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8770797252655</t>
+    <t xml:space="preserve">2.11598038673401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91120827198029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87707984447479</t>
   </si>
   <si>
     <t xml:space="preserve">1.84295094013214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97946572303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86001527309418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94533681869507</t>
+    <t xml:space="preserve">1.97946560382843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86001515388489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94533693790436</t>
   </si>
   <si>
     <t xml:space="preserve">1.96240139007568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99652981758118</t>
+    <t xml:space="preserve">1.99653005599976</t>
   </si>
   <si>
     <t xml:space="preserve">2.81561923027039</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9009416103363</t>
+    <t xml:space="preserve">2.90094137191772</t>
   </si>
   <si>
     <t xml:space="preserve">2.88387703895569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76442623138428</t>
+    <t xml:space="preserve">2.76442646980286</t>
   </si>
   <si>
     <t xml:space="preserve">2.73029780387878</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">2.6791045665741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74736213684082</t>
+    <t xml:space="preserve">2.74736189842224</t>
   </si>
   <si>
     <t xml:space="preserve">2.83268356323242</t>
@@ -824,7 +824,7 @@
     <t xml:space="preserve">2.79855513572693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78149080276489</t>
+    <t xml:space="preserve">2.78149056434631</t>
   </si>
   <si>
     <t xml:space="preserve">2.9350700378418</t>
@@ -833,40 +833,40 @@
     <t xml:space="preserve">2.96919870376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02039194107056</t>
+    <t xml:space="preserve">3.02039170265198</t>
   </si>
   <si>
     <t xml:space="preserve">3.00332713127136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03745627403259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98626303672791</t>
+    <t xml:space="preserve">3.03745603561401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98626279830933</t>
   </si>
   <si>
     <t xml:space="preserve">3.05452036857605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07158470153809</t>
+    <t xml:space="preserve">3.07158493995667</t>
   </si>
   <si>
     <t xml:space="preserve">3.13984251022339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11424565315247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1313099861145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06305241584778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16543865203857</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19956755638123</t>
+    <t xml:space="preserve">3.11424589157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13131022453308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06305265426636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16543889045715</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1995677947998</t>
   </si>
   <si>
     <t xml:space="preserve">3.15690660476685</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">3.27635717391968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24222826957703</t>
+    <t xml:space="preserve">3.24222850799561</t>
   </si>
   <si>
     <t xml:space="preserve">3.26782488822937</t>
@@ -887,10 +887,10 @@
     <t xml:space="preserve">3.31048607826233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3446147441864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32755041122437</t>
+    <t xml:space="preserve">3.34461498260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32755017280579</t>
   </si>
   <si>
     <t xml:space="preserve">3.28488922119141</t>
@@ -914,46 +914,46 @@
     <t xml:space="preserve">3.24974226951599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20606303215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15364742279053</t>
+    <t xml:space="preserve">3.20606279373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15364766120911</t>
   </si>
   <si>
     <t xml:space="preserve">3.21479892730713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17111945152283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26721405982971</t>
+    <t xml:space="preserve">3.17111968994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26721382141113</t>
   </si>
   <si>
     <t xml:space="preserve">3.36330842971802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49434661865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58170485496521</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56423354148865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59044122695923</t>
+    <t xml:space="preserve">3.49434638023376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58170533180237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56423330307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59044098854065</t>
   </si>
   <si>
     <t xml:space="preserve">3.5030825138092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51181817054749</t>
+    <t xml:space="preserve">3.51181840896606</t>
   </si>
   <si>
     <t xml:space="preserve">3.54676175117493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63412022590637</t>
+    <t xml:space="preserve">3.63411998748779</t>
   </si>
   <si>
     <t xml:space="preserve">3.62538456916809</t>
@@ -962,10 +962,10 @@
     <t xml:space="preserve">3.7476863861084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69527125358582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66906356811523</t>
+    <t xml:space="preserve">3.69527149200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66906380653381</t>
   </si>
   <si>
     <t xml:space="preserve">3.60791277885437</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">3.55549788475037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66032791137695</t>
+    <t xml:space="preserve">3.66032814979553</t>
   </si>
   <si>
     <t xml:space="preserve">3.65159201622009</t>
@@ -983,37 +983,37 @@
     <t xml:space="preserve">3.68653535842896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70400714874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75642275810242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57296943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53802609443665</t>
+    <t xml:space="preserve">3.7040069103241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75642251968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57296967506409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53802585601807</t>
   </si>
   <si>
     <t xml:space="preserve">3.3458366394043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3895161151886</t>
+    <t xml:space="preserve">3.38951635360718</t>
   </si>
   <si>
     <t xml:space="preserve">3.42445969581604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45066714286804</t>
+    <t xml:space="preserve">3.45066738128662</t>
   </si>
   <si>
     <t xml:space="preserve">3.44193148612976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4856104850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4069881439209</t>
+    <t xml:space="preserve">3.48561072349548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40698790550232</t>
   </si>
   <si>
     <t xml:space="preserve">3.35457253456116</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">3.46813893318176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47687482833862</t>
+    <t xml:space="preserve">3.47687458992004</t>
   </si>
   <si>
     <t xml:space="preserve">3.79136610031128</t>
@@ -1040,22 +1040,22 @@
     <t xml:space="preserve">3.87872457504272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17574453353882</t>
+    <t xml:space="preserve">4.17574405670166</t>
   </si>
   <si>
     <t xml:space="preserve">4.31551790237427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35046148300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1844801902771</t>
+    <t xml:space="preserve">4.35046100616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18447971343994</t>
   </si>
   <si>
     <t xml:space="preserve">4.20195150375366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25436639785767</t>
+    <t xml:space="preserve">4.25436687469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.14080047607422</t>
@@ -1067,19 +1067,19 @@
     <t xml:space="preserve">3.98355507850647</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94861149787903</t>
+    <t xml:space="preserve">3.94861173629761</t>
   </si>
   <si>
     <t xml:space="preserve">3.93113970756531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08838558197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07091331481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12332916259766</t>
+    <t xml:space="preserve">4.08838510513306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07091379165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12332820892334</t>
   </si>
   <si>
     <t xml:space="preserve">4.00102663040161</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">4.00976276397705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93987584114075</t>
+    <t xml:space="preserve">3.93987560272217</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
@@ -1097,13 +1097,13 @@
     <t xml:space="preserve">4.2106876373291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29804611206055</t>
+    <t xml:space="preserve">4.29804658889771</t>
   </si>
   <si>
     <t xml:space="preserve">4.28930997848511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21942377090454</t>
+    <t xml:space="preserve">4.21942329406738</t>
   </si>
   <si>
     <t xml:space="preserve">4.19321632385254</t>
@@ -1112,7 +1112,7 @@
     <t xml:space="preserve">4.14953660964966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16700792312622</t>
+    <t xml:space="preserve">4.16700839996338</t>
   </si>
   <si>
     <t xml:space="preserve">4.11459302902222</t>
@@ -1121,46 +1121,46 @@
     <t xml:space="preserve">4.06217765808105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78262996673584</t>
+    <t xml:space="preserve">3.78263020515442</t>
   </si>
   <si>
     <t xml:space="preserve">3.80010175704956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82630944252014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83504557609558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84378147125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77389430999756</t>
+    <t xml:space="preserve">3.82630968093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.835045337677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84378123283386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77389454841614</t>
   </si>
   <si>
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734739303589</t>
+    <t xml:space="preserve">3.95734763145447</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86125302314758</t>
+    <t xml:space="preserve">3.861252784729</t>
   </si>
   <si>
     <t xml:space="preserve">3.76515817642212</t>
   </si>
   <si>
-    <t xml:space="preserve">3.81757354736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64285635948181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67779946327209</t>
+    <t xml:space="preserve">3.8175733089447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64285612106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67779970169067</t>
   </si>
   <si>
     <t xml:space="preserve">3.7389509677887</t>
@@ -1169,10 +1169,10 @@
     <t xml:space="preserve">3.85251712799072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71274304389954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92240381240845</t>
+    <t xml:space="preserve">3.71274328231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92240357398987</t>
   </si>
   <si>
     <t xml:space="preserve">3.61664843559265</t>
@@ -1181,40 +1181,40 @@
     <t xml:space="preserve">3.39825224876404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23227071762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05755305290222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97019481658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95272302627563</t>
+    <t xml:space="preserve">3.23227047920227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05755352973938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97019457817078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95272278785706</t>
   </si>
   <si>
     <t xml:space="preserve">2.91777944564819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90904331207275</t>
+    <t xml:space="preserve">2.90904355049133</t>
   </si>
   <si>
     <t xml:space="preserve">3.37204432487488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38078022003174</t>
+    <t xml:space="preserve">3.38077998161316</t>
   </si>
   <si>
     <t xml:space="preserve">3.41572380065918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31962895393372</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27595019340515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28468561172485</t>
+    <t xml:space="preserve">3.31962919235229</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27594995498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28468585014343</t>
   </si>
   <si>
     <t xml:space="preserve">3.50245499610901</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">3.32098078727722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26653814315796</t>
+    <t xml:space="preserve">3.26653838157654</t>
   </si>
   <si>
     <t xml:space="preserve">3.39357042312622</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">3.23024344444275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19394874572754</t>
+    <t xml:space="preserve">3.19394850730896</t>
   </si>
   <si>
     <t xml:space="preserve">3.25746440887451</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">3.2211697101593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10321140289307</t>
+    <t xml:space="preserve">3.10321164131165</t>
   </si>
   <si>
     <t xml:space="preserve">2.99432682991028</t>
@@ -1286,13 +1286,13 @@
     <t xml:space="preserve">2.95803189277649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85822105407715</t>
+    <t xml:space="preserve">2.85822129249573</t>
   </si>
   <si>
     <t xml:space="preserve">2.89451599121094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8672947883606</t>
+    <t xml:space="preserve">2.86729502677917</t>
   </si>
   <si>
     <t xml:space="preserve">2.81285238265991</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">2.75841021537781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70396780967712</t>
+    <t xml:space="preserve">2.7039680480957</t>
   </si>
   <si>
     <t xml:space="preserve">2.72211527824402</t>
@@ -1313,16 +1313,16 @@
     <t xml:space="preserve">2.64952564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7947051525116</t>
+    <t xml:space="preserve">2.79470491409302</t>
   </si>
   <si>
     <t xml:space="preserve">2.92173719406128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05784273147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02154803276062</t>
+    <t xml:space="preserve">3.05784296989441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02154779434204</t>
   </si>
   <si>
     <t xml:space="preserve">3.13950634002686</t>
@@ -1352,46 +1352,46 @@
     <t xml:space="preserve">3.08506417274475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01247429847717</t>
+    <t xml:space="preserve">3.01247406005859</t>
   </si>
   <si>
     <t xml:space="preserve">2.88544225692749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7765576839447</t>
+    <t xml:space="preserve">2.77655744552612</t>
   </si>
   <si>
     <t xml:space="preserve">2.71304154396057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6313784122467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68582034111023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66767287254333</t>
+    <t xml:space="preserve">2.63137817382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68582057952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66767311096191</t>
   </si>
   <si>
     <t xml:space="preserve">2.55878829956055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52249336242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67674660682678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64045214653015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87636852264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83099985122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60415697097778</t>
+    <t xml:space="preserve">2.52249360084534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67674684524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64045190811157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87636876106262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83099961280823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6041567325592</t>
   </si>
   <si>
     <t xml:space="preserve">2.73118901252747</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">2.91266345977783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12135887145996</t>
+    <t xml:space="preserve">3.12135910987854</t>
   </si>
   <si>
     <t xml:space="preserve">3.0759904384613</t>
@@ -1427,46 +1427,46 @@
     <t xml:space="preserve">3.0941379070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38449692726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41171765327454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37542319297791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42079138755798</t>
+    <t xml:space="preserve">3.38449668884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41171789169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37542295455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42079162597656</t>
   </si>
   <si>
     <t xml:space="preserve">3.43893885612488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36634945869446</t>
+    <t xml:space="preserve">3.36634922027588</t>
   </si>
   <si>
     <t xml:space="preserve">3.35727572441101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20302248001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27561187744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29375958442688</t>
+    <t xml:space="preserve">3.20302224159241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27561211585999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29375982284546</t>
   </si>
   <si>
     <t xml:space="preserve">3.1667275428772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11228513717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78563141822815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84007382392883</t>
+    <t xml:space="preserve">3.11228537559509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78563117980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84007358551025</t>
   </si>
   <si>
     <t xml:space="preserve">2.82192611694336</t>
@@ -56410,7 +56410,7 @@
     </row>
     <row r="2090">
       <c r="A2090" s="1" t="n">
-        <v>46006.6909953704</v>
+        <v>46006.3333333333</v>
       </c>
       <c r="B2090" t="n">
         <v>60484</v>
@@ -56431,6 +56431,32 @@
         <v>581</v>
       </c>
       <c r="H2090" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2091">
+      <c r="A2091" s="1" t="n">
+        <v>46007.6911458333</v>
+      </c>
+      <c r="B2091" t="n">
+        <v>59641</v>
+      </c>
+      <c r="C2091" t="n">
+        <v>3.94000005722046</v>
+      </c>
+      <c r="D2091" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="E2091" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="F2091" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="G2091" t="s">
+        <v>581</v>
+      </c>
+      <c r="H2091" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="583" uniqueCount="583">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="584">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02345776557922</t>
+    <t xml:space="preserve">3.02345752716064</t>
   </si>
   <si>
     <t xml:space="preserve">NDT.MI</t>
@@ -56,52 +56,52 @@
     <t xml:space="preserve">2.97266817092896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94578003883362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95773029327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9622118473053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93532347679138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91291618347168</t>
+    <t xml:space="preserve">2.94577980041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95773005485535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96221160888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9353232383728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91291642189026</t>
   </si>
   <si>
     <t xml:space="preserve">2.97864365577698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98611235618591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03540802001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05632138252258</t>
+    <t xml:space="preserve">2.98611259460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03540825843811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.056321144104</t>
   </si>
   <si>
     <t xml:space="preserve">3.0593090057373</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05034589767456</t>
+    <t xml:space="preserve">3.05034613609314</t>
   </si>
   <si>
     <t xml:space="preserve">2.98760628700256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95026111602783</t>
+    <t xml:space="preserve">2.95026135444641</t>
   </si>
   <si>
     <t xml:space="preserve">3.01598882675171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01001310348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02495121955872</t>
+    <t xml:space="preserve">3.01001381874084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02495169639587</t>
   </si>
   <si>
     <t xml:space="preserve">3.0174822807312</t>
@@ -113,22 +113,22 @@
     <t xml:space="preserve">2.99955677986145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0443708896637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.959223985672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00254416465759</t>
+    <t xml:space="preserve">3.04437112808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95922374725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00254440307617</t>
   </si>
   <si>
     <t xml:space="preserve">2.92785429954529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90843462944031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.896484375</t>
+    <t xml:space="preserve">2.90843486785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89648461341858</t>
   </si>
   <si>
     <t xml:space="preserve">2.91889142990112</t>
@@ -143,22 +143,22 @@
     <t xml:space="preserve">2.90544724464417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90992832183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92337274551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83822584152222</t>
+    <t xml:space="preserve">2.90992856025696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9233729839325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8382260799408</t>
   </si>
   <si>
     <t xml:space="preserve">2.86063313484192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82627558708191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77996754646301</t>
+    <t xml:space="preserve">2.82627534866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77996730804443</t>
   </si>
   <si>
     <t xml:space="preserve">2.84569501876831</t>
@@ -170,40 +170,40 @@
     <t xml:space="preserve">2.88303995132446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79639959335327</t>
+    <t xml:space="preserve">2.79639935493469</t>
   </si>
   <si>
     <t xml:space="preserve">2.87557077407837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89797830581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80088114738464</t>
+    <t xml:space="preserve">2.89797806739807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80088090896606</t>
   </si>
   <si>
     <t xml:space="preserve">2.74262261390686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8217945098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75009155273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76353621482849</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77847409248352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78594303131104</t>
+    <t xml:space="preserve">2.82179403305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7500913143158</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76353597640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77847385406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78594279289246</t>
   </si>
   <si>
     <t xml:space="preserve">2.79341197013855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69631481170654</t>
+    <t xml:space="preserve">2.69631457328796</t>
   </si>
   <si>
     <t xml:space="preserve">2.6515007019043</t>
@@ -212,13 +212,13 @@
     <t xml:space="preserve">2.62162446975708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53946566581726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56934142112732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61415553092957</t>
+    <t xml:space="preserve">2.53946542739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5693416595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61415576934814</t>
   </si>
   <si>
     <t xml:space="preserve">2.65896964073181</t>
@@ -230,19 +230,19 @@
     <t xml:space="preserve">2.70378375053406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77100491523743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81581878662109</t>
+    <t xml:space="preserve">2.77100467681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81581902503967</t>
   </si>
   <si>
     <t xml:space="preserve">2.73365998268127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66643881797791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68137669563293</t>
+    <t xml:space="preserve">2.66643857955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68137645721436</t>
   </si>
   <si>
     <t xml:space="preserve">2.74112892150879</t>
@@ -251,19 +251,19 @@
     <t xml:space="preserve">2.72619080543518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8307569026947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.893150806427</t>
+    <t xml:space="preserve">2.83075714111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89315056800842</t>
   </si>
   <si>
     <t xml:space="preserve">2.69871830940247</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83870983123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93203687667847</t>
+    <t xml:space="preserve">2.83870959281921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93203711509705</t>
   </si>
   <si>
     <t xml:space="preserve">2.87759637832642</t>
@@ -272,7 +272,7 @@
     <t xml:space="preserve">2.83093237876892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81537771224976</t>
+    <t xml:space="preserve">2.81537747383118</t>
   </si>
   <si>
     <t xml:space="preserve">2.84648704528809</t>
@@ -281,55 +281,55 @@
     <t xml:space="preserve">2.79982304573059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73760461807251</t>
+    <t xml:space="preserve">2.73760509490967</t>
   </si>
   <si>
     <t xml:space="preserve">2.76093673706055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80760049819946</t>
+    <t xml:space="preserve">2.80760025978088</t>
   </si>
   <si>
     <t xml:space="preserve">3.00980973243713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95536875724792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90870547294617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88537335395813</t>
+    <t xml:space="preserve">2.9553689956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90870523452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88537311553955</t>
   </si>
   <si>
     <t xml:space="preserve">2.82315516471863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86204147338867</t>
+    <t xml:space="preserve">2.86204171180725</t>
   </si>
   <si>
     <t xml:space="preserve">3.00203251838684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91648268699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85426449775696</t>
+    <t xml:space="preserve">2.9164822101593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85426425933838</t>
   </si>
   <si>
     <t xml:space="preserve">2.7298276424408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68316388130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72205018997192</t>
+    <t xml:space="preserve">2.68316411972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7220504283905</t>
   </si>
   <si>
     <t xml:space="preserve">2.75315976142883</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70649552345276</t>
+    <t xml:space="preserve">2.70649600028992</t>
   </si>
   <si>
     <t xml:space="preserve">2.93981432914734</t>
@@ -344,22 +344,22 @@
     <t xml:space="preserve">2.86981868743896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94759154319763</t>
+    <t xml:space="preserve">2.94759178161621</t>
   </si>
   <si>
     <t xml:space="preserve">2.98647785186768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63650012016296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55094981193542</t>
+    <t xml:space="preserve">2.63650035858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.550950050354</t>
   </si>
   <si>
     <t xml:space="preserve">2.51984095573425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41095900535583</t>
+    <t xml:space="preserve">2.41095876693726</t>
   </si>
   <si>
     <t xml:space="preserve">2.34096336364746</t>
@@ -368,28 +368,28 @@
     <t xml:space="preserve">2.34874057769775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36429524421692</t>
+    <t xml:space="preserve">2.3642954826355</t>
   </si>
   <si>
     <t xml:space="preserve">2.2554132938385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24763584136963</t>
+    <t xml:space="preserve">2.24763607978821</t>
   </si>
   <si>
     <t xml:space="preserve">2.3254086971283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23208093643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18541765213013</t>
+    <t xml:space="preserve">2.23208117485046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18541741371155</t>
   </si>
   <si>
     <t xml:space="preserve">2.27874517440796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26319026947021</t>
+    <t xml:space="preserve">2.26319050788879</t>
   </si>
   <si>
     <t xml:space="preserve">2.21652674674988</t>
@@ -404,25 +404,25 @@
     <t xml:space="preserve">2.10764455795288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15430879592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17764043807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22430372238159</t>
+    <t xml:space="preserve">2.15430808067322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17764019966125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22430396080017</t>
   </si>
   <si>
     <t xml:space="preserve">2.35651779174805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48873162269592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52761816978455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43429064750671</t>
+    <t xml:space="preserve">2.4887318611145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52761793136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43429088592529</t>
   </si>
   <si>
     <t xml:space="preserve">2.44206809997559</t>
@@ -431,58 +431,58 @@
     <t xml:space="preserve">2.5587272644043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44984555244446</t>
+    <t xml:space="preserve">2.44984531402588</t>
   </si>
   <si>
     <t xml:space="preserve">2.37207221984863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33318591117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29429960250854</t>
+    <t xml:space="preserve">2.33318614959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29429984092712</t>
   </si>
   <si>
     <t xml:space="preserve">2.37984991073608</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71427321434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58205914497375</t>
+    <t xml:space="preserve">2.71427297592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58205938339233</t>
   </si>
   <si>
     <t xml:space="preserve">2.62872314453125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65983200073242</t>
+    <t xml:space="preserve">2.65983247756958</t>
   </si>
   <si>
     <t xml:space="preserve">2.57428193092346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67538642883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64427781105042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69094109535217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76871418952942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90092802047729</t>
+    <t xml:space="preserve">2.67538690567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64427757263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69094133377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76871395111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90092778205872</t>
   </si>
   <si>
     <t xml:space="preserve">2.9631462097168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92425966262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97092318534851</t>
+    <t xml:space="preserve">2.92425990104675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97092366218567</t>
   </si>
   <si>
     <t xml:space="preserve">3.01758742332458</t>
@@ -491,7 +491,7 @@
     <t xml:space="preserve">3.04869675636292</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03314185142517</t>
+    <t xml:space="preserve">3.03314208984375</t>
   </si>
   <si>
     <t xml:space="preserve">3.0642511844635</t>
@@ -509,10 +509,10 @@
     <t xml:space="preserve">3.01191973686218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10907816886902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09288549423218</t>
+    <t xml:space="preserve">3.1090784072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09288501739502</t>
   </si>
   <si>
     <t xml:space="preserve">3.12527132034302</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">3.0766921043396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99572658538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30339574813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41674757003784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35197520256042</t>
+    <t xml:space="preserve">2.99572682380676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30339598655701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41674709320068</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35197496414185</t>
   </si>
   <si>
     <t xml:space="preserve">3.33578181266785</t>
@@ -542,13 +542,13 @@
     <t xml:space="preserve">3.23862338066101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31958913803101</t>
+    <t xml:space="preserve">3.31958866119385</t>
   </si>
   <si>
     <t xml:space="preserve">3.27100944519043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28720235824585</t>
+    <t xml:space="preserve">3.28720259666443</t>
   </si>
   <si>
     <t xml:space="preserve">3.22243022918701</t>
@@ -560,16 +560,16 @@
     <t xml:space="preserve">3.20623707771301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1414647102356</t>
+    <t xml:space="preserve">3.14146447181702</t>
   </si>
   <si>
     <t xml:space="preserve">3.40055441856384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49771308898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38436126708984</t>
+    <t xml:space="preserve">3.49771356582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38436150550842</t>
   </si>
   <si>
     <t xml:space="preserve">3.25481629371643</t>
@@ -578,10 +578,10 @@
     <t xml:space="preserve">3.19004416465759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96334028244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97953343391418</t>
+    <t xml:space="preserve">2.96334052085876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97953367233276</t>
   </si>
   <si>
     <t xml:space="preserve">2.80140924453735</t>
@@ -593,16 +593,16 @@
     <t xml:space="preserve">2.86618161201477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84998822212219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78521609306335</t>
+    <t xml:space="preserve">2.84998869895935</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78521633148193</t>
   </si>
   <si>
     <t xml:space="preserve">2.75282979011536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72044372558594</t>
+    <t xml:space="preserve">2.72044348716736</t>
   </si>
   <si>
     <t xml:space="preserve">2.83379530906677</t>
@@ -611,10 +611,10 @@
     <t xml:space="preserve">2.76902318000793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73663711547852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81760239601135</t>
+    <t xml:space="preserve">2.73663663864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81760215759277</t>
   </si>
   <si>
     <t xml:space="preserve">2.89856767654419</t>
@@ -623,22 +623,22 @@
     <t xml:space="preserve">2.91476082801819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63947796821594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67186403274536</t>
+    <t xml:space="preserve">2.63947772979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67186427116394</t>
   </si>
   <si>
     <t xml:space="preserve">2.62328481674194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68805718421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70425033569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60709166526794</t>
+    <t xml:space="preserve">2.68805742263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70425009727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60709190368652</t>
   </si>
   <si>
     <t xml:space="preserve">2.59089875221252</t>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">2.42896747589111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54231905937195</t>
+    <t xml:space="preserve">2.54231929779053</t>
   </si>
   <si>
     <t xml:space="preserve">2.46135377883911</t>
@@ -665,10 +665,10 @@
     <t xml:space="preserve">2.40607476234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28662443161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13304495811462</t>
+    <t xml:space="preserve">2.28662419319153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1330451965332</t>
   </si>
   <si>
     <t xml:space="preserve">2.08185195922852</t>
@@ -677,13 +677,13 @@
     <t xml:space="preserve">2.06478762626648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03065872192383</t>
+    <t xml:space="preserve">2.03065896034241</t>
   </si>
   <si>
     <t xml:space="preserve">2.1671736240387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09891629219055</t>
+    <t xml:space="preserve">2.09891605377197</t>
   </si>
   <si>
     <t xml:space="preserve">2.26955986022949</t>
@@ -695,19 +695,19 @@
     <t xml:space="preserve">2.32075309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55965399742126</t>
+    <t xml:space="preserve">2.55965423583984</t>
   </si>
   <si>
     <t xml:space="preserve">2.54258990287781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45726823806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57671856880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62791132926941</t>
+    <t xml:space="preserve">2.45726799964905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5767183303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62791156768799</t>
   </si>
   <si>
     <t xml:space="preserve">2.61084699630737</t>
@@ -716,16 +716,16 @@
     <t xml:space="preserve">2.64497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59378266334534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69616889953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71323323249817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44020342826843</t>
+    <t xml:space="preserve">2.59378290176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69616913795471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71323299407959</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44020318984985</t>
   </si>
   <si>
     <t xml:space="preserve">2.42313933372498</t>
@@ -734,25 +734,25 @@
     <t xml:space="preserve">2.47433233261108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15010929107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33781719207764</t>
+    <t xml:space="preserve">2.15010952949524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33781743049622</t>
   </si>
   <si>
     <t xml:space="preserve">2.30368852615356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25249576568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23543119430542</t>
+    <t xml:space="preserve">2.25249552726746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23543095588684</t>
   </si>
   <si>
     <t xml:space="preserve">2.37194609642029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3890106678009</t>
+    <t xml:space="preserve">2.38901042938232</t>
   </si>
   <si>
     <t xml:space="preserve">2.20130252838135</t>
@@ -764,16 +764,16 @@
     <t xml:space="preserve">2.01359438896179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04772329330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11598062515259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91120851039886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87707984447479</t>
+    <t xml:space="preserve">2.04772305488586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11598038673401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91120827198029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8770797252655</t>
   </si>
   <si>
     <t xml:space="preserve">1.84295094013214</t>
@@ -782,82 +782,82 @@
     <t xml:space="preserve">1.97946584224701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86001515388489</t>
+    <t xml:space="preserve">1.86001539230347</t>
   </si>
   <si>
     <t xml:space="preserve">1.94533717632294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96240127086639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99652993679047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81561923027039</t>
+    <t xml:space="preserve">1.96240139007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99653005599976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81561946868896</t>
   </si>
   <si>
     <t xml:space="preserve">2.90094137191772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88387703895569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76442623138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73029756546021</t>
+    <t xml:space="preserve">2.88387680053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76442670822144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73029780387878</t>
   </si>
   <si>
     <t xml:space="preserve">2.6791045665741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74736189842224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83268356323242</t>
+    <t xml:space="preserve">2.74736213684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.832683801651</t>
   </si>
   <si>
     <t xml:space="preserve">2.86681246757507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79855489730835</t>
+    <t xml:space="preserve">2.79855513572693</t>
   </si>
   <si>
     <t xml:space="preserve">2.78149056434631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9350700378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96919846534729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02039194107056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00332713127136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03745603561401</t>
+    <t xml:space="preserve">2.93507027626038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96919894218445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02039170265198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00332736968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03745627403259</t>
   </si>
   <si>
     <t xml:space="preserve">2.98626303672791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05452060699463</t>
+    <t xml:space="preserve">3.05452013015747</t>
   </si>
   <si>
     <t xml:space="preserve">3.07158470153809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13984227180481</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.11424589157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1313099861145</t>
+    <t xml:space="preserve">3.13984251022339</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.11424565315247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13131022453308</t>
   </si>
   <si>
     <t xml:space="preserve">3.06305265426636</t>
@@ -875,13 +875,13 @@
     <t xml:space="preserve">3.2336962223053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27635717391968</t>
+    <t xml:space="preserve">3.2763569355011</t>
   </si>
   <si>
     <t xml:space="preserve">3.24222850799561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26782488822937</t>
+    <t xml:space="preserve">3.26782512664795</t>
   </si>
   <si>
     <t xml:space="preserve">3.31048607826233</t>
@@ -890,22 +890,22 @@
     <t xml:space="preserve">3.3446147441864</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32755041122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28488945960999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18250346183777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29342150688171</t>
+    <t xml:space="preserve">3.32755017280579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28488922119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18250298500061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29342126846313</t>
   </si>
   <si>
     <t xml:space="preserve">3.33710074424744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32836484909058</t>
+    <t xml:space="preserve">3.32836508750916</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342174530029</t>
@@ -926,7 +926,7 @@
     <t xml:space="preserve">3.17111968994141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26721405982971</t>
+    <t xml:space="preserve">3.26721382141113</t>
   </si>
   <si>
     <t xml:space="preserve">3.36330842971802</t>
@@ -938,22 +938,22 @@
     <t xml:space="preserve">3.58170509338379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56423354148865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59044122695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5030825138092</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51181817054749</t>
+    <t xml:space="preserve">3.56423330307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59044098854065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50308275222778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51181840896606</t>
   </si>
   <si>
     <t xml:space="preserve">3.54676151275635</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63412046432495</t>
+    <t xml:space="preserve">3.63412022590637</t>
   </si>
   <si>
     <t xml:space="preserve">3.62538480758667</t>
@@ -962,22 +962,22 @@
     <t xml:space="preserve">3.74768662452698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69527125358582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66906356811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60791301727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55549764633179</t>
+    <t xml:space="preserve">3.69527149200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66906380653381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60791277885437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55549788475037</t>
   </si>
   <si>
     <t xml:space="preserve">3.66032791137695</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65159177780151</t>
+    <t xml:space="preserve">3.65159201622009</t>
   </si>
   <si>
     <t xml:space="preserve">3.68653535842896</t>
@@ -995,25 +995,25 @@
     <t xml:space="preserve">3.53802585601807</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3458366394043</t>
+    <t xml:space="preserve">3.34583687782288</t>
   </si>
   <si>
     <t xml:space="preserve">3.38951635360718</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42445969581604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45066738128662</t>
+    <t xml:space="preserve">3.42445945739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45066714286804</t>
   </si>
   <si>
     <t xml:space="preserve">3.44193148612976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4856104850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4069881439209</t>
+    <t xml:space="preserve">3.48561072349548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40698790550232</t>
   </si>
   <si>
     <t xml:space="preserve">3.35457253456116</t>
@@ -1022,7 +1022,7 @@
     <t xml:space="preserve">3.45940327644348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52928972244263</t>
+    <t xml:space="preserve">3.52928996086121</t>
   </si>
   <si>
     <t xml:space="preserve">3.46813893318176</t>
@@ -1031,13 +1031,13 @@
     <t xml:space="preserve">3.47687458992004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79136633872986</t>
+    <t xml:space="preserve">3.79136610031128</t>
   </si>
   <si>
     <t xml:space="preserve">3.7214789390564</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8787248134613</t>
+    <t xml:space="preserve">3.87872457504272</t>
   </si>
   <si>
     <t xml:space="preserve">4.17574453353882</t>
@@ -1049,34 +1049,34 @@
     <t xml:space="preserve">4.35046148300171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18447971343994</t>
+    <t xml:space="preserve">4.1844801902771</t>
   </si>
   <si>
     <t xml:space="preserve">4.20195150375366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25436687469482</t>
+    <t xml:space="preserve">4.25436639785767</t>
   </si>
   <si>
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493202209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98355484008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94861197471619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93114018440247</t>
+    <t xml:space="preserve">3.90493178367615</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98355507850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94861173629761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93113970756531</t>
   </si>
   <si>
     <t xml:space="preserve">4.08838510513306</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07091331481934</t>
+    <t xml:space="preserve">4.07091379165649</t>
   </si>
   <si>
     <t xml:space="preserve">4.1233286857605</t>
@@ -1085,7 +1085,7 @@
     <t xml:space="preserve">4.00102663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00976276397705</t>
+    <t xml:space="preserve">4.00976228713989</t>
   </si>
   <si>
     <t xml:space="preserve">3.93987607955933</t>
@@ -1094,16 +1094,16 @@
     <t xml:space="preserve">4.0971212387085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2106876373291</t>
+    <t xml:space="preserve">4.21068716049194</t>
   </si>
   <si>
     <t xml:space="preserve">4.29804611206055</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28931045532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21942329406738</t>
+    <t xml:space="preserve">4.28930997848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21942377090454</t>
   </si>
   <si>
     <t xml:space="preserve">4.19321584701538</t>
@@ -1112,70 +1112,70 @@
     <t xml:space="preserve">4.1495361328125</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16700792312622</t>
+    <t xml:space="preserve">4.16700839996338</t>
   </si>
   <si>
     <t xml:space="preserve">4.11459302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06217813491821</t>
+    <t xml:space="preserve">4.06217765808105</t>
   </si>
   <si>
     <t xml:space="preserve">3.78262996673584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80010175704956</t>
+    <t xml:space="preserve">3.80010151863098</t>
   </si>
   <si>
     <t xml:space="preserve">3.82630968093872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83504509925842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84378099441528</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77389454841614</t>
+    <t xml:space="preserve">3.83504486083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84378123283386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77389430999756</t>
   </si>
   <si>
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734786987305</t>
+    <t xml:space="preserve">3.95734763145447</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86125302314758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76515865325928</t>
+    <t xml:space="preserve">3.861252784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7651584148407</t>
   </si>
   <si>
     <t xml:space="preserve">3.8175733089447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64285612106323</t>
+    <t xml:space="preserve">3.64285635948181</t>
   </si>
   <si>
     <t xml:space="preserve">3.67779970169067</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73895072937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85251665115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71274304389954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92240381240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61664867401123</t>
+    <t xml:space="preserve">3.7389509677887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85251712799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71274328231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92240357398987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61664843559265</t>
   </si>
   <si>
     <t xml:space="preserve">3.39825224876404</t>
@@ -1190,7 +1190,7 @@
     <t xml:space="preserve">2.97019457817078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95272302627563</t>
+    <t xml:space="preserve">2.95272278785706</t>
   </si>
   <si>
     <t xml:space="preserve">2.91777920722961</t>
@@ -1202,13 +1202,13 @@
     <t xml:space="preserve">3.37204432487488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38078022003174</t>
+    <t xml:space="preserve">3.38077998161316</t>
   </si>
   <si>
     <t xml:space="preserve">3.41572380065918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31962895393372</t>
+    <t xml:space="preserve">3.31962919235229</t>
   </si>
   <si>
     <t xml:space="preserve">3.27594995498657</t>
@@ -1761,6 +1761,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.57999992370605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51999998092651</t>
   </si>
 </sst>
 </file>
@@ -56491,7 +56494,7 @@
     </row>
     <row r="2093">
       <c r="A2093" s="1" t="n">
-        <v>46009.6868865741</v>
+        <v>46009.3333333333</v>
       </c>
       <c r="B2093" t="n">
         <v>29296</v>
@@ -56512,6 +56515,32 @@
         <v>582</v>
       </c>
       <c r="H2093" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2094">
+      <c r="A2094" s="1" t="n">
+        <v>46010.6909837963</v>
+      </c>
+      <c r="B2094" t="n">
+        <v>63969</v>
+      </c>
+      <c r="C2094" t="n">
+        <v>3.77999997138977</v>
+      </c>
+      <c r="D2094" t="n">
+        <v>3.46000003814697</v>
+      </c>
+      <c r="E2094" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="F2094" t="n">
+        <v>3.51999998092651</v>
+      </c>
+      <c r="G2094" t="s">
+        <v>583</v>
+      </c>
+      <c r="H2094" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="584" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="585" uniqueCount="585">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02345752716064</t>
+    <t xml:space="preserve">3.02345776557922</t>
   </si>
   <si>
     <t xml:space="preserve">NDT.MI</t>
@@ -59,7 +59,7 @@
     <t xml:space="preserve">2.94577980041504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95773005485535</t>
+    <t xml:space="preserve">2.95773029327393</t>
   </si>
   <si>
     <t xml:space="preserve">2.96221160888672</t>
@@ -68,19 +68,19 @@
     <t xml:space="preserve">2.9353232383728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91291642189026</t>
+    <t xml:space="preserve">2.91291618347168</t>
   </si>
   <si>
     <t xml:space="preserve">2.97864365577698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98611259460449</t>
+    <t xml:space="preserve">2.98611235618591</t>
   </si>
   <si>
     <t xml:space="preserve">3.03540825843811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.056321144104</t>
+    <t xml:space="preserve">3.05632138252258</t>
   </si>
   <si>
     <t xml:space="preserve">3.0593090057373</t>
@@ -89,7 +89,7 @@
     <t xml:space="preserve">3.05034613609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98760628700256</t>
+    <t xml:space="preserve">2.98760604858398</t>
   </si>
   <si>
     <t xml:space="preserve">2.95026135444641</t>
@@ -101,7 +101,7 @@
     <t xml:space="preserve">3.01001381874084</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02495169639587</t>
+    <t xml:space="preserve">3.02495145797729</t>
   </si>
   <si>
     <t xml:space="preserve">3.0174822807312</t>
@@ -116,25 +116,25 @@
     <t xml:space="preserve">3.04437112808228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95922374725342</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00254440307617</t>
+    <t xml:space="preserve">2.95922422409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00254464149475</t>
   </si>
   <si>
     <t xml:space="preserve">2.92785429954529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90843486785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89648461341858</t>
+    <t xml:space="preserve">2.90843510627747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.896484375</t>
   </si>
   <si>
     <t xml:space="preserve">2.91889142990112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9159038066864</t>
+    <t xml:space="preserve">2.91590356826782</t>
   </si>
   <si>
     <t xml:space="preserve">2.92038536071777</t>
@@ -143,22 +143,22 @@
     <t xml:space="preserve">2.90544724464417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90992856025696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9233729839325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8382260799408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86063313484192</t>
+    <t xml:space="preserve">2.90992879867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92337274551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83822584152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8606333732605</t>
   </si>
   <si>
     <t xml:space="preserve">2.82627534866333</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77996730804443</t>
+    <t xml:space="preserve">2.77996754646301</t>
   </si>
   <si>
     <t xml:space="preserve">2.84569501876831</t>
@@ -167,16 +167,16 @@
     <t xml:space="preserve">2.86810183525085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88303995132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79639935493469</t>
+    <t xml:space="preserve">2.88304018974304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79639959335327</t>
   </si>
   <si>
     <t xml:space="preserve">2.87557077407837</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89797806739807</t>
+    <t xml:space="preserve">2.89797830581665</t>
   </si>
   <si>
     <t xml:space="preserve">2.80088090896606</t>
@@ -185,25 +185,25 @@
     <t xml:space="preserve">2.74262261390686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82179403305054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7500913143158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76353597640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77847385406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78594279289246</t>
+    <t xml:space="preserve">2.82179427146912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75009155273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76353573799133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77847409248352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78594303131104</t>
   </si>
   <si>
     <t xml:space="preserve">2.79341197013855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69631457328796</t>
+    <t xml:space="preserve">2.69631481170654</t>
   </si>
   <si>
     <t xml:space="preserve">2.6515007019043</t>
@@ -215,31 +215,31 @@
     <t xml:space="preserve">2.53946542739868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5693416595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61415576934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65896964073181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68884539604187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70378375053406</t>
+    <t xml:space="preserve">2.56934118270874</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61415553092957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65896987915039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68884563446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70378351211548</t>
   </si>
   <si>
     <t xml:space="preserve">2.77100467681885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81581902503967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73365998268127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66643857955933</t>
+    <t xml:space="preserve">2.81581878662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7336597442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66643881797791</t>
   </si>
   <si>
     <t xml:space="preserve">2.68137645721436</t>
@@ -248,31 +248,31 @@
     <t xml:space="preserve">2.74112892150879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72619080543518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83075714111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89315056800842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69871830940247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83870959281921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93203711509705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87759637832642</t>
+    <t xml:space="preserve">2.72619104385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8307569026947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.893150806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69871854782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83870983123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93203687667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87759590148926</t>
   </si>
   <si>
     <t xml:space="preserve">2.83093237876892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81537747383118</t>
+    <t xml:space="preserve">2.81537771224976</t>
   </si>
   <si>
     <t xml:space="preserve">2.84648704528809</t>
@@ -281,7 +281,7 @@
     <t xml:space="preserve">2.79982304573059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73760509490967</t>
+    <t xml:space="preserve">2.73760461807251</t>
   </si>
   <si>
     <t xml:space="preserve">2.76093673706055</t>
@@ -290,7 +290,7 @@
     <t xml:space="preserve">2.80760025978088</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00980973243713</t>
+    <t xml:space="preserve">3.00980997085571</t>
   </si>
   <si>
     <t xml:space="preserve">2.9553689956665</t>
@@ -305,16 +305,16 @@
     <t xml:space="preserve">2.82315516471863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86204171180725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00203251838684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9164822101593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85426425933838</t>
+    <t xml:space="preserve">2.86204147338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00203275680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91648268699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85426449775696</t>
   </si>
   <si>
     <t xml:space="preserve">2.7298276424408</t>
@@ -326,34 +326,34 @@
     <t xml:space="preserve">2.7220504283905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75315976142883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70649600028992</t>
+    <t xml:space="preserve">2.75315952301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70649576187134</t>
   </si>
   <si>
     <t xml:space="preserve">2.93981432914734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99425530433655</t>
+    <t xml:space="preserve">2.99425506591797</t>
   </si>
   <si>
     <t xml:space="preserve">2.97870087623596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86981868743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94759178161621</t>
+    <t xml:space="preserve">2.86981892585754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94759154319763</t>
   </si>
   <si>
     <t xml:space="preserve">2.98647785186768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63650035858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.550950050354</t>
+    <t xml:space="preserve">2.63650012016296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55094981193542</t>
   </si>
   <si>
     <t xml:space="preserve">2.51984095573425</t>
@@ -368,100 +368,100 @@
     <t xml:space="preserve">2.34874057769775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3642954826355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2554132938385</t>
+    <t xml:space="preserve">2.36429524421692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25541305541992</t>
   </si>
   <si>
     <t xml:space="preserve">2.24763607978821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3254086971283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23208117485046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18541741371155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27874517440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26319050788879</t>
+    <t xml:space="preserve">2.32540845870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23208141326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18541765213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27874493598938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26319026947021</t>
   </si>
   <si>
     <t xml:space="preserve">2.21652674674988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06875824928284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14653134346008</t>
+    <t xml:space="preserve">2.06875848770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1465311050415</t>
   </si>
   <si>
     <t xml:space="preserve">2.10764455795288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15430808067322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17764019966125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22430396080017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35651779174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4887318611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52761793136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43429088592529</t>
+    <t xml:space="preserve">2.1543083190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17764043807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22430372238159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35651803016663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48873162269592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52761840820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43429064750671</t>
   </si>
   <si>
     <t xml:space="preserve">2.44206809997559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5587272644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44984531402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37207221984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33318614959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29429984092712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37984991073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71427297592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58205938339233</t>
+    <t xml:space="preserve">2.55872750282288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44984555244446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37207245826721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33318591117859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29429960250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3798496723175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71427321434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58205890655518</t>
   </si>
   <si>
     <t xml:space="preserve">2.62872314453125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65983247756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57428193092346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67538690567017</t>
+    <t xml:space="preserve">2.65983200073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57428169250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67538666725159</t>
   </si>
   <si>
     <t xml:space="preserve">2.64427757263184</t>
@@ -470,16 +470,16 @@
     <t xml:space="preserve">2.69094133377075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76871395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90092778205872</t>
+    <t xml:space="preserve">2.76871418952942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90092825889587</t>
   </si>
   <si>
     <t xml:space="preserve">2.9631462097168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92425990104675</t>
+    <t xml:space="preserve">2.92425966262817</t>
   </si>
   <si>
     <t xml:space="preserve">2.97092366218567</t>
@@ -488,10 +488,10 @@
     <t xml:space="preserve">3.01758742332458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04869675636292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03314208984375</t>
+    <t xml:space="preserve">3.04869627952576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03314185142517</t>
   </si>
   <si>
     <t xml:space="preserve">3.0642511844635</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">3.07980561256409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0604989528656</t>
+    <t xml:space="preserve">3.06049919128418</t>
   </si>
   <si>
     <t xml:space="preserve">3.02811288833618</t>
@@ -512,37 +512,37 @@
     <t xml:space="preserve">3.1090784072876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09288501739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.12527132034302</t>
+    <t xml:space="preserve">3.0928852558136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12527108192444</t>
   </si>
   <si>
     <t xml:space="preserve">3.0766921043396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99572682380676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30339598655701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41674709320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35197496414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33578181266785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36816835403442</t>
+    <t xml:space="preserve">2.99572658538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30339574813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41674757003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35197520256042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33578205108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36816787719727</t>
   </si>
   <si>
     <t xml:space="preserve">3.23862338066101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31958866119385</t>
+    <t xml:space="preserve">3.31958889961243</t>
   </si>
   <si>
     <t xml:space="preserve">3.27100944519043</t>
@@ -560,46 +560,46 @@
     <t xml:space="preserve">3.20623707771301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14146447181702</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40055441856384</t>
+    <t xml:space="preserve">3.14146494865417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40055418014526</t>
   </si>
   <si>
     <t xml:space="preserve">3.49771356582642</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38436150550842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25481629371643</t>
+    <t xml:space="preserve">3.38436126708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25481653213501</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004416465759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96334052085876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97953367233276</t>
+    <t xml:space="preserve">2.96334028244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97953343391418</t>
   </si>
   <si>
     <t xml:space="preserve">2.80140924453735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88237476348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86618161201477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84998869895935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78521633148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75282979011536</t>
+    <t xml:space="preserve">2.88237452507019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86618185043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84998822212219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78521609306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75283002853394</t>
   </si>
   <si>
     <t xml:space="preserve">2.72044348716736</t>
@@ -608,22 +608,22 @@
     <t xml:space="preserve">2.83379530906677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76902318000793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73663663864136</t>
+    <t xml:space="preserve">2.76902294158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73663687705994</t>
   </si>
   <si>
     <t xml:space="preserve">2.81760215759277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89856767654419</t>
+    <t xml:space="preserve">2.89856791496277</t>
   </si>
   <si>
     <t xml:space="preserve">2.91476082801819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63947772979736</t>
+    <t xml:space="preserve">2.63947796821594</t>
   </si>
   <si>
     <t xml:space="preserve">2.67186427116394</t>
@@ -632,16 +632,16 @@
     <t xml:space="preserve">2.62328481674194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68805742263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70425009727478</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60709190368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59089875221252</t>
+    <t xml:space="preserve">2.68805718421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70425057411194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60709166526794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5908989906311</t>
   </si>
   <si>
     <t xml:space="preserve">2.42896747589111</t>
@@ -653,13 +653,13 @@
     <t xml:space="preserve">2.46135377883911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31561541557312</t>
+    <t xml:space="preserve">2.3156156539917</t>
   </si>
   <si>
     <t xml:space="preserve">2.2994225025177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35488176345825</t>
+    <t xml:space="preserve">2.35488152503967</t>
   </si>
   <si>
     <t xml:space="preserve">2.40607476234436</t>
@@ -668,22 +668,22 @@
     <t xml:space="preserve">2.28662419319153</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1330451965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08185195922852</t>
+    <t xml:space="preserve">2.13304495811462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08185219764709</t>
   </si>
   <si>
     <t xml:space="preserve">2.06478762626648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03065896034241</t>
+    <t xml:space="preserve">2.03065872192383</t>
   </si>
   <si>
     <t xml:space="preserve">2.1671736240387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09891605377197</t>
+    <t xml:space="preserve">2.09891629219055</t>
   </si>
   <si>
     <t xml:space="preserve">2.26955986022949</t>
@@ -692,16 +692,16 @@
     <t xml:space="preserve">2.21836686134338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32075309753418</t>
+    <t xml:space="preserve">2.3207528591156</t>
   </si>
   <si>
     <t xml:space="preserve">2.55965423583984</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54258990287781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45726799964905</t>
+    <t xml:space="preserve">2.54258966445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45726776123047</t>
   </si>
   <si>
     <t xml:space="preserve">2.5767183303833</t>
@@ -722,28 +722,28 @@
     <t xml:space="preserve">2.69616913795471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71323299407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44020318984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42313933372498</t>
+    <t xml:space="preserve">2.71323347091675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44020342826843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4231390953064</t>
   </si>
   <si>
     <t xml:space="preserve">2.47433233261108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15010952949524</t>
+    <t xml:space="preserve">2.15010929107666</t>
   </si>
   <si>
     <t xml:space="preserve">2.33781743049622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30368852615356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25249552726746</t>
+    <t xml:space="preserve">2.30368876457214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25249576568604</t>
   </si>
   <si>
     <t xml:space="preserve">2.23543095588684</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">2.38901042938232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20130252838135</t>
+    <t xml:space="preserve">2.20130228996277</t>
   </si>
   <si>
     <t xml:space="preserve">2.18423795700073</t>
@@ -764,28 +764,28 @@
     <t xml:space="preserve">2.01359438896179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04772305488586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11598038673401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91120827198029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8770797252655</t>
+    <t xml:space="preserve">2.04772353172302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11598062515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.911208152771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87707984447479</t>
   </si>
   <si>
     <t xml:space="preserve">1.84295094013214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97946584224701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86001539230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94533717632294</t>
+    <t xml:space="preserve">1.97946572303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86001527309418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94533681869507</t>
   </si>
   <si>
     <t xml:space="preserve">1.96240139007568</t>
@@ -800,10 +800,10 @@
     <t xml:space="preserve">2.90094137191772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88387680053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76442670822144</t>
+    <t xml:space="preserve">2.88387727737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76442646980286</t>
   </si>
   <si>
     <t xml:space="preserve">2.73029780387878</t>
@@ -812,10 +812,10 @@
     <t xml:space="preserve">2.6791045665741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74736213684082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.832683801651</t>
+    <t xml:space="preserve">2.74736189842224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83268356323242</t>
   </si>
   <si>
     <t xml:space="preserve">2.86681246757507</t>
@@ -827,25 +827,25 @@
     <t xml:space="preserve">2.78149056434631</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93507027626038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96919894218445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02039170265198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00332736968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03745627403259</t>
+    <t xml:space="preserve">2.9350700378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96919870376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02039194107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00332713127136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03745603561401</t>
   </si>
   <si>
     <t xml:space="preserve">2.98626303672791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05452013015747</t>
+    <t xml:space="preserve">3.05452060699463</t>
   </si>
   <si>
     <t xml:space="preserve">3.07158470153809</t>
@@ -854,13 +854,13 @@
     <t xml:space="preserve">3.13984251022339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11424565315247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13131022453308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06305265426636</t>
+    <t xml:space="preserve">3.11424589157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1313099861145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06305241584778</t>
   </si>
   <si>
     <t xml:space="preserve">3.16543865203857</t>
@@ -869,25 +869,25 @@
     <t xml:space="preserve">3.19956755638123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15690684318542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2336962223053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2763569355011</t>
+    <t xml:space="preserve">3.15690660476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23369598388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27635717391968</t>
   </si>
   <si>
     <t xml:space="preserve">3.24222850799561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26782512664795</t>
+    <t xml:space="preserve">3.26782488822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.31048607826233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3446147441864</t>
+    <t xml:space="preserve">3.34461498260498</t>
   </si>
   <si>
     <t xml:space="preserve">3.32755017280579</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">3.28488922119141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18250298500061</t>
+    <t xml:space="preserve">3.18250322341919</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342126846313</t>
@@ -905,16 +905,16 @@
     <t xml:space="preserve">3.33710074424744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32836508750916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29342174530029</t>
+    <t xml:space="preserve">3.32836484909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29342150688171</t>
   </si>
   <si>
     <t xml:space="preserve">3.24974226951599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20606303215027</t>
+    <t xml:space="preserve">3.20606279373169</t>
   </si>
   <si>
     <t xml:space="preserve">3.15364766120911</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">3.21479892730713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17111968994141</t>
+    <t xml:space="preserve">3.17111945152283</t>
   </si>
   <si>
     <t xml:space="preserve">3.26721382141113</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">3.36330842971802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49434638023376</t>
+    <t xml:space="preserve">3.49434661865234</t>
   </si>
   <si>
     <t xml:space="preserve">3.58170509338379</t>
@@ -941,40 +941,40 @@
     <t xml:space="preserve">3.56423330307007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59044098854065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50308275222778</t>
+    <t xml:space="preserve">3.59044122695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5030825138092</t>
   </si>
   <si>
     <t xml:space="preserve">3.51181840896606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54676151275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63412022590637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62538480758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74768662452698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69527149200439</t>
+    <t xml:space="preserve">3.54676175117493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63411998748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62538456916809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7476863861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69527125358582</t>
   </si>
   <si>
     <t xml:space="preserve">3.66906380653381</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60791277885437</t>
+    <t xml:space="preserve">3.60791301727295</t>
   </si>
   <si>
     <t xml:space="preserve">3.55549788475037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66032791137695</t>
+    <t xml:space="preserve">3.66032814979553</t>
   </si>
   <si>
     <t xml:space="preserve">3.65159201622009</t>
@@ -983,7 +983,7 @@
     <t xml:space="preserve">3.68653535842896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70400714874268</t>
+    <t xml:space="preserve">3.7040069103241</t>
   </si>
   <si>
     <t xml:space="preserve">3.75642251968384</t>
@@ -992,19 +992,19 @@
     <t xml:space="preserve">3.57296967506409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53802585601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34583687782288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38951635360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42445945739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45066714286804</t>
+    <t xml:space="preserve">3.53802609443665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3458366394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3895161151886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42445993423462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45066738128662</t>
   </si>
   <si>
     <t xml:space="preserve">3.44193148612976</t>
@@ -1013,10 +1013,10 @@
     <t xml:space="preserve">3.48561072349548</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40698790550232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35457253456116</t>
+    <t xml:space="preserve">3.4069881439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35457229614258</t>
   </si>
   <si>
     <t xml:space="preserve">3.45940327644348</t>
@@ -1028,19 +1028,19 @@
     <t xml:space="preserve">3.46813893318176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47687458992004</t>
+    <t xml:space="preserve">3.47687482833862</t>
   </si>
   <si>
     <t xml:space="preserve">3.79136610031128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7214789390564</t>
+    <t xml:space="preserve">3.72147941589355</t>
   </si>
   <si>
     <t xml:space="preserve">3.87872457504272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17574453353882</t>
+    <t xml:space="preserve">4.17574405670166</t>
   </si>
   <si>
     <t xml:space="preserve">4.31551790237427</t>
@@ -1049,19 +1049,19 @@
     <t xml:space="preserve">4.35046148300171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1844801902771</t>
+    <t xml:space="preserve">4.18447971343994</t>
   </si>
   <si>
     <t xml:space="preserve">4.20195150375366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25436639785767</t>
+    <t xml:space="preserve">4.25436687469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493178367615</t>
+    <t xml:space="preserve">3.90493226051331</t>
   </si>
   <si>
     <t xml:space="preserve">3.98355507850647</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">3.93113970756531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08838510513306</t>
+    <t xml:space="preserve">4.08838558197021</t>
   </si>
   <si>
     <t xml:space="preserve">4.07091379165649</t>
@@ -1085,16 +1085,16 @@
     <t xml:space="preserve">4.00102663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00976228713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93987607955933</t>
+    <t xml:space="preserve">4.00976324081421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93987584114075</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21068716049194</t>
+    <t xml:space="preserve">4.2106876373291</t>
   </si>
   <si>
     <t xml:space="preserve">4.29804611206055</t>
@@ -1103,16 +1103,16 @@
     <t xml:space="preserve">4.28930997848511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21942377090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19321584701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1495361328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16700839996338</t>
+    <t xml:space="preserve">4.21942329406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19321632385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14953660964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16700792312622</t>
   </si>
   <si>
     <t xml:space="preserve">4.11459302902222</t>
@@ -1124,40 +1124,40 @@
     <t xml:space="preserve">3.78262996673584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80010151863098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82630968093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83504486083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84378123283386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77389430999756</t>
+    <t xml:space="preserve">3.80010175704956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8263099193573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83504557609558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84378147125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77389454841614</t>
   </si>
   <si>
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734763145447</t>
+    <t xml:space="preserve">3.95734786987305</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.861252784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7651584148407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8175733089447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64285635948181</t>
+    <t xml:space="preserve">3.86125302314758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76515793800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81757354736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64285612106323</t>
   </si>
   <si>
     <t xml:space="preserve">3.67779970169067</t>
@@ -1172,49 +1172,49 @@
     <t xml:space="preserve">3.71274328231812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92240357398987</t>
+    <t xml:space="preserve">3.92240381240845</t>
   </si>
   <si>
     <t xml:space="preserve">3.61664843559265</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39825224876404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23227071762085</t>
+    <t xml:space="preserve">3.39825201034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23227047920227</t>
   </si>
   <si>
     <t xml:space="preserve">3.0575532913208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97019457817078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95272278785706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91777920722961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90904331207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37204432487488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38077998161316</t>
+    <t xml:space="preserve">2.97019481658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95272302627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91777944564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90904355049133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3720440864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38078022003174</t>
   </si>
   <si>
     <t xml:space="preserve">3.41572380065918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31962919235229</t>
+    <t xml:space="preserve">3.31962895393372</t>
   </si>
   <si>
     <t xml:space="preserve">3.27594995498657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28468585014343</t>
+    <t xml:space="preserve">3.28468561172485</t>
   </si>
   <si>
     <t xml:space="preserve">3.50245499610901</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">3.32098078727722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26653838157654</t>
+    <t xml:space="preserve">3.26653814315796</t>
   </si>
   <si>
     <t xml:space="preserve">3.39357042312622</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">3.23024344444275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19394850730896</t>
+    <t xml:space="preserve">3.19394874572754</t>
   </si>
   <si>
     <t xml:space="preserve">3.25746440887451</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">3.2211697101593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10321164131165</t>
+    <t xml:space="preserve">3.10321140289307</t>
   </si>
   <si>
     <t xml:space="preserve">2.99432682991028</t>
@@ -1286,13 +1286,13 @@
     <t xml:space="preserve">2.95803189277649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85822129249573</t>
+    <t xml:space="preserve">2.85822105407715</t>
   </si>
   <si>
     <t xml:space="preserve">2.89451599121094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86729502677917</t>
+    <t xml:space="preserve">2.8672947883606</t>
   </si>
   <si>
     <t xml:space="preserve">2.81285238265991</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">2.75841021537781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7039680480957</t>
+    <t xml:space="preserve">2.70396780967712</t>
   </si>
   <si>
     <t xml:space="preserve">2.72211527824402</t>
@@ -1313,16 +1313,16 @@
     <t xml:space="preserve">2.64952564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79470491409302</t>
+    <t xml:space="preserve">2.7947051525116</t>
   </si>
   <si>
     <t xml:space="preserve">2.92173719406128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05784296989441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02154779434204</t>
+    <t xml:space="preserve">3.05784273147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02154803276062</t>
   </si>
   <si>
     <t xml:space="preserve">3.13950634002686</t>
@@ -1352,46 +1352,46 @@
     <t xml:space="preserve">3.08506417274475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01247406005859</t>
+    <t xml:space="preserve">3.01247429847717</t>
   </si>
   <si>
     <t xml:space="preserve">2.88544225692749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77655744552612</t>
+    <t xml:space="preserve">2.7765576839447</t>
   </si>
   <si>
     <t xml:space="preserve">2.71304154396057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63137817382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68582057952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66767311096191</t>
+    <t xml:space="preserve">2.6313784122467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68582034111023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66767287254333</t>
   </si>
   <si>
     <t xml:space="preserve">2.55878829956055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52249360084534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67674684524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64045190811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87636876106262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83099961280823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6041567325592</t>
+    <t xml:space="preserve">2.52249336242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67674660682678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64045214653015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87636852264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83099985122681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60415697097778</t>
   </si>
   <si>
     <t xml:space="preserve">2.73118901252747</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">2.91266345977783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12135910987854</t>
+    <t xml:space="preserve">3.12135887145996</t>
   </si>
   <si>
     <t xml:space="preserve">3.0759904384613</t>
@@ -1427,46 +1427,46 @@
     <t xml:space="preserve">3.0941379070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38449668884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41171789169312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37542295455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42079162597656</t>
+    <t xml:space="preserve">3.38449692726135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41171765327454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37542319297791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42079138755798</t>
   </si>
   <si>
     <t xml:space="preserve">3.43893885612488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36634922027588</t>
+    <t xml:space="preserve">3.36634945869446</t>
   </si>
   <si>
     <t xml:space="preserve">3.35727572441101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20302224159241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27561211585999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29375982284546</t>
+    <t xml:space="preserve">3.20302248001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27561187744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29375958442688</t>
   </si>
   <si>
     <t xml:space="preserve">3.1667275428772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11228537559509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78563117980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84007358551025</t>
+    <t xml:space="preserve">3.11228513717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78563141822815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84007382392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.82192611694336</t>
@@ -1764,6 +1764,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.51999998092651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.6800000667572</t>
   </si>
 </sst>
 </file>
@@ -56520,7 +56523,7 @@
     </row>
     <row r="2094">
       <c r="A2094" s="1" t="n">
-        <v>46010.6909837963</v>
+        <v>46010.3333333333</v>
       </c>
       <c r="B2094" t="n">
         <v>63969</v>
@@ -56541,6 +56544,32 @@
         <v>583</v>
       </c>
       <c r="H2094" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2095">
+      <c r="A2095" s="1" t="n">
+        <v>46013.6874421296</v>
+      </c>
+      <c r="B2095" t="n">
+        <v>61108</v>
+      </c>
+      <c r="C2095" t="n">
+        <v>3.74000000953674</v>
+      </c>
+      <c r="D2095" t="n">
+        <v>3.53999996185303</v>
+      </c>
+      <c r="E2095" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="F2095" t="n">
+        <v>3.6800000667572</v>
+      </c>
+      <c r="G2095" t="s">
+        <v>584</v>
+      </c>
+      <c r="H2095" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02345776557922</t>
+    <t xml:space="preserve">3.02345752716064</t>
   </si>
   <si>
     <t xml:space="preserve">NDT.MI</t>
@@ -47,31 +47,31 @@
     <t xml:space="preserve">2.96519923210144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88901543617249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98013758659363</t>
+    <t xml:space="preserve">2.88901519775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98013734817505</t>
   </si>
   <si>
     <t xml:space="preserve">2.97266840934753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94577980041504</t>
+    <t xml:space="preserve">2.94578003883362</t>
   </si>
   <si>
     <t xml:space="preserve">2.95773029327393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96221160888672</t>
+    <t xml:space="preserve">2.9622118473053</t>
   </si>
   <si>
     <t xml:space="preserve">2.9353232383728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91291618347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97864365577698</t>
+    <t xml:space="preserve">2.91291642189026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97864317893982</t>
   </si>
   <si>
     <t xml:space="preserve">2.98611259460449</t>
@@ -89,16 +89,16 @@
     <t xml:space="preserve">3.05034613609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98760604858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95026135444641</t>
+    <t xml:space="preserve">2.98760652542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95026159286499</t>
   </si>
   <si>
     <t xml:space="preserve">3.01598858833313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01001381874084</t>
+    <t xml:space="preserve">3.01001334190369</t>
   </si>
   <si>
     <t xml:space="preserve">3.02495145797729</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">3.0174822807312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03092646598816</t>
+    <t xml:space="preserve">3.03092670440674</t>
   </si>
   <si>
     <t xml:space="preserve">2.99955654144287</t>
@@ -119,37 +119,37 @@
     <t xml:space="preserve">2.95922422409058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00254440307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92785453796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90843510627747</t>
+    <t xml:space="preserve">3.00254416465759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92785429954529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90843486785889</t>
   </si>
   <si>
     <t xml:space="preserve">2.896484375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91889142990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9159038066864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92038512229919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90544700622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90992879867554</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92337274551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83822584152222</t>
+    <t xml:space="preserve">2.91889119148254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91590356826782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92038536071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90544724464417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90992856025696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9233729839325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83822560310364</t>
   </si>
   <si>
     <t xml:space="preserve">2.86063313484192</t>
@@ -164,31 +164,31 @@
     <t xml:space="preserve">2.84569501876831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86810183525085</t>
+    <t xml:space="preserve">2.86810207366943</t>
   </si>
   <si>
     <t xml:space="preserve">2.88304018974304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79639959335327</t>
+    <t xml:space="preserve">2.79639935493469</t>
   </si>
   <si>
     <t xml:space="preserve">2.87557101249695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89797830581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80088090896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74262237548828</t>
+    <t xml:space="preserve">2.89797854423523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80088114738464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74262261390686</t>
   </si>
   <si>
     <t xml:space="preserve">2.82179427146912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7500913143158</t>
+    <t xml:space="preserve">2.75009155273438</t>
   </si>
   <si>
     <t xml:space="preserve">2.76353573799133</t>
@@ -197,7 +197,7 @@
     <t xml:space="preserve">2.77847385406494</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78594279289246</t>
+    <t xml:space="preserve">2.78594303131104</t>
   </si>
   <si>
     <t xml:space="preserve">2.79341173171997</t>
@@ -206,88 +206,88 @@
     <t xml:space="preserve">2.69631481170654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65150046348572</t>
+    <t xml:space="preserve">2.6515007019043</t>
   </si>
   <si>
     <t xml:space="preserve">2.62162470817566</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53946566581726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56934118270874</t>
+    <t xml:space="preserve">2.53946542739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5693416595459</t>
   </si>
   <si>
     <t xml:space="preserve">2.61415553092957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65896964073181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68884563446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70378351211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77100491523743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81581878662109</t>
+    <t xml:space="preserve">2.65896940231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68884587287903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70378375053406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77100515365601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81581926345825</t>
   </si>
   <si>
     <t xml:space="preserve">2.7336597442627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66643881797791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68137645721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74112868309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72619104385376</t>
+    <t xml:space="preserve">2.66643857955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68137621879578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74112892150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72619080543518</t>
   </si>
   <si>
     <t xml:space="preserve">2.83075714111328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89315056800842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69871878623962</t>
+    <t xml:space="preserve">2.893150806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69871854782104</t>
   </si>
   <si>
     <t xml:space="preserve">2.83870983123779</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93203687667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87759590148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8309326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81537771224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84648704528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79982304573059</t>
+    <t xml:space="preserve">2.93203735351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87759613990784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83093237876892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81537747383118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84648680686951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79982280731201</t>
   </si>
   <si>
     <t xml:space="preserve">2.73760485649109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76093649864197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80760025978088</t>
+    <t xml:space="preserve">2.76093673706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80760049819946</t>
   </si>
   <si>
     <t xml:space="preserve">3.00980997085571</t>
@@ -296,31 +296,31 @@
     <t xml:space="preserve">2.9553689956665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90870499610901</t>
+    <t xml:space="preserve">2.90870523452759</t>
   </si>
   <si>
     <t xml:space="preserve">2.88537335395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82315492630005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86204171180725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00203275680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91648268699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85426425933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72982788085938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68316411972046</t>
+    <t xml:space="preserve">2.82315516471863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86204147338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00203251838684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91648244857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8542640209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7298276424408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68316388130188</t>
   </si>
   <si>
     <t xml:space="preserve">2.7220504283905</t>
@@ -329,7 +329,7 @@
     <t xml:space="preserve">2.75315952301025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70649576187134</t>
+    <t xml:space="preserve">2.70649600028992</t>
   </si>
   <si>
     <t xml:space="preserve">2.93981432914734</t>
@@ -338,10 +338,10 @@
     <t xml:space="preserve">2.99425530433655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97870063781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86981892585754</t>
+    <t xml:space="preserve">2.97870087623596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86981868743896</t>
   </si>
   <si>
     <t xml:space="preserve">2.94759178161621</t>
@@ -350,7 +350,7 @@
     <t xml:space="preserve">2.98647785186768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63650012016296</t>
+    <t xml:space="preserve">2.63650035858154</t>
   </si>
   <si>
     <t xml:space="preserve">2.550950050354</t>
@@ -362,64 +362,64 @@
     <t xml:space="preserve">2.41095852851868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34096336364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34874081611633</t>
+    <t xml:space="preserve">2.34096312522888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34874057769775</t>
   </si>
   <si>
     <t xml:space="preserve">2.36429500579834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25541305541992</t>
+    <t xml:space="preserve">2.2554132938385</t>
   </si>
   <si>
     <t xml:space="preserve">2.24763607978821</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32540845870972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23208141326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18541765213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2787446975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26319026947021</t>
+    <t xml:space="preserve">2.3254086971283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23208117485046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18541741371155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27874517440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26319050788879</t>
   </si>
   <si>
     <t xml:space="preserve">2.21652674674988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06875848770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14653086662292</t>
+    <t xml:space="preserve">2.06875824928284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14653134346008</t>
   </si>
   <si>
     <t xml:space="preserve">2.10764479637146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1543083190918</t>
+    <t xml:space="preserve">2.15430855751038</t>
   </si>
   <si>
     <t xml:space="preserve">2.17764019966125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22430372238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35651803016663</t>
+    <t xml:space="preserve">2.22430396080017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35651755332947</t>
   </si>
   <si>
     <t xml:space="preserve">2.4887318611145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52761816978455</t>
+    <t xml:space="preserve">2.52761793136597</t>
   </si>
   <si>
     <t xml:space="preserve">2.43429088592529</t>
@@ -428,34 +428,34 @@
     <t xml:space="preserve">2.44206809997559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55872750282288</t>
+    <t xml:space="preserve">2.55872702598572</t>
   </si>
   <si>
     <t xml:space="preserve">2.44984555244446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37207245826721</t>
+    <t xml:space="preserve">2.37207269668579</t>
   </si>
   <si>
     <t xml:space="preserve">2.33318614959717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29429984092712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3798496723175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71427297592163</t>
+    <t xml:space="preserve">2.29429936408997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37984991073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71427321434021</t>
   </si>
   <si>
     <t xml:space="preserve">2.58205890655518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62872290611267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65983200073242</t>
+    <t xml:space="preserve">2.62872266769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65983247756958</t>
   </si>
   <si>
     <t xml:space="preserve">2.57428193092346</t>
@@ -464,13 +464,13 @@
     <t xml:space="preserve">2.67538666725159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64427781105042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69094109535217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76871395111084</t>
+    <t xml:space="preserve">2.64427757263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69094157218933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76871371269226</t>
   </si>
   <si>
     <t xml:space="preserve">2.90092802047729</t>
@@ -479,31 +479,31 @@
     <t xml:space="preserve">2.9631462097168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92425966262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97092366218567</t>
+    <t xml:space="preserve">2.92426013946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97092342376709</t>
   </si>
   <si>
     <t xml:space="preserve">3.01758742332458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04869651794434</t>
+    <t xml:space="preserve">3.04869675636292</t>
   </si>
   <si>
     <t xml:space="preserve">3.03314185142517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06425094604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07980561256409</t>
+    <t xml:space="preserve">3.06425070762634</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07980537414551</t>
   </si>
   <si>
     <t xml:space="preserve">3.06049919128418</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0281126499176</t>
+    <t xml:space="preserve">3.02811288833618</t>
   </si>
   <si>
     <t xml:space="preserve">3.01191973686218</t>
@@ -515,10 +515,10 @@
     <t xml:space="preserve">3.0928852558136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12527132034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07669186592102</t>
+    <t xml:space="preserve">3.1252715587616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0766921043396</t>
   </si>
   <si>
     <t xml:space="preserve">2.99572658538818</t>
@@ -527,16 +527,16 @@
     <t xml:space="preserve">3.30339574813843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41674733161926</t>
+    <t xml:space="preserve">3.41674709320068</t>
   </si>
   <si>
     <t xml:space="preserve">3.35197520256042</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33578181266785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36816787719727</t>
+    <t xml:space="preserve">3.33578205108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36816811561584</t>
   </si>
   <si>
     <t xml:space="preserve">3.23862338066101</t>
@@ -557,49 +557,49 @@
     <t xml:space="preserve">3.17385101318359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20623731613159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14146494865417</t>
+    <t xml:space="preserve">3.20623707771301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1414647102356</t>
   </si>
   <si>
     <t xml:space="preserve">3.40055441856384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49771356582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38436126708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25481653213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19004416465759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96334028244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97953343391418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80140924453735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88237452507019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86618185043335</t>
+    <t xml:space="preserve">3.49771332740784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38436150550842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25481629371643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19004392623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96334052085876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97953367233276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80140948295593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88237476348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86618137359619</t>
   </si>
   <si>
     <t xml:space="preserve">2.84998846054077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78521633148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75283026695251</t>
+    <t xml:space="preserve">2.78521609306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75282979011536</t>
   </si>
   <si>
     <t xml:space="preserve">2.72044348716736</t>
@@ -608,37 +608,37 @@
     <t xml:space="preserve">2.83379554748535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76902294158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73663687705994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81760215759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89856791496277</t>
+    <t xml:space="preserve">2.76902318000793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73663663864136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81760239601135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89856767654419</t>
   </si>
   <si>
     <t xml:space="preserve">2.91476082801819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63947820663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67186450958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62328457832336</t>
+    <t xml:space="preserve">2.63947796821594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67186403274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62328505516052</t>
   </si>
   <si>
     <t xml:space="preserve">2.68805742263794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70425057411194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60709166526794</t>
+    <t xml:space="preserve">2.70425033569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60709190368652</t>
   </si>
   <si>
     <t xml:space="preserve">2.59089875221252</t>
@@ -647,10 +647,10 @@
     <t xml:space="preserve">2.42896747589111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54231929779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46135354042053</t>
+    <t xml:space="preserve">2.54231953620911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46135377883911</t>
   </si>
   <si>
     <t xml:space="preserve">2.3156156539917</t>
@@ -659,19 +659,19 @@
     <t xml:space="preserve">2.2994225025177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35488176345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40607476234436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.28662419319153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13304471969604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08185195922852</t>
+    <t xml:space="preserve">2.35488152503967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40607452392578</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.28662443161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1330451965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08185172080994</t>
   </si>
   <si>
     <t xml:space="preserve">2.06478762626648</t>
@@ -701,16 +701,16 @@
     <t xml:space="preserve">2.54258966445923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45726823806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57671856880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62791132926941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61084699630737</t>
+    <t xml:space="preserve">2.45726799964905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5767183303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62791156768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61084723472595</t>
   </si>
   <si>
     <t xml:space="preserve">2.64497566223145</t>
@@ -719,10 +719,10 @@
     <t xml:space="preserve">2.59378266334534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69616913795471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71323323249817</t>
+    <t xml:space="preserve">2.69616889953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71323347091675</t>
   </si>
   <si>
     <t xml:space="preserve">2.44020342826843</t>
@@ -731,10 +731,10 @@
     <t xml:space="preserve">2.4231390953064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47433233261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15010929107666</t>
+    <t xml:space="preserve">2.47433257102966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15010952949524</t>
   </si>
   <si>
     <t xml:space="preserve">2.33781743049622</t>
@@ -746,7 +746,7 @@
     <t xml:space="preserve">2.25249552726746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23543095588684</t>
+    <t xml:space="preserve">2.23543119430542</t>
   </si>
   <si>
     <t xml:space="preserve">2.37194609642029</t>
@@ -755,55 +755,55 @@
     <t xml:space="preserve">2.38901042938232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20130228996277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18423795700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01359415054321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04772329330444</t>
+    <t xml:space="preserve">2.20130252838135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18423819541931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01359438896179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04772353172302</t>
   </si>
   <si>
     <t xml:space="preserve">2.11598062515259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91120839118958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8770797252655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84295094013214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97946572303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86001527309418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94533705711365</t>
+    <t xml:space="preserve">1.91120851039886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87707960605621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84295105934143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97946584224701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86001539230347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94533693790436</t>
   </si>
   <si>
     <t xml:space="preserve">1.96240139007568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99653005599976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81561970710754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9009416103363</t>
+    <t xml:space="preserve">1.99652993679047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81561946868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90094137191772</t>
   </si>
   <si>
     <t xml:space="preserve">2.88387703895569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76442623138428</t>
+    <t xml:space="preserve">2.76442646980286</t>
   </si>
   <si>
     <t xml:space="preserve">2.73029756546021</t>
@@ -821,34 +821,34 @@
     <t xml:space="preserve">2.86681246757507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79855513572693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78149080276489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93507027626038</t>
+    <t xml:space="preserve">2.79855489730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78149056434631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93506979942322</t>
   </si>
   <si>
     <t xml:space="preserve">2.96919870376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02039194107056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00332736968994</t>
+    <t xml:space="preserve">3.02039170265198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00332760810852</t>
   </si>
   <si>
     <t xml:space="preserve">3.03745603561401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98626327514648</t>
+    <t xml:space="preserve">2.98626303672791</t>
   </si>
   <si>
     <t xml:space="preserve">3.05452060699463</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07158470153809</t>
+    <t xml:space="preserve">3.07158446311951</t>
   </si>
   <si>
     <t xml:space="preserve">3.13984251022339</t>
@@ -857,22 +857,22 @@
     <t xml:space="preserve">3.11424589157104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1313099861145</t>
+    <t xml:space="preserve">3.13131022453308</t>
   </si>
   <si>
     <t xml:space="preserve">3.06305241584778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16543889045715</t>
+    <t xml:space="preserve">3.16543912887573</t>
   </si>
   <si>
     <t xml:space="preserve">3.19956755638123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15690660476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2336962223053</t>
+    <t xml:space="preserve">3.15690684318542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23369598388672</t>
   </si>
   <si>
     <t xml:space="preserve">3.2763569355011</t>
@@ -881,13 +881,13 @@
     <t xml:space="preserve">3.24222826957703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26782464981079</t>
+    <t xml:space="preserve">3.26782488822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.31048607826233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34461498260498</t>
+    <t xml:space="preserve">3.3446147441864</t>
   </si>
   <si>
     <t xml:space="preserve">3.32755041122437</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">3.28488922119141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18250298500061</t>
+    <t xml:space="preserve">3.18250346183777</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342150688171</t>
@@ -908,13 +908,13 @@
     <t xml:space="preserve">3.32836484909058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24974226951599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20606279373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15364766120911</t>
+    <t xml:space="preserve">3.24974250793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20606303215027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15364742279053</t>
   </si>
   <si>
     <t xml:space="preserve">3.21479892730713</t>
@@ -923,19 +923,19 @@
     <t xml:space="preserve">3.17111945152283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26721382141113</t>
+    <t xml:space="preserve">3.26721405982971</t>
   </si>
   <si>
     <t xml:space="preserve">3.36330842971802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49434661865234</t>
+    <t xml:space="preserve">3.49434638023376</t>
   </si>
   <si>
     <t xml:space="preserve">3.58170509338379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56423330307007</t>
+    <t xml:space="preserve">3.56423354148865</t>
   </si>
   <si>
     <t xml:space="preserve">3.59044122695923</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">3.5030825138092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51181840896606</t>
+    <t xml:space="preserve">3.51181817054749</t>
   </si>
   <si>
     <t xml:space="preserve">3.54676175117493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63411998748779</t>
+    <t xml:space="preserve">3.63412022590637</t>
   </si>
   <si>
     <t xml:space="preserve">3.62538456916809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7476863861084</t>
+    <t xml:space="preserve">3.74768662452698</t>
   </si>
   <si>
     <t xml:space="preserve">3.69527125358582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66906380653381</t>
+    <t xml:space="preserve">3.66906332969666</t>
   </si>
   <si>
     <t xml:space="preserve">3.60791301727295</t>
@@ -971,22 +971,22 @@
     <t xml:space="preserve">3.55549788475037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66032814979553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65159201622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68653535842896</t>
+    <t xml:space="preserve">3.66032767295837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65159177780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68653512001038</t>
   </si>
   <si>
     <t xml:space="preserve">3.7040069103241</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75642251968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57296967506409</t>
+    <t xml:space="preserve">3.75642275810242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57296943664551</t>
   </si>
   <si>
     <t xml:space="preserve">3.53802609443665</t>
@@ -995,28 +995,28 @@
     <t xml:space="preserve">3.3458366394043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3895161151886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42445993423462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45066738128662</t>
+    <t xml:space="preserve">3.38951635360718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42445969581604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45066714286804</t>
   </si>
   <si>
     <t xml:space="preserve">3.44193148612976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48561072349548</t>
+    <t xml:space="preserve">3.4856104850769</t>
   </si>
   <si>
     <t xml:space="preserve">3.4069881439209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35457229614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45940327644348</t>
+    <t xml:space="preserve">3.35457253456116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4594030380249</t>
   </si>
   <si>
     <t xml:space="preserve">3.52928996086121</t>
@@ -1025,19 +1025,19 @@
     <t xml:space="preserve">3.46813893318176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47687482833862</t>
+    <t xml:space="preserve">3.47687458992004</t>
   </si>
   <si>
     <t xml:space="preserve">3.79136610031128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72147941589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87872457504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17574405670166</t>
+    <t xml:space="preserve">3.72147917747498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8787248134613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17574453353882</t>
   </si>
   <si>
     <t xml:space="preserve">4.31551790237427</t>
@@ -1046,34 +1046,34 @@
     <t xml:space="preserve">4.35046148300171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18447971343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20195150375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25436687469482</t>
+    <t xml:space="preserve">4.1844801902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20195198059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25436639785767</t>
   </si>
   <si>
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493226051331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98355507850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94861173629761</t>
+    <t xml:space="preserve">3.90493202209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98355484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94861149787903</t>
   </si>
   <si>
     <t xml:space="preserve">3.93113970756531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08838558197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07091379165649</t>
+    <t xml:space="preserve">4.08838510513306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07091331481934</t>
   </si>
   <si>
     <t xml:space="preserve">4.1233286857605</t>
@@ -1082,16 +1082,16 @@
     <t xml:space="preserve">4.00102663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00976324081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93987584114075</t>
+    <t xml:space="preserve">4.00976276397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93987560272217</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2106876373291</t>
+    <t xml:space="preserve">4.21068811416626</t>
   </si>
   <si>
     <t xml:space="preserve">4.29804611206055</t>
@@ -1100,7 +1100,7 @@
     <t xml:space="preserve">4.28930997848511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21942329406738</t>
+    <t xml:space="preserve">4.21942377090454</t>
   </si>
   <si>
     <t xml:space="preserve">4.19321632385254</t>
@@ -1109,28 +1109,28 @@
     <t xml:space="preserve">4.14953660964966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16700792312622</t>
+    <t xml:space="preserve">4.16700839996338</t>
   </si>
   <si>
     <t xml:space="preserve">4.11459302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06217765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78262996673584</t>
+    <t xml:space="preserve">4.06217813491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78263020515442</t>
   </si>
   <si>
     <t xml:space="preserve">3.80010175704956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8263099193573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83504557609558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84378147125244</t>
+    <t xml:space="preserve">3.82630944252014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83504509925842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84378123283386</t>
   </si>
   <si>
     <t xml:space="preserve">3.77389454841614</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734786987305</t>
+    <t xml:space="preserve">3.95734739303589</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
@@ -1148,16 +1148,16 @@
     <t xml:space="preserve">3.86125302314758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76515793800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81757354736328</t>
+    <t xml:space="preserve">3.7651584148407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8175733089447</t>
   </si>
   <si>
     <t xml:space="preserve">3.64285612106323</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67779970169067</t>
+    <t xml:space="preserve">3.67779946327209</t>
   </si>
   <si>
     <t xml:space="preserve">3.7389509677887</t>
@@ -1166,43 +1166,43 @@
     <t xml:space="preserve">3.85251712799072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71274328231812</t>
+    <t xml:space="preserve">3.71274304389954</t>
   </si>
   <si>
     <t xml:space="preserve">3.92240381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61664843559265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39825201034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23227047920227</t>
+    <t xml:space="preserve">3.61664867401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39825224876404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23227071762085</t>
   </si>
   <si>
     <t xml:space="preserve">3.0575532913208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97019481658936</t>
+    <t xml:space="preserve">2.97019457817078</t>
   </si>
   <si>
     <t xml:space="preserve">2.95272302627563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91777944564819</t>
+    <t xml:space="preserve">2.91777920722961</t>
   </si>
   <si>
     <t xml:space="preserve">2.90904355049133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3720440864563</t>
+    <t xml:space="preserve">3.37204432487488</t>
   </si>
   <si>
     <t xml:space="preserve">3.38078022003174</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41572380065918</t>
+    <t xml:space="preserve">3.41572403907776</t>
   </si>
   <si>
     <t xml:space="preserve">3.31962895393372</t>
@@ -56575,7 +56575,7 @@
     </row>
     <row r="2096">
       <c r="A2096" s="1" t="n">
-        <v>46014.6868171296</v>
+        <v>46014.3333333333</v>
       </c>
       <c r="B2096" t="n">
         <v>42759</v>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519923210144</t>
+    <t xml:space="preserve">2.96519899368286</t>
   </si>
   <si>
     <t xml:space="preserve">2.88901519775391</t>
@@ -56,46 +56,46 @@
     <t xml:space="preserve">2.97266840934753</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94578003883362</t>
+    <t xml:space="preserve">2.94577980041504</t>
   </si>
   <si>
     <t xml:space="preserve">2.95773029327393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9622118473053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9353232383728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91291642189026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97864317893982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98611259460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03540825843811</t>
+    <t xml:space="preserve">2.96221208572388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93532347679138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9129159450531</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97864365577698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98611235618591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03540802001953</t>
   </si>
   <si>
     <t xml:space="preserve">3.056321144104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05930876731873</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05034613609314</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98760652542114</t>
+    <t xml:space="preserve">3.0593090057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05034637451172</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98760676383972</t>
   </si>
   <si>
     <t xml:space="preserve">2.95026159286499</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01598858833313</t>
+    <t xml:space="preserve">3.01598834991455</t>
   </si>
   <si>
     <t xml:space="preserve">3.01001334190369</t>
@@ -110,16 +110,16 @@
     <t xml:space="preserve">3.03092670440674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99955654144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0443708896637</t>
+    <t xml:space="preserve">2.99955677986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04437112808228</t>
   </si>
   <si>
     <t xml:space="preserve">2.95922422409058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00254416465759</t>
+    <t xml:space="preserve">3.00254440307617</t>
   </si>
   <si>
     <t xml:space="preserve">2.92785429954529</t>
@@ -128,22 +128,22 @@
     <t xml:space="preserve">2.90843486785889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.896484375</t>
+    <t xml:space="preserve">2.89648461341858</t>
   </si>
   <si>
     <t xml:space="preserve">2.91889119148254</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91590356826782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92038536071777</t>
+    <t xml:space="preserve">2.9159038066864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92038559913635</t>
   </si>
   <si>
     <t xml:space="preserve">2.90544724464417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90992856025696</t>
+    <t xml:space="preserve">2.90992832183838</t>
   </si>
   <si>
     <t xml:space="preserve">2.9233729839325</t>
@@ -152,22 +152,22 @@
     <t xml:space="preserve">2.83822560310364</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86063313484192</t>
+    <t xml:space="preserve">2.8606333732605</t>
   </si>
   <si>
     <t xml:space="preserve">2.82627558708191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77996754646301</t>
+    <t xml:space="preserve">2.77996778488159</t>
   </si>
   <si>
     <t xml:space="preserve">2.84569501876831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86810207366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88304018974304</t>
+    <t xml:space="preserve">2.86810183525085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88303995132446</t>
   </si>
   <si>
     <t xml:space="preserve">2.79639935493469</t>
@@ -176,10 +176,10 @@
     <t xml:space="preserve">2.87557101249695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89797854423523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80088114738464</t>
+    <t xml:space="preserve">2.89797806739807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80088138580322</t>
   </si>
   <si>
     <t xml:space="preserve">2.74262261390686</t>
@@ -191,46 +191,46 @@
     <t xml:space="preserve">2.75009155273438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76353573799133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77847385406494</t>
+    <t xml:space="preserve">2.76353597640991</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77847361564636</t>
   </si>
   <si>
     <t xml:space="preserve">2.78594303131104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79341173171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69631481170654</t>
+    <t xml:space="preserve">2.79341197013855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69631457328796</t>
   </si>
   <si>
     <t xml:space="preserve">2.6515007019043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62162470817566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53946542739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5693416595459</t>
+    <t xml:space="preserve">2.62162446975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53946566581726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56934142112732</t>
   </si>
   <si>
     <t xml:space="preserve">2.61415553092957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65896940231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68884587287903</t>
+    <t xml:space="preserve">2.65896964073181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68884563446045</t>
   </si>
   <si>
     <t xml:space="preserve">2.70378375053406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77100515365601</t>
+    <t xml:space="preserve">2.77100491523743</t>
   </si>
   <si>
     <t xml:space="preserve">2.81581926345825</t>
@@ -242,13 +242,13 @@
     <t xml:space="preserve">2.66643857955933</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68137621879578</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74112892150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72619080543518</t>
+    <t xml:space="preserve">2.68137645721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74112868309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72619104385376</t>
   </si>
   <si>
     <t xml:space="preserve">2.83075714111328</t>
@@ -257,13 +257,13 @@
     <t xml:space="preserve">2.893150806427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69871854782104</t>
+    <t xml:space="preserve">2.69871830940247</t>
   </si>
   <si>
     <t xml:space="preserve">2.83870983123779</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93203735351562</t>
+    <t xml:space="preserve">2.93203711509705</t>
   </si>
   <si>
     <t xml:space="preserve">2.87759613990784</t>
@@ -275,7 +275,7 @@
     <t xml:space="preserve">2.81537747383118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84648680686951</t>
+    <t xml:space="preserve">2.84648704528809</t>
   </si>
   <si>
     <t xml:space="preserve">2.79982280731201</t>
@@ -284,7 +284,7 @@
     <t xml:space="preserve">2.73760485649109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76093673706055</t>
+    <t xml:space="preserve">2.76093697547913</t>
   </si>
   <si>
     <t xml:space="preserve">2.80760049819946</t>
@@ -299,13 +299,13 @@
     <t xml:space="preserve">2.90870523452759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88537335395813</t>
+    <t xml:space="preserve">2.88537311553955</t>
   </si>
   <si>
     <t xml:space="preserve">2.82315516471863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86204147338867</t>
+    <t xml:space="preserve">2.86204171180725</t>
   </si>
   <si>
     <t xml:space="preserve">3.00203251838684</t>
@@ -314,13 +314,13 @@
     <t xml:space="preserve">2.91648244857788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8542640209198</t>
+    <t xml:space="preserve">2.85426425933838</t>
   </si>
   <si>
     <t xml:space="preserve">2.7298276424408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68316388130188</t>
+    <t xml:space="preserve">2.6831636428833</t>
   </si>
   <si>
     <t xml:space="preserve">2.7220504283905</t>
@@ -329,7 +329,7 @@
     <t xml:space="preserve">2.75315952301025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70649600028992</t>
+    <t xml:space="preserve">2.70649576187134</t>
   </si>
   <si>
     <t xml:space="preserve">2.93981432914734</t>
@@ -347,34 +347,34 @@
     <t xml:space="preserve">2.94759178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98647785186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63650035858154</t>
+    <t xml:space="preserve">2.98647809028625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63650059700012</t>
   </si>
   <si>
     <t xml:space="preserve">2.550950050354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51984095573425</t>
+    <t xml:space="preserve">2.51984071731567</t>
   </si>
   <si>
     <t xml:space="preserve">2.41095852851868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34096312522888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34874057769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36429500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2554132938385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24763607978821</t>
+    <t xml:space="preserve">2.34096336364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34874081611633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3642954826355</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25541305541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24763584136963</t>
   </si>
   <si>
     <t xml:space="preserve">2.3254086971283</t>
@@ -383,28 +383,28 @@
     <t xml:space="preserve">2.23208117485046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18541741371155</t>
+    <t xml:space="preserve">2.18541765213013</t>
   </si>
   <si>
     <t xml:space="preserve">2.27874517440796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26319050788879</t>
+    <t xml:space="preserve">2.26319026947021</t>
   </si>
   <si>
     <t xml:space="preserve">2.21652674674988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06875824928284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14653134346008</t>
+    <t xml:space="preserve">2.06875848770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1465311050415</t>
   </si>
   <si>
     <t xml:space="preserve">2.10764479637146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15430855751038</t>
+    <t xml:space="preserve">2.15430808067322</t>
   </si>
   <si>
     <t xml:space="preserve">2.17764019966125</t>
@@ -413,7 +413,7 @@
     <t xml:space="preserve">2.22430396080017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35651755332947</t>
+    <t xml:space="preserve">2.35651779174805</t>
   </si>
   <si>
     <t xml:space="preserve">2.4887318611145</t>
@@ -434,25 +434,25 @@
     <t xml:space="preserve">2.44984555244446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37207269668579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33318614959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29429936408997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37984991073608</t>
+    <t xml:space="preserve">2.37207245826721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33318638801575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29429960250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3798496723175</t>
   </si>
   <si>
     <t xml:space="preserve">2.71427321434021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58205890655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62872266769409</t>
+    <t xml:space="preserve">2.58205914497375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62872314453125</t>
   </si>
   <si>
     <t xml:space="preserve">2.65983247756958</t>
@@ -467,19 +467,19 @@
     <t xml:space="preserve">2.64427757263184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69094157218933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76871371269226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90092802047729</t>
+    <t xml:space="preserve">2.69094133377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76871395111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90092778205872</t>
   </si>
   <si>
     <t xml:space="preserve">2.9631462097168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92426013946533</t>
+    <t xml:space="preserve">2.92425990104675</t>
   </si>
   <si>
     <t xml:space="preserve">2.97092342376709</t>
@@ -488,34 +488,34 @@
     <t xml:space="preserve">3.01758742332458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04869675636292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03314185142517</t>
+    <t xml:space="preserve">3.04869651794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03314208984375</t>
   </si>
   <si>
     <t xml:space="preserve">3.06425070762634</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07980537414551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06049919128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02811288833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01191973686218</t>
+    <t xml:space="preserve">3.07980561256409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0604989528656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0281126499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0119194984436</t>
   </si>
   <si>
     <t xml:space="preserve">3.10907816886902</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0928852558136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1252715587616</t>
+    <t xml:space="preserve">3.09288501739502</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12527132034302</t>
   </si>
   <si>
     <t xml:space="preserve">3.0766921043396</t>
@@ -524,64 +524,64 @@
     <t xml:space="preserve">2.99572658538818</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30339574813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41674709320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35197520256042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33578205108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36816811561584</t>
+    <t xml:space="preserve">3.30339550971985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41674733161926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35197496414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33578181266785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36816787719727</t>
   </si>
   <si>
     <t xml:space="preserve">3.23862338066101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31958889961243</t>
+    <t xml:space="preserve">3.31958866119385</t>
   </si>
   <si>
     <t xml:space="preserve">3.27100944519043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28720259666443</t>
+    <t xml:space="preserve">3.28720235824585</t>
   </si>
   <si>
     <t xml:space="preserve">3.22243022918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17385101318359</t>
+    <t xml:space="preserve">3.17385077476501</t>
   </si>
   <si>
     <t xml:space="preserve">3.20623707771301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1414647102356</t>
+    <t xml:space="preserve">3.14146447181702</t>
   </si>
   <si>
     <t xml:space="preserve">3.40055441856384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49771332740784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38436150550842</t>
+    <t xml:space="preserve">3.49771308898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38436126708984</t>
   </si>
   <si>
     <t xml:space="preserve">3.25481629371643</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19004392623901</t>
+    <t xml:space="preserve">3.19004416465759</t>
   </si>
   <si>
     <t xml:space="preserve">2.96334052085876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97953367233276</t>
+    <t xml:space="preserve">2.97953343391418</t>
   </si>
   <si>
     <t xml:space="preserve">2.80140948295593</t>
@@ -590,25 +590,25 @@
     <t xml:space="preserve">2.88237476348877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86618137359619</t>
+    <t xml:space="preserve">2.86618161201477</t>
   </si>
   <si>
     <t xml:space="preserve">2.84998846054077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78521609306335</t>
+    <t xml:space="preserve">2.78521633148193</t>
   </si>
   <si>
     <t xml:space="preserve">2.75282979011536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72044348716736</t>
+    <t xml:space="preserve">2.72044324874878</t>
   </si>
   <si>
     <t xml:space="preserve">2.83379554748535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76902318000793</t>
+    <t xml:space="preserve">2.76902294158936</t>
   </si>
   <si>
     <t xml:space="preserve">2.73663663864136</t>
@@ -629,13 +629,13 @@
     <t xml:space="preserve">2.67186403274536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62328505516052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68805742263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70425033569336</t>
+    <t xml:space="preserve">2.62328481674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68805718421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70425009727478</t>
   </si>
   <si>
     <t xml:space="preserve">2.60709190368652</t>
@@ -644,10 +644,10 @@
     <t xml:space="preserve">2.59089875221252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42896747589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54231953620911</t>
+    <t xml:space="preserve">2.42896771430969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54231929779053</t>
   </si>
   <si>
     <t xml:space="preserve">2.46135377883911</t>
@@ -656,22 +656,22 @@
     <t xml:space="preserve">2.3156156539917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2994225025177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35488152503967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.40607452392578</t>
+    <t xml:space="preserve">2.29942226409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35488176345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.40607476234436</t>
   </si>
   <si>
     <t xml:space="preserve">2.28662443161011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1330451965332</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08185172080994</t>
+    <t xml:space="preserve">2.13304495811462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08185195922852</t>
   </si>
   <si>
     <t xml:space="preserve">2.06478762626648</t>
@@ -683,7 +683,7 @@
     <t xml:space="preserve">2.1671736240387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09891629219055</t>
+    <t xml:space="preserve">2.09891653060913</t>
   </si>
   <si>
     <t xml:space="preserve">2.26955986022949</t>
@@ -704,10 +704,10 @@
     <t xml:space="preserve">2.45726799964905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5767183303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62791156768799</t>
+    <t xml:space="preserve">2.57671856880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62791132926941</t>
   </si>
   <si>
     <t xml:space="preserve">2.61084723472595</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">2.59378266334534</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69616889953613</t>
+    <t xml:space="preserve">2.69616913795471</t>
   </si>
   <si>
     <t xml:space="preserve">2.71323347091675</t>
@@ -734,25 +734,25 @@
     <t xml:space="preserve">2.47433257102966</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15010952949524</t>
+    <t xml:space="preserve">2.15010929107666</t>
   </si>
   <si>
     <t xml:space="preserve">2.33781743049622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30368876457214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25249552726746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23543119430542</t>
+    <t xml:space="preserve">2.30368852615356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25249576568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23543095588684</t>
   </si>
   <si>
     <t xml:space="preserve">2.37194609642029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38901042938232</t>
+    <t xml:space="preserve">2.38901019096375</t>
   </si>
   <si>
     <t xml:space="preserve">2.20130252838135</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">2.18423819541931</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01359438896179</t>
+    <t xml:space="preserve">2.01359415054321</t>
   </si>
   <si>
     <t xml:space="preserve">2.04772353172302</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">2.11598062515259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91120851039886</t>
+    <t xml:space="preserve">1.91120839118958</t>
   </si>
   <si>
     <t xml:space="preserve">1.87707960605621</t>
@@ -779,16 +779,16 @@
     <t xml:space="preserve">1.84295105934143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97946584224701</t>
+    <t xml:space="preserve">1.97946560382843</t>
   </si>
   <si>
     <t xml:space="preserve">1.86001539230347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94533693790436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96240139007568</t>
+    <t xml:space="preserve">1.94533705711365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96240162849426</t>
   </si>
   <si>
     <t xml:space="preserve">1.99652993679047</t>
@@ -800,19 +800,19 @@
     <t xml:space="preserve">2.90094137191772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88387703895569</t>
+    <t xml:space="preserve">2.88387680053711</t>
   </si>
   <si>
     <t xml:space="preserve">2.76442646980286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73029756546021</t>
+    <t xml:space="preserve">2.73029780387878</t>
   </si>
   <si>
     <t xml:space="preserve">2.6791045665741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74736189842224</t>
+    <t xml:space="preserve">2.74736166000366</t>
   </si>
   <si>
     <t xml:space="preserve">2.832683801651</t>
@@ -824,10 +824,10 @@
     <t xml:space="preserve">2.79855489730835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78149056434631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93506979942322</t>
+    <t xml:space="preserve">2.78149080276489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9350700378418</t>
   </si>
   <si>
     <t xml:space="preserve">2.96919870376587</t>
@@ -836,19 +836,19 @@
     <t xml:space="preserve">3.02039170265198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00332760810852</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03745603561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98626303672791</t>
+    <t xml:space="preserve">3.00332736968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03745579719543</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98626327514648</t>
   </si>
   <si>
     <t xml:space="preserve">3.05452060699463</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07158446311951</t>
+    <t xml:space="preserve">3.07158470153809</t>
   </si>
   <si>
     <t xml:space="preserve">3.13984251022339</t>
@@ -857,28 +857,28 @@
     <t xml:space="preserve">3.11424589157104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13131022453308</t>
+    <t xml:space="preserve">3.1313099861145</t>
   </si>
   <si>
     <t xml:space="preserve">3.06305241584778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16543912887573</t>
+    <t xml:space="preserve">3.16543889045715</t>
   </si>
   <si>
     <t xml:space="preserve">3.19956755638123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15690684318542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23369598388672</t>
+    <t xml:space="preserve">3.15690660476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2336962223053</t>
   </si>
   <si>
     <t xml:space="preserve">3.2763569355011</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24222826957703</t>
+    <t xml:space="preserve">3.24222850799561</t>
   </si>
   <si>
     <t xml:space="preserve">3.26782488822937</t>
@@ -890,13 +890,13 @@
     <t xml:space="preserve">3.3446147441864</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32755041122437</t>
+    <t xml:space="preserve">3.32755017280579</t>
   </si>
   <si>
     <t xml:space="preserve">3.28488922119141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18250346183777</t>
+    <t xml:space="preserve">3.18250322341919</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342150688171</t>
@@ -905,25 +905,25 @@
     <t xml:space="preserve">3.33710074424744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32836484909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24974250793457</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20606303215027</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15364742279053</t>
+    <t xml:space="preserve">3.32836508750916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24974226951599</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20606279373169</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15364766120911</t>
   </si>
   <si>
     <t xml:space="preserve">3.21479892730713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17111945152283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26721405982971</t>
+    <t xml:space="preserve">3.17111968994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26721382141113</t>
   </si>
   <si>
     <t xml:space="preserve">3.36330842971802</t>
@@ -932,64 +932,64 @@
     <t xml:space="preserve">3.49434638023376</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58170509338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56423354148865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59044122695923</t>
+    <t xml:space="preserve">3.58170533180237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56423330307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59044098854065</t>
   </si>
   <si>
     <t xml:space="preserve">3.5030825138092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51181817054749</t>
+    <t xml:space="preserve">3.51181840896606</t>
   </si>
   <si>
     <t xml:space="preserve">3.54676175117493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63412022590637</t>
+    <t xml:space="preserve">3.63411998748779</t>
   </si>
   <si>
     <t xml:space="preserve">3.62538456916809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74768662452698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69527125358582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66906332969666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60791301727295</t>
+    <t xml:space="preserve">3.7476863861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69527149200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66906380653381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60791277885437</t>
   </si>
   <si>
     <t xml:space="preserve">3.55549788475037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66032767295837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65159177780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68653512001038</t>
+    <t xml:space="preserve">3.66032814979553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65159201622009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68653535842896</t>
   </si>
   <si>
     <t xml:space="preserve">3.7040069103241</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75642275810242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57296943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53802609443665</t>
+    <t xml:space="preserve">3.75642251968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57296967506409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53802585601807</t>
   </si>
   <si>
     <t xml:space="preserve">3.3458366394043</t>
@@ -1001,16 +1001,16 @@
     <t xml:space="preserve">3.42445969581604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45066714286804</t>
+    <t xml:space="preserve">3.45066738128662</t>
   </si>
   <si>
     <t xml:space="preserve">3.44193148612976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4856104850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4069881439209</t>
+    <t xml:space="preserve">3.48561072349548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40698790550232</t>
   </si>
   <si>
     <t xml:space="preserve">3.35457253456116</t>
@@ -1034,37 +1034,37 @@
     <t xml:space="preserve">3.72147917747498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8787248134613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17574453353882</t>
+    <t xml:space="preserve">3.87872457504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17574405670166</t>
   </si>
   <si>
     <t xml:space="preserve">4.31551790237427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35046148300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1844801902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20195198059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25436639785767</t>
+    <t xml:space="preserve">4.35046100616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18447971343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20195150375366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25436687469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493202209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98355484008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94861149787903</t>
+    <t xml:space="preserve">3.90493226051331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98355507850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94861173629761</t>
   </si>
   <si>
     <t xml:space="preserve">3.93113970756531</t>
@@ -1073,10 +1073,10 @@
     <t xml:space="preserve">4.08838510513306</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07091331481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1233286857605</t>
+    <t xml:space="preserve">4.07091379165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12332820892334</t>
   </si>
   <si>
     <t xml:space="preserve">4.00102663040161</t>
@@ -1091,16 +1091,16 @@
     <t xml:space="preserve">4.0971212387085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21068811416626</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29804611206055</t>
+    <t xml:space="preserve">4.2106876373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29804658889771</t>
   </si>
   <si>
     <t xml:space="preserve">4.28930997848511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21942377090454</t>
+    <t xml:space="preserve">4.21942329406738</t>
   </si>
   <si>
     <t xml:space="preserve">4.19321632385254</t>
@@ -1115,7 +1115,7 @@
     <t xml:space="preserve">4.11459302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06217813491821</t>
+    <t xml:space="preserve">4.06217765808105</t>
   </si>
   <si>
     <t xml:space="preserve">3.78263020515442</t>
@@ -1124,10 +1124,10 @@
     <t xml:space="preserve">3.80010175704956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82630944252014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83504509925842</t>
+    <t xml:space="preserve">3.82630968093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.835045337677</t>
   </si>
   <si>
     <t xml:space="preserve">3.84378123283386</t>
@@ -1139,16 +1139,16 @@
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734739303589</t>
+    <t xml:space="preserve">3.95734763145447</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86125302314758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7651584148407</t>
+    <t xml:space="preserve">3.861252784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76515817642212</t>
   </si>
   <si>
     <t xml:space="preserve">3.8175733089447</t>
@@ -1157,7 +1157,7 @@
     <t xml:space="preserve">3.64285612106323</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67779946327209</t>
+    <t xml:space="preserve">3.67779970169067</t>
   </si>
   <si>
     <t xml:space="preserve">3.7389509677887</t>
@@ -1166,31 +1166,31 @@
     <t xml:space="preserve">3.85251712799072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71274304389954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92240381240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61664867401123</t>
+    <t xml:space="preserve">3.71274328231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92240357398987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61664843559265</t>
   </si>
   <si>
     <t xml:space="preserve">3.39825224876404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23227071762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0575532913208</t>
+    <t xml:space="preserve">3.23227047920227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05755352973938</t>
   </si>
   <si>
     <t xml:space="preserve">2.97019457817078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95272302627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91777920722961</t>
+    <t xml:space="preserve">2.95272278785706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91777944564819</t>
   </si>
   <si>
     <t xml:space="preserve">2.90904355049133</t>
@@ -1199,19 +1199,19 @@
     <t xml:space="preserve">3.37204432487488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38078022003174</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41572403907776</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31962895393372</t>
+    <t xml:space="preserve">3.38077998161316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41572380065918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31962919235229</t>
   </si>
   <si>
     <t xml:space="preserve">3.27594995498657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28468561172485</t>
+    <t xml:space="preserve">3.28468585014343</t>
   </si>
   <si>
     <t xml:space="preserve">3.50245499610901</t>
@@ -1247,7 +1247,7 @@
     <t xml:space="preserve">3.32098078727722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26653814315796</t>
+    <t xml:space="preserve">3.26653838157654</t>
   </si>
   <si>
     <t xml:space="preserve">3.39357042312622</t>
@@ -1256,7 +1256,7 @@
     <t xml:space="preserve">3.23024344444275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19394874572754</t>
+    <t xml:space="preserve">3.19394850730896</t>
   </si>
   <si>
     <t xml:space="preserve">3.25746440887451</t>
@@ -1271,7 +1271,7 @@
     <t xml:space="preserve">3.2211697101593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10321140289307</t>
+    <t xml:space="preserve">3.10321164131165</t>
   </si>
   <si>
     <t xml:space="preserve">2.99432682991028</t>
@@ -1283,13 +1283,13 @@
     <t xml:space="preserve">2.95803189277649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85822105407715</t>
+    <t xml:space="preserve">2.85822129249573</t>
   </si>
   <si>
     <t xml:space="preserve">2.89451599121094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8672947883606</t>
+    <t xml:space="preserve">2.86729502677917</t>
   </si>
   <si>
     <t xml:space="preserve">2.81285238265991</t>
@@ -1301,7 +1301,7 @@
     <t xml:space="preserve">2.75841021537781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70396780967712</t>
+    <t xml:space="preserve">2.7039680480957</t>
   </si>
   <si>
     <t xml:space="preserve">2.72211527824402</t>
@@ -1310,16 +1310,16 @@
     <t xml:space="preserve">2.64952564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7947051525116</t>
+    <t xml:space="preserve">2.79470491409302</t>
   </si>
   <si>
     <t xml:space="preserve">2.92173719406128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05784273147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02154803276062</t>
+    <t xml:space="preserve">3.05784296989441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02154779434204</t>
   </si>
   <si>
     <t xml:space="preserve">3.13950634002686</t>
@@ -1349,46 +1349,46 @@
     <t xml:space="preserve">3.08506417274475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01247429847717</t>
+    <t xml:space="preserve">3.01247406005859</t>
   </si>
   <si>
     <t xml:space="preserve">2.88544225692749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7765576839447</t>
+    <t xml:space="preserve">2.77655744552612</t>
   </si>
   <si>
     <t xml:space="preserve">2.71304154396057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6313784122467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68582034111023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66767287254333</t>
+    <t xml:space="preserve">2.63137817382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68582057952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66767311096191</t>
   </si>
   <si>
     <t xml:space="preserve">2.55878829956055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52249336242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67674660682678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64045214653015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87636852264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83099985122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60415697097778</t>
+    <t xml:space="preserve">2.52249360084534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67674684524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64045190811157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87636876106262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83099961280823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6041567325592</t>
   </si>
   <si>
     <t xml:space="preserve">2.73118901252747</t>
@@ -1415,7 +1415,7 @@
     <t xml:space="preserve">2.91266345977783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12135887145996</t>
+    <t xml:space="preserve">3.12135910987854</t>
   </si>
   <si>
     <t xml:space="preserve">3.0759904384613</t>
@@ -1424,46 +1424,46 @@
     <t xml:space="preserve">3.0941379070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38449692726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41171765327454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37542319297791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42079138755798</t>
+    <t xml:space="preserve">3.38449668884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41171789169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37542295455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42079162597656</t>
   </si>
   <si>
     <t xml:space="preserve">3.43893885612488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36634945869446</t>
+    <t xml:space="preserve">3.36634922027588</t>
   </si>
   <si>
     <t xml:space="preserve">3.35727572441101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20302248001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27561187744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29375958442688</t>
+    <t xml:space="preserve">3.20302224159241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27561211585999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29375982284546</t>
   </si>
   <si>
     <t xml:space="preserve">3.1667275428772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11228513717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78563141822815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84007382392883</t>
+    <t xml:space="preserve">3.11228537559509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78563117980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84007358551025</t>
   </si>
   <si>
     <t xml:space="preserve">2.82192611694336</t>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="586" uniqueCount="586">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="587" uniqueCount="587">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02345752716064</t>
+    <t xml:space="preserve">3.02345776557922</t>
   </si>
   <si>
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519899368286</t>
+    <t xml:space="preserve">2.96519923210144</t>
   </si>
   <si>
     <t xml:space="preserve">2.88901567459106</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98013710975647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97266817092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94578003883362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95773029327393</t>
+    <t xml:space="preserve">2.98013758659363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97266840934753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9457802772522</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9577305316925</t>
   </si>
   <si>
     <t xml:space="preserve">2.96221160888672</t>
@@ -68,16 +68,16 @@
     <t xml:space="preserve">2.9353232383728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91291642189026</t>
+    <t xml:space="preserve">2.91291618347168</t>
   </si>
   <si>
     <t xml:space="preserve">2.9786434173584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98611235618591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03540802001953</t>
+    <t xml:space="preserve">2.98611259460449</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03540825843811</t>
   </si>
   <si>
     <t xml:space="preserve">3.05632138252258</t>
@@ -89,19 +89,19 @@
     <t xml:space="preserve">3.05034589767456</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98760604858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95026111602783</t>
+    <t xml:space="preserve">2.98760652542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95026135444641</t>
   </si>
   <si>
     <t xml:space="preserve">3.01598882675171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01001334190369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02495121955872</t>
+    <t xml:space="preserve">3.01001358032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02495169639587</t>
   </si>
   <si>
     <t xml:space="preserve">3.0174822807312</t>
@@ -110,28 +110,28 @@
     <t xml:space="preserve">3.03092670440674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99955677986145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0443708896637</t>
+    <t xml:space="preserve">2.99955654144287</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04437136650085</t>
   </si>
   <si>
     <t xml:space="preserve">2.959223985672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00254416465759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92785453796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90843462944031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9188916683197</t>
+    <t xml:space="preserve">3.00254440307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92785429954529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90843510627747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89648461341858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91889119148254</t>
   </si>
   <si>
     <t xml:space="preserve">2.9159038066864</t>
@@ -143,19 +143,19 @@
     <t xml:space="preserve">2.90544724464417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90992856025696</t>
+    <t xml:space="preserve">2.90992879867554</t>
   </si>
   <si>
     <t xml:space="preserve">2.92337274551392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8382260799408</t>
+    <t xml:space="preserve">2.83822584152222</t>
   </si>
   <si>
     <t xml:space="preserve">2.86063289642334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82627582550049</t>
+    <t xml:space="preserve">2.82627558708191</t>
   </si>
   <si>
     <t xml:space="preserve">2.77996754646301</t>
@@ -167,34 +167,34 @@
     <t xml:space="preserve">2.86810207366943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88304018974304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79639959335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87557077407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89797830581665</t>
+    <t xml:space="preserve">2.88303971290588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79639935493469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87557101249695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89797806739807</t>
   </si>
   <si>
     <t xml:space="preserve">2.80088114738464</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74262261390686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82179427146912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7500913143158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76353597640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7784743309021</t>
+    <t xml:space="preserve">2.74262285232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82179403305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75009179115295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76353573799133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77847409248352</t>
   </si>
   <si>
     <t xml:space="preserve">2.78594303131104</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">2.69631481170654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6515007019043</t>
+    <t xml:space="preserve">2.65150094032288</t>
   </si>
   <si>
     <t xml:space="preserve">2.62162446975708</t>
@@ -215,13 +215,13 @@
     <t xml:space="preserve">2.53946542739868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.56934118270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61415529251099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65896964073181</t>
+    <t xml:space="preserve">2.56934142112732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61415553092957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65896987915039</t>
   </si>
   <si>
     <t xml:space="preserve">2.68884563446045</t>
@@ -230,37 +230,37 @@
     <t xml:space="preserve">2.70378375053406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77100467681885</t>
+    <t xml:space="preserve">2.77100491523743</t>
   </si>
   <si>
     <t xml:space="preserve">2.81581878662109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73365998268127</t>
+    <t xml:space="preserve">2.7336597442627</t>
   </si>
   <si>
     <t xml:space="preserve">2.66643881797791</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68137669563293</t>
+    <t xml:space="preserve">2.68137645721436</t>
   </si>
   <si>
     <t xml:space="preserve">2.74112868309021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72619080543518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83075666427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89315104484558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69871830940247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83870959281921</t>
+    <t xml:space="preserve">2.72619104385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83075737953186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.893150806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69871854782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83870983123779</t>
   </si>
   <si>
     <t xml:space="preserve">2.93203687667847</t>
@@ -272,16 +272,16 @@
     <t xml:space="preserve">2.83093237876892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81537771224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84648704528809</t>
+    <t xml:space="preserve">2.81537795066833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84648680686951</t>
   </si>
   <si>
     <t xml:space="preserve">2.79982304573059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73760485649109</t>
+    <t xml:space="preserve">2.73760461807251</t>
   </si>
   <si>
     <t xml:space="preserve">2.76093697547913</t>
@@ -293,76 +293,76 @@
     <t xml:space="preserve">3.00980973243713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9553689956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90870547294617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88537311553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82315516471863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86204147338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00203275680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91648268699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8542640209198</t>
+    <t xml:space="preserve">2.95536875724792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90870523452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88537359237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82315492630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86204171180725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00203227996826</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91648244857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85426425933838</t>
   </si>
   <si>
     <t xml:space="preserve">2.7298276424408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68316388130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72205018997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75315976142883</t>
+    <t xml:space="preserve">2.68316411972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7220504283905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75315952301025</t>
   </si>
   <si>
     <t xml:space="preserve">2.70649576187134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93981456756592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99425506591797</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97870063781738</t>
+    <t xml:space="preserve">2.93981432914734</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99425554275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9787003993988</t>
   </si>
   <si>
     <t xml:space="preserve">2.86981868743896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94759130477905</t>
+    <t xml:space="preserve">2.94759202003479</t>
   </si>
   <si>
     <t xml:space="preserve">2.98647809028625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63650012016296</t>
+    <t xml:space="preserve">2.63650059700012</t>
   </si>
   <si>
     <t xml:space="preserve">2.550950050354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51984095573425</t>
+    <t xml:space="preserve">2.51984071731567</t>
   </si>
   <si>
     <t xml:space="preserve">2.41095876693726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34096336364746</t>
+    <t xml:space="preserve">2.34096312522888</t>
   </si>
   <si>
     <t xml:space="preserve">2.34874057769775</t>
@@ -374,37 +374,37 @@
     <t xml:space="preserve">2.2554132938385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24763584136963</t>
+    <t xml:space="preserve">2.24763607978821</t>
   </si>
   <si>
     <t xml:space="preserve">2.3254086971283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23208117485046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18541741371155</t>
+    <t xml:space="preserve">2.23208141326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18541765213013</t>
   </si>
   <si>
     <t xml:space="preserve">2.27874517440796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26319050788879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21652674674988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06875848770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1465311050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10764479637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15430855751038</t>
+    <t xml:space="preserve">2.26319003105164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2165265083313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06875824928284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14653086662292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10764455795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1543083190918</t>
   </si>
   <si>
     <t xml:space="preserve">2.17764019966125</t>
@@ -413,19 +413,19 @@
     <t xml:space="preserve">2.22430372238159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35651803016663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4887318611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52761816978455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43429064750671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44206833839417</t>
+    <t xml:space="preserve">2.35651779174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48873162269592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52761793136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43429088592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44206786155701</t>
   </si>
   <si>
     <t xml:space="preserve">2.5587272644043</t>
@@ -437,7 +437,7 @@
     <t xml:space="preserve">2.37207245826721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33318614959717</t>
+    <t xml:space="preserve">2.33318591117859</t>
   </si>
   <si>
     <t xml:space="preserve">2.29429960250854</t>
@@ -446,25 +446,25 @@
     <t xml:space="preserve">2.3798496723175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71427321434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58205938339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62872290611267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65983200073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57428169250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67538642883301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64427757263184</t>
+    <t xml:space="preserve">2.71427273750305</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58205890655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62872314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.659832239151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57428193092346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67538666725159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64427733421326</t>
   </si>
   <si>
     <t xml:space="preserve">2.69094133377075</t>
@@ -476,10 +476,10 @@
     <t xml:space="preserve">2.90092802047729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9631462097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92425966262817</t>
+    <t xml:space="preserve">2.96314597129822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92425990104675</t>
   </si>
   <si>
     <t xml:space="preserve">2.97092342376709</t>
@@ -488,55 +488,55 @@
     <t xml:space="preserve">3.01758742332458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04869675636292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03314208984375</t>
+    <t xml:space="preserve">3.04869627952576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03314185142517</t>
   </si>
   <si>
     <t xml:space="preserve">3.0642511844635</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07980561256409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06049919128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02811312675476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01191997528076</t>
+    <t xml:space="preserve">3.07980585098267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0604989528656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02811288833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01191973686218</t>
   </si>
   <si>
     <t xml:space="preserve">3.1090784072876</t>
   </si>
   <si>
-    <t xml:space="preserve">3.09288501739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1252715587616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0766921043396</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9957263469696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30339574813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41674733161926</t>
+    <t xml:space="preserve">3.0928852558136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12527108192444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07669186592102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99572658538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30339598655701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41674757003784</t>
   </si>
   <si>
     <t xml:space="preserve">3.35197520256042</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33578205108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36816835403442</t>
+    <t xml:space="preserve">3.33578181266785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36816811561584</t>
   </si>
   <si>
     <t xml:space="preserve">3.23862338066101</t>
@@ -548,7 +548,7 @@
     <t xml:space="preserve">3.27100944519043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28720259666443</t>
+    <t xml:space="preserve">3.28720235824585</t>
   </si>
   <si>
     <t xml:space="preserve">3.22243022918701</t>
@@ -557,22 +557,22 @@
     <t xml:space="preserve">3.17385077476501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20623707771301</t>
+    <t xml:space="preserve">3.20623731613159</t>
   </si>
   <si>
     <t xml:space="preserve">3.1414647102356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40055441856384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49771308898926</t>
+    <t xml:space="preserve">3.40055418014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49771332740784</t>
   </si>
   <si>
     <t xml:space="preserve">3.38436126708984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25481629371643</t>
+    <t xml:space="preserve">3.25481653213501</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004416465759</t>
@@ -581,25 +581,25 @@
     <t xml:space="preserve">2.96334028244019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97953343391418</t>
+    <t xml:space="preserve">2.97953367233276</t>
   </si>
   <si>
     <t xml:space="preserve">2.80140924453735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88237452507019</t>
+    <t xml:space="preserve">2.88237500190735</t>
   </si>
   <si>
     <t xml:space="preserve">2.86618161201477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84998846054077</t>
+    <t xml:space="preserve">2.84998822212219</t>
   </si>
   <si>
     <t xml:space="preserve">2.78521609306335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75283002853394</t>
+    <t xml:space="preserve">2.75282979011536</t>
   </si>
   <si>
     <t xml:space="preserve">2.72044372558594</t>
@@ -614,7 +614,7 @@
     <t xml:space="preserve">2.73663687705994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81760215759277</t>
+    <t xml:space="preserve">2.81760239601135</t>
   </si>
   <si>
     <t xml:space="preserve">2.89856767654419</t>
@@ -626,7 +626,7 @@
     <t xml:space="preserve">2.63947796821594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67186427116394</t>
+    <t xml:space="preserve">2.67186403274536</t>
   </si>
   <si>
     <t xml:space="preserve">2.62328481674194</t>
@@ -638,28 +638,28 @@
     <t xml:space="preserve">2.70425033569336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60709166526794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59089875221252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42896771430969</t>
+    <t xml:space="preserve">2.60709190368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59089851379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42896747589111</t>
   </si>
   <si>
     <t xml:space="preserve">2.54231905937195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46135354042053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3156156539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2994225025177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35488176345825</t>
+    <t xml:space="preserve">2.46135377883911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31561541557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29942274093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35488152503967</t>
   </si>
   <si>
     <t xml:space="preserve">2.40607476234436</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">2.06478762626648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03065872192383</t>
+    <t xml:space="preserve">2.03065896034241</t>
   </si>
   <si>
     <t xml:space="preserve">2.1671736240387</t>
@@ -698,7 +698,7 @@
     <t xml:space="preserve">2.55965423583984</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54258966445923</t>
+    <t xml:space="preserve">2.54258990287781</t>
   </si>
   <si>
     <t xml:space="preserve">2.45726799964905</t>
@@ -707,7 +707,7 @@
     <t xml:space="preserve">2.5767183303833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62791156768799</t>
+    <t xml:space="preserve">2.62791132926941</t>
   </si>
   <si>
     <t xml:space="preserve">2.61084699630737</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">2.69616913795471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71323347091675</t>
+    <t xml:space="preserve">2.71323323249817</t>
   </si>
   <si>
     <t xml:space="preserve">2.44020342826843</t>
@@ -737,7 +737,7 @@
     <t xml:space="preserve">2.15010929107666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33781743049622</t>
+    <t xml:space="preserve">2.33781719207764</t>
   </si>
   <si>
     <t xml:space="preserve">2.30368876457214</t>
@@ -746,10 +746,10 @@
     <t xml:space="preserve">2.25249576568604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23543119430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37194609642029</t>
+    <t xml:space="preserve">2.23543095588684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37194633483887</t>
   </si>
   <si>
     <t xml:space="preserve">2.38901042938232</t>
@@ -767,10 +767,10 @@
     <t xml:space="preserve">2.04772329330444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11598038673401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91120827198029</t>
+    <t xml:space="preserve">2.11598062515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91120839118958</t>
   </si>
   <si>
     <t xml:space="preserve">1.87707984447479</t>
@@ -779,7 +779,7 @@
     <t xml:space="preserve">1.84295094013214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97946560382843</t>
+    <t xml:space="preserve">1.97946584224701</t>
   </si>
   <si>
     <t xml:space="preserve">1.86001515388489</t>
@@ -788,10 +788,10 @@
     <t xml:space="preserve">1.94533693790436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96240139007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99653005599976</t>
+    <t xml:space="preserve">1.96240127086639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99652993679047</t>
   </si>
   <si>
     <t xml:space="preserve">2.81561923027039</t>
@@ -803,13 +803,13 @@
     <t xml:space="preserve">2.88387703895569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76442646980286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73029780387878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6791045665741</t>
+    <t xml:space="preserve">2.76442623138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73029756546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67910432815552</t>
   </si>
   <si>
     <t xml:space="preserve">2.74736189842224</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">2.86681246757507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79855513572693</t>
+    <t xml:space="preserve">2.79855489730835</t>
   </si>
   <si>
     <t xml:space="preserve">2.78149056434631</t>
@@ -839,16 +839,16 @@
     <t xml:space="preserve">3.00332713127136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03745603561401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98626279830933</t>
+    <t xml:space="preserve">3.03745627403259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98626303672791</t>
   </si>
   <si>
     <t xml:space="preserve">3.05452036857605</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07158493995667</t>
+    <t xml:space="preserve">3.07158470153809</t>
   </si>
   <si>
     <t xml:space="preserve">3.13984251022339</t>
@@ -866,19 +866,19 @@
     <t xml:space="preserve">3.16543889045715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1995677947998</t>
+    <t xml:space="preserve">3.19956755638123</t>
   </si>
   <si>
     <t xml:space="preserve">3.15690660476685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2336962223053</t>
+    <t xml:space="preserve">3.23369646072388</t>
   </si>
   <si>
     <t xml:space="preserve">3.27635717391968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24222850799561</t>
+    <t xml:space="preserve">3.24222826957703</t>
   </si>
   <si>
     <t xml:space="preserve">3.26782488822937</t>
@@ -887,16 +887,16 @@
     <t xml:space="preserve">3.31048607826233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34461498260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32755017280579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28488922119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18250322341919</t>
+    <t xml:space="preserve">3.34461450576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32755041122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28488945960999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18250346183777</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342126846313</t>
@@ -905,28 +905,28 @@
     <t xml:space="preserve">3.33710074424744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32836508750916</t>
+    <t xml:space="preserve">3.32836484909058</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342150688171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24974226951599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20606279373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15364766120911</t>
+    <t xml:space="preserve">3.24974250793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20606303215027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15364742279053</t>
   </si>
   <si>
     <t xml:space="preserve">3.21479892730713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17111968994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26721382141113</t>
+    <t xml:space="preserve">3.17111945152283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26721405982971</t>
   </si>
   <si>
     <t xml:space="preserve">3.36330842971802</t>
@@ -935,64 +935,64 @@
     <t xml:space="preserve">3.49434638023376</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58170533180237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56423330307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59044098854065</t>
+    <t xml:space="preserve">3.58170509338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56423354148865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59044122695923</t>
   </si>
   <si>
     <t xml:space="preserve">3.5030825138092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51181840896606</t>
+    <t xml:space="preserve">3.51181817054749</t>
   </si>
   <si>
     <t xml:space="preserve">3.54676175117493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63411998748779</t>
+    <t xml:space="preserve">3.63412022590637</t>
   </si>
   <si>
     <t xml:space="preserve">3.62538456916809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7476863861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69527149200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66906380653381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60791277885437</t>
+    <t xml:space="preserve">3.74768662452698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69527125358582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66906332969666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60791301727295</t>
   </si>
   <si>
     <t xml:space="preserve">3.55549788475037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66032814979553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65159201622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68653535842896</t>
+    <t xml:space="preserve">3.66032767295837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65159177780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68653512001038</t>
   </si>
   <si>
     <t xml:space="preserve">3.7040069103241</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75642251968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57296967506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53802585601807</t>
+    <t xml:space="preserve">3.75642275810242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57296943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53802609443665</t>
   </si>
   <si>
     <t xml:space="preserve">3.3458366394043</t>
@@ -1004,16 +1004,16 @@
     <t xml:space="preserve">3.42445969581604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45066738128662</t>
+    <t xml:space="preserve">3.45066714286804</t>
   </si>
   <si>
     <t xml:space="preserve">3.44193148612976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48561072349548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40698790550232</t>
+    <t xml:space="preserve">3.4856104850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4069881439209</t>
   </si>
   <si>
     <t xml:space="preserve">3.35457253456116</t>
@@ -1037,37 +1037,37 @@
     <t xml:space="preserve">3.72147917747498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.87872457504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17574405670166</t>
+    <t xml:space="preserve">3.8787248134613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17574453353882</t>
   </si>
   <si>
     <t xml:space="preserve">4.31551790237427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35046100616455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.18447971343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20195150375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25436687469482</t>
+    <t xml:space="preserve">4.35046148300171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1844801902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20195198059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25436639785767</t>
   </si>
   <si>
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493226051331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98355507850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94861173629761</t>
+    <t xml:space="preserve">3.90493202209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98355484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94861149787903</t>
   </si>
   <si>
     <t xml:space="preserve">3.93113970756531</t>
@@ -1076,10 +1076,10 @@
     <t xml:space="preserve">4.08838510513306</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07091379165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12332820892334</t>
+    <t xml:space="preserve">4.07091331481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1233286857605</t>
   </si>
   <si>
     <t xml:space="preserve">4.00102663040161</t>
@@ -1094,16 +1094,16 @@
     <t xml:space="preserve">4.0971212387085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2106876373291</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29804658889771</t>
+    <t xml:space="preserve">4.21068811416626</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29804611206055</t>
   </si>
   <si>
     <t xml:space="preserve">4.28930997848511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21942329406738</t>
+    <t xml:space="preserve">4.21942377090454</t>
   </si>
   <si>
     <t xml:space="preserve">4.19321632385254</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">4.11459302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06217765808105</t>
+    <t xml:space="preserve">4.06217813491821</t>
   </si>
   <si>
     <t xml:space="preserve">3.78263020515442</t>
@@ -1127,10 +1127,10 @@
     <t xml:space="preserve">3.80010175704956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82630968093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.835045337677</t>
+    <t xml:space="preserve">3.82630944252014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83504509925842</t>
   </si>
   <si>
     <t xml:space="preserve">3.84378123283386</t>
@@ -1142,16 +1142,16 @@
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734763145447</t>
+    <t xml:space="preserve">3.95734739303589</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.861252784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76515817642212</t>
+    <t xml:space="preserve">3.86125302314758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7651584148407</t>
   </si>
   <si>
     <t xml:space="preserve">3.8175733089447</t>
@@ -1160,7 +1160,7 @@
     <t xml:space="preserve">3.64285612106323</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67779970169067</t>
+    <t xml:space="preserve">3.67779946327209</t>
   </si>
   <si>
     <t xml:space="preserve">3.7389509677887</t>
@@ -1169,31 +1169,31 @@
     <t xml:space="preserve">3.85251712799072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71274328231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92240357398987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61664843559265</t>
+    <t xml:space="preserve">3.71274304389954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92240381240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61664867401123</t>
   </si>
   <si>
     <t xml:space="preserve">3.39825224876404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23227047920227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05755352973938</t>
+    <t xml:space="preserve">3.23227071762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0575532913208</t>
   </si>
   <si>
     <t xml:space="preserve">2.97019457817078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95272278785706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91777944564819</t>
+    <t xml:space="preserve">2.95272302627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91777920722961</t>
   </si>
   <si>
     <t xml:space="preserve">2.90904355049133</t>
@@ -1202,19 +1202,19 @@
     <t xml:space="preserve">3.37204432487488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38077998161316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41572380065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31962919235229</t>
+    <t xml:space="preserve">3.38078022003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41572403907776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31962895393372</t>
   </si>
   <si>
     <t xml:space="preserve">3.27594995498657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28468585014343</t>
+    <t xml:space="preserve">3.28468561172485</t>
   </si>
   <si>
     <t xml:space="preserve">3.50245499610901</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">3.32098078727722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26653838157654</t>
+    <t xml:space="preserve">3.26653814315796</t>
   </si>
   <si>
     <t xml:space="preserve">3.39357042312622</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">3.23024344444275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19394850730896</t>
+    <t xml:space="preserve">3.19394874572754</t>
   </si>
   <si>
     <t xml:space="preserve">3.25746440887451</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">3.2211697101593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10321164131165</t>
+    <t xml:space="preserve">3.10321140289307</t>
   </si>
   <si>
     <t xml:space="preserve">2.99432682991028</t>
@@ -1286,13 +1286,13 @@
     <t xml:space="preserve">2.95803189277649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85822129249573</t>
+    <t xml:space="preserve">2.85822105407715</t>
   </si>
   <si>
     <t xml:space="preserve">2.89451599121094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86729502677917</t>
+    <t xml:space="preserve">2.8672947883606</t>
   </si>
   <si>
     <t xml:space="preserve">2.81285238265991</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">2.75841021537781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7039680480957</t>
+    <t xml:space="preserve">2.70396780967712</t>
   </si>
   <si>
     <t xml:space="preserve">2.72211527824402</t>
@@ -1313,16 +1313,16 @@
     <t xml:space="preserve">2.64952564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79470491409302</t>
+    <t xml:space="preserve">2.7947051525116</t>
   </si>
   <si>
     <t xml:space="preserve">2.92173719406128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05784296989441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02154779434204</t>
+    <t xml:space="preserve">3.05784273147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02154803276062</t>
   </si>
   <si>
     <t xml:space="preserve">3.13950634002686</t>
@@ -1352,46 +1352,46 @@
     <t xml:space="preserve">3.08506417274475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01247406005859</t>
+    <t xml:space="preserve">3.01247429847717</t>
   </si>
   <si>
     <t xml:space="preserve">2.88544225692749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77655744552612</t>
+    <t xml:space="preserve">2.7765576839447</t>
   </si>
   <si>
     <t xml:space="preserve">2.71304154396057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63137817382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68582057952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66767311096191</t>
+    <t xml:space="preserve">2.6313784122467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68582034111023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66767287254333</t>
   </si>
   <si>
     <t xml:space="preserve">2.55878829956055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52249360084534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67674684524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64045190811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87636876106262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83099961280823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6041567325592</t>
+    <t xml:space="preserve">2.52249336242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67674660682678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64045214653015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87636852264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83099985122681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60415697097778</t>
   </si>
   <si>
     <t xml:space="preserve">2.73118901252747</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">2.91266345977783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12135910987854</t>
+    <t xml:space="preserve">3.12135887145996</t>
   </si>
   <si>
     <t xml:space="preserve">3.0759904384613</t>
@@ -1427,46 +1427,46 @@
     <t xml:space="preserve">3.0941379070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38449668884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41171789169312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37542295455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42079162597656</t>
+    <t xml:space="preserve">3.38449692726135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41171765327454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37542319297791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42079138755798</t>
   </si>
   <si>
     <t xml:space="preserve">3.43893885612488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36634922027588</t>
+    <t xml:space="preserve">3.36634945869446</t>
   </si>
   <si>
     <t xml:space="preserve">3.35727572441101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20302224159241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27561211585999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29375982284546</t>
+    <t xml:space="preserve">3.20302248001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27561187744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29375958442688</t>
   </si>
   <si>
     <t xml:space="preserve">3.1667275428772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11228537559509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78563117980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84007358551025</t>
+    <t xml:space="preserve">3.11228513717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78563141822815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84007382392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.82192611694336</t>
@@ -1770,6 +1770,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.77999997138977</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85999989509583</t>
   </si>
 </sst>
 </file>
@@ -56602,6 +56605,32 @@
         <v>9</v>
       </c>
     </row>
+    <row r="2097">
+      <c r="A2097" s="1" t="n">
+        <v>46020.6912731481</v>
+      </c>
+      <c r="B2097" t="n">
+        <v>151050</v>
+      </c>
+      <c r="C2097" t="n">
+        <v>4</v>
+      </c>
+      <c r="D2097" t="n">
+        <v>3.72000002861023</v>
+      </c>
+      <c r="E2097" t="n">
+        <v>3.88000011444092</v>
+      </c>
+      <c r="F2097" t="n">
+        <v>3.85999989509583</v>
+      </c>
+      <c r="G2097" t="s">
+        <v>586</v>
+      </c>
+      <c r="H2097" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02345776557922</t>
+    <t xml:space="preserve">3.02345752716064</t>
   </si>
   <si>
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519923210144</t>
+    <t xml:space="preserve">2.96519947052002</t>
   </si>
   <si>
     <t xml:space="preserve">2.88901543617249</t>
@@ -53,10 +53,10 @@
     <t xml:space="preserve">2.98013734817505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97266817092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94578003883362</t>
+    <t xml:space="preserve">2.97266840934753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94577980041504</t>
   </si>
   <si>
     <t xml:space="preserve">2.95773029327393</t>
@@ -65,7 +65,7 @@
     <t xml:space="preserve">2.96221160888672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9353232383728</t>
+    <t xml:space="preserve">2.93532299995422</t>
   </si>
   <si>
     <t xml:space="preserve">2.91291642189026</t>
@@ -74,13 +74,13 @@
     <t xml:space="preserve">2.9786434173584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98611235618591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03540802001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.056321144104</t>
+    <t xml:space="preserve">2.98611211776733</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03540825843811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05632138252258</t>
   </si>
   <si>
     <t xml:space="preserve">3.0593090057373</t>
@@ -95,28 +95,28 @@
     <t xml:space="preserve">2.95026135444641</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01598882675171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01001334190369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02495145797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01748204231262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03092646598816</t>
+    <t xml:space="preserve">3.01598858833313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01001358032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02495169639587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01748251914978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03092670440674</t>
   </si>
   <si>
     <t xml:space="preserve">2.99955677986145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04437136650085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95922422409058</t>
+    <t xml:space="preserve">3.0443708896637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95922446250916</t>
   </si>
   <si>
     <t xml:space="preserve">3.00254440307617</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">2.92785429954529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90843486785889</t>
+    <t xml:space="preserve">2.90843462944031</t>
   </si>
   <si>
     <t xml:space="preserve">2.89648461341858</t>
@@ -140,13 +140,13 @@
     <t xml:space="preserve">2.92038536071777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90544700622559</t>
+    <t xml:space="preserve">2.90544724464417</t>
   </si>
   <si>
     <t xml:space="preserve">2.90992856025696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92337274551392</t>
+    <t xml:space="preserve">2.9233729839325</t>
   </si>
   <si>
     <t xml:space="preserve">2.83822584152222</t>
@@ -155,31 +155,31 @@
     <t xml:space="preserve">2.86063313484192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82627582550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77996802330017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84569478034973</t>
+    <t xml:space="preserve">2.82627558708191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77996754646301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84569501876831</t>
   </si>
   <si>
     <t xml:space="preserve">2.86810183525085</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88304018974304</t>
+    <t xml:space="preserve">2.88303995132446</t>
   </si>
   <si>
     <t xml:space="preserve">2.79639935493469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87557101249695</t>
+    <t xml:space="preserve">2.87557077407837</t>
   </si>
   <si>
     <t xml:space="preserve">2.89797806739807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80088114738464</t>
+    <t xml:space="preserve">2.80088090896606</t>
   </si>
   <si>
     <t xml:space="preserve">2.74262261390686</t>
@@ -194,76 +194,76 @@
     <t xml:space="preserve">2.76353621482849</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77847361564636</t>
+    <t xml:space="preserve">2.77847409248352</t>
   </si>
   <si>
     <t xml:space="preserve">2.78594279289246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79341173171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69631481170654</t>
+    <t xml:space="preserve">2.79341197013855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69631457328796</t>
   </si>
   <si>
     <t xml:space="preserve">2.6515007019043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62162470817566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53946542739868</t>
+    <t xml:space="preserve">2.62162446975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5394651889801</t>
   </si>
   <si>
     <t xml:space="preserve">2.5693416595459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61415553092957</t>
+    <t xml:space="preserve">2.61415576934814</t>
   </si>
   <si>
     <t xml:space="preserve">2.65896964073181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68884587287903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70378375053406</t>
+    <t xml:space="preserve">2.68884563446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70378351211548</t>
   </si>
   <si>
     <t xml:space="preserve">2.77100491523743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81581902503967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7336597442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66643857955933</t>
+    <t xml:space="preserve">2.81581926345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73365998268127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66643881797791</t>
   </si>
   <si>
     <t xml:space="preserve">2.68137669563293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74112868309021</t>
+    <t xml:space="preserve">2.74112892150879</t>
   </si>
   <si>
     <t xml:space="preserve">2.72619080543518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8307569026947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89315056800842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69871878623962</t>
+    <t xml:space="preserve">2.83075714111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89315104484558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69871854782104</t>
   </si>
   <si>
     <t xml:space="preserve">2.83870983123779</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93203735351562</t>
+    <t xml:space="preserve">2.93203711509705</t>
   </si>
   <si>
     <t xml:space="preserve">2.87759613990784</t>
@@ -272,16 +272,16 @@
     <t xml:space="preserve">2.83093237876892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81537771224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84648680686951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79982304573059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73760485649109</t>
+    <t xml:space="preserve">2.81537747383118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84648704528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79982328414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73760509490967</t>
   </si>
   <si>
     <t xml:space="preserve">2.76093673706055</t>
@@ -290,46 +290,46 @@
     <t xml:space="preserve">2.80760049819946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00980997085571</t>
+    <t xml:space="preserve">3.00980973243713</t>
   </si>
   <si>
     <t xml:space="preserve">2.9553689956665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90870499610901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88537311553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82315516471863</t>
+    <t xml:space="preserve">2.90870547294617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88537335395813</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82315540313721</t>
   </si>
   <si>
     <t xml:space="preserve">2.86204171180725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00203251838684</t>
+    <t xml:space="preserve">3.00203227996826</t>
   </si>
   <si>
     <t xml:space="preserve">2.91648244857788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85426425933838</t>
+    <t xml:space="preserve">2.85426449775696</t>
   </si>
   <si>
     <t xml:space="preserve">2.7298276424408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68316388130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72205018997192</t>
+    <t xml:space="preserve">2.68316411972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7220504283905</t>
   </si>
   <si>
     <t xml:space="preserve">2.75315952301025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70649552345276</t>
+    <t xml:space="preserve">2.70649576187134</t>
   </si>
   <si>
     <t xml:space="preserve">2.93981432914734</t>
@@ -341,31 +341,31 @@
     <t xml:space="preserve">2.97870087623596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86981916427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94759154319763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98647785186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63650035858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.550950050354</t>
+    <t xml:space="preserve">2.86981868743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94759178161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98647809028625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63650012016296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55094981193542</t>
   </si>
   <si>
     <t xml:space="preserve">2.51984095573425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41095876693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34096336364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34874057769775</t>
+    <t xml:space="preserve">2.41095900535583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34096360206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34874081611633</t>
   </si>
   <si>
     <t xml:space="preserve">2.36429524421692</t>
@@ -374,19 +374,19 @@
     <t xml:space="preserve">2.2554132938385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24763607978821</t>
+    <t xml:space="preserve">2.24763584136963</t>
   </si>
   <si>
     <t xml:space="preserve">2.3254086971283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23208117485046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18541765213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27874493598938</t>
+    <t xml:space="preserve">2.23208093643188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18541741371155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27874517440796</t>
   </si>
   <si>
     <t xml:space="preserve">2.26319050788879</t>
@@ -395,28 +395,28 @@
     <t xml:space="preserve">2.21652674674988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06875848770142</t>
+    <t xml:space="preserve">2.06875824928284</t>
   </si>
   <si>
     <t xml:space="preserve">2.1465311050415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10764479637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15430808067322</t>
+    <t xml:space="preserve">2.10764455795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1543083190918</t>
   </si>
   <si>
     <t xml:space="preserve">2.17764019966125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22430372238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35651803016663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4887318611145</t>
+    <t xml:space="preserve">2.22430396080017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35651755332947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48873209953308</t>
   </si>
   <si>
     <t xml:space="preserve">2.52761816978455</t>
@@ -425,16 +425,16 @@
     <t xml:space="preserve">2.43429112434387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44206809997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5587272644043</t>
+    <t xml:space="preserve">2.44206786155701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55872702598572</t>
   </si>
   <si>
     <t xml:space="preserve">2.44984555244446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37207245826721</t>
+    <t xml:space="preserve">2.37207221984863</t>
   </si>
   <si>
     <t xml:space="preserve">2.33318614959717</t>
@@ -443,70 +443,70 @@
     <t xml:space="preserve">2.29429960250854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37984943389893</t>
+    <t xml:space="preserve">2.37984991073608</t>
   </si>
   <si>
     <t xml:space="preserve">2.71427321434021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58205890655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62872290611267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65983200073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57428216934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67538690567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64427733421326</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69094133377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76871395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90092802047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96314597129822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92425990104675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97092318534851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01758742332458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04869627952576</t>
+    <t xml:space="preserve">2.58205914497375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62872266769409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.659832239151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57428193092346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67538666725159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64427757263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69094109535217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76871418952942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90092778205872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9631462097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92426013946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97092342376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01758718490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04869651794434</t>
   </si>
   <si>
     <t xml:space="preserve">3.03314185142517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06425070762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07980561256409</t>
+    <t xml:space="preserve">3.06425094604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07980537414551</t>
   </si>
   <si>
     <t xml:space="preserve">3.0604989528656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0281126499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0119194984436</t>
+    <t xml:space="preserve">3.02811288833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01191973686218</t>
   </si>
   <si>
     <t xml:space="preserve">3.10907816886902</t>
@@ -515,7 +515,7 @@
     <t xml:space="preserve">3.09288501739502</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1252715587616</t>
+    <t xml:space="preserve">3.12527132034302</t>
   </si>
   <si>
     <t xml:space="preserve">3.0766921043396</t>
@@ -530,16 +530,16 @@
     <t xml:space="preserve">3.41674733161926</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35197496414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33578181266785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36816811561584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23862338066101</t>
+    <t xml:space="preserve">3.351975440979</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33578205108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36816835403442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23862314224243</t>
   </si>
   <si>
     <t xml:space="preserve">3.31958866119385</t>
@@ -551,10 +551,10 @@
     <t xml:space="preserve">3.28720235824585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22242999076843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17385077476501</t>
+    <t xml:space="preserve">3.22243022918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17385101318359</t>
   </si>
   <si>
     <t xml:space="preserve">3.20623707771301</t>
@@ -566,22 +566,22 @@
     <t xml:space="preserve">3.40055441856384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49771332740784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38436102867126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25481629371643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19004392623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96334028244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97953343391418</t>
+    <t xml:space="preserve">3.49771308898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38436126708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25481653213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19004416465759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96334052085876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97953391075134</t>
   </si>
   <si>
     <t xml:space="preserve">2.80140924453735</t>
@@ -596,37 +596,37 @@
     <t xml:space="preserve">2.84998846054077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78521633148193</t>
+    <t xml:space="preserve">2.78521609306335</t>
   </si>
   <si>
     <t xml:space="preserve">2.75282979011536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72044372558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83379530906677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76902270317078</t>
+    <t xml:space="preserve">2.72044348716736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83379554748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76902318000793</t>
   </si>
   <si>
     <t xml:space="preserve">2.73663663864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81760215759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89856743812561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91476106643677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63947796821594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67186427116394</t>
+    <t xml:space="preserve">2.81760239601135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89856767654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91476082801819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63947772979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67186403274536</t>
   </si>
   <si>
     <t xml:space="preserve">2.62328481674194</t>
@@ -659,16 +659,16 @@
     <t xml:space="preserve">2.2994225025177</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35488176345825</t>
+    <t xml:space="preserve">2.35488152503967</t>
   </si>
   <si>
     <t xml:space="preserve">2.40607476234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28662443161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1330451965332</t>
+    <t xml:space="preserve">2.28662419319153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13304495811462</t>
   </si>
   <si>
     <t xml:space="preserve">2.08185195922852</t>
@@ -680,34 +680,34 @@
     <t xml:space="preserve">2.03065896034241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16717338562012</t>
+    <t xml:space="preserve">2.1671736240387</t>
   </si>
   <si>
     <t xml:space="preserve">2.09891629219055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26955986022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2183666229248</t>
+    <t xml:space="preserve">2.26956009864807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21836686134338</t>
   </si>
   <si>
     <t xml:space="preserve">2.32075309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55965399742126</t>
+    <t xml:space="preserve">2.55965423583984</t>
   </si>
   <si>
     <t xml:space="preserve">2.54258990287781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45726776123047</t>
+    <t xml:space="preserve">2.45726799964905</t>
   </si>
   <si>
     <t xml:space="preserve">2.5767183303833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62791156768799</t>
+    <t xml:space="preserve">2.62791132926941</t>
   </si>
   <si>
     <t xml:space="preserve">2.61084699630737</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">2.64497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59378266334534</t>
+    <t xml:space="preserve">2.59378290176392</t>
   </si>
   <si>
     <t xml:space="preserve">2.69616913795471</t>
@@ -725,22 +725,22 @@
     <t xml:space="preserve">2.71323323249817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44020318984985</t>
+    <t xml:space="preserve">2.44020342826843</t>
   </si>
   <si>
     <t xml:space="preserve">2.42313933372498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47433257102966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15010952949524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33781743049622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30368852615356</t>
+    <t xml:space="preserve">2.47433233261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15010929107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33781719207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30368876457214</t>
   </si>
   <si>
     <t xml:space="preserve">2.25249576568604</t>
@@ -749,19 +749,19 @@
     <t xml:space="preserve">2.23543095588684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37194609642029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38901019096375</t>
+    <t xml:space="preserve">2.37194633483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38901042938232</t>
   </si>
   <si>
     <t xml:space="preserve">2.20130252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18423819541931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01359438896179</t>
+    <t xml:space="preserve">2.18423795700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01359415054321</t>
   </si>
   <si>
     <t xml:space="preserve">2.04772329330444</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">1.91120839118958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87707960605621</t>
+    <t xml:space="preserve">1.87707984447479</t>
   </si>
   <si>
     <t xml:space="preserve">1.84295094013214</t>
@@ -782,40 +782,40 @@
     <t xml:space="preserve">1.97946584224701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86001539230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94533705711365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96240139007568</t>
+    <t xml:space="preserve">1.86001515388489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94533693790436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96240127086639</t>
   </si>
   <si>
     <t xml:space="preserve">1.99652993679047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81561946868896</t>
+    <t xml:space="preserve">2.81561923027039</t>
   </si>
   <si>
     <t xml:space="preserve">2.90094137191772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88387680053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76442670822144</t>
+    <t xml:space="preserve">2.88387703895569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76442623138428</t>
   </si>
   <si>
     <t xml:space="preserve">2.73029756546021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6791045665741</t>
+    <t xml:space="preserve">2.67910432815552</t>
   </si>
   <si>
     <t xml:space="preserve">2.74736189842224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.832683801651</t>
+    <t xml:space="preserve">2.83268356323242</t>
   </si>
   <si>
     <t xml:space="preserve">2.86681246757507</t>
@@ -836,10 +836,10 @@
     <t xml:space="preserve">3.02039170265198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00332736968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03745603561401</t>
+    <t xml:space="preserve">3.00332713127136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03745627403259</t>
   </si>
   <si>
     <t xml:space="preserve">2.98626303672791</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.13131022453308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06305241584778</t>
+    <t xml:space="preserve">3.06305265426636</t>
   </si>
   <si>
     <t xml:space="preserve">3.16543889045715</t>
@@ -869,19 +869,19 @@
     <t xml:space="preserve">3.19956755638123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15690684318542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23369598388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2763569355011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24222850799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26782512664795</t>
+    <t xml:space="preserve">3.15690660476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23369646072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27635717391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24222826957703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26782488822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.31048607826233</t>
@@ -890,43 +890,43 @@
     <t xml:space="preserve">3.34461450576782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32755017280579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28488922119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18250322341919</t>
+    <t xml:space="preserve">3.32755041122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28488945960999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18250346183777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29342126846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33710074424744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32836484909058</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342150688171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33710074424744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32836508750916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29342174530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24974226951599</t>
+    <t xml:space="preserve">3.24974250793457</t>
   </si>
   <si>
     <t xml:space="preserve">3.20606303215027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15364766120911</t>
+    <t xml:space="preserve">3.15364742279053</t>
   </si>
   <si>
     <t xml:space="preserve">3.21479892730713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17111968994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26721382141113</t>
+    <t xml:space="preserve">3.17111945152283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26721405982971</t>
   </si>
   <si>
     <t xml:space="preserve">3.36330842971802</t>
@@ -938,70 +938,70 @@
     <t xml:space="preserve">3.58170509338379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56423330307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59044098854065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50308275222778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51181840896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54676151275635</t>
+    <t xml:space="preserve">3.56423354148865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59044122695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5030825138092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51181817054749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54676175117493</t>
   </si>
   <si>
     <t xml:space="preserve">3.63412022590637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62538480758667</t>
+    <t xml:space="preserve">3.62538456916809</t>
   </si>
   <si>
     <t xml:space="preserve">3.74768662452698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69527149200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66906380653381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60791277885437</t>
+    <t xml:space="preserve">3.69527125358582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66906332969666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60791301727295</t>
   </si>
   <si>
     <t xml:space="preserve">3.55549788475037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66032791137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65159201622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68653535842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70400714874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75642251968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57296967506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53802585601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34583687782288</t>
+    <t xml:space="preserve">3.66032767295837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65159177780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68653512001038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7040069103241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75642275810242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57296943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53802609443665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3458366394043</t>
   </si>
   <si>
     <t xml:space="preserve">3.38951635360718</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42445945739746</t>
+    <t xml:space="preserve">3.42445969581604</t>
   </si>
   <si>
     <t xml:space="preserve">3.45066714286804</t>
@@ -1010,16 +1010,16 @@
     <t xml:space="preserve">3.44193148612976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48561072349548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40698790550232</t>
+    <t xml:space="preserve">3.4856104850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4069881439209</t>
   </si>
   <si>
     <t xml:space="preserve">3.35457253456116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45940327644348</t>
+    <t xml:space="preserve">3.4594030380249</t>
   </si>
   <si>
     <t xml:space="preserve">3.52928996086121</t>
@@ -1034,10 +1034,10 @@
     <t xml:space="preserve">3.79136610031128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7214789390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87872457504272</t>
+    <t xml:space="preserve">3.72147917747498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8787248134613</t>
   </si>
   <si>
     <t xml:space="preserve">4.17574453353882</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">4.1844801902771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20195150375366</t>
+    <t xml:space="preserve">4.20195198059082</t>
   </si>
   <si>
     <t xml:space="preserve">4.25436639785767</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493178367615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98355507850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94861173629761</t>
+    <t xml:space="preserve">3.90493202209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98355484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94861149787903</t>
   </si>
   <si>
     <t xml:space="preserve">3.93113970756531</t>
@@ -1076,7 +1076,7 @@
     <t xml:space="preserve">4.08838510513306</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07091379165649</t>
+    <t xml:space="preserve">4.07091331481934</t>
   </si>
   <si>
     <t xml:space="preserve">4.1233286857605</t>
@@ -1085,16 +1085,16 @@
     <t xml:space="preserve">4.00102663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00976228713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93987607955933</t>
+    <t xml:space="preserve">4.00976276397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93987560272217</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21068716049194</t>
+    <t xml:space="preserve">4.21068811416626</t>
   </si>
   <si>
     <t xml:space="preserve">4.29804611206055</t>
@@ -1106,10 +1106,10 @@
     <t xml:space="preserve">4.21942377090454</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19321584701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1495361328125</t>
+    <t xml:space="preserve">4.19321632385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14953660964966</t>
   </si>
   <si>
     <t xml:space="preserve">4.16700839996338</t>
@@ -1118,37 +1118,37 @@
     <t xml:space="preserve">4.11459302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06217765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78262996673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80010151863098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82630968093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83504486083984</t>
+    <t xml:space="preserve">4.06217813491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78263020515442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80010175704956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82630944252014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83504509925842</t>
   </si>
   <si>
     <t xml:space="preserve">3.84378123283386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77389430999756</t>
+    <t xml:space="preserve">3.77389454841614</t>
   </si>
   <si>
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734763145447</t>
+    <t xml:space="preserve">3.95734739303589</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.861252784729</t>
+    <t xml:space="preserve">3.86125302314758</t>
   </si>
   <si>
     <t xml:space="preserve">3.7651584148407</t>
@@ -1157,10 +1157,10 @@
     <t xml:space="preserve">3.8175733089447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64285635948181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67779970169067</t>
+    <t xml:space="preserve">3.64285612106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67779946327209</t>
   </si>
   <si>
     <t xml:space="preserve">3.7389509677887</t>
@@ -1169,13 +1169,13 @@
     <t xml:space="preserve">3.85251712799072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71274328231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92240357398987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61664843559265</t>
+    <t xml:space="preserve">3.71274304389954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92240381240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61664867401123</t>
   </si>
   <si>
     <t xml:space="preserve">3.39825224876404</t>
@@ -1190,31 +1190,31 @@
     <t xml:space="preserve">2.97019457817078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95272278785706</t>
+    <t xml:space="preserve">2.95272302627563</t>
   </si>
   <si>
     <t xml:space="preserve">2.91777920722961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90904331207275</t>
+    <t xml:space="preserve">2.90904355049133</t>
   </si>
   <si>
     <t xml:space="preserve">3.37204432487488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38077998161316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41572380065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31962919235229</t>
+    <t xml:space="preserve">3.38078022003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41572403907776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31962895393372</t>
   </si>
   <si>
     <t xml:space="preserve">3.27594995498657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28468585014343</t>
+    <t xml:space="preserve">3.28468561172485</t>
   </si>
   <si>
     <t xml:space="preserve">3.50245499610901</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">3.32098078727722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26653838157654</t>
+    <t xml:space="preserve">3.26653814315796</t>
   </si>
   <si>
     <t xml:space="preserve">3.39357042312622</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">3.23024344444275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19394850730896</t>
+    <t xml:space="preserve">3.19394874572754</t>
   </si>
   <si>
     <t xml:space="preserve">3.25746440887451</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">3.2211697101593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10321164131165</t>
+    <t xml:space="preserve">3.10321140289307</t>
   </si>
   <si>
     <t xml:space="preserve">2.99432682991028</t>
@@ -1286,13 +1286,13 @@
     <t xml:space="preserve">2.95803189277649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85822129249573</t>
+    <t xml:space="preserve">2.85822105407715</t>
   </si>
   <si>
     <t xml:space="preserve">2.89451599121094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86729502677917</t>
+    <t xml:space="preserve">2.8672947883606</t>
   </si>
   <si>
     <t xml:space="preserve">2.81285238265991</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">2.75841021537781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7039680480957</t>
+    <t xml:space="preserve">2.70396780967712</t>
   </si>
   <si>
     <t xml:space="preserve">2.72211527824402</t>
@@ -1313,16 +1313,16 @@
     <t xml:space="preserve">2.64952564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79470491409302</t>
+    <t xml:space="preserve">2.7947051525116</t>
   </si>
   <si>
     <t xml:space="preserve">2.92173719406128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05784296989441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02154779434204</t>
+    <t xml:space="preserve">3.05784273147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02154803276062</t>
   </si>
   <si>
     <t xml:space="preserve">3.13950634002686</t>
@@ -1352,46 +1352,46 @@
     <t xml:space="preserve">3.08506417274475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01247406005859</t>
+    <t xml:space="preserve">3.01247429847717</t>
   </si>
   <si>
     <t xml:space="preserve">2.88544225692749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77655744552612</t>
+    <t xml:space="preserve">2.7765576839447</t>
   </si>
   <si>
     <t xml:space="preserve">2.71304154396057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63137817382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68582057952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66767311096191</t>
+    <t xml:space="preserve">2.6313784122467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68582034111023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66767287254333</t>
   </si>
   <si>
     <t xml:space="preserve">2.55878829956055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52249360084534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67674684524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64045190811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87636876106262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83099961280823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6041567325592</t>
+    <t xml:space="preserve">2.52249336242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67674660682678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64045214653015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87636852264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83099985122681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60415697097778</t>
   </si>
   <si>
     <t xml:space="preserve">2.73118901252747</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">2.91266345977783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12135910987854</t>
+    <t xml:space="preserve">3.12135887145996</t>
   </si>
   <si>
     <t xml:space="preserve">3.0759904384613</t>
@@ -1427,46 +1427,46 @@
     <t xml:space="preserve">3.0941379070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38449668884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41171789169312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37542295455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42079162597656</t>
+    <t xml:space="preserve">3.38449692726135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41171765327454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37542319297791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42079138755798</t>
   </si>
   <si>
     <t xml:space="preserve">3.43893885612488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36634922027588</t>
+    <t xml:space="preserve">3.36634945869446</t>
   </si>
   <si>
     <t xml:space="preserve">3.35727572441101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20302224159241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27561211585999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29375982284546</t>
+    <t xml:space="preserve">3.20302248001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27561187744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29375958442688</t>
   </si>
   <si>
     <t xml:space="preserve">3.1667275428772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11228537559509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78563117980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84007358551025</t>
+    <t xml:space="preserve">3.11228513717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78563141822815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84007382392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.82192611694336</t>
@@ -56662,7 +56662,7 @@
     </row>
     <row r="2099">
       <c r="A2099" s="1" t="n">
-        <v>46024.6844791667</v>
+        <v>46024.3333333333</v>
       </c>
       <c r="B2099" t="n">
         <v>39735</v>
@@ -56683,6 +56683,32 @@
         <v>587</v>
       </c>
       <c r="H2099" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2100">
+      <c r="A2100" s="1" t="n">
+        <v>46027.6912847222</v>
+      </c>
+      <c r="B2100" t="n">
+        <v>39279</v>
+      </c>
+      <c r="C2100" t="n">
+        <v>3.88000011444092</v>
+      </c>
+      <c r="D2100" t="n">
+        <v>3.79999995231628</v>
+      </c>
+      <c r="E2100" t="n">
+        <v>3.8199999332428</v>
+      </c>
+      <c r="F2100" t="n">
+        <v>3.8199999332428</v>
+      </c>
+      <c r="G2100" t="s">
+        <v>587</v>
+      </c>
+      <c r="H2100" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="590">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -38,28 +38,28 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02345752716064</t>
+    <t xml:space="preserve">3.02345776557922</t>
   </si>
   <si>
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519923210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88901567459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98013758659363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97266864776611</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94578003883362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9577305316925</t>
+    <t xml:space="preserve">2.96519947052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88901543617249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98013734817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97266840934753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94577956199646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95773029327393</t>
   </si>
   <si>
     <t xml:space="preserve">2.9622118473053</t>
@@ -77,19 +77,19 @@
     <t xml:space="preserve">2.98611235618591</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03540802001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.056321144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05930924415588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05034637451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98760652542114</t>
+    <t xml:space="preserve">3.03540849685669</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05632138252258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0593090057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05034613609314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98760628700256</t>
   </si>
   <si>
     <t xml:space="preserve">2.95026135444641</t>
@@ -101,19 +101,19 @@
     <t xml:space="preserve">3.01001358032227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02495145797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01748204231262</t>
+    <t xml:space="preserve">3.02495121955872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01748251914978</t>
   </si>
   <si>
     <t xml:space="preserve">3.03092670440674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99955654144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04437112808228</t>
+    <t xml:space="preserve">2.99955677986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0443708896637</t>
   </si>
   <si>
     <t xml:space="preserve">2.959223985672</t>
@@ -128,67 +128,67 @@
     <t xml:space="preserve">2.90843486785889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91889119148254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91590356826782</t>
+    <t xml:space="preserve">2.89648413658142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91889142990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91590404510498</t>
   </si>
   <si>
     <t xml:space="preserve">2.92038536071777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90544700622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90992832183838</t>
+    <t xml:space="preserve">2.90544724464417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90992856025696</t>
   </si>
   <si>
     <t xml:space="preserve">2.9233729839325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83822560310364</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86063289642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82627558708191</t>
+    <t xml:space="preserve">2.83822584152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86063313484192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82627534866333</t>
   </si>
   <si>
     <t xml:space="preserve">2.77996778488159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84569478034973</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86810183525085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88304018974304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79639935493469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87557125091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89797806739807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80088114738464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74262261390686</t>
+    <t xml:space="preserve">2.84569501876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86810207366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88303995132446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79639959335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87557101249695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89797830581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80088090896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74262237548828</t>
   </si>
   <si>
     <t xml:space="preserve">2.82179427146912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75009155273438</t>
+    <t xml:space="preserve">2.75009179115295</t>
   </si>
   <si>
     <t xml:space="preserve">2.76353597640991</t>
@@ -203,22 +203,22 @@
     <t xml:space="preserve">2.79341197013855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69631481170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6515007019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62162446975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53946542739868</t>
+    <t xml:space="preserve">2.69631457328796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65150046348572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62162470817566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5394651889801</t>
   </si>
   <si>
     <t xml:space="preserve">2.5693416595459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61415553092957</t>
+    <t xml:space="preserve">2.61415576934814</t>
   </si>
   <si>
     <t xml:space="preserve">2.65896964073181</t>
@@ -227,25 +227,25 @@
     <t xml:space="preserve">2.68884563446045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70378351211548</t>
+    <t xml:space="preserve">2.70378375053406</t>
   </si>
   <si>
     <t xml:space="preserve">2.77100491523743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81581902503967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7336597442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66643881797791</t>
+    <t xml:space="preserve">2.81581926345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73365950584412</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66643834114075</t>
   </si>
   <si>
     <t xml:space="preserve">2.68137645721436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74112868309021</t>
+    <t xml:space="preserve">2.74112892150879</t>
   </si>
   <si>
     <t xml:space="preserve">2.72619080543518</t>
@@ -254,10 +254,10 @@
     <t xml:space="preserve">2.8307569026947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.893150806427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69871854782104</t>
+    <t xml:space="preserve">2.89315056800842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69871878623962</t>
   </si>
   <si>
     <t xml:space="preserve">2.83870983123779</t>
@@ -266,28 +266,28 @@
     <t xml:space="preserve">2.93203711509705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87759613990784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83093237876892</t>
+    <t xml:space="preserve">2.87759590148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8309326171875</t>
   </si>
   <si>
     <t xml:space="preserve">2.81537771224976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84648704528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79982280731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73760461807251</t>
+    <t xml:space="preserve">2.84648680686951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79982328414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73760509490967</t>
   </si>
   <si>
     <t xml:space="preserve">2.76093673706055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80760025978088</t>
+    <t xml:space="preserve">2.80760049819946</t>
   </si>
   <si>
     <t xml:space="preserve">3.00980997085571</t>
@@ -302,16 +302,16 @@
     <t xml:space="preserve">2.88537335395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82315492630005</t>
+    <t xml:space="preserve">2.82315540313721</t>
   </si>
   <si>
     <t xml:space="preserve">2.86204171180725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00203251838684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91648268699646</t>
+    <t xml:space="preserve">3.00203275680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91648244857788</t>
   </si>
   <si>
     <t xml:space="preserve">2.85426425933838</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">2.7220504283905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75315952301025</t>
+    <t xml:space="preserve">2.75315928459167</t>
   </si>
   <si>
     <t xml:space="preserve">2.70649576187134</t>
@@ -338,16 +338,16 @@
     <t xml:space="preserve">2.99425530433655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97870063781738</t>
+    <t xml:space="preserve">2.97870087623596</t>
   </si>
   <si>
     <t xml:space="preserve">2.86981892585754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94759154319763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98647785186768</t>
+    <t xml:space="preserve">2.94759130477905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98647809028625</t>
   </si>
   <si>
     <t xml:space="preserve">2.63650035858154</t>
@@ -359,19 +359,19 @@
     <t xml:space="preserve">2.51984095573425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41095852851868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34096336364746</t>
+    <t xml:space="preserve">2.41095876693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34096312522888</t>
   </si>
   <si>
     <t xml:space="preserve">2.34874057769775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36429524421692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25541305541992</t>
+    <t xml:space="preserve">2.36429500579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2554132938385</t>
   </si>
   <si>
     <t xml:space="preserve">2.24763607978821</t>
@@ -380,34 +380,34 @@
     <t xml:space="preserve">2.3254086971283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23208117485046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18541765213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27874517440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26319050788879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21652698516846</t>
+    <t xml:space="preserve">2.23208141326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18541741371155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27874493598938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26319026947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21652674674988</t>
   </si>
   <si>
     <t xml:space="preserve">2.06875824928284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1465311050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10764503479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1543083190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17764043807983</t>
+    <t xml:space="preserve">2.14653134346008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10764455795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15430855751038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17763996124268</t>
   </si>
   <si>
     <t xml:space="preserve">2.22430396080017</t>
@@ -416,19 +416,19 @@
     <t xml:space="preserve">2.35651779174805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4887318611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52761816978455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43429088592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44206786155701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5587272644043</t>
+    <t xml:space="preserve">2.48873162269592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52761840820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43429112434387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44206809997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55872750282288</t>
   </si>
   <si>
     <t xml:space="preserve">2.44984531402588</t>
@@ -437,34 +437,34 @@
     <t xml:space="preserve">2.37207221984863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33318591117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29429960250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3798496723175</t>
+    <t xml:space="preserve">2.33318614959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29429984092712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37984943389893</t>
   </si>
   <si>
     <t xml:space="preserve">2.71427321434021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58205914497375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62872314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65983200073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57428193092346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67538690567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64427757263184</t>
+    <t xml:space="preserve">2.58205890655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62872290611267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.659832239151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57428169250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67538666725159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64427733421326</t>
   </si>
   <si>
     <t xml:space="preserve">2.69094133377075</t>
@@ -473,52 +473,52 @@
     <t xml:space="preserve">2.76871395111084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90092778205872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96314597129822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92425990104675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97092342376709</t>
+    <t xml:space="preserve">2.90092802047729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9631462097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92426013946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97092366218567</t>
   </si>
   <si>
     <t xml:space="preserve">3.01758742332458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04869651794434</t>
+    <t xml:space="preserve">3.04869627952576</t>
   </si>
   <si>
     <t xml:space="preserve">3.03314185142517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06425094604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07980585098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0604989528656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0281126499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01191973686218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10907816886902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09288501739502</t>
+    <t xml:space="preserve">3.0642511844635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07980561256409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06049919128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02811288833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01191997528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1090784072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0928852558136</t>
   </si>
   <si>
     <t xml:space="preserve">3.12527132034302</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0766921043396</t>
+    <t xml:space="preserve">3.07669234275818</t>
   </si>
   <si>
     <t xml:space="preserve">2.99572658538818</t>
@@ -527,25 +527,25 @@
     <t xml:space="preserve">3.30339574813843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41674733161926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35197496414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33578181266785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36816787719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23862361907959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31958889961243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27100968360901</t>
+    <t xml:space="preserve">3.41674757003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35197520256042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33578205108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36816811561584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23862338066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31958913803101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27100944519043</t>
   </si>
   <si>
     <t xml:space="preserve">3.28720259666443</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">3.22243022918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17385101318359</t>
+    <t xml:space="preserve">3.17385125160217</t>
   </si>
   <si>
     <t xml:space="preserve">3.20623707771301</t>
@@ -563,25 +563,25 @@
     <t xml:space="preserve">3.1414647102356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40055465698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49771356582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38436126708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25481653213501</t>
+    <t xml:space="preserve">3.40055418014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49771332740784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38436150550842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25481677055359</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004416465759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96334052085876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97953343391418</t>
+    <t xml:space="preserve">2.96334028244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97953367233276</t>
   </si>
   <si>
     <t xml:space="preserve">2.80140924453735</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">2.88237476348877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86618161201477</t>
+    <t xml:space="preserve">2.86618185043335</t>
   </si>
   <si>
     <t xml:space="preserve">2.84998822212219</t>
@@ -605,34 +605,34 @@
     <t xml:space="preserve">2.72044348716736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83379554748535</t>
+    <t xml:space="preserve">2.83379530906677</t>
   </si>
   <si>
     <t xml:space="preserve">2.76902294158936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73663687705994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81760215759277</t>
+    <t xml:space="preserve">2.73663711547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81760239601135</t>
   </si>
   <si>
     <t xml:space="preserve">2.89856791496277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91476106643677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63947820663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67186450958252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62328457832336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68805742263794</t>
+    <t xml:space="preserve">2.91476082801819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63947796821594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67186427116394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62328505516052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68805718421936</t>
   </si>
   <si>
     <t xml:space="preserve">2.70425057411194</t>
@@ -641,43 +641,43 @@
     <t xml:space="preserve">2.60709166526794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59089851379395</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42896747589111</t>
+    <t xml:space="preserve">2.59089875221252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42896771430969</t>
   </si>
   <si>
     <t xml:space="preserve">2.54231929779053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46135354042053</t>
+    <t xml:space="preserve">2.46135377883911</t>
   </si>
   <si>
     <t xml:space="preserve">2.3156156539917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29942226409912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35488176345825</t>
+    <t xml:space="preserve">2.2994225025177</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35488152503967</t>
   </si>
   <si>
     <t xml:space="preserve">2.40607476234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28662443161011</t>
+    <t xml:space="preserve">2.28662419319153</t>
   </si>
   <si>
     <t xml:space="preserve">2.13304495811462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08185195922852</t>
+    <t xml:space="preserve">2.08185219764709</t>
   </si>
   <si>
     <t xml:space="preserve">2.06478762626648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03065896034241</t>
+    <t xml:space="preserve">2.03065872192383</t>
   </si>
   <si>
     <t xml:space="preserve">2.1671736240387</t>
@@ -689,40 +689,40 @@
     <t xml:space="preserve">2.26955986022949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21836638450623</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32075309753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55965399742126</t>
+    <t xml:space="preserve">2.21836686134338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3207528591156</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55965423583984</t>
   </si>
   <si>
     <t xml:space="preserve">2.54258966445923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45726799964905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57671856880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62791132926941</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61084723472595</t>
+    <t xml:space="preserve">2.45726776123047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5767183303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62791156768799</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61084699630737</t>
   </si>
   <si>
     <t xml:space="preserve">2.64497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59378266334534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69616889953613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71323323249817</t>
+    <t xml:space="preserve">2.59378290176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69616913795471</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71323347091675</t>
   </si>
   <si>
     <t xml:space="preserve">2.44020342826843</t>
@@ -743,13 +743,13 @@
     <t xml:space="preserve">2.30368876457214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25249552726746</t>
+    <t xml:space="preserve">2.25249576568604</t>
   </si>
   <si>
     <t xml:space="preserve">2.23543095588684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37194633483887</t>
+    <t xml:space="preserve">2.37194609642029</t>
   </si>
   <si>
     <t xml:space="preserve">2.38901042938232</t>
@@ -770,52 +770,52 @@
     <t xml:space="preserve">2.11598062515259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91120839118958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8770797252655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84295105934143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97946560382843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86001539230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94533705711365</t>
+    <t xml:space="preserve">1.911208152771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87707984447479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84295094013214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97946572303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86001527309418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94533681869507</t>
   </si>
   <si>
     <t xml:space="preserve">1.96240139007568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99653017520905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81561970710754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9009416103363</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88387703895569</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76442623138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73029756546021</t>
+    <t xml:space="preserve">1.99653005599976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81561946868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90094137191772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88387727737427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76442646980286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73029780387878</t>
   </si>
   <si>
     <t xml:space="preserve">2.6791045665741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74736166000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.832683801651</t>
+    <t xml:space="preserve">2.74736189842224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83268356323242</t>
   </si>
   <si>
     <t xml:space="preserve">2.86681246757507</t>
@@ -824,7 +824,7 @@
     <t xml:space="preserve">2.79855513572693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78149080276489</t>
+    <t xml:space="preserve">2.78149056434631</t>
   </si>
   <si>
     <t xml:space="preserve">2.9350700378418</t>
@@ -833,13 +833,13 @@
     <t xml:space="preserve">2.96919870376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02039170265198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00332736968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03745579719543</t>
+    <t xml:space="preserve">3.02039194107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00332713127136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03745603561401</t>
   </si>
   <si>
     <t xml:space="preserve">2.98626303672791</t>
@@ -863,7 +863,7 @@
     <t xml:space="preserve">3.06305241584778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16543889045715</t>
+    <t xml:space="preserve">3.16543865203857</t>
   </si>
   <si>
     <t xml:space="preserve">3.19956755638123</t>
@@ -872,25 +872,25 @@
     <t xml:space="preserve">3.15690660476685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2336962223053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27635669708252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24222826957703</t>
+    <t xml:space="preserve">3.23369598388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27635717391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24222850799561</t>
   </si>
   <si>
     <t xml:space="preserve">3.26782488822937</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31048583984375</t>
+    <t xml:space="preserve">3.31048607826233</t>
   </si>
   <si>
     <t xml:space="preserve">3.34461498260498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32755041122437</t>
+    <t xml:space="preserve">3.32755017280579</t>
   </si>
   <si>
     <t xml:space="preserve">3.28488922119141</t>
@@ -1779,6 +1779,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.83999991416931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79999995231628</t>
   </si>
 </sst>
 </file>
@@ -56743,7 +56746,7 @@
     </row>
     <row r="2102">
       <c r="A2102" s="1" t="n">
-        <v>46029.6802893518</v>
+        <v>46029.3333333333</v>
       </c>
       <c r="B2102" t="n">
         <v>19804</v>
@@ -56764,6 +56767,32 @@
         <v>588</v>
       </c>
       <c r="H2102" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2103">
+      <c r="A2103" s="1" t="n">
+        <v>46030.69125</v>
+      </c>
+      <c r="B2103" t="n">
+        <v>45307</v>
+      </c>
+      <c r="C2103" t="n">
+        <v>3.85999989509583</v>
+      </c>
+      <c r="D2103" t="n">
+        <v>3.70000004768372</v>
+      </c>
+      <c r="E2103" t="n">
+        <v>3.85999989509583</v>
+      </c>
+      <c r="F2103" t="n">
+        <v>3.79999995231628</v>
+      </c>
+      <c r="G2103" t="s">
+        <v>589</v>
+      </c>
+      <c r="H2103" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -38,13 +38,13 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02345776557922</t>
+    <t xml:space="preserve">3.02345752716064</t>
   </si>
   <si>
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519947052002</t>
+    <t xml:space="preserve">2.96519923210144</t>
   </si>
   <si>
     <t xml:space="preserve">2.88901543617249</t>
@@ -53,13 +53,13 @@
     <t xml:space="preserve">2.98013734817505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97266840934753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94577956199646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95773029327393</t>
+    <t xml:space="preserve">2.97266817092896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94577980041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9577305316925</t>
   </si>
   <si>
     <t xml:space="preserve">2.9622118473053</t>
@@ -71,16 +71,16 @@
     <t xml:space="preserve">2.91291642189026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9786434173584</t>
+    <t xml:space="preserve">2.97864365577698</t>
   </si>
   <si>
     <t xml:space="preserve">2.98611235618591</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03540849685669</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05632138252258</t>
+    <t xml:space="preserve">3.03540802001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.056321144104</t>
   </si>
   <si>
     <t xml:space="preserve">3.0593090057373</t>
@@ -95,13 +95,13 @@
     <t xml:space="preserve">2.95026135444641</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01598858833313</t>
+    <t xml:space="preserve">3.01598882675171</t>
   </si>
   <si>
     <t xml:space="preserve">3.01001358032227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02495121955872</t>
+    <t xml:space="preserve">3.02495169639587</t>
   </si>
   <si>
     <t xml:space="preserve">3.01748251914978</t>
@@ -113,7 +113,7 @@
     <t xml:space="preserve">2.99955677986145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0443708896637</t>
+    <t xml:space="preserve">3.04437112808228</t>
   </si>
   <si>
     <t xml:space="preserve">2.959223985672</t>
@@ -128,19 +128,19 @@
     <t xml:space="preserve">2.90843486785889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89648413658142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91889142990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91590404510498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92038536071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90544724464417</t>
+    <t xml:space="preserve">2.89648461341858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91889119148254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9159038066864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92038512229919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90544700622559</t>
   </si>
   <si>
     <t xml:space="preserve">2.90992856025696</t>
@@ -149,13 +149,13 @@
     <t xml:space="preserve">2.9233729839325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83822584152222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86063313484192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82627534866333</t>
+    <t xml:space="preserve">2.8382260799408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8606333732605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82627558708191</t>
   </si>
   <si>
     <t xml:space="preserve">2.77996778488159</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">2.88303995132446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79639959335327</t>
+    <t xml:space="preserve">2.79639935493469</t>
   </si>
   <si>
     <t xml:space="preserve">2.87557101249695</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">2.82179427146912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75009179115295</t>
+    <t xml:space="preserve">2.75009155273438</t>
   </si>
   <si>
     <t xml:space="preserve">2.76353597640991</t>
@@ -197,19 +197,19 @@
     <t xml:space="preserve">2.77847385406494</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78594279289246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79341197013855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69631457328796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65150046348572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62162470817566</t>
+    <t xml:space="preserve">2.78594303131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79341220855713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69631481170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6515007019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62162446975708</t>
   </si>
   <si>
     <t xml:space="preserve">2.5394651889801</t>
@@ -218,7 +218,7 @@
     <t xml:space="preserve">2.5693416595459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61415576934814</t>
+    <t xml:space="preserve">2.61415553092957</t>
   </si>
   <si>
     <t xml:space="preserve">2.65896964073181</t>
@@ -230,28 +230,28 @@
     <t xml:space="preserve">2.70378375053406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77100491523743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81581926345825</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73365950584412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66643834114075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68137645721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74112892150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72619080543518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8307569026947</t>
+    <t xml:space="preserve">2.77100467681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81581902503967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7336597442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66643905639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68137669563293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74112868309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7261905670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83075714111328</t>
   </si>
   <si>
     <t xml:space="preserve">2.89315056800842</t>
@@ -260,31 +260,31 @@
     <t xml:space="preserve">2.69871878623962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83870983123779</t>
+    <t xml:space="preserve">2.83870959281921</t>
   </si>
   <si>
     <t xml:space="preserve">2.93203711509705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87759590148926</t>
+    <t xml:space="preserve">2.87759613990784</t>
   </si>
   <si>
     <t xml:space="preserve">2.8309326171875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81537771224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84648680686951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79982328414917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73760509490967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76093673706055</t>
+    <t xml:space="preserve">2.81537795066833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84648704528809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79982304573059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73760461807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76093697547913</t>
   </si>
   <si>
     <t xml:space="preserve">2.80760049819946</t>
@@ -293,10 +293,10 @@
     <t xml:space="preserve">3.00980997085571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95536875724792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90870523452759</t>
+    <t xml:space="preserve">2.9553689956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90870499610901</t>
   </si>
   <si>
     <t xml:space="preserve">2.88537335395813</t>
@@ -311,16 +311,16 @@
     <t xml:space="preserve">3.00203275680542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91648244857788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85426425933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7298276424408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68316388130188</t>
+    <t xml:space="preserve">2.9164822101593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85426449775696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72982740402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68316411972046</t>
   </si>
   <si>
     <t xml:space="preserve">2.7220504283905</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">2.86981892585754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94759130477905</t>
+    <t xml:space="preserve">2.94759178161621</t>
   </si>
   <si>
     <t xml:space="preserve">2.98647809028625</t>
@@ -353,7 +353,7 @@
     <t xml:space="preserve">2.63650035858154</t>
   </si>
   <si>
-    <t xml:space="preserve">2.550950050354</t>
+    <t xml:space="preserve">2.55095028877258</t>
   </si>
   <si>
     <t xml:space="preserve">2.51984095573425</t>
@@ -362,31 +362,31 @@
     <t xml:space="preserve">2.41095876693726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34096312522888</t>
+    <t xml:space="preserve">2.34096336364746</t>
   </si>
   <si>
     <t xml:space="preserve">2.34874057769775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36429500579834</t>
+    <t xml:space="preserve">2.36429524421692</t>
   </si>
   <si>
     <t xml:space="preserve">2.2554132938385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24763607978821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3254086971283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23208141326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18541741371155</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27874493598938</t>
+    <t xml:space="preserve">2.24763631820679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32540845870972</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23208117485046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18541765213013</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2787446975708</t>
   </si>
   <si>
     <t xml:space="preserve">2.26319026947021</t>
@@ -398,34 +398,34 @@
     <t xml:space="preserve">2.06875824928284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14653134346008</t>
+    <t xml:space="preserve">2.1465311050415</t>
   </si>
   <si>
     <t xml:space="preserve">2.10764455795288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15430855751038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17763996124268</t>
+    <t xml:space="preserve">2.1543083190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17764019966125</t>
   </si>
   <si>
     <t xml:space="preserve">2.22430396080017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35651779174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48873162269592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52761840820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43429112434387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44206809997559</t>
+    <t xml:space="preserve">2.35651803016663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4887318611145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52761816978455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43429064750671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44206786155701</t>
   </si>
   <si>
     <t xml:space="preserve">2.55872750282288</t>
@@ -434,16 +434,16 @@
     <t xml:space="preserve">2.44984531402588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37207221984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33318614959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29429984092712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37984943389893</t>
+    <t xml:space="preserve">2.37207245826721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33318591117859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29429960250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37984991073608</t>
   </si>
   <si>
     <t xml:space="preserve">2.71427321434021</t>
@@ -461,52 +461,52 @@
     <t xml:space="preserve">2.57428169250488</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67538666725159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64427733421326</t>
+    <t xml:space="preserve">2.67538690567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64427757263184</t>
   </si>
   <si>
     <t xml:space="preserve">2.69094133377075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76871395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90092802047729</t>
+    <t xml:space="preserve">2.76871418952942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90092754364014</t>
   </si>
   <si>
     <t xml:space="preserve">2.9631462097168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92426013946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97092366218567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01758742332458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04869627952576</t>
+    <t xml:space="preserve">2.92425990104675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97092342376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01758766174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04869604110718</t>
   </si>
   <si>
     <t xml:space="preserve">3.03314185142517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0642511844635</t>
+    <t xml:space="preserve">3.06425094604492</t>
   </si>
   <si>
     <t xml:space="preserve">3.07980561256409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06049919128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02811288833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01191997528076</t>
+    <t xml:space="preserve">3.0604989528656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0281126499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0119194984436</t>
   </si>
   <si>
     <t xml:space="preserve">3.1090784072876</t>
@@ -515,70 +515,70 @@
     <t xml:space="preserve">3.0928852558136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12527132034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07669234275818</t>
+    <t xml:space="preserve">3.1252715587616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0766921043396</t>
   </si>
   <si>
     <t xml:space="preserve">2.99572658538818</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30339574813843</t>
+    <t xml:space="preserve">3.30339598655701</t>
   </si>
   <si>
     <t xml:space="preserve">3.41674757003784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35197520256042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33578205108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36816811561584</t>
+    <t xml:space="preserve">3.35197472572327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33578157424927</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36816835403442</t>
   </si>
   <si>
     <t xml:space="preserve">3.23862338066101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31958913803101</t>
+    <t xml:space="preserve">3.31958866119385</t>
   </si>
   <si>
     <t xml:space="preserve">3.27100944519043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28720259666443</t>
+    <t xml:space="preserve">3.28720283508301</t>
   </si>
   <si>
     <t xml:space="preserve">3.22243022918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17385125160217</t>
+    <t xml:space="preserve">3.17385053634644</t>
   </si>
   <si>
     <t xml:space="preserve">3.20623707771301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1414647102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40055418014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49771332740784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38436150550842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25481677055359</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19004416465759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96334028244019</t>
+    <t xml:space="preserve">3.14146494865417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40055441856384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49771308898926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38436126708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25481653213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19004392623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96334052085876</t>
   </si>
   <si>
     <t xml:space="preserve">2.97953367233276</t>
@@ -590,13 +590,13 @@
     <t xml:space="preserve">2.88237476348877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86618185043335</t>
+    <t xml:space="preserve">2.86618137359619</t>
   </si>
   <si>
     <t xml:space="preserve">2.84998822212219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78521609306335</t>
+    <t xml:space="preserve">2.78521633148193</t>
   </si>
   <si>
     <t xml:space="preserve">2.75283002853394</t>
@@ -605,19 +605,19 @@
     <t xml:space="preserve">2.72044348716736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83379530906677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76902294158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73663711547852</t>
+    <t xml:space="preserve">2.83379554748535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76902318000793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73663663864136</t>
   </si>
   <si>
     <t xml:space="preserve">2.81760239601135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89856791496277</t>
+    <t xml:space="preserve">2.89856767654419</t>
   </si>
   <si>
     <t xml:space="preserve">2.91476082801819</t>
@@ -632,22 +632,22 @@
     <t xml:space="preserve">2.62328505516052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68805718421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70425057411194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60709166526794</t>
+    <t xml:space="preserve">2.68805694580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70425009727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60709190368652</t>
   </si>
   <si>
     <t xml:space="preserve">2.59089875221252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42896771430969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54231929779053</t>
+    <t xml:space="preserve">2.42896747589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54231905937195</t>
   </si>
   <si>
     <t xml:space="preserve">2.46135377883911</t>
@@ -656,10 +656,10 @@
     <t xml:space="preserve">2.3156156539917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2994225025177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35488152503967</t>
+    <t xml:space="preserve">2.29942274093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35488176345825</t>
   </si>
   <si>
     <t xml:space="preserve">2.40607476234436</t>
@@ -671,13 +671,13 @@
     <t xml:space="preserve">2.13304495811462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08185219764709</t>
+    <t xml:space="preserve">2.08185195922852</t>
   </si>
   <si>
     <t xml:space="preserve">2.06478762626648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03065872192383</t>
+    <t xml:space="preserve">2.03065896034241</t>
   </si>
   <si>
     <t xml:space="preserve">2.1671736240387</t>
@@ -692,16 +692,16 @@
     <t xml:space="preserve">2.21836686134338</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3207528591156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55965423583984</t>
+    <t xml:space="preserve">2.32075309753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55965399742126</t>
   </si>
   <si>
     <t xml:space="preserve">2.54258966445923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45726776123047</t>
+    <t xml:space="preserve">2.45726799964905</t>
   </si>
   <si>
     <t xml:space="preserve">2.5767183303833</t>
@@ -722,13 +722,13 @@
     <t xml:space="preserve">2.69616913795471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71323347091675</t>
+    <t xml:space="preserve">2.71323323249817</t>
   </si>
   <si>
     <t xml:space="preserve">2.44020342826843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4231390953064</t>
+    <t xml:space="preserve">2.42313933372498</t>
   </si>
   <si>
     <t xml:space="preserve">2.47433233261108</t>
@@ -737,16 +737,16 @@
     <t xml:space="preserve">2.15010929107666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33781743049622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30368876457214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25249576568604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23543095588684</t>
+    <t xml:space="preserve">2.33781719207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30368852615356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25249552726746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23543119430542</t>
   </si>
   <si>
     <t xml:space="preserve">2.37194609642029</t>
@@ -755,37 +755,37 @@
     <t xml:space="preserve">2.38901042938232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20130228996277</t>
+    <t xml:space="preserve">2.20130252838135</t>
   </si>
   <si>
     <t xml:space="preserve">2.18423795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01359438896179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04772353172302</t>
+    <t xml:space="preserve">2.01359415054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04772305488586</t>
   </si>
   <si>
     <t xml:space="preserve">2.11598062515259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.911208152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87707984447479</t>
+    <t xml:space="preserve">1.91120851039886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87707960605621</t>
   </si>
   <si>
     <t xml:space="preserve">1.84295094013214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97946572303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86001527309418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94533681869507</t>
+    <t xml:space="preserve">1.97946584224701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86001539230347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94533717632294</t>
   </si>
   <si>
     <t xml:space="preserve">1.96240139007568</t>
@@ -794,16 +794,16 @@
     <t xml:space="preserve">1.99653005599976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81561946868896</t>
+    <t xml:space="preserve">2.81561923027039</t>
   </si>
   <si>
     <t xml:space="preserve">2.90094137191772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88387727737427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76442646980286</t>
+    <t xml:space="preserve">2.88387680053711</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76442670822144</t>
   </si>
   <si>
     <t xml:space="preserve">2.73029780387878</t>
@@ -812,7 +812,7 @@
     <t xml:space="preserve">2.6791045665741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74736189842224</t>
+    <t xml:space="preserve">2.74736213684082</t>
   </si>
   <si>
     <t xml:space="preserve">2.83268356323242</t>
@@ -824,28 +824,28 @@
     <t xml:space="preserve">2.79855513572693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78149056434631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9350700378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96919870376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02039194107056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00332713127136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03745603561401</t>
+    <t xml:space="preserve">2.78149080276489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93507027626038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96919894218445</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02039170265198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00332736968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03745627403259</t>
   </si>
   <si>
     <t xml:space="preserve">2.98626303672791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05452060699463</t>
+    <t xml:space="preserve">3.05452036857605</t>
   </si>
   <si>
     <t xml:space="preserve">3.07158470153809</t>
@@ -854,10 +854,10 @@
     <t xml:space="preserve">3.13984251022339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11424589157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1313099861145</t>
+    <t xml:space="preserve">3.11424565315247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13131022453308</t>
   </si>
   <si>
     <t xml:space="preserve">3.06305241584778</t>
@@ -872,7 +872,7 @@
     <t xml:space="preserve">3.15690660476685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23369598388672</t>
+    <t xml:space="preserve">3.2336962223053</t>
   </si>
   <si>
     <t xml:space="preserve">3.27635717391968</t>
@@ -881,13 +881,13 @@
     <t xml:space="preserve">3.24222850799561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26782488822937</t>
+    <t xml:space="preserve">3.26782512664795</t>
   </si>
   <si>
     <t xml:space="preserve">3.31048607826233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34461498260498</t>
+    <t xml:space="preserve">3.34461450576782</t>
   </si>
   <si>
     <t xml:space="preserve">3.32755017280579</t>
@@ -896,25 +896,25 @@
     <t xml:space="preserve">3.28488922119141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18250322341919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29342126846313</t>
+    <t xml:space="preserve">3.18250298500061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29342150688171</t>
   </si>
   <si>
     <t xml:space="preserve">3.33710074424744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32836484909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29342150688171</t>
+    <t xml:space="preserve">3.32836508750916</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29342174530029</t>
   </si>
   <si>
     <t xml:space="preserve">3.24974226951599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20606279373169</t>
+    <t xml:space="preserve">3.20606303215027</t>
   </si>
   <si>
     <t xml:space="preserve">3.15364766120911</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">3.21479892730713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17111945152283</t>
+    <t xml:space="preserve">3.17111968994141</t>
   </si>
   <si>
     <t xml:space="preserve">3.26721382141113</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">3.36330842971802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49434661865234</t>
+    <t xml:space="preserve">3.49434638023376</t>
   </si>
   <si>
     <t xml:space="preserve">3.58170509338379</t>
@@ -941,40 +941,40 @@
     <t xml:space="preserve">3.56423330307007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59044122695923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.5030825138092</t>
+    <t xml:space="preserve">3.59044098854065</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.50308275222778</t>
   </si>
   <si>
     <t xml:space="preserve">3.51181840896606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54676175117493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63411998748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62538456916809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7476863861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69527125358582</t>
+    <t xml:space="preserve">3.54676151275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63412022590637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62538480758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74768662452698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69527149200439</t>
   </si>
   <si>
     <t xml:space="preserve">3.66906380653381</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60791301727295</t>
+    <t xml:space="preserve">3.60791277885437</t>
   </si>
   <si>
     <t xml:space="preserve">3.55549788475037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66032814979553</t>
+    <t xml:space="preserve">3.66032791137695</t>
   </si>
   <si>
     <t xml:space="preserve">3.65159201622009</t>
@@ -983,7 +983,7 @@
     <t xml:space="preserve">3.68653535842896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7040069103241</t>
+    <t xml:space="preserve">3.70400714874268</t>
   </si>
   <si>
     <t xml:space="preserve">3.75642251968384</t>
@@ -992,19 +992,19 @@
     <t xml:space="preserve">3.57296967506409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53802609443665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3458366394043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3895161151886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42445993423462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45066738128662</t>
+    <t xml:space="preserve">3.53802585601807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34583687782288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38951635360718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42445945739746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45066714286804</t>
   </si>
   <si>
     <t xml:space="preserve">3.44193148612976</t>
@@ -1013,10 +1013,10 @@
     <t xml:space="preserve">3.48561072349548</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4069881439209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35457229614258</t>
+    <t xml:space="preserve">3.40698790550232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35457253456116</t>
   </si>
   <si>
     <t xml:space="preserve">3.45940327644348</t>
@@ -1028,19 +1028,19 @@
     <t xml:space="preserve">3.46813893318176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47687482833862</t>
+    <t xml:space="preserve">3.47687458992004</t>
   </si>
   <si>
     <t xml:space="preserve">3.79136610031128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72147941589355</t>
+    <t xml:space="preserve">3.7214789390564</t>
   </si>
   <si>
     <t xml:space="preserve">3.87872457504272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17574405670166</t>
+    <t xml:space="preserve">4.17574453353882</t>
   </si>
   <si>
     <t xml:space="preserve">4.31551790237427</t>
@@ -1049,19 +1049,19 @@
     <t xml:space="preserve">4.35046148300171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18447971343994</t>
+    <t xml:space="preserve">4.1844801902771</t>
   </si>
   <si>
     <t xml:space="preserve">4.20195150375366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25436687469482</t>
+    <t xml:space="preserve">4.25436639785767</t>
   </si>
   <si>
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493226051331</t>
+    <t xml:space="preserve">3.90493178367615</t>
   </si>
   <si>
     <t xml:space="preserve">3.98355507850647</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">3.93113970756531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08838558197021</t>
+    <t xml:space="preserve">4.08838510513306</t>
   </si>
   <si>
     <t xml:space="preserve">4.07091379165649</t>
@@ -1085,16 +1085,16 @@
     <t xml:space="preserve">4.00102663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00976324081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93987584114075</t>
+    <t xml:space="preserve">4.00976228713989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93987607955933</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2106876373291</t>
+    <t xml:space="preserve">4.21068716049194</t>
   </si>
   <si>
     <t xml:space="preserve">4.29804611206055</t>
@@ -1103,16 +1103,16 @@
     <t xml:space="preserve">4.28930997848511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21942329406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19321632385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14953660964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16700792312622</t>
+    <t xml:space="preserve">4.21942377090454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19321584701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1495361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16700839996338</t>
   </si>
   <si>
     <t xml:space="preserve">4.11459302902222</t>
@@ -1124,40 +1124,40 @@
     <t xml:space="preserve">3.78262996673584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80010175704956</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8263099193573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83504557609558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84378147125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77389454841614</t>
+    <t xml:space="preserve">3.80010151863098</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82630968093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83504486083984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84378123283386</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77389430999756</t>
   </si>
   <si>
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734786987305</t>
+    <t xml:space="preserve">3.95734763145447</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86125302314758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76515793800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81757354736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64285612106323</t>
+    <t xml:space="preserve">3.861252784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7651584148407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8175733089447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64285635948181</t>
   </si>
   <si>
     <t xml:space="preserve">3.67779970169067</t>
@@ -1172,49 +1172,49 @@
     <t xml:space="preserve">3.71274328231812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92240381240845</t>
+    <t xml:space="preserve">3.92240357398987</t>
   </si>
   <si>
     <t xml:space="preserve">3.61664843559265</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39825201034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23227047920227</t>
+    <t xml:space="preserve">3.39825224876404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23227071762085</t>
   </si>
   <si>
     <t xml:space="preserve">3.0575532913208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97019481658936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95272302627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91777944564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90904355049133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3720440864563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38078022003174</t>
+    <t xml:space="preserve">2.97019457817078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95272278785706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91777920722961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90904331207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37204432487488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38077998161316</t>
   </si>
   <si>
     <t xml:space="preserve">3.41572380065918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31962895393372</t>
+    <t xml:space="preserve">3.31962919235229</t>
   </si>
   <si>
     <t xml:space="preserve">3.27594995498657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28468561172485</t>
+    <t xml:space="preserve">3.28468585014343</t>
   </si>
   <si>
     <t xml:space="preserve">3.50245499610901</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">3.32098078727722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26653814315796</t>
+    <t xml:space="preserve">3.26653838157654</t>
   </si>
   <si>
     <t xml:space="preserve">3.39357042312622</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">3.23024344444275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19394874572754</t>
+    <t xml:space="preserve">3.19394850730896</t>
   </si>
   <si>
     <t xml:space="preserve">3.25746440887451</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">3.2211697101593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10321140289307</t>
+    <t xml:space="preserve">3.10321164131165</t>
   </si>
   <si>
     <t xml:space="preserve">2.99432682991028</t>
@@ -1286,13 +1286,13 @@
     <t xml:space="preserve">2.95803189277649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85822105407715</t>
+    <t xml:space="preserve">2.85822129249573</t>
   </si>
   <si>
     <t xml:space="preserve">2.89451599121094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8672947883606</t>
+    <t xml:space="preserve">2.86729502677917</t>
   </si>
   <si>
     <t xml:space="preserve">2.81285238265991</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">2.75841021537781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70396780967712</t>
+    <t xml:space="preserve">2.7039680480957</t>
   </si>
   <si>
     <t xml:space="preserve">2.72211527824402</t>
@@ -1313,16 +1313,16 @@
     <t xml:space="preserve">2.64952564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7947051525116</t>
+    <t xml:space="preserve">2.79470491409302</t>
   </si>
   <si>
     <t xml:space="preserve">2.92173719406128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05784273147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02154803276062</t>
+    <t xml:space="preserve">3.05784296989441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02154779434204</t>
   </si>
   <si>
     <t xml:space="preserve">3.13950634002686</t>
@@ -1352,46 +1352,46 @@
     <t xml:space="preserve">3.08506417274475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01247429847717</t>
+    <t xml:space="preserve">3.01247406005859</t>
   </si>
   <si>
     <t xml:space="preserve">2.88544225692749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7765576839447</t>
+    <t xml:space="preserve">2.77655744552612</t>
   </si>
   <si>
     <t xml:space="preserve">2.71304154396057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6313784122467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68582034111023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66767287254333</t>
+    <t xml:space="preserve">2.63137817382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68582057952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66767311096191</t>
   </si>
   <si>
     <t xml:space="preserve">2.55878829956055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52249336242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67674660682678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64045214653015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87636852264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83099985122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60415697097778</t>
+    <t xml:space="preserve">2.52249360084534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67674684524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64045190811157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87636876106262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83099961280823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6041567325592</t>
   </si>
   <si>
     <t xml:space="preserve">2.73118901252747</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">2.91266345977783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12135887145996</t>
+    <t xml:space="preserve">3.12135910987854</t>
   </si>
   <si>
     <t xml:space="preserve">3.0759904384613</t>
@@ -1427,46 +1427,46 @@
     <t xml:space="preserve">3.0941379070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38449692726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41171765327454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37542319297791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42079138755798</t>
+    <t xml:space="preserve">3.38449668884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41171789169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37542295455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42079162597656</t>
   </si>
   <si>
     <t xml:space="preserve">3.43893885612488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36634945869446</t>
+    <t xml:space="preserve">3.36634922027588</t>
   </si>
   <si>
     <t xml:space="preserve">3.35727572441101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20302248001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27561187744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29375958442688</t>
+    <t xml:space="preserve">3.20302224159241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27561211585999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29375982284546</t>
   </si>
   <si>
     <t xml:space="preserve">3.1667275428772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11228513717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78563141822815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84007382392883</t>
+    <t xml:space="preserve">3.11228537559509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78563117980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84007358551025</t>
   </si>
   <si>
     <t xml:space="preserve">2.82192611694336</t>
@@ -56772,7 +56772,7 @@
     </row>
     <row r="2103">
       <c r="A2103" s="1" t="n">
-        <v>46030.69125</v>
+        <v>46030.3333333333</v>
       </c>
       <c r="B2103" t="n">
         <v>45307</v>
@@ -56793,6 +56793,32 @@
         <v>589</v>
       </c>
       <c r="H2103" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2104">
+      <c r="A2104" s="1" t="n">
+        <v>46031.6912152778</v>
+      </c>
+      <c r="B2104" t="n">
+        <v>30435</v>
+      </c>
+      <c r="C2104" t="n">
+        <v>3.85999989509583</v>
+      </c>
+      <c r="D2104" t="n">
+        <v>3.79999995231628</v>
+      </c>
+      <c r="E2104" t="n">
+        <v>3.83999991416931</v>
+      </c>
+      <c r="F2104" t="n">
+        <v>3.85999989509583</v>
+      </c>
+      <c r="G2104" t="s">
+        <v>586</v>
+      </c>
+      <c r="H2104" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -44,46 +44,46 @@
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519923210144</t>
+    <t xml:space="preserve">2.96519947052002</t>
   </si>
   <si>
     <t xml:space="preserve">2.88901543617249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98013734817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97266817092896</t>
+    <t xml:space="preserve">2.98013710975647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97266864776611</t>
   </si>
   <si>
     <t xml:space="preserve">2.94577980041504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9577305316925</t>
+    <t xml:space="preserve">2.95773029327393</t>
   </si>
   <si>
     <t xml:space="preserve">2.9622118473053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9353232383728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91291642189026</t>
+    <t xml:space="preserve">2.93532347679138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91291618347168</t>
   </si>
   <si>
     <t xml:space="preserve">2.97864365577698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98611235618591</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03540802001953</t>
+    <t xml:space="preserve">2.98611283302307</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03540778160095</t>
   </si>
   <si>
     <t xml:space="preserve">3.056321144104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0593090057373</t>
+    <t xml:space="preserve">3.05930948257446</t>
   </si>
   <si>
     <t xml:space="preserve">3.05034613609314</t>
@@ -95,19 +95,19 @@
     <t xml:space="preserve">2.95026135444641</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01598882675171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01001358032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02495169639587</t>
+    <t xml:space="preserve">3.01598858833313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01001334190369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02495121955872</t>
   </si>
   <si>
     <t xml:space="preserve">3.01748251914978</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03092670440674</t>
+    <t xml:space="preserve">3.03092646598816</t>
   </si>
   <si>
     <t xml:space="preserve">2.99955677986145</t>
@@ -122,28 +122,28 @@
     <t xml:space="preserve">3.00254440307617</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92785429954529</t>
+    <t xml:space="preserve">2.92785406112671</t>
   </si>
   <si>
     <t xml:space="preserve">2.90843486785889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89648461341858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91889119148254</t>
+    <t xml:space="preserve">2.896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91889142990112</t>
   </si>
   <si>
     <t xml:space="preserve">2.9159038066864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92038512229919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90544700622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90992856025696</t>
+    <t xml:space="preserve">2.92038536071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90544724464417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90992879867554</t>
   </si>
   <si>
     <t xml:space="preserve">2.9233729839325</t>
@@ -152,13 +152,13 @@
     <t xml:space="preserve">2.8382260799408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8606333732605</t>
+    <t xml:space="preserve">2.86063313484192</t>
   </si>
   <si>
     <t xml:space="preserve">2.82627558708191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77996778488159</t>
+    <t xml:space="preserve">2.77996754646301</t>
   </si>
   <si>
     <t xml:space="preserve">2.84569501876831</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">2.86810207366943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88303995132446</t>
+    <t xml:space="preserve">2.88303971290588</t>
   </si>
   <si>
     <t xml:space="preserve">2.79639935493469</t>
@@ -176,43 +176,43 @@
     <t xml:space="preserve">2.87557101249695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89797830581665</t>
+    <t xml:space="preserve">2.89797806739807</t>
   </si>
   <si>
     <t xml:space="preserve">2.80088090896606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74262237548828</t>
+    <t xml:space="preserve">2.74262261390686</t>
   </si>
   <si>
     <t xml:space="preserve">2.82179427146912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75009155273438</t>
+    <t xml:space="preserve">2.75009179115295</t>
   </si>
   <si>
     <t xml:space="preserve">2.76353597640991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77847385406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78594303131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79341220855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69631481170654</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6515007019043</t>
+    <t xml:space="preserve">2.77847409248352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78594279289246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79341197013855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69631457328796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65150046348572</t>
   </si>
   <si>
     <t xml:space="preserve">2.62162446975708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5394651889801</t>
+    <t xml:space="preserve">2.53946566581726</t>
   </si>
   <si>
     <t xml:space="preserve">2.5693416595459</t>
@@ -239,10 +239,10 @@
     <t xml:space="preserve">2.7336597442627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66643905639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68137669563293</t>
+    <t xml:space="preserve">2.66643881797791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68137645721436</t>
   </si>
   <si>
     <t xml:space="preserve">2.74112868309021</t>
@@ -251,13 +251,13 @@
     <t xml:space="preserve">2.7261905670166</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83075714111328</t>
+    <t xml:space="preserve">2.8307569026947</t>
   </si>
   <si>
     <t xml:space="preserve">2.89315056800842</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69871878623962</t>
+    <t xml:space="preserve">2.69871854782104</t>
   </si>
   <si>
     <t xml:space="preserve">2.83870959281921</t>
@@ -272,61 +272,61 @@
     <t xml:space="preserve">2.8309326171875</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81537795066833</t>
+    <t xml:space="preserve">2.81537771224976</t>
   </si>
   <si>
     <t xml:space="preserve">2.84648704528809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79982304573059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73760461807251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76093697547913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80760049819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00980997085571</t>
+    <t xml:space="preserve">2.79982328414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73760509490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76093649864197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80760025978088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00980973243713</t>
   </si>
   <si>
     <t xml:space="preserve">2.9553689956665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90870499610901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88537335395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82315540313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86204171180725</t>
+    <t xml:space="preserve">2.90870523452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88537359237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82315516471863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86204147338867</t>
   </si>
   <si>
     <t xml:space="preserve">3.00203275680542</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9164822101593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85426449775696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72982740402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68316411972046</t>
+    <t xml:space="preserve">2.91648244857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85426425933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7298276424408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68316388130188</t>
   </si>
   <si>
     <t xml:space="preserve">2.7220504283905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75315928459167</t>
+    <t xml:space="preserve">2.75315952301025</t>
   </si>
   <si>
     <t xml:space="preserve">2.70649576187134</t>
@@ -335,25 +335,25 @@
     <t xml:space="preserve">2.93981432914734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99425530433655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97870087623596</t>
+    <t xml:space="preserve">2.99425506591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97870063781738</t>
   </si>
   <si>
     <t xml:space="preserve">2.86981892585754</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94759178161621</t>
+    <t xml:space="preserve">2.94759154319763</t>
   </si>
   <si>
     <t xml:space="preserve">2.98647809028625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63650035858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55095028877258</t>
+    <t xml:space="preserve">2.63650012016296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.550950050354</t>
   </si>
   <si>
     <t xml:space="preserve">2.51984095573425</t>
@@ -368,43 +368,43 @@
     <t xml:space="preserve">2.34874057769775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36429524421692</t>
+    <t xml:space="preserve">2.36429500579834</t>
   </si>
   <si>
     <t xml:space="preserve">2.2554132938385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24763631820679</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32540845870972</t>
+    <t xml:space="preserve">2.24763584136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32540893554688</t>
   </si>
   <si>
     <t xml:space="preserve">2.23208117485046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18541765213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2787446975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26319026947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21652674674988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06875824928284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1465311050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10764455795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1543083190918</t>
+    <t xml:space="preserve">2.18541741371155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27874517440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26319050788879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2165265083313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06875848770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14653134346008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10764479637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15430855751038</t>
   </si>
   <si>
     <t xml:space="preserve">2.17764019966125</t>
@@ -413,19 +413,19 @@
     <t xml:space="preserve">2.22430396080017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35651803016663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4887318611145</t>
+    <t xml:space="preserve">2.35651779174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48873162269592</t>
   </si>
   <si>
     <t xml:space="preserve">2.52761816978455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43429064750671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44206786155701</t>
+    <t xml:space="preserve">2.43429088592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44206809997559</t>
   </si>
   <si>
     <t xml:space="preserve">2.55872750282288</t>
@@ -437,28 +437,28 @@
     <t xml:space="preserve">2.37207245826721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33318591117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29429960250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37984991073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71427321434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58205890655518</t>
+    <t xml:space="preserve">2.33318614959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29429984092712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3798496723175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71427297592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58205914497375</t>
   </si>
   <si>
     <t xml:space="preserve">2.62872290611267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.659832239151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57428169250488</t>
+    <t xml:space="preserve">2.65983247756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57428193092346</t>
   </si>
   <si>
     <t xml:space="preserve">2.67538690567017</t>
@@ -467,46 +467,46 @@
     <t xml:space="preserve">2.64427757263184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69094133377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76871418952942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90092754364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9631462097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92425990104675</t>
+    <t xml:space="preserve">2.69094157218933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76871395111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90092778205872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96314644813538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92426013946533</t>
   </si>
   <si>
     <t xml:space="preserve">2.97092342376709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01758766174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04869604110718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03314185142517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06425094604492</t>
+    <t xml:space="preserve">3.01758718490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04869651794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03314161300659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0642511844635</t>
   </si>
   <si>
     <t xml:space="preserve">3.07980561256409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0604989528656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0281126499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0119194984436</t>
+    <t xml:space="preserve">3.06049919128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02811288833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01191973686218</t>
   </si>
   <si>
     <t xml:space="preserve">3.1090784072876</t>
@@ -524,16 +524,16 @@
     <t xml:space="preserve">2.99572658538818</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30339598655701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41674757003784</t>
+    <t xml:space="preserve">3.30339574813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41674733161926</t>
   </si>
   <si>
     <t xml:space="preserve">3.35197472572327</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33578157424927</t>
+    <t xml:space="preserve">3.33578181266785</t>
   </si>
   <si>
     <t xml:space="preserve">3.36816835403442</t>
@@ -542,25 +542,25 @@
     <t xml:space="preserve">3.23862338066101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31958866119385</t>
+    <t xml:space="preserve">3.31958889961243</t>
   </si>
   <si>
     <t xml:space="preserve">3.27100944519043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28720283508301</t>
+    <t xml:space="preserve">3.28720259666443</t>
   </si>
   <si>
     <t xml:space="preserve">3.22243022918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17385053634644</t>
+    <t xml:space="preserve">3.17385077476501</t>
   </si>
   <si>
     <t xml:space="preserve">3.20623707771301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14146494865417</t>
+    <t xml:space="preserve">3.1414647102356</t>
   </si>
   <si>
     <t xml:space="preserve">3.40055441856384</t>
@@ -572,7 +572,7 @@
     <t xml:space="preserve">3.38436126708984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25481653213501</t>
+    <t xml:space="preserve">3.25481629371643</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004392623901</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">2.96334052085876</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97953367233276</t>
+    <t xml:space="preserve">2.97953343391418</t>
   </si>
   <si>
     <t xml:space="preserve">2.80140924453735</t>
@@ -590,13 +590,13 @@
     <t xml:space="preserve">2.88237476348877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86618137359619</t>
+    <t xml:space="preserve">2.86618161201477</t>
   </si>
   <si>
     <t xml:space="preserve">2.84998822212219</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78521633148193</t>
+    <t xml:space="preserve">2.78521609306335</t>
   </si>
   <si>
     <t xml:space="preserve">2.75283002853394</t>
@@ -611,13 +611,13 @@
     <t xml:space="preserve">2.76902318000793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73663663864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81760239601135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89856767654419</t>
+    <t xml:space="preserve">2.73663687705994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81760215759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89856791496277</t>
   </si>
   <si>
     <t xml:space="preserve">2.91476082801819</t>
@@ -629,13 +629,13 @@
     <t xml:space="preserve">2.67186427116394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62328505516052</t>
+    <t xml:space="preserve">2.62328481674194</t>
   </si>
   <si>
     <t xml:space="preserve">2.68805694580078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70425009727478</t>
+    <t xml:space="preserve">2.70425033569336</t>
   </si>
   <si>
     <t xml:space="preserve">2.60709190368652</t>
@@ -650,7 +650,7 @@
     <t xml:space="preserve">2.54231905937195</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46135377883911</t>
+    <t xml:space="preserve">2.46135354042053</t>
   </si>
   <si>
     <t xml:space="preserve">2.3156156539917</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">2.06478762626648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03065896034241</t>
+    <t xml:space="preserve">2.03065872192383</t>
   </si>
   <si>
     <t xml:space="preserve">2.1671736240387</t>
@@ -707,7 +707,7 @@
     <t xml:space="preserve">2.5767183303833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62791156768799</t>
+    <t xml:space="preserve">2.62791132926941</t>
   </si>
   <si>
     <t xml:space="preserve">2.61084699630737</t>
@@ -716,13 +716,13 @@
     <t xml:space="preserve">2.64497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59378290176392</t>
+    <t xml:space="preserve">2.59378266334534</t>
   </si>
   <si>
     <t xml:space="preserve">2.69616913795471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71323323249817</t>
+    <t xml:space="preserve">2.71323347091675</t>
   </si>
   <si>
     <t xml:space="preserve">2.44020342826843</t>
@@ -764,7 +764,7 @@
     <t xml:space="preserve">2.01359415054321</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04772305488586</t>
+    <t xml:space="preserve">2.04772329330444</t>
   </si>
   <si>
     <t xml:space="preserve">2.11598062515259</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">1.91120851039886</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87707960605621</t>
+    <t xml:space="preserve">1.87707984447479</t>
   </si>
   <si>
     <t xml:space="preserve">1.84295094013214</t>
@@ -782,7 +782,7 @@
     <t xml:space="preserve">1.97946584224701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86001539230347</t>
+    <t xml:space="preserve">1.86001515388489</t>
   </si>
   <si>
     <t xml:space="preserve">1.94533717632294</t>
@@ -800,10 +800,10 @@
     <t xml:space="preserve">2.90094137191772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88387680053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76442670822144</t>
+    <t xml:space="preserve">2.88387703895569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76442646980286</t>
   </si>
   <si>
     <t xml:space="preserve">2.73029780387878</t>
@@ -821,19 +821,19 @@
     <t xml:space="preserve">2.86681246757507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79855513572693</t>
+    <t xml:space="preserve">2.79855489730835</t>
   </si>
   <si>
     <t xml:space="preserve">2.78149080276489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93507027626038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96919894218445</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02039170265198</t>
+    <t xml:space="preserve">2.9350700378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96919870376587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02039194107056</t>
   </si>
   <si>
     <t xml:space="preserve">3.00332736968994</t>
@@ -851,13 +851,13 @@
     <t xml:space="preserve">3.07158470153809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13984251022339</t>
+    <t xml:space="preserve">3.13984227180481</t>
   </si>
   <si>
     <t xml:space="preserve">3.11424565315247</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13131022453308</t>
+    <t xml:space="preserve">3.1313099861145</t>
   </si>
   <si>
     <t xml:space="preserve">3.06305241584778</t>
@@ -881,13 +881,13 @@
     <t xml:space="preserve">3.24222850799561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26782512664795</t>
+    <t xml:space="preserve">3.26782488822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.31048607826233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34461450576782</t>
+    <t xml:space="preserve">3.3446147441864</t>
   </si>
   <si>
     <t xml:space="preserve">3.32755017280579</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">3.28488922119141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18250298500061</t>
+    <t xml:space="preserve">3.18250322341919</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342150688171</t>
@@ -56798,7 +56798,7 @@
     </row>
     <row r="2104">
       <c r="A2104" s="1" t="n">
-        <v>46031.6912152778</v>
+        <v>46031.3333333333</v>
       </c>
       <c r="B2104" t="n">
         <v>30435</v>
@@ -56819,6 +56819,32 @@
         <v>586</v>
       </c>
       <c r="H2104" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2105">
+      <c r="A2105" s="1" t="n">
+        <v>46034.6912384259</v>
+      </c>
+      <c r="B2105" t="n">
+        <v>8037</v>
+      </c>
+      <c r="C2105" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="D2105" t="n">
+        <v>3.77999997138977</v>
+      </c>
+      <c r="E2105" t="n">
+        <v>3.90000009536743</v>
+      </c>
+      <c r="F2105" t="n">
+        <v>3.85999989509583</v>
+      </c>
+      <c r="G2105" t="s">
+        <v>586</v>
+      </c>
+      <c r="H2105" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="589" uniqueCount="589">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="590" uniqueCount="590">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,13 +44,13 @@
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519899368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88901519775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98013710975647</t>
+    <t xml:space="preserve">2.96519947052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88901543617249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98013734817505</t>
   </si>
   <si>
     <t xml:space="preserve">2.97266817092896</t>
@@ -80,13 +80,13 @@
     <t xml:space="preserve">3.03540825843811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.056321144104</t>
+    <t xml:space="preserve">3.05632138252258</t>
   </si>
   <si>
     <t xml:space="preserve">3.0593090057373</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05034589767456</t>
+    <t xml:space="preserve">3.05034637451172</t>
   </si>
   <si>
     <t xml:space="preserve">2.98760604858398</t>
@@ -95,34 +95,34 @@
     <t xml:space="preserve">2.95026135444641</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01598858833313</t>
+    <t xml:space="preserve">3.01598834991455</t>
   </si>
   <si>
     <t xml:space="preserve">3.01001358032227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02495145797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0174822807312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03092670440674</t>
+    <t xml:space="preserve">3.02495169639587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01748251914978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03092646598816</t>
   </si>
   <si>
     <t xml:space="preserve">2.99955677986145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04437112808228</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95922422409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00254416465759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92785429954529</t>
+    <t xml:space="preserve">3.0443708896637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.959223985672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00254440307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92785406112671</t>
   </si>
   <si>
     <t xml:space="preserve">2.90843486785889</t>
@@ -140,13 +140,13 @@
     <t xml:space="preserve">2.92038512229919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90544700622559</t>
+    <t xml:space="preserve">2.90544748306274</t>
   </si>
   <si>
     <t xml:space="preserve">2.90992832183838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9233729839325</t>
+    <t xml:space="preserve">2.92337274551392</t>
   </si>
   <si>
     <t xml:space="preserve">2.83822584152222</t>
@@ -155,7 +155,7 @@
     <t xml:space="preserve">2.86063313484192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82627558708191</t>
+    <t xml:space="preserve">2.82627582550049</t>
   </si>
   <si>
     <t xml:space="preserve">2.77996754646301</t>
@@ -170,25 +170,25 @@
     <t xml:space="preserve">2.88303995132446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79639935493469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87557125091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89797806739807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80088090896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74262237548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82179427146912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75009155273438</t>
+    <t xml:space="preserve">2.79639959335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87557101249695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89797854423523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80088138580322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74262261390686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8217945098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75009179115295</t>
   </si>
   <si>
     <t xml:space="preserve">2.76353597640991</t>
@@ -197,13 +197,13 @@
     <t xml:space="preserve">2.77847409248352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78594279289246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79341220855713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69631481170654</t>
+    <t xml:space="preserve">2.78594303131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79341197013855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69631457328796</t>
   </si>
   <si>
     <t xml:space="preserve">2.6515007019043</t>
@@ -212,10 +212,10 @@
     <t xml:space="preserve">2.62162446975708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53946542739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5693416595459</t>
+    <t xml:space="preserve">2.53946566581726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56934142112732</t>
   </si>
   <si>
     <t xml:space="preserve">2.61415553092957</t>
@@ -224,22 +224,22 @@
     <t xml:space="preserve">2.65896964073181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68884587287903</t>
+    <t xml:space="preserve">2.68884539604187</t>
   </si>
   <si>
     <t xml:space="preserve">2.70378351211548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77100491523743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81581902503967</t>
+    <t xml:space="preserve">2.77100515365601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81581878662109</t>
   </si>
   <si>
     <t xml:space="preserve">2.73365998268127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66643857955933</t>
+    <t xml:space="preserve">2.66643905639648</t>
   </si>
   <si>
     <t xml:space="preserve">2.68137669563293</t>
@@ -263,34 +263,34 @@
     <t xml:space="preserve">2.83870959281921</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93203711509705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87759613990784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83093214035034</t>
+    <t xml:space="preserve">2.93203687667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87759637832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83093237876892</t>
   </si>
   <si>
     <t xml:space="preserve">2.81537747383118</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84648704528809</t>
+    <t xml:space="preserve">2.84648680686951</t>
   </si>
   <si>
     <t xml:space="preserve">2.79982328414917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73760509490967</t>
+    <t xml:space="preserve">2.73760485649109</t>
   </si>
   <si>
     <t xml:space="preserve">2.76093673706055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80760049819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00980997085571</t>
+    <t xml:space="preserve">2.80760025978088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00980973243713</t>
   </si>
   <si>
     <t xml:space="preserve">2.95536875724792</t>
@@ -302,37 +302,37 @@
     <t xml:space="preserve">2.88537335395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82315516471863</t>
+    <t xml:space="preserve">2.82315492630005</t>
   </si>
   <si>
     <t xml:space="preserve">2.86204171180725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00203251838684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91648244857788</t>
+    <t xml:space="preserve">3.00203275680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91648268699646</t>
   </si>
   <si>
     <t xml:space="preserve">2.85426425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7298276424408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68316411972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7220504283905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75315928459167</t>
+    <t xml:space="preserve">2.72982788085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68316388130188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72205018997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75315952301025</t>
   </si>
   <si>
     <t xml:space="preserve">2.70649576187134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93981432914734</t>
+    <t xml:space="preserve">2.93981409072876</t>
   </si>
   <si>
     <t xml:space="preserve">2.99425554275513</t>
@@ -347,34 +347,34 @@
     <t xml:space="preserve">2.94759178161621</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98647809028625</t>
+    <t xml:space="preserve">2.98647785186768</t>
   </si>
   <si>
     <t xml:space="preserve">2.63650035858154</t>
   </si>
   <si>
-    <t xml:space="preserve">2.550950050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51984095573425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41095900535583</t>
+    <t xml:space="preserve">2.55094981193542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51984119415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41095876693726</t>
   </si>
   <si>
     <t xml:space="preserve">2.34096336364746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34874081611633</t>
+    <t xml:space="preserve">2.34874057769775</t>
   </si>
   <si>
     <t xml:space="preserve">2.36429500579834</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2554132938385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24763607978821</t>
+    <t xml:space="preserve">2.25541353225708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24763584136963</t>
   </si>
   <si>
     <t xml:space="preserve">2.3254086971283</t>
@@ -392,28 +392,28 @@
     <t xml:space="preserve">2.26319050788879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21652674674988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06875824928284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14653134346008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10764455795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1543083190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17764019966125</t>
+    <t xml:space="preserve">2.2165265083313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06875848770142</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14653086662292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10764479637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15430855751038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17764043807983</t>
   </si>
   <si>
     <t xml:space="preserve">2.22430396080017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35651755332947</t>
+    <t xml:space="preserve">2.35651779174805</t>
   </si>
   <si>
     <t xml:space="preserve">2.4887318611145</t>
@@ -422,16 +422,16 @@
     <t xml:space="preserve">2.52761816978455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43429112434387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44206786155701</t>
+    <t xml:space="preserve">2.43429088592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44206833839417</t>
   </si>
   <si>
     <t xml:space="preserve">2.5587272644043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44984555244446</t>
+    <t xml:space="preserve">2.44984531402588</t>
   </si>
   <si>
     <t xml:space="preserve">2.37207245826721</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">2.33318591117859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29429936408997</t>
+    <t xml:space="preserve">2.29429960250854</t>
   </si>
   <si>
     <t xml:space="preserve">2.37984991073608</t>
@@ -452,40 +452,40 @@
     <t xml:space="preserve">2.58205890655518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62872266769409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65983247756958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57428193092346</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67538690567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64427757263184</t>
+    <t xml:space="preserve">2.62872314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.659832239151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57428169250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67538642883301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64427781105042</t>
   </si>
   <si>
     <t xml:space="preserve">2.69094109535217</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76871395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90092778205872</t>
+    <t xml:space="preserve">2.76871418952942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90092802047729</t>
   </si>
   <si>
     <t xml:space="preserve">2.9631462097168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92426013946533</t>
+    <t xml:space="preserve">2.92425966262817</t>
   </si>
   <si>
     <t xml:space="preserve">2.97092342376709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01758718490601</t>
+    <t xml:space="preserve">3.01758742332458</t>
   </si>
   <si>
     <t xml:space="preserve">3.04869651794434</t>
@@ -500,7 +500,7 @@
     <t xml:space="preserve">3.07980537414551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0604989528656</t>
+    <t xml:space="preserve">3.06049871444702</t>
   </si>
   <si>
     <t xml:space="preserve">3.02811288833618</t>
@@ -515,25 +515,25 @@
     <t xml:space="preserve">3.0928852558136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12527132034302</t>
+    <t xml:space="preserve">3.1252715587616</t>
   </si>
   <si>
     <t xml:space="preserve">3.07669186592102</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99572658538818</t>
+    <t xml:space="preserve">2.99572682380676</t>
   </si>
   <si>
     <t xml:space="preserve">3.30339574813843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41674733161926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.351975440979</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33578205108643</t>
+    <t xml:space="preserve">3.41674757003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35197520256042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33578181266785</t>
   </si>
   <si>
     <t xml:space="preserve">3.36816835403442</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">3.31958866119385</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27100944519043</t>
+    <t xml:space="preserve">3.27100968360901</t>
   </si>
   <si>
     <t xml:space="preserve">3.28720259666443</t>
@@ -554,40 +554,40 @@
     <t xml:space="preserve">3.22243022918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17385101318359</t>
+    <t xml:space="preserve">3.17385077476501</t>
   </si>
   <si>
     <t xml:space="preserve">3.20623707771301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1414647102356</t>
+    <t xml:space="preserve">3.14146494865417</t>
   </si>
   <si>
     <t xml:space="preserve">3.40055418014526</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49771308898926</t>
+    <t xml:space="preserve">3.49771332740784</t>
   </si>
   <si>
     <t xml:space="preserve">3.38436126708984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25481629371643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19004416465759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96334052085876</t>
+    <t xml:space="preserve">3.25481653213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19004392623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96334028244019</t>
   </si>
   <si>
     <t xml:space="preserve">2.97953367233276</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80140924453735</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88237452507019</t>
+    <t xml:space="preserve">2.80140900611877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88237476348877</t>
   </si>
   <si>
     <t xml:space="preserve">2.86618161201477</t>
@@ -596,40 +596,40 @@
     <t xml:space="preserve">2.84998846054077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78521633148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75282979011536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72044348716736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83379554748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76902341842651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73663663864136</t>
+    <t xml:space="preserve">2.78521609306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75283002853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72044372558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83379530906677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76902318000793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73663687705994</t>
   </si>
   <si>
     <t xml:space="preserve">2.81760239601135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89856767654419</t>
+    <t xml:space="preserve">2.89856791496277</t>
   </si>
   <si>
     <t xml:space="preserve">2.91476082801819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63947796821594</t>
+    <t xml:space="preserve">2.63947772979736</t>
   </si>
   <si>
     <t xml:space="preserve">2.67186403274536</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62328481674194</t>
+    <t xml:space="preserve">2.62328505516052</t>
   </si>
   <si>
     <t xml:space="preserve">2.68805718421936</t>
@@ -647,7 +647,7 @@
     <t xml:space="preserve">2.42896723747253</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54231929779053</t>
+    <t xml:space="preserve">2.54231953620911</t>
   </si>
   <si>
     <t xml:space="preserve">2.46135354042053</t>
@@ -1779,6 +1779,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.79999995231628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72000002861023</t>
   </si>
 </sst>
 </file>
@@ -56899,7 +56902,7 @@
     </row>
     <row r="2108">
       <c r="A2108" s="1" t="n">
-        <v>46037.6562615741</v>
+        <v>46037.3333333333</v>
       </c>
       <c r="B2108" t="n">
         <v>10180</v>
@@ -56920,6 +56923,32 @@
         <v>580</v>
       </c>
       <c r="H2108" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2109">
+      <c r="A2109" s="1" t="n">
+        <v>46038.6910763889</v>
+      </c>
+      <c r="B2109" t="n">
+        <v>20045</v>
+      </c>
+      <c r="C2109" t="n">
+        <v>3.79999995231628</v>
+      </c>
+      <c r="D2109" t="n">
+        <v>3.72000002861023</v>
+      </c>
+      <c r="E2109" t="n">
+        <v>3.79999995231628</v>
+      </c>
+      <c r="F2109" t="n">
+        <v>3.72000002861023</v>
+      </c>
+      <c r="G2109" t="s">
+        <v>589</v>
+      </c>
+      <c r="H2109" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="592" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="593" uniqueCount="593">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -44,16 +44,16 @@
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519923210144</t>
+    <t xml:space="preserve">2.96519899368286</t>
   </si>
   <si>
     <t xml:space="preserve">2.88901543617249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98013734817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97266840934753</t>
+    <t xml:space="preserve">2.98013758659363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97266817092896</t>
   </si>
   <si>
     <t xml:space="preserve">2.94578003883362</t>
@@ -68,10 +68,10 @@
     <t xml:space="preserve">2.9353232383728</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91291618347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97864389419556</t>
+    <t xml:space="preserve">2.91291642189026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97864365577698</t>
   </si>
   <si>
     <t xml:space="preserve">2.98611235618591</t>
@@ -80,7 +80,7 @@
     <t xml:space="preserve">3.03540802001953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.056321144104</t>
+    <t xml:space="preserve">3.05632138252258</t>
   </si>
   <si>
     <t xml:space="preserve">3.05930876731873</t>
@@ -89,46 +89,46 @@
     <t xml:space="preserve">3.05034613609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98760628700256</t>
+    <t xml:space="preserve">2.98760652542114</t>
   </si>
   <si>
     <t xml:space="preserve">2.95026135444641</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01598858833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01001358032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02495169639587</t>
+    <t xml:space="preserve">3.01598882675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01001334190369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02495145797729</t>
   </si>
   <si>
     <t xml:space="preserve">3.0174822807312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03092670440674</t>
+    <t xml:space="preserve">3.03092646598816</t>
   </si>
   <si>
     <t xml:space="preserve">2.99955677986145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0443708896637</t>
+    <t xml:space="preserve">3.04437112808228</t>
   </si>
   <si>
     <t xml:space="preserve">2.95922374725342</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00254464149475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92785453796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90843486785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89648461341858</t>
+    <t xml:space="preserve">3.00254440307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92785429954529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90843510627747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.896484375</t>
   </si>
   <si>
     <t xml:space="preserve">2.91889142990112</t>
@@ -137,139 +137,139 @@
     <t xml:space="preserve">2.9159038066864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92038559913635</t>
+    <t xml:space="preserve">2.92038536071777</t>
   </si>
   <si>
     <t xml:space="preserve">2.90544700622559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90992856025696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9233729839325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83822631835938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86063289642334</t>
+    <t xml:space="preserve">2.90992832183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92337274551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83822584152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86063313484192</t>
   </si>
   <si>
     <t xml:space="preserve">2.82627558708191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77996778488159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84569501876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86810207366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88303995132446</t>
+    <t xml:space="preserve">2.77996730804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84569525718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86810159683228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88304018974304</t>
   </si>
   <si>
     <t xml:space="preserve">2.79639935493469</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87557101249695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89797806739807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80088090896606</t>
+    <t xml:space="preserve">2.87557077407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89797854423523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80088114738464</t>
   </si>
   <si>
     <t xml:space="preserve">2.74262261390686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82179403305054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75009202957153</t>
+    <t xml:space="preserve">2.82179427146912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75009179115295</t>
   </si>
   <si>
     <t xml:space="preserve">2.76353597640991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77847409248352</t>
+    <t xml:space="preserve">2.77847385406494</t>
   </si>
   <si>
     <t xml:space="preserve">2.78594279289246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79341220855713</t>
+    <t xml:space="preserve">2.79341197013855</t>
   </si>
   <si>
     <t xml:space="preserve">2.69631457328796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65150046348572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62162470817566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53946566581726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56934142112732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61415553092957</t>
+    <t xml:space="preserve">2.6515007019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62162446975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53946542739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5693416595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61415576934814</t>
   </si>
   <si>
     <t xml:space="preserve">2.65896964073181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68884563446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70378375053406</t>
+    <t xml:space="preserve">2.68884539604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70378398895264</t>
   </si>
   <si>
     <t xml:space="preserve">2.77100467681885</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81581878662109</t>
+    <t xml:space="preserve">2.81581902503967</t>
   </si>
   <si>
     <t xml:space="preserve">2.7336597442627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66643857955933</t>
+    <t xml:space="preserve">2.66643881797791</t>
   </si>
   <si>
     <t xml:space="preserve">2.68137645721436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74112868309021</t>
+    <t xml:space="preserve">2.74112892150879</t>
   </si>
   <si>
     <t xml:space="preserve">2.72619080543518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83075666427612</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.893150806427</t>
+    <t xml:space="preserve">2.8307569026947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89315056800842</t>
   </si>
   <si>
     <t xml:space="preserve">2.69871854782104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83870959281921</t>
+    <t xml:space="preserve">2.83870983123779</t>
   </si>
   <si>
     <t xml:space="preserve">2.93203711509705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87759613990784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8309326171875</t>
+    <t xml:space="preserve">2.87759637832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83093214035034</t>
   </si>
   <si>
     <t xml:space="preserve">2.81537771224976</t>
@@ -290,13 +290,13 @@
     <t xml:space="preserve">2.80760049819946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00980997085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9553689956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90870547294617</t>
+    <t xml:space="preserve">3.00980973243713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95536875724792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90870523452759</t>
   </si>
   <si>
     <t xml:space="preserve">2.88537311553955</t>
@@ -305,7 +305,7 @@
     <t xml:space="preserve">2.82315516471863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86204171180725</t>
+    <t xml:space="preserve">2.86204147338867</t>
   </si>
   <si>
     <t xml:space="preserve">3.00203251838684</t>
@@ -314,7 +314,7 @@
     <t xml:space="preserve">2.91648268699646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8542640209198</t>
+    <t xml:space="preserve">2.85426425933838</t>
   </si>
   <si>
     <t xml:space="preserve">2.7298276424408</t>
@@ -329,7 +329,7 @@
     <t xml:space="preserve">2.75315952301025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70649576187134</t>
+    <t xml:space="preserve">2.70649600028992</t>
   </si>
   <si>
     <t xml:space="preserve">2.93981432914734</t>
@@ -338,19 +338,19 @@
     <t xml:space="preserve">2.99425530433655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97870063781738</t>
+    <t xml:space="preserve">2.97870111465454</t>
   </si>
   <si>
     <t xml:space="preserve">2.86981868743896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94759130477905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98647809028625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63650035858154</t>
+    <t xml:space="preserve">2.94759154319763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98647785186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63650012016296</t>
   </si>
   <si>
     <t xml:space="preserve">2.550950050354</t>
@@ -359,13 +359,13 @@
     <t xml:space="preserve">2.51984095573425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41095876693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34096336364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34874057769775</t>
+    <t xml:space="preserve">2.41095900535583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34096360206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34874081611633</t>
   </si>
   <si>
     <t xml:space="preserve">2.36429524421692</t>
@@ -374,13 +374,13 @@
     <t xml:space="preserve">2.2554132938385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24763584136963</t>
+    <t xml:space="preserve">2.24763607978821</t>
   </si>
   <si>
     <t xml:space="preserve">2.3254086971283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23208141326904</t>
+    <t xml:space="preserve">2.23208117485046</t>
   </si>
   <si>
     <t xml:space="preserve">2.18541765213013</t>
@@ -389,34 +389,34 @@
     <t xml:space="preserve">2.27874493598938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26319026947021</t>
+    <t xml:space="preserve">2.26319050788879</t>
   </si>
   <si>
     <t xml:space="preserve">2.21652674674988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06875824928284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1465311050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10764503479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15430855751038</t>
+    <t xml:space="preserve">2.06875801086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14653134346008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10764455795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1543083190918</t>
   </si>
   <si>
     <t xml:space="preserve">2.17764019966125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22430396080017</t>
+    <t xml:space="preserve">2.22430372238159</t>
   </si>
   <si>
     <t xml:space="preserve">2.35651779174805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4887318611145</t>
+    <t xml:space="preserve">2.48873162269592</t>
   </si>
   <si>
     <t xml:space="preserve">2.52761793136597</t>
@@ -428,76 +428,76 @@
     <t xml:space="preserve">2.44206809997559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55872702598572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44984531402588</t>
+    <t xml:space="preserve">2.5587272644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44984555244446</t>
   </si>
   <si>
     <t xml:space="preserve">2.37207221984863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33318638801575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29429936408997</t>
+    <t xml:space="preserve">2.33318591117859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29429984092712</t>
   </si>
   <si>
     <t xml:space="preserve">2.3798496723175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71427297592163</t>
+    <t xml:space="preserve">2.71427345275879</t>
   </si>
   <si>
     <t xml:space="preserve">2.58205890655518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62872338294983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65983200073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57428169250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67538666725159</t>
+    <t xml:space="preserve">2.62872290611267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.659832239151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57428216934204</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67538690567017</t>
   </si>
   <si>
     <t xml:space="preserve">2.64427757263184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69094133377075</t>
+    <t xml:space="preserve">2.69094109535217</t>
   </si>
   <si>
     <t xml:space="preserve">2.76871395111084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90092802047729</t>
+    <t xml:space="preserve">2.90092778205872</t>
   </si>
   <si>
     <t xml:space="preserve">2.9631462097168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92426013946533</t>
+    <t xml:space="preserve">2.92425990104675</t>
   </si>
   <si>
     <t xml:space="preserve">2.97092366218567</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01758742332458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04869675636292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03314161300659</t>
+    <t xml:space="preserve">3.01758766174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04869651794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03314208984375</t>
   </si>
   <si>
     <t xml:space="preserve">3.06425094604492</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07980561256409</t>
+    <t xml:space="preserve">3.07980585098267</t>
   </si>
   <si>
     <t xml:space="preserve">3.06049919128418</t>
@@ -506,10 +506,10 @@
     <t xml:space="preserve">3.02811288833618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01191997528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1090784072876</t>
+    <t xml:space="preserve">3.01191973686218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10907816886902</t>
   </si>
   <si>
     <t xml:space="preserve">3.0928852558136</t>
@@ -518,10 +518,10 @@
     <t xml:space="preserve">3.12527132034302</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07669234275818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99572658538818</t>
+    <t xml:space="preserve">3.0766921043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99572682380676</t>
   </si>
   <si>
     <t xml:space="preserve">3.30339574813843</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">3.36816811561584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23862338066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31958913803101</t>
+    <t xml:space="preserve">3.23862314224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31958866119385</t>
   </si>
   <si>
     <t xml:space="preserve">3.27100944519043</t>
@@ -554,13 +554,13 @@
     <t xml:space="preserve">3.22243022918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17385125160217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20623707771301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1414647102356</t>
+    <t xml:space="preserve">3.17385077476501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20623731613159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14146494865417</t>
   </si>
   <si>
     <t xml:space="preserve">3.40055418014526</t>
@@ -569,10 +569,10 @@
     <t xml:space="preserve">3.49771332740784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38436150550842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25481677055359</t>
+    <t xml:space="preserve">3.38436102867126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25481629371643</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004416465759</t>
@@ -581,46 +581,46 @@
     <t xml:space="preserve">2.96334028244019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97953367233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80140924453735</t>
+    <t xml:space="preserve">2.97953343391418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80140900611877</t>
   </si>
   <si>
     <t xml:space="preserve">2.88237476348877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86618185043335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84998822212219</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78521609306335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75283002853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72044348716736</t>
+    <t xml:space="preserve">2.86618161201477</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84998846054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78521633148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75282979011536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72044372558594</t>
   </si>
   <si>
     <t xml:space="preserve">2.83379530906677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76902294158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73663711547852</t>
+    <t xml:space="preserve">2.76902318000793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73663663864136</t>
   </si>
   <si>
     <t xml:space="preserve">2.81760239601135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89856791496277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91476082801819</t>
+    <t xml:space="preserve">2.89856767654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91476106643677</t>
   </si>
   <si>
     <t xml:space="preserve">2.63947796821594</t>
@@ -632,52 +632,52 @@
     <t xml:space="preserve">2.62328505516052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68805718421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70425057411194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60709166526794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59089875221252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42896771430969</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54231929779053</t>
+    <t xml:space="preserve">2.68805694580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70425033569336</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60709190368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59089851379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42896747589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54231905937195</t>
   </si>
   <si>
     <t xml:space="preserve">2.46135377883911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3156156539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2994225025177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35488152503967</t>
+    <t xml:space="preserve">2.31561541557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29942274093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35488176345825</t>
   </si>
   <si>
     <t xml:space="preserve">2.40607476234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28662419319153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13304495811462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08185219764709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06478762626648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03065872192383</t>
+    <t xml:space="preserve">2.28662443161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1330451965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08185195922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0647873878479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03065896034241</t>
   </si>
   <si>
     <t xml:space="preserve">2.1671736240387</t>
@@ -689,25 +689,25 @@
     <t xml:space="preserve">2.26955986022949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21836686134338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3207528591156</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55965423583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54258966445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45726776123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5767183303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62791156768799</t>
+    <t xml:space="preserve">2.2183666229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32075333595276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55965399742126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54258990287781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45726799964905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57671856880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62791132926941</t>
   </si>
   <si>
     <t xml:space="preserve">2.61084699630737</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">2.69616913795471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71323347091675</t>
+    <t xml:space="preserve">2.71323323249817</t>
   </si>
   <si>
     <t xml:space="preserve">2.44020342826843</t>
@@ -734,7 +734,7 @@
     <t xml:space="preserve">2.47433233261108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15010929107666</t>
+    <t xml:space="preserve">2.15010952949524</t>
   </si>
   <si>
     <t xml:space="preserve">2.33781743049622</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">2.30368876457214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25249576568604</t>
+    <t xml:space="preserve">2.25249552726746</t>
   </si>
   <si>
     <t xml:space="preserve">2.23543095588684</t>
@@ -755,7 +755,7 @@
     <t xml:space="preserve">2.38901042938232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20130228996277</t>
+    <t xml:space="preserve">2.20130252838135</t>
   </si>
   <si>
     <t xml:space="preserve">2.18423795700073</t>
@@ -764,34 +764,34 @@
     <t xml:space="preserve">2.01359438896179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04772353172302</t>
+    <t xml:space="preserve">2.04772305488586</t>
   </si>
   <si>
     <t xml:space="preserve">2.11598062515259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.911208152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87707984447479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84295094013214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97946572303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86001527309418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94533681869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96240139007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99653005599976</t>
+    <t xml:space="preserve">1.91120851039886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87707960605621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84295105934143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97946584224701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86001539230347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94533693790436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96240150928497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99652993679047</t>
   </si>
   <si>
     <t xml:space="preserve">2.81561946868896</t>
@@ -800,16 +800,16 @@
     <t xml:space="preserve">2.90094137191772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88387727737427</t>
+    <t xml:space="preserve">2.88387703895569</t>
   </si>
   <si>
     <t xml:space="preserve">2.76442646980286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73029780387878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6791045665741</t>
+    <t xml:space="preserve">2.73029756546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67910432815552</t>
   </si>
   <si>
     <t xml:space="preserve">2.74736189842224</t>
@@ -818,10 +818,10 @@
     <t xml:space="preserve">2.83268356323242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86681246757507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79855513572693</t>
+    <t xml:space="preserve">2.86681222915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79855489730835</t>
   </si>
   <si>
     <t xml:space="preserve">2.78149056434631</t>
@@ -833,10 +833,10 @@
     <t xml:space="preserve">2.96919870376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02039194107056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00332713127136</t>
+    <t xml:space="preserve">3.02039170265198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00332736968994</t>
   </si>
   <si>
     <t xml:space="preserve">3.03745603561401</t>
@@ -845,10 +845,10 @@
     <t xml:space="preserve">2.98626303672791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05452060699463</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07158470153809</t>
+    <t xml:space="preserve">3.05452013015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07158493995667</t>
   </si>
   <si>
     <t xml:space="preserve">3.13984251022339</t>
@@ -857,28 +857,28 @@
     <t xml:space="preserve">3.11424589157104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1313099861145</t>
+    <t xml:space="preserve">3.13131022453308</t>
   </si>
   <si>
     <t xml:space="preserve">3.06305241584778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16543865203857</t>
+    <t xml:space="preserve">3.16543889045715</t>
   </si>
   <si>
     <t xml:space="preserve">3.19956755638123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15690660476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23369598388672</t>
+    <t xml:space="preserve">3.15690684318542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2336962223053</t>
   </si>
   <si>
     <t xml:space="preserve">3.27635717391968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24222850799561</t>
+    <t xml:space="preserve">3.24222826957703</t>
   </si>
   <si>
     <t xml:space="preserve">3.26782488822937</t>
@@ -887,19 +887,19 @@
     <t xml:space="preserve">3.31048607826233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34461498260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32755017280579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28488922119141</t>
+    <t xml:space="preserve">3.34461450576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32755041122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28488945960999</t>
   </si>
   <si>
     <t xml:space="preserve">3.18250322341919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29342126846313</t>
+    <t xml:space="preserve">3.29342150688171</t>
   </si>
   <si>
     <t xml:space="preserve">3.33710074424744</t>
@@ -908,13 +908,13 @@
     <t xml:space="preserve">3.32836484909058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29342150688171</t>
+    <t xml:space="preserve">3.29342174530029</t>
   </si>
   <si>
     <t xml:space="preserve">3.24974226951599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20606279373169</t>
+    <t xml:space="preserve">3.20606303215027</t>
   </si>
   <si>
     <t xml:space="preserve">3.15364766120911</t>
@@ -923,22 +923,22 @@
     <t xml:space="preserve">3.21479892730713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17111945152283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26721382141113</t>
+    <t xml:space="preserve">3.17111968994141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26721405982971</t>
   </si>
   <si>
     <t xml:space="preserve">3.36330842971802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49434661865234</t>
+    <t xml:space="preserve">3.49434638023376</t>
   </si>
   <si>
     <t xml:space="preserve">3.58170509338379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56423330307007</t>
+    <t xml:space="preserve">3.56423354148865</t>
   </si>
   <si>
     <t xml:space="preserve">3.59044122695923</t>
@@ -947,43 +947,43 @@
     <t xml:space="preserve">3.5030825138092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51181840896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54676175117493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63411998748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62538456916809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7476863861084</t>
+    <t xml:space="preserve">3.51181817054749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54676151275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63412046432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62538480758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74768662452698</t>
   </si>
   <si>
     <t xml:space="preserve">3.69527125358582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66906380653381</t>
+    <t xml:space="preserve">3.66906356811523</t>
   </si>
   <si>
     <t xml:space="preserve">3.60791301727295</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55549788475037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66032814979553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65159201622009</t>
+    <t xml:space="preserve">3.55549764633179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66032791137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65159177780151</t>
   </si>
   <si>
     <t xml:space="preserve">3.68653535842896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7040069103241</t>
+    <t xml:space="preserve">3.70400714874268</t>
   </si>
   <si>
     <t xml:space="preserve">3.75642251968384</t>
@@ -992,16 +992,16 @@
     <t xml:space="preserve">3.57296967506409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53802609443665</t>
+    <t xml:space="preserve">3.53802585601807</t>
   </si>
   <si>
     <t xml:space="preserve">3.3458366394043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3895161151886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42445993423462</t>
+    <t xml:space="preserve">3.38951635360718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42445969581604</t>
   </si>
   <si>
     <t xml:space="preserve">3.45066738128662</t>
@@ -1010,37 +1010,37 @@
     <t xml:space="preserve">3.44193148612976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48561072349548</t>
+    <t xml:space="preserve">3.4856104850769</t>
   </si>
   <si>
     <t xml:space="preserve">3.4069881439209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35457229614258</t>
+    <t xml:space="preserve">3.35457253456116</t>
   </si>
   <si>
     <t xml:space="preserve">3.45940327644348</t>
   </si>
   <si>
-    <t xml:space="preserve">3.52928996086121</t>
+    <t xml:space="preserve">3.52928972244263</t>
   </si>
   <si>
     <t xml:space="preserve">3.46813893318176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47687482833862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79136610031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72147941589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87872457504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17574405670166</t>
+    <t xml:space="preserve">3.47687458992004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79136633872986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7214789390564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8787248134613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17574453353882</t>
   </si>
   <si>
     <t xml:space="preserve">4.31551790237427</t>
@@ -1061,22 +1061,22 @@
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493226051331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98355507850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94861173629761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93113970756531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08838558197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07091379165649</t>
+    <t xml:space="preserve">3.90493202209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98355484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94861197471619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93114018440247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08838510513306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07091331481934</t>
   </si>
   <si>
     <t xml:space="preserve">4.1233286857605</t>
@@ -1085,10 +1085,10 @@
     <t xml:space="preserve">4.00102663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00976324081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93987584114075</t>
+    <t xml:space="preserve">4.00976276397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93987607955933</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
@@ -1100,16 +1100,16 @@
     <t xml:space="preserve">4.29804611206055</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28930997848511</t>
+    <t xml:space="preserve">4.28931045532227</t>
   </si>
   <si>
     <t xml:space="preserve">4.21942329406738</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19321632385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14953660964966</t>
+    <t xml:space="preserve">4.19321584701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1495361328125</t>
   </si>
   <si>
     <t xml:space="preserve">4.16700792312622</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">4.11459302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06217765808105</t>
+    <t xml:space="preserve">4.06217813491821</t>
   </si>
   <si>
     <t xml:space="preserve">3.78262996673584</t>
@@ -1127,13 +1127,13 @@
     <t xml:space="preserve">3.80010175704956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8263099193573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83504557609558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84378147125244</t>
+    <t xml:space="preserve">3.82630968093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83504509925842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84378099441528</t>
   </si>
   <si>
     <t xml:space="preserve">3.77389454841614</t>
@@ -1151,10 +1151,10 @@
     <t xml:space="preserve">3.86125302314758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76515793800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81757354736328</t>
+    <t xml:space="preserve">3.76515865325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8175733089447</t>
   </si>
   <si>
     <t xml:space="preserve">3.64285612106323</t>
@@ -1163,43 +1163,43 @@
     <t xml:space="preserve">3.67779970169067</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7389509677887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85251712799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71274328231812</t>
+    <t xml:space="preserve">3.73895072937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85251665115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71274304389954</t>
   </si>
   <si>
     <t xml:space="preserve">3.92240381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61664843559265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39825201034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23227047920227</t>
+    <t xml:space="preserve">3.61664867401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39825224876404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23227071762085</t>
   </si>
   <si>
     <t xml:space="preserve">3.0575532913208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97019481658936</t>
+    <t xml:space="preserve">2.97019457817078</t>
   </si>
   <si>
     <t xml:space="preserve">2.95272302627563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91777944564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90904355049133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3720440864563</t>
+    <t xml:space="preserve">2.91777920722961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90904331207275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37204432487488</t>
   </si>
   <si>
     <t xml:space="preserve">3.38078022003174</t>
@@ -1214,7 +1214,7 @@
     <t xml:space="preserve">3.27594995498657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28468561172485</t>
+    <t xml:space="preserve">3.28468585014343</t>
   </si>
   <si>
     <t xml:space="preserve">3.50245499610901</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">3.32098078727722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26653814315796</t>
+    <t xml:space="preserve">3.26653838157654</t>
   </si>
   <si>
     <t xml:space="preserve">3.39357042312622</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">3.23024344444275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19394874572754</t>
+    <t xml:space="preserve">3.19394850730896</t>
   </si>
   <si>
     <t xml:space="preserve">3.25746440887451</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">3.2211697101593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10321140289307</t>
+    <t xml:space="preserve">3.10321164131165</t>
   </si>
   <si>
     <t xml:space="preserve">2.99432682991028</t>
@@ -1286,13 +1286,13 @@
     <t xml:space="preserve">2.95803189277649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85822105407715</t>
+    <t xml:space="preserve">2.85822129249573</t>
   </si>
   <si>
     <t xml:space="preserve">2.89451599121094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8672947883606</t>
+    <t xml:space="preserve">2.86729502677917</t>
   </si>
   <si>
     <t xml:space="preserve">2.81285238265991</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">2.75841021537781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70396780967712</t>
+    <t xml:space="preserve">2.7039680480957</t>
   </si>
   <si>
     <t xml:space="preserve">2.72211527824402</t>
@@ -1313,16 +1313,16 @@
     <t xml:space="preserve">2.64952564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7947051525116</t>
+    <t xml:space="preserve">2.79470491409302</t>
   </si>
   <si>
     <t xml:space="preserve">2.92173719406128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05784273147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02154803276062</t>
+    <t xml:space="preserve">3.05784296989441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02154779434204</t>
   </si>
   <si>
     <t xml:space="preserve">3.13950634002686</t>
@@ -1352,46 +1352,46 @@
     <t xml:space="preserve">3.08506417274475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01247429847717</t>
+    <t xml:space="preserve">3.01247406005859</t>
   </si>
   <si>
     <t xml:space="preserve">2.88544225692749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7765576839447</t>
+    <t xml:space="preserve">2.77655744552612</t>
   </si>
   <si>
     <t xml:space="preserve">2.71304154396057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6313784122467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68582034111023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66767287254333</t>
+    <t xml:space="preserve">2.63137817382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68582057952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66767311096191</t>
   </si>
   <si>
     <t xml:space="preserve">2.55878829956055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52249336242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67674660682678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64045214653015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87636852264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83099985122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60415697097778</t>
+    <t xml:space="preserve">2.52249360084534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67674684524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64045190811157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87636876106262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83099961280823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6041567325592</t>
   </si>
   <si>
     <t xml:space="preserve">2.73118901252747</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">2.91266345977783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12135887145996</t>
+    <t xml:space="preserve">3.12135910987854</t>
   </si>
   <si>
     <t xml:space="preserve">3.0759904384613</t>
@@ -1427,46 +1427,46 @@
     <t xml:space="preserve">3.0941379070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38449692726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41171765327454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37542319297791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42079138755798</t>
+    <t xml:space="preserve">3.38449668884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41171789169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37542295455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42079162597656</t>
   </si>
   <si>
     <t xml:space="preserve">3.43893885612488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36634945869446</t>
+    <t xml:space="preserve">3.36634922027588</t>
   </si>
   <si>
     <t xml:space="preserve">3.35727572441101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20302248001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27561187744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29375958442688</t>
+    <t xml:space="preserve">3.20302224159241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27561211585999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29375982284546</t>
   </si>
   <si>
     <t xml:space="preserve">3.1667275428772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11228513717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78563141822815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84007382392883</t>
+    <t xml:space="preserve">3.11228537559509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78563117980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84007358551025</t>
   </si>
   <si>
     <t xml:space="preserve">2.82192611694336</t>
@@ -1788,6 +1788,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.74000000953674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66000008583069</t>
   </si>
 </sst>
 </file>
@@ -56960,7 +56963,7 @@
     </row>
     <row r="2110">
       <c r="A2110" s="1" t="n">
-        <v>46041.6910532407</v>
+        <v>46041.3333333333</v>
       </c>
       <c r="B2110" t="n">
         <v>15845</v>
@@ -56981,6 +56984,32 @@
         <v>591</v>
       </c>
       <c r="H2110" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2111">
+      <c r="A2111" s="1" t="n">
+        <v>46042.6912731481</v>
+      </c>
+      <c r="B2111" t="n">
+        <v>24769</v>
+      </c>
+      <c r="C2111" t="n">
+        <v>3.74000000953674</v>
+      </c>
+      <c r="D2111" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="E2111" t="n">
+        <v>3.74000000953674</v>
+      </c>
+      <c r="F2111" t="n">
+        <v>3.66000008583069</v>
+      </c>
+      <c r="G2111" t="s">
+        <v>592</v>
+      </c>
+      <c r="H2111" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="594" uniqueCount="594">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="595" uniqueCount="595">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,19 +47,19 @@
     <t xml:space="preserve">2.96519923210144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88901567459106</t>
+    <t xml:space="preserve">2.88901543617249</t>
   </si>
   <si>
     <t xml:space="preserve">2.98013710975647</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97266817092896</t>
+    <t xml:space="preserve">2.97266793251038</t>
   </si>
   <si>
     <t xml:space="preserve">2.94578003883362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9577305316925</t>
+    <t xml:space="preserve">2.95773029327393</t>
   </si>
   <si>
     <t xml:space="preserve">2.96221160888672</t>
@@ -77,13 +77,13 @@
     <t xml:space="preserve">2.98611259460449</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03540802001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05632138252258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05930924415588</t>
+    <t xml:space="preserve">3.03540825843811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.056321144104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0593090057373</t>
   </si>
   <si>
     <t xml:space="preserve">3.05034613609314</t>
@@ -98,13 +98,13 @@
     <t xml:space="preserve">3.01598858833313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01001310348511</t>
+    <t xml:space="preserve">3.01001334190369</t>
   </si>
   <si>
     <t xml:space="preserve">3.02495145797729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0174822807312</t>
+    <t xml:space="preserve">3.01748204231262</t>
   </si>
   <si>
     <t xml:space="preserve">3.03092670440674</t>
@@ -113,19 +113,19 @@
     <t xml:space="preserve">2.99955677986145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0443708896637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.959223985672</t>
+    <t xml:space="preserve">3.04437136650085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95922422409058</t>
   </si>
   <si>
     <t xml:space="preserve">3.00254440307617</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92785429954529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90843486785889</t>
+    <t xml:space="preserve">2.92785406112671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90843510627747</t>
   </si>
   <si>
     <t xml:space="preserve">2.896484375</t>
@@ -134,46 +134,46 @@
     <t xml:space="preserve">2.91889142990112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91590404510498</t>
+    <t xml:space="preserve">2.91590356826782</t>
   </si>
   <si>
     <t xml:space="preserve">2.92038512229919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90544724464417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90992832183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9233729839325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83822584152222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8606333732605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82627558708191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77996778488159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84569501876831</t>
+    <t xml:space="preserve">2.90544700622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90992856025696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92337274551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8382260799408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86063289642334</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82627582550049</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77996754646301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84569478034973</t>
   </si>
   <si>
     <t xml:space="preserve">2.86810207366943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88303971290588</t>
+    <t xml:space="preserve">2.88303995132446</t>
   </si>
   <si>
     <t xml:space="preserve">2.79639959335327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87557101249695</t>
+    <t xml:space="preserve">2.87557125091553</t>
   </si>
   <si>
     <t xml:space="preserve">2.89797830581665</t>
@@ -182,10 +182,10 @@
     <t xml:space="preserve">2.80088090896606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74262237548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82179427146912</t>
+    <t xml:space="preserve">2.74262261390686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82179403305054</t>
   </si>
   <si>
     <t xml:space="preserve">2.75009155273438</t>
@@ -194,31 +194,31 @@
     <t xml:space="preserve">2.76353597640991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77847385406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78594255447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79341220855713</t>
+    <t xml:space="preserve">2.7784743309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78594303131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79341197013855</t>
   </si>
   <si>
     <t xml:space="preserve">2.69631481170654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65150046348572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62162446975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53946566581726</t>
+    <t xml:space="preserve">2.6515007019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6216242313385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53946542739868</t>
   </si>
   <si>
     <t xml:space="preserve">2.56934142112732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61415553092957</t>
+    <t xml:space="preserve">2.61415529251099</t>
   </si>
   <si>
     <t xml:space="preserve">2.65896964073181</t>
@@ -227,10 +227,10 @@
     <t xml:space="preserve">2.68884563446045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70378375053406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77100491523743</t>
+    <t xml:space="preserve">2.70378398895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77100515365601</t>
   </si>
   <si>
     <t xml:space="preserve">2.81581902503967</t>
@@ -239,28 +239,28 @@
     <t xml:space="preserve">2.7336597442627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66643857955933</t>
+    <t xml:space="preserve">2.66643881797791</t>
   </si>
   <si>
     <t xml:space="preserve">2.68137669563293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74112915992737</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72619104385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8307569026947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89315056800842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69871878623962</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83870983123779</t>
+    <t xml:space="preserve">2.74112892150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72619080543518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83075737953186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89315104484558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69871854782104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83870959281921</t>
   </si>
   <si>
     <t xml:space="preserve">2.93203711509705</t>
@@ -269,10 +269,10 @@
     <t xml:space="preserve">2.87759613990784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83093237876892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81537771224976</t>
+    <t xml:space="preserve">2.8309326171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81537795066833</t>
   </si>
   <si>
     <t xml:space="preserve">2.84648680686951</t>
@@ -281,85 +281,85 @@
     <t xml:space="preserve">2.79982304573059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73760485649109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76093649864197</t>
+    <t xml:space="preserve">2.73760461807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76093697547913</t>
   </si>
   <si>
     <t xml:space="preserve">2.80760049819946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00980973243713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95536875724792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90870547294617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88537335395813</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82315540313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86204147338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00203227996826</t>
+    <t xml:space="preserve">3.00980997085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9553689956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90870523452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88537359237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82315516471863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86204171180725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00203251838684</t>
   </si>
   <si>
     <t xml:space="preserve">2.91648244857788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85426449775696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7298276424408</t>
+    <t xml:space="preserve">2.85426425933838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72982740402222</t>
   </si>
   <si>
     <t xml:space="preserve">2.68316411972046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7220504283905</t>
+    <t xml:space="preserve">2.72205018997192</t>
   </si>
   <si>
     <t xml:space="preserve">2.75315952301025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70649552345276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93981432914734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99425530433655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97870111465454</t>
+    <t xml:space="preserve">2.70649576187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93981456756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99425554275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97870063781738</t>
   </si>
   <si>
     <t xml:space="preserve">2.86981868743896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94759154319763</t>
+    <t xml:space="preserve">2.94759202003479</t>
   </si>
   <si>
     <t xml:space="preserve">2.98647809028625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63650012016296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55095028877258</t>
+    <t xml:space="preserve">2.63650059700012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55094981193542</t>
   </si>
   <si>
     <t xml:space="preserve">2.51984071731567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41095900535583</t>
+    <t xml:space="preserve">2.41095876693726</t>
   </si>
   <si>
     <t xml:space="preserve">2.34096336364746</t>
@@ -374,70 +374,70 @@
     <t xml:space="preserve">2.2554132938385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24763584136963</t>
+    <t xml:space="preserve">2.24763607978821</t>
   </si>
   <si>
     <t xml:space="preserve">2.3254086971283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23208093643188</t>
+    <t xml:space="preserve">2.23208141326904</t>
   </si>
   <si>
     <t xml:space="preserve">2.18541765213013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27874541282654</t>
+    <t xml:space="preserve">2.27874517440796</t>
   </si>
   <si>
     <t xml:space="preserve">2.26319026947021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21652674674988</t>
+    <t xml:space="preserve">2.2165265083313</t>
   </si>
   <si>
     <t xml:space="preserve">2.06875824928284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14653134346008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10764455795288</t>
+    <t xml:space="preserve">2.14653086662292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10764479637146</t>
   </si>
   <si>
     <t xml:space="preserve">2.15430855751038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17764019966125</t>
+    <t xml:space="preserve">2.17764043807983</t>
   </si>
   <si>
     <t xml:space="preserve">2.22430396080017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35651779174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4887318611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52761816978455</t>
+    <t xml:space="preserve">2.35651803016663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48873162269592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52761793136597</t>
   </si>
   <si>
     <t xml:space="preserve">2.43429064750671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44206809997559</t>
+    <t xml:space="preserve">2.44206786155701</t>
   </si>
   <si>
     <t xml:space="preserve">2.5587272644043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44984555244446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37207198143005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33318591117859</t>
+    <t xml:space="preserve">2.44984531402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37207245826721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33318614959717</t>
   </si>
   <si>
     <t xml:space="preserve">2.29429984092712</t>
@@ -446,40 +446,40 @@
     <t xml:space="preserve">2.3798496723175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71427321434021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58205914497375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62872290611267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.659832239151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57428193092346</t>
+    <t xml:space="preserve">2.71427297592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58205890655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62872314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65983200073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57428169250488</t>
   </si>
   <si>
     <t xml:space="preserve">2.67538666725159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64427781105042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69094109535217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76871395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90092754364014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9631462097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92426013946533</t>
+    <t xml:space="preserve">2.64427757263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69094133377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76871418952942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90092802047729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96314597129822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92425990104675</t>
   </si>
   <si>
     <t xml:space="preserve">2.97092342376709</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">3.01758742332458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04869651794434</t>
+    <t xml:space="preserve">3.04869627952576</t>
   </si>
   <si>
     <t xml:space="preserve">3.03314185142517</t>
@@ -497,22 +497,22 @@
     <t xml:space="preserve">3.0642511844635</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07980585098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0604989528656</t>
+    <t xml:space="preserve">3.07980561256409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06049919128418</t>
   </si>
   <si>
     <t xml:space="preserve">3.02811288833618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01191973686218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10907816886902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09288549423218</t>
+    <t xml:space="preserve">3.01191997528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1090784072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0928852558136</t>
   </si>
   <si>
     <t xml:space="preserve">3.12527132034302</t>
@@ -521,67 +521,67 @@
     <t xml:space="preserve">3.0766921043396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99572682380676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30339598655701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41674757003784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35197520256042</t>
+    <t xml:space="preserve">2.99572658538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30339574813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41674733161926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35197496414185</t>
   </si>
   <si>
     <t xml:space="preserve">3.33578181266785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36816835403442</t>
+    <t xml:space="preserve">3.36816811561584</t>
   </si>
   <si>
     <t xml:space="preserve">3.23862338066101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31958866119385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27100944519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28720259666443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22243022918701</t>
+    <t xml:space="preserve">3.31958889961243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27100920677185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28720235824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22242999076843</t>
   </si>
   <si>
     <t xml:space="preserve">3.17385077476501</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20623731613159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14146494865417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40055441856384</t>
+    <t xml:space="preserve">3.20623707771301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1414647102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40055418014526</t>
   </si>
   <si>
     <t xml:space="preserve">3.49771332740784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38436102867126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25481629371643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19004392623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96334004402161</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97953343391418</t>
+    <t xml:space="preserve">3.38436126708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25481653213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19004416465759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96334028244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97953367233276</t>
   </si>
   <si>
     <t xml:space="preserve">2.80140924453735</t>
@@ -593,16 +593,16 @@
     <t xml:space="preserve">2.86618161201477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84998846054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78521633148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75282955169678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72044372558594</t>
+    <t xml:space="preserve">2.84998822212219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78521609306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75283002853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72044348716736</t>
   </si>
   <si>
     <t xml:space="preserve">2.83379530906677</t>
@@ -617,7 +617,7 @@
     <t xml:space="preserve">2.81760239601135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89856743812561</t>
+    <t xml:space="preserve">2.89856767654419</t>
   </si>
   <si>
     <t xml:space="preserve">2.91476082801819</t>
@@ -626,46 +626,46 @@
     <t xml:space="preserve">2.63947796821594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67186427116394</t>
+    <t xml:space="preserve">2.67186403274536</t>
   </si>
   <si>
     <t xml:space="preserve">2.62328481674194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68805694580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70425033569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60709190368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59089875221252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42896747589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54231929779053</t>
+    <t xml:space="preserve">2.68805718421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70425057411194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60709166526794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59089851379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42896771430969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54231905937195</t>
   </si>
   <si>
     <t xml:space="preserve">2.46135377883911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31561541557312</t>
+    <t xml:space="preserve">2.3156156539917</t>
   </si>
   <si>
     <t xml:space="preserve">2.29942274093628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35488176345825</t>
+    <t xml:space="preserve">2.35488152503967</t>
   </si>
   <si>
     <t xml:space="preserve">2.40607476234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28662443161011</t>
+    <t xml:space="preserve">2.28662419319153</t>
   </si>
   <si>
     <t xml:space="preserve">2.13304495811462</t>
@@ -686,25 +686,25 @@
     <t xml:space="preserve">2.09891629219055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26955986022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2183666229248</t>
+    <t xml:space="preserve">2.26956009864807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21836686134338</t>
   </si>
   <si>
     <t xml:space="preserve">2.32075309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55965399742126</t>
+    <t xml:space="preserve">2.55965423583984</t>
   </si>
   <si>
     <t xml:space="preserve">2.54258990287781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45726823806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57671856880188</t>
+    <t xml:space="preserve">2.45726799964905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5767183303833</t>
   </si>
   <si>
     <t xml:space="preserve">2.62791132926941</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">2.59378290176392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69616889953613</t>
+    <t xml:space="preserve">2.69616913795471</t>
   </si>
   <si>
     <t xml:space="preserve">2.71323323249817</t>
@@ -740,16 +740,16 @@
     <t xml:space="preserve">2.33781719207764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30368852615356</t>
+    <t xml:space="preserve">2.30368876457214</t>
   </si>
   <si>
     <t xml:space="preserve">2.25249576568604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23543119430542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37194609642029</t>
+    <t xml:space="preserve">2.23543095588684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37194633483887</t>
   </si>
   <si>
     <t xml:space="preserve">2.38901042938232</t>
@@ -761,19 +761,19 @@
     <t xml:space="preserve">2.18423795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01359438896179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04772305488586</t>
+    <t xml:space="preserve">2.01359415054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04772329330444</t>
   </si>
   <si>
     <t xml:space="preserve">2.11598062515259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91120851039886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87707960605621</t>
+    <t xml:space="preserve">1.91120839118958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87707984447479</t>
   </si>
   <si>
     <t xml:space="preserve">1.84295094013214</t>
@@ -782,10 +782,10 @@
     <t xml:space="preserve">1.97946584224701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86001539230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94533717632294</t>
+    <t xml:space="preserve">1.86001515388489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94533693790436</t>
   </si>
   <si>
     <t xml:space="preserve">1.96240127086639</t>
@@ -800,16 +800,16 @@
     <t xml:space="preserve">2.90094137191772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88387680053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76442646980286</t>
+    <t xml:space="preserve">2.88387703895569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76442623138428</t>
   </si>
   <si>
     <t xml:space="preserve">2.73029756546021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6791045665741</t>
+    <t xml:space="preserve">2.67910432815552</t>
   </si>
   <si>
     <t xml:space="preserve">2.74736189842224</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">2.86681246757507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79855513572693</t>
+    <t xml:space="preserve">2.79855489730835</t>
   </si>
   <si>
     <t xml:space="preserve">2.78149056434631</t>
@@ -839,7 +839,7 @@
     <t xml:space="preserve">3.00332713127136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03745603561401</t>
+    <t xml:space="preserve">3.03745627403259</t>
   </si>
   <si>
     <t xml:space="preserve">2.98626303672791</t>
@@ -863,25 +863,25 @@
     <t xml:space="preserve">3.06305265426636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16543865203857</t>
+    <t xml:space="preserve">3.16543889045715</t>
   </si>
   <si>
     <t xml:space="preserve">3.19956755638123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15690684318542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2336962223053</t>
+    <t xml:space="preserve">3.15690660476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23369646072388</t>
   </si>
   <si>
     <t xml:space="preserve">3.27635717391968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24222850799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26782512664795</t>
+    <t xml:space="preserve">3.24222826957703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26782488822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.31048607826233</t>
@@ -896,34 +896,34 @@
     <t xml:space="preserve">3.28488945960999</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18250322341919</t>
+    <t xml:space="preserve">3.18250346183777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29342126846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33710074424744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32836484909058</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342150688171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33710074424744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32836484909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29342174530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24974226951599</t>
+    <t xml:space="preserve">3.24974250793457</t>
   </si>
   <si>
     <t xml:space="preserve">3.20606303215027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15364766120911</t>
+    <t xml:space="preserve">3.15364742279053</t>
   </si>
   <si>
     <t xml:space="preserve">3.21479892730713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17111968994141</t>
+    <t xml:space="preserve">3.17111945152283</t>
   </si>
   <si>
     <t xml:space="preserve">3.26721405982971</t>
@@ -950,13 +950,13 @@
     <t xml:space="preserve">3.51181817054749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54676151275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63412046432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62538480758667</t>
+    <t xml:space="preserve">3.54676175117493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63412022590637</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62538456916809</t>
   </si>
   <si>
     <t xml:space="preserve">3.74768662452698</t>
@@ -965,34 +965,34 @@
     <t xml:space="preserve">3.69527125358582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66906356811523</t>
+    <t xml:space="preserve">3.66906332969666</t>
   </si>
   <si>
     <t xml:space="preserve">3.60791301727295</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55549764633179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66032791137695</t>
+    <t xml:space="preserve">3.55549788475037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66032767295837</t>
   </si>
   <si>
     <t xml:space="preserve">3.65159177780151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68653535842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70400714874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75642251968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57296967506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53802585601807</t>
+    <t xml:space="preserve">3.68653512001038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7040069103241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75642275810242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57296943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53802609443665</t>
   </si>
   <si>
     <t xml:space="preserve">3.3458366394043</t>
@@ -1004,7 +1004,7 @@
     <t xml:space="preserve">3.42445969581604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45066738128662</t>
+    <t xml:space="preserve">3.45066714286804</t>
   </si>
   <si>
     <t xml:space="preserve">3.44193148612976</t>
@@ -1019,10 +1019,10 @@
     <t xml:space="preserve">3.35457253456116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45940327644348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52928972244263</t>
+    <t xml:space="preserve">3.4594030380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52928996086121</t>
   </si>
   <si>
     <t xml:space="preserve">3.46813893318176</t>
@@ -1031,10 +1031,10 @@
     <t xml:space="preserve">3.47687458992004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79136633872986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7214789390564</t>
+    <t xml:space="preserve">3.79136610031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72147917747498</t>
   </si>
   <si>
     <t xml:space="preserve">3.8787248134613</t>
@@ -1049,13 +1049,13 @@
     <t xml:space="preserve">4.35046148300171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18447971343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20195150375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25436687469482</t>
+    <t xml:space="preserve">4.1844801902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20195198059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25436639785767</t>
   </si>
   <si>
     <t xml:space="preserve">4.14080047607422</t>
@@ -1067,10 +1067,10 @@
     <t xml:space="preserve">3.98355484008789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94861197471619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93114018440247</t>
+    <t xml:space="preserve">3.94861149787903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93113970756531</t>
   </si>
   <si>
     <t xml:space="preserve">4.08838510513306</t>
@@ -1088,31 +1088,31 @@
     <t xml:space="preserve">4.00976276397705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93987607955933</t>
+    <t xml:space="preserve">3.93987560272217</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2106876373291</t>
+    <t xml:space="preserve">4.21068811416626</t>
   </si>
   <si>
     <t xml:space="preserve">4.29804611206055</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28931045532227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21942329406738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19321584701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1495361328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16700792312622</t>
+    <t xml:space="preserve">4.28930997848511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21942377090454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19321632385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14953660964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16700839996338</t>
   </si>
   <si>
     <t xml:space="preserve">4.11459302902222</t>
@@ -1121,19 +1121,19 @@
     <t xml:space="preserve">4.06217813491821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78262996673584</t>
+    <t xml:space="preserve">3.78263020515442</t>
   </si>
   <si>
     <t xml:space="preserve">3.80010175704956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82630968093872</t>
+    <t xml:space="preserve">3.82630944252014</t>
   </si>
   <si>
     <t xml:space="preserve">3.83504509925842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84378099441528</t>
+    <t xml:space="preserve">3.84378123283386</t>
   </si>
   <si>
     <t xml:space="preserve">3.77389454841614</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734786987305</t>
+    <t xml:space="preserve">3.95734739303589</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">3.86125302314758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76515865325928</t>
+    <t xml:space="preserve">3.7651584148407</t>
   </si>
   <si>
     <t xml:space="preserve">3.8175733089447</t>
@@ -1160,13 +1160,13 @@
     <t xml:space="preserve">3.64285612106323</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67779970169067</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.73895072937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85251665115356</t>
+    <t xml:space="preserve">3.67779946327209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7389509677887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85251712799072</t>
   </si>
   <si>
     <t xml:space="preserve">3.71274304389954</t>
@@ -1196,7 +1196,7 @@
     <t xml:space="preserve">2.91777920722961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90904331207275</t>
+    <t xml:space="preserve">2.90904355049133</t>
   </si>
   <si>
     <t xml:space="preserve">3.37204432487488</t>
@@ -1205,7 +1205,7 @@
     <t xml:space="preserve">3.38078022003174</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41572380065918</t>
+    <t xml:space="preserve">3.41572403907776</t>
   </si>
   <si>
     <t xml:space="preserve">3.31962895393372</t>
@@ -1214,7 +1214,7 @@
     <t xml:space="preserve">3.27594995498657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28468585014343</t>
+    <t xml:space="preserve">3.28468561172485</t>
   </si>
   <si>
     <t xml:space="preserve">3.50245499610901</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">3.32098078727722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26653838157654</t>
+    <t xml:space="preserve">3.26653814315796</t>
   </si>
   <si>
     <t xml:space="preserve">3.39357042312622</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">3.23024344444275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19394850730896</t>
+    <t xml:space="preserve">3.19394874572754</t>
   </si>
   <si>
     <t xml:space="preserve">3.25746440887451</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">3.2211697101593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10321164131165</t>
+    <t xml:space="preserve">3.10321140289307</t>
   </si>
   <si>
     <t xml:space="preserve">2.99432682991028</t>
@@ -1286,13 +1286,13 @@
     <t xml:space="preserve">2.95803189277649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85822129249573</t>
+    <t xml:space="preserve">2.85822105407715</t>
   </si>
   <si>
     <t xml:space="preserve">2.89451599121094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86729502677917</t>
+    <t xml:space="preserve">2.8672947883606</t>
   </si>
   <si>
     <t xml:space="preserve">2.81285238265991</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">2.75841021537781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7039680480957</t>
+    <t xml:space="preserve">2.70396780967712</t>
   </si>
   <si>
     <t xml:space="preserve">2.72211527824402</t>
@@ -1313,16 +1313,16 @@
     <t xml:space="preserve">2.64952564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79470491409302</t>
+    <t xml:space="preserve">2.7947051525116</t>
   </si>
   <si>
     <t xml:space="preserve">2.92173719406128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05784296989441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02154779434204</t>
+    <t xml:space="preserve">3.05784273147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02154803276062</t>
   </si>
   <si>
     <t xml:space="preserve">3.13950634002686</t>
@@ -1352,46 +1352,46 @@
     <t xml:space="preserve">3.08506417274475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01247406005859</t>
+    <t xml:space="preserve">3.01247429847717</t>
   </si>
   <si>
     <t xml:space="preserve">2.88544225692749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77655744552612</t>
+    <t xml:space="preserve">2.7765576839447</t>
   </si>
   <si>
     <t xml:space="preserve">2.71304154396057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63137817382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68582057952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66767311096191</t>
+    <t xml:space="preserve">2.6313784122467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68582034111023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66767287254333</t>
   </si>
   <si>
     <t xml:space="preserve">2.55878829956055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52249360084534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67674684524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64045190811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87636876106262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83099961280823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6041567325592</t>
+    <t xml:space="preserve">2.52249336242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67674660682678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64045214653015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87636852264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83099985122681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60415697097778</t>
   </si>
   <si>
     <t xml:space="preserve">2.73118901252747</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">2.91266345977783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12135910987854</t>
+    <t xml:space="preserve">3.12135887145996</t>
   </si>
   <si>
     <t xml:space="preserve">3.0759904384613</t>
@@ -1427,46 +1427,46 @@
     <t xml:space="preserve">3.0941379070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38449668884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41171789169312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37542295455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42079162597656</t>
+    <t xml:space="preserve">3.38449692726135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41171765327454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37542319297791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42079138755798</t>
   </si>
   <si>
     <t xml:space="preserve">3.43893885612488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36634922027588</t>
+    <t xml:space="preserve">3.36634945869446</t>
   </si>
   <si>
     <t xml:space="preserve">3.35727572441101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20302224159241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27561211585999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29375982284546</t>
+    <t xml:space="preserve">3.20302248001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27561187744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29375958442688</t>
   </si>
   <si>
     <t xml:space="preserve">3.1667275428772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11228537559509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78563117980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84007358551025</t>
+    <t xml:space="preserve">3.11228513717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78563141822815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84007382392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.82192611694336</t>
@@ -1794,6 +1794,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.70000004768372</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61999988555908</t>
   </si>
 </sst>
 </file>
@@ -57096,7 +57099,7 @@
     </row>
     <row r="2115">
       <c r="A2115" s="1" t="n">
-        <v>46048.69125</v>
+        <v>46048.3333333333</v>
       </c>
       <c r="B2115" t="n">
         <v>32522</v>
@@ -57117,6 +57120,32 @@
         <v>584</v>
       </c>
       <c r="H2115" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2116">
+      <c r="A2116" s="1" t="n">
+        <v>46049.6911689815</v>
+      </c>
+      <c r="B2116" t="n">
+        <v>18549</v>
+      </c>
+      <c r="C2116" t="n">
+        <v>3.6800000667572</v>
+      </c>
+      <c r="D2116" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="E2116" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="F2116" t="n">
+        <v>3.61999988555908</v>
+      </c>
+      <c r="G2116" t="s">
+        <v>594</v>
+      </c>
+      <c r="H2116" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519899368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88901543617249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98013758659363</t>
+    <t xml:space="preserve">2.96519923210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88901519775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98013734817505</t>
   </si>
   <si>
     <t xml:space="preserve">2.97266817092896</t>
@@ -59,55 +59,55 @@
     <t xml:space="preserve">2.94577980041504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95773005485535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96221208572388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9353232383728</t>
+    <t xml:space="preserve">2.95773029327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96221160888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93532347679138</t>
   </si>
   <si>
     <t xml:space="preserve">2.91291618347168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9786434173584</t>
+    <t xml:space="preserve">2.97864365577698</t>
   </si>
   <si>
     <t xml:space="preserve">2.98611259460449</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03540802001953</t>
+    <t xml:space="preserve">3.03540825843811</t>
   </si>
   <si>
     <t xml:space="preserve">3.056321144104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0593090057373</t>
+    <t xml:space="preserve">3.05930924415588</t>
   </si>
   <si>
     <t xml:space="preserve">3.05034613609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98760652542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95026135444641</t>
+    <t xml:space="preserve">2.98760628700256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95026159286499</t>
   </si>
   <si>
     <t xml:space="preserve">3.01598858833313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01001358032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02495145797729</t>
+    <t xml:space="preserve">3.01001310348511</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02495169639587</t>
   </si>
   <si>
     <t xml:space="preserve">3.0174822807312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03092646598816</t>
+    <t xml:space="preserve">3.03092670440674</t>
   </si>
   <si>
     <t xml:space="preserve">2.99955677986145</t>
@@ -116,31 +116,31 @@
     <t xml:space="preserve">3.04437112808228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95922422409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00254440307617</t>
+    <t xml:space="preserve">2.959223985672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00254416465759</t>
   </si>
   <si>
     <t xml:space="preserve">2.92785429954529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90843510627747</t>
+    <t xml:space="preserve">2.90843486785889</t>
   </si>
   <si>
     <t xml:space="preserve">2.89648461341858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91889119148254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9159038066864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92038559913635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90544700622559</t>
+    <t xml:space="preserve">2.91889142990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91590356826782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92038536071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90544748306274</t>
   </si>
   <si>
     <t xml:space="preserve">2.90992856025696</t>
@@ -152,34 +152,34 @@
     <t xml:space="preserve">2.83822584152222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8606333732605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82627534866333</t>
+    <t xml:space="preserve">2.86063313484192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82627582550049</t>
   </si>
   <si>
     <t xml:space="preserve">2.77996754646301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84569478034973</t>
+    <t xml:space="preserve">2.84569501876831</t>
   </si>
   <si>
     <t xml:space="preserve">2.86810207366943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88303995132446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79639935493469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87557101249695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89797830581665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80088138580322</t>
+    <t xml:space="preserve">2.88304018974304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79639959335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87557125091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89797806739807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80088090896606</t>
   </si>
   <si>
     <t xml:space="preserve">2.74262261390686</t>
@@ -188,28 +188,28 @@
     <t xml:space="preserve">2.82179427146912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75009155273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76353597640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77847361564636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78594279289246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79341197013855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69631457328796</t>
+    <t xml:space="preserve">2.75009179115295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76353573799133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77847385406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78594303131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79341173171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69631481170654</t>
   </si>
   <si>
     <t xml:space="preserve">2.6515007019043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62162470817566</t>
+    <t xml:space="preserve">2.62162446975708</t>
   </si>
   <si>
     <t xml:space="preserve">2.53946566581726</t>
@@ -218,43 +218,43 @@
     <t xml:space="preserve">2.56934142112732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61415576934814</t>
+    <t xml:space="preserve">2.61415553092957</t>
   </si>
   <si>
     <t xml:space="preserve">2.65896940231323</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68884539604187</t>
+    <t xml:space="preserve">2.68884563446045</t>
   </si>
   <si>
     <t xml:space="preserve">2.70378375053406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77100491523743</t>
+    <t xml:space="preserve">2.77100467681885</t>
   </si>
   <si>
     <t xml:space="preserve">2.81581902503967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73365998268127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66643834114075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68137645721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74112892150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72619080543518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83075714111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89315056800842</t>
+    <t xml:space="preserve">2.7336597442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66643857955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68137669563293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74112868309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72619104385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8307569026947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.893150806427</t>
   </si>
   <si>
     <t xml:space="preserve">2.69871854782104</t>
@@ -263,34 +263,34 @@
     <t xml:space="preserve">2.83870983123779</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93203735351562</t>
+    <t xml:space="preserve">2.93203711509705</t>
   </si>
   <si>
     <t xml:space="preserve">2.87759613990784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83093237876892</t>
+    <t xml:space="preserve">2.8309326171875</t>
   </si>
   <si>
     <t xml:space="preserve">2.81537771224976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84648704528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79982304573059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73760509490967</t>
+    <t xml:space="preserve">2.84648680686951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79982328414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73760485649109</t>
   </si>
   <si>
     <t xml:space="preserve">2.76093673706055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80760025978088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00980997085571</t>
+    <t xml:space="preserve">2.80760049819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00980973243713</t>
   </si>
   <si>
     <t xml:space="preserve">2.9553689956665</t>
@@ -299,46 +299,46 @@
     <t xml:space="preserve">2.90870523452759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88537311553955</t>
+    <t xml:space="preserve">2.88537359237671</t>
   </si>
   <si>
     <t xml:space="preserve">2.82315516471863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86204171180725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00203251838684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91648244857788</t>
+    <t xml:space="preserve">2.86204147338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00203275680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91648268699646</t>
   </si>
   <si>
     <t xml:space="preserve">2.85426425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7298276424408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6831636428833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7220504283905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75315976142883</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70649576187134</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93981432914734</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99425530433655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97870087623596</t>
+    <t xml:space="preserve">2.72982740402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68316411972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72205066680908</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75315952301025</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70649600028992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93981456756592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99425506591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97870063781738</t>
   </si>
   <si>
     <t xml:space="preserve">2.86981868743896</t>
@@ -350,13 +350,13 @@
     <t xml:space="preserve">2.98647785186768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63650035858154</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.550950050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51984095573425</t>
+    <t xml:space="preserve">2.63650012016296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55095028877258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51984119415283</t>
   </si>
   <si>
     <t xml:space="preserve">2.41095876693726</t>
@@ -365,13 +365,13 @@
     <t xml:space="preserve">2.34096336364746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34874057769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3642954826355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2554132938385</t>
+    <t xml:space="preserve">2.34874105453491</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36429524421692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25541353225708</t>
   </si>
   <si>
     <t xml:space="preserve">2.24763607978821</t>
@@ -383,10 +383,10 @@
     <t xml:space="preserve">2.23208117485046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18541765213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27874517440796</t>
+    <t xml:space="preserve">2.18541741371155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2787446975708</t>
   </si>
   <si>
     <t xml:space="preserve">2.26319050788879</t>
@@ -398,40 +398,40 @@
     <t xml:space="preserve">2.06875824928284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1465311050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10764503479004</t>
+    <t xml:space="preserve">2.14653134346008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10764479637146</t>
   </si>
   <si>
     <t xml:space="preserve">2.15430808067322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17763996124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22430372238159</t>
+    <t xml:space="preserve">2.17764019966125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22430419921875</t>
   </si>
   <si>
     <t xml:space="preserve">2.35651779174805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48873162269592</t>
+    <t xml:space="preserve">2.4887318611145</t>
   </si>
   <si>
     <t xml:space="preserve">2.52761793136597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43429088592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44206786155701</t>
+    <t xml:space="preserve">2.43429112434387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44206809997559</t>
   </si>
   <si>
     <t xml:space="preserve">2.5587272644043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44984555244446</t>
+    <t xml:space="preserve">2.44984531402588</t>
   </si>
   <si>
     <t xml:space="preserve">2.37207245826721</t>
@@ -440,40 +440,40 @@
     <t xml:space="preserve">2.33318614959717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29429984092712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3798496723175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71427345275879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58205914497375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62872314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.659832239151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57428216934204</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67538666725159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64427757263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69094133377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76871395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90092802047729</t>
+    <t xml:space="preserve">2.29429960250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37984991073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71427297592163</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58205938339233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62872290611267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65983200073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57428169250488</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67538690567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64427781105042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69094109535217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76871418952942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90092778205872</t>
   </si>
   <si>
     <t xml:space="preserve">2.96314597129822</t>
@@ -482,7 +482,7 @@
     <t xml:space="preserve">2.92425990104675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97092342376709</t>
+    <t xml:space="preserve">2.97092366218567</t>
   </si>
   <si>
     <t xml:space="preserve">3.01758766174316</t>
@@ -494,19 +494,19 @@
     <t xml:space="preserve">3.03314208984375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06425070762634</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07980585098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0604989528656</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0281126499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0119194984436</t>
+    <t xml:space="preserve">3.06425094604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07980537414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06049919128418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02811288833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01191997528076</t>
   </si>
   <si>
     <t xml:space="preserve">3.10907816886902</t>
@@ -515,13 +515,13 @@
     <t xml:space="preserve">3.09288501739502</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1252715587616</t>
+    <t xml:space="preserve">3.12527132034302</t>
   </si>
   <si>
     <t xml:space="preserve">3.0766921043396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99572682380676</t>
+    <t xml:space="preserve">2.99572658538818</t>
   </si>
   <si>
     <t xml:space="preserve">3.30339574813843</t>
@@ -530,10 +530,10 @@
     <t xml:space="preserve">3.41674733161926</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35197496414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33578181266785</t>
+    <t xml:space="preserve">3.35197472572327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33578157424927</t>
   </si>
   <si>
     <t xml:space="preserve">3.36816811561584</t>
@@ -542,19 +542,19 @@
     <t xml:space="preserve">3.23862338066101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31958866119385</t>
+    <t xml:space="preserve">3.31958889961243</t>
   </si>
   <si>
     <t xml:space="preserve">3.27100944519043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28720235824585</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22242999076843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17385077476501</t>
+    <t xml:space="preserve">3.28720283508301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22243022918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17385101318359</t>
   </si>
   <si>
     <t xml:space="preserve">3.20623707771301</t>
@@ -566,28 +566,28 @@
     <t xml:space="preserve">3.40055441856384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49771332740784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38436102867126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25481629371643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19004392623901</t>
+    <t xml:space="preserve">3.49771356582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38436150550842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25481653213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19004416465759</t>
   </si>
   <si>
     <t xml:space="preserve">2.96334028244019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97953343391418</t>
+    <t xml:space="preserve">2.97953367233276</t>
   </si>
   <si>
     <t xml:space="preserve">2.80140924453735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88237476348877</t>
+    <t xml:space="preserve">2.88237452507019</t>
   </si>
   <si>
     <t xml:space="preserve">2.86618161201477</t>
@@ -599,28 +599,28 @@
     <t xml:space="preserve">2.78521633148193</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75282979011536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72044372558594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83379530906677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76902270317078</t>
+    <t xml:space="preserve">2.75283002853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72044348716736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83379578590393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76902294158936</t>
   </si>
   <si>
     <t xml:space="preserve">2.73663663864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81760215759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89856743812561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91476106643677</t>
+    <t xml:space="preserve">2.81760239601135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89856767654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91476082801819</t>
   </si>
   <si>
     <t xml:space="preserve">2.63947796821594</t>
@@ -635,10 +635,10 @@
     <t xml:space="preserve">2.68805718421936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70425033569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60709190368652</t>
+    <t xml:space="preserve">2.70425057411194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60709166526794</t>
   </si>
   <si>
     <t xml:space="preserve">2.59089875221252</t>
@@ -653,7 +653,7 @@
     <t xml:space="preserve">2.46135377883911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31561541557312</t>
+    <t xml:space="preserve">2.3156156539917</t>
   </si>
   <si>
     <t xml:space="preserve">2.2994225025177</t>
@@ -665,10 +665,10 @@
     <t xml:space="preserve">2.40607476234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28662443161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1330451965332</t>
+    <t xml:space="preserve">2.28662419319153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13304495811462</t>
   </si>
   <si>
     <t xml:space="preserve">2.08185195922852</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">2.03065896034241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16717338562012</t>
+    <t xml:space="preserve">2.16717386245728</t>
   </si>
   <si>
     <t xml:space="preserve">2.09891629219055</t>
@@ -689,34 +689,34 @@
     <t xml:space="preserve">2.26955986022949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2183666229248</t>
+    <t xml:space="preserve">2.21836686134338</t>
   </si>
   <si>
     <t xml:space="preserve">2.32075309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55965399742126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54258990287781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45726776123047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5767183303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62791156768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61084699630737</t>
+    <t xml:space="preserve">2.55965423583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54258966445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45726799964905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57671856880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62791132926941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61084723472595</t>
   </si>
   <si>
     <t xml:space="preserve">2.64497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59378266334534</t>
+    <t xml:space="preserve">2.59378290176392</t>
   </si>
   <si>
     <t xml:space="preserve">2.69616913795471</t>
@@ -725,16 +725,16 @@
     <t xml:space="preserve">2.71323323249817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44020318984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42313933372498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47433257102966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15010952949524</t>
+    <t xml:space="preserve">2.44020342826843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4231390953064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47433233261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15010929107666</t>
   </si>
   <si>
     <t xml:space="preserve">2.33781743049622</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">2.30368852615356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25249576568604</t>
+    <t xml:space="preserve">2.25249552726746</t>
   </si>
   <si>
     <t xml:space="preserve">2.23543095588684</t>
@@ -752,46 +752,46 @@
     <t xml:space="preserve">2.37194609642029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38901019096375</t>
+    <t xml:space="preserve">2.38901042938232</t>
   </si>
   <si>
     <t xml:space="preserve">2.20130252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18423819541931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01359438896179</t>
+    <t xml:space="preserve">2.18423795700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01359415054321</t>
   </si>
   <si>
     <t xml:space="preserve">2.04772329330444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11598062515259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91120839118958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87707960605621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84295094013214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97946584224701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86001539230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94533705711365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96240139007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99652993679047</t>
+    <t xml:space="preserve">2.11598038673401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91120827198029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8770797252655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84295105934143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97946560382843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86001527309418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94533717632294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96240162849426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99653005599976</t>
   </si>
   <si>
     <t xml:space="preserve">2.81561946868896</t>
@@ -803,10 +803,10 @@
     <t xml:space="preserve">2.88387680053711</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76442670822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73029756546021</t>
+    <t xml:space="preserve">2.76442646980286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73029780387878</t>
   </si>
   <si>
     <t xml:space="preserve">2.6791045665741</t>
@@ -821,16 +821,16 @@
     <t xml:space="preserve">2.86681246757507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79855489730835</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78149056434631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9350700378418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96919870376587</t>
+    <t xml:space="preserve">2.79855513572693</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78149080276489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93507027626038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96919894218445</t>
   </si>
   <si>
     <t xml:space="preserve">3.02039170265198</t>
@@ -842,7 +842,7 @@
     <t xml:space="preserve">3.03745603561401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98626303672791</t>
+    <t xml:space="preserve">2.98626327514648</t>
   </si>
   <si>
     <t xml:space="preserve">3.05452036857605</t>
@@ -857,10 +857,10 @@
     <t xml:space="preserve">3.11424589157104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13131022453308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06305241584778</t>
+    <t xml:space="preserve">3.1313099861145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06305265426636</t>
   </si>
   <si>
     <t xml:space="preserve">3.16543889045715</t>
@@ -869,10 +869,10 @@
     <t xml:space="preserve">3.19956755638123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15690684318542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23369598388672</t>
+    <t xml:space="preserve">3.15690660476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2336962223053</t>
   </si>
   <si>
     <t xml:space="preserve">3.2763569355011</t>
@@ -881,13 +881,13 @@
     <t xml:space="preserve">3.24222850799561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26782512664795</t>
+    <t xml:space="preserve">3.26782488822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.31048607826233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34461450576782</t>
+    <t xml:space="preserve">3.34461498260498</t>
   </si>
   <si>
     <t xml:space="preserve">3.32755017280579</t>
@@ -896,25 +896,25 @@
     <t xml:space="preserve">3.28488922119141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18250322341919</t>
+    <t xml:space="preserve">3.18250298500061</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29342126846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33710074424744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32836508750916</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342150688171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33710074424744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32836508750916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29342174530029</t>
-  </si>
-  <si>
     <t xml:space="preserve">3.24974226951599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20606303215027</t>
+    <t xml:space="preserve">3.20606279373169</t>
   </si>
   <si>
     <t xml:space="preserve">3.15364766120911</t>
@@ -935,7 +935,7 @@
     <t xml:space="preserve">3.49434638023376</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58170509338379</t>
+    <t xml:space="preserve">3.58170533180237</t>
   </si>
   <si>
     <t xml:space="preserve">3.56423330307007</t>
@@ -944,22 +944,22 @@
     <t xml:space="preserve">3.59044098854065</t>
   </si>
   <si>
-    <t xml:space="preserve">3.50308275222778</t>
+    <t xml:space="preserve">3.5030825138092</t>
   </si>
   <si>
     <t xml:space="preserve">3.51181840896606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54676151275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63412022590637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62538480758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74768662452698</t>
+    <t xml:space="preserve">3.54676175117493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63411998748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62538456916809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7476863861084</t>
   </si>
   <si>
     <t xml:space="preserve">3.69527149200439</t>
@@ -974,7 +974,7 @@
     <t xml:space="preserve">3.55549788475037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66032791137695</t>
+    <t xml:space="preserve">3.66032814979553</t>
   </si>
   <si>
     <t xml:space="preserve">3.65159201622009</t>
@@ -983,7 +983,7 @@
     <t xml:space="preserve">3.68653535842896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70400714874268</t>
+    <t xml:space="preserve">3.7040069103241</t>
   </si>
   <si>
     <t xml:space="preserve">3.75642251968384</t>
@@ -995,16 +995,16 @@
     <t xml:space="preserve">3.53802585601807</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34583687782288</t>
+    <t xml:space="preserve">3.3458366394043</t>
   </si>
   <si>
     <t xml:space="preserve">3.38951635360718</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42445945739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45066714286804</t>
+    <t xml:space="preserve">3.42445969581604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45066738128662</t>
   </si>
   <si>
     <t xml:space="preserve">3.44193148612976</t>
@@ -1019,7 +1019,7 @@
     <t xml:space="preserve">3.35457253456116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45940327644348</t>
+    <t xml:space="preserve">3.4594030380249</t>
   </si>
   <si>
     <t xml:space="preserve">3.52928996086121</t>
@@ -1034,34 +1034,34 @@
     <t xml:space="preserve">3.79136610031128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7214789390564</t>
+    <t xml:space="preserve">3.72147917747498</t>
   </si>
   <si>
     <t xml:space="preserve">3.87872457504272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17574453353882</t>
+    <t xml:space="preserve">4.17574405670166</t>
   </si>
   <si>
     <t xml:space="preserve">4.31551790237427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35046148300171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1844801902771</t>
+    <t xml:space="preserve">4.35046100616455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.18447971343994</t>
   </si>
   <si>
     <t xml:space="preserve">4.20195150375366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25436639785767</t>
+    <t xml:space="preserve">4.25436687469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493178367615</t>
+    <t xml:space="preserve">3.90493226051331</t>
   </si>
   <si>
     <t xml:space="preserve">3.98355507850647</t>
@@ -1079,37 +1079,37 @@
     <t xml:space="preserve">4.07091379165649</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1233286857605</t>
+    <t xml:space="preserve">4.12332820892334</t>
   </si>
   <si>
     <t xml:space="preserve">4.00102663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00976228713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93987607955933</t>
+    <t xml:space="preserve">4.00976276397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93987560272217</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21068716049194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.29804611206055</t>
+    <t xml:space="preserve">4.2106876373291</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.29804658889771</t>
   </si>
   <si>
     <t xml:space="preserve">4.28930997848511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21942377090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19321584701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1495361328125</t>
+    <t xml:space="preserve">4.21942329406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19321632385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14953660964966</t>
   </si>
   <si>
     <t xml:space="preserve">4.16700839996338</t>
@@ -1121,22 +1121,22 @@
     <t xml:space="preserve">4.06217765808105</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78262996673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80010151863098</t>
+    <t xml:space="preserve">3.78263020515442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80010175704956</t>
   </si>
   <si>
     <t xml:space="preserve">3.82630968093872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83504486083984</t>
+    <t xml:space="preserve">3.835045337677</t>
   </si>
   <si>
     <t xml:space="preserve">3.84378123283386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77389430999756</t>
+    <t xml:space="preserve">3.77389454841614</t>
   </si>
   <si>
     <t xml:space="preserve">4.03597021102905</t>
@@ -1151,13 +1151,13 @@
     <t xml:space="preserve">3.861252784729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7651584148407</t>
+    <t xml:space="preserve">3.76515817642212</t>
   </si>
   <si>
     <t xml:space="preserve">3.8175733089447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64285635948181</t>
+    <t xml:space="preserve">3.64285612106323</t>
   </si>
   <si>
     <t xml:space="preserve">3.67779970169067</t>
@@ -1181,10 +1181,10 @@
     <t xml:space="preserve">3.39825224876404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23227071762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0575532913208</t>
+    <t xml:space="preserve">3.23227047920227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05755352973938</t>
   </si>
   <si>
     <t xml:space="preserve">2.97019457817078</t>
@@ -1193,10 +1193,10 @@
     <t xml:space="preserve">2.95272278785706</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91777920722961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90904331207275</t>
+    <t xml:space="preserve">2.91777944564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90904355049133</t>
   </si>
   <si>
     <t xml:space="preserve">3.37204432487488</t>
@@ -57180,7 +57180,7 @@
     </row>
     <row r="2118">
       <c r="A2118" s="1" t="n">
-        <v>46051.6910185185</v>
+        <v>46051.3333333333</v>
       </c>
       <c r="B2118" t="n">
         <v>42367</v>
@@ -57201,6 +57201,32 @@
         <v>595</v>
       </c>
       <c r="H2118" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2119">
+      <c r="A2119" s="1" t="n">
+        <v>46052.6003819444</v>
+      </c>
+      <c r="B2119" t="n">
+        <v>11169</v>
+      </c>
+      <c r="C2119" t="n">
+        <v>3.64000010490417</v>
+      </c>
+      <c r="D2119" t="n">
+        <v>3.53999996185303</v>
+      </c>
+      <c r="E2119" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="F2119" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="G2119" t="s">
+        <v>582</v>
+      </c>
+      <c r="H2119" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="596" uniqueCount="596">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="597" uniqueCount="597">
   <si>
     <t xml:space="preserve">date</t>
   </si>
@@ -47,16 +47,16 @@
     <t xml:space="preserve">2.96519923210144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88901519775391</t>
+    <t xml:space="preserve">2.88901543617249</t>
   </si>
   <si>
     <t xml:space="preserve">2.98013734817505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97266817092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94577980041504</t>
+    <t xml:space="preserve">2.97266793251038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94578003883362</t>
   </si>
   <si>
     <t xml:space="preserve">2.95773029327393</t>
@@ -65,13 +65,13 @@
     <t xml:space="preserve">2.96221160888672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93532347679138</t>
+    <t xml:space="preserve">2.9353232383728</t>
   </si>
   <si>
     <t xml:space="preserve">2.91291618347168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97864365577698</t>
+    <t xml:space="preserve">2.9786434173584</t>
   </si>
   <si>
     <t xml:space="preserve">2.98611259460449</t>
@@ -80,28 +80,28 @@
     <t xml:space="preserve">3.03540825843811</t>
   </si>
   <si>
-    <t xml:space="preserve">3.056321144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05930924415588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05034613609314</t>
+    <t xml:space="preserve">3.05632138252258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05930948257446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05034589767456</t>
   </si>
   <si>
     <t xml:space="preserve">2.98760628700256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95026159286499</t>
+    <t xml:space="preserve">2.95026135444641</t>
   </si>
   <si>
     <t xml:space="preserve">3.01598858833313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01001310348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02495169639587</t>
+    <t xml:space="preserve">3.01001334190369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02495145797729</t>
   </si>
   <si>
     <t xml:space="preserve">3.0174822807312</t>
@@ -110,55 +110,55 @@
     <t xml:space="preserve">3.03092670440674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99955677986145</t>
+    <t xml:space="preserve">2.99955654144287</t>
   </si>
   <si>
     <t xml:space="preserve">3.04437112808228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.959223985672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00254416465759</t>
+    <t xml:space="preserve">2.95922422409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00254440307617</t>
   </si>
   <si>
     <t xml:space="preserve">2.92785429954529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90843486785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89648461341858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91889142990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91590356826782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92038536071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90544748306274</t>
+    <t xml:space="preserve">2.90843510627747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91889119148254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9159038066864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92038512229919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90544724464417</t>
   </si>
   <si>
     <t xml:space="preserve">2.90992856025696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9233729839325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83822584152222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86063313484192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82627582550049</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77996754646301</t>
+    <t xml:space="preserve">2.92337274551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8382260799408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8606333732605</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82627558708191</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77996778488159</t>
   </si>
   <si>
     <t xml:space="preserve">2.84569501876831</t>
@@ -167,7 +167,7 @@
     <t xml:space="preserve">2.86810207366943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88304018974304</t>
+    <t xml:space="preserve">2.88303995132446</t>
   </si>
   <si>
     <t xml:space="preserve">2.79639959335327</t>
@@ -176,10 +176,10 @@
     <t xml:space="preserve">2.87557125091553</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89797806739807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80088090896606</t>
+    <t xml:space="preserve">2.89797782897949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80088114738464</t>
   </si>
   <si>
     <t xml:space="preserve">2.74262261390686</t>
@@ -200,7 +200,7 @@
     <t xml:space="preserve">2.78594303131104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79341173171997</t>
+    <t xml:space="preserve">2.79341197013855</t>
   </si>
   <si>
     <t xml:space="preserve">2.69631481170654</t>
@@ -209,19 +209,19 @@
     <t xml:space="preserve">2.6515007019043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62162446975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53946566581726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56934142112732</t>
+    <t xml:space="preserve">2.62162470817566</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53946542739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5693416595459</t>
   </si>
   <si>
     <t xml:space="preserve">2.61415553092957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65896940231323</t>
+    <t xml:space="preserve">2.65896964073181</t>
   </si>
   <si>
     <t xml:space="preserve">2.68884563446045</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">2.70378375053406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77100467681885</t>
+    <t xml:space="preserve">2.77100491523743</t>
   </si>
   <si>
     <t xml:space="preserve">2.81581902503967</t>
@@ -239,31 +239,31 @@
     <t xml:space="preserve">2.7336597442627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66643857955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68137669563293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74112868309021</t>
+    <t xml:space="preserve">2.66643881797791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68137693405151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74112892150879</t>
   </si>
   <si>
     <t xml:space="preserve">2.72619104385376</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8307569026947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.893150806427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69871854782104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83870983123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93203711509705</t>
+    <t xml:space="preserve">2.83075737953186</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89315104484558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69871878623962</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83870959281921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93203687667847</t>
   </si>
   <si>
     <t xml:space="preserve">2.87759613990784</t>
@@ -275,10 +275,10 @@
     <t xml:space="preserve">2.81537771224976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84648680686951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79982328414917</t>
+    <t xml:space="preserve">2.84648656845093</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79982304573059</t>
   </si>
   <si>
     <t xml:space="preserve">2.73760485649109</t>
@@ -290,40 +290,40 @@
     <t xml:space="preserve">2.80760049819946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00980973243713</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9553689956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90870523452759</t>
+    <t xml:space="preserve">3.00980997085571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95536923408508</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90870499610901</t>
   </si>
   <si>
     <t xml:space="preserve">2.88537359237671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82315516471863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86204147338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00203275680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91648268699646</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85426425933838</t>
+    <t xml:space="preserve">2.82315540313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86204171180725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00203251838684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91648244857788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8542640209198</t>
   </si>
   <si>
     <t xml:space="preserve">2.72982740402222</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68316411972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72205066680908</t>
+    <t xml:space="preserve">2.68316388130188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7220504283905</t>
   </si>
   <si>
     <t xml:space="preserve">2.75315952301025</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">2.93981456756592</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99425506591797</t>
+    <t xml:space="preserve">2.99425530433655</t>
   </si>
   <si>
     <t xml:space="preserve">2.97870063781738</t>
@@ -344,34 +344,34 @@
     <t xml:space="preserve">2.86981868743896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94759154319763</t>
+    <t xml:space="preserve">2.94759178161621</t>
   </si>
   <si>
     <t xml:space="preserve">2.98647785186768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63650012016296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55095028877258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51984119415283</t>
+    <t xml:space="preserve">2.63650035858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.550950050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51984095573425</t>
   </si>
   <si>
     <t xml:space="preserve">2.41095876693726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34096336364746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34874105453491</t>
+    <t xml:space="preserve">2.34096312522888</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34874081611633</t>
   </si>
   <si>
     <t xml:space="preserve">2.36429524421692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25541353225708</t>
+    <t xml:space="preserve">2.2554132938385</t>
   </si>
   <si>
     <t xml:space="preserve">2.24763607978821</t>
@@ -380,13 +380,13 @@
     <t xml:space="preserve">2.3254086971283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23208117485046</t>
+    <t xml:space="preserve">2.23208141326904</t>
   </si>
   <si>
     <t xml:space="preserve">2.18541741371155</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2787446975708</t>
+    <t xml:space="preserve">2.27874493598938</t>
   </si>
   <si>
     <t xml:space="preserve">2.26319050788879</t>
@@ -398,22 +398,22 @@
     <t xml:space="preserve">2.06875824928284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14653134346008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10764479637146</t>
+    <t xml:space="preserve">2.1465311050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10764503479004</t>
   </si>
   <si>
     <t xml:space="preserve">2.15430808067322</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17764019966125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22430419921875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35651779174805</t>
+    <t xml:space="preserve">2.17764043807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22430396080017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35651803016663</t>
   </si>
   <si>
     <t xml:space="preserve">2.4887318611145</t>
@@ -422,25 +422,25 @@
     <t xml:space="preserve">2.52761793136597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43429112434387</t>
+    <t xml:space="preserve">2.43429088592529</t>
   </si>
   <si>
     <t xml:space="preserve">2.44206809997559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5587272644043</t>
+    <t xml:space="preserve">2.55872702598572</t>
   </si>
   <si>
     <t xml:space="preserve">2.44984531402588</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37207245826721</t>
+    <t xml:space="preserve">2.37207221984863</t>
   </si>
   <si>
     <t xml:space="preserve">2.33318614959717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29429960250854</t>
+    <t xml:space="preserve">2.29429984092712</t>
   </si>
   <si>
     <t xml:space="preserve">2.37984991073608</t>
@@ -449,7 +449,7 @@
     <t xml:space="preserve">2.71427297592163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58205938339233</t>
+    <t xml:space="preserve">2.58205914497375</t>
   </si>
   <si>
     <t xml:space="preserve">2.62872290611267</t>
@@ -458,16 +458,16 @@
     <t xml:space="preserve">2.65983200073242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57428169250488</t>
+    <t xml:space="preserve">2.57428193092346</t>
   </si>
   <si>
     <t xml:space="preserve">2.67538690567017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64427781105042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69094109535217</t>
+    <t xml:space="preserve">2.64427757263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69094133377075</t>
   </si>
   <si>
     <t xml:space="preserve">2.76871418952942</t>
@@ -482,28 +482,28 @@
     <t xml:space="preserve">2.92425990104675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97092366218567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01758766174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04869651794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03314208984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06425094604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07980537414551</t>
+    <t xml:space="preserve">2.97092318534851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01758742332458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04869675636292</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03314161300659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0642511844635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07980561256409</t>
   </si>
   <si>
     <t xml:space="preserve">3.06049919128418</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02811288833618</t>
+    <t xml:space="preserve">3.0281126499176</t>
   </si>
   <si>
     <t xml:space="preserve">3.01191997528076</t>
@@ -518,7 +518,7 @@
     <t xml:space="preserve">3.12527132034302</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0766921043396</t>
+    <t xml:space="preserve">3.07669234275818</t>
   </si>
   <si>
     <t xml:space="preserve">2.99572658538818</t>
@@ -548,13 +548,13 @@
     <t xml:space="preserve">3.27100944519043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28720283508301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22243022918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17385101318359</t>
+    <t xml:space="preserve">3.28720259666443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22242999076843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17385125160217</t>
   </si>
   <si>
     <t xml:space="preserve">3.20623707771301</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">3.19004416465759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96334028244019</t>
+    <t xml:space="preserve">2.96334004402161</t>
   </si>
   <si>
     <t xml:space="preserve">2.97953367233276</t>
@@ -587,7 +587,7 @@
     <t xml:space="preserve">2.80140924453735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88237452507019</t>
+    <t xml:space="preserve">2.88237476348877</t>
   </si>
   <si>
     <t xml:space="preserve">2.86618161201477</t>
@@ -605,7 +605,7 @@
     <t xml:space="preserve">2.72044348716736</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83379578590393</t>
+    <t xml:space="preserve">2.83379554748535</t>
   </si>
   <si>
     <t xml:space="preserve">2.76902294158936</t>
@@ -614,7 +614,7 @@
     <t xml:space="preserve">2.73663663864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81760239601135</t>
+    <t xml:space="preserve">2.81760263442993</t>
   </si>
   <si>
     <t xml:space="preserve">2.89856767654419</t>
@@ -623,16 +623,16 @@
     <t xml:space="preserve">2.91476082801819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63947796821594</t>
+    <t xml:space="preserve">2.63947820663452</t>
   </si>
   <si>
     <t xml:space="preserve">2.67186427116394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62328481674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68805718421936</t>
+    <t xml:space="preserve">2.62328505516052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68805742263794</t>
   </si>
   <si>
     <t xml:space="preserve">2.70425057411194</t>
@@ -644,7 +644,7 @@
     <t xml:space="preserve">2.59089875221252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42896747589111</t>
+    <t xml:space="preserve">2.42896771430969</t>
   </si>
   <si>
     <t xml:space="preserve">2.54231929779053</t>
@@ -1800,6 +1800,9 @@
   </si>
   <si>
     <t xml:space="preserve">3.55999994277954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53999996185303</t>
   </si>
 </sst>
 </file>
@@ -57206,10 +57209,10 @@
     </row>
     <row r="2119">
       <c r="A2119" s="1" t="n">
-        <v>46052.6003819444</v>
+        <v>46052.3333333333</v>
       </c>
       <c r="B2119" t="n">
-        <v>11169</v>
+        <v>11202</v>
       </c>
       <c r="C2119" t="n">
         <v>3.64000010490417</v>
@@ -57221,12 +57224,38 @@
         <v>3.59999990463257</v>
       </c>
       <c r="F2119" t="n">
+        <v>3.53999996185303</v>
+      </c>
+      <c r="G2119" t="s">
+        <v>596</v>
+      </c>
+      <c r="H2119" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2120">
+      <c r="A2120" s="1" t="n">
+        <v>46055.6912384259</v>
+      </c>
+      <c r="B2120" t="n">
+        <v>5491</v>
+      </c>
+      <c r="C2120" t="n">
         <v>3.57999992370605</v>
       </c>
-      <c r="G2119" t="s">
+      <c r="D2120" t="n">
+        <v>3.53999996185303</v>
+      </c>
+      <c r="E2120" t="n">
+        <v>3.53999996185303</v>
+      </c>
+      <c r="F2120" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="G2120" t="s">
         <v>582</v>
       </c>
-      <c r="H2119" t="s">
+      <c r="H2120" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02345752716064</t>
+    <t xml:space="preserve">3.02345776557922</t>
   </si>
   <si>
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519923210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88901543617249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98013734817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97266793251038</t>
+    <t xml:space="preserve">2.96519899368286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88901519775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98013758659363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97266817092896</t>
   </si>
   <si>
     <t xml:space="preserve">2.94578003883362</t>
@@ -65,40 +65,40 @@
     <t xml:space="preserve">2.96221160888672</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9353232383728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91291618347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9786434173584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98611259460449</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03540825843811</t>
+    <t xml:space="preserve">2.93532299995422</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91291642189026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97864365577698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98611235618591</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03540802001953</t>
   </si>
   <si>
     <t xml:space="preserve">3.05632138252258</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05930948257446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05034589767456</t>
+    <t xml:space="preserve">3.05930876731873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05034613609314</t>
   </si>
   <si>
     <t xml:space="preserve">2.98760628700256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95026135444641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01598858833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01001334190369</t>
+    <t xml:space="preserve">2.95026159286499</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01598882675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01001358032227</t>
   </si>
   <si>
     <t xml:space="preserve">3.02495145797729</t>
@@ -107,7 +107,7 @@
     <t xml:space="preserve">3.0174822807312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03092670440674</t>
+    <t xml:space="preserve">3.03092646598816</t>
   </si>
   <si>
     <t xml:space="preserve">2.99955654144287</t>
@@ -116,43 +116,43 @@
     <t xml:space="preserve">3.04437112808228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95922422409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00254440307617</t>
+    <t xml:space="preserve">2.95922374725342</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00254464149475</t>
   </si>
   <si>
     <t xml:space="preserve">2.92785429954529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90843510627747</t>
+    <t xml:space="preserve">2.90843486785889</t>
   </si>
   <si>
     <t xml:space="preserve">2.896484375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91889119148254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9159038066864</t>
+    <t xml:space="preserve">2.91889142990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91590404510498</t>
   </si>
   <si>
     <t xml:space="preserve">2.92038512229919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90544724464417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90992856025696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92337274551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8382260799408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8606333732605</t>
+    <t xml:space="preserve">2.90544700622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90992832183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9233729839325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83822584152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86063313484192</t>
   </si>
   <si>
     <t xml:space="preserve">2.82627558708191</t>
@@ -164,19 +164,19 @@
     <t xml:space="preserve">2.84569501876831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86810207366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88303995132446</t>
+    <t xml:space="preserve">2.86810183525085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88304018974304</t>
   </si>
   <si>
     <t xml:space="preserve">2.79639959335327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87557125091553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89797782897949</t>
+    <t xml:space="preserve">2.87557101249695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89797830581665</t>
   </si>
   <si>
     <t xml:space="preserve">2.80088114738464</t>
@@ -185,61 +185,61 @@
     <t xml:space="preserve">2.74262261390686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82179427146912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75009179115295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76353573799133</t>
+    <t xml:space="preserve">2.82179474830627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75009155273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76353621482849</t>
   </si>
   <si>
     <t xml:space="preserve">2.77847385406494</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78594303131104</t>
+    <t xml:space="preserve">2.78594279289246</t>
   </si>
   <si>
     <t xml:space="preserve">2.79341197013855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69631481170654</t>
+    <t xml:space="preserve">2.69631457328796</t>
   </si>
   <si>
     <t xml:space="preserve">2.6515007019043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62162470817566</t>
+    <t xml:space="preserve">2.6216242313385</t>
   </si>
   <si>
     <t xml:space="preserve">2.53946542739868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5693416595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61415553092957</t>
+    <t xml:space="preserve">2.56934142112732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61415576934814</t>
   </si>
   <si>
     <t xml:space="preserve">2.65896964073181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68884563446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70378375053406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77100491523743</t>
+    <t xml:space="preserve">2.68884539604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70378398895264</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77100467681885</t>
   </si>
   <si>
     <t xml:space="preserve">2.81581902503967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7336597442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66643881797791</t>
+    <t xml:space="preserve">2.73366022109985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66643857955933</t>
   </si>
   <si>
     <t xml:space="preserve">2.68137693405151</t>
@@ -248,40 +248,40 @@
     <t xml:space="preserve">2.74112892150879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72619104385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83075737953186</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89315104484558</t>
+    <t xml:space="preserve">2.72619080543518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83075714111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89315056800842</t>
   </si>
   <si>
     <t xml:space="preserve">2.69871878623962</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83870959281921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93203687667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87759613990784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8309326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81537771224976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84648656845093</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79982304573059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73760485649109</t>
+    <t xml:space="preserve">2.83870983123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93203711509705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87759637832642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83093237876892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81537795066833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84648728370667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79982328414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73760461807251</t>
   </si>
   <si>
     <t xml:space="preserve">2.76093673706055</t>
@@ -293,13 +293,13 @@
     <t xml:space="preserve">3.00980997085571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95536923408508</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90870499610901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88537359237671</t>
+    <t xml:space="preserve">2.95536875724792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90870523452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88537311553955</t>
   </si>
   <si>
     <t xml:space="preserve">2.82315540313721</t>
@@ -308,16 +308,16 @@
     <t xml:space="preserve">2.86204171180725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00203251838684</t>
+    <t xml:space="preserve">3.00203275680542</t>
   </si>
   <si>
     <t xml:space="preserve">2.91648244857788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8542640209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72982740402222</t>
+    <t xml:space="preserve">2.85426449775696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7298276424408</t>
   </si>
   <si>
     <t xml:space="preserve">2.68316388130188</t>
@@ -329,25 +329,25 @@
     <t xml:space="preserve">2.75315952301025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70649600028992</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93981456756592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99425530433655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97870063781738</t>
+    <t xml:space="preserve">2.70649576187134</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93981409072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99425554275513</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97870087623596</t>
   </si>
   <si>
     <t xml:space="preserve">2.86981868743896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94759178161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98647785186768</t>
+    <t xml:space="preserve">2.94759154319763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98647809028625</t>
   </si>
   <si>
     <t xml:space="preserve">2.63650035858154</t>
@@ -356,31 +356,31 @@
     <t xml:space="preserve">2.550950050354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51984095573425</t>
+    <t xml:space="preserve">2.51984119415283</t>
   </si>
   <si>
     <t xml:space="preserve">2.41095876693726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34096312522888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34874081611633</t>
+    <t xml:space="preserve">2.34096336364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34874057769775</t>
   </si>
   <si>
     <t xml:space="preserve">2.36429524421692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2554132938385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24763607978821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3254086971283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23208141326904</t>
+    <t xml:space="preserve">2.25541305541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24763584136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32540893554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23208117485046</t>
   </si>
   <si>
     <t xml:space="preserve">2.18541741371155</t>
@@ -395,22 +395,22 @@
     <t xml:space="preserve">2.21652674674988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06875824928284</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1465311050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10764503479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15430808067322</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17764043807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22430396080017</t>
+    <t xml:space="preserve">2.06875801086426</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14653134346008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10764479637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15430855751038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17764019966125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22430372238159</t>
   </si>
   <si>
     <t xml:space="preserve">2.35651803016663</t>
@@ -419,118 +419,118 @@
     <t xml:space="preserve">2.4887318611145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52761793136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43429088592529</t>
+    <t xml:space="preserve">2.52761816978455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43429064750671</t>
   </si>
   <si>
     <t xml:space="preserve">2.44206809997559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55872702598572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44984531402588</t>
+    <t xml:space="preserve">2.55872750282288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44984555244446</t>
   </si>
   <si>
     <t xml:space="preserve">2.37207221984863</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33318614959717</t>
+    <t xml:space="preserve">2.33318591117859</t>
   </si>
   <si>
     <t xml:space="preserve">2.29429984092712</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37984991073608</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71427297592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58205914497375</t>
+    <t xml:space="preserve">2.3798496723175</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71427321434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58205890655518</t>
   </si>
   <si>
     <t xml:space="preserve">2.62872290611267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65983200073242</t>
+    <t xml:space="preserve">2.659832239151</t>
   </si>
   <si>
     <t xml:space="preserve">2.57428193092346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67538690567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64427757263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69094133377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76871418952942</t>
+    <t xml:space="preserve">2.67538666725159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64427781105042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69094109535217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76871395111084</t>
   </si>
   <si>
     <t xml:space="preserve">2.90092778205872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96314597129822</t>
+    <t xml:space="preserve">2.9631462097168</t>
   </si>
   <si>
     <t xml:space="preserve">2.92425990104675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97092318534851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01758742332458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04869675636292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03314161300659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0642511844635</t>
+    <t xml:space="preserve">2.97092342376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01758766174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04869651794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03314208984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06425094604492</t>
   </si>
   <si>
     <t xml:space="preserve">3.07980561256409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06049919128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0281126499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01191997528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10907816886902</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09288501739502</t>
+    <t xml:space="preserve">3.06049871444702</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02811288833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0119194984436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1090784072876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0928852558136</t>
   </si>
   <si>
     <t xml:space="preserve">3.12527132034302</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07669234275818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99572658538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30339574813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41674733161926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35197472572327</t>
+    <t xml:space="preserve">3.0766921043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99572682380676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30339598655701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41674780845642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35197520256042</t>
   </si>
   <si>
     <t xml:space="preserve">3.33578157424927</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">3.36816811561584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23862338066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31958889961243</t>
+    <t xml:space="preserve">3.23862314224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31958866119385</t>
   </si>
   <si>
     <t xml:space="preserve">3.27100944519043</t>
@@ -551,25 +551,25 @@
     <t xml:space="preserve">3.28720259666443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22242999076843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17385125160217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20623707771301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1414647102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40055441856384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49771356582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38436150550842</t>
+    <t xml:space="preserve">3.22243022918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17385077476501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20623731613159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14146494865417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40055418014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49771332740784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38436126708984</t>
   </si>
   <si>
     <t xml:space="preserve">3.25481653213501</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">3.19004416465759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96334004402161</t>
+    <t xml:space="preserve">2.96334052085876</t>
   </si>
   <si>
     <t xml:space="preserve">2.97953367233276</t>
@@ -593,28 +593,28 @@
     <t xml:space="preserve">2.86618161201477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84998846054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78521633148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75283002853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72044348716736</t>
+    <t xml:space="preserve">2.84998822212219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78521609306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75282979011536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72044372558594</t>
   </si>
   <si>
     <t xml:space="preserve">2.83379554748535</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76902294158936</t>
+    <t xml:space="preserve">2.76902318000793</t>
   </si>
   <si>
     <t xml:space="preserve">2.73663663864136</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81760263442993</t>
+    <t xml:space="preserve">2.81760239601135</t>
   </si>
   <si>
     <t xml:space="preserve">2.89856767654419</t>
@@ -623,28 +623,28 @@
     <t xml:space="preserve">2.91476082801819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63947820663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67186427116394</t>
+    <t xml:space="preserve">2.63947796821594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67186403274536</t>
   </si>
   <si>
     <t xml:space="preserve">2.62328505516052</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68805742263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70425057411194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60709166526794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59089875221252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42896771430969</t>
+    <t xml:space="preserve">2.68805718421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70425009727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60709190368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59089851379395</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42896723747253</t>
   </si>
   <si>
     <t xml:space="preserve">2.54231929779053</t>
@@ -653,10 +653,10 @@
     <t xml:space="preserve">2.46135377883911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3156156539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2994225025177</t>
+    <t xml:space="preserve">2.31561541557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29942274093628</t>
   </si>
   <si>
     <t xml:space="preserve">2.35488176345825</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">2.40607476234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28662419319153</t>
+    <t xml:space="preserve">2.28662443161011</t>
   </si>
   <si>
     <t xml:space="preserve">2.13304495811462</t>
@@ -680,7 +680,7 @@
     <t xml:space="preserve">2.03065896034241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16717386245728</t>
+    <t xml:space="preserve">2.1671736240387</t>
   </si>
   <si>
     <t xml:space="preserve">2.09891629219055</t>
@@ -689,19 +689,19 @@
     <t xml:space="preserve">2.26955986022949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21836686134338</t>
+    <t xml:space="preserve">2.2183666229248</t>
   </si>
   <si>
     <t xml:space="preserve">2.32075309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55965423583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54258966445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45726799964905</t>
+    <t xml:space="preserve">2.55965399742126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54258990287781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45726823806763</t>
   </si>
   <si>
     <t xml:space="preserve">2.57671856880188</t>
@@ -710,7 +710,7 @@
     <t xml:space="preserve">2.62791132926941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61084723472595</t>
+    <t xml:space="preserve">2.61084699630737</t>
   </si>
   <si>
     <t xml:space="preserve">2.64497566223145</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">2.59378290176392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69616913795471</t>
+    <t xml:space="preserve">2.69616889953613</t>
   </si>
   <si>
     <t xml:space="preserve">2.71323323249817</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">2.44020342826843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4231390953064</t>
+    <t xml:space="preserve">2.42313933372498</t>
   </si>
   <si>
     <t xml:space="preserve">2.47433233261108</t>
@@ -737,16 +737,16 @@
     <t xml:space="preserve">2.15010929107666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33781743049622</t>
+    <t xml:space="preserve">2.33781719207764</t>
   </si>
   <si>
     <t xml:space="preserve">2.30368852615356</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25249552726746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23543095588684</t>
+    <t xml:space="preserve">2.25249576568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23543119430542</t>
   </si>
   <si>
     <t xml:space="preserve">2.37194609642029</t>
@@ -761,40 +761,40 @@
     <t xml:space="preserve">2.18423795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01359415054321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04772329330444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11598038673401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91120827198029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8770797252655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84295105934143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97946560382843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86001527309418</t>
+    <t xml:space="preserve">2.01359438896179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04772305488586</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11598062515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91120851039886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87707960605621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84295094013214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97946584224701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86001539230347</t>
   </si>
   <si>
     <t xml:space="preserve">1.94533717632294</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96240162849426</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99653005599976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81561946868896</t>
+    <t xml:space="preserve">1.96240127086639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99652993679047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81561923027039</t>
   </si>
   <si>
     <t xml:space="preserve">2.90094137191772</t>
@@ -806,7 +806,7 @@
     <t xml:space="preserve">2.76442646980286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73029780387878</t>
+    <t xml:space="preserve">2.73029756546021</t>
   </si>
   <si>
     <t xml:space="preserve">2.6791045665741</t>
@@ -815,7 +815,7 @@
     <t xml:space="preserve">2.74736189842224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.832683801651</t>
+    <t xml:space="preserve">2.83268356323242</t>
   </si>
   <si>
     <t xml:space="preserve">2.86681246757507</t>
@@ -824,25 +824,25 @@
     <t xml:space="preserve">2.79855513572693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78149080276489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93507027626038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96919894218445</t>
+    <t xml:space="preserve">2.78149056434631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9350700378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96919870376587</t>
   </si>
   <si>
     <t xml:space="preserve">3.02039170265198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00332736968994</t>
+    <t xml:space="preserve">3.00332713127136</t>
   </si>
   <si>
     <t xml:space="preserve">3.03745603561401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98626327514648</t>
+    <t xml:space="preserve">2.98626303672791</t>
   </si>
   <si>
     <t xml:space="preserve">3.05452036857605</t>
@@ -857,64 +857,64 @@
     <t xml:space="preserve">3.11424589157104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1313099861145</t>
+    <t xml:space="preserve">3.13131022453308</t>
   </si>
   <si>
     <t xml:space="preserve">3.06305265426636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16543889045715</t>
+    <t xml:space="preserve">3.16543865203857</t>
   </si>
   <si>
     <t xml:space="preserve">3.19956755638123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15690660476685</t>
+    <t xml:space="preserve">3.15690684318542</t>
   </si>
   <si>
     <t xml:space="preserve">3.2336962223053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2763569355011</t>
+    <t xml:space="preserve">3.27635717391968</t>
   </si>
   <si>
     <t xml:space="preserve">3.24222850799561</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26782488822937</t>
+    <t xml:space="preserve">3.26782512664795</t>
   </si>
   <si>
     <t xml:space="preserve">3.31048607826233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34461498260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32755017280579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28488922119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18250298500061</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29342126846313</t>
+    <t xml:space="preserve">3.34461450576782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32755041122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28488945960999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18250322341919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29342150688171</t>
   </si>
   <si>
     <t xml:space="preserve">3.33710074424744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32836508750916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29342150688171</t>
+    <t xml:space="preserve">3.32836484909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29342174530029</t>
   </si>
   <si>
     <t xml:space="preserve">3.24974226951599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20606279373169</t>
+    <t xml:space="preserve">3.20606303215027</t>
   </si>
   <si>
     <t xml:space="preserve">3.15364766120911</t>
@@ -926,7 +926,7 @@
     <t xml:space="preserve">3.17111968994141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26721382141113</t>
+    <t xml:space="preserve">3.26721405982971</t>
   </si>
   <si>
     <t xml:space="preserve">3.36330842971802</t>
@@ -935,55 +935,55 @@
     <t xml:space="preserve">3.49434638023376</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58170533180237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56423330307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59044098854065</t>
+    <t xml:space="preserve">3.58170509338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56423354148865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59044122695923</t>
   </si>
   <si>
     <t xml:space="preserve">3.5030825138092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51181840896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54676175117493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63411998748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62538456916809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7476863861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69527149200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66906380653381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60791277885437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55549788475037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66032814979553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65159201622009</t>
+    <t xml:space="preserve">3.51181817054749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54676151275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63412046432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62538480758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74768662452698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69527125358582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66906356811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60791301727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55549764633179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66032791137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65159177780151</t>
   </si>
   <si>
     <t xml:space="preserve">3.68653535842896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7040069103241</t>
+    <t xml:space="preserve">3.70400714874268</t>
   </si>
   <si>
     <t xml:space="preserve">3.75642251968384</t>
@@ -1010,19 +1010,19 @@
     <t xml:space="preserve">3.44193148612976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48561072349548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40698790550232</t>
+    <t xml:space="preserve">3.4856104850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4069881439209</t>
   </si>
   <si>
     <t xml:space="preserve">3.35457253456116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4594030380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52928996086121</t>
+    <t xml:space="preserve">3.45940327644348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52928972244263</t>
   </si>
   <si>
     <t xml:space="preserve">3.46813893318176</t>
@@ -1031,22 +1031,22 @@
     <t xml:space="preserve">3.47687458992004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79136610031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72147917747498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87872457504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17574405670166</t>
+    <t xml:space="preserve">3.79136633872986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7214789390564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8787248134613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17574453353882</t>
   </si>
   <si>
     <t xml:space="preserve">4.31551790237427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35046100616455</t>
+    <t xml:space="preserve">4.35046148300171</t>
   </si>
   <si>
     <t xml:space="preserve">4.18447971343994</t>
@@ -1061,25 +1061,25 @@
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493226051331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98355507850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94861173629761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93113970756531</t>
+    <t xml:space="preserve">3.90493202209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98355484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94861197471619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93114018440247</t>
   </si>
   <si>
     <t xml:space="preserve">4.08838510513306</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07091379165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12332820892334</t>
+    <t xml:space="preserve">4.07091331481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1233286857605</t>
   </si>
   <si>
     <t xml:space="preserve">4.00102663040161</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">4.00976276397705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93987560272217</t>
+    <t xml:space="preserve">3.93987607955933</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
@@ -1097,31 +1097,31 @@
     <t xml:space="preserve">4.2106876373291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29804658889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28930997848511</t>
+    <t xml:space="preserve">4.29804611206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28931045532227</t>
   </si>
   <si>
     <t xml:space="preserve">4.21942329406738</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19321632385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14953660964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16700839996338</t>
+    <t xml:space="preserve">4.19321584701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1495361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16700792312622</t>
   </si>
   <si>
     <t xml:space="preserve">4.11459302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06217765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78263020515442</t>
+    <t xml:space="preserve">4.06217813491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78262996673584</t>
   </si>
   <si>
     <t xml:space="preserve">3.80010175704956</t>
@@ -1130,10 +1130,10 @@
     <t xml:space="preserve">3.82630968093872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.835045337677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84378123283386</t>
+    <t xml:space="preserve">3.83504509925842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84378099441528</t>
   </si>
   <si>
     <t xml:space="preserve">3.77389454841614</t>
@@ -1142,16 +1142,16 @@
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734763145447</t>
+    <t xml:space="preserve">3.95734786987305</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.861252784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76515817642212</t>
+    <t xml:space="preserve">3.86125302314758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76515865325928</t>
   </si>
   <si>
     <t xml:space="preserve">3.8175733089447</t>
@@ -1163,52 +1163,52 @@
     <t xml:space="preserve">3.67779970169067</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7389509677887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85251712799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71274328231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92240357398987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61664843559265</t>
+    <t xml:space="preserve">3.73895072937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85251665115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71274304389954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92240381240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61664867401123</t>
   </si>
   <si>
     <t xml:space="preserve">3.39825224876404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23227047920227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05755352973938</t>
+    <t xml:space="preserve">3.23227071762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0575532913208</t>
   </si>
   <si>
     <t xml:space="preserve">2.97019457817078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95272278785706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91777944564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90904355049133</t>
+    <t xml:space="preserve">2.95272302627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91777920722961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90904331207275</t>
   </si>
   <si>
     <t xml:space="preserve">3.37204432487488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38077998161316</t>
+    <t xml:space="preserve">3.38078022003174</t>
   </si>
   <si>
     <t xml:space="preserve">3.41572380065918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31962919235229</t>
+    <t xml:space="preserve">3.31962895393372</t>
   </si>
   <si>
     <t xml:space="preserve">3.27594995498657</t>
@@ -57235,7 +57235,7 @@
     </row>
     <row r="2120">
       <c r="A2120" s="1" t="n">
-        <v>46055.6912384259</v>
+        <v>46055.3333333333</v>
       </c>
       <c r="B2120" t="n">
         <v>5491</v>
@@ -57256,6 +57256,32 @@
         <v>582</v>
       </c>
       <c r="H2120" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2121">
+      <c r="A2121" s="1" t="n">
+        <v>46056.6910532407</v>
+      </c>
+      <c r="B2121" t="n">
+        <v>34167</v>
+      </c>
+      <c r="C2121" t="n">
+        <v>3.74000000953674</v>
+      </c>
+      <c r="D2121" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="E2121" t="n">
+        <v>3.59999990463257</v>
+      </c>
+      <c r="F2121" t="n">
+        <v>3.70000004768372</v>
+      </c>
+      <c r="G2121" t="s">
+        <v>593</v>
+      </c>
+      <c r="H2121" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -44,7 +44,7 @@
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519923210144</t>
+    <t xml:space="preserve">2.96519947052002</t>
   </si>
   <si>
     <t xml:space="preserve">2.88901543617249</t>
@@ -59,22 +59,22 @@
     <t xml:space="preserve">2.94578003883362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95773077011108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9622118473053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9353232383728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91291642189026</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97864317893982</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98611211776733</t>
+    <t xml:space="preserve">2.95773029327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96221160888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93532347679138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91291618347168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97864365577698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98611235618591</t>
   </si>
   <si>
     <t xml:space="preserve">3.03540802001953</t>
@@ -89,28 +89,28 @@
     <t xml:space="preserve">3.05034613609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98760652542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95026159286499</t>
+    <t xml:space="preserve">2.98760628700256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95026135444641</t>
   </si>
   <si>
     <t xml:space="preserve">3.01598858833313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01001381874084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02495169639587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01748251914978</t>
+    <t xml:space="preserve">3.01001358032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02495145797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0174822807312</t>
   </si>
   <si>
     <t xml:space="preserve">3.03092670440674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99955654144287</t>
+    <t xml:space="preserve">2.99955677986145</t>
   </si>
   <si>
     <t xml:space="preserve">3.04437112808228</t>
@@ -122,7 +122,7 @@
     <t xml:space="preserve">3.00254464149475</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92785453796387</t>
+    <t xml:space="preserve">2.92785429954529</t>
   </si>
   <si>
     <t xml:space="preserve">2.90843486785889</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">2.92038512229919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90544700622559</t>
+    <t xml:space="preserve">2.90544724464417</t>
   </si>
   <si>
     <t xml:space="preserve">2.90992856025696</t>
@@ -158,46 +158,46 @@
     <t xml:space="preserve">2.82627558708191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77996778488159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84569501876831</t>
+    <t xml:space="preserve">2.77996754646301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84569478034973</t>
   </si>
   <si>
     <t xml:space="preserve">2.86810207366943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88303995132446</t>
+    <t xml:space="preserve">2.88304018974304</t>
   </si>
   <si>
     <t xml:space="preserve">2.79639959335327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87557101249695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89797830581665</t>
+    <t xml:space="preserve">2.87557077407837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89797854423523</t>
   </si>
   <si>
     <t xml:space="preserve">2.80088090896606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74262285232544</t>
+    <t xml:space="preserve">2.74262261390686</t>
   </si>
   <si>
     <t xml:space="preserve">2.8217945098877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75009155273438</t>
+    <t xml:space="preserve">2.7500913143158</t>
   </si>
   <si>
     <t xml:space="preserve">2.76353573799133</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77847385406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78594279289246</t>
+    <t xml:space="preserve">2.77847409248352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78594303131104</t>
   </si>
   <si>
     <t xml:space="preserve">2.79341173171997</t>
@@ -206,7 +206,7 @@
     <t xml:space="preserve">2.69631481170654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6515007019043</t>
+    <t xml:space="preserve">2.65150094032288</t>
   </si>
   <si>
     <t xml:space="preserve">2.62162470817566</t>
@@ -215,43 +215,43 @@
     <t xml:space="preserve">2.53946542739868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5693416595459</t>
+    <t xml:space="preserve">2.56934142112732</t>
   </si>
   <si>
     <t xml:space="preserve">2.61415576934814</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65896940231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68884539604187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70378351211548</t>
+    <t xml:space="preserve">2.65896964073181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68884587287903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70378375053406</t>
   </si>
   <si>
     <t xml:space="preserve">2.77100491523743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81581902503967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73365950584412</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66643881797791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68137669563293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74112868309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72619080543518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8307569026947</t>
+    <t xml:space="preserve">2.81581878662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7336597442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66643857955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68137645721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74112892150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72619104385376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83075714111328</t>
   </si>
   <si>
     <t xml:space="preserve">2.893150806427</t>
@@ -260,22 +260,22 @@
     <t xml:space="preserve">2.69871854782104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83870959281921</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93203687667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87759613990784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8309326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81537747383118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84648680686951</t>
+    <t xml:space="preserve">2.83870983123779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93203663825989</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87759590148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83093237876892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81537795066833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84648704528809</t>
   </si>
   <si>
     <t xml:space="preserve">2.79982304573059</t>
@@ -284,10 +284,10 @@
     <t xml:space="preserve">2.73760485649109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76093697547913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80760073661804</t>
+    <t xml:space="preserve">2.76093673706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80760049819946</t>
   </si>
   <si>
     <t xml:space="preserve">3.00980997085571</t>
@@ -296,19 +296,19 @@
     <t xml:space="preserve">2.9553689956665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90870499610901</t>
+    <t xml:space="preserve">2.90870523452759</t>
   </si>
   <si>
     <t xml:space="preserve">2.88537335395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82315516471863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86204147338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00203227996826</t>
+    <t xml:space="preserve">2.82315492630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86204171180725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00203275680542</t>
   </si>
   <si>
     <t xml:space="preserve">2.91648268699646</t>
@@ -317,7 +317,7 @@
     <t xml:space="preserve">2.85426425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7298276424408</t>
+    <t xml:space="preserve">2.72982740402222</t>
   </si>
   <si>
     <t xml:space="preserve">2.68316411972046</t>
@@ -326,7 +326,7 @@
     <t xml:space="preserve">2.7220504283905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75315952301025</t>
+    <t xml:space="preserve">2.75315976142883</t>
   </si>
   <si>
     <t xml:space="preserve">2.70649576187134</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">2.93981432914734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99425554275513</t>
+    <t xml:space="preserve">2.99425530433655</t>
   </si>
   <si>
     <t xml:space="preserve">2.97870063781738</t>
@@ -350,34 +350,34 @@
     <t xml:space="preserve">2.98647785186768</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63650035858154</t>
+    <t xml:space="preserve">2.63650012016296</t>
   </si>
   <si>
     <t xml:space="preserve">2.550950050354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51984071731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41095876693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34096312522888</t>
+    <t xml:space="preserve">2.51984095573425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41095900535583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34096336364746</t>
   </si>
   <si>
     <t xml:space="preserve">2.34874081611633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36429500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2554132938385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24763607978821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3254086971283</t>
+    <t xml:space="preserve">2.36429524421692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.25541305541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24763631820679</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32540845870972</t>
   </si>
   <si>
     <t xml:space="preserve">2.23208117485046</t>
@@ -386,16 +386,16 @@
     <t xml:space="preserve">2.18541765213013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27874517440796</t>
+    <t xml:space="preserve">2.27874493598938</t>
   </si>
   <si>
     <t xml:space="preserve">2.26319026947021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2165265083313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06875824928284</t>
+    <t xml:space="preserve">2.21652698516846</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06875848770142</t>
   </si>
   <si>
     <t xml:space="preserve">2.1465311050415</t>
@@ -410,7 +410,7 @@
     <t xml:space="preserve">2.17764019966125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.22430396080017</t>
+    <t xml:space="preserve">2.22430372238159</t>
   </si>
   <si>
     <t xml:space="preserve">2.35651779174805</t>
@@ -422,7 +422,7 @@
     <t xml:space="preserve">2.52761793136597</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43429112434387</t>
+    <t xml:space="preserve">2.43429088592529</t>
   </si>
   <si>
     <t xml:space="preserve">2.44206809997559</t>
@@ -431,13 +431,13 @@
     <t xml:space="preserve">2.55872750282288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44984531402588</t>
+    <t xml:space="preserve">2.44984555244446</t>
   </si>
   <si>
     <t xml:space="preserve">2.37207245826721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33318567276001</t>
+    <t xml:space="preserve">2.33318591117859</t>
   </si>
   <si>
     <t xml:space="preserve">2.29429960250854</t>
@@ -449,34 +449,34 @@
     <t xml:space="preserve">2.71427297592163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58205938339233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62872314453125</t>
+    <t xml:space="preserve">2.58205914497375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62872290611267</t>
   </si>
   <si>
     <t xml:space="preserve">2.65983200073242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57428216934204</t>
+    <t xml:space="preserve">2.57428169250488</t>
   </si>
   <si>
     <t xml:space="preserve">2.67538666725159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64427781105042</t>
+    <t xml:space="preserve">2.64427757263184</t>
   </si>
   <si>
     <t xml:space="preserve">2.69094133377075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76871418952942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90092778205872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96314597129822</t>
+    <t xml:space="preserve">2.76871395111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90092802047729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9631462097168</t>
   </si>
   <si>
     <t xml:space="preserve">2.92425966262817</t>
@@ -488,7 +488,7 @@
     <t xml:space="preserve">3.01758766174316</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04869651794434</t>
+    <t xml:space="preserve">3.04869627952576</t>
   </si>
   <si>
     <t xml:space="preserve">3.03314185142517</t>
@@ -497,10 +497,10 @@
     <t xml:space="preserve">3.0642511844635</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07980585098267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0604989528656</t>
+    <t xml:space="preserve">3.07980537414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06049919128418</t>
   </si>
   <si>
     <t xml:space="preserve">3.0281126499176</t>
@@ -509,13 +509,13 @@
     <t xml:space="preserve">3.01191973686218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10907816886902</t>
+    <t xml:space="preserve">3.1090784072876</t>
   </si>
   <si>
     <t xml:space="preserve">3.0928852558136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12527108192444</t>
+    <t xml:space="preserve">3.1252715587616</t>
   </si>
   <si>
     <t xml:space="preserve">3.0766921043396</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">3.30339574813843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41674733161926</t>
+    <t xml:space="preserve">3.41674709320068</t>
   </si>
   <si>
     <t xml:space="preserve">3.35197496414185</t>
@@ -545,28 +545,28 @@
     <t xml:space="preserve">3.31958889961243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27100968360901</t>
+    <t xml:space="preserve">3.27100944519043</t>
   </si>
   <si>
     <t xml:space="preserve">3.28720259666443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22243022918701</t>
+    <t xml:space="preserve">3.22242999076843</t>
   </si>
   <si>
     <t xml:space="preserve">3.17385101318359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20623731613159</t>
+    <t xml:space="preserve">3.20623707771301</t>
   </si>
   <si>
     <t xml:space="preserve">3.14146494865417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40055441856384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49771356582642</t>
+    <t xml:space="preserve">3.40055465698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.497713804245</t>
   </si>
   <si>
     <t xml:space="preserve">3.38436150550842</t>
@@ -587,40 +587,40 @@
     <t xml:space="preserve">2.80140924453735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88237476348877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86618161201477</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84998846054077</t>
+    <t xml:space="preserve">2.88237452507019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86618185043335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84998869895935</t>
   </si>
   <si>
     <t xml:space="preserve">2.78521609306335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75283026695251</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72044348716736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83379554748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76902294158936</t>
+    <t xml:space="preserve">2.75283002853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72044324874878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83379530906677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76902270317078</t>
   </si>
   <si>
     <t xml:space="preserve">2.73663687705994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81760239601135</t>
+    <t xml:space="preserve">2.81760215759277</t>
   </si>
   <si>
     <t xml:space="preserve">2.89856791496277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91476082801819</t>
+    <t xml:space="preserve">2.91476106643677</t>
   </si>
   <si>
     <t xml:space="preserve">2.63947820663452</t>
@@ -632,7 +632,7 @@
     <t xml:space="preserve">2.62328481674194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68805766105652</t>
+    <t xml:space="preserve">2.68805742263794</t>
   </si>
   <si>
     <t xml:space="preserve">2.70425057411194</t>
@@ -641,37 +641,37 @@
     <t xml:space="preserve">2.60709166526794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59089875221252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42896723747253</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54231929779053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46135354042053</t>
+    <t xml:space="preserve">2.5908989906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42896747589111</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54231953620911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46135377883911</t>
   </si>
   <si>
     <t xml:space="preserve">2.3156156539917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2994225025177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35488176345825</t>
+    <t xml:space="preserve">2.29942226409912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35488152503967</t>
   </si>
   <si>
     <t xml:space="preserve">2.40607476234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28662419319153</t>
+    <t xml:space="preserve">2.28662443161011</t>
   </si>
   <si>
     <t xml:space="preserve">2.13304471969604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08185195922852</t>
+    <t xml:space="preserve">2.08185219764709</t>
   </si>
   <si>
     <t xml:space="preserve">2.06478762626648</t>
@@ -695,13 +695,13 @@
     <t xml:space="preserve">2.32075309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55965399742126</t>
+    <t xml:space="preserve">2.55965423583984</t>
   </si>
   <si>
     <t xml:space="preserve">2.54258966445923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45726823806763</t>
+    <t xml:space="preserve">2.45726799964905</t>
   </si>
   <si>
     <t xml:space="preserve">2.57671856880188</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">2.64497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59378266334534</t>
+    <t xml:space="preserve">2.59378290176392</t>
   </si>
   <si>
     <t xml:space="preserve">2.69616913795471</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">2.44020342826843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4231390953064</t>
+    <t xml:space="preserve">2.42313885688782</t>
   </si>
   <si>
     <t xml:space="preserve">2.47433233261108</t>
@@ -743,7 +743,7 @@
     <t xml:space="preserve">2.30368876457214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25249552726746</t>
+    <t xml:space="preserve">2.25249576568604</t>
   </si>
   <si>
     <t xml:space="preserve">2.23543095588684</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">2.37194609642029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38901042938232</t>
+    <t xml:space="preserve">2.38901019096375</t>
   </si>
   <si>
     <t xml:space="preserve">2.20130228996277</t>
@@ -761,22 +761,22 @@
     <t xml:space="preserve">2.18423795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01359415054321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04772329330444</t>
+    <t xml:space="preserve">2.01359438896179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04772353172302</t>
   </si>
   <si>
     <t xml:space="preserve">2.11598062515259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91120839118958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8770797252655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84295094013214</t>
+    <t xml:space="preserve">1.911208152771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87707960605621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84295105934143</t>
   </si>
   <si>
     <t xml:space="preserve">1.97946572303772</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">1.86001527309418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94533705711365</t>
+    <t xml:space="preserve">1.94533681869507</t>
   </si>
   <si>
     <t xml:space="preserve">1.96240139007568</t>
@@ -794,19 +794,19 @@
     <t xml:space="preserve">1.99653005599976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81561970710754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9009416103363</t>
+    <t xml:space="preserve">2.81561946868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90094137191772</t>
   </si>
   <si>
     <t xml:space="preserve">2.88387703895569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76442623138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73029756546021</t>
+    <t xml:space="preserve">2.76442646980286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73029780387878</t>
   </si>
   <si>
     <t xml:space="preserve">2.6791045665741</t>
@@ -818,7 +818,7 @@
     <t xml:space="preserve">2.832683801651</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86681246757507</t>
+    <t xml:space="preserve">2.86681222915649</t>
   </si>
   <si>
     <t xml:space="preserve">2.79855513572693</t>
@@ -827,7 +827,7 @@
     <t xml:space="preserve">2.78149080276489</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93507027626038</t>
+    <t xml:space="preserve">2.9350700378418</t>
   </si>
   <si>
     <t xml:space="preserve">2.96919870376587</t>
@@ -872,22 +872,22 @@
     <t xml:space="preserve">3.15690660476685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2336962223053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2763569355011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24222826957703</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26782464981079</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31048607826233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34461498260498</t>
+    <t xml:space="preserve">3.23369598388672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27635717391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24222850799561</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26782488822937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31048631668091</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3446147441864</t>
   </si>
   <si>
     <t xml:space="preserve">3.32755041122437</t>
@@ -896,7 +896,7 @@
     <t xml:space="preserve">3.28488922119141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18250298500061</t>
+    <t xml:space="preserve">3.18250322341919</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342150688171</t>
@@ -57336,7 +57336,7 @@
     </row>
     <row r="2124">
       <c r="A2124" s="1" t="n">
-        <v>46059.6910648148</v>
+        <v>46059.3333333333</v>
       </c>
       <c r="B2124" t="n">
         <v>5917</v>
@@ -57357,6 +57357,32 @@
         <v>590</v>
       </c>
       <c r="H2124" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2125">
+      <c r="A2125" s="1" t="n">
+        <v>46062.6912037037</v>
+      </c>
+      <c r="B2125" t="n">
+        <v>8169</v>
+      </c>
+      <c r="C2125" t="n">
+        <v>3.79999995231628</v>
+      </c>
+      <c r="D2125" t="n">
+        <v>3.74000000953674</v>
+      </c>
+      <c r="E2125" t="n">
+        <v>3.77999997138977</v>
+      </c>
+      <c r="F2125" t="n">
+        <v>3.77999997138977</v>
+      </c>
+      <c r="G2125" t="s">
+        <v>584</v>
+      </c>
+      <c r="H2125" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -44,13 +44,13 @@
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519947052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88901543617249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98013734817505</t>
+    <t xml:space="preserve">2.96519923210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88901519775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98013758659363</t>
   </si>
   <si>
     <t xml:space="preserve">2.97266817092896</t>
@@ -62,28 +62,28 @@
     <t xml:space="preserve">2.95773029327393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96221160888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93532347679138</t>
+    <t xml:space="preserve">2.9622118473053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9353232383728</t>
   </si>
   <si>
     <t xml:space="preserve">2.91291618347168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97864365577698</t>
+    <t xml:space="preserve">2.9786434173584</t>
   </si>
   <si>
     <t xml:space="preserve">2.98611235618591</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03540802001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.056321144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05930924415588</t>
+    <t xml:space="preserve">3.03540825843811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05632138252258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0593090057373</t>
   </si>
   <si>
     <t xml:space="preserve">3.05034613609314</t>
@@ -104,10 +104,10 @@
     <t xml:space="preserve">3.02495145797729</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0174822807312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03092670440674</t>
+    <t xml:space="preserve">3.01748251914978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03092646598816</t>
   </si>
   <si>
     <t xml:space="preserve">2.99955677986145</t>
@@ -119,10 +119,10 @@
     <t xml:space="preserve">2.959223985672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00254464149475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92785429954529</t>
+    <t xml:space="preserve">3.00254416465759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92785453796387</t>
   </si>
   <si>
     <t xml:space="preserve">2.90843486785889</t>
@@ -131,7 +131,7 @@
     <t xml:space="preserve">2.89648461341858</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91889119148254</t>
+    <t xml:space="preserve">2.91889142990112</t>
   </si>
   <si>
     <t xml:space="preserve">2.9159038066864</t>
@@ -146,37 +146,37 @@
     <t xml:space="preserve">2.90992856025696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92337274551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83822584152222</t>
+    <t xml:space="preserve">2.9233729839325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83822631835938</t>
   </si>
   <si>
     <t xml:space="preserve">2.86063313484192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82627558708191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77996754646301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84569478034973</t>
+    <t xml:space="preserve">2.82627534866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77996778488159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84569525718689</t>
   </si>
   <si>
     <t xml:space="preserve">2.86810207366943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88304018974304</t>
+    <t xml:space="preserve">2.88303995132446</t>
   </si>
   <si>
     <t xml:space="preserve">2.79639959335327</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87557077407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89797854423523</t>
+    <t xml:space="preserve">2.87557125091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89797806739807</t>
   </si>
   <si>
     <t xml:space="preserve">2.80088090896606</t>
@@ -188,10 +188,10 @@
     <t xml:space="preserve">2.8217945098877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7500913143158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76353573799133</t>
+    <t xml:space="preserve">2.75009179115295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76353597640991</t>
   </si>
   <si>
     <t xml:space="preserve">2.77847409248352</t>
@@ -206,52 +206,52 @@
     <t xml:space="preserve">2.69631481170654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65150094032288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62162470817566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53946542739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56934142112732</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61415576934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65896964073181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68884587287903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70378375053406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77100491523743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81581878662109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7336597442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66643857955933</t>
+    <t xml:space="preserve">2.65150046348572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62162446975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.53946566581726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5693416595459</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61415553092957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65896940231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68884539604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7037832736969</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77100467681885</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81581902503967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73365998268127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66643881797791</t>
   </si>
   <si>
     <t xml:space="preserve">2.68137645721436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74112892150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72619104385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83075714111328</t>
+    <t xml:space="preserve">2.74112868309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72619080543518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8307569026947</t>
   </si>
   <si>
     <t xml:space="preserve">2.893150806427</t>
@@ -260,19 +260,19 @@
     <t xml:space="preserve">2.69871854782104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83870983123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93203663825989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87759590148926</t>
+    <t xml:space="preserve">2.83870959281921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93203711509705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87759637832642</t>
   </si>
   <si>
     <t xml:space="preserve">2.83093237876892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81537795066833</t>
+    <t xml:space="preserve">2.81537771224976</t>
   </si>
   <si>
     <t xml:space="preserve">2.84648704528809</t>
@@ -281,19 +281,19 @@
     <t xml:space="preserve">2.79982304573059</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73760485649109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76093673706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80760049819946</t>
+    <t xml:space="preserve">2.73760509490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76093649864197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80760025978088</t>
   </si>
   <si>
     <t xml:space="preserve">3.00980997085571</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9553689956665</t>
+    <t xml:space="preserve">2.95536851882935</t>
   </si>
   <si>
     <t xml:space="preserve">2.90870523452759</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">2.88537335395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82315492630005</t>
+    <t xml:space="preserve">2.82315516471863</t>
   </si>
   <si>
     <t xml:space="preserve">2.86204171180725</t>
@@ -317,22 +317,22 @@
     <t xml:space="preserve">2.85426425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72982740402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68316411972046</t>
+    <t xml:space="preserve">2.72982788085938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68316388130188</t>
   </si>
   <si>
     <t xml:space="preserve">2.7220504283905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75315976142883</t>
+    <t xml:space="preserve">2.75315952301025</t>
   </si>
   <si>
     <t xml:space="preserve">2.70649576187134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93981432914734</t>
+    <t xml:space="preserve">2.93981409072876</t>
   </si>
   <si>
     <t xml:space="preserve">2.99425530433655</t>
@@ -341,46 +341,46 @@
     <t xml:space="preserve">2.97870063781738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86981892585754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94759178161621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98647785186768</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63650012016296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.550950050354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51984095573425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41095900535583</t>
+    <t xml:space="preserve">2.86981868743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94759154319763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98647809028625</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63650035858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55094981193542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51984119415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41095876693726</t>
   </si>
   <si>
     <t xml:space="preserve">2.34096336364746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34874081611633</t>
+    <t xml:space="preserve">2.34874057769775</t>
   </si>
   <si>
     <t xml:space="preserve">2.36429524421692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25541305541992</t>
+    <t xml:space="preserve">2.2554132938385</t>
   </si>
   <si>
     <t xml:space="preserve">2.24763631820679</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32540845870972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23208117485046</t>
+    <t xml:space="preserve">2.3254086971283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23208141326904</t>
   </si>
   <si>
     <t xml:space="preserve">2.18541765213013</t>
@@ -389,28 +389,28 @@
     <t xml:space="preserve">2.27874493598938</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26319026947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21652698516846</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06875848770142</t>
+    <t xml:space="preserve">2.26319050788879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21652674674988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06875824928284</t>
   </si>
   <si>
     <t xml:space="preserve">2.1465311050415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10764479637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1543083190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17764019966125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22430372238159</t>
+    <t xml:space="preserve">2.10764503479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15430808067322</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17763996124268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22430396080017</t>
   </si>
   <si>
     <t xml:space="preserve">2.35651779174805</t>
@@ -419,19 +419,19 @@
     <t xml:space="preserve">2.4887318611145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52761793136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43429088592529</t>
+    <t xml:space="preserve">2.52761816978455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43429112434387</t>
   </si>
   <si>
     <t xml:space="preserve">2.44206809997559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55872750282288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44984555244446</t>
+    <t xml:space="preserve">2.5587272644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44984531402588</t>
   </si>
   <si>
     <t xml:space="preserve">2.37207245826721</t>
@@ -440,25 +440,25 @@
     <t xml:space="preserve">2.33318591117859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29429960250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3798496723175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71427297592163</t>
+    <t xml:space="preserve">2.29429936408997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37984991073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71427321434021</t>
   </si>
   <si>
     <t xml:space="preserve">2.58205914497375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62872290611267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65983200073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57428169250488</t>
+    <t xml:space="preserve">2.62872314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65983176231384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57428193092346</t>
   </si>
   <si>
     <t xml:space="preserve">2.67538666725159</t>
@@ -467,13 +467,13 @@
     <t xml:space="preserve">2.64427757263184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69094133377075</t>
+    <t xml:space="preserve">2.69094109535217</t>
   </si>
   <si>
     <t xml:space="preserve">2.76871395111084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90092802047729</t>
+    <t xml:space="preserve">2.90092825889587</t>
   </si>
   <si>
     <t xml:space="preserve">2.9631462097168</t>
@@ -485,28 +485,28 @@
     <t xml:space="preserve">2.97092342376709</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01758766174316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04869627952576</t>
+    <t xml:space="preserve">3.01758742332458</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04869651794434</t>
   </si>
   <si>
     <t xml:space="preserve">3.03314185142517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0642511844635</t>
+    <t xml:space="preserve">3.06425094604492</t>
   </si>
   <si>
     <t xml:space="preserve">3.07980537414551</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06049919128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0281126499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01191973686218</t>
+    <t xml:space="preserve">3.0604989528656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02811288833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01191997528076</t>
   </si>
   <si>
     <t xml:space="preserve">3.1090784072876</t>
@@ -521,7 +521,7 @@
     <t xml:space="preserve">3.0766921043396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99572658538818</t>
+    <t xml:space="preserve">2.99572682380676</t>
   </si>
   <si>
     <t xml:space="preserve">3.30339574813843</t>
@@ -539,7 +539,7 @@
     <t xml:space="preserve">3.36816787719727</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23862338066101</t>
+    <t xml:space="preserve">3.23862314224243</t>
   </si>
   <si>
     <t xml:space="preserve">3.31958889961243</t>
@@ -554,49 +554,49 @@
     <t xml:space="preserve">3.22242999076843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17385101318359</t>
+    <t xml:space="preserve">3.17385077476501</t>
   </si>
   <si>
     <t xml:space="preserve">3.20623707771301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14146494865417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40055465698242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.497713804245</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38436150550842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25481653213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19004416465759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96334028244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97953343391418</t>
+    <t xml:space="preserve">3.1414647102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40055394172668</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49771356582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38436126708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25481629371643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19004392623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96334052085876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97953367233276</t>
   </si>
   <si>
     <t xml:space="preserve">2.80140924453735</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88237452507019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86618185043335</t>
+    <t xml:space="preserve">2.88237476348877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86618161201477</t>
   </si>
   <si>
     <t xml:space="preserve">2.84998869895935</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78521609306335</t>
+    <t xml:space="preserve">2.78521585464478</t>
   </si>
   <si>
     <t xml:space="preserve">2.75283002853394</t>
@@ -608,46 +608,46 @@
     <t xml:space="preserve">2.83379530906677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76902270317078</t>
+    <t xml:space="preserve">2.76902294158936</t>
   </si>
   <si>
     <t xml:space="preserve">2.73663687705994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81760215759277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89856791496277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91476106643677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63947820663452</t>
+    <t xml:space="preserve">2.81760239601135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89856767654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91476082801819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63947796821594</t>
   </si>
   <si>
     <t xml:space="preserve">2.67186427116394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62328481674194</t>
+    <t xml:space="preserve">2.62328505516052</t>
   </si>
   <si>
     <t xml:space="preserve">2.68805742263794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70425057411194</t>
+    <t xml:space="preserve">2.70425033569336</t>
   </si>
   <si>
     <t xml:space="preserve">2.60709166526794</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5908989906311</t>
+    <t xml:space="preserve">2.59089851379395</t>
   </si>
   <si>
     <t xml:space="preserve">2.42896747589111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54231953620911</t>
+    <t xml:space="preserve">2.54231905937195</t>
   </si>
   <si>
     <t xml:space="preserve">2.46135377883911</t>
@@ -656,7 +656,7 @@
     <t xml:space="preserve">2.3156156539917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29942226409912</t>
+    <t xml:space="preserve">2.2994225025177</t>
   </si>
   <si>
     <t xml:space="preserve">2.35488152503967</t>
@@ -668,13 +668,13 @@
     <t xml:space="preserve">2.28662443161011</t>
   </si>
   <si>
-    <t xml:space="preserve">2.13304471969604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08185219764709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06478762626648</t>
+    <t xml:space="preserve">2.1330451965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08185195922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0647873878479</t>
   </si>
   <si>
     <t xml:space="preserve">2.03065896034241</t>
@@ -686,28 +686,28 @@
     <t xml:space="preserve">2.09891629219055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26955986022949</t>
+    <t xml:space="preserve">2.26956009864807</t>
   </si>
   <si>
     <t xml:space="preserve">2.2183666229248</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32075309753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55965423583984</t>
+    <t xml:space="preserve">2.32075333595276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55965399742126</t>
   </si>
   <si>
     <t xml:space="preserve">2.54258966445923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45726799964905</t>
+    <t xml:space="preserve">2.45726823806763</t>
   </si>
   <si>
     <t xml:space="preserve">2.57671856880188</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62791132926941</t>
+    <t xml:space="preserve">2.62791156768799</t>
   </si>
   <si>
     <t xml:space="preserve">2.61084699630737</t>
@@ -719,7 +719,7 @@
     <t xml:space="preserve">2.59378290176392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69616913795471</t>
+    <t xml:space="preserve">2.69616889953613</t>
   </si>
   <si>
     <t xml:space="preserve">2.71323323249817</t>
@@ -728,13 +728,13 @@
     <t xml:space="preserve">2.44020342826843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42313885688782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.47433233261108</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15010929107666</t>
+    <t xml:space="preserve">2.4231390953064</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.47433257102966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15010952949524</t>
   </si>
   <si>
     <t xml:space="preserve">2.33781743049622</t>
@@ -743,19 +743,19 @@
     <t xml:space="preserve">2.30368876457214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25249576568604</t>
+    <t xml:space="preserve">2.25249552726746</t>
   </si>
   <si>
     <t xml:space="preserve">2.23543095588684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37194609642029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38901019096375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.20130228996277</t>
+    <t xml:space="preserve">2.37194585800171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38901042938232</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.20130252838135</t>
   </si>
   <si>
     <t xml:space="preserve">2.18423795700073</t>
@@ -764,34 +764,34 @@
     <t xml:space="preserve">2.01359438896179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04772353172302</t>
+    <t xml:space="preserve">2.04772329330444</t>
   </si>
   <si>
     <t xml:space="preserve">2.11598062515259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.911208152771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87707960605621</t>
+    <t xml:space="preserve">1.91120851039886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8770797252655</t>
   </si>
   <si>
     <t xml:space="preserve">1.84295105934143</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97946572303772</t>
+    <t xml:space="preserve">1.97946584224701</t>
   </si>
   <si>
     <t xml:space="preserve">1.86001527309418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94533681869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96240139007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99653005599976</t>
+    <t xml:space="preserve">1.94533693790436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96240150928497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99652993679047</t>
   </si>
   <si>
     <t xml:space="preserve">2.81561946868896</t>
@@ -806,10 +806,10 @@
     <t xml:space="preserve">2.76442646980286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73029780387878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6791045665741</t>
+    <t xml:space="preserve">2.73029756546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67910432815552</t>
   </si>
   <si>
     <t xml:space="preserve">2.74736189842224</t>
@@ -821,31 +821,31 @@
     <t xml:space="preserve">2.86681222915649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79855513572693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78149080276489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9350700378418</t>
+    <t xml:space="preserve">2.79855489730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78149056434631</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93506979942322</t>
   </si>
   <si>
     <t xml:space="preserve">2.96919870376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02039194107056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00332736968994</t>
+    <t xml:space="preserve">3.02039170265198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00332760810852</t>
   </si>
   <si>
     <t xml:space="preserve">3.03745603561401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98626327514648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05452060699463</t>
+    <t xml:space="preserve">2.98626303672791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05452036857605</t>
   </si>
   <si>
     <t xml:space="preserve">3.07158470153809</t>
@@ -857,46 +857,46 @@
     <t xml:space="preserve">3.11424589157104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1313099861145</t>
+    <t xml:space="preserve">3.13131022453308</t>
   </si>
   <si>
     <t xml:space="preserve">3.06305241584778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16543889045715</t>
+    <t xml:space="preserve">3.16543912887573</t>
   </si>
   <si>
     <t xml:space="preserve">3.19956755638123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15690660476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23369598388672</t>
+    <t xml:space="preserve">3.15690684318542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2336962223053</t>
   </si>
   <si>
     <t xml:space="preserve">3.27635717391968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24222850799561</t>
+    <t xml:space="preserve">3.24222826957703</t>
   </si>
   <si>
     <t xml:space="preserve">3.26782488822937</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31048631668091</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3446147441864</t>
+    <t xml:space="preserve">3.31048607826233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34461450576782</t>
   </si>
   <si>
     <t xml:space="preserve">3.32755041122437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28488922119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18250322341919</t>
+    <t xml:space="preserve">3.28488945960999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18250346183777</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342150688171</t>
@@ -908,13 +908,13 @@
     <t xml:space="preserve">3.32836484909058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24974226951599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20606279373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15364766120911</t>
+    <t xml:space="preserve">3.24974250793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20606303215027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15364742279053</t>
   </si>
   <si>
     <t xml:space="preserve">3.21479892730713</t>
@@ -923,19 +923,19 @@
     <t xml:space="preserve">3.17111945152283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26721382141113</t>
+    <t xml:space="preserve">3.26721405982971</t>
   </si>
   <si>
     <t xml:space="preserve">3.36330842971802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49434661865234</t>
+    <t xml:space="preserve">3.49434638023376</t>
   </si>
   <si>
     <t xml:space="preserve">3.58170509338379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56423330307007</t>
+    <t xml:space="preserve">3.56423354148865</t>
   </si>
   <si>
     <t xml:space="preserve">3.59044122695923</t>
@@ -944,25 +944,25 @@
     <t xml:space="preserve">3.5030825138092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51181840896606</t>
+    <t xml:space="preserve">3.51181817054749</t>
   </si>
   <si>
     <t xml:space="preserve">3.54676175117493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63411998748779</t>
+    <t xml:space="preserve">3.63412022590637</t>
   </si>
   <si>
     <t xml:space="preserve">3.62538456916809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7476863861084</t>
+    <t xml:space="preserve">3.74768662452698</t>
   </si>
   <si>
     <t xml:space="preserve">3.69527125358582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66906380653381</t>
+    <t xml:space="preserve">3.66906332969666</t>
   </si>
   <si>
     <t xml:space="preserve">3.60791301727295</t>
@@ -971,22 +971,22 @@
     <t xml:space="preserve">3.55549788475037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66032814979553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65159201622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68653535842896</t>
+    <t xml:space="preserve">3.66032767295837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65159177780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68653512001038</t>
   </si>
   <si>
     <t xml:space="preserve">3.7040069103241</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75642251968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57296967506409</t>
+    <t xml:space="preserve">3.75642275810242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57296943664551</t>
   </si>
   <si>
     <t xml:space="preserve">3.53802609443665</t>
@@ -995,28 +995,28 @@
     <t xml:space="preserve">3.3458366394043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3895161151886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42445993423462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45066738128662</t>
+    <t xml:space="preserve">3.38951635360718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42445969581604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45066714286804</t>
   </si>
   <si>
     <t xml:space="preserve">3.44193148612976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48561072349548</t>
+    <t xml:space="preserve">3.4856104850769</t>
   </si>
   <si>
     <t xml:space="preserve">3.4069881439209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35457229614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45940327644348</t>
+    <t xml:space="preserve">3.35457253456116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4594030380249</t>
   </si>
   <si>
     <t xml:space="preserve">3.52928996086121</t>
@@ -1025,19 +1025,19 @@
     <t xml:space="preserve">3.46813893318176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47687482833862</t>
+    <t xml:space="preserve">3.47687458992004</t>
   </si>
   <si>
     <t xml:space="preserve">3.79136610031128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72147941589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87872457504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17574405670166</t>
+    <t xml:space="preserve">3.72147917747498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8787248134613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17574453353882</t>
   </si>
   <si>
     <t xml:space="preserve">4.31551790237427</t>
@@ -1046,34 +1046,34 @@
     <t xml:space="preserve">4.35046148300171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18447971343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20195150375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25436687469482</t>
+    <t xml:space="preserve">4.1844801902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20195198059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25436639785767</t>
   </si>
   <si>
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493226051331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98355507850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94861173629761</t>
+    <t xml:space="preserve">3.90493202209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98355484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94861149787903</t>
   </si>
   <si>
     <t xml:space="preserve">3.93113970756531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08838558197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07091379165649</t>
+    <t xml:space="preserve">4.08838510513306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07091331481934</t>
   </si>
   <si>
     <t xml:space="preserve">4.1233286857605</t>
@@ -1082,16 +1082,16 @@
     <t xml:space="preserve">4.00102663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00976324081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93987584114075</t>
+    <t xml:space="preserve">4.00976276397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93987560272217</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2106876373291</t>
+    <t xml:space="preserve">4.21068811416626</t>
   </si>
   <si>
     <t xml:space="preserve">4.29804611206055</t>
@@ -1100,7 +1100,7 @@
     <t xml:space="preserve">4.28930997848511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21942329406738</t>
+    <t xml:space="preserve">4.21942377090454</t>
   </si>
   <si>
     <t xml:space="preserve">4.19321632385254</t>
@@ -1109,28 +1109,28 @@
     <t xml:space="preserve">4.14953660964966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16700792312622</t>
+    <t xml:space="preserve">4.16700839996338</t>
   </si>
   <si>
     <t xml:space="preserve">4.11459302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06217765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78262996673584</t>
+    <t xml:space="preserve">4.06217813491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78263020515442</t>
   </si>
   <si>
     <t xml:space="preserve">3.80010175704956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8263099193573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83504557609558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84378147125244</t>
+    <t xml:space="preserve">3.82630944252014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83504509925842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84378123283386</t>
   </si>
   <si>
     <t xml:space="preserve">3.77389454841614</t>
@@ -1139,7 +1139,7 @@
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734786987305</t>
+    <t xml:space="preserve">3.95734739303589</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
@@ -1148,16 +1148,16 @@
     <t xml:space="preserve">3.86125302314758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76515793800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81757354736328</t>
+    <t xml:space="preserve">3.7651584148407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8175733089447</t>
   </si>
   <si>
     <t xml:space="preserve">3.64285612106323</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67779970169067</t>
+    <t xml:space="preserve">3.67779946327209</t>
   </si>
   <si>
     <t xml:space="preserve">3.7389509677887</t>
@@ -1166,43 +1166,43 @@
     <t xml:space="preserve">3.85251712799072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71274328231812</t>
+    <t xml:space="preserve">3.71274304389954</t>
   </si>
   <si>
     <t xml:space="preserve">3.92240381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61664843559265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39825201034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23227047920227</t>
+    <t xml:space="preserve">3.61664867401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39825224876404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23227071762085</t>
   </si>
   <si>
     <t xml:space="preserve">3.0575532913208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97019481658936</t>
+    <t xml:space="preserve">2.97019457817078</t>
   </si>
   <si>
     <t xml:space="preserve">2.95272302627563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91777944564819</t>
+    <t xml:space="preserve">2.91777920722961</t>
   </si>
   <si>
     <t xml:space="preserve">2.90904355049133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3720440864563</t>
+    <t xml:space="preserve">3.37204432487488</t>
   </si>
   <si>
     <t xml:space="preserve">3.38078022003174</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41572380065918</t>
+    <t xml:space="preserve">3.41572403907776</t>
   </si>
   <si>
     <t xml:space="preserve">3.31962895393372</t>
@@ -57362,7 +57362,7 @@
     </row>
     <row r="2125">
       <c r="A2125" s="1" t="n">
-        <v>46062.6912037037</v>
+        <v>46062.3333333333</v>
       </c>
       <c r="B2125" t="n">
         <v>8169</v>
@@ -57383,6 +57383,32 @@
         <v>584</v>
       </c>
       <c r="H2125" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2126">
+      <c r="A2126" s="1" t="n">
+        <v>46063.6911574074</v>
+      </c>
+      <c r="B2126" t="n">
+        <v>13003</v>
+      </c>
+      <c r="C2126" t="n">
+        <v>3.79999995231628</v>
+      </c>
+      <c r="D2126" t="n">
+        <v>3.70000004768372</v>
+      </c>
+      <c r="E2126" t="n">
+        <v>3.79999995231628</v>
+      </c>
+      <c r="F2126" t="n">
+        <v>3.79999995231628</v>
+      </c>
+      <c r="G2126" t="s">
+        <v>588</v>
+      </c>
+      <c r="H2126" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -53,28 +53,28 @@
     <t xml:space="preserve">2.98013734817505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97266840934753</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94578003883362</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95773029327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9622118473053</t>
+    <t xml:space="preserve">2.97266864776611</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94577980041504</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9577305316925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96221160888672</t>
   </si>
   <si>
     <t xml:space="preserve">2.93532347679138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91291642189026</t>
+    <t xml:space="preserve">2.91291618347168</t>
   </si>
   <si>
     <t xml:space="preserve">2.9786434173584</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98611259460449</t>
+    <t xml:space="preserve">2.98611235618591</t>
   </si>
   <si>
     <t xml:space="preserve">3.03540802001953</t>
@@ -83,22 +83,22 @@
     <t xml:space="preserve">3.056321144104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0593090057373</t>
+    <t xml:space="preserve">3.05930876731873</t>
   </si>
   <si>
     <t xml:space="preserve">3.05034637451172</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98760628700256</t>
+    <t xml:space="preserve">2.98760676383972</t>
   </si>
   <si>
     <t xml:space="preserve">2.95026135444641</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01598882675171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01001334190369</t>
+    <t xml:space="preserve">3.01598858833313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01001358032227</t>
   </si>
   <si>
     <t xml:space="preserve">3.02495145797729</t>
@@ -107,16 +107,16 @@
     <t xml:space="preserve">3.0174822807312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03092670440674</t>
+    <t xml:space="preserve">3.03092646598816</t>
   </si>
   <si>
     <t xml:space="preserve">2.99955654144287</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0443708896637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95922446250916</t>
+    <t xml:space="preserve">3.04437112808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95922422409058</t>
   </si>
   <si>
     <t xml:space="preserve">3.00254440307617</t>
@@ -125,13 +125,13 @@
     <t xml:space="preserve">2.92785429954529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90843510627747</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89648461341858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91889142990112</t>
+    <t xml:space="preserve">2.90843486785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91889119148254</t>
   </si>
   <si>
     <t xml:space="preserve">2.9159038066864</t>
@@ -140,7 +140,7 @@
     <t xml:space="preserve">2.92038559913635</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90544724464417</t>
+    <t xml:space="preserve">2.90544700622559</t>
   </si>
   <si>
     <t xml:space="preserve">2.90992856025696</t>
@@ -155,10 +155,10 @@
     <t xml:space="preserve">2.8606333732605</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82627558708191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77996778488159</t>
+    <t xml:space="preserve">2.82627534866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77996802330017</t>
   </si>
   <si>
     <t xml:space="preserve">2.84569501876831</t>
@@ -167,19 +167,19 @@
     <t xml:space="preserve">2.86810207366943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88304018974304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79639935493469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87557125091553</t>
+    <t xml:space="preserve">2.88303995132446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79639959335327</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87557101249695</t>
   </si>
   <si>
     <t xml:space="preserve">2.89797806739807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80088114738464</t>
+    <t xml:space="preserve">2.80088090896606</t>
   </si>
   <si>
     <t xml:space="preserve">2.74262261390686</t>
@@ -188,13 +188,13 @@
     <t xml:space="preserve">2.82179427146912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75009202957153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76353597640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77847361564636</t>
+    <t xml:space="preserve">2.75009155273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76353573799133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77847385406494</t>
   </si>
   <si>
     <t xml:space="preserve">2.78594303131104</t>
@@ -203,70 +203,70 @@
     <t xml:space="preserve">2.79341197013855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69631481170654</t>
+    <t xml:space="preserve">2.69631457328796</t>
   </si>
   <si>
     <t xml:space="preserve">2.6515007019043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62162446975708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53946566581726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56934142112732</t>
+    <t xml:space="preserve">2.6216242313385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5394651889801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56934118270874</t>
   </si>
   <si>
     <t xml:space="preserve">2.61415553092957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65896940231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68884563446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70378398895264</t>
+    <t xml:space="preserve">2.65896964073181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68884587287903</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70378375053406</t>
   </si>
   <si>
     <t xml:space="preserve">2.77100491523743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81581902503967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73365998268127</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66643881797791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68137669563293</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74112892150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72619104385376</t>
+    <t xml:space="preserve">2.81581926345825</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7336597442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66643834114075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68137645721436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74112868309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72619080543518</t>
   </si>
   <si>
     <t xml:space="preserve">2.83075714111328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89315056800842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69871878623962</t>
+    <t xml:space="preserve">2.893150806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69871830940247</t>
   </si>
   <si>
     <t xml:space="preserve">2.83870983123779</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93203711509705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87759590148926</t>
+    <t xml:space="preserve">2.93203735351562</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87759613990784</t>
   </si>
   <si>
     <t xml:space="preserve">2.83093237876892</t>
@@ -278,28 +278,28 @@
     <t xml:space="preserve">2.84648704528809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79982280731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73760485649109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76093697547913</t>
+    <t xml:space="preserve">2.79982304573059</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73760461807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76093673706055</t>
   </si>
   <si>
     <t xml:space="preserve">2.80760049819946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00980973243713</t>
+    <t xml:space="preserve">3.00980997085571</t>
   </si>
   <si>
     <t xml:space="preserve">2.9553689956665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90870499610901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88537335395813</t>
+    <t xml:space="preserve">2.90870523452759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88537311553955</t>
   </si>
   <si>
     <t xml:space="preserve">2.82315516471863</t>
@@ -308,7 +308,7 @@
     <t xml:space="preserve">2.86204171180725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00203227996826</t>
+    <t xml:space="preserve">3.00203251838684</t>
   </si>
   <si>
     <t xml:space="preserve">2.91648244857788</t>
@@ -320,16 +320,16 @@
     <t xml:space="preserve">2.7298276424408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68316411972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7220504283905</t>
+    <t xml:space="preserve">2.6831636428833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72205018997192</t>
   </si>
   <si>
     <t xml:space="preserve">2.75315952301025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70649576187134</t>
+    <t xml:space="preserve">2.70649552345276</t>
   </si>
   <si>
     <t xml:space="preserve">2.93981432914734</t>
@@ -338,70 +338,70 @@
     <t xml:space="preserve">2.99425530433655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97870063781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86981892585754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94759154319763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98647785186768</t>
+    <t xml:space="preserve">2.97870087623596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86981868743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94759178161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98647809028625</t>
   </si>
   <si>
     <t xml:space="preserve">2.63650012016296</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55094981193542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51984095573425</t>
+    <t xml:space="preserve">2.55095028877258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51984071731567</t>
   </si>
   <si>
     <t xml:space="preserve">2.41095876693726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34096360206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34874081611633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36429500579834</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25541353225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24763607978821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32540893554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23208117485046</t>
+    <t xml:space="preserve">2.34096336364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34874057769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36429524421692</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2554132938385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24763584136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3254086971283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23208093643188</t>
   </si>
   <si>
     <t xml:space="preserve">2.18541765213013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27874517440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26319050788879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21652674674988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06875848770142</t>
+    <t xml:space="preserve">2.27874541282654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26319026947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2165265083313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06875824928284</t>
   </si>
   <si>
     <t xml:space="preserve">2.1465311050415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10764455795288</t>
+    <t xml:space="preserve">2.10764479637146</t>
   </si>
   <si>
     <t xml:space="preserve">2.15430808067322</t>
@@ -413,25 +413,25 @@
     <t xml:space="preserve">2.22430396080017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35651803016663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.4887318611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52761816978455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43429112434387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44206809997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55872702598572</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44984531402588</t>
+    <t xml:space="preserve">2.35651779174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48873162269592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52761840820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43429088592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44206833839417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55872750282288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44984555244446</t>
   </si>
   <si>
     <t xml:space="preserve">2.37207245826721</t>
@@ -440,7 +440,7 @@
     <t xml:space="preserve">2.33318614959717</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29429960250854</t>
+    <t xml:space="preserve">2.29429984092712</t>
   </si>
   <si>
     <t xml:space="preserve">2.3798496723175</t>
@@ -449,22 +449,22 @@
     <t xml:space="preserve">2.71427321434021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58205890655518</t>
+    <t xml:space="preserve">2.58205914497375</t>
   </si>
   <si>
     <t xml:space="preserve">2.62872290611267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.659832239151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57428193092346</t>
+    <t xml:space="preserve">2.65983247756958</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57428216934204</t>
   </si>
   <si>
     <t xml:space="preserve">2.67538666725159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64427733421326</t>
+    <t xml:space="preserve">2.64427757263184</t>
   </si>
   <si>
     <t xml:space="preserve">2.69094133377075</t>
@@ -473,28 +473,28 @@
     <t xml:space="preserve">2.76871395111084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90092802047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96314597129822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92425966262817</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97092318534851</t>
+    <t xml:space="preserve">2.90092778205872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9631462097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92425990104675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97092342376709</t>
   </si>
   <si>
     <t xml:space="preserve">3.01758742332458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04869627952576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03314161300659</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06425070762634</t>
+    <t xml:space="preserve">3.04869651794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03314185142517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06425094604492</t>
   </si>
   <si>
     <t xml:space="preserve">3.07980561256409</t>
@@ -533,7 +533,7 @@
     <t xml:space="preserve">3.35197496414185</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33578157424927</t>
+    <t xml:space="preserve">3.33578181266785</t>
   </si>
   <si>
     <t xml:space="preserve">3.36816787719727</t>
@@ -542,13 +542,13 @@
     <t xml:space="preserve">3.23862338066101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31958889961243</t>
+    <t xml:space="preserve">3.31958866119385</t>
   </si>
   <si>
     <t xml:space="preserve">3.27100944519043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28720259666443</t>
+    <t xml:space="preserve">3.28720235824585</t>
   </si>
   <si>
     <t xml:space="preserve">3.22243022918701</t>
@@ -560,22 +560,22 @@
     <t xml:space="preserve">3.20623707771301</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1414647102356</t>
+    <t xml:space="preserve">3.14146447181702</t>
   </si>
   <si>
     <t xml:space="preserve">3.40055441856384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49771332740784</t>
+    <t xml:space="preserve">3.49771308898926</t>
   </si>
   <si>
     <t xml:space="preserve">3.38436126708984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25481653213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19004392623901</t>
+    <t xml:space="preserve">3.25481629371643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19004416465759</t>
   </si>
   <si>
     <t xml:space="preserve">2.96334052085876</t>
@@ -584,7 +584,7 @@
     <t xml:space="preserve">2.97953343391418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80140924453735</t>
+    <t xml:space="preserve">2.80140948295593</t>
   </si>
   <si>
     <t xml:space="preserve">2.88237476348877</t>
@@ -596,7 +596,7 @@
     <t xml:space="preserve">2.84998846054077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78521609306335</t>
+    <t xml:space="preserve">2.78521633148193</t>
   </si>
   <si>
     <t xml:space="preserve">2.75282979011536</t>
@@ -623,10 +623,10 @@
     <t xml:space="preserve">2.91476082801819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63947820663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67186427116394</t>
+    <t xml:space="preserve">2.63947796821594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67186403274536</t>
   </si>
   <si>
     <t xml:space="preserve">2.62328481674194</t>
@@ -635,22 +635,22 @@
     <t xml:space="preserve">2.68805718421936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70425033569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60709166526794</t>
+    <t xml:space="preserve">2.70425009727478</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60709190368652</t>
   </si>
   <si>
     <t xml:space="preserve">2.59089875221252</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42896747589111</t>
+    <t xml:space="preserve">2.42896771430969</t>
   </si>
   <si>
     <t xml:space="preserve">2.54231929779053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46135354042053</t>
+    <t xml:space="preserve">2.46135377883911</t>
   </si>
   <si>
     <t xml:space="preserve">2.3156156539917</t>
@@ -57440,7 +57440,7 @@
     </row>
     <row r="2128">
       <c r="A2128" s="1" t="n">
-        <v>46065.6588078704</v>
+        <v>46065.3333333333</v>
       </c>
       <c r="B2128" t="n">
         <v>4407</v>
@@ -57461,6 +57461,32 @@
         <v>584</v>
       </c>
       <c r="H2128" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2129">
+      <c r="A2129" s="1" t="n">
+        <v>46066.6415625</v>
+      </c>
+      <c r="B2129" t="n">
+        <v>4674</v>
+      </c>
+      <c r="C2129" t="n">
+        <v>3.77999997138977</v>
+      </c>
+      <c r="D2129" t="n">
+        <v>3.70000004768372</v>
+      </c>
+      <c r="E2129" t="n">
+        <v>3.72000002861023</v>
+      </c>
+      <c r="F2129" t="n">
+        <v>3.77999997138977</v>
+      </c>
+      <c r="G2129" t="s">
+        <v>584</v>
+      </c>
+      <c r="H2129" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02345752716064</t>
+    <t xml:space="preserve">3.02345776557922</t>
   </si>
   <si>
     <t xml:space="preserve">NDT.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">2.96519923210144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88901543617249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98013734817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97266817092896</t>
+    <t xml:space="preserve">2.88901519775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98013710975647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97266840934753</t>
   </si>
   <si>
     <t xml:space="preserve">2.94577980041504</t>
@@ -62,25 +62,25 @@
     <t xml:space="preserve">2.95773029327393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96221160888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93532347679138</t>
+    <t xml:space="preserve">2.9622118473053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9353232383728</t>
   </si>
   <si>
     <t xml:space="preserve">2.91291642189026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97864365577698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98611259460449</t>
+    <t xml:space="preserve">2.97864317893982</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98611235618591</t>
   </si>
   <si>
     <t xml:space="preserve">3.03540802001953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.056321144104</t>
+    <t xml:space="preserve">3.05632138252258</t>
   </si>
   <si>
     <t xml:space="preserve">3.0593090057373</t>
@@ -89,49 +89,49 @@
     <t xml:space="preserve">3.05034613609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98760604858398</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95026135444641</t>
+    <t xml:space="preserve">2.98760628700256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95026111602783</t>
   </si>
   <si>
     <t xml:space="preserve">3.01598882675171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01001334190369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02495145797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0174822807312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03092646598816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99955654144287</t>
+    <t xml:space="preserve">3.01001358032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02495169639587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01748204231262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03092670440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99955677986145</t>
   </si>
   <si>
     <t xml:space="preserve">3.04437112808228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95922374725342</t>
+    <t xml:space="preserve">2.95922422409058</t>
   </si>
   <si>
     <t xml:space="preserve">3.00254440307617</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92785406112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90843486785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9188916683197</t>
+    <t xml:space="preserve">2.92785453796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90843462944031</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89648461341858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91889095306396</t>
   </si>
   <si>
     <t xml:space="preserve">2.9159038066864</t>
@@ -140,16 +140,16 @@
     <t xml:space="preserve">2.92038536071777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90544724464417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90992856025696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9233729839325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8382260799408</t>
+    <t xml:space="preserve">2.90544700622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90992832183838</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92337274551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83822584152222</t>
   </si>
   <si>
     <t xml:space="preserve">2.86063313484192</t>
@@ -158,7 +158,7 @@
     <t xml:space="preserve">2.82627558708191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77996754646301</t>
+    <t xml:space="preserve">2.77996778488159</t>
   </si>
   <si>
     <t xml:space="preserve">2.84569501876831</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">2.88304018974304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79639911651611</t>
+    <t xml:space="preserve">2.79639935493469</t>
   </si>
   <si>
     <t xml:space="preserve">2.87557101249695</t>
@@ -188,19 +188,19 @@
     <t xml:space="preserve">2.82179427146912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7500913143158</t>
+    <t xml:space="preserve">2.75009155273438</t>
   </si>
   <si>
     <t xml:space="preserve">2.76353597640991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77847385406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78594279289246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79341197013855</t>
+    <t xml:space="preserve">2.77847361564636</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78594255447388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79341173171997</t>
   </si>
   <si>
     <t xml:space="preserve">2.69631457328796</t>
@@ -212,46 +212,46 @@
     <t xml:space="preserve">2.62162446975708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53946542739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5693416595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61415576934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65896987915039</t>
+    <t xml:space="preserve">2.53946566581726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56934142112732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61415553092957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65896964073181</t>
   </si>
   <si>
     <t xml:space="preserve">2.68884563446045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70378375053406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77100467681885</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81581902503967</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7336597442627</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66643857955933</t>
+    <t xml:space="preserve">2.70378351211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77100491523743</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81581878662109</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73365998268127</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66643834114075</t>
   </si>
   <si>
     <t xml:space="preserve">2.68137645721436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74112892150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72619104385376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8307569026947</t>
+    <t xml:space="preserve">2.74112868309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7261905670166</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83075714111328</t>
   </si>
   <si>
     <t xml:space="preserve">2.89315056800842</t>
@@ -260,67 +260,67 @@
     <t xml:space="preserve">2.69871854782104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83870983123779</t>
+    <t xml:space="preserve">2.83870959281921</t>
   </si>
   <si>
     <t xml:space="preserve">2.93203711509705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87759637832642</t>
+    <t xml:space="preserve">2.87759590148926</t>
   </si>
   <si>
     <t xml:space="preserve">2.83093237876892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81537795066833</t>
+    <t xml:space="preserve">2.81537747383118</t>
   </si>
   <si>
     <t xml:space="preserve">2.84648704528809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79982352256775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73760509490967</t>
+    <t xml:space="preserve">2.79982280731201</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73760485649109</t>
   </si>
   <si>
     <t xml:space="preserve">2.76093673706055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80760049819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00980973243713</t>
+    <t xml:space="preserve">2.80760025978088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00980997085571</t>
   </si>
   <si>
     <t xml:space="preserve">2.9553689956665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90870523452759</t>
+    <t xml:space="preserve">2.90870499610901</t>
   </si>
   <si>
     <t xml:space="preserve">2.88537311553955</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82315516471863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86204147338867</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00203275680542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91648244857788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.85426425933838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7298276424408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6831636428833</t>
+    <t xml:space="preserve">2.82315492630005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86204171180725</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00203251838684</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9164822101593</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8542640209198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72982740402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68316388130188</t>
   </si>
   <si>
     <t xml:space="preserve">2.72205018997192</t>
@@ -329,7 +329,7 @@
     <t xml:space="preserve">2.75315952301025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70649576187134</t>
+    <t xml:space="preserve">2.70649552345276</t>
   </si>
   <si>
     <t xml:space="preserve">2.93981432914734</t>
@@ -338,37 +338,37 @@
     <t xml:space="preserve">2.99425530433655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97870063781738</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86981868743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94759154319763</t>
+    <t xml:space="preserve">2.97870087623596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86981892585754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94759178161621</t>
   </si>
   <si>
     <t xml:space="preserve">2.98647809028625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63650012016296</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55095028877258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51984095573425</t>
+    <t xml:space="preserve">2.63650035858154</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.550950050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51984119415283</t>
   </si>
   <si>
     <t xml:space="preserve">2.41095876693726</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34096312522888</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34874057769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3642954826355</t>
+    <t xml:space="preserve">2.34096360206604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34874081611633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36429524421692</t>
   </si>
   <si>
     <t xml:space="preserve">2.2554132938385</t>
@@ -383,7 +383,7 @@
     <t xml:space="preserve">2.23208117485046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18541741371155</t>
+    <t xml:space="preserve">2.18541765213013</t>
   </si>
   <si>
     <t xml:space="preserve">2.27874493598938</t>
@@ -392,55 +392,55 @@
     <t xml:space="preserve">2.26319050788879</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2165265083313</t>
+    <t xml:space="preserve">2.21652674674988</t>
   </si>
   <si>
     <t xml:space="preserve">2.06875848770142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14653134346008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10764503479004</t>
+    <t xml:space="preserve">2.1465311050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10764479637146</t>
   </si>
   <si>
     <t xml:space="preserve">2.1543083190918</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17764043807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22430372238159</t>
+    <t xml:space="preserve">2.17764019966125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22430396080017</t>
   </si>
   <si>
     <t xml:space="preserve">2.35651803016663</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4887318611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52761793136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43429088592529</t>
+    <t xml:space="preserve">2.48873209953308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52761816978455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43429112434387</t>
   </si>
   <si>
     <t xml:space="preserve">2.44206809997559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5587272644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44984531402588</t>
+    <t xml:space="preserve">2.55872702598572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44984555244446</t>
   </si>
   <si>
     <t xml:space="preserve">2.37207245826721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33318614959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29429984092712</t>
+    <t xml:space="preserve">2.33318638801575</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29429936408997</t>
   </si>
   <si>
     <t xml:space="preserve">2.3798496723175</t>
@@ -455,34 +455,34 @@
     <t xml:space="preserve">2.62872314453125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65983200073242</t>
+    <t xml:space="preserve">2.659832239151</t>
   </si>
   <si>
     <t xml:space="preserve">2.57428193092346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67538690567017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64427733421326</t>
+    <t xml:space="preserve">2.67538666725159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64427757263184</t>
   </si>
   <si>
     <t xml:space="preserve">2.69094133377075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76871418952942</t>
+    <t xml:space="preserve">2.76871395111084</t>
   </si>
   <si>
     <t xml:space="preserve">2.90092778205872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96314597129822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92425990104675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97092342376709</t>
+    <t xml:space="preserve">2.9631462097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92425966262817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97092318534851</t>
   </si>
   <si>
     <t xml:space="preserve">3.01758742332458</t>
@@ -494,19 +494,19 @@
     <t xml:space="preserve">3.03314208984375</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0642511844635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07980585098267</t>
+    <t xml:space="preserve">3.06425094604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07980561256409</t>
   </si>
   <si>
     <t xml:space="preserve">3.0604989528656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02811288833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01191973686218</t>
+    <t xml:space="preserve">3.0281126499176</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0119194984436</t>
   </si>
   <si>
     <t xml:space="preserve">3.1090784072876</t>
@@ -521,13 +521,13 @@
     <t xml:space="preserve">3.0766921043396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99572682380676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30339598655701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41674757003784</t>
+    <t xml:space="preserve">2.99572658538818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30339550971985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41674733161926</t>
   </si>
   <si>
     <t xml:space="preserve">3.35197496414185</t>
@@ -536,7 +536,7 @@
     <t xml:space="preserve">3.33578181266785</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36816835403442</t>
+    <t xml:space="preserve">3.36816787719727</t>
   </si>
   <si>
     <t xml:space="preserve">3.23862338066101</t>
@@ -548,28 +548,28 @@
     <t xml:space="preserve">3.27100944519043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28720259666443</t>
+    <t xml:space="preserve">3.28720235824585</t>
   </si>
   <si>
     <t xml:space="preserve">3.22243022918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17385077476501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20623731613159</t>
+    <t xml:space="preserve">3.17385101318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20623707771301</t>
   </si>
   <si>
     <t xml:space="preserve">3.1414647102356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40055441856384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49771356582642</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38436126708984</t>
+    <t xml:space="preserve">3.40055465698242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49771332740784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38436150550842</t>
   </si>
   <si>
     <t xml:space="preserve">3.25481629371643</t>
@@ -578,7 +578,7 @@
     <t xml:space="preserve">3.19004416465759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96334028244019</t>
+    <t xml:space="preserve">2.96334052085876</t>
   </si>
   <si>
     <t xml:space="preserve">2.97953343391418</t>
@@ -593,16 +593,16 @@
     <t xml:space="preserve">2.86618161201477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84998869895935</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78521633148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75282979011536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72044372558594</t>
+    <t xml:space="preserve">2.84998846054077</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78521609306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75283002853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72044348716736</t>
   </si>
   <si>
     <t xml:space="preserve">2.83379530906677</t>
@@ -611,40 +611,40 @@
     <t xml:space="preserve">2.76902294158936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73663663864136</t>
+    <t xml:space="preserve">2.73663687705994</t>
   </si>
   <si>
     <t xml:space="preserve">2.81760215759277</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89856743812561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91476106643677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63947772979736</t>
+    <t xml:space="preserve">2.89856767654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91476082801819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63947820663452</t>
   </si>
   <si>
     <t xml:space="preserve">2.67186427116394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62328481674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68805718421936</t>
+    <t xml:space="preserve">2.62328505516052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68805742263794</t>
   </si>
   <si>
     <t xml:space="preserve">2.70425033569336</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60709190368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59089875221252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42896747589111</t>
+    <t xml:space="preserve">2.6070921421051</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5908989906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42896771430969</t>
   </si>
   <si>
     <t xml:space="preserve">2.54231929779053</t>
@@ -653,10 +653,10 @@
     <t xml:space="preserve">2.46135377883911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31561541557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29942274093628</t>
+    <t xml:space="preserve">2.3156156539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2994225025177</t>
   </si>
   <si>
     <t xml:space="preserve">2.35488176345825</t>
@@ -665,10 +665,10 @@
     <t xml:space="preserve">2.40607476234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28662419319153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1330451965332</t>
+    <t xml:space="preserve">2.28662443161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13304495811462</t>
   </si>
   <si>
     <t xml:space="preserve">2.08185195922852</t>
@@ -683,64 +683,64 @@
     <t xml:space="preserve">2.1671736240387</t>
   </si>
   <si>
-    <t xml:space="preserve">2.09891605377197</t>
+    <t xml:space="preserve">2.09891629219055</t>
   </si>
   <si>
     <t xml:space="preserve">2.26955986022949</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21836686134338</t>
+    <t xml:space="preserve">2.21836638450623</t>
   </si>
   <si>
     <t xml:space="preserve">2.32075309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55965423583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54258990287781</t>
+    <t xml:space="preserve">2.55965399742126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54258966445923</t>
   </si>
   <si>
     <t xml:space="preserve">2.45726799964905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5767183303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62791156768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61084699630737</t>
+    <t xml:space="preserve">2.57671856880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62791132926941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61084723472595</t>
   </si>
   <si>
     <t xml:space="preserve">2.64497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59378290176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69616913795471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71323299407959</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44020318984985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42313933372498</t>
+    <t xml:space="preserve">2.59378266334534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69616889953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71323323249817</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44020342826843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4231390953064</t>
   </si>
   <si>
     <t xml:space="preserve">2.47433233261108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15010952949524</t>
+    <t xml:space="preserve">2.15010929107666</t>
   </si>
   <si>
     <t xml:space="preserve">2.33781743049622</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30368852615356</t>
+    <t xml:space="preserve">2.30368876457214</t>
   </si>
   <si>
     <t xml:space="preserve">2.25249552726746</t>
@@ -749,13 +749,13 @@
     <t xml:space="preserve">2.23543095588684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37194609642029</t>
+    <t xml:space="preserve">2.37194633483887</t>
   </si>
   <si>
     <t xml:space="preserve">2.38901042938232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20130252838135</t>
+    <t xml:space="preserve">2.20130228996277</t>
   </si>
   <si>
     <t xml:space="preserve">2.18423795700073</t>
@@ -764,55 +764,55 @@
     <t xml:space="preserve">2.01359438896179</t>
   </si>
   <si>
-    <t xml:space="preserve">2.04772305488586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11598038673401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91120827198029</t>
+    <t xml:space="preserve">2.04772353172302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11598062515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91120839118958</t>
   </si>
   <si>
     <t xml:space="preserve">1.8770797252655</t>
   </si>
   <si>
-    <t xml:space="preserve">1.84295094013214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97946584224701</t>
+    <t xml:space="preserve">1.84295105934143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97946560382843</t>
   </si>
   <si>
     <t xml:space="preserve">1.86001539230347</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94533717632294</t>
+    <t xml:space="preserve">1.94533705711365</t>
   </si>
   <si>
     <t xml:space="preserve">1.96240139007568</t>
   </si>
   <si>
-    <t xml:space="preserve">1.99653005599976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81561946868896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90094137191772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88387680053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76442670822144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73029780387878</t>
+    <t xml:space="preserve">1.99653017520905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81561970710754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9009416103363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88387703895569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76442623138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73029756546021</t>
   </si>
   <si>
     <t xml:space="preserve">2.6791045665741</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74736213684082</t>
+    <t xml:space="preserve">2.74736166000366</t>
   </si>
   <si>
     <t xml:space="preserve">2.832683801651</t>
@@ -824,13 +824,13 @@
     <t xml:space="preserve">2.79855513572693</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78149056434631</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93507027626038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96919894218445</t>
+    <t xml:space="preserve">2.78149080276489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9350700378418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96919870376587</t>
   </si>
   <si>
     <t xml:space="preserve">3.02039170265198</t>
@@ -839,13 +839,13 @@
     <t xml:space="preserve">3.00332736968994</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03745627403259</t>
+    <t xml:space="preserve">3.03745579719543</t>
   </si>
   <si>
     <t xml:space="preserve">2.98626303672791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05452013015747</t>
+    <t xml:space="preserve">3.05452060699463</t>
   </si>
   <si>
     <t xml:space="preserve">3.07158470153809</t>
@@ -854,49 +854,49 @@
     <t xml:space="preserve">3.13984251022339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11424565315247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13131022453308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06305265426636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.16543865203857</t>
+    <t xml:space="preserve">3.11424589157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1313099861145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06305241584778</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.16543889045715</t>
   </si>
   <si>
     <t xml:space="preserve">3.19956755638123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15690684318542</t>
+    <t xml:space="preserve">3.15690660476685</t>
   </si>
   <si>
     <t xml:space="preserve">3.2336962223053</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2763569355011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24222850799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26782512664795</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31048607826233</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.3446147441864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32755017280579</t>
+    <t xml:space="preserve">3.27635669708252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24222826957703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26782488822937</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31048583984375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34461498260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32755041122437</t>
   </si>
   <si>
     <t xml:space="preserve">3.28488922119141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.18250298500061</t>
+    <t xml:space="preserve">3.18250322341919</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342126846313</t>
@@ -905,16 +905,16 @@
     <t xml:space="preserve">3.33710074424744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32836508750916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29342174530029</t>
+    <t xml:space="preserve">3.32836484909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29342150688171</t>
   </si>
   <si>
     <t xml:space="preserve">3.24974226951599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20606303215027</t>
+    <t xml:space="preserve">3.20606279373169</t>
   </si>
   <si>
     <t xml:space="preserve">3.15364766120911</t>
@@ -923,7 +923,7 @@
     <t xml:space="preserve">3.21479892730713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17111968994141</t>
+    <t xml:space="preserve">3.17111945152283</t>
   </si>
   <si>
     <t xml:space="preserve">3.26721382141113</t>
@@ -932,7 +932,7 @@
     <t xml:space="preserve">3.36330842971802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49434638023376</t>
+    <t xml:space="preserve">3.49434661865234</t>
   </si>
   <si>
     <t xml:space="preserve">3.58170509338379</t>
@@ -941,40 +941,40 @@
     <t xml:space="preserve">3.56423330307007</t>
   </si>
   <si>
-    <t xml:space="preserve">3.59044098854065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50308275222778</t>
+    <t xml:space="preserve">3.59044122695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5030825138092</t>
   </si>
   <si>
     <t xml:space="preserve">3.51181840896606</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54676151275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63412022590637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62538480758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74768662452698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69527149200439</t>
+    <t xml:space="preserve">3.54676175117493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63411998748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62538456916809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7476863861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69527125358582</t>
   </si>
   <si>
     <t xml:space="preserve">3.66906380653381</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60791277885437</t>
+    <t xml:space="preserve">3.60791301727295</t>
   </si>
   <si>
     <t xml:space="preserve">3.55549788475037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66032791137695</t>
+    <t xml:space="preserve">3.66032814979553</t>
   </si>
   <si>
     <t xml:space="preserve">3.65159201622009</t>
@@ -983,7 +983,7 @@
     <t xml:space="preserve">3.68653535842896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70400714874268</t>
+    <t xml:space="preserve">3.7040069103241</t>
   </si>
   <si>
     <t xml:space="preserve">3.75642251968384</t>
@@ -992,19 +992,19 @@
     <t xml:space="preserve">3.57296967506409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.53802585601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34583687782288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38951635360718</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42445945739746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45066714286804</t>
+    <t xml:space="preserve">3.53802609443665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3458366394043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3895161151886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42445993423462</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45066738128662</t>
   </si>
   <si>
     <t xml:space="preserve">3.44193148612976</t>
@@ -1013,10 +1013,10 @@
     <t xml:space="preserve">3.48561072349548</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40698790550232</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35457253456116</t>
+    <t xml:space="preserve">3.4069881439209</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35457229614258</t>
   </si>
   <si>
     <t xml:space="preserve">3.45940327644348</t>
@@ -1028,19 +1028,19 @@
     <t xml:space="preserve">3.46813893318176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47687458992004</t>
+    <t xml:space="preserve">3.47687482833862</t>
   </si>
   <si>
     <t xml:space="preserve">3.79136610031128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7214789390564</t>
+    <t xml:space="preserve">3.72147941589355</t>
   </si>
   <si>
     <t xml:space="preserve">3.87872457504272</t>
   </si>
   <si>
-    <t xml:space="preserve">4.17574453353882</t>
+    <t xml:space="preserve">4.17574405670166</t>
   </si>
   <si>
     <t xml:space="preserve">4.31551790237427</t>
@@ -1049,19 +1049,19 @@
     <t xml:space="preserve">4.35046148300171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1844801902771</t>
+    <t xml:space="preserve">4.18447971343994</t>
   </si>
   <si>
     <t xml:space="preserve">4.20195150375366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25436639785767</t>
+    <t xml:space="preserve">4.25436687469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493178367615</t>
+    <t xml:space="preserve">3.90493226051331</t>
   </si>
   <si>
     <t xml:space="preserve">3.98355507850647</t>
@@ -1073,7 +1073,7 @@
     <t xml:space="preserve">3.93113970756531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08838510513306</t>
+    <t xml:space="preserve">4.08838558197021</t>
   </si>
   <si>
     <t xml:space="preserve">4.07091379165649</t>
@@ -1085,16 +1085,16 @@
     <t xml:space="preserve">4.00102663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00976228713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93987607955933</t>
+    <t xml:space="preserve">4.00976324081421</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93987584114075</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21068716049194</t>
+    <t xml:space="preserve">4.2106876373291</t>
   </si>
   <si>
     <t xml:space="preserve">4.29804611206055</t>
@@ -1103,16 +1103,16 @@
     <t xml:space="preserve">4.28930997848511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21942377090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19321584701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1495361328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16700839996338</t>
+    <t xml:space="preserve">4.21942329406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19321632385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14953660964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16700792312622</t>
   </si>
   <si>
     <t xml:space="preserve">4.11459302902222</t>
@@ -1124,40 +1124,40 @@
     <t xml:space="preserve">3.78262996673584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.80010151863098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82630968093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83504486083984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84378123283386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77389430999756</t>
+    <t xml:space="preserve">3.80010175704956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8263099193573</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83504557609558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84378147125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77389454841614</t>
   </si>
   <si>
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734763145447</t>
+    <t xml:space="preserve">3.95734786987305</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.861252784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7651584148407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8175733089447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64285635948181</t>
+    <t xml:space="preserve">3.86125302314758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76515793800354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81757354736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64285612106323</t>
   </si>
   <si>
     <t xml:space="preserve">3.67779970169067</t>
@@ -1172,49 +1172,49 @@
     <t xml:space="preserve">3.71274328231812</t>
   </si>
   <si>
-    <t xml:space="preserve">3.92240357398987</t>
+    <t xml:space="preserve">3.92240381240845</t>
   </si>
   <si>
     <t xml:space="preserve">3.61664843559265</t>
   </si>
   <si>
-    <t xml:space="preserve">3.39825224876404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23227071762085</t>
+    <t xml:space="preserve">3.39825201034546</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23227047920227</t>
   </si>
   <si>
     <t xml:space="preserve">3.0575532913208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97019457817078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95272278785706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91777920722961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90904331207275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37204432487488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38077998161316</t>
+    <t xml:space="preserve">2.97019481658936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95272302627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91777944564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90904355049133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3720440864563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38078022003174</t>
   </si>
   <si>
     <t xml:space="preserve">3.41572380065918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31962919235229</t>
+    <t xml:space="preserve">3.31962895393372</t>
   </si>
   <si>
     <t xml:space="preserve">3.27594995498657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28468585014343</t>
+    <t xml:space="preserve">3.28468561172485</t>
   </si>
   <si>
     <t xml:space="preserve">3.50245499610901</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">3.32098078727722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26653838157654</t>
+    <t xml:space="preserve">3.26653814315796</t>
   </si>
   <si>
     <t xml:space="preserve">3.39357042312622</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">3.23024344444275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19394850730896</t>
+    <t xml:space="preserve">3.19394874572754</t>
   </si>
   <si>
     <t xml:space="preserve">3.25746440887451</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">3.2211697101593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10321164131165</t>
+    <t xml:space="preserve">3.10321140289307</t>
   </si>
   <si>
     <t xml:space="preserve">2.99432682991028</t>
@@ -1286,13 +1286,13 @@
     <t xml:space="preserve">2.95803189277649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85822129249573</t>
+    <t xml:space="preserve">2.85822105407715</t>
   </si>
   <si>
     <t xml:space="preserve">2.89451599121094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86729502677917</t>
+    <t xml:space="preserve">2.8672947883606</t>
   </si>
   <si>
     <t xml:space="preserve">2.81285238265991</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">2.75841021537781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7039680480957</t>
+    <t xml:space="preserve">2.70396780967712</t>
   </si>
   <si>
     <t xml:space="preserve">2.72211527824402</t>
@@ -1313,16 +1313,16 @@
     <t xml:space="preserve">2.64952564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79470491409302</t>
+    <t xml:space="preserve">2.7947051525116</t>
   </si>
   <si>
     <t xml:space="preserve">2.92173719406128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05784296989441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02154779434204</t>
+    <t xml:space="preserve">3.05784273147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02154803276062</t>
   </si>
   <si>
     <t xml:space="preserve">3.13950634002686</t>
@@ -1352,46 +1352,46 @@
     <t xml:space="preserve">3.08506417274475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01247406005859</t>
+    <t xml:space="preserve">3.01247429847717</t>
   </si>
   <si>
     <t xml:space="preserve">2.88544225692749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77655744552612</t>
+    <t xml:space="preserve">2.7765576839447</t>
   </si>
   <si>
     <t xml:space="preserve">2.71304154396057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63137817382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68582057952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66767311096191</t>
+    <t xml:space="preserve">2.6313784122467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68582034111023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66767287254333</t>
   </si>
   <si>
     <t xml:space="preserve">2.55878829956055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52249360084534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67674684524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64045190811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87636876106262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83099961280823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6041567325592</t>
+    <t xml:space="preserve">2.52249336242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67674660682678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64045214653015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87636852264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83099985122681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60415697097778</t>
   </si>
   <si>
     <t xml:space="preserve">2.73118901252747</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">2.91266345977783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12135910987854</t>
+    <t xml:space="preserve">3.12135887145996</t>
   </si>
   <si>
     <t xml:space="preserve">3.0759904384613</t>
@@ -1427,46 +1427,46 @@
     <t xml:space="preserve">3.0941379070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38449668884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41171789169312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37542295455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42079162597656</t>
+    <t xml:space="preserve">3.38449692726135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41171765327454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37542319297791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42079138755798</t>
   </si>
   <si>
     <t xml:space="preserve">3.43893885612488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36634922027588</t>
+    <t xml:space="preserve">3.36634945869446</t>
   </si>
   <si>
     <t xml:space="preserve">3.35727572441101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20302224159241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27561211585999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29375982284546</t>
+    <t xml:space="preserve">3.20302248001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27561187744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29375958442688</t>
   </si>
   <si>
     <t xml:space="preserve">3.1667275428772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11228537559509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78563117980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84007358551025</t>
+    <t xml:space="preserve">3.11228513717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78563141822815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84007382392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.82192611694336</t>
@@ -57495,7 +57495,7 @@
     </row>
     <row r="2130">
       <c r="A2130" s="1" t="n">
-        <v>46069.6675925926</v>
+        <v>46069.3333333333</v>
       </c>
       <c r="B2130" t="n">
         <v>6623</v>
@@ -57516,6 +57516,32 @@
         <v>585</v>
       </c>
       <c r="H2130" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2131">
+      <c r="A2131" s="1" t="n">
+        <v>46070.6203009259</v>
+      </c>
+      <c r="B2131" t="n">
+        <v>11174</v>
+      </c>
+      <c r="C2131" t="n">
+        <v>3.77999997138977</v>
+      </c>
+      <c r="D2131" t="n">
+        <v>3.72000002861023</v>
+      </c>
+      <c r="E2131" t="n">
+        <v>3.74000000953674</v>
+      </c>
+      <c r="F2131" t="n">
+        <v>3.72000002861023</v>
+      </c>
+      <c r="G2131" t="s">
+        <v>590</v>
+      </c>
+      <c r="H2131" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -38,19 +38,19 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02345776557922</t>
+    <t xml:space="preserve">3.02345752716064</t>
   </si>
   <si>
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519923210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88901519775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98013710975647</t>
+    <t xml:space="preserve">2.96519947052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88901567459106</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98013734817505</t>
   </si>
   <si>
     <t xml:space="preserve">2.97266840934753</t>
@@ -65,13 +65,13 @@
     <t xml:space="preserve">2.9622118473053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9353232383728</t>
+    <t xml:space="preserve">2.93532347679138</t>
   </si>
   <si>
     <t xml:space="preserve">2.91291642189026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97864317893982</t>
+    <t xml:space="preserve">2.97864365577698</t>
   </si>
   <si>
     <t xml:space="preserve">2.98611235618591</t>
@@ -86,52 +86,52 @@
     <t xml:space="preserve">3.0593090057373</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05034613609314</t>
+    <t xml:space="preserve">3.05034589767456</t>
   </si>
   <si>
     <t xml:space="preserve">2.98760628700256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95026111602783</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01598882675171</t>
+    <t xml:space="preserve">2.95026135444641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01598834991455</t>
   </si>
   <si>
     <t xml:space="preserve">3.01001358032227</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02495169639587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01748204231262</t>
+    <t xml:space="preserve">3.02495145797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01748251914978</t>
   </si>
   <si>
     <t xml:space="preserve">3.03092670440674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99955677986145</t>
+    <t xml:space="preserve">2.99955701828003</t>
   </si>
   <si>
     <t xml:space="preserve">3.04437112808228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95922422409058</t>
+    <t xml:space="preserve">2.959223985672</t>
   </si>
   <si>
     <t xml:space="preserve">3.00254440307617</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92785453796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90843462944031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89648461341858</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91889095306396</t>
+    <t xml:space="preserve">2.92785429954529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90843486785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91889119148254</t>
   </si>
   <si>
     <t xml:space="preserve">2.9159038066864</t>
@@ -140,16 +140,16 @@
     <t xml:space="preserve">2.92038536071777</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90544700622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90992832183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92337274551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83822584152222</t>
+    <t xml:space="preserve">2.90544724464417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90992856025696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9233729839325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83822560310364</t>
   </si>
   <si>
     <t xml:space="preserve">2.86063313484192</t>
@@ -158,10 +158,10 @@
     <t xml:space="preserve">2.82627558708191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77996778488159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84569501876831</t>
+    <t xml:space="preserve">2.77996754646301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84569525718689</t>
   </si>
   <si>
     <t xml:space="preserve">2.86810207366943</t>
@@ -176,7 +176,7 @@
     <t xml:space="preserve">2.87557101249695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89797806739807</t>
+    <t xml:space="preserve">2.89797830581665</t>
   </si>
   <si>
     <t xml:space="preserve">2.80088090896606</t>
@@ -188,22 +188,22 @@
     <t xml:space="preserve">2.82179427146912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75009155273438</t>
+    <t xml:space="preserve">2.75009179115295</t>
   </si>
   <si>
     <t xml:space="preserve">2.76353597640991</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77847361564636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78594255447388</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79341173171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69631457328796</t>
+    <t xml:space="preserve">2.77847385406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78594303131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79341197013855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69631433486938</t>
   </si>
   <si>
     <t xml:space="preserve">2.6515007019043</t>
@@ -212,16 +212,16 @@
     <t xml:space="preserve">2.62162446975708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53946566581726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56934142112732</t>
+    <t xml:space="preserve">2.53946542739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5693416595459</t>
   </si>
   <si>
     <t xml:space="preserve">2.61415553092957</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65896964073181</t>
+    <t xml:space="preserve">2.65896940231323</t>
   </si>
   <si>
     <t xml:space="preserve">2.68884563446045</t>
@@ -233,34 +233,34 @@
     <t xml:space="preserve">2.77100491523743</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81581878662109</t>
+    <t xml:space="preserve">2.81581926345825</t>
   </si>
   <si>
     <t xml:space="preserve">2.73365998268127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66643834114075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68137645721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74112868309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7261905670166</t>
+    <t xml:space="preserve">2.66643857955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68137669563293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74112892150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72619080543518</t>
   </si>
   <si>
     <t xml:space="preserve">2.83075714111328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89315056800842</t>
+    <t xml:space="preserve">2.893150806427</t>
   </si>
   <si>
     <t xml:space="preserve">2.69871854782104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83870959281921</t>
+    <t xml:space="preserve">2.83870983123779</t>
   </si>
   <si>
     <t xml:space="preserve">2.93203711509705</t>
@@ -278,7 +278,7 @@
     <t xml:space="preserve">2.84648704528809</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79982280731201</t>
+    <t xml:space="preserve">2.79982328414917</t>
   </si>
   <si>
     <t xml:space="preserve">2.73760485649109</t>
@@ -290,19 +290,19 @@
     <t xml:space="preserve">2.80760025978088</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00980997085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9553689956665</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90870499610901</t>
+    <t xml:space="preserve">3.00980973243713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95536875724792</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90870547294617</t>
   </si>
   <si>
     <t xml:space="preserve">2.88537311553955</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82315492630005</t>
+    <t xml:space="preserve">2.82315516471863</t>
   </si>
   <si>
     <t xml:space="preserve">2.86204171180725</t>
@@ -311,16 +311,16 @@
     <t xml:space="preserve">3.00203251838684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9164822101593</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8542640209198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72982740402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68316388130188</t>
+    <t xml:space="preserve">2.91648268699646</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.85426449775696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7298276424408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68316411972046</t>
   </si>
   <si>
     <t xml:space="preserve">2.72205018997192</t>
@@ -329,19 +329,19 @@
     <t xml:space="preserve">2.75315952301025</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70649552345276</t>
+    <t xml:space="preserve">2.70649576187134</t>
   </si>
   <si>
     <t xml:space="preserve">2.93981432914734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99425530433655</t>
+    <t xml:space="preserve">2.99425554275513</t>
   </si>
   <si>
     <t xml:space="preserve">2.97870087623596</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86981892585754</t>
+    <t xml:space="preserve">2.86981868743896</t>
   </si>
   <si>
     <t xml:space="preserve">2.94759178161621</t>
@@ -356,13 +356,13 @@
     <t xml:space="preserve">2.550950050354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51984119415283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41095876693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34096360206604</t>
+    <t xml:space="preserve">2.51984095573425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41095900535583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34096336364746</t>
   </si>
   <si>
     <t xml:space="preserve">2.34874081611633</t>
@@ -371,25 +371,25 @@
     <t xml:space="preserve">2.36429524421692</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2554132938385</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24763607978821</t>
+    <t xml:space="preserve">2.25541305541992</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24763584136963</t>
   </si>
   <si>
     <t xml:space="preserve">2.3254086971283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23208117485046</t>
+    <t xml:space="preserve">2.23208093643188</t>
   </si>
   <si>
     <t xml:space="preserve">2.18541765213013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27874493598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26319050788879</t>
+    <t xml:space="preserve">2.27874517440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26319026947021</t>
   </si>
   <si>
     <t xml:space="preserve">2.21652674674988</t>
@@ -401,34 +401,34 @@
     <t xml:space="preserve">2.1465311050415</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10764479637146</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1543083190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17764019966125</t>
+    <t xml:space="preserve">2.10764455795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15430855751038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17763996124268</t>
   </si>
   <si>
     <t xml:space="preserve">2.22430396080017</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35651803016663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48873209953308</t>
+    <t xml:space="preserve">2.35651779174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4887318611145</t>
   </si>
   <si>
     <t xml:space="preserve">2.52761816978455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43429112434387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44206809997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55872702598572</t>
+    <t xml:space="preserve">2.43429088592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44206786155701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55872750282288</t>
   </si>
   <si>
     <t xml:space="preserve">2.44984555244446</t>
@@ -437,16 +437,16 @@
     <t xml:space="preserve">2.37207245826721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33318638801575</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29429936408997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3798496723175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71427297592163</t>
+    <t xml:space="preserve">2.33318591117859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29429960250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37984991073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71427321434021</t>
   </si>
   <si>
     <t xml:space="preserve">2.58205914497375</t>
@@ -455,46 +455,46 @@
     <t xml:space="preserve">2.62872314453125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.659832239151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57428193092346</t>
+    <t xml:space="preserve">2.65983200073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57428169250488</t>
   </si>
   <si>
     <t xml:space="preserve">2.67538666725159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64427757263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69094133377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76871395111084</t>
+    <t xml:space="preserve">2.64427781105042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69094109535217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.768714427948</t>
   </si>
   <si>
     <t xml:space="preserve">2.90092778205872</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9631462097168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92425966262817</t>
+    <t xml:space="preserve">2.96314597129822</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92426013946533</t>
   </si>
   <si>
     <t xml:space="preserve">2.97092318534851</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01758742332458</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04869651794434</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03314208984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06425094604492</t>
+    <t xml:space="preserve">3.01758718490601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04869627952576</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03314185142517</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0642511844635</t>
   </si>
   <si>
     <t xml:space="preserve">3.07980561256409</t>
@@ -503,46 +503,46 @@
     <t xml:space="preserve">3.0604989528656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0281126499176</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0119194984436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1090784072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09288501739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1252715587616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0766921043396</t>
+    <t xml:space="preserve">3.02811288833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01191973686218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10907816886902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0928852558136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12527132034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07669186592102</t>
   </si>
   <si>
     <t xml:space="preserve">2.99572658538818</t>
   </si>
   <si>
-    <t xml:space="preserve">3.30339550971985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41674733161926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35197496414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33578181266785</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36816787719727</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23862338066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31958866119385</t>
+    <t xml:space="preserve">3.30339574813843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41674757003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35197520256042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33578205108643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36816835403442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23862314224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31958889961243</t>
   </si>
   <si>
     <t xml:space="preserve">3.27100944519043</t>
@@ -557,31 +557,31 @@
     <t xml:space="preserve">3.17385101318359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20623707771301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1414647102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40055465698242</t>
+    <t xml:space="preserve">3.20623731613159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14146494865417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40055418014526</t>
   </si>
   <si>
     <t xml:space="preserve">3.49771332740784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38436150550842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25481629371643</t>
+    <t xml:space="preserve">3.38436126708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25481653213501</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004416465759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96334052085876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97953343391418</t>
+    <t xml:space="preserve">2.96334028244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97953367233276</t>
   </si>
   <si>
     <t xml:space="preserve">2.80140924453735</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">2.86618161201477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84998846054077</t>
+    <t xml:space="preserve">2.84998822212219</t>
   </si>
   <si>
     <t xml:space="preserve">2.78521609306335</t>
@@ -602,19 +602,19 @@
     <t xml:space="preserve">2.75283002853394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72044348716736</t>
+    <t xml:space="preserve">2.72044372558594</t>
   </si>
   <si>
     <t xml:space="preserve">2.83379530906677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76902294158936</t>
+    <t xml:space="preserve">2.76902318000793</t>
   </si>
   <si>
     <t xml:space="preserve">2.73663687705994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81760215759277</t>
+    <t xml:space="preserve">2.81760239601135</t>
   </si>
   <si>
     <t xml:space="preserve">2.89856767654419</t>
@@ -623,49 +623,49 @@
     <t xml:space="preserve">2.91476082801819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63947820663452</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67186427116394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62328505516052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68805742263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70425033569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6070921421051</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5908989906311</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42896771430969</t>
+    <t xml:space="preserve">2.63947772979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67186403274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62328481674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68805718421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70425057411194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60709190368652</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59089875221252</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42896747589111</t>
   </si>
   <si>
     <t xml:space="preserve">2.54231929779053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.46135377883911</t>
+    <t xml:space="preserve">2.46135354042053</t>
   </si>
   <si>
     <t xml:space="preserve">2.3156156539917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2994225025177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35488176345825</t>
+    <t xml:space="preserve">2.29942274093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35488152503967</t>
   </si>
   <si>
     <t xml:space="preserve">2.40607476234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28662443161011</t>
+    <t xml:space="preserve">2.28662419319153</t>
   </si>
   <si>
     <t xml:space="preserve">2.13304495811462</t>
@@ -686,40 +686,40 @@
     <t xml:space="preserve">2.09891629219055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26955986022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21836638450623</t>
+    <t xml:space="preserve">2.26956009864807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21836686134338</t>
   </si>
   <si>
     <t xml:space="preserve">2.32075309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55965399742126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54258966445923</t>
+    <t xml:space="preserve">2.55965423583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54258990287781</t>
   </si>
   <si>
     <t xml:space="preserve">2.45726799964905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57671856880188</t>
+    <t xml:space="preserve">2.5767183303833</t>
   </si>
   <si>
     <t xml:space="preserve">2.62791132926941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61084723472595</t>
+    <t xml:space="preserve">2.61084699630737</t>
   </si>
   <si>
     <t xml:space="preserve">2.64497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59378266334534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69616889953613</t>
+    <t xml:space="preserve">2.59378290176392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69616913795471</t>
   </si>
   <si>
     <t xml:space="preserve">2.71323323249817</t>
@@ -728,7 +728,7 @@
     <t xml:space="preserve">2.44020342826843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4231390953064</t>
+    <t xml:space="preserve">2.42313933372498</t>
   </si>
   <si>
     <t xml:space="preserve">2.47433233261108</t>
@@ -737,13 +737,13 @@
     <t xml:space="preserve">2.15010929107666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33781743049622</t>
+    <t xml:space="preserve">2.33781719207764</t>
   </si>
   <si>
     <t xml:space="preserve">2.30368876457214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25249552726746</t>
+    <t xml:space="preserve">2.25249576568604</t>
   </si>
   <si>
     <t xml:space="preserve">2.23543095588684</t>
@@ -755,16 +755,16 @@
     <t xml:space="preserve">2.38901042938232</t>
   </si>
   <si>
-    <t xml:space="preserve">2.20130228996277</t>
+    <t xml:space="preserve">2.20130252838135</t>
   </si>
   <si>
     <t xml:space="preserve">2.18423795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01359438896179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04772353172302</t>
+    <t xml:space="preserve">2.01359415054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04772329330444</t>
   </si>
   <si>
     <t xml:space="preserve">2.11598062515259</t>
@@ -773,31 +773,31 @@
     <t xml:space="preserve">1.91120839118958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.8770797252655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84295105934143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97946560382843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86001539230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94533705711365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96240139007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99653017520905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81561970710754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9009416103363</t>
+    <t xml:space="preserve">1.87707984447479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84295094013214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97946584224701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86001515388489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94533693790436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96240127086639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99652993679047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81561923027039</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90094137191772</t>
   </si>
   <si>
     <t xml:space="preserve">2.88387703895569</t>
@@ -809,22 +809,22 @@
     <t xml:space="preserve">2.73029756546021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6791045665741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74736166000366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.832683801651</t>
+    <t xml:space="preserve">2.67910432815552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74736189842224</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83268356323242</t>
   </si>
   <si>
     <t xml:space="preserve">2.86681246757507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79855513572693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78149080276489</t>
+    <t xml:space="preserve">2.79855489730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78149056434631</t>
   </si>
   <si>
     <t xml:space="preserve">2.9350700378418</t>
@@ -836,16 +836,16 @@
     <t xml:space="preserve">3.02039170265198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00332736968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03745579719543</t>
+    <t xml:space="preserve">3.00332713127136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03745627403259</t>
   </si>
   <si>
     <t xml:space="preserve">2.98626303672791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05452060699463</t>
+    <t xml:space="preserve">3.05452036857605</t>
   </si>
   <si>
     <t xml:space="preserve">3.07158470153809</t>
@@ -857,10 +857,10 @@
     <t xml:space="preserve">3.11424589157104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1313099861145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.06305241584778</t>
+    <t xml:space="preserve">3.13131022453308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06305265426636</t>
   </si>
   <si>
     <t xml:space="preserve">3.16543889045715</t>
@@ -872,10 +872,10 @@
     <t xml:space="preserve">3.15690660476685</t>
   </si>
   <si>
-    <t xml:space="preserve">3.2336962223053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27635669708252</t>
+    <t xml:space="preserve">3.23369646072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27635717391968</t>
   </si>
   <si>
     <t xml:space="preserve">3.24222826957703</t>
@@ -884,19 +884,19 @@
     <t xml:space="preserve">3.26782488822937</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31048583984375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34461498260498</t>
+    <t xml:space="preserve">3.31048607826233</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.34461450576782</t>
   </si>
   <si>
     <t xml:space="preserve">3.32755041122437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28488922119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18250322341919</t>
+    <t xml:space="preserve">3.28488945960999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18250346183777</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342126846313</t>
@@ -911,13 +911,13 @@
     <t xml:space="preserve">3.29342150688171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24974226951599</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20606279373169</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15364766120911</t>
+    <t xml:space="preserve">3.24974250793457</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20606303215027</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15364742279053</t>
   </si>
   <si>
     <t xml:space="preserve">3.21479892730713</t>
@@ -926,19 +926,19 @@
     <t xml:space="preserve">3.17111945152283</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26721382141113</t>
+    <t xml:space="preserve">3.26721405982971</t>
   </si>
   <si>
     <t xml:space="preserve">3.36330842971802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49434661865234</t>
+    <t xml:space="preserve">3.49434638023376</t>
   </si>
   <si>
     <t xml:space="preserve">3.58170509338379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56423330307007</t>
+    <t xml:space="preserve">3.56423354148865</t>
   </si>
   <si>
     <t xml:space="preserve">3.59044122695923</t>
@@ -947,25 +947,25 @@
     <t xml:space="preserve">3.5030825138092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51181840896606</t>
+    <t xml:space="preserve">3.51181817054749</t>
   </si>
   <si>
     <t xml:space="preserve">3.54676175117493</t>
   </si>
   <si>
-    <t xml:space="preserve">3.63411998748779</t>
+    <t xml:space="preserve">3.63412022590637</t>
   </si>
   <si>
     <t xml:space="preserve">3.62538456916809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7476863861084</t>
+    <t xml:space="preserve">3.74768662452698</t>
   </si>
   <si>
     <t xml:space="preserve">3.69527125358582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66906380653381</t>
+    <t xml:space="preserve">3.66906332969666</t>
   </si>
   <si>
     <t xml:space="preserve">3.60791301727295</t>
@@ -974,22 +974,22 @@
     <t xml:space="preserve">3.55549788475037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66032814979553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65159201622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68653535842896</t>
+    <t xml:space="preserve">3.66032767295837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65159177780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68653512001038</t>
   </si>
   <si>
     <t xml:space="preserve">3.7040069103241</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75642251968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57296967506409</t>
+    <t xml:space="preserve">3.75642275810242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57296943664551</t>
   </si>
   <si>
     <t xml:space="preserve">3.53802609443665</t>
@@ -998,28 +998,28 @@
     <t xml:space="preserve">3.3458366394043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3895161151886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42445993423462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45066738128662</t>
+    <t xml:space="preserve">3.38951635360718</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42445969581604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.45066714286804</t>
   </si>
   <si>
     <t xml:space="preserve">3.44193148612976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48561072349548</t>
+    <t xml:space="preserve">3.4856104850769</t>
   </si>
   <si>
     <t xml:space="preserve">3.4069881439209</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35457229614258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.45940327644348</t>
+    <t xml:space="preserve">3.35457253456116</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4594030380249</t>
   </si>
   <si>
     <t xml:space="preserve">3.52928996086121</t>
@@ -1028,19 +1028,19 @@
     <t xml:space="preserve">3.46813893318176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47687482833862</t>
+    <t xml:space="preserve">3.47687458992004</t>
   </si>
   <si>
     <t xml:space="preserve">3.79136610031128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.72147941589355</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87872457504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17574405670166</t>
+    <t xml:space="preserve">3.72147917747498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8787248134613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17574453353882</t>
   </si>
   <si>
     <t xml:space="preserve">4.31551790237427</t>
@@ -1049,34 +1049,34 @@
     <t xml:space="preserve">4.35046148300171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.18447971343994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20195150375366</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25436687469482</t>
+    <t xml:space="preserve">4.1844801902771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20195198059082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25436639785767</t>
   </si>
   <si>
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493226051331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98355507850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94861173629761</t>
+    <t xml:space="preserve">3.90493202209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98355484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94861149787903</t>
   </si>
   <si>
     <t xml:space="preserve">3.93113970756531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08838558197021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.07091379165649</t>
+    <t xml:space="preserve">4.08838510513306</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.07091331481934</t>
   </si>
   <si>
     <t xml:space="preserve">4.1233286857605</t>
@@ -1085,16 +1085,16 @@
     <t xml:space="preserve">4.00102663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00976324081421</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93987584114075</t>
+    <t xml:space="preserve">4.00976276397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93987560272217</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.2106876373291</t>
+    <t xml:space="preserve">4.21068811416626</t>
   </si>
   <si>
     <t xml:space="preserve">4.29804611206055</t>
@@ -1103,7 +1103,7 @@
     <t xml:space="preserve">4.28930997848511</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21942329406738</t>
+    <t xml:space="preserve">4.21942377090454</t>
   </si>
   <si>
     <t xml:space="preserve">4.19321632385254</t>
@@ -1112,28 +1112,28 @@
     <t xml:space="preserve">4.14953660964966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16700792312622</t>
+    <t xml:space="preserve">4.16700839996338</t>
   </si>
   <si>
     <t xml:space="preserve">4.11459302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06217765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78262996673584</t>
+    <t xml:space="preserve">4.06217813491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78263020515442</t>
   </si>
   <si>
     <t xml:space="preserve">3.80010175704956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8263099193573</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83504557609558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84378147125244</t>
+    <t xml:space="preserve">3.82630944252014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83504509925842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84378123283386</t>
   </si>
   <si>
     <t xml:space="preserve">3.77389454841614</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734786987305</t>
+    <t xml:space="preserve">3.95734739303589</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
@@ -1151,16 +1151,16 @@
     <t xml:space="preserve">3.86125302314758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76515793800354</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81757354736328</t>
+    <t xml:space="preserve">3.7651584148407</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8175733089447</t>
   </si>
   <si>
     <t xml:space="preserve">3.64285612106323</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67779970169067</t>
+    <t xml:space="preserve">3.67779946327209</t>
   </si>
   <si>
     <t xml:space="preserve">3.7389509677887</t>
@@ -1169,43 +1169,43 @@
     <t xml:space="preserve">3.85251712799072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71274328231812</t>
+    <t xml:space="preserve">3.71274304389954</t>
   </si>
   <si>
     <t xml:space="preserve">3.92240381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61664843559265</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.39825201034546</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23227047920227</t>
+    <t xml:space="preserve">3.61664867401123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.39825224876404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23227071762085</t>
   </si>
   <si>
     <t xml:space="preserve">3.0575532913208</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97019481658936</t>
+    <t xml:space="preserve">2.97019457817078</t>
   </si>
   <si>
     <t xml:space="preserve">2.95272302627563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91777944564819</t>
+    <t xml:space="preserve">2.91777920722961</t>
   </si>
   <si>
     <t xml:space="preserve">2.90904355049133</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3720440864563</t>
+    <t xml:space="preserve">3.37204432487488</t>
   </si>
   <si>
     <t xml:space="preserve">3.38078022003174</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41572380065918</t>
+    <t xml:space="preserve">3.41572403907776</t>
   </si>
   <si>
     <t xml:space="preserve">3.31962895393372</t>
@@ -57521,7 +57521,7 @@
     </row>
     <row r="2131">
       <c r="A2131" s="1" t="n">
-        <v>46070.6203009259</v>
+        <v>46070.3333333333</v>
       </c>
       <c r="B2131" t="n">
         <v>11174</v>
@@ -57542,6 +57542,32 @@
         <v>590</v>
       </c>
       <c r="H2131" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2132">
+      <c r="A2132" s="1" t="n">
+        <v>46071.6664467593</v>
+      </c>
+      <c r="B2132" t="n">
+        <v>2678</v>
+      </c>
+      <c r="C2132" t="n">
+        <v>3.77999997138977</v>
+      </c>
+      <c r="D2132" t="n">
+        <v>3.6800000667572</v>
+      </c>
+      <c r="E2132" t="n">
+        <v>3.77999997138977</v>
+      </c>
+      <c r="F2132" t="n">
+        <v>3.6800000667572</v>
+      </c>
+      <c r="G2132" t="s">
+        <v>584</v>
+      </c>
+      <c r="H2132" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02345752716064</t>
+    <t xml:space="preserve">3.02345728874207</t>
   </si>
   <si>
     <t xml:space="preserve">NDT.MI</t>
@@ -47,13 +47,13 @@
     <t xml:space="preserve">2.96519947052002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88901567459106</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98013734817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97266840934753</t>
+    <t xml:space="preserve">2.88901543617249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98013758659363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97266817092896</t>
   </si>
   <si>
     <t xml:space="preserve">2.94577980041504</t>
@@ -62,13 +62,13 @@
     <t xml:space="preserve">2.95773029327393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9622118473053</t>
+    <t xml:space="preserve">2.96221160888672</t>
   </si>
   <si>
     <t xml:space="preserve">2.93532347679138</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91291642189026</t>
+    <t xml:space="preserve">2.91291618347168</t>
   </si>
   <si>
     <t xml:space="preserve">2.97864365577698</t>
@@ -77,25 +77,25 @@
     <t xml:space="preserve">2.98611235618591</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03540802001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05632138252258</t>
+    <t xml:space="preserve">3.03540825843811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05632162094116</t>
   </si>
   <si>
     <t xml:space="preserve">3.0593090057373</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05034589767456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98760628700256</t>
+    <t xml:space="preserve">3.05034613609314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98760652542114</t>
   </si>
   <si>
     <t xml:space="preserve">2.95026135444641</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01598834991455</t>
+    <t xml:space="preserve">3.01598882675171</t>
   </si>
   <si>
     <t xml:space="preserve">3.01001358032227</t>
@@ -110,19 +110,19 @@
     <t xml:space="preserve">3.03092670440674</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99955701828003</t>
+    <t xml:space="preserve">2.99955677986145</t>
   </si>
   <si>
     <t xml:space="preserve">3.04437112808228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.959223985672</t>
+    <t xml:space="preserve">2.95922374725342</t>
   </si>
   <si>
     <t xml:space="preserve">3.00254440307617</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92785429954529</t>
+    <t xml:space="preserve">2.92785406112671</t>
   </si>
   <si>
     <t xml:space="preserve">2.90843486785889</t>
@@ -131,13 +131,13 @@
     <t xml:space="preserve">2.896484375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91889119148254</t>
+    <t xml:space="preserve">2.91889142990112</t>
   </si>
   <si>
     <t xml:space="preserve">2.9159038066864</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92038536071777</t>
+    <t xml:space="preserve">2.92038512229919</t>
   </si>
   <si>
     <t xml:space="preserve">2.90544724464417</t>
@@ -149,34 +149,34 @@
     <t xml:space="preserve">2.9233729839325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83822560310364</t>
+    <t xml:space="preserve">2.8382260799408</t>
   </si>
   <si>
     <t xml:space="preserve">2.86063313484192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82627558708191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77996754646301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84569525718689</t>
+    <t xml:space="preserve">2.82627534866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77996778488159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84569501876831</t>
   </si>
   <si>
     <t xml:space="preserve">2.86810207366943</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88304018974304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79639935493469</t>
+    <t xml:space="preserve">2.88303995132446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79639959335327</t>
   </si>
   <si>
     <t xml:space="preserve">2.87557101249695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89797830581665</t>
+    <t xml:space="preserve">2.89797806739807</t>
   </si>
   <si>
     <t xml:space="preserve">2.80088090896606</t>
@@ -188,7 +188,7 @@
     <t xml:space="preserve">2.82179427146912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75009179115295</t>
+    <t xml:space="preserve">2.75009155273438</t>
   </si>
   <si>
     <t xml:space="preserve">2.76353597640991</t>
@@ -200,25 +200,25 @@
     <t xml:space="preserve">2.78594303131104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79341197013855</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69631433486938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6515007019043</t>
+    <t xml:space="preserve">2.79341173171997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69631457328796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65150046348572</t>
   </si>
   <si>
     <t xml:space="preserve">2.62162446975708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53946542739868</t>
+    <t xml:space="preserve">2.5394651889801</t>
   </si>
   <si>
     <t xml:space="preserve">2.5693416595459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61415553092957</t>
+    <t xml:space="preserve">2.61415576934814</t>
   </si>
   <si>
     <t xml:space="preserve">2.65896940231323</t>
@@ -227,22 +227,22 @@
     <t xml:space="preserve">2.68884563446045</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70378351211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77100491523743</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81581926345825</t>
+    <t xml:space="preserve">2.70378375053406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77100515365601</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81581902503967</t>
   </si>
   <si>
     <t xml:space="preserve">2.73365998268127</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66643857955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68137669563293</t>
+    <t xml:space="preserve">2.66643834114075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68137645721436</t>
   </si>
   <si>
     <t xml:space="preserve">2.74112892150879</t>
@@ -251,28 +251,28 @@
     <t xml:space="preserve">2.72619080543518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83075714111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.893150806427</t>
+    <t xml:space="preserve">2.8307569026947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89315056800842</t>
   </si>
   <si>
     <t xml:space="preserve">2.69871854782104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83870983123779</t>
+    <t xml:space="preserve">2.83870959281921</t>
   </si>
   <si>
     <t xml:space="preserve">2.93203711509705</t>
   </si>
   <si>
-    <t xml:space="preserve">2.87759590148926</t>
+    <t xml:space="preserve">2.87759613990784</t>
   </si>
   <si>
     <t xml:space="preserve">2.83093237876892</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81537747383118</t>
+    <t xml:space="preserve">2.81537771224976</t>
   </si>
   <si>
     <t xml:space="preserve">2.84648704528809</t>
@@ -281,13 +281,13 @@
     <t xml:space="preserve">2.79982328414917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73760485649109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76093673706055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80760025978088</t>
+    <t xml:space="preserve">2.73760509490967</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76093649864197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80760049819946</t>
   </si>
   <si>
     <t xml:space="preserve">3.00980973243713</t>
@@ -296,13 +296,13 @@
     <t xml:space="preserve">2.95536875724792</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90870547294617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88537311553955</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82315516471863</t>
+    <t xml:space="preserve">2.90870499610901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88537359237671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82315540313721</t>
   </si>
   <si>
     <t xml:space="preserve">2.86204171180725</t>
@@ -314,16 +314,16 @@
     <t xml:space="preserve">2.91648268699646</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85426449775696</t>
+    <t xml:space="preserve">2.85426425933838</t>
   </si>
   <si>
     <t xml:space="preserve">2.7298276424408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68316411972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72205018997192</t>
+    <t xml:space="preserve">2.68316388130188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7220504283905</t>
   </si>
   <si>
     <t xml:space="preserve">2.75315952301025</t>
@@ -335,7 +335,7 @@
     <t xml:space="preserve">2.93981432914734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99425554275513</t>
+    <t xml:space="preserve">2.99425530433655</t>
   </si>
   <si>
     <t xml:space="preserve">2.97870087623596</t>
@@ -344,7 +344,7 @@
     <t xml:space="preserve">2.86981868743896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94759178161621</t>
+    <t xml:space="preserve">2.94759154319763</t>
   </si>
   <si>
     <t xml:space="preserve">2.98647809028625</t>
@@ -353,40 +353,40 @@
     <t xml:space="preserve">2.63650035858154</t>
   </si>
   <si>
-    <t xml:space="preserve">2.550950050354</t>
+    <t xml:space="preserve">2.55094981193542</t>
   </si>
   <si>
     <t xml:space="preserve">2.51984095573425</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41095900535583</t>
+    <t xml:space="preserve">2.41095876693726</t>
   </si>
   <si>
     <t xml:space="preserve">2.34096336364746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34874081611633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36429524421692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25541305541992</t>
+    <t xml:space="preserve">2.34874057769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36429500579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2554132938385</t>
   </si>
   <si>
     <t xml:space="preserve">2.24763584136963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3254086971283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23208093643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18541765213013</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.27874517440796</t>
+    <t xml:space="preserve">2.32540893554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23208117485046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18541741371155</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.27874493598938</t>
   </si>
   <si>
     <t xml:space="preserve">2.26319026947021</t>
@@ -395,10 +395,10 @@
     <t xml:space="preserve">2.21652674674988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06875848770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1465311050415</t>
+    <t xml:space="preserve">2.06875824928284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.14653134346008</t>
   </si>
   <si>
     <t xml:space="preserve">2.10764455795288</t>
@@ -407,136 +407,136 @@
     <t xml:space="preserve">2.15430855751038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17763996124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22430396080017</t>
+    <t xml:space="preserve">2.17764019966125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22430372238159</t>
   </si>
   <si>
     <t xml:space="preserve">2.35651779174805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4887318611145</t>
+    <t xml:space="preserve">2.48873162269592</t>
   </si>
   <si>
     <t xml:space="preserve">2.52761816978455</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43429088592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44206786155701</t>
+    <t xml:space="preserve">2.43429112434387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44206809997559</t>
   </si>
   <si>
     <t xml:space="preserve">2.55872750282288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44984555244446</t>
+    <t xml:space="preserve">2.44984531402588</t>
   </si>
   <si>
     <t xml:space="preserve">2.37207245826721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33318591117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29429960250854</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37984991073608</t>
+    <t xml:space="preserve">2.33318614959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29429984092712</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37984943389893</t>
   </si>
   <si>
     <t xml:space="preserve">2.71427321434021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58205914497375</t>
+    <t xml:space="preserve">2.58205890655518</t>
   </si>
   <si>
     <t xml:space="preserve">2.62872314453125</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65983200073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57428169250488</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67538666725159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64427781105042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69094109535217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.768714427948</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90092778205872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96314597129822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92426013946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97092318534851</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01758718490601</t>
+    <t xml:space="preserve">2.659832239151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57428193092346</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67538690567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64427757263184</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69094133377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76871395111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90092802047729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9631462097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92425990104675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97092342376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01758742332458</t>
   </si>
   <si>
     <t xml:space="preserve">3.04869627952576</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03314185142517</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0642511844635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07980561256409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0604989528656</t>
+    <t xml:space="preserve">3.03314161300659</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06425094604492</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07980537414551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.06049919128418</t>
   </si>
   <si>
     <t xml:space="preserve">3.02811288833618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01191973686218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10907816886902</t>
+    <t xml:space="preserve">3.01191997528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1090784072876</t>
   </si>
   <si>
     <t xml:space="preserve">3.0928852558136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12527132034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07669186592102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99572658538818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.30339574813843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41674757003784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35197520256042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33578205108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36816835403442</t>
+    <t xml:space="preserve">3.1252715587616</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07669234275818</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99572682380676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.30339550971985</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41674733161926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35197496414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33578181266785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36816811561584</t>
   </si>
   <si>
     <t xml:space="preserve">3.23862314224243</t>
@@ -545,22 +545,22 @@
     <t xml:space="preserve">3.31958889961243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27100944519043</t>
+    <t xml:space="preserve">3.27100920677185</t>
   </si>
   <si>
     <t xml:space="preserve">3.28720235824585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22243022918701</t>
+    <t xml:space="preserve">3.22242999076843</t>
   </si>
   <si>
     <t xml:space="preserve">3.17385101318359</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20623731613159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14146494865417</t>
+    <t xml:space="preserve">3.20623707771301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1414647102356</t>
   </si>
   <si>
     <t xml:space="preserve">3.40055418014526</t>
@@ -572,16 +572,16 @@
     <t xml:space="preserve">3.38436126708984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25481653213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19004416465759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96334028244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97953367233276</t>
+    <t xml:space="preserve">3.25481629371643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19004392623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96334052085876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97953343391418</t>
   </si>
   <si>
     <t xml:space="preserve">2.80140924453735</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">2.88237476348877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86618161201477</t>
+    <t xml:space="preserve">2.86618185043335</t>
   </si>
   <si>
     <t xml:space="preserve">2.84998822212219</t>
@@ -602,28 +602,28 @@
     <t xml:space="preserve">2.75283002853394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72044372558594</t>
+    <t xml:space="preserve">2.72044348716736</t>
   </si>
   <si>
     <t xml:space="preserve">2.83379530906677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76902318000793</t>
+    <t xml:space="preserve">2.76902294158936</t>
   </si>
   <si>
     <t xml:space="preserve">2.73663687705994</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81760239601135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89856767654419</t>
+    <t xml:space="preserve">2.81760215759277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89856791496277</t>
   </si>
   <si>
     <t xml:space="preserve">2.91476082801819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63947772979736</t>
+    <t xml:space="preserve">2.63947796821594</t>
   </si>
   <si>
     <t xml:space="preserve">2.67186403274536</t>
@@ -638,10 +638,10 @@
     <t xml:space="preserve">2.70425057411194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.60709190368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59089875221252</t>
+    <t xml:space="preserve">2.60709166526794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59089851379395</t>
   </si>
   <si>
     <t xml:space="preserve">2.42896747589111</t>
@@ -659,13 +659,13 @@
     <t xml:space="preserve">2.29942274093628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35488152503967</t>
+    <t xml:space="preserve">2.35488176345825</t>
   </si>
   <si>
     <t xml:space="preserve">2.40607476234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28662419319153</t>
+    <t xml:space="preserve">2.28662443161011</t>
   </si>
   <si>
     <t xml:space="preserve">2.13304495811462</t>
@@ -677,7 +677,7 @@
     <t xml:space="preserve">2.06478762626648</t>
   </si>
   <si>
-    <t xml:space="preserve">2.03065896034241</t>
+    <t xml:space="preserve">2.03065872192383</t>
   </si>
   <si>
     <t xml:space="preserve">2.1671736240387</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">2.09891629219055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26956009864807</t>
+    <t xml:space="preserve">2.26955986022949</t>
   </si>
   <si>
     <t xml:space="preserve">2.21836686134338</t>
@@ -695,16 +695,16 @@
     <t xml:space="preserve">2.32075309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55965423583984</t>
+    <t xml:space="preserve">2.55965399742126</t>
   </si>
   <si>
     <t xml:space="preserve">2.54258990287781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45726799964905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5767183303833</t>
+    <t xml:space="preserve">2.45726823806763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57671856880188</t>
   </si>
   <si>
     <t xml:space="preserve">2.62791132926941</t>
@@ -716,10 +716,10 @@
     <t xml:space="preserve">2.64497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59378290176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69616913795471</t>
+    <t xml:space="preserve">2.59378266334534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69616889953613</t>
   </si>
   <si>
     <t xml:space="preserve">2.71323323249817</t>
@@ -740,19 +740,19 @@
     <t xml:space="preserve">2.33781719207764</t>
   </si>
   <si>
-    <t xml:space="preserve">2.30368876457214</t>
+    <t xml:space="preserve">2.30368852615356</t>
   </si>
   <si>
     <t xml:space="preserve">2.25249576568604</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23543095588684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37194633483887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38901042938232</t>
+    <t xml:space="preserve">2.23543119430542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37194609642029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3890106678009</t>
   </si>
   <si>
     <t xml:space="preserve">2.20130252838135</t>
@@ -761,7 +761,7 @@
     <t xml:space="preserve">2.18423795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01359415054321</t>
+    <t xml:space="preserve">2.01359438896179</t>
   </si>
   <si>
     <t xml:space="preserve">2.04772329330444</t>
@@ -770,7 +770,7 @@
     <t xml:space="preserve">2.11598062515259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91120839118958</t>
+    <t xml:space="preserve">1.91120851039886</t>
   </si>
   <si>
     <t xml:space="preserve">1.87707984447479</t>
@@ -785,7 +785,7 @@
     <t xml:space="preserve">1.86001515388489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94533693790436</t>
+    <t xml:space="preserve">1.94533717632294</t>
   </si>
   <si>
     <t xml:space="preserve">1.96240127086639</t>
@@ -809,7 +809,7 @@
     <t xml:space="preserve">2.73029756546021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67910432815552</t>
+    <t xml:space="preserve">2.6791045665741</t>
   </si>
   <si>
     <t xml:space="preserve">2.74736189842224</t>
@@ -830,55 +830,55 @@
     <t xml:space="preserve">2.9350700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96919870376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02039170265198</t>
+    <t xml:space="preserve">2.96919846534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02039194107056</t>
   </si>
   <si>
     <t xml:space="preserve">3.00332713127136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03745627403259</t>
+    <t xml:space="preserve">3.03745603561401</t>
   </si>
   <si>
     <t xml:space="preserve">2.98626303672791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05452036857605</t>
+    <t xml:space="preserve">3.05452060699463</t>
   </si>
   <si>
     <t xml:space="preserve">3.07158470153809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13984251022339</t>
+    <t xml:space="preserve">3.13984227180481</t>
   </si>
   <si>
     <t xml:space="preserve">3.11424589157104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13131022453308</t>
+    <t xml:space="preserve">3.1313099861145</t>
   </si>
   <si>
     <t xml:space="preserve">3.06305265426636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16543889045715</t>
+    <t xml:space="preserve">3.16543865203857</t>
   </si>
   <si>
     <t xml:space="preserve">3.19956755638123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15690660476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23369646072388</t>
+    <t xml:space="preserve">3.15690684318542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2336962223053</t>
   </si>
   <si>
     <t xml:space="preserve">3.27635717391968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24222826957703</t>
+    <t xml:space="preserve">3.24222850799561</t>
   </si>
   <si>
     <t xml:space="preserve">3.26782488822937</t>
@@ -887,7 +887,7 @@
     <t xml:space="preserve">3.31048607826233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34461450576782</t>
+    <t xml:space="preserve">3.3446147441864</t>
   </si>
   <si>
     <t xml:space="preserve">3.32755041122437</t>
@@ -899,7 +899,7 @@
     <t xml:space="preserve">3.18250346183777</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29342126846313</t>
+    <t xml:space="preserve">3.29342150688171</t>
   </si>
   <si>
     <t xml:space="preserve">3.33710074424744</t>
@@ -908,22 +908,22 @@
     <t xml:space="preserve">3.32836484909058</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29342150688171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24974250793457</t>
+    <t xml:space="preserve">3.29342174530029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24974226951599</t>
   </si>
   <si>
     <t xml:space="preserve">3.20606303215027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15364742279053</t>
+    <t xml:space="preserve">3.15364766120911</t>
   </si>
   <si>
     <t xml:space="preserve">3.21479892730713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17111945152283</t>
+    <t xml:space="preserve">3.17111968994141</t>
   </si>
   <si>
     <t xml:space="preserve">3.26721405982971</t>
@@ -950,13 +950,13 @@
     <t xml:space="preserve">3.51181817054749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54676175117493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63412022590637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62538456916809</t>
+    <t xml:space="preserve">3.54676151275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63412046432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62538480758667</t>
   </si>
   <si>
     <t xml:space="preserve">3.74768662452698</t>
@@ -965,34 +965,34 @@
     <t xml:space="preserve">3.69527125358582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66906332969666</t>
+    <t xml:space="preserve">3.66906356811523</t>
   </si>
   <si>
     <t xml:space="preserve">3.60791301727295</t>
   </si>
   <si>
-    <t xml:space="preserve">3.55549788475037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66032767295837</t>
+    <t xml:space="preserve">3.55549764633179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66032791137695</t>
   </si>
   <si>
     <t xml:space="preserve">3.65159177780151</t>
   </si>
   <si>
-    <t xml:space="preserve">3.68653512001038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7040069103241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75642275810242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57296943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53802609443665</t>
+    <t xml:space="preserve">3.68653535842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70400714874268</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75642251968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57296967506409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53802585601807</t>
   </si>
   <si>
     <t xml:space="preserve">3.3458366394043</t>
@@ -1004,7 +1004,7 @@
     <t xml:space="preserve">3.42445969581604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45066714286804</t>
+    <t xml:space="preserve">3.45066738128662</t>
   </si>
   <si>
     <t xml:space="preserve">3.44193148612976</t>
@@ -1019,10 +1019,10 @@
     <t xml:space="preserve">3.35457253456116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4594030380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52928996086121</t>
+    <t xml:space="preserve">3.45940327644348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52928972244263</t>
   </si>
   <si>
     <t xml:space="preserve">3.46813893318176</t>
@@ -1031,10 +1031,10 @@
     <t xml:space="preserve">3.47687458992004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79136610031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72147917747498</t>
+    <t xml:space="preserve">3.79136633872986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7214789390564</t>
   </si>
   <si>
     <t xml:space="preserve">3.8787248134613</t>
@@ -1049,13 +1049,13 @@
     <t xml:space="preserve">4.35046148300171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1844801902771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.20195198059082</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.25436639785767</t>
+    <t xml:space="preserve">4.18447971343994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.20195150375366</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.25436687469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.14080047607422</t>
@@ -1067,10 +1067,10 @@
     <t xml:space="preserve">3.98355484008789</t>
   </si>
   <si>
-    <t xml:space="preserve">3.94861149787903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93113970756531</t>
+    <t xml:space="preserve">3.94861197471619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93114018440247</t>
   </si>
   <si>
     <t xml:space="preserve">4.08838510513306</t>
@@ -1088,31 +1088,31 @@
     <t xml:space="preserve">4.00976276397705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93987560272217</t>
+    <t xml:space="preserve">3.93987607955933</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21068811416626</t>
+    <t xml:space="preserve">4.2106876373291</t>
   </si>
   <si>
     <t xml:space="preserve">4.29804611206055</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28930997848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21942377090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19321632385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14953660964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16700839996338</t>
+    <t xml:space="preserve">4.28931045532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21942329406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19321584701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1495361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16700792312622</t>
   </si>
   <si>
     <t xml:space="preserve">4.11459302902222</t>
@@ -1121,19 +1121,19 @@
     <t xml:space="preserve">4.06217813491821</t>
   </si>
   <si>
-    <t xml:space="preserve">3.78263020515442</t>
+    <t xml:space="preserve">3.78262996673584</t>
   </si>
   <si>
     <t xml:space="preserve">3.80010175704956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82630944252014</t>
+    <t xml:space="preserve">3.82630968093872</t>
   </si>
   <si>
     <t xml:space="preserve">3.83504509925842</t>
   </si>
   <si>
-    <t xml:space="preserve">3.84378123283386</t>
+    <t xml:space="preserve">3.84378099441528</t>
   </si>
   <si>
     <t xml:space="preserve">3.77389454841614</t>
@@ -1142,7 +1142,7 @@
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734739303589</t>
+    <t xml:space="preserve">3.95734786987305</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
@@ -1151,7 +1151,7 @@
     <t xml:space="preserve">3.86125302314758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7651584148407</t>
+    <t xml:space="preserve">3.76515865325928</t>
   </si>
   <si>
     <t xml:space="preserve">3.8175733089447</t>
@@ -1160,13 +1160,13 @@
     <t xml:space="preserve">3.64285612106323</t>
   </si>
   <si>
-    <t xml:space="preserve">3.67779946327209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7389509677887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85251712799072</t>
+    <t xml:space="preserve">3.67779970169067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73895072937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85251665115356</t>
   </si>
   <si>
     <t xml:space="preserve">3.71274304389954</t>
@@ -1196,7 +1196,7 @@
     <t xml:space="preserve">2.91777920722961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90904355049133</t>
+    <t xml:space="preserve">2.90904331207275</t>
   </si>
   <si>
     <t xml:space="preserve">3.37204432487488</t>
@@ -1205,7 +1205,7 @@
     <t xml:space="preserve">3.38078022003174</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41572403907776</t>
+    <t xml:space="preserve">3.41572380065918</t>
   </si>
   <si>
     <t xml:space="preserve">3.31962895393372</t>
@@ -1214,7 +1214,7 @@
     <t xml:space="preserve">3.27594995498657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28468561172485</t>
+    <t xml:space="preserve">3.28468585014343</t>
   </si>
   <si>
     <t xml:space="preserve">3.50245499610901</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">3.32098078727722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26653814315796</t>
+    <t xml:space="preserve">3.26653838157654</t>
   </si>
   <si>
     <t xml:space="preserve">3.39357042312622</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">3.23024344444275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19394874572754</t>
+    <t xml:space="preserve">3.19394850730896</t>
   </si>
   <si>
     <t xml:space="preserve">3.25746440887451</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">3.2211697101593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10321140289307</t>
+    <t xml:space="preserve">3.10321164131165</t>
   </si>
   <si>
     <t xml:space="preserve">2.99432682991028</t>
@@ -1286,13 +1286,13 @@
     <t xml:space="preserve">2.95803189277649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85822105407715</t>
+    <t xml:space="preserve">2.85822129249573</t>
   </si>
   <si>
     <t xml:space="preserve">2.89451599121094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8672947883606</t>
+    <t xml:space="preserve">2.86729502677917</t>
   </si>
   <si>
     <t xml:space="preserve">2.81285238265991</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">2.75841021537781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70396780967712</t>
+    <t xml:space="preserve">2.7039680480957</t>
   </si>
   <si>
     <t xml:space="preserve">2.72211527824402</t>
@@ -1313,16 +1313,16 @@
     <t xml:space="preserve">2.64952564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7947051525116</t>
+    <t xml:space="preserve">2.79470491409302</t>
   </si>
   <si>
     <t xml:space="preserve">2.92173719406128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05784273147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02154803276062</t>
+    <t xml:space="preserve">3.05784296989441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02154779434204</t>
   </si>
   <si>
     <t xml:space="preserve">3.13950634002686</t>
@@ -1352,46 +1352,46 @@
     <t xml:space="preserve">3.08506417274475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01247429847717</t>
+    <t xml:space="preserve">3.01247406005859</t>
   </si>
   <si>
     <t xml:space="preserve">2.88544225692749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7765576839447</t>
+    <t xml:space="preserve">2.77655744552612</t>
   </si>
   <si>
     <t xml:space="preserve">2.71304154396057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6313784122467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68582034111023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66767287254333</t>
+    <t xml:space="preserve">2.63137817382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68582057952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66767311096191</t>
   </si>
   <si>
     <t xml:space="preserve">2.55878829956055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52249336242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67674660682678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64045214653015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87636852264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83099985122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60415697097778</t>
+    <t xml:space="preserve">2.52249360084534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67674684524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64045190811157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87636876106262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83099961280823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6041567325592</t>
   </si>
   <si>
     <t xml:space="preserve">2.73118901252747</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">2.91266345977783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12135887145996</t>
+    <t xml:space="preserve">3.12135910987854</t>
   </si>
   <si>
     <t xml:space="preserve">3.0759904384613</t>
@@ -1427,46 +1427,46 @@
     <t xml:space="preserve">3.0941379070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38449692726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41171765327454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37542319297791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42079138755798</t>
+    <t xml:space="preserve">3.38449668884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41171789169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37542295455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42079162597656</t>
   </si>
   <si>
     <t xml:space="preserve">3.43893885612488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36634945869446</t>
+    <t xml:space="preserve">3.36634922027588</t>
   </si>
   <si>
     <t xml:space="preserve">3.35727572441101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20302248001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27561187744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29375958442688</t>
+    <t xml:space="preserve">3.20302224159241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27561211585999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29375982284546</t>
   </si>
   <si>
     <t xml:space="preserve">3.1667275428772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11228513717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78563141822815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84007382392883</t>
+    <t xml:space="preserve">3.11228537559509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78563117980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84007358551025</t>
   </si>
   <si>
     <t xml:space="preserve">2.82192611694336</t>
@@ -57547,7 +57547,7 @@
     </row>
     <row r="2132">
       <c r="A2132" s="1" t="n">
-        <v>46071.6664467593</v>
+        <v>46071.3333333333</v>
       </c>
       <c r="B2132" t="n">
         <v>2678</v>
@@ -57568,6 +57568,32 @@
         <v>584</v>
       </c>
       <c r="H2132" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2133">
+      <c r="A2133" s="1" t="n">
+        <v>46072.6701041667</v>
+      </c>
+      <c r="B2133" t="n">
+        <v>6864</v>
+      </c>
+      <c r="C2133" t="n">
+        <v>3.74000000953674</v>
+      </c>
+      <c r="D2133" t="n">
+        <v>3.66000008583069</v>
+      </c>
+      <c r="E2133" t="n">
+        <v>3.72000002861023</v>
+      </c>
+      <c r="F2133" t="n">
+        <v>3.74000000953674</v>
+      </c>
+      <c r="G2133" t="s">
+        <v>591</v>
+      </c>
+      <c r="H2133" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519899368286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88901519775391</t>
+    <t xml:space="preserve">2.96519947052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88901543617249</t>
   </si>
   <si>
     <t xml:space="preserve">2.98013734817505</t>
@@ -59,31 +59,31 @@
     <t xml:space="preserve">2.94577980041504</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95773029327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9622118473053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9353232383728</t>
+    <t xml:space="preserve">2.9577305316925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96221160888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93532347679138</t>
   </si>
   <si>
     <t xml:space="preserve">2.91291642189026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97864365577698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98611211776733</t>
+    <t xml:space="preserve">2.97864389419556</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98611235618591</t>
   </si>
   <si>
     <t xml:space="preserve">3.03540802001953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.056321144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05930876731873</t>
+    <t xml:space="preserve">3.05632138252258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0593090057373</t>
   </si>
   <si>
     <t xml:space="preserve">3.05034613609314</t>
@@ -98,28 +98,28 @@
     <t xml:space="preserve">3.01598858833313</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01001310348511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02495145797729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0174822807312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03092670440674</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99955654144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04437112808228</t>
+    <t xml:space="preserve">3.01001358032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02495121955872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01748251914978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03092694282532</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99955677986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0443708896637</t>
   </si>
   <si>
     <t xml:space="preserve">2.959223985672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00254440307617</t>
+    <t xml:space="preserve">3.00254464149475</t>
   </si>
   <si>
     <t xml:space="preserve">2.92785429954529</t>
@@ -128,19 +128,19 @@
     <t xml:space="preserve">2.90843486785889</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89648413658142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91889142990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91590356826782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92038536071777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90544700622559</t>
+    <t xml:space="preserve">2.896484375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91889119148254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9159038066864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92038512229919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90544724464417</t>
   </si>
   <si>
     <t xml:space="preserve">2.90992856025696</t>
@@ -149,61 +149,61 @@
     <t xml:space="preserve">2.9233729839325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8382260799408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8606333732605</t>
+    <t xml:space="preserve">2.83822584152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86063313484192</t>
   </si>
   <si>
     <t xml:space="preserve">2.82627558708191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77996778488159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84569501876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86810183525085</t>
+    <t xml:space="preserve">2.77996730804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84569525718689</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86810207366943</t>
   </si>
   <si>
     <t xml:space="preserve">2.88304018974304</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79639935493469</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87557125091553</t>
+    <t xml:space="preserve">2.79639983177185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87557077407837</t>
   </si>
   <si>
     <t xml:space="preserve">2.89797830581665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80088090896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74262285232544</t>
+    <t xml:space="preserve">2.80088067054749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74262237548828</t>
   </si>
   <si>
     <t xml:space="preserve">2.82179427146912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7500913143158</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76353597640991</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77847361564636</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78594303131104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79341173171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69631481170654</t>
+    <t xml:space="preserve">2.75009179115295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76353573799133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77847409248352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78594279289246</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79341197013855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69631457328796</t>
   </si>
   <si>
     <t xml:space="preserve">2.6515007019043</t>
@@ -212,25 +212,25 @@
     <t xml:space="preserve">2.62162446975708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.53946542739868</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56934118270874</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61415576934814</t>
+    <t xml:space="preserve">2.5394651889801</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.56934142112732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61415553092957</t>
   </si>
   <si>
     <t xml:space="preserve">2.65896964073181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68884563446045</t>
+    <t xml:space="preserve">2.68884587287903</t>
   </si>
   <si>
     <t xml:space="preserve">2.70378375053406</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77100467681885</t>
+    <t xml:space="preserve">2.77100491523743</t>
   </si>
   <si>
     <t xml:space="preserve">2.81581902503967</t>
@@ -239,58 +239,58 @@
     <t xml:space="preserve">2.7336597442627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66643881797791</t>
+    <t xml:space="preserve">2.66643857955933</t>
   </si>
   <si>
     <t xml:space="preserve">2.68137669563293</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74112868309021</t>
+    <t xml:space="preserve">2.74112892150879</t>
   </si>
   <si>
     <t xml:space="preserve">2.72619080543518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8307569026947</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.893150806427</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69871854782104</t>
+    <t xml:space="preserve">2.83075714111328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89315056800842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69871878623962</t>
   </si>
   <si>
     <t xml:space="preserve">2.83870983123779</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93203735351562</t>
+    <t xml:space="preserve">2.93203711509705</t>
   </si>
   <si>
     <t xml:space="preserve">2.87759613990784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83093237876892</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81537771224976</t>
+    <t xml:space="preserve">2.8309326171875</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81537747383118</t>
   </si>
   <si>
     <t xml:space="preserve">2.84648680686951</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79982280731201</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73760461807251</t>
+    <t xml:space="preserve">2.79982328414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73760485649109</t>
   </si>
   <si>
     <t xml:space="preserve">2.76093673706055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80760049819946</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00980997085571</t>
+    <t xml:space="preserve">2.80760025978088</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00980973243713</t>
   </si>
   <si>
     <t xml:space="preserve">2.9553689956665</t>
@@ -302,16 +302,16 @@
     <t xml:space="preserve">2.88537335395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82315516471863</t>
+    <t xml:space="preserve">2.82315540313721</t>
   </si>
   <si>
     <t xml:space="preserve">2.86204171180725</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00203251838684</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91648268699646</t>
+    <t xml:space="preserve">3.00203275680542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91648244857788</t>
   </si>
   <si>
     <t xml:space="preserve">2.85426449775696</t>
@@ -320,13 +320,13 @@
     <t xml:space="preserve">2.7298276424408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68316388130188</t>
+    <t xml:space="preserve">2.68316411972046</t>
   </si>
   <si>
     <t xml:space="preserve">2.72205018997192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75315928459167</t>
+    <t xml:space="preserve">2.75315952301025</t>
   </si>
   <si>
     <t xml:space="preserve">2.70649576187134</t>
@@ -338,16 +338,16 @@
     <t xml:space="preserve">2.99425530433655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97870111465454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86981916427612</t>
+    <t xml:space="preserve">2.97870087623596</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86981868743896</t>
   </si>
   <si>
     <t xml:space="preserve">2.94759154319763</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98647785186768</t>
+    <t xml:space="preserve">2.98647809028625</t>
   </si>
   <si>
     <t xml:space="preserve">2.63650012016296</t>
@@ -356,58 +356,58 @@
     <t xml:space="preserve">2.550950050354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51984095573425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41095876693726</t>
+    <t xml:space="preserve">2.51984119415283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41095900535583</t>
   </si>
   <si>
     <t xml:space="preserve">2.34096336364746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34874057769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36429524421692</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.25541353225708</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.24763607978821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32540845870972</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23208117485046</t>
+    <t xml:space="preserve">2.34874081611633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36429500579834</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2554132938385</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.24763584136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3254086971283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23208093643188</t>
   </si>
   <si>
     <t xml:space="preserve">2.18541765213013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27874493598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26319050788879</t>
+    <t xml:space="preserve">2.27874517440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26319026947021</t>
   </si>
   <si>
     <t xml:space="preserve">2.21652674674988</t>
   </si>
   <si>
-    <t xml:space="preserve">2.06875824928284</t>
+    <t xml:space="preserve">2.06875848770142</t>
   </si>
   <si>
     <t xml:space="preserve">2.14653134346008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10764503479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1543083190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17764019966125</t>
+    <t xml:space="preserve">2.10764455795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15430855751038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17763996124268</t>
   </si>
   <si>
     <t xml:space="preserve">2.22430396080017</t>
@@ -416,13 +416,13 @@
     <t xml:space="preserve">2.35651779174805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4887318611145</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52761816978455</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43429088592529</t>
+    <t xml:space="preserve">2.48873162269592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52761840820312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43429112434387</t>
   </si>
   <si>
     <t xml:space="preserve">2.44206786155701</t>
@@ -431,16 +431,16 @@
     <t xml:space="preserve">2.55872750282288</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44984531402588</t>
+    <t xml:space="preserve">2.44984555244446</t>
   </si>
   <si>
     <t xml:space="preserve">2.37207245826721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33318614959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29429960250854</t>
+    <t xml:space="preserve">2.33318591117859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29429984092712</t>
   </si>
   <si>
     <t xml:space="preserve">2.3798496723175</t>
@@ -455,16 +455,16 @@
     <t xml:space="preserve">2.62872290611267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65983200073242</t>
+    <t xml:space="preserve">2.659832239151</t>
   </si>
   <si>
     <t xml:space="preserve">2.57428193092346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67538666725159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64427757263184</t>
+    <t xml:space="preserve">2.67538690567017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64427733421326</t>
   </si>
   <si>
     <t xml:space="preserve">2.69094109535217</t>
@@ -473,19 +473,19 @@
     <t xml:space="preserve">2.76871395111084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90092802047729</t>
+    <t xml:space="preserve">2.90092778205872</t>
   </si>
   <si>
     <t xml:space="preserve">2.9631462097168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92425990104675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97092342376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01758742332458</t>
+    <t xml:space="preserve">2.92426013946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97092318534851</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01758718490601</t>
   </si>
   <si>
     <t xml:space="preserve">3.04869627952576</t>
@@ -494,7 +494,7 @@
     <t xml:space="preserve">3.03314185142517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06425094604492</t>
+    <t xml:space="preserve">3.0642511844635</t>
   </si>
   <si>
     <t xml:space="preserve">3.07980561256409</t>
@@ -503,67 +503,67 @@
     <t xml:space="preserve">3.0604989528656</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0281126499176</t>
+    <t xml:space="preserve">3.02811288833618</t>
   </si>
   <si>
     <t xml:space="preserve">3.01191973686218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1090784072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.09288501739502</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1252715587616</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07669234275818</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99572682380676</t>
+    <t xml:space="preserve">3.10907816886902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0928852558136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.12527132034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07669186592102</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99572658538818</t>
   </si>
   <si>
     <t xml:space="preserve">3.30339574813843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41674733161926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35197496414185</t>
+    <t xml:space="preserve">3.41674757003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35197520256042</t>
   </si>
   <si>
     <t xml:space="preserve">3.33578205108643</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36816811561584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23862338066101</t>
+    <t xml:space="preserve">3.36816835403442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23862314224243</t>
   </si>
   <si>
     <t xml:space="preserve">3.31958889961243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27100968360901</t>
+    <t xml:space="preserve">3.27100944519043</t>
   </si>
   <si>
     <t xml:space="preserve">3.28720235824585</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22242999076843</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17385077476501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20623707771301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1414647102356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40055465698242</t>
+    <t xml:space="preserve">3.22243022918701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17385101318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20623731613159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.14146494865417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40055418014526</t>
   </si>
   <si>
     <t xml:space="preserve">3.49771332740784</t>
@@ -581,7 +581,7 @@
     <t xml:space="preserve">2.96334028244019</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97953343391418</t>
+    <t xml:space="preserve">2.97953367233276</t>
   </si>
   <si>
     <t xml:space="preserve">2.80140924453735</t>
@@ -599,49 +599,49 @@
     <t xml:space="preserve">2.78521609306335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75282979011536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72044348716736</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83379554748535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76902294158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73663663864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81760215759277</t>
+    <t xml:space="preserve">2.75283002853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72044372558594</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83379530906677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76902318000793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73663687705994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81760239601135</t>
   </si>
   <si>
     <t xml:space="preserve">2.89856767654419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91476106643677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63947796821594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67186427116394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62328505516052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68805742263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70425033569336</t>
+    <t xml:space="preserve">2.91476082801819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63947772979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67186403274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62328481674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68805718421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70425057411194</t>
   </si>
   <si>
     <t xml:space="preserve">2.60709190368652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59089851379395</t>
+    <t xml:space="preserve">2.59089875221252</t>
   </si>
   <si>
     <t xml:space="preserve">2.42896747589111</t>
@@ -653,22 +653,22 @@
     <t xml:space="preserve">2.46135354042053</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31561541557312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2994225025177</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35488176345825</t>
+    <t xml:space="preserve">2.3156156539917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29942274093628</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35488152503967</t>
   </si>
   <si>
     <t xml:space="preserve">2.40607476234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28662443161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1330451965332</t>
+    <t xml:space="preserve">2.28662419319153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13304495811462</t>
   </si>
   <si>
     <t xml:space="preserve">2.08185195922852</t>
@@ -680,34 +680,34 @@
     <t xml:space="preserve">2.03065896034241</t>
   </si>
   <si>
-    <t xml:space="preserve">2.16717338562012</t>
+    <t xml:space="preserve">2.1671736240387</t>
   </si>
   <si>
     <t xml:space="preserve">2.09891629219055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26955986022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2183666229248</t>
+    <t xml:space="preserve">2.26956009864807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21836686134338</t>
   </si>
   <si>
     <t xml:space="preserve">2.32075309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55965399742126</t>
+    <t xml:space="preserve">2.55965423583984</t>
   </si>
   <si>
     <t xml:space="preserve">2.54258990287781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45726776123047</t>
+    <t xml:space="preserve">2.45726799964905</t>
   </si>
   <si>
     <t xml:space="preserve">2.5767183303833</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62791156768799</t>
+    <t xml:space="preserve">2.62791132926941</t>
   </si>
   <si>
     <t xml:space="preserve">2.61084699630737</t>
@@ -716,7 +716,7 @@
     <t xml:space="preserve">2.64497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59378266334534</t>
+    <t xml:space="preserve">2.59378290176392</t>
   </si>
   <si>
     <t xml:space="preserve">2.69616913795471</t>
@@ -725,22 +725,22 @@
     <t xml:space="preserve">2.71323323249817</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44020318984985</t>
+    <t xml:space="preserve">2.44020342826843</t>
   </si>
   <si>
     <t xml:space="preserve">2.42313933372498</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47433257102966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15010952949524</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33781743049622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30368852615356</t>
+    <t xml:space="preserve">2.47433233261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15010929107666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33781719207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30368876457214</t>
   </si>
   <si>
     <t xml:space="preserve">2.25249576568604</t>
@@ -749,19 +749,19 @@
     <t xml:space="preserve">2.23543095588684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37194609642029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.38901019096375</t>
+    <t xml:space="preserve">2.37194633483887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.38901042938232</t>
   </si>
   <si>
     <t xml:space="preserve">2.20130252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18423819541931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01359438896179</t>
+    <t xml:space="preserve">2.18423795700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01359415054321</t>
   </si>
   <si>
     <t xml:space="preserve">2.04772329330444</t>
@@ -773,7 +773,7 @@
     <t xml:space="preserve">1.91120839118958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87707960605621</t>
+    <t xml:space="preserve">1.87707984447479</t>
   </si>
   <si>
     <t xml:space="preserve">1.84295094013214</t>
@@ -782,40 +782,40 @@
     <t xml:space="preserve">1.97946584224701</t>
   </si>
   <si>
-    <t xml:space="preserve">1.86001539230347</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94533705711365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96240139007568</t>
+    <t xml:space="preserve">1.86001515388489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94533693790436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96240127086639</t>
   </si>
   <si>
     <t xml:space="preserve">1.99652993679047</t>
   </si>
   <si>
-    <t xml:space="preserve">2.81561946868896</t>
+    <t xml:space="preserve">2.81561923027039</t>
   </si>
   <si>
     <t xml:space="preserve">2.90094137191772</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88387680053711</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76442670822144</t>
+    <t xml:space="preserve">2.88387703895569</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76442623138428</t>
   </si>
   <si>
     <t xml:space="preserve">2.73029756546021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6791045665741</t>
+    <t xml:space="preserve">2.67910432815552</t>
   </si>
   <si>
     <t xml:space="preserve">2.74736189842224</t>
   </si>
   <si>
-    <t xml:space="preserve">2.832683801651</t>
+    <t xml:space="preserve">2.83268356323242</t>
   </si>
   <si>
     <t xml:space="preserve">2.86681246757507</t>
@@ -836,10 +836,10 @@
     <t xml:space="preserve">3.02039170265198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00332736968994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03745603561401</t>
+    <t xml:space="preserve">3.00332713127136</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03745627403259</t>
   </si>
   <si>
     <t xml:space="preserve">2.98626303672791</t>
@@ -860,7 +860,7 @@
     <t xml:space="preserve">3.13131022453308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06305241584778</t>
+    <t xml:space="preserve">3.06305265426636</t>
   </si>
   <si>
     <t xml:space="preserve">3.16543889045715</t>
@@ -869,19 +869,19 @@
     <t xml:space="preserve">3.19956755638123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15690684318542</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23369598388672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.2763569355011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24222850799561</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26782512664795</t>
+    <t xml:space="preserve">3.15690660476685</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23369646072388</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27635717391968</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.24222826957703</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26782488822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.31048607826233</t>
@@ -890,43 +890,43 @@
     <t xml:space="preserve">3.34461450576782</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32755017280579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28488922119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18250322341919</t>
+    <t xml:space="preserve">3.32755041122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28488945960999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18250346183777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29342126846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33710074424744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32836484909058</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342150688171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33710074424744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32836508750916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29342174530029</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.24974226951599</t>
+    <t xml:space="preserve">3.24974250793457</t>
   </si>
   <si>
     <t xml:space="preserve">3.20606303215027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15364766120911</t>
+    <t xml:space="preserve">3.15364742279053</t>
   </si>
   <si>
     <t xml:space="preserve">3.21479892730713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17111968994141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.26721382141113</t>
+    <t xml:space="preserve">3.17111945152283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.26721405982971</t>
   </si>
   <si>
     <t xml:space="preserve">3.36330842971802</t>
@@ -938,70 +938,70 @@
     <t xml:space="preserve">3.58170509338379</t>
   </si>
   <si>
-    <t xml:space="preserve">3.56423330307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59044098854065</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.50308275222778</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.51181840896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54676151275635</t>
+    <t xml:space="preserve">3.56423354148865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59044122695923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.5030825138092</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.51181817054749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54676175117493</t>
   </si>
   <si>
     <t xml:space="preserve">3.63412022590637</t>
   </si>
   <si>
-    <t xml:space="preserve">3.62538480758667</t>
+    <t xml:space="preserve">3.62538456916809</t>
   </si>
   <si>
     <t xml:space="preserve">3.74768662452698</t>
   </si>
   <si>
-    <t xml:space="preserve">3.69527149200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66906380653381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60791277885437</t>
+    <t xml:space="preserve">3.69527125358582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66906332969666</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60791301727295</t>
   </si>
   <si>
     <t xml:space="preserve">3.55549788475037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66032791137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65159201622009</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68653535842896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.70400714874268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.75642251968384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57296967506409</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53802585601807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.34583687782288</t>
+    <t xml:space="preserve">3.66032767295837</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65159177780151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68653512001038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7040069103241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.75642275810242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57296943664551</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53802609443665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.3458366394043</t>
   </si>
   <si>
     <t xml:space="preserve">3.38951635360718</t>
   </si>
   <si>
-    <t xml:space="preserve">3.42445945739746</t>
+    <t xml:space="preserve">3.42445969581604</t>
   </si>
   <si>
     <t xml:space="preserve">3.45066714286804</t>
@@ -1010,16 +1010,16 @@
     <t xml:space="preserve">3.44193148612976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48561072349548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40698790550232</t>
+    <t xml:space="preserve">3.4856104850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4069881439209</t>
   </si>
   <si>
     <t xml:space="preserve">3.35457253456116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45940327644348</t>
+    <t xml:space="preserve">3.4594030380249</t>
   </si>
   <si>
     <t xml:space="preserve">3.52928996086121</t>
@@ -1034,10 +1034,10 @@
     <t xml:space="preserve">3.79136610031128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7214789390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87872457504272</t>
+    <t xml:space="preserve">3.72147917747498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8787248134613</t>
   </si>
   <si>
     <t xml:space="preserve">4.17574453353882</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">4.1844801902771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20195150375366</t>
+    <t xml:space="preserve">4.20195198059082</t>
   </si>
   <si>
     <t xml:space="preserve">4.25436639785767</t>
@@ -1061,13 +1061,13 @@
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493178367615</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98355507850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94861173629761</t>
+    <t xml:space="preserve">3.90493202209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98355484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94861149787903</t>
   </si>
   <si>
     <t xml:space="preserve">3.93113970756531</t>
@@ -1076,7 +1076,7 @@
     <t xml:space="preserve">4.08838510513306</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07091379165649</t>
+    <t xml:space="preserve">4.07091331481934</t>
   </si>
   <si>
     <t xml:space="preserve">4.1233286857605</t>
@@ -1085,16 +1085,16 @@
     <t xml:space="preserve">4.00102663040161</t>
   </si>
   <si>
-    <t xml:space="preserve">4.00976228713989</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93987607955933</t>
+    <t xml:space="preserve">4.00976276397705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93987560272217</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21068716049194</t>
+    <t xml:space="preserve">4.21068811416626</t>
   </si>
   <si>
     <t xml:space="preserve">4.29804611206055</t>
@@ -1106,10 +1106,10 @@
     <t xml:space="preserve">4.21942377090454</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19321584701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1495361328125</t>
+    <t xml:space="preserve">4.19321632385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14953660964966</t>
   </si>
   <si>
     <t xml:space="preserve">4.16700839996338</t>
@@ -1118,37 +1118,37 @@
     <t xml:space="preserve">4.11459302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06217765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78262996673584</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.80010151863098</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.82630968093872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83504486083984</t>
+    <t xml:space="preserve">4.06217813491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78263020515442</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.80010175704956</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.82630944252014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83504509925842</t>
   </si>
   <si>
     <t xml:space="preserve">3.84378123283386</t>
   </si>
   <si>
-    <t xml:space="preserve">3.77389430999756</t>
+    <t xml:space="preserve">3.77389454841614</t>
   </si>
   <si>
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734763145447</t>
+    <t xml:space="preserve">3.95734739303589</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.861252784729</t>
+    <t xml:space="preserve">3.86125302314758</t>
   </si>
   <si>
     <t xml:space="preserve">3.7651584148407</t>
@@ -1157,10 +1157,10 @@
     <t xml:space="preserve">3.8175733089447</t>
   </si>
   <si>
-    <t xml:space="preserve">3.64285635948181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67779970169067</t>
+    <t xml:space="preserve">3.64285612106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67779946327209</t>
   </si>
   <si>
     <t xml:space="preserve">3.7389509677887</t>
@@ -1169,13 +1169,13 @@
     <t xml:space="preserve">3.85251712799072</t>
   </si>
   <si>
-    <t xml:space="preserve">3.71274328231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92240357398987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61664843559265</t>
+    <t xml:space="preserve">3.71274304389954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92240381240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61664867401123</t>
   </si>
   <si>
     <t xml:space="preserve">3.39825224876404</t>
@@ -1190,31 +1190,31 @@
     <t xml:space="preserve">2.97019457817078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95272278785706</t>
+    <t xml:space="preserve">2.95272302627563</t>
   </si>
   <si>
     <t xml:space="preserve">2.91777920722961</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90904331207275</t>
+    <t xml:space="preserve">2.90904355049133</t>
   </si>
   <si>
     <t xml:space="preserve">3.37204432487488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38077998161316</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41572380065918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31962919235229</t>
+    <t xml:space="preserve">3.38078022003174</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41572403907776</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31962895393372</t>
   </si>
   <si>
     <t xml:space="preserve">3.27594995498657</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28468585014343</t>
+    <t xml:space="preserve">3.28468561172485</t>
   </si>
   <si>
     <t xml:space="preserve">3.50245499610901</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">3.32098078727722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26653838157654</t>
+    <t xml:space="preserve">3.26653814315796</t>
   </si>
   <si>
     <t xml:space="preserve">3.39357042312622</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">3.23024344444275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19394850730896</t>
+    <t xml:space="preserve">3.19394874572754</t>
   </si>
   <si>
     <t xml:space="preserve">3.25746440887451</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">3.2211697101593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10321164131165</t>
+    <t xml:space="preserve">3.10321140289307</t>
   </si>
   <si>
     <t xml:space="preserve">2.99432682991028</t>
@@ -1286,13 +1286,13 @@
     <t xml:space="preserve">2.95803189277649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85822129249573</t>
+    <t xml:space="preserve">2.85822105407715</t>
   </si>
   <si>
     <t xml:space="preserve">2.89451599121094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86729502677917</t>
+    <t xml:space="preserve">2.8672947883606</t>
   </si>
   <si>
     <t xml:space="preserve">2.81285238265991</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">2.75841021537781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7039680480957</t>
+    <t xml:space="preserve">2.70396780967712</t>
   </si>
   <si>
     <t xml:space="preserve">2.72211527824402</t>
@@ -1313,16 +1313,16 @@
     <t xml:space="preserve">2.64952564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79470491409302</t>
+    <t xml:space="preserve">2.7947051525116</t>
   </si>
   <si>
     <t xml:space="preserve">2.92173719406128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05784296989441</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02154779434204</t>
+    <t xml:space="preserve">3.05784273147583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02154803276062</t>
   </si>
   <si>
     <t xml:space="preserve">3.13950634002686</t>
@@ -1352,46 +1352,46 @@
     <t xml:space="preserve">3.08506417274475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01247406005859</t>
+    <t xml:space="preserve">3.01247429847717</t>
   </si>
   <si>
     <t xml:space="preserve">2.88544225692749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77655744552612</t>
+    <t xml:space="preserve">2.7765576839447</t>
   </si>
   <si>
     <t xml:space="preserve">2.71304154396057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63137817382812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68582057952881</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66767311096191</t>
+    <t xml:space="preserve">2.6313784122467</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68582034111023</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66767287254333</t>
   </si>
   <si>
     <t xml:space="preserve">2.55878829956055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52249360084534</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67674684524536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64045190811157</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87636876106262</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83099961280823</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6041567325592</t>
+    <t xml:space="preserve">2.52249336242676</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67674660682678</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64045214653015</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87636852264404</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83099985122681</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60415697097778</t>
   </si>
   <si>
     <t xml:space="preserve">2.73118901252747</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">2.91266345977783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12135910987854</t>
+    <t xml:space="preserve">3.12135887145996</t>
   </si>
   <si>
     <t xml:space="preserve">3.0759904384613</t>
@@ -1427,46 +1427,46 @@
     <t xml:space="preserve">3.0941379070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38449668884277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41171789169312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37542295455933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42079162597656</t>
+    <t xml:space="preserve">3.38449692726135</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41171765327454</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37542319297791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42079138755798</t>
   </si>
   <si>
     <t xml:space="preserve">3.43893885612488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36634922027588</t>
+    <t xml:space="preserve">3.36634945869446</t>
   </si>
   <si>
     <t xml:space="preserve">3.35727572441101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20302224159241</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27561211585999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29375982284546</t>
+    <t xml:space="preserve">3.20302248001099</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27561187744141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29375958442688</t>
   </si>
   <si>
     <t xml:space="preserve">3.1667275428772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11228537559509</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78563117980957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84007358551025</t>
+    <t xml:space="preserve">3.11228513717651</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78563141822815</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84007382392883</t>
   </si>
   <si>
     <t xml:space="preserve">2.82192611694336</t>
@@ -57625,7 +57625,7 @@
     </row>
     <row r="2135">
       <c r="A2135" s="1" t="n">
-        <v>46076.6510185185</v>
+        <v>46076.3333333333</v>
       </c>
       <c r="B2135" t="n">
         <v>16587</v>
@@ -57646,6 +57646,32 @@
         <v>581</v>
       </c>
       <c r="H2135" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2136">
+      <c r="A2136" s="1" t="n">
+        <v>46077.6447916667</v>
+      </c>
+      <c r="B2136" t="n">
+        <v>2120</v>
+      </c>
+      <c r="C2136" t="n">
+        <v>3.79999995231628</v>
+      </c>
+      <c r="D2136" t="n">
+        <v>3.74000000953674</v>
+      </c>
+      <c r="E2136" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="F2136" t="n">
+        <v>3.74000000953674</v>
+      </c>
+      <c r="G2136" t="s">
+        <v>591</v>
+      </c>
+      <c r="H2136" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -38,7 +38,7 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02345752716064</t>
+    <t xml:space="preserve">3.02345776557922</t>
   </si>
   <si>
     <t xml:space="preserve">NDT.MI</t>
@@ -47,148 +47,148 @@
     <t xml:space="preserve">2.96519947052002</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88901543617249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98013734817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97266817092896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94577980041504</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9577305316925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96221160888672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93532347679138</t>
+    <t xml:space="preserve">2.88901519775391</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98013710975647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97266840934753</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94578003883362</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95773029327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9622118473053</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9353232383728</t>
   </si>
   <si>
     <t xml:space="preserve">2.91291642189026</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97864389419556</t>
+    <t xml:space="preserve">2.97864365577698</t>
   </si>
   <si>
     <t xml:space="preserve">2.98611235618591</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03540802001953</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05632138252258</t>
+    <t xml:space="preserve">3.03540825843811</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.056321144104</t>
   </si>
   <si>
     <t xml:space="preserve">3.0593090057373</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05034613609314</t>
+    <t xml:space="preserve">3.05034637451172</t>
   </si>
   <si>
     <t xml:space="preserve">2.98760628700256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95026135444641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01598858833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01001358032227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02495121955872</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01748251914978</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03092694282532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99955677986145</t>
+    <t xml:space="preserve">2.95026087760925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01598882675171</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01001381874084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02495145797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0174822807312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03092670440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99955654144287</t>
   </si>
   <si>
     <t xml:space="preserve">3.0443708896637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.959223985672</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00254464149475</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92785429954529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90843486785889</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.896484375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91889119148254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9159038066864</t>
+    <t xml:space="preserve">2.95922422409058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00254440307617</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92785453796387</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90843510627747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89648461341858</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91889142990112</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91590404510498</t>
   </si>
   <si>
     <t xml:space="preserve">2.92038512229919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90544724464417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90992856025696</t>
+    <t xml:space="preserve">2.90544748306274</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90992832183838</t>
   </si>
   <si>
     <t xml:space="preserve">2.9233729839325</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83822584152222</t>
+    <t xml:space="preserve">2.8382260799408</t>
   </si>
   <si>
     <t xml:space="preserve">2.86063313484192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82627558708191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77996730804443</t>
+    <t xml:space="preserve">2.82627534866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77996754646301</t>
   </si>
   <si>
     <t xml:space="preserve">2.84569525718689</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86810207366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88304018974304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79639983177185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87557077407837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89797830581665</t>
+    <t xml:space="preserve">2.86810183525085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88303995132446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79639935493469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87557101249695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89797806739807</t>
   </si>
   <si>
     <t xml:space="preserve">2.80088067054749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74262237548828</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82179427146912</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75009179115295</t>
+    <t xml:space="preserve">2.74262261390686</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8217945098877</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75009155273438</t>
   </si>
   <si>
     <t xml:space="preserve">2.76353573799133</t>
@@ -200,31 +200,31 @@
     <t xml:space="preserve">2.78594279289246</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79341197013855</t>
+    <t xml:space="preserve">2.79341173171997</t>
   </si>
   <si>
     <t xml:space="preserve">2.69631457328796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6515007019043</t>
+    <t xml:space="preserve">2.65150094032288</t>
   </si>
   <si>
     <t xml:space="preserve">2.62162446975708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5394651889801</t>
+    <t xml:space="preserve">2.53946542739868</t>
   </si>
   <si>
     <t xml:space="preserve">2.56934142112732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61415553092957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65896964073181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68884587287903</t>
+    <t xml:space="preserve">2.61415576934814</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65896940231323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68884539604187</t>
   </si>
   <si>
     <t xml:space="preserve">2.70378375053406</t>
@@ -236,7 +236,7 @@
     <t xml:space="preserve">2.81581902503967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7336597442627</t>
+    <t xml:space="preserve">2.73366022109985</t>
   </si>
   <si>
     <t xml:space="preserve">2.66643857955933</t>
@@ -254,28 +254,28 @@
     <t xml:space="preserve">2.83075714111328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89315056800842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69871878623962</t>
+    <t xml:space="preserve">2.89315104484558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69871854782104</t>
   </si>
   <si>
     <t xml:space="preserve">2.83870983123779</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93203711509705</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87759613990784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8309326171875</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81537747383118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84648680686951</t>
+    <t xml:space="preserve">2.93203687667847</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87759590148926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83093237876892</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81537771224976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84648704528809</t>
   </si>
   <si>
     <t xml:space="preserve">2.79982328414917</t>
@@ -287,10 +287,10 @@
     <t xml:space="preserve">2.76093673706055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80760025978088</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00980973243713</t>
+    <t xml:space="preserve">2.80760049819946</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00980997085571</t>
   </si>
   <si>
     <t xml:space="preserve">2.9553689956665</t>
@@ -302,28 +302,28 @@
     <t xml:space="preserve">2.88537335395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82315540313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86204171180725</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00203275680542</t>
+    <t xml:space="preserve">2.82315516471863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86204147338867</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00203251838684</t>
   </si>
   <si>
     <t xml:space="preserve">2.91648244857788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85426449775696</t>
+    <t xml:space="preserve">2.85426425933838</t>
   </si>
   <si>
     <t xml:space="preserve">2.7298276424408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68316411972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72205018997192</t>
+    <t xml:space="preserve">2.68316388130188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.7220504283905</t>
   </si>
   <si>
     <t xml:space="preserve">2.75315952301025</t>
@@ -335,28 +335,28 @@
     <t xml:space="preserve">2.93981432914734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99425530433655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97870087623596</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86981868743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94759154319763</t>
+    <t xml:space="preserve">2.99425506591797</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97870063781738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86981892585754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94759178161621</t>
   </si>
   <si>
     <t xml:space="preserve">2.98647809028625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63650012016296</t>
+    <t xml:space="preserve">2.63650035858154</t>
   </si>
   <si>
     <t xml:space="preserve">2.550950050354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51984119415283</t>
+    <t xml:space="preserve">2.51984071731567</t>
   </si>
   <si>
     <t xml:space="preserve">2.41095900535583</t>
@@ -365,31 +365,31 @@
     <t xml:space="preserve">2.34096336364746</t>
   </si>
   <si>
-    <t xml:space="preserve">2.34874081611633</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36429500579834</t>
+    <t xml:space="preserve">2.34874057769775</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.36429524421692</t>
   </si>
   <si>
     <t xml:space="preserve">2.2554132938385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24763584136963</t>
+    <t xml:space="preserve">2.24763607978821</t>
   </si>
   <si>
     <t xml:space="preserve">2.3254086971283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23208093643188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18541765213013</t>
+    <t xml:space="preserve">2.23208141326904</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18541741371155</t>
   </si>
   <si>
     <t xml:space="preserve">2.27874517440796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26319026947021</t>
+    <t xml:space="preserve">2.26319050788879</t>
   </si>
   <si>
     <t xml:space="preserve">2.21652674674988</t>
@@ -398,22 +398,22 @@
     <t xml:space="preserve">2.06875848770142</t>
   </si>
   <si>
-    <t xml:space="preserve">2.14653134346008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10764455795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15430855751038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17763996124268</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22430396080017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35651779174805</t>
+    <t xml:space="preserve">2.1465311050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10764479637146</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1543083190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17764019966125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22430372238159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35651803016663</t>
   </si>
   <si>
     <t xml:space="preserve">2.48873162269592</t>
@@ -422,31 +422,31 @@
     <t xml:space="preserve">2.52761840820312</t>
   </si>
   <si>
-    <t xml:space="preserve">2.43429112434387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44206786155701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55872750282288</t>
+    <t xml:space="preserve">2.43429088592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44206809997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5587272644043</t>
   </si>
   <si>
     <t xml:space="preserve">2.44984555244446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37207245826721</t>
+    <t xml:space="preserve">2.37207221984863</t>
   </si>
   <si>
     <t xml:space="preserve">2.33318591117859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29429984092712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3798496723175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71427321434021</t>
+    <t xml:space="preserve">2.29429960250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37984943389893</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71427297592163</t>
   </si>
   <si>
     <t xml:space="preserve">2.58205914497375</t>
@@ -455,34 +455,34 @@
     <t xml:space="preserve">2.62872290611267</t>
   </si>
   <si>
-    <t xml:space="preserve">2.659832239151</t>
+    <t xml:space="preserve">2.65983176231384</t>
   </si>
   <si>
     <t xml:space="preserve">2.57428193092346</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67538690567017</t>
+    <t xml:space="preserve">2.67538666725159</t>
   </si>
   <si>
     <t xml:space="preserve">2.64427733421326</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69094109535217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76871395111084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90092778205872</t>
+    <t xml:space="preserve">2.69094133377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76871371269226</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90092802047729</t>
   </si>
   <si>
     <t xml:space="preserve">2.9631462097168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92426013946533</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97092318534851</t>
+    <t xml:space="preserve">2.92425990104675</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97092366218567</t>
   </si>
   <si>
     <t xml:space="preserve">3.01758718490601</t>
@@ -491,7 +491,7 @@
     <t xml:space="preserve">3.04869627952576</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03314185142517</t>
+    <t xml:space="preserve">3.03314208984375</t>
   </si>
   <si>
     <t xml:space="preserve">3.0642511844635</t>
@@ -506,7 +506,7 @@
     <t xml:space="preserve">3.02811288833618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01191973686218</t>
+    <t xml:space="preserve">3.01191997528076</t>
   </si>
   <si>
     <t xml:space="preserve">3.10907816886902</t>
@@ -515,10 +515,10 @@
     <t xml:space="preserve">3.0928852558136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12527132034302</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07669186592102</t>
+    <t xml:space="preserve">3.12527108192444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0766921043396</t>
   </si>
   <si>
     <t xml:space="preserve">2.99572658538818</t>
@@ -527,7 +527,7 @@
     <t xml:space="preserve">3.30339574813843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41674757003784</t>
+    <t xml:space="preserve">3.41674709320068</t>
   </si>
   <si>
     <t xml:space="preserve">3.35197520256042</t>
@@ -536,52 +536,52 @@
     <t xml:space="preserve">3.33578205108643</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36816835403442</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23862314224243</t>
+    <t xml:space="preserve">3.36816811561584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.23862338066101</t>
   </si>
   <si>
     <t xml:space="preserve">3.31958889961243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27100944519043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28720235824585</t>
+    <t xml:space="preserve">3.27100968360901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28720259666443</t>
   </si>
   <si>
     <t xml:space="preserve">3.22243022918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17385101318359</t>
+    <t xml:space="preserve">3.17385077476501</t>
   </si>
   <si>
     <t xml:space="preserve">3.20623731613159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.14146494865417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40055418014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49771332740784</t>
+    <t xml:space="preserve">3.1414647102356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40055441856384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49771308898926</t>
   </si>
   <si>
     <t xml:space="preserve">3.38436126708984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25481653213501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19004416465759</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96334028244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97953367233276</t>
+    <t xml:space="preserve">3.25481629371643</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19004392623901</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96334052085876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97953343391418</t>
   </si>
   <si>
     <t xml:space="preserve">2.80140924453735</t>
@@ -593,7 +593,7 @@
     <t xml:space="preserve">2.86618161201477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84998822212219</t>
+    <t xml:space="preserve">2.84998846054077</t>
   </si>
   <si>
     <t xml:space="preserve">2.78521609306335</t>
@@ -602,7 +602,7 @@
     <t xml:space="preserve">2.75283002853394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72044372558594</t>
+    <t xml:space="preserve">2.72044324874878</t>
   </si>
   <si>
     <t xml:space="preserve">2.83379530906677</t>
@@ -611,19 +611,19 @@
     <t xml:space="preserve">2.76902318000793</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73663687705994</t>
+    <t xml:space="preserve">2.73663663864136</t>
   </si>
   <si>
     <t xml:space="preserve">2.81760239601135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89856767654419</t>
+    <t xml:space="preserve">2.89856791496277</t>
   </si>
   <si>
     <t xml:space="preserve">2.91476082801819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63947772979736</t>
+    <t xml:space="preserve">2.63947820663452</t>
   </si>
   <si>
     <t xml:space="preserve">2.67186403274536</t>
@@ -632,22 +632,22 @@
     <t xml:space="preserve">2.62328481674194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68805718421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70425057411194</t>
+    <t xml:space="preserve">2.68805742263794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70425033569336</t>
   </si>
   <si>
     <t xml:space="preserve">2.60709190368652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59089875221252</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.42896747589111</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54231929779053</t>
+    <t xml:space="preserve">2.5908989906311</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.42896723747253</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54231953620911</t>
   </si>
   <si>
     <t xml:space="preserve">2.46135354042053</t>
@@ -656,13 +656,13 @@
     <t xml:space="preserve">2.3156156539917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29942274093628</t>
+    <t xml:space="preserve">2.2994225025177</t>
   </si>
   <si>
     <t xml:space="preserve">2.35488152503967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40607476234436</t>
+    <t xml:space="preserve">2.40607452392578</t>
   </si>
   <si>
     <t xml:space="preserve">2.28662419319153</t>
@@ -671,7 +671,7 @@
     <t xml:space="preserve">2.13304495811462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08185195922852</t>
+    <t xml:space="preserve">2.08185172080994</t>
   </si>
   <si>
     <t xml:space="preserve">2.06478762626648</t>
@@ -689,25 +689,25 @@
     <t xml:space="preserve">2.26956009864807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.21836686134338</t>
+    <t xml:space="preserve">2.2183666229248</t>
   </si>
   <si>
     <t xml:space="preserve">2.32075309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55965423583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54258990287781</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45726799964905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5767183303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62791132926941</t>
+    <t xml:space="preserve">2.55965399742126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54258966445923</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45726823806763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57671856880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62791156768799</t>
   </si>
   <si>
     <t xml:space="preserve">2.61084699630737</t>
@@ -716,19 +716,19 @@
     <t xml:space="preserve">2.64497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59378290176392</t>
+    <t xml:space="preserve">2.59378266334534</t>
   </si>
   <si>
     <t xml:space="preserve">2.69616913795471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71323323249817</t>
+    <t xml:space="preserve">2.71323347091675</t>
   </si>
   <si>
     <t xml:space="preserve">2.44020342826843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42313933372498</t>
+    <t xml:space="preserve">2.4231390953064</t>
   </si>
   <si>
     <t xml:space="preserve">2.47433233261108</t>
@@ -737,19 +737,19 @@
     <t xml:space="preserve">2.15010929107666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33781719207764</t>
+    <t xml:space="preserve">2.33781743049622</t>
   </si>
   <si>
     <t xml:space="preserve">2.30368876457214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25249576568604</t>
+    <t xml:space="preserve">2.25249552726746</t>
   </si>
   <si>
     <t xml:space="preserve">2.23543095588684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37194633483887</t>
+    <t xml:space="preserve">2.37194585800171</t>
   </si>
   <si>
     <t xml:space="preserve">2.38901042938232</t>
@@ -758,10 +758,10 @@
     <t xml:space="preserve">2.20130252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18423795700073</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01359415054321</t>
+    <t xml:space="preserve">2.18423819541931</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01359438896179</t>
   </si>
   <si>
     <t xml:space="preserve">2.04772329330444</t>
@@ -773,49 +773,49 @@
     <t xml:space="preserve">1.91120839118958</t>
   </si>
   <si>
-    <t xml:space="preserve">1.87707984447479</t>
+    <t xml:space="preserve">1.8770797252655</t>
   </si>
   <si>
     <t xml:space="preserve">1.84295094013214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97946584224701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86001515388489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94533693790436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96240127086639</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99652993679047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81561923027039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90094137191772</t>
+    <t xml:space="preserve">1.97946572303772</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86001527309418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94533705711365</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.9624011516571</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99653005599976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81561946868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9009416103363</t>
   </si>
   <si>
     <t xml:space="preserve">2.88387703895569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76442623138428</t>
+    <t xml:space="preserve">2.76442646980286</t>
   </si>
   <si>
     <t xml:space="preserve">2.73029756546021</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67910432815552</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74736189842224</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83268356323242</t>
+    <t xml:space="preserve">2.6791045665741</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74736213684082</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.832683801651</t>
   </si>
   <si>
     <t xml:space="preserve">2.86681246757507</t>
@@ -824,7 +824,7 @@
     <t xml:space="preserve">2.79855489730835</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78149056434631</t>
+    <t xml:space="preserve">2.78149080276489</t>
   </si>
   <si>
     <t xml:space="preserve">2.9350700378418</t>
@@ -833,10 +833,10 @@
     <t xml:space="preserve">2.96919870376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02039170265198</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00332713127136</t>
+    <t xml:space="preserve">3.02039194107056</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00332736968994</t>
   </si>
   <si>
     <t xml:space="preserve">3.03745627403259</t>
@@ -845,7 +845,7 @@
     <t xml:space="preserve">2.98626303672791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05452036857605</t>
+    <t xml:space="preserve">3.05452060699463</t>
   </si>
   <si>
     <t xml:space="preserve">3.07158470153809</t>
@@ -860,19 +860,19 @@
     <t xml:space="preserve">3.13131022453308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06305265426636</t>
+    <t xml:space="preserve">3.06305241584778</t>
   </si>
   <si>
     <t xml:space="preserve">3.16543889045715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19956755638123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15690660476685</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.23369646072388</t>
+    <t xml:space="preserve">3.1995677947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15690684318542</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.2336962223053</t>
   </si>
   <si>
     <t xml:space="preserve">3.27635717391968</t>
@@ -881,37 +881,37 @@
     <t xml:space="preserve">3.24222826957703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26782488822937</t>
+    <t xml:space="preserve">3.26782464981079</t>
   </si>
   <si>
     <t xml:space="preserve">3.31048607826233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34461450576782</t>
+    <t xml:space="preserve">3.3446147441864</t>
   </si>
   <si>
     <t xml:space="preserve">3.32755041122437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28488945960999</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18250346183777</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29342126846313</t>
+    <t xml:space="preserve">3.28488922119141</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18250322341919</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29342174530029</t>
   </si>
   <si>
     <t xml:space="preserve">3.33710074424744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32836484909058</t>
+    <t xml:space="preserve">3.32836508750916</t>
   </si>
   <si>
     <t xml:space="preserve">3.29342150688171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24974250793457</t>
+    <t xml:space="preserve">3.24974226951599</t>
   </si>
   <si>
     <t xml:space="preserve">3.20606303215027</t>
@@ -932,10 +932,10 @@
     <t xml:space="preserve">3.36330842971802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49434638023376</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58170509338379</t>
+    <t xml:space="preserve">3.49434661865234</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58170485496521</t>
   </si>
   <si>
     <t xml:space="preserve">3.56423354148865</t>
@@ -959,31 +959,31 @@
     <t xml:space="preserve">3.62538456916809</t>
   </si>
   <si>
-    <t xml:space="preserve">3.74768662452698</t>
+    <t xml:space="preserve">3.7476863861084</t>
   </si>
   <si>
     <t xml:space="preserve">3.69527125358582</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66906332969666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60791301727295</t>
+    <t xml:space="preserve">3.66906356811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60791277885437</t>
   </si>
   <si>
     <t xml:space="preserve">3.55549788475037</t>
   </si>
   <si>
-    <t xml:space="preserve">3.66032767295837</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65159177780151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.68653512001038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7040069103241</t>
+    <t xml:space="preserve">3.66032791137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65159201622009</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.68653535842896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.70400714874268</t>
   </si>
   <si>
     <t xml:space="preserve">3.75642275810242</t>
@@ -998,7 +998,7 @@
     <t xml:space="preserve">3.3458366394043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38951635360718</t>
+    <t xml:space="preserve">3.3895161151886</t>
   </si>
   <si>
     <t xml:space="preserve">3.42445969581604</t>
@@ -1028,7 +1028,7 @@
     <t xml:space="preserve">3.46813893318176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47687458992004</t>
+    <t xml:space="preserve">3.47687482833862</t>
   </si>
   <si>
     <t xml:space="preserve">3.79136610031128</t>
@@ -1037,7 +1037,7 @@
     <t xml:space="preserve">3.72147917747498</t>
   </si>
   <si>
-    <t xml:space="preserve">3.8787248134613</t>
+    <t xml:space="preserve">3.87872457504272</t>
   </si>
   <si>
     <t xml:space="preserve">4.17574453353882</t>
@@ -1052,7 +1052,7 @@
     <t xml:space="preserve">4.1844801902771</t>
   </si>
   <si>
-    <t xml:space="preserve">4.20195198059082</t>
+    <t xml:space="preserve">4.20195150375366</t>
   </si>
   <si>
     <t xml:space="preserve">4.25436639785767</t>
@@ -1061,10 +1061,10 @@
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493202209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98355484008789</t>
+    <t xml:space="preserve">3.90493226051331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98355507850647</t>
   </si>
   <si>
     <t xml:space="preserve">3.94861149787903</t>
@@ -1073,13 +1073,13 @@
     <t xml:space="preserve">3.93113970756531</t>
   </si>
   <si>
-    <t xml:space="preserve">4.08838510513306</t>
+    <t xml:space="preserve">4.08838558197021</t>
   </si>
   <si>
     <t xml:space="preserve">4.07091331481934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1233286857605</t>
+    <t xml:space="preserve">4.12332916259766</t>
   </si>
   <si>
     <t xml:space="preserve">4.00102663040161</t>
@@ -1088,13 +1088,13 @@
     <t xml:space="preserve">4.00976276397705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93987560272217</t>
+    <t xml:space="preserve">3.93987584114075</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
   </si>
   <si>
-    <t xml:space="preserve">4.21068811416626</t>
+    <t xml:space="preserve">4.2106876373291</t>
   </si>
   <si>
     <t xml:space="preserve">4.29804611206055</t>
@@ -1112,16 +1112,16 @@
     <t xml:space="preserve">4.14953660964966</t>
   </si>
   <si>
-    <t xml:space="preserve">4.16700839996338</t>
+    <t xml:space="preserve">4.16700792312622</t>
   </si>
   <si>
     <t xml:space="preserve">4.11459302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06217813491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78263020515442</t>
+    <t xml:space="preserve">4.06217765808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78262996673584</t>
   </si>
   <si>
     <t xml:space="preserve">3.80010175704956</t>
@@ -1130,13 +1130,13 @@
     <t xml:space="preserve">3.82630944252014</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83504509925842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84378123283386</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77389454841614</t>
+    <t xml:space="preserve">3.83504557609558</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84378147125244</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77389430999756</t>
   </si>
   <si>
     <t xml:space="preserve">4.03597021102905</t>
@@ -1151,13 +1151,13 @@
     <t xml:space="preserve">3.86125302314758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7651584148407</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8175733089447</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64285612106323</t>
+    <t xml:space="preserve">3.76515817642212</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.81757354736328</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64285635948181</t>
   </si>
   <si>
     <t xml:space="preserve">3.67779946327209</t>
@@ -1175,7 +1175,7 @@
     <t xml:space="preserve">3.92240381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61664867401123</t>
+    <t xml:space="preserve">3.61664843559265</t>
   </si>
   <si>
     <t xml:space="preserve">3.39825224876404</t>
@@ -1184,19 +1184,19 @@
     <t xml:space="preserve">3.23227071762085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0575532913208</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97019457817078</t>
+    <t xml:space="preserve">3.05755305290222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97019481658936</t>
   </si>
   <si>
     <t xml:space="preserve">2.95272302627563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91777920722961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90904355049133</t>
+    <t xml:space="preserve">2.91777944564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90904331207275</t>
   </si>
   <si>
     <t xml:space="preserve">3.37204432487488</t>
@@ -1205,13 +1205,13 @@
     <t xml:space="preserve">3.38078022003174</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41572403907776</t>
+    <t xml:space="preserve">3.41572380065918</t>
   </si>
   <si>
     <t xml:space="preserve">3.31962895393372</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27594995498657</t>
+    <t xml:space="preserve">3.27595019340515</t>
   </si>
   <si>
     <t xml:space="preserve">3.28468561172485</t>
@@ -57651,7 +57651,7 @@
     </row>
     <row r="2136">
       <c r="A2136" s="1" t="n">
-        <v>46077.6447916667</v>
+        <v>46077.3333333333</v>
       </c>
       <c r="B2136" t="n">
         <v>2120</v>
@@ -57672,6 +57672,32 @@
         <v>591</v>
       </c>
       <c r="H2136" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2137">
+      <c r="A2137" s="1" t="n">
+        <v>46078.6910532407</v>
+      </c>
+      <c r="B2137" t="n">
+        <v>6468</v>
+      </c>
+      <c r="C2137" t="n">
+        <v>3.79999995231628</v>
+      </c>
+      <c r="D2137" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="E2137" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="F2137" t="n">
+        <v>3.77999997138977</v>
+      </c>
+      <c r="G2137" t="s">
+        <v>585</v>
+      </c>
+      <c r="H2137" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -38,43 +38,43 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02345776557922</t>
+    <t xml:space="preserve">3.02345752716064</t>
   </si>
   <si>
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519947052002</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88901519775391</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98013710975647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97266840934753</t>
+    <t xml:space="preserve">2.96519923210144</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88901543617249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98013734817505</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97266817092896</t>
   </si>
   <si>
     <t xml:space="preserve">2.94578003883362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95773029327393</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9622118473053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9353232383728</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91291642189026</t>
+    <t xml:space="preserve">2.9577305316925</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96221160888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93532347679138</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91291618347168</t>
   </si>
   <si>
     <t xml:space="preserve">2.97864365577698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98611235618591</t>
+    <t xml:space="preserve">2.98611259460449</t>
   </si>
   <si>
     <t xml:space="preserve">3.03540825843811</t>
@@ -83,49 +83,49 @@
     <t xml:space="preserve">3.056321144104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0593090057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05034637451172</t>
+    <t xml:space="preserve">3.05930876731873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05034613609314</t>
   </si>
   <si>
     <t xml:space="preserve">2.98760628700256</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95026087760925</t>
+    <t xml:space="preserve">2.95026135444641</t>
   </si>
   <si>
     <t xml:space="preserve">3.01598882675171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01001381874084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02495145797729</t>
+    <t xml:space="preserve">3.01001358032227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02495169639587</t>
   </si>
   <si>
     <t xml:space="preserve">3.0174822807312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03092670440674</t>
+    <t xml:space="preserve">3.03092646598816</t>
   </si>
   <si>
     <t xml:space="preserve">2.99955654144287</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0443708896637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95922422409058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00254440307617</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92785453796387</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90843510627747</t>
+    <t xml:space="preserve">3.04437136650085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.959223985672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00254464149475</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92785429954529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90843462944031</t>
   </si>
   <si>
     <t xml:space="preserve">2.89648461341858</t>
@@ -134,19 +134,19 @@
     <t xml:space="preserve">2.91889142990112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91590404510498</t>
+    <t xml:space="preserve">2.9159038066864</t>
   </si>
   <si>
     <t xml:space="preserve">2.92038512229919</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90544748306274</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90992832183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9233729839325</t>
+    <t xml:space="preserve">2.90544700622559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90992879867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92337274551392</t>
   </si>
   <si>
     <t xml:space="preserve">2.8382260799408</t>
@@ -155,19 +155,19 @@
     <t xml:space="preserve">2.86063313484192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82627534866333</t>
+    <t xml:space="preserve">2.82627582550049</t>
   </si>
   <si>
     <t xml:space="preserve">2.77996754646301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84569525718689</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86810183525085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88303995132446</t>
+    <t xml:space="preserve">2.84569501876831</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86810207366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88303971290588</t>
   </si>
   <si>
     <t xml:space="preserve">2.79639935493469</t>
@@ -179,37 +179,37 @@
     <t xml:space="preserve">2.89797806739807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80088067054749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74262261390686</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8217945098877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75009155273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76353573799133</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77847409248352</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78594279289246</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79341173171997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69631457328796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65150094032288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62162446975708</t>
+    <t xml:space="preserve">2.80088114738464</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74262285232544</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82179403305054</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75009179115295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76353549957275</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77847385406494</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78594303131104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79341197013855</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69631481170654</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6515007019043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62162470817566</t>
   </si>
   <si>
     <t xml:space="preserve">2.53946542739868</t>
@@ -218,16 +218,16 @@
     <t xml:space="preserve">2.56934142112732</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61415576934814</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65896940231323</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68884539604187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70378375053406</t>
+    <t xml:space="preserve">2.61415553092957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65896964073181</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68884563446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70378351211548</t>
   </si>
   <si>
     <t xml:space="preserve">2.77100491523743</t>
@@ -236,13 +236,13 @@
     <t xml:space="preserve">2.81581902503967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73366022109985</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66643857955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68137669563293</t>
+    <t xml:space="preserve">2.7336597442627</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66643905639648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68137693405151</t>
   </si>
   <si>
     <t xml:space="preserve">2.74112892150879</t>
@@ -254,46 +254,46 @@
     <t xml:space="preserve">2.83075714111328</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89315104484558</t>
+    <t xml:space="preserve">2.893150806427</t>
   </si>
   <si>
     <t xml:space="preserve">2.69871854782104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83870983123779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93203687667847</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87759590148926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83093237876892</t>
+    <t xml:space="preserve">2.83870959281921</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.93203711509705</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87759613990784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8309326171875</t>
   </si>
   <si>
     <t xml:space="preserve">2.81537771224976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84648704528809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79982328414917</t>
+    <t xml:space="preserve">2.84648680686951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79982304573059</t>
   </si>
   <si>
     <t xml:space="preserve">2.73760485649109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76093673706055</t>
+    <t xml:space="preserve">2.76093697547913</t>
   </si>
   <si>
     <t xml:space="preserve">2.80760049819946</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00980997085571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9553689956665</t>
+    <t xml:space="preserve">3.00980973243713</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95536875724792</t>
   </si>
   <si>
     <t xml:space="preserve">2.90870523452759</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">2.88537335395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82315516471863</t>
+    <t xml:space="preserve">2.82315492630005</t>
   </si>
   <si>
     <t xml:space="preserve">2.86204147338867</t>
@@ -314,19 +314,19 @@
     <t xml:space="preserve">2.91648244857788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85426425933838</t>
+    <t xml:space="preserve">2.85426449775696</t>
   </si>
   <si>
     <t xml:space="preserve">2.7298276424408</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68316388130188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7220504283905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75315952301025</t>
+    <t xml:space="preserve">2.68316411972046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72205018997192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75315976142883</t>
   </si>
   <si>
     <t xml:space="preserve">2.70649576187134</t>
@@ -335,22 +335,22 @@
     <t xml:space="preserve">2.93981432914734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99425506591797</t>
+    <t xml:space="preserve">2.99425554275513</t>
   </si>
   <si>
     <t xml:space="preserve">2.97870063781738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86981892585754</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94759178161621</t>
+    <t xml:space="preserve">2.86981868743896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94759202003479</t>
   </si>
   <si>
     <t xml:space="preserve">2.98647809028625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63650035858154</t>
+    <t xml:space="preserve">2.63650059700012</t>
   </si>
   <si>
     <t xml:space="preserve">2.550950050354</t>
@@ -359,43 +359,43 @@
     <t xml:space="preserve">2.51984071731567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41095900535583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34096336364746</t>
+    <t xml:space="preserve">2.41095876693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34096312522888</t>
   </si>
   <si>
     <t xml:space="preserve">2.34874057769775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36429524421692</t>
+    <t xml:space="preserve">2.36429500579834</t>
   </si>
   <si>
     <t xml:space="preserve">2.2554132938385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24763607978821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3254086971283</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23208141326904</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.18541741371155</t>
+    <t xml:space="preserve">2.24763584136963</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32540893554688</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23208117485046</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.18541765213013</t>
   </si>
   <si>
     <t xml:space="preserve">2.27874517440796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26319050788879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21652674674988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06875848770142</t>
+    <t xml:space="preserve">2.26319003105164</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2165265083313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06875824928284</t>
   </si>
   <si>
     <t xml:space="preserve">2.1465311050415</t>
@@ -404,37 +404,37 @@
     <t xml:space="preserve">2.10764479637146</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1543083190918</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17764019966125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22430372238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35651803016663</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48873162269592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52761840820312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43429088592529</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44206809997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5587272644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44984555244446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37207221984863</t>
+    <t xml:space="preserve">2.15430855751038</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17764043807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22430396080017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35651779174805</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.48873209953308</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52761793136597</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43429064750671</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44206833839417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55872750282288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44984531402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37207269668579</t>
   </si>
   <si>
     <t xml:space="preserve">2.33318591117859</t>
@@ -443,19 +443,19 @@
     <t xml:space="preserve">2.29429960250854</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37984943389893</t>
+    <t xml:space="preserve">2.3798496723175</t>
   </si>
   <si>
     <t xml:space="preserve">2.71427297592163</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58205914497375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62872290611267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65983176231384</t>
+    <t xml:space="preserve">2.58205890655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62872314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65983200073242</t>
   </si>
   <si>
     <t xml:space="preserve">2.57428193092346</t>
@@ -464,40 +464,40 @@
     <t xml:space="preserve">2.67538666725159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64427733421326</t>
+    <t xml:space="preserve">2.64427757263184</t>
   </si>
   <si>
     <t xml:space="preserve">2.69094133377075</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76871371269226</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90092802047729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9631462097168</t>
+    <t xml:space="preserve">2.76871418952942</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90092825889587</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96314597129822</t>
   </si>
   <si>
     <t xml:space="preserve">2.92425990104675</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97092366218567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01758718490601</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04869627952576</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03314208984375</t>
+    <t xml:space="preserve">2.97092342376709</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01758766174316</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.04869651794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03314185142517</t>
   </si>
   <si>
     <t xml:space="preserve">3.0642511844635</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07980561256409</t>
+    <t xml:space="preserve">3.07980585098267</t>
   </si>
   <si>
     <t xml:space="preserve">3.0604989528656</t>
@@ -506,19 +506,19 @@
     <t xml:space="preserve">3.02811288833618</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01191997528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10907816886902</t>
+    <t xml:space="preserve">3.01191973686218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1090784072876</t>
   </si>
   <si>
     <t xml:space="preserve">3.0928852558136</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12527108192444</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0766921043396</t>
+    <t xml:space="preserve">3.12527132034302</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07669186592102</t>
   </si>
   <si>
     <t xml:space="preserve">2.99572658538818</t>
@@ -527,13 +527,13 @@
     <t xml:space="preserve">3.30339574813843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41674709320068</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35197520256042</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33578205108643</t>
+    <t xml:space="preserve">3.41674757003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35197496414185</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33578181266785</t>
   </si>
   <si>
     <t xml:space="preserve">3.36816811561584</t>
@@ -545,7 +545,7 @@
     <t xml:space="preserve">3.31958889961243</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27100968360901</t>
+    <t xml:space="preserve">3.27100944519043</t>
   </si>
   <si>
     <t xml:space="preserve">3.28720259666443</t>
@@ -554,31 +554,31 @@
     <t xml:space="preserve">3.22243022918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17385077476501</t>
+    <t xml:space="preserve">3.17385101318359</t>
   </si>
   <si>
     <t xml:space="preserve">3.20623731613159</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1414647102356</t>
+    <t xml:space="preserve">3.14146494865417</t>
   </si>
   <si>
     <t xml:space="preserve">3.40055441856384</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49771308898926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.38436126708984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25481629371643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.19004392623901</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96334052085876</t>
+    <t xml:space="preserve">3.49771356582642</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.38436102867126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25481653213501</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19004416465759</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96334028244019</t>
   </si>
   <si>
     <t xml:space="preserve">2.97953343391418</t>
@@ -590,7 +590,7 @@
     <t xml:space="preserve">2.88237476348877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86618161201477</t>
+    <t xml:space="preserve">2.86618185043335</t>
   </si>
   <si>
     <t xml:space="preserve">2.84998846054077</t>
@@ -602,16 +602,16 @@
     <t xml:space="preserve">2.75283002853394</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72044324874878</t>
+    <t xml:space="preserve">2.72044348716736</t>
   </si>
   <si>
     <t xml:space="preserve">2.83379530906677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76902318000793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73663663864136</t>
+    <t xml:space="preserve">2.76902294158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73663687705994</t>
   </si>
   <si>
     <t xml:space="preserve">2.81760239601135</t>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">2.91476082801819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63947820663452</t>
+    <t xml:space="preserve">2.63947796821594</t>
   </si>
   <si>
     <t xml:space="preserve">2.67186403274536</t>
@@ -632,10 +632,10 @@
     <t xml:space="preserve">2.62328481674194</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68805742263794</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70425033569336</t>
+    <t xml:space="preserve">2.68805718421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70425057411194</t>
   </si>
   <si>
     <t xml:space="preserve">2.60709190368652</t>
@@ -644,7 +644,7 @@
     <t xml:space="preserve">2.5908989906311</t>
   </si>
   <si>
-    <t xml:space="preserve">2.42896723747253</t>
+    <t xml:space="preserve">2.42896747589111</t>
   </si>
   <si>
     <t xml:space="preserve">2.54231953620911</t>
@@ -656,13 +656,13 @@
     <t xml:space="preserve">2.3156156539917</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2994225025177</t>
+    <t xml:space="preserve">2.29942274093628</t>
   </si>
   <si>
     <t xml:space="preserve">2.35488152503967</t>
   </si>
   <si>
-    <t xml:space="preserve">2.40607452392578</t>
+    <t xml:space="preserve">2.40607476234436</t>
   </si>
   <si>
     <t xml:space="preserve">2.28662419319153</t>
@@ -671,7 +671,7 @@
     <t xml:space="preserve">2.13304495811462</t>
   </si>
   <si>
-    <t xml:space="preserve">2.08185172080994</t>
+    <t xml:space="preserve">2.08185219764709</t>
   </si>
   <si>
     <t xml:space="preserve">2.06478762626648</t>
@@ -689,28 +689,28 @@
     <t xml:space="preserve">2.26956009864807</t>
   </si>
   <si>
-    <t xml:space="preserve">2.2183666229248</t>
+    <t xml:space="preserve">2.21836686134338</t>
   </si>
   <si>
     <t xml:space="preserve">2.32075309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55965399742126</t>
+    <t xml:space="preserve">2.55965423583984</t>
   </si>
   <si>
     <t xml:space="preserve">2.54258966445923</t>
   </si>
   <si>
-    <t xml:space="preserve">2.45726823806763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57671856880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62791156768799</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61084699630737</t>
+    <t xml:space="preserve">2.45726799964905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5767183303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62791132926941</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61084723472595</t>
   </si>
   <si>
     <t xml:space="preserve">2.64497566223145</t>
@@ -722,7 +722,7 @@
     <t xml:space="preserve">2.69616913795471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71323347091675</t>
+    <t xml:space="preserve">2.71323323249817</t>
   </si>
   <si>
     <t xml:space="preserve">2.44020342826843</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">2.4231390953064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.47433233261108</t>
+    <t xml:space="preserve">2.4743320941925</t>
   </si>
   <si>
     <t xml:space="preserve">2.15010929107666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33781743049622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30368876457214</t>
+    <t xml:space="preserve">2.33781719207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30368852615356</t>
   </si>
   <si>
     <t xml:space="preserve">2.25249552726746</t>
@@ -749,7 +749,7 @@
     <t xml:space="preserve">2.23543095588684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37194585800171</t>
+    <t xml:space="preserve">2.37194633483887</t>
   </si>
   <si>
     <t xml:space="preserve">2.38901042938232</t>
@@ -758,10 +758,10 @@
     <t xml:space="preserve">2.20130252838135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.18423819541931</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.01359438896179</t>
+    <t xml:space="preserve">2.18423795700073</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.01359415054321</t>
   </si>
   <si>
     <t xml:space="preserve">2.04772329330444</t>
@@ -785,16 +785,16 @@
     <t xml:space="preserve">1.86001527309418</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94533705711365</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.9624011516571</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99653005599976</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81561946868896</t>
+    <t xml:space="preserve">1.94533681869507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96240139007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99652981758118</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81561923027039</t>
   </si>
   <si>
     <t xml:space="preserve">2.9009416103363</t>
@@ -803,10 +803,10 @@
     <t xml:space="preserve">2.88387703895569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76442646980286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73029756546021</t>
+    <t xml:space="preserve">2.76442623138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73029780387878</t>
   </si>
   <si>
     <t xml:space="preserve">2.6791045665741</t>
@@ -815,13 +815,13 @@
     <t xml:space="preserve">2.74736213684082</t>
   </si>
   <si>
-    <t xml:space="preserve">2.832683801651</t>
+    <t xml:space="preserve">2.83268356323242</t>
   </si>
   <si>
     <t xml:space="preserve">2.86681246757507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79855489730835</t>
+    <t xml:space="preserve">2.79855513572693</t>
   </si>
   <si>
     <t xml:space="preserve">2.78149080276489</t>
@@ -836,7 +836,7 @@
     <t xml:space="preserve">3.02039194107056</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00332736968994</t>
+    <t xml:space="preserve">3.00332713127136</t>
   </si>
   <si>
     <t xml:space="preserve">3.03745627403259</t>
@@ -845,7 +845,7 @@
     <t xml:space="preserve">2.98626303672791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05452060699463</t>
+    <t xml:space="preserve">3.05452036857605</t>
   </si>
   <si>
     <t xml:space="preserve">3.07158470153809</t>
@@ -854,22 +854,22 @@
     <t xml:space="preserve">3.13984251022339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11424589157104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13131022453308</t>
+    <t xml:space="preserve">3.11424565315247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1313099861145</t>
   </si>
   <si>
     <t xml:space="preserve">3.06305241584778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16543889045715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1995677947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15690684318542</t>
+    <t xml:space="preserve">3.16543865203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19956755638123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15690660476685</t>
   </si>
   <si>
     <t xml:space="preserve">3.2336962223053</t>
@@ -881,7 +881,7 @@
     <t xml:space="preserve">3.24222826957703</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26782464981079</t>
+    <t xml:space="preserve">3.26782488822937</t>
   </si>
   <si>
     <t xml:space="preserve">3.31048607826233</t>
@@ -899,7 +899,7 @@
     <t xml:space="preserve">3.18250322341919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29342174530029</t>
+    <t xml:space="preserve">3.29342126846313</t>
   </si>
   <si>
     <t xml:space="preserve">3.33710074424744</t>
@@ -57677,7 +57677,7 @@
     </row>
     <row r="2137">
       <c r="A2137" s="1" t="n">
-        <v>46078.6910532407</v>
+        <v>46078.3333333333</v>
       </c>
       <c r="B2137" t="n">
         <v>6468</v>
@@ -57698,6 +57698,32 @@
         <v>585</v>
       </c>
       <c r="H2137" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2138">
+      <c r="A2138" s="1" t="n">
+        <v>46079.6839351852</v>
+      </c>
+      <c r="B2138" t="n">
+        <v>4624</v>
+      </c>
+      <c r="C2138" t="n">
+        <v>3.79999995231628</v>
+      </c>
+      <c r="D2138" t="n">
+        <v>3.74000000953674</v>
+      </c>
+      <c r="E2138" t="n">
+        <v>3.74000000953674</v>
+      </c>
+      <c r="F2138" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="G2138" t="s">
+        <v>581</v>
+      </c>
+      <c r="H2138" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -47,7 +47,7 @@
     <t xml:space="preserve">2.96519923210144</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88901543617249</t>
+    <t xml:space="preserve">2.88901567459106</t>
   </si>
   <si>
     <t xml:space="preserve">2.98013734817505</t>
@@ -77,28 +77,28 @@
     <t xml:space="preserve">2.98611259460449</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03540825843811</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.056321144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05930876731873</t>
+    <t xml:space="preserve">3.03540802001953</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05632138252258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0593090057373</t>
   </si>
   <si>
     <t xml:space="preserve">3.05034613609314</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98760628700256</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95026135444641</t>
+    <t xml:space="preserve">2.98760652542114</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95026159286499</t>
   </si>
   <si>
     <t xml:space="preserve">3.01598882675171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01001358032227</t>
+    <t xml:space="preserve">3.01001334190369</t>
   </si>
   <si>
     <t xml:space="preserve">3.02495169639587</t>
@@ -107,28 +107,28 @@
     <t xml:space="preserve">3.0174822807312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03092646598816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99955654144287</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.04437136650085</t>
+    <t xml:space="preserve">3.03092670440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99955677986145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0443708896637</t>
   </si>
   <si>
     <t xml:space="preserve">2.959223985672</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00254464149475</t>
+    <t xml:space="preserve">3.00254440307617</t>
   </si>
   <si>
     <t xml:space="preserve">2.92785429954529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90843462944031</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89648461341858</t>
+    <t xml:space="preserve">2.90843486785889</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.896484375</t>
   </si>
   <si>
     <t xml:space="preserve">2.91889142990112</t>
@@ -143,19 +143,19 @@
     <t xml:space="preserve">2.90544700622559</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90992879867554</t>
+    <t xml:space="preserve">2.90992832183838</t>
   </si>
   <si>
     <t xml:space="preserve">2.92337274551392</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8382260799408</t>
+    <t xml:space="preserve">2.83822584152222</t>
   </si>
   <si>
     <t xml:space="preserve">2.86063313484192</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82627582550049</t>
+    <t xml:space="preserve">2.82627558708191</t>
   </si>
   <si>
     <t xml:space="preserve">2.77996754646301</t>
@@ -164,40 +164,40 @@
     <t xml:space="preserve">2.84569501876831</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86810207366943</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88303971290588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79639935493469</t>
+    <t xml:space="preserve">2.86810183525085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88304018974304</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79639959335327</t>
   </si>
   <si>
     <t xml:space="preserve">2.87557101249695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89797806739807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80088114738464</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74262285232544</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82179403305054</t>
+    <t xml:space="preserve">2.89797830581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80088090896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74262237548828</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82179427146912</t>
   </si>
   <si>
     <t xml:space="preserve">2.75009179115295</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76353549957275</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77847385406494</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78594303131104</t>
+    <t xml:space="preserve">2.76353573799133</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77847409248352</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78594279289246</t>
   </si>
   <si>
     <t xml:space="preserve">2.79341197013855</t>
@@ -206,13 +206,13 @@
     <t xml:space="preserve">2.69631481170654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6515007019043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62162470817566</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.53946542739868</t>
+    <t xml:space="preserve">2.65150046348572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62162446975708</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5394651889801</t>
   </si>
   <si>
     <t xml:space="preserve">2.56934142112732</t>
@@ -224,13 +224,13 @@
     <t xml:space="preserve">2.65896964073181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68884563446045</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70378351211548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77100491523743</t>
+    <t xml:space="preserve">2.68884539604187</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70378375053406</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77100467681885</t>
   </si>
   <si>
     <t xml:space="preserve">2.81581902503967</t>
@@ -239,10 +239,10 @@
     <t xml:space="preserve">2.7336597442627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66643905639648</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68137693405151</t>
+    <t xml:space="preserve">2.66643857955933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68137645721436</t>
   </si>
   <si>
     <t xml:space="preserve">2.74112892150879</t>
@@ -251,16 +251,16 @@
     <t xml:space="preserve">2.72619080543518</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83075714111328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.893150806427</t>
+    <t xml:space="preserve">2.8307569026947</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89315056800842</t>
   </si>
   <si>
     <t xml:space="preserve">2.69871854782104</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83870959281921</t>
+    <t xml:space="preserve">2.83870983123779</t>
   </si>
   <si>
     <t xml:space="preserve">2.93203711509705</t>
@@ -269,7 +269,7 @@
     <t xml:space="preserve">2.87759613990784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8309326171875</t>
+    <t xml:space="preserve">2.83093237876892</t>
   </si>
   <si>
     <t xml:space="preserve">2.81537771224976</t>
@@ -284,10 +284,10 @@
     <t xml:space="preserve">2.73760485649109</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76093697547913</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80760049819946</t>
+    <t xml:space="preserve">2.76093649864197</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80760073661804</t>
   </si>
   <si>
     <t xml:space="preserve">3.00980973243713</t>
@@ -302,7 +302,7 @@
     <t xml:space="preserve">2.88537335395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82315492630005</t>
+    <t xml:space="preserve">2.82315540313721</t>
   </si>
   <si>
     <t xml:space="preserve">2.86204147338867</t>
@@ -314,7 +314,7 @@
     <t xml:space="preserve">2.91648244857788</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85426449775696</t>
+    <t xml:space="preserve">2.85426425933838</t>
   </si>
   <si>
     <t xml:space="preserve">2.7298276424408</t>
@@ -323,10 +323,10 @@
     <t xml:space="preserve">2.68316411972046</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72205018997192</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75315976142883</t>
+    <t xml:space="preserve">2.7220504283905</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75315952301025</t>
   </si>
   <si>
     <t xml:space="preserve">2.70649576187134</t>
@@ -335,40 +335,40 @@
     <t xml:space="preserve">2.93981432914734</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99425554275513</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97870063781738</t>
+    <t xml:space="preserve">2.99425530433655</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97870111465454</t>
   </si>
   <si>
     <t xml:space="preserve">2.86981868743896</t>
   </si>
   <si>
-    <t xml:space="preserve">2.94759202003479</t>
+    <t xml:space="preserve">2.94759154319763</t>
   </si>
   <si>
     <t xml:space="preserve">2.98647809028625</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63650059700012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.550950050354</t>
+    <t xml:space="preserve">2.63650012016296</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55095028877258</t>
   </si>
   <si>
     <t xml:space="preserve">2.51984071731567</t>
   </si>
   <si>
-    <t xml:space="preserve">2.41095876693726</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34096312522888</t>
+    <t xml:space="preserve">2.41095900535583</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34096360206604</t>
   </si>
   <si>
     <t xml:space="preserve">2.34874057769775</t>
   </si>
   <si>
-    <t xml:space="preserve">2.36429500579834</t>
+    <t xml:space="preserve">2.36429524421692</t>
   </si>
   <si>
     <t xml:space="preserve">2.2554132938385</t>
@@ -377,10 +377,10 @@
     <t xml:space="preserve">2.24763584136963</t>
   </si>
   <si>
-    <t xml:space="preserve">2.32540893554688</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23208117485046</t>
+    <t xml:space="preserve">2.3254086971283</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23208093643188</t>
   </si>
   <si>
     <t xml:space="preserve">2.18541765213013</t>
@@ -389,37 +389,37 @@
     <t xml:space="preserve">2.27874517440796</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26319003105164</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2165265083313</t>
+    <t xml:space="preserve">2.26319026947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21652674674988</t>
   </si>
   <si>
     <t xml:space="preserve">2.06875824928284</t>
   </si>
   <si>
-    <t xml:space="preserve">2.1465311050415</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10764479637146</t>
+    <t xml:space="preserve">2.14653134346008</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10764455795288</t>
   </si>
   <si>
     <t xml:space="preserve">2.15430855751038</t>
   </si>
   <si>
-    <t xml:space="preserve">2.17764043807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22430396080017</t>
+    <t xml:space="preserve">2.17764019966125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22430372238159</t>
   </si>
   <si>
     <t xml:space="preserve">2.35651779174805</t>
   </si>
   <si>
-    <t xml:space="preserve">2.48873209953308</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52761793136597</t>
+    <t xml:space="preserve">2.48873162269592</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52761816978455</t>
   </si>
   <si>
     <t xml:space="preserve">2.43429064750671</t>
@@ -428,34 +428,34 @@
     <t xml:space="preserve">2.44206833839417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55872750282288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44984531402588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37207269668579</t>
+    <t xml:space="preserve">2.5587272644043</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44984555244446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37207221984863</t>
   </si>
   <si>
     <t xml:space="preserve">2.33318591117859</t>
   </si>
   <si>
-    <t xml:space="preserve">2.29429960250854</t>
+    <t xml:space="preserve">2.29429984092712</t>
   </si>
   <si>
     <t xml:space="preserve">2.3798496723175</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71427297592163</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.58205890655518</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62872314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65983200073242</t>
+    <t xml:space="preserve">2.71427321434021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.58205914497375</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62872290611267</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.659832239151</t>
   </si>
   <si>
     <t xml:space="preserve">2.57428193092346</t>
@@ -467,25 +467,25 @@
     <t xml:space="preserve">2.64427757263184</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69094133377075</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76871418952942</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90092825889587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96314597129822</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92425990104675</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97092342376709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01758766174316</t>
+    <t xml:space="preserve">2.69094109535217</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76871395111084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90092754364014</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9631462097168</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92426013946533</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97092366218567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01758742332458</t>
   </si>
   <si>
     <t xml:space="preserve">3.04869651794434</t>
@@ -494,13 +494,13 @@
     <t xml:space="preserve">3.03314185142517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0642511844635</t>
+    <t xml:space="preserve">3.06425094604492</t>
   </si>
   <si>
     <t xml:space="preserve">3.07980585098267</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0604989528656</t>
+    <t xml:space="preserve">3.06049919128418</t>
   </si>
   <si>
     <t xml:space="preserve">3.02811288833618</t>
@@ -509,7 +509,7 @@
     <t xml:space="preserve">3.01191973686218</t>
   </si>
   <si>
-    <t xml:space="preserve">3.1090784072876</t>
+    <t xml:space="preserve">3.10907816886902</t>
   </si>
   <si>
     <t xml:space="preserve">3.0928852558136</t>
@@ -518,10 +518,10 @@
     <t xml:space="preserve">3.12527132034302</t>
   </si>
   <si>
-    <t xml:space="preserve">3.07669186592102</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99572658538818</t>
+    <t xml:space="preserve">3.0766921043396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99572682380676</t>
   </si>
   <si>
     <t xml:space="preserve">3.30339574813843</t>
@@ -530,19 +530,19 @@
     <t xml:space="preserve">3.41674757003784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.35197496414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33578181266785</t>
+    <t xml:space="preserve">3.35197520256042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33578205108643</t>
   </si>
   <si>
     <t xml:space="preserve">3.36816811561584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23862338066101</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31958889961243</t>
+    <t xml:space="preserve">3.23862314224243</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31958866119385</t>
   </si>
   <si>
     <t xml:space="preserve">3.27100944519043</t>
@@ -554,7 +554,7 @@
     <t xml:space="preserve">3.22243022918701</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17385101318359</t>
+    <t xml:space="preserve">3.17385077476501</t>
   </si>
   <si>
     <t xml:space="preserve">3.20623731613159</t>
@@ -563,16 +563,16 @@
     <t xml:space="preserve">3.14146494865417</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40055441856384</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49771356582642</t>
+    <t xml:space="preserve">3.40055418014526</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49771332740784</t>
   </si>
   <si>
     <t xml:space="preserve">3.38436102867126</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25481653213501</t>
+    <t xml:space="preserve">3.25481629371643</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004416465759</t>
@@ -584,97 +584,97 @@
     <t xml:space="preserve">2.97953343391418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.80140924453735</t>
+    <t xml:space="preserve">2.80140900611877</t>
   </si>
   <si>
     <t xml:space="preserve">2.88237476348877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86618185043335</t>
+    <t xml:space="preserve">2.86618161201477</t>
   </si>
   <si>
     <t xml:space="preserve">2.84998846054077</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78521609306335</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75283002853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72044348716736</t>
+    <t xml:space="preserve">2.78521633148193</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75282979011536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72044372558594</t>
   </si>
   <si>
     <t xml:space="preserve">2.83379530906677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76902294158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73663687705994</t>
+    <t xml:space="preserve">2.76902318000793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73663663864136</t>
   </si>
   <si>
     <t xml:space="preserve">2.81760239601135</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89856791496277</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91476082801819</t>
+    <t xml:space="preserve">2.89856767654419</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91476106643677</t>
   </si>
   <si>
     <t xml:space="preserve">2.63947796821594</t>
   </si>
   <si>
-    <t xml:space="preserve">2.67186403274536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62328481674194</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68805718421936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70425057411194</t>
+    <t xml:space="preserve">2.67186427116394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62328505516052</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68805694580078</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70425033569336</t>
   </si>
   <si>
     <t xml:space="preserve">2.60709190368652</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5908989906311</t>
+    <t xml:space="preserve">2.59089851379395</t>
   </si>
   <si>
     <t xml:space="preserve">2.42896747589111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54231953620911</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.46135354042053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3156156539917</t>
+    <t xml:space="preserve">2.54231905937195</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.46135377883911</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.31561541557312</t>
   </si>
   <si>
     <t xml:space="preserve">2.29942274093628</t>
   </si>
   <si>
-    <t xml:space="preserve">2.35488152503967</t>
+    <t xml:space="preserve">2.35488176345825</t>
   </si>
   <si>
     <t xml:space="preserve">2.40607476234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28662419319153</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.13304495811462</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.08185219764709</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06478762626648</t>
+    <t xml:space="preserve">2.28662443161011</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1330451965332</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.08185195922852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.0647873878479</t>
   </si>
   <si>
     <t xml:space="preserve">2.03065896034241</t>
@@ -686,37 +686,37 @@
     <t xml:space="preserve">2.09891629219055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26956009864807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21836686134338</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32075309753418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55965423583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54258966445923</t>
+    <t xml:space="preserve">2.26955986022949</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2183666229248</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32075333595276</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55965399742126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54258990287781</t>
   </si>
   <si>
     <t xml:space="preserve">2.45726799964905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5767183303833</t>
+    <t xml:space="preserve">2.57671856880188</t>
   </si>
   <si>
     <t xml:space="preserve">2.62791132926941</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61084723472595</t>
+    <t xml:space="preserve">2.61084699630737</t>
   </si>
   <si>
     <t xml:space="preserve">2.64497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59378266334534</t>
+    <t xml:space="preserve">2.59378290176392</t>
   </si>
   <si>
     <t xml:space="preserve">2.69616913795471</t>
@@ -731,16 +731,16 @@
     <t xml:space="preserve">2.4231390953064</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4743320941925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15010929107666</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33781719207764</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30368852615356</t>
+    <t xml:space="preserve">2.47433233261108</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15010952949524</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33781743049622</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30368876457214</t>
   </si>
   <si>
     <t xml:space="preserve">2.25249552726746</t>
@@ -749,7 +749,7 @@
     <t xml:space="preserve">2.23543095588684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.37194633483887</t>
+    <t xml:space="preserve">2.37194609642029</t>
   </si>
   <si>
     <t xml:space="preserve">2.38901042938232</t>
@@ -761,70 +761,70 @@
     <t xml:space="preserve">2.18423795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01359415054321</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04772329330444</t>
+    <t xml:space="preserve">2.01359438896179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04772305488586</t>
   </si>
   <si>
     <t xml:space="preserve">2.11598062515259</t>
   </si>
   <si>
-    <t xml:space="preserve">1.91120839118958</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.8770797252655</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84295094013214</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97946572303772</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86001527309418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.94533681869507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96240139007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99652981758118</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81561923027039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9009416103363</t>
+    <t xml:space="preserve">1.91120851039886</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87707960605621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84295105934143</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97946584224701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86001539230347</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.94533693790436</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96240150928497</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99652993679047</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81561946868896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90094137191772</t>
   </si>
   <si>
     <t xml:space="preserve">2.88387703895569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76442623138428</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73029780387878</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.6791045665741</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74736213684082</t>
+    <t xml:space="preserve">2.76442646980286</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73029756546021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67910432815552</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74736189842224</t>
   </si>
   <si>
     <t xml:space="preserve">2.83268356323242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86681246757507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79855513572693</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78149080276489</t>
+    <t xml:space="preserve">2.86681222915649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79855489730835</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78149056434631</t>
   </si>
   <si>
     <t xml:space="preserve">2.9350700378418</t>
@@ -833,43 +833,43 @@
     <t xml:space="preserve">2.96919870376587</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02039194107056</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.00332713127136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03745627403259</t>
+    <t xml:space="preserve">3.02039170265198</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.00332736968994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03745603561401</t>
   </si>
   <si>
     <t xml:space="preserve">2.98626303672791</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05452036857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07158470153809</t>
+    <t xml:space="preserve">3.05452013015747</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07158493995667</t>
   </si>
   <si>
     <t xml:space="preserve">3.13984251022339</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11424565315247</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1313099861145</t>
+    <t xml:space="preserve">3.11424589157104</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13131022453308</t>
   </si>
   <si>
     <t xml:space="preserve">3.06305241584778</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16543865203857</t>
+    <t xml:space="preserve">3.16543889045715</t>
   </si>
   <si>
     <t xml:space="preserve">3.19956755638123</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15690660476685</t>
+    <t xml:space="preserve">3.15690684318542</t>
   </si>
   <si>
     <t xml:space="preserve">3.2336962223053</t>
@@ -887,28 +887,28 @@
     <t xml:space="preserve">3.31048607826233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3446147441864</t>
+    <t xml:space="preserve">3.34461450576782</t>
   </si>
   <si>
     <t xml:space="preserve">3.32755041122437</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28488922119141</t>
+    <t xml:space="preserve">3.28488945960999</t>
   </si>
   <si>
     <t xml:space="preserve">3.18250322341919</t>
   </si>
   <si>
-    <t xml:space="preserve">3.29342126846313</t>
+    <t xml:space="preserve">3.29342150688171</t>
   </si>
   <si>
     <t xml:space="preserve">3.33710074424744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32836508750916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29342150688171</t>
+    <t xml:space="preserve">3.32836484909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29342174530029</t>
   </si>
   <si>
     <t xml:space="preserve">3.24974226951599</t>
@@ -917,13 +917,13 @@
     <t xml:space="preserve">3.20606303215027</t>
   </si>
   <si>
-    <t xml:space="preserve">3.15364742279053</t>
+    <t xml:space="preserve">3.15364766120911</t>
   </si>
   <si>
     <t xml:space="preserve">3.21479892730713</t>
   </si>
   <si>
-    <t xml:space="preserve">3.17111945152283</t>
+    <t xml:space="preserve">3.17111968994141</t>
   </si>
   <si>
     <t xml:space="preserve">3.26721405982971</t>
@@ -932,10 +932,10 @@
     <t xml:space="preserve">3.36330842971802</t>
   </si>
   <si>
-    <t xml:space="preserve">3.49434661865234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.58170485496521</t>
+    <t xml:space="preserve">3.49434638023376</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.58170509338379</t>
   </si>
   <si>
     <t xml:space="preserve">3.56423354148865</t>
@@ -950,16 +950,16 @@
     <t xml:space="preserve">3.51181817054749</t>
   </si>
   <si>
-    <t xml:space="preserve">3.54676175117493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63412022590637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62538456916809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7476863861084</t>
+    <t xml:space="preserve">3.54676151275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63412046432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62538480758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74768662452698</t>
   </si>
   <si>
     <t xml:space="preserve">3.69527125358582</t>
@@ -968,16 +968,16 @@
     <t xml:space="preserve">3.66906356811523</t>
   </si>
   <si>
-    <t xml:space="preserve">3.60791277885437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55549788475037</t>
+    <t xml:space="preserve">3.60791301727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55549764633179</t>
   </si>
   <si>
     <t xml:space="preserve">3.66032791137695</t>
   </si>
   <si>
-    <t xml:space="preserve">3.65159201622009</t>
+    <t xml:space="preserve">3.65159177780151</t>
   </si>
   <si>
     <t xml:space="preserve">3.68653535842896</t>
@@ -986,25 +986,25 @@
     <t xml:space="preserve">3.70400714874268</t>
   </si>
   <si>
-    <t xml:space="preserve">3.75642275810242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.57296943664551</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.53802609443665</t>
+    <t xml:space="preserve">3.75642251968384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.57296967506409</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.53802585601807</t>
   </si>
   <si>
     <t xml:space="preserve">3.3458366394043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.3895161151886</t>
+    <t xml:space="preserve">3.38951635360718</t>
   </si>
   <si>
     <t xml:space="preserve">3.42445969581604</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45066714286804</t>
+    <t xml:space="preserve">3.45066738128662</t>
   </si>
   <si>
     <t xml:space="preserve">3.44193148612976</t>
@@ -1019,25 +1019,25 @@
     <t xml:space="preserve">3.35457253456116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4594030380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52928996086121</t>
+    <t xml:space="preserve">3.45940327644348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52928972244263</t>
   </si>
   <si>
     <t xml:space="preserve">3.46813893318176</t>
   </si>
   <si>
-    <t xml:space="preserve">3.47687482833862</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.79136610031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72147917747498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87872457504272</t>
+    <t xml:space="preserve">3.47687458992004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.79136633872986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7214789390564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8787248134613</t>
   </si>
   <si>
     <t xml:space="preserve">4.17574453353882</t>
@@ -1049,37 +1049,37 @@
     <t xml:space="preserve">4.35046148300171</t>
   </si>
   <si>
-    <t xml:space="preserve">4.1844801902771</t>
+    <t xml:space="preserve">4.18447971343994</t>
   </si>
   <si>
     <t xml:space="preserve">4.20195150375366</t>
   </si>
   <si>
-    <t xml:space="preserve">4.25436639785767</t>
+    <t xml:space="preserve">4.25436687469482</t>
   </si>
   <si>
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493226051331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98355507850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94861149787903</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93113970756531</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.08838558197021</t>
+    <t xml:space="preserve">3.90493202209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98355484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94861197471619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93114018440247</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.08838510513306</t>
   </si>
   <si>
     <t xml:space="preserve">4.07091331481934</t>
   </si>
   <si>
-    <t xml:space="preserve">4.12332916259766</t>
+    <t xml:space="preserve">4.1233286857605</t>
   </si>
   <si>
     <t xml:space="preserve">4.00102663040161</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">4.00976276397705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93987584114075</t>
+    <t xml:space="preserve">3.93987607955933</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
@@ -1100,16 +1100,16 @@
     <t xml:space="preserve">4.29804611206055</t>
   </si>
   <si>
-    <t xml:space="preserve">4.28930997848511</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.21942377090454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.19321632385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14953660964966</t>
+    <t xml:space="preserve">4.28931045532227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.21942329406738</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.19321584701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1495361328125</t>
   </si>
   <si>
     <t xml:space="preserve">4.16700792312622</t>
@@ -1118,7 +1118,7 @@
     <t xml:space="preserve">4.11459302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06217765808105</t>
+    <t xml:space="preserve">4.06217813491821</t>
   </si>
   <si>
     <t xml:space="preserve">3.78262996673584</t>
@@ -1127,22 +1127,22 @@
     <t xml:space="preserve">3.80010175704956</t>
   </si>
   <si>
-    <t xml:space="preserve">3.82630944252014</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.83504557609558</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84378147125244</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.77389430999756</t>
+    <t xml:space="preserve">3.82630968093872</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.83504509925842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84378099441528</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.77389454841614</t>
   </si>
   <si>
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734739303589</t>
+    <t xml:space="preserve">3.95734786987305</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
@@ -1151,22 +1151,22 @@
     <t xml:space="preserve">3.86125302314758</t>
   </si>
   <si>
-    <t xml:space="preserve">3.76515817642212</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.81757354736328</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.64285635948181</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.67779946327209</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7389509677887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85251712799072</t>
+    <t xml:space="preserve">3.76515865325928</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8175733089447</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.64285612106323</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.67779970169067</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.73895072937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85251665115356</t>
   </si>
   <si>
     <t xml:space="preserve">3.71274304389954</t>
@@ -1175,7 +1175,7 @@
     <t xml:space="preserve">3.92240381240845</t>
   </si>
   <si>
-    <t xml:space="preserve">3.61664843559265</t>
+    <t xml:space="preserve">3.61664867401123</t>
   </si>
   <si>
     <t xml:space="preserve">3.39825224876404</t>
@@ -1184,16 +1184,16 @@
     <t xml:space="preserve">3.23227071762085</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05755305290222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97019481658936</t>
+    <t xml:space="preserve">3.0575532913208</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97019457817078</t>
   </si>
   <si>
     <t xml:space="preserve">2.95272302627563</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91777944564819</t>
+    <t xml:space="preserve">2.91777920722961</t>
   </si>
   <si>
     <t xml:space="preserve">2.90904331207275</t>
@@ -1211,10 +1211,10 @@
     <t xml:space="preserve">3.31962895393372</t>
   </si>
   <si>
-    <t xml:space="preserve">3.27595019340515</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28468561172485</t>
+    <t xml:space="preserve">3.27594995498657</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28468585014343</t>
   </si>
   <si>
     <t xml:space="preserve">3.50245499610901</t>
@@ -1250,7 +1250,7 @@
     <t xml:space="preserve">3.32098078727722</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26653814315796</t>
+    <t xml:space="preserve">3.26653838157654</t>
   </si>
   <si>
     <t xml:space="preserve">3.39357042312622</t>
@@ -1259,7 +1259,7 @@
     <t xml:space="preserve">3.23024344444275</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19394874572754</t>
+    <t xml:space="preserve">3.19394850730896</t>
   </si>
   <si>
     <t xml:space="preserve">3.25746440887451</t>
@@ -1274,7 +1274,7 @@
     <t xml:space="preserve">3.2211697101593</t>
   </si>
   <si>
-    <t xml:space="preserve">3.10321140289307</t>
+    <t xml:space="preserve">3.10321164131165</t>
   </si>
   <si>
     <t xml:space="preserve">2.99432682991028</t>
@@ -1286,13 +1286,13 @@
     <t xml:space="preserve">2.95803189277649</t>
   </si>
   <si>
-    <t xml:space="preserve">2.85822105407715</t>
+    <t xml:space="preserve">2.85822129249573</t>
   </si>
   <si>
     <t xml:space="preserve">2.89451599121094</t>
   </si>
   <si>
-    <t xml:space="preserve">2.8672947883606</t>
+    <t xml:space="preserve">2.86729502677917</t>
   </si>
   <si>
     <t xml:space="preserve">2.81285238265991</t>
@@ -1304,7 +1304,7 @@
     <t xml:space="preserve">2.75841021537781</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70396780967712</t>
+    <t xml:space="preserve">2.7039680480957</t>
   </si>
   <si>
     <t xml:space="preserve">2.72211527824402</t>
@@ -1313,16 +1313,16 @@
     <t xml:space="preserve">2.64952564239502</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7947051525116</t>
+    <t xml:space="preserve">2.79470491409302</t>
   </si>
   <si>
     <t xml:space="preserve">2.92173719406128</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05784273147583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02154803276062</t>
+    <t xml:space="preserve">3.05784296989441</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02154779434204</t>
   </si>
   <si>
     <t xml:space="preserve">3.13950634002686</t>
@@ -1352,46 +1352,46 @@
     <t xml:space="preserve">3.08506417274475</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01247429847717</t>
+    <t xml:space="preserve">3.01247406005859</t>
   </si>
   <si>
     <t xml:space="preserve">2.88544225692749</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7765576839447</t>
+    <t xml:space="preserve">2.77655744552612</t>
   </si>
   <si>
     <t xml:space="preserve">2.71304154396057</t>
   </si>
   <si>
-    <t xml:space="preserve">2.6313784122467</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68582034111023</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.66767287254333</t>
+    <t xml:space="preserve">2.63137817382812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68582057952881</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.66767311096191</t>
   </si>
   <si>
     <t xml:space="preserve">2.55878829956055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52249336242676</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67674660682678</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.64045214653015</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87636852264404</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83099985122681</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60415697097778</t>
+    <t xml:space="preserve">2.52249360084534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67674684524536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.64045190811157</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87636876106262</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83099961280823</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6041567325592</t>
   </si>
   <si>
     <t xml:space="preserve">2.73118901252747</t>
@@ -1418,7 +1418,7 @@
     <t xml:space="preserve">2.91266345977783</t>
   </si>
   <si>
-    <t xml:space="preserve">3.12135887145996</t>
+    <t xml:space="preserve">3.12135910987854</t>
   </si>
   <si>
     <t xml:space="preserve">3.0759904384613</t>
@@ -1427,46 +1427,46 @@
     <t xml:space="preserve">3.0941379070282</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38449692726135</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.41171765327454</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.37542319297791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.42079138755798</t>
+    <t xml:space="preserve">3.38449668884277</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.41171789169312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.37542295455933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.42079162597656</t>
   </si>
   <si>
     <t xml:space="preserve">3.43893885612488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.36634945869446</t>
+    <t xml:space="preserve">3.36634922027588</t>
   </si>
   <si>
     <t xml:space="preserve">3.35727572441101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20302248001099</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.27561187744141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29375958442688</t>
+    <t xml:space="preserve">3.20302224159241</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.27561211585999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29375982284546</t>
   </si>
   <si>
     <t xml:space="preserve">3.1667275428772</t>
   </si>
   <si>
-    <t xml:space="preserve">3.11228513717651</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78563141822815</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84007382392883</t>
+    <t xml:space="preserve">3.11228537559509</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78563117980957</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84007358551025</t>
   </si>
   <si>
     <t xml:space="preserve">2.82192611694336</t>
@@ -57703,7 +57703,7 @@
     </row>
     <row r="2138">
       <c r="A2138" s="1" t="n">
-        <v>46079.6839351852</v>
+        <v>46079.3333333333</v>
       </c>
       <c r="B2138" t="n">
         <v>4624</v>
@@ -57724,6 +57724,32 @@
         <v>581</v>
       </c>
       <c r="H2138" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2139">
+      <c r="A2139" s="1" t="n">
+        <v>46080.6912847222</v>
+      </c>
+      <c r="B2139" t="n">
+        <v>4519</v>
+      </c>
+      <c r="C2139" t="n">
+        <v>3.79999995231628</v>
+      </c>
+      <c r="D2139" t="n">
+        <v>3.72000002861023</v>
+      </c>
+      <c r="E2139" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="F2139" t="n">
+        <v>3.75999999046326</v>
+      </c>
+      <c r="G2139" t="s">
+        <v>581</v>
+      </c>
+      <c r="H2139" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -44,10 +44,10 @@
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519923210144</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88901567459106</t>
+    <t xml:space="preserve">2.96519947052002</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88901543617249</t>
   </si>
   <si>
     <t xml:space="preserve">2.98013734817505</t>
@@ -59,10 +59,10 @@
     <t xml:space="preserve">2.94578003883362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9577305316925</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.96221160888672</t>
+    <t xml:space="preserve">2.95773005485535</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9622118473053</t>
   </si>
   <si>
     <t xml:space="preserve">2.93532347679138</t>
@@ -74,28 +74,28 @@
     <t xml:space="preserve">2.97864365577698</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98611259460449</t>
+    <t xml:space="preserve">2.98611235618591</t>
   </si>
   <si>
     <t xml:space="preserve">3.03540802001953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05632138252258</t>
+    <t xml:space="preserve">3.056321144104</t>
   </si>
   <si>
     <t xml:space="preserve">3.0593090057373</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05034613609314</t>
+    <t xml:space="preserve">3.05034637451172</t>
   </si>
   <si>
     <t xml:space="preserve">2.98760652542114</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95026159286499</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01598882675171</t>
+    <t xml:space="preserve">2.95026135444641</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01598858833313</t>
   </si>
   <si>
     <t xml:space="preserve">3.01001334190369</t>
@@ -107,16 +107,16 @@
     <t xml:space="preserve">3.0174822807312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03092670440674</t>
+    <t xml:space="preserve">3.03092646598816</t>
   </si>
   <si>
     <t xml:space="preserve">2.99955677986145</t>
   </si>
   <si>
-    <t xml:space="preserve">3.0443708896637</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.959223985672</t>
+    <t xml:space="preserve">3.04437112808228</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95922374725342</t>
   </si>
   <si>
     <t xml:space="preserve">3.00254440307617</t>
@@ -125,7 +125,7 @@
     <t xml:space="preserve">2.92785429954529</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90843486785889</t>
+    <t xml:space="preserve">2.90843462944031</t>
   </si>
   <si>
     <t xml:space="preserve">2.896484375</t>
@@ -134,70 +134,70 @@
     <t xml:space="preserve">2.91889142990112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9159038066864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92038512229919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90544700622559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90992832183838</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92337274551392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.83822584152222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86063313484192</t>
+    <t xml:space="preserve">2.91590356826782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92038536071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90544724464417</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90992856025696</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9233729839325</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.8382260799408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86063289642334</t>
   </si>
   <si>
     <t xml:space="preserve">2.82627558708191</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77996754646301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.84569501876831</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86810183525085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88304018974304</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79639959335327</t>
+    <t xml:space="preserve">2.77996730804443</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.84569478034973</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86810207366943</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88303995132446</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79639935493469</t>
   </si>
   <si>
     <t xml:space="preserve">2.87557101249695</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89797830581665</t>
+    <t xml:space="preserve">2.89797806739807</t>
   </si>
   <si>
     <t xml:space="preserve">2.80088090896606</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74262237548828</t>
+    <t xml:space="preserve">2.74262261390686</t>
   </si>
   <si>
     <t xml:space="preserve">2.82179427146912</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75009179115295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76353573799133</t>
+    <t xml:space="preserve">2.75009155273438</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76353549957275</t>
   </si>
   <si>
     <t xml:space="preserve">2.77847409248352</t>
   </si>
   <si>
-    <t xml:space="preserve">2.78594279289246</t>
+    <t xml:space="preserve">2.78594303131104</t>
   </si>
   <si>
     <t xml:space="preserve">2.79341197013855</t>
@@ -206,16 +206,16 @@
     <t xml:space="preserve">2.69631481170654</t>
   </si>
   <si>
-    <t xml:space="preserve">2.65150046348572</t>
+    <t xml:space="preserve">2.6515007019043</t>
   </si>
   <si>
     <t xml:space="preserve">2.62162446975708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5394651889801</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.56934142112732</t>
+    <t xml:space="preserve">2.53946542739868</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.5693416595459</t>
   </si>
   <si>
     <t xml:space="preserve">2.61415553092957</t>
@@ -224,13 +224,13 @@
     <t xml:space="preserve">2.65896964073181</t>
   </si>
   <si>
-    <t xml:space="preserve">2.68884539604187</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70378375053406</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77100467681885</t>
+    <t xml:space="preserve">2.68884563446045</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70378351211548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77100491523743</t>
   </si>
   <si>
     <t xml:space="preserve">2.81581902503967</t>
@@ -245,19 +245,19 @@
     <t xml:space="preserve">2.68137645721436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.74112892150879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72619080543518</t>
+    <t xml:space="preserve">2.74112868309021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72619128227234</t>
   </si>
   <si>
     <t xml:space="preserve">2.8307569026947</t>
   </si>
   <si>
-    <t xml:space="preserve">2.89315056800842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69871854782104</t>
+    <t xml:space="preserve">2.893150806427</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69871830940247</t>
   </si>
   <si>
     <t xml:space="preserve">2.83870983123779</t>
@@ -269,61 +269,61 @@
     <t xml:space="preserve">2.87759613990784</t>
   </si>
   <si>
-    <t xml:space="preserve">2.83093237876892</t>
+    <t xml:space="preserve">2.8309326171875</t>
   </si>
   <si>
     <t xml:space="preserve">2.81537771224976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84648680686951</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79982304573059</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73760485649109</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76093649864197</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80760073661804</t>
+    <t xml:space="preserve">2.84648728370667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79982328414917</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73760461807251</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76093673706055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80760049819946</t>
   </si>
   <si>
     <t xml:space="preserve">3.00980973243713</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95536875724792</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90870523452759</t>
+    <t xml:space="preserve">2.9553689956665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90870547294617</t>
   </si>
   <si>
     <t xml:space="preserve">2.88537335395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82315540313721</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86204147338867</t>
+    <t xml:space="preserve">2.82315516471863</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86204171180725</t>
   </si>
   <si>
     <t xml:space="preserve">3.00203251838684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91648244857788</t>
+    <t xml:space="preserve">2.91648268699646</t>
   </si>
   <si>
     <t xml:space="preserve">2.85426425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.7298276424408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68316411972046</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.7220504283905</t>
+    <t xml:space="preserve">2.72982740402222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68316388130188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72205018997192</t>
   </si>
   <si>
     <t xml:space="preserve">2.75315952301025</t>
@@ -332,13 +332,13 @@
     <t xml:space="preserve">2.70649576187134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93981432914734</t>
+    <t xml:space="preserve">2.93981456756592</t>
   </si>
   <si>
     <t xml:space="preserve">2.99425530433655</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97870111465454</t>
+    <t xml:space="preserve">2.97870063781738</t>
   </si>
   <si>
     <t xml:space="preserve">2.86981868743896</t>
@@ -353,22 +353,22 @@
     <t xml:space="preserve">2.63650012016296</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55095028877258</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.51984071731567</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41095900535583</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34096360206604</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.34874057769775</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.36429524421692</t>
+    <t xml:space="preserve">2.550950050354</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.51984095573425</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41095876693726</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34096336364746</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.34874081611633</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3642954826355</t>
   </si>
   <si>
     <t xml:space="preserve">2.2554132938385</t>
@@ -380,85 +380,85 @@
     <t xml:space="preserve">2.3254086971283</t>
   </si>
   <si>
-    <t xml:space="preserve">2.23208093643188</t>
+    <t xml:space="preserve">2.23208117485046</t>
   </si>
   <si>
     <t xml:space="preserve">2.18541765213013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27874517440796</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26319026947021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.21652674674988</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06875824928284</t>
+    <t xml:space="preserve">2.27874493598938</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26319050788879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2165265083313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06875848770142</t>
   </si>
   <si>
     <t xml:space="preserve">2.14653134346008</t>
   </si>
   <si>
-    <t xml:space="preserve">2.10764455795288</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15430855751038</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17764019966125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22430372238159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35651779174805</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.48873162269592</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.52761816978455</t>
+    <t xml:space="preserve">2.10764503479004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.15430879592896</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17764043807983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22430396080017</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35651803016663</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.4887318611145</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.52761793136597</t>
   </si>
   <si>
     <t xml:space="preserve">2.43429064750671</t>
   </si>
   <si>
-    <t xml:space="preserve">2.44206833839417</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5587272644043</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44984555244446</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37207221984863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.33318591117859</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29429984092712</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.3798496723175</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71427321434021</t>
+    <t xml:space="preserve">2.44206809997559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55872702598572</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44984531402588</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37207245826721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.33318614959717</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29429936408997</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.37984991073608</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71427273750305</t>
   </si>
   <si>
     <t xml:space="preserve">2.58205914497375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62872290611267</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.659832239151</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57428193092346</t>
+    <t xml:space="preserve">2.62872314453125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.65983200073242</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57428169250488</t>
   </si>
   <si>
     <t xml:space="preserve">2.67538666725159</t>
@@ -473,13 +473,13 @@
     <t xml:space="preserve">2.76871395111084</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90092754364014</t>
+    <t xml:space="preserve">2.90092802047729</t>
   </si>
   <si>
     <t xml:space="preserve">2.9631462097168</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92426013946533</t>
+    <t xml:space="preserve">2.92425990104675</t>
   </si>
   <si>
     <t xml:space="preserve">2.97092366218567</t>
@@ -488,28 +488,28 @@
     <t xml:space="preserve">3.01758742332458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04869651794434</t>
+    <t xml:space="preserve">3.04869675636292</t>
   </si>
   <si>
     <t xml:space="preserve">3.03314185142517</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06425094604492</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07980585098267</t>
+    <t xml:space="preserve">3.0642511844635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07980561256409</t>
   </si>
   <si>
     <t xml:space="preserve">3.06049919128418</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02811288833618</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01191973686218</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.10907816886902</t>
+    <t xml:space="preserve">3.02811312675476</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01191997528076</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1090784072876</t>
   </si>
   <si>
     <t xml:space="preserve">3.0928852558136</t>
@@ -521,16 +521,16 @@
     <t xml:space="preserve">3.0766921043396</t>
   </si>
   <si>
-    <t xml:space="preserve">2.99572682380676</t>
+    <t xml:space="preserve">2.99572658538818</t>
   </si>
   <si>
     <t xml:space="preserve">3.30339574813843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41674757003784</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35197520256042</t>
+    <t xml:space="preserve">3.41674733161926</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35197496414185</t>
   </si>
   <si>
     <t xml:space="preserve">3.33578205108643</t>
@@ -539,10 +539,10 @@
     <t xml:space="preserve">3.36816811561584</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23862314224243</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.31958866119385</t>
+    <t xml:space="preserve">3.23862338066101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.31958889961243</t>
   </si>
   <si>
     <t xml:space="preserve">3.27100944519043</t>
@@ -551,16 +551,16 @@
     <t xml:space="preserve">3.28720259666443</t>
   </si>
   <si>
-    <t xml:space="preserve">3.22243022918701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.17385077476501</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.20623731613159</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.14146494865417</t>
+    <t xml:space="preserve">3.22243046760559</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.17385101318359</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.20623707771301</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.1414647102356</t>
   </si>
   <si>
     <t xml:space="preserve">3.40055418014526</t>
@@ -569,91 +569,91 @@
     <t xml:space="preserve">3.49771332740784</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38436102867126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.25481629371643</t>
+    <t xml:space="preserve">3.38436126708984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.25481653213501</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004416465759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96334028244019</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97953343391418</t>
+    <t xml:space="preserve">2.96334052085876</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97953367233276</t>
   </si>
   <si>
     <t xml:space="preserve">2.80140900611877</t>
   </si>
   <si>
-    <t xml:space="preserve">2.88237476348877</t>
+    <t xml:space="preserve">2.88237452507019</t>
   </si>
   <si>
     <t xml:space="preserve">2.86618161201477</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84998846054077</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.78521633148193</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75282979011536</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72044372558594</t>
+    <t xml:space="preserve">2.84998822212219</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.78521609306335</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75283002853394</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72044348716736</t>
   </si>
   <si>
     <t xml:space="preserve">2.83379530906677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76902318000793</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73663663864136</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81760239601135</t>
+    <t xml:space="preserve">2.76902294158936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73663687705994</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81760215759277</t>
   </si>
   <si>
     <t xml:space="preserve">2.89856767654419</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91476106643677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63947796821594</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67186427116394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62328505516052</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68805694580078</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.70425033569336</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.60709190368652</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.59089851379395</t>
+    <t xml:space="preserve">2.91476082801819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63947772979736</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.67186403274536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62328481674194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68805718421936</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.70425057411194</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.60709166526794</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.59089875221252</t>
   </si>
   <si>
     <t xml:space="preserve">2.42896747589111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54231905937195</t>
+    <t xml:space="preserve">2.54231929779053</t>
   </si>
   <si>
     <t xml:space="preserve">2.46135377883911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.31561541557312</t>
+    <t xml:space="preserve">2.3156156539917</t>
   </si>
   <si>
     <t xml:space="preserve">2.29942274093628</t>
@@ -665,19 +665,19 @@
     <t xml:space="preserve">2.40607476234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28662443161011</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.1330451965332</t>
+    <t xml:space="preserve">2.28662419319153</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.13304495811462</t>
   </si>
   <si>
     <t xml:space="preserve">2.08185195922852</t>
   </si>
   <si>
-    <t xml:space="preserve">2.0647873878479</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.03065896034241</t>
+    <t xml:space="preserve">2.06478762626648</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.03065872192383</t>
   </si>
   <si>
     <t xml:space="preserve">2.1671736240387</t>
@@ -686,28 +686,28 @@
     <t xml:space="preserve">2.09891629219055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26955986022949</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2183666229248</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.32075333595276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55965399742126</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54258990287781</t>
+    <t xml:space="preserve">2.26956009864807</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21836686134338</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.32075309753418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55965423583984</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54258966445923</t>
   </si>
   <si>
     <t xml:space="preserve">2.45726799964905</t>
   </si>
   <si>
-    <t xml:space="preserve">2.57671856880188</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62791132926941</t>
+    <t xml:space="preserve">2.5767183303833</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62791156768799</t>
   </si>
   <si>
     <t xml:space="preserve">2.61084699630737</t>
@@ -722,19 +722,19 @@
     <t xml:space="preserve">2.69616913795471</t>
   </si>
   <si>
-    <t xml:space="preserve">2.71323323249817</t>
+    <t xml:space="preserve">2.71323347091675</t>
   </si>
   <si>
     <t xml:space="preserve">2.44020342826843</t>
   </si>
   <si>
-    <t xml:space="preserve">2.4231390953064</t>
+    <t xml:space="preserve">2.42313933372498</t>
   </si>
   <si>
     <t xml:space="preserve">2.47433233261108</t>
   </si>
   <si>
-    <t xml:space="preserve">2.15010952949524</t>
+    <t xml:space="preserve">2.15010929107666</t>
   </si>
   <si>
     <t xml:space="preserve">2.33781743049622</t>
@@ -743,10 +743,10 @@
     <t xml:space="preserve">2.30368876457214</t>
   </si>
   <si>
-    <t xml:space="preserve">2.25249552726746</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.23543095588684</t>
+    <t xml:space="preserve">2.25249576568604</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.23543119430542</t>
   </si>
   <si>
     <t xml:space="preserve">2.37194609642029</t>
@@ -761,40 +761,40 @@
     <t xml:space="preserve">2.18423795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01359438896179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.04772305488586</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.11598062515259</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91120851039886</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.87707960605621</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.84295105934143</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.97946584224701</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.86001539230347</t>
+    <t xml:space="preserve">2.01359415054321</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.04772329330444</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.11598038673401</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91120827198029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.87707984447479</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.84295094013214</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.97946560382843</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.86001515388489</t>
   </si>
   <si>
     <t xml:space="preserve">1.94533693790436</t>
   </si>
   <si>
-    <t xml:space="preserve">1.96240150928497</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99652993679047</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81561946868896</t>
+    <t xml:space="preserve">1.96240139007568</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99653005599976</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81561923027039</t>
   </si>
   <si>
     <t xml:space="preserve">2.90094137191772</t>
@@ -806,10 +806,10 @@
     <t xml:space="preserve">2.76442646980286</t>
   </si>
   <si>
-    <t xml:space="preserve">2.73029756546021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.67910432815552</t>
+    <t xml:space="preserve">2.73029780387878</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.6791045665741</t>
   </si>
   <si>
     <t xml:space="preserve">2.74736189842224</t>
@@ -818,10 +818,10 @@
     <t xml:space="preserve">2.83268356323242</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86681222915649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79855489730835</t>
+    <t xml:space="preserve">2.86681246757507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79855513572693</t>
   </si>
   <si>
     <t xml:space="preserve">2.78149056434631</t>
@@ -836,16 +836,16 @@
     <t xml:space="preserve">3.02039170265198</t>
   </si>
   <si>
-    <t xml:space="preserve">3.00332736968994</t>
+    <t xml:space="preserve">3.00332713127136</t>
   </si>
   <si>
     <t xml:space="preserve">3.03745603561401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98626303672791</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05452013015747</t>
+    <t xml:space="preserve">2.98626279830933</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05452036857605</t>
   </si>
   <si>
     <t xml:space="preserve">3.07158493995667</t>
@@ -860,16 +860,16 @@
     <t xml:space="preserve">3.13131022453308</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06305241584778</t>
+    <t xml:space="preserve">3.06305265426636</t>
   </si>
   <si>
     <t xml:space="preserve">3.16543889045715</t>
   </si>
   <si>
-    <t xml:space="preserve">3.19956755638123</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15690684318542</t>
+    <t xml:space="preserve">3.1995677947998</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15690660476685</t>
   </si>
   <si>
     <t xml:space="preserve">3.2336962223053</t>
@@ -878,7 +878,7 @@
     <t xml:space="preserve">3.27635717391968</t>
   </si>
   <si>
-    <t xml:space="preserve">3.24222826957703</t>
+    <t xml:space="preserve">3.24222850799561</t>
   </si>
   <si>
     <t xml:space="preserve">3.26782488822937</t>
@@ -887,34 +887,34 @@
     <t xml:space="preserve">3.31048607826233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34461450576782</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32755041122437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28488945960999</t>
+    <t xml:space="preserve">3.34461498260498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32755017280579</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28488922119141</t>
   </si>
   <si>
     <t xml:space="preserve">3.18250322341919</t>
   </si>
   <si>
+    <t xml:space="preserve">3.29342126846313</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33710074424744</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32836508750916</t>
+  </si>
+  <si>
     <t xml:space="preserve">3.29342150688171</t>
   </si>
   <si>
-    <t xml:space="preserve">3.33710074424744</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32836484909058</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29342174530029</t>
-  </si>
-  <si>
     <t xml:space="preserve">3.24974226951599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20606303215027</t>
+    <t xml:space="preserve">3.20606279373169</t>
   </si>
   <si>
     <t xml:space="preserve">3.15364766120911</t>
@@ -926,7 +926,7 @@
     <t xml:space="preserve">3.17111968994141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26721405982971</t>
+    <t xml:space="preserve">3.26721382141113</t>
   </si>
   <si>
     <t xml:space="preserve">3.36330842971802</t>
@@ -935,55 +935,55 @@
     <t xml:space="preserve">3.49434638023376</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58170509338379</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56423354148865</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59044122695923</t>
+    <t xml:space="preserve">3.58170533180237</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56423330307007</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59044098854065</t>
   </si>
   <si>
     <t xml:space="preserve">3.5030825138092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51181817054749</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54676151275635</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63412046432495</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62538480758667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.74768662452698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69527125358582</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66906356811523</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60791301727295</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55549764633179</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66032791137695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65159177780151</t>
+    <t xml:space="preserve">3.51181840896606</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54676175117493</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63411998748779</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62538456916809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7476863861084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69527149200439</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66906380653381</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60791277885437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55549788475037</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66032814979553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65159201622009</t>
   </si>
   <si>
     <t xml:space="preserve">3.68653535842896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.70400714874268</t>
+    <t xml:space="preserve">3.7040069103241</t>
   </si>
   <si>
     <t xml:space="preserve">3.75642251968384</t>
@@ -1010,19 +1010,19 @@
     <t xml:space="preserve">3.44193148612976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4856104850769</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.4069881439209</t>
+    <t xml:space="preserve">3.48561072349548</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.40698790550232</t>
   </si>
   <si>
     <t xml:space="preserve">3.35457253456116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.45940327644348</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52928972244263</t>
+    <t xml:space="preserve">3.4594030380249</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52928996086121</t>
   </si>
   <si>
     <t xml:space="preserve">3.46813893318176</t>
@@ -1031,22 +1031,22 @@
     <t xml:space="preserve">3.47687458992004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79136633872986</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7214789390564</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.8787248134613</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17574453353882</t>
+    <t xml:space="preserve">3.79136610031128</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.72147917747498</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.87872457504272</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17574405670166</t>
   </si>
   <si>
     <t xml:space="preserve">4.31551790237427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35046148300171</t>
+    <t xml:space="preserve">4.35046100616455</t>
   </si>
   <si>
     <t xml:space="preserve">4.18447971343994</t>
@@ -1061,25 +1061,25 @@
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493202209473</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98355484008789</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94861197471619</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93114018440247</t>
+    <t xml:space="preserve">3.90493226051331</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98355507850647</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94861173629761</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93113970756531</t>
   </si>
   <si>
     <t xml:space="preserve">4.08838510513306</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07091331481934</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1233286857605</t>
+    <t xml:space="preserve">4.07091379165649</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.12332820892334</t>
   </si>
   <si>
     <t xml:space="preserve">4.00102663040161</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">4.00976276397705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93987607955933</t>
+    <t xml:space="preserve">3.93987560272217</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
@@ -1097,31 +1097,31 @@
     <t xml:space="preserve">4.2106876373291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29804611206055</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28931045532227</t>
+    <t xml:space="preserve">4.29804658889771</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28930997848511</t>
   </si>
   <si>
     <t xml:space="preserve">4.21942329406738</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19321584701538</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.1495361328125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16700792312622</t>
+    <t xml:space="preserve">4.19321632385254</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.14953660964966</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16700839996338</t>
   </si>
   <si>
     <t xml:space="preserve">4.11459302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06217813491821</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78262996673584</t>
+    <t xml:space="preserve">4.06217765808105</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78263020515442</t>
   </si>
   <si>
     <t xml:space="preserve">3.80010175704956</t>
@@ -1130,10 +1130,10 @@
     <t xml:space="preserve">3.82630968093872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.83504509925842</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84378099441528</t>
+    <t xml:space="preserve">3.835045337677</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84378123283386</t>
   </si>
   <si>
     <t xml:space="preserve">3.77389454841614</t>
@@ -1142,16 +1142,16 @@
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734786987305</t>
+    <t xml:space="preserve">3.95734763145447</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.86125302314758</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76515865325928</t>
+    <t xml:space="preserve">3.861252784729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76515817642212</t>
   </si>
   <si>
     <t xml:space="preserve">3.8175733089447</t>
@@ -1163,52 +1163,52 @@
     <t xml:space="preserve">3.67779970169067</t>
   </si>
   <si>
-    <t xml:space="preserve">3.73895072937012</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85251665115356</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71274304389954</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92240381240845</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61664867401123</t>
+    <t xml:space="preserve">3.7389509677887</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85251712799072</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71274328231812</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92240357398987</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61664843559265</t>
   </si>
   <si>
     <t xml:space="preserve">3.39825224876404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23227071762085</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0575532913208</t>
+    <t xml:space="preserve">3.23227047920227</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05755352973938</t>
   </si>
   <si>
     <t xml:space="preserve">2.97019457817078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95272302627563</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91777920722961</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90904331207275</t>
+    <t xml:space="preserve">2.95272278785706</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91777944564819</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90904355049133</t>
   </si>
   <si>
     <t xml:space="preserve">3.37204432487488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38078022003174</t>
+    <t xml:space="preserve">3.38077998161316</t>
   </si>
   <si>
     <t xml:space="preserve">3.41572380065918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31962895393372</t>
+    <t xml:space="preserve">3.31962919235229</t>
   </si>
   <si>
     <t xml:space="preserve">3.27594995498657</t>
@@ -57729,7 +57729,7 @@
     </row>
     <row r="2139">
       <c r="A2139" s="1" t="n">
-        <v>46080.6912847222</v>
+        <v>46080.3333333333</v>
       </c>
       <c r="B2139" t="n">
         <v>4519</v>
@@ -57750,6 +57750,32 @@
         <v>581</v>
       </c>
       <c r="H2139" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2140">
+      <c r="A2140" s="1" t="n">
+        <v>46083.6831597222</v>
+      </c>
+      <c r="B2140" t="n">
+        <v>51012</v>
+      </c>
+      <c r="C2140" t="n">
+        <v>3.74000000953674</v>
+      </c>
+      <c r="D2140" t="n">
+        <v>3.40000009536743</v>
+      </c>
+      <c r="E2140" t="n">
+        <v>3.66000008583069</v>
+      </c>
+      <c r="F2140" t="n">
+        <v>3.57999992370605</v>
+      </c>
+      <c r="G2140" t="s">
+        <v>582</v>
+      </c>
+      <c r="H2140" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -53,22 +53,22 @@
     <t xml:space="preserve">2.98013734817505</t>
   </si>
   <si>
-    <t xml:space="preserve">2.97266817092896</t>
+    <t xml:space="preserve">2.97266840934753</t>
   </si>
   <si>
     <t xml:space="preserve">2.94578003883362</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95773005485535</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9622118473053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93532347679138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91291618347168</t>
+    <t xml:space="preserve">2.95773029327393</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.96221160888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9353232383728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91291570663452</t>
   </si>
   <si>
     <t xml:space="preserve">2.97864365577698</t>
@@ -80,43 +80,43 @@
     <t xml:space="preserve">3.03540802001953</t>
   </si>
   <si>
-    <t xml:space="preserve">3.056321144104</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0593090057373</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05034637451172</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98760652542114</t>
+    <t xml:space="preserve">3.05632138252258</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05930876731873</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05034613609314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98760628700256</t>
   </si>
   <si>
     <t xml:space="preserve">2.95026135444641</t>
   </si>
   <si>
-    <t xml:space="preserve">3.01598858833313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01001334190369</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02495169639587</t>
+    <t xml:space="preserve">3.01598906517029</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01001381874084</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02495145797729</t>
   </si>
   <si>
     <t xml:space="preserve">3.0174822807312</t>
   </si>
   <si>
-    <t xml:space="preserve">3.03092646598816</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99955677986145</t>
+    <t xml:space="preserve">3.03092670440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99955654144287</t>
   </si>
   <si>
     <t xml:space="preserve">3.04437112808228</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95922374725342</t>
+    <t xml:space="preserve">2.959223985672</t>
   </si>
   <si>
     <t xml:space="preserve">3.00254440307617</t>
@@ -131,10 +131,10 @@
     <t xml:space="preserve">2.896484375</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91889142990112</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91590356826782</t>
+    <t xml:space="preserve">2.91889095306396</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91590404510498</t>
   </si>
   <si>
     <t xml:space="preserve">2.92038536071777</t>
@@ -143,10 +143,10 @@
     <t xml:space="preserve">2.90544724464417</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90992856025696</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.9233729839325</t>
+    <t xml:space="preserve">2.90992879867554</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92337274551392</t>
   </si>
   <si>
     <t xml:space="preserve">2.8382260799408</t>
@@ -155,10 +155,10 @@
     <t xml:space="preserve">2.86063289642334</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82627558708191</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.77996730804443</t>
+    <t xml:space="preserve">2.82627534866333</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.77996778488159</t>
   </si>
   <si>
     <t xml:space="preserve">2.84569478034973</t>
@@ -170,7 +170,7 @@
     <t xml:space="preserve">2.88303995132446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79639935493469</t>
+    <t xml:space="preserve">2.79639959335327</t>
   </si>
   <si>
     <t xml:space="preserve">2.87557101249695</t>
@@ -191,7 +191,7 @@
     <t xml:space="preserve">2.75009155273438</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76353549957275</t>
+    <t xml:space="preserve">2.76353573799133</t>
   </si>
   <si>
     <t xml:space="preserve">2.77847409248352</t>
@@ -209,16 +209,16 @@
     <t xml:space="preserve">2.6515007019043</t>
   </si>
   <si>
-    <t xml:space="preserve">2.62162446975708</t>
+    <t xml:space="preserve">2.62162470817566</t>
   </si>
   <si>
     <t xml:space="preserve">2.53946542739868</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5693416595459</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.61415553092957</t>
+    <t xml:space="preserve">2.56934142112732</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.61415529251099</t>
   </si>
   <si>
     <t xml:space="preserve">2.65896964073181</t>
@@ -230,7 +230,7 @@
     <t xml:space="preserve">2.70378351211548</t>
   </si>
   <si>
-    <t xml:space="preserve">2.77100491523743</t>
+    <t xml:space="preserve">2.77100467681885</t>
   </si>
   <si>
     <t xml:space="preserve">2.81581902503967</t>
@@ -239,31 +239,31 @@
     <t xml:space="preserve">2.7336597442627</t>
   </si>
   <si>
-    <t xml:space="preserve">2.66643857955933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68137645721436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.74112868309021</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72619128227234</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8307569026947</t>
+    <t xml:space="preserve">2.66643881797791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68137669563293</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.74112892150879</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72619080543518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83075714111328</t>
   </si>
   <si>
     <t xml:space="preserve">2.893150806427</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69871830940247</t>
+    <t xml:space="preserve">2.69871854782104</t>
   </si>
   <si>
     <t xml:space="preserve">2.83870983123779</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93203711509705</t>
+    <t xml:space="preserve">2.93203687667847</t>
   </si>
   <si>
     <t xml:space="preserve">2.87759613990784</t>
@@ -275,16 +275,16 @@
     <t xml:space="preserve">2.81537771224976</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84648728370667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.79982328414917</t>
+    <t xml:space="preserve">2.84648680686951</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.79982304573059</t>
   </si>
   <si>
     <t xml:space="preserve">2.73760461807251</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76093673706055</t>
+    <t xml:space="preserve">2.76093697547913</t>
   </si>
   <si>
     <t xml:space="preserve">2.80760049819946</t>
@@ -296,31 +296,31 @@
     <t xml:space="preserve">2.9553689956665</t>
   </si>
   <si>
-    <t xml:space="preserve">2.90870547294617</t>
+    <t xml:space="preserve">2.90870523452759</t>
   </si>
   <si>
     <t xml:space="preserve">2.88537335395813</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82315516471863</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86204171180725</t>
+    <t xml:space="preserve">2.82315540313721</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86204147338867</t>
   </si>
   <si>
     <t xml:space="preserve">3.00203251838684</t>
   </si>
   <si>
-    <t xml:space="preserve">2.91648268699646</t>
+    <t xml:space="preserve">2.9164822101593</t>
   </si>
   <si>
     <t xml:space="preserve">2.85426425933838</t>
   </si>
   <si>
-    <t xml:space="preserve">2.72982740402222</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68316388130188</t>
+    <t xml:space="preserve">2.7298276424408</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.68316411972046</t>
   </si>
   <si>
     <t xml:space="preserve">2.72205018997192</t>
@@ -332,7 +332,7 @@
     <t xml:space="preserve">2.70649576187134</t>
   </si>
   <si>
-    <t xml:space="preserve">2.93981456756592</t>
+    <t xml:space="preserve">2.93981432914734</t>
   </si>
   <si>
     <t xml:space="preserve">2.99425530433655</t>
@@ -341,25 +341,25 @@
     <t xml:space="preserve">2.97870063781738</t>
   </si>
   <si>
-    <t xml:space="preserve">2.86981868743896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.94759154319763</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98647809028625</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.63650012016296</t>
+    <t xml:space="preserve">2.86981892585754</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.94759178161621</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98647785186768</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.63650035858154</t>
   </si>
   <si>
     <t xml:space="preserve">2.550950050354</t>
   </si>
   <si>
-    <t xml:space="preserve">2.51984095573425</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.41095876693726</t>
+    <t xml:space="preserve">2.51984071731567</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.41095900535583</t>
   </si>
   <si>
     <t xml:space="preserve">2.34096336364746</t>
@@ -368,13 +368,13 @@
     <t xml:space="preserve">2.34874081611633</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3642954826355</t>
+    <t xml:space="preserve">2.36429524421692</t>
   </si>
   <si>
     <t xml:space="preserve">2.2554132938385</t>
   </si>
   <si>
-    <t xml:space="preserve">2.24763584136963</t>
+    <t xml:space="preserve">2.24763607978821</t>
   </si>
   <si>
     <t xml:space="preserve">2.3254086971283</t>
@@ -386,49 +386,49 @@
     <t xml:space="preserve">2.18541765213013</t>
   </si>
   <si>
-    <t xml:space="preserve">2.27874493598938</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.26319050788879</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.2165265083313</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.06875848770142</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.14653134346008</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.10764503479004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.15430879592896</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.17764043807983</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.22430396080017</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.35651803016663</t>
+    <t xml:space="preserve">2.27874517440796</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.26319026947021</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.21652674674988</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.06875824928284</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1465311050415</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.10764455795288</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.1543083190918</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.17764019966125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.22430372238159</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.35651755332947</t>
   </si>
   <si>
     <t xml:space="preserve">2.4887318611145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.52761793136597</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.43429064750671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.44206809997559</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.55872702598572</t>
+    <t xml:space="preserve">2.52761816978455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.43429088592529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.44206786155701</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.55872750282288</t>
   </si>
   <si>
     <t xml:space="preserve">2.44984531402588</t>
@@ -437,46 +437,46 @@
     <t xml:space="preserve">2.37207245826721</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33318614959717</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29429936408997</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.37984991073608</t>
+    <t xml:space="preserve">2.33318591117859</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.29429960250854</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.3798496723175</t>
   </si>
   <si>
     <t xml:space="preserve">2.71427273750305</t>
   </si>
   <si>
-    <t xml:space="preserve">2.58205914497375</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62872314453125</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65983200073242</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.57428169250488</t>
+    <t xml:space="preserve">2.58205890655518</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62872338294983</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.659832239151</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57428193092346</t>
   </si>
   <si>
     <t xml:space="preserve">2.67538666725159</t>
   </si>
   <si>
-    <t xml:space="preserve">2.64427757263184</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69094109535217</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76871395111084</t>
+    <t xml:space="preserve">2.64427733421326</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69094133377075</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76871418952942</t>
   </si>
   <si>
     <t xml:space="preserve">2.90092802047729</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9631462097168</t>
+    <t xml:space="preserve">2.96314597129822</t>
   </si>
   <si>
     <t xml:space="preserve">2.92425990104675</t>
@@ -488,10 +488,10 @@
     <t xml:space="preserve">3.01758742332458</t>
   </si>
   <si>
-    <t xml:space="preserve">3.04869675636292</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03314185142517</t>
+    <t xml:space="preserve">3.04869651794434</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03314161300659</t>
   </si>
   <si>
     <t xml:space="preserve">3.0642511844635</t>
@@ -500,19 +500,19 @@
     <t xml:space="preserve">3.07980561256409</t>
   </si>
   <si>
-    <t xml:space="preserve">3.06049919128418</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02811312675476</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01191997528076</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1090784072876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0928852558136</t>
+    <t xml:space="preserve">3.0604989528656</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02811288833618</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01191973686218</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.10907816886902</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.09288549423218</t>
   </si>
   <si>
     <t xml:space="preserve">3.12527132034302</t>
@@ -527,31 +527,31 @@
     <t xml:space="preserve">3.30339574813843</t>
   </si>
   <si>
-    <t xml:space="preserve">3.41674733161926</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.35197496414185</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.33578205108643</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.36816811561584</t>
+    <t xml:space="preserve">3.41674757003784</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.35197520256042</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.33578181266785</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.36816835403442</t>
   </si>
   <si>
     <t xml:space="preserve">3.23862338066101</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31958889961243</t>
+    <t xml:space="preserve">3.31958913803101</t>
   </si>
   <si>
     <t xml:space="preserve">3.27100944519043</t>
   </si>
   <si>
-    <t xml:space="preserve">3.28720259666443</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.22243046760559</t>
+    <t xml:space="preserve">3.28720235824585</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.22243022918701</t>
   </si>
   <si>
     <t xml:space="preserve">3.17385101318359</t>
@@ -563,31 +563,31 @@
     <t xml:space="preserve">3.1414647102356</t>
   </si>
   <si>
-    <t xml:space="preserve">3.40055418014526</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.49771332740784</t>
+    <t xml:space="preserve">3.40055441856384</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.49771308898926</t>
   </si>
   <si>
     <t xml:space="preserve">3.38436126708984</t>
   </si>
   <si>
-    <t xml:space="preserve">3.25481653213501</t>
+    <t xml:space="preserve">3.25481629371643</t>
   </si>
   <si>
     <t xml:space="preserve">3.19004416465759</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96334052085876</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97953367233276</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80140900611877</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.88237452507019</t>
+    <t xml:space="preserve">2.96334028244019</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97953343391418</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80140924453735</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.88237476348877</t>
   </si>
   <si>
     <t xml:space="preserve">2.86618161201477</t>
@@ -599,22 +599,22 @@
     <t xml:space="preserve">2.78521609306335</t>
   </si>
   <si>
-    <t xml:space="preserve">2.75283002853394</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.72044348716736</t>
+    <t xml:space="preserve">2.75282979011536</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.72044372558594</t>
   </si>
   <si>
     <t xml:space="preserve">2.83379530906677</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76902294158936</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73663687705994</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.81760215759277</t>
+    <t xml:space="preserve">2.76902318000793</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73663711547852</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.81760239601135</t>
   </si>
   <si>
     <t xml:space="preserve">2.89856767654419</t>
@@ -623,7 +623,7 @@
     <t xml:space="preserve">2.91476082801819</t>
   </si>
   <si>
-    <t xml:space="preserve">2.63947772979736</t>
+    <t xml:space="preserve">2.63947796821594</t>
   </si>
   <si>
     <t xml:space="preserve">2.67186403274536</t>
@@ -635,7 +635,7 @@
     <t xml:space="preserve">2.68805718421936</t>
   </si>
   <si>
-    <t xml:space="preserve">2.70425057411194</t>
+    <t xml:space="preserve">2.70425033569336</t>
   </si>
   <si>
     <t xml:space="preserve">2.60709166526794</t>
@@ -647,16 +647,16 @@
     <t xml:space="preserve">2.42896747589111</t>
   </si>
   <si>
-    <t xml:space="preserve">2.54231929779053</t>
+    <t xml:space="preserve">2.54231905937195</t>
   </si>
   <si>
     <t xml:space="preserve">2.46135377883911</t>
   </si>
   <si>
-    <t xml:space="preserve">2.3156156539917</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.29942274093628</t>
+    <t xml:space="preserve">2.31561541557312</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.2994225025177</t>
   </si>
   <si>
     <t xml:space="preserve">2.35488176345825</t>
@@ -665,7 +665,7 @@
     <t xml:space="preserve">2.40607476234436</t>
   </si>
   <si>
-    <t xml:space="preserve">2.28662419319153</t>
+    <t xml:space="preserve">2.28662443161011</t>
   </si>
   <si>
     <t xml:space="preserve">2.13304495811462</t>
@@ -686,7 +686,7 @@
     <t xml:space="preserve">2.09891629219055</t>
   </si>
   <si>
-    <t xml:space="preserve">2.26956009864807</t>
+    <t xml:space="preserve">2.26955986022949</t>
   </si>
   <si>
     <t xml:space="preserve">2.21836686134338</t>
@@ -695,19 +695,19 @@
     <t xml:space="preserve">2.32075309753418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.55965423583984</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.54258966445923</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.45726799964905</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.5767183303833</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.62791156768799</t>
+    <t xml:space="preserve">2.55965399742126</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.54258990287781</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.45726823806763</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.57671856880188</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.62791132926941</t>
   </si>
   <si>
     <t xml:space="preserve">2.61084699630737</t>
@@ -716,13 +716,13 @@
     <t xml:space="preserve">2.64497566223145</t>
   </si>
   <si>
-    <t xml:space="preserve">2.59378290176392</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.69616913795471</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.71323347091675</t>
+    <t xml:space="preserve">2.59378266334534</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.69616889953613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.71323323249817</t>
   </si>
   <si>
     <t xml:space="preserve">2.44020342826843</t>
@@ -737,10 +737,10 @@
     <t xml:space="preserve">2.15010929107666</t>
   </si>
   <si>
-    <t xml:space="preserve">2.33781743049622</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.30368876457214</t>
+    <t xml:space="preserve">2.33781719207764</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.30368852615356</t>
   </si>
   <si>
     <t xml:space="preserve">2.25249576568604</t>
@@ -752,7 +752,7 @@
     <t xml:space="preserve">2.37194609642029</t>
   </si>
   <si>
-    <t xml:space="preserve">2.38901042938232</t>
+    <t xml:space="preserve">2.3890106678009</t>
   </si>
   <si>
     <t xml:space="preserve">2.20130252838135</t>
@@ -761,16 +761,16 @@
     <t xml:space="preserve">2.18423795700073</t>
   </si>
   <si>
-    <t xml:space="preserve">2.01359415054321</t>
+    <t xml:space="preserve">2.01359438896179</t>
   </si>
   <si>
     <t xml:space="preserve">2.04772329330444</t>
   </si>
   <si>
-    <t xml:space="preserve">2.11598038673401</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.91120827198029</t>
+    <t xml:space="preserve">2.11598062515259</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.91120851039886</t>
   </si>
   <si>
     <t xml:space="preserve">1.87707984447479</t>
@@ -779,19 +779,19 @@
     <t xml:space="preserve">1.84295094013214</t>
   </si>
   <si>
-    <t xml:space="preserve">1.97946560382843</t>
+    <t xml:space="preserve">1.97946584224701</t>
   </si>
   <si>
     <t xml:space="preserve">1.86001515388489</t>
   </si>
   <si>
-    <t xml:space="preserve">1.94533693790436</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.96240139007568</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.99653005599976</t>
+    <t xml:space="preserve">1.94533717632294</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.96240127086639</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.99652993679047</t>
   </si>
   <si>
     <t xml:space="preserve">2.81561923027039</t>
@@ -803,10 +803,10 @@
     <t xml:space="preserve">2.88387703895569</t>
   </si>
   <si>
-    <t xml:space="preserve">2.76442646980286</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.73029780387878</t>
+    <t xml:space="preserve">2.76442623138428</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.73029756546021</t>
   </si>
   <si>
     <t xml:space="preserve">2.6791045665741</t>
@@ -821,7 +821,7 @@
     <t xml:space="preserve">2.86681246757507</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79855513572693</t>
+    <t xml:space="preserve">2.79855489730835</t>
   </si>
   <si>
     <t xml:space="preserve">2.78149056434631</t>
@@ -830,10 +830,10 @@
     <t xml:space="preserve">2.9350700378418</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96919870376587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02039170265198</t>
+    <t xml:space="preserve">2.96919846534729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02039194107056</t>
   </si>
   <si>
     <t xml:space="preserve">3.00332713127136</t>
@@ -842,34 +842,34 @@
     <t xml:space="preserve">3.03745603561401</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98626279830933</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05452036857605</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.07158493995667</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.13984251022339</t>
+    <t xml:space="preserve">2.98626303672791</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05452060699463</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.07158470153809</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.13984227180481</t>
   </si>
   <si>
     <t xml:space="preserve">3.11424589157104</t>
   </si>
   <si>
-    <t xml:space="preserve">3.13131022453308</t>
+    <t xml:space="preserve">3.1313099861145</t>
   </si>
   <si>
     <t xml:space="preserve">3.06305265426636</t>
   </si>
   <si>
-    <t xml:space="preserve">3.16543889045715</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.1995677947998</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.15690660476685</t>
+    <t xml:space="preserve">3.16543865203857</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.19956755638123</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.15690684318542</t>
   </si>
   <si>
     <t xml:space="preserve">3.2336962223053</t>
@@ -887,34 +887,34 @@
     <t xml:space="preserve">3.31048607826233</t>
   </si>
   <si>
-    <t xml:space="preserve">3.34461498260498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.32755017280579</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.28488922119141</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.18250322341919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29342126846313</t>
+    <t xml:space="preserve">3.3446147441864</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.32755041122437</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.28488945960999</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.18250346183777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29342150688171</t>
   </si>
   <si>
     <t xml:space="preserve">3.33710074424744</t>
   </si>
   <si>
-    <t xml:space="preserve">3.32836508750916</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.29342150688171</t>
+    <t xml:space="preserve">3.32836484909058</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.29342174530029</t>
   </si>
   <si>
     <t xml:space="preserve">3.24974226951599</t>
   </si>
   <si>
-    <t xml:space="preserve">3.20606279373169</t>
+    <t xml:space="preserve">3.20606303215027</t>
   </si>
   <si>
     <t xml:space="preserve">3.15364766120911</t>
@@ -926,7 +926,7 @@
     <t xml:space="preserve">3.17111968994141</t>
   </si>
   <si>
-    <t xml:space="preserve">3.26721382141113</t>
+    <t xml:space="preserve">3.26721405982971</t>
   </si>
   <si>
     <t xml:space="preserve">3.36330842971802</t>
@@ -935,55 +935,55 @@
     <t xml:space="preserve">3.49434638023376</t>
   </si>
   <si>
-    <t xml:space="preserve">3.58170533180237</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.56423330307007</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.59044098854065</t>
+    <t xml:space="preserve">3.58170509338379</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.56423354148865</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.59044122695923</t>
   </si>
   <si>
     <t xml:space="preserve">3.5030825138092</t>
   </si>
   <si>
-    <t xml:space="preserve">3.51181840896606</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.54676175117493</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.63411998748779</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.62538456916809</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.7476863861084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.69527149200439</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66906380653381</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.60791277885437</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.55549788475037</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.66032814979553</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.65159201622009</t>
+    <t xml:space="preserve">3.51181817054749</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.54676151275635</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.63412046432495</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.62538480758667</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.74768662452698</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.69527125358582</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66906356811523</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.60791301727295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.55549764633179</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.66032791137695</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.65159177780151</t>
   </si>
   <si>
     <t xml:space="preserve">3.68653535842896</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7040069103241</t>
+    <t xml:space="preserve">3.70400714874268</t>
   </si>
   <si>
     <t xml:space="preserve">3.75642251968384</t>
@@ -1010,19 +1010,19 @@
     <t xml:space="preserve">3.44193148612976</t>
   </si>
   <si>
-    <t xml:space="preserve">3.48561072349548</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.40698790550232</t>
+    <t xml:space="preserve">3.4856104850769</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.4069881439209</t>
   </si>
   <si>
     <t xml:space="preserve">3.35457253456116</t>
   </si>
   <si>
-    <t xml:space="preserve">3.4594030380249</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.52928996086121</t>
+    <t xml:space="preserve">3.45940327644348</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.52928972244263</t>
   </si>
   <si>
     <t xml:space="preserve">3.46813893318176</t>
@@ -1031,22 +1031,22 @@
     <t xml:space="preserve">3.47687458992004</t>
   </si>
   <si>
-    <t xml:space="preserve">3.79136610031128</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.72147917747498</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.87872457504272</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.17574405670166</t>
+    <t xml:space="preserve">3.79136633872986</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.7214789390564</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.8787248134613</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.17574453353882</t>
   </si>
   <si>
     <t xml:space="preserve">4.31551790237427</t>
   </si>
   <si>
-    <t xml:space="preserve">4.35046100616455</t>
+    <t xml:space="preserve">4.35046148300171</t>
   </si>
   <si>
     <t xml:space="preserve">4.18447971343994</t>
@@ -1061,25 +1061,25 @@
     <t xml:space="preserve">4.14080047607422</t>
   </si>
   <si>
-    <t xml:space="preserve">3.90493226051331</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.98355507850647</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.94861173629761</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.93113970756531</t>
+    <t xml:space="preserve">3.90493202209473</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.98355484008789</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.94861197471619</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.93114018440247</t>
   </si>
   <si>
     <t xml:space="preserve">4.08838510513306</t>
   </si>
   <si>
-    <t xml:space="preserve">4.07091379165649</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.12332820892334</t>
+    <t xml:space="preserve">4.07091331481934</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1233286857605</t>
   </si>
   <si>
     <t xml:space="preserve">4.00102663040161</t>
@@ -1088,7 +1088,7 @@
     <t xml:space="preserve">4.00976276397705</t>
   </si>
   <si>
-    <t xml:space="preserve">3.93987560272217</t>
+    <t xml:space="preserve">3.93987607955933</t>
   </si>
   <si>
     <t xml:space="preserve">4.0971212387085</t>
@@ -1097,31 +1097,31 @@
     <t xml:space="preserve">4.2106876373291</t>
   </si>
   <si>
-    <t xml:space="preserve">4.29804658889771</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.28930997848511</t>
+    <t xml:space="preserve">4.29804611206055</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.28931045532227</t>
   </si>
   <si>
     <t xml:space="preserve">4.21942329406738</t>
   </si>
   <si>
-    <t xml:space="preserve">4.19321632385254</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.14953660964966</t>
-  </si>
-  <si>
-    <t xml:space="preserve">4.16700839996338</t>
+    <t xml:space="preserve">4.19321584701538</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.1495361328125</t>
+  </si>
+  <si>
+    <t xml:space="preserve">4.16700792312622</t>
   </si>
   <si>
     <t xml:space="preserve">4.11459302902222</t>
   </si>
   <si>
-    <t xml:space="preserve">4.06217765808105</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.78263020515442</t>
+    <t xml:space="preserve">4.06217813491821</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.78262996673584</t>
   </si>
   <si>
     <t xml:space="preserve">3.80010175704956</t>
@@ -1130,10 +1130,10 @@
     <t xml:space="preserve">3.82630968093872</t>
   </si>
   <si>
-    <t xml:space="preserve">3.835045337677</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.84378123283386</t>
+    <t xml:space="preserve">3.83504509925842</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.84378099441528</t>
   </si>
   <si>
     <t xml:space="preserve">3.77389454841614</t>
@@ -1142,16 +1142,16 @@
     <t xml:space="preserve">4.03597021102905</t>
   </si>
   <si>
-    <t xml:space="preserve">3.95734763145447</t>
+    <t xml:space="preserve">3.95734786987305</t>
   </si>
   <si>
     <t xml:space="preserve">3.808837890625</t>
   </si>
   <si>
-    <t xml:space="preserve">3.861252784729</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.76515817642212</t>
+    <t xml:space="preserve">3.86125302314758</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.76515865325928</t>
   </si>
   <si>
     <t xml:space="preserve">3.8175733089447</t>
@@ -1163,52 +1163,52 @@
     <t xml:space="preserve">3.67779970169067</t>
   </si>
   <si>
-    <t xml:space="preserve">3.7389509677887</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.85251712799072</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.71274328231812</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.92240357398987</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.61664843559265</t>
+    <t xml:space="preserve">3.73895072937012</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.85251665115356</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.71274304389954</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.92240381240845</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.61664867401123</t>
   </si>
   <si>
     <t xml:space="preserve">3.39825224876404</t>
   </si>
   <si>
-    <t xml:space="preserve">3.23227047920227</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05755352973938</t>
+    <t xml:space="preserve">3.23227071762085</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.0575532913208</t>
   </si>
   <si>
     <t xml:space="preserve">2.97019457817078</t>
   </si>
   <si>
-    <t xml:space="preserve">2.95272278785706</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91777944564819</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90904355049133</t>
+    <t xml:space="preserve">2.95272302627563</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91777920722961</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90904331207275</t>
   </si>
   <si>
     <t xml:space="preserve">3.37204432487488</t>
   </si>
   <si>
-    <t xml:space="preserve">3.38077998161316</t>
+    <t xml:space="preserve">3.38078022003174</t>
   </si>
   <si>
     <t xml:space="preserve">3.41572380065918</t>
   </si>
   <si>
-    <t xml:space="preserve">3.31962919235229</t>
+    <t xml:space="preserve">3.31962895393372</t>
   </si>
   <si>
     <t xml:space="preserve">3.27594995498657</t>
@@ -57755,7 +57755,7 @@
     </row>
     <row r="2140">
       <c r="A2140" s="1" t="n">
-        <v>46083.6831597222</v>
+        <v>46083.3333333333</v>
       </c>
       <c r="B2140" t="n">
         <v>51012</v>
@@ -57776,6 +57776,32 @@
         <v>582</v>
       </c>
       <c r="H2140" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="2141">
+      <c r="A2141" s="1" t="n">
+        <v>46084.6913078704</v>
+      </c>
+      <c r="B2141" t="n">
+        <v>25234</v>
+      </c>
+      <c r="C2141" t="n">
+        <v>3.51999998092651</v>
+      </c>
+      <c r="D2141" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="E2141" t="n">
+        <v>3.51999998092651</v>
+      </c>
+      <c r="F2141" t="n">
+        <v>3.29999995231628</v>
+      </c>
+      <c r="G2141" t="s">
+        <v>573</v>
+      </c>
+      <c r="H2141" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/NDT.MI.xlsx
+++ b/data/NDT.MI.xlsx
@@ -38,22 +38,22 @@
     <t xml:space="preserve">ticker</t>
   </si>
   <si>
-    <t xml:space="preserve">3.02345776557922</t>
+    <t xml:space="preserve">3.02345752716064</t>
   </si>
   <si>
     <t xml:space="preserve">NDT.MI</t>
   </si>
   <si>
-    <t xml:space="preserve">2.96519923210144</t>
+    <t xml:space="preserve">2.96519947052002</t>
   </si>
   <si>
     <t xml:space="preserve">2.88901543617249</t>
   </si>
   <si>
-    <t xml:space="preserve">2.98013734817505</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97266840934753</t>
+    <t xml:space="preserve">2.98013758659363</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.97266817092896</t>
   </si>
   <si>
     <t xml:space="preserve">2.94577980041504</t>
@@ -62,19 +62,19 @@
     <t xml:space="preserve">2.95773029327393</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9622118473053</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.93532347679138</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.91291618347168</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.97864365577698</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98611235618591</t>
+    <t xml:space="preserve">2.96221160888672</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9353232383728</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.91291642189026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.9786434173584</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98611259460449</t>
   </si>
   <si>
     <t xml:space="preserve">3.03540802001953</t>
@@ -83,49 +83,49 @@
     <t xml:space="preserve">3.05632138252258</t>
   </si>
   <si>
-    <t xml:space="preserve">3.05930924415588</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.05034589767456</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.98760652542114</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.95026135444641</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01598882675171</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.01001381874084</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.02495169639587</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.0174822807312</t>
-  </si>
-  <si>
-    <t xml:space="preserve">3.03092694282532</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.99955677986145</t>
+    <t xml:space="preserve">3.0593090057373</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.05034613609314</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.98760628700256</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.95026111602783</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01598834991455</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01001334190369</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.02495145797729</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.01748251914978</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3.03092670440674</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.99955654144287</t>
   </si>
   <si>
     <t xml:space="preserve">3.0443708896637</t>
   </si>
   <si>
-    <t xml:space="preserve">2.959223985672</t>
+    <t xml:space="preserve">2.95922422409058</t>
   </si>
   <si>
     <t xml:space="preserve">3.00254440307617</t>
   </si>
   <si>
-    <t xml:space="preserve">2.92785406112671</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90843462944031</t>
+    <t xml:space="preserve">2.92785429954529</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90843510627747</t>
   </si>
   <si>
     <t xml:space="preserve">2.896484375</t>
@@ -134,34 +134,34 @@
     <t xml:space="preserve">2.91889142990112</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9159038066864</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.92038512229919</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.90544748306274</t>
+    <t xml:space="preserve">2.91590356826782</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.92038536071777</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.90544724464417</t>
   </si>
   <si>
     <t xml:space="preserve">2.90992856025696</t>
   </si>
   <si>
-    <t xml:space="preserve">2.9233729839325</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.8382260799408</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.86063289642334</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.82627534866333</t>
+    <t xml:space="preserve">2.92337274551392</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.83822584152222</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.86063313484192</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.82627558708191</t>
   </si>
   <si>
     <t xml:space="preserve">2.77996754646301</t>
   </si>
   <si>
-    <t xml:space="preserve">2.84569501876831</t>
+    <t xml:space="preserve">2.84569525718689</t>
   </si>
   <si>
     <t xml:space="preserve">2.86810207366943</t>
@@ -170,28 +170,28 @@
     <t xml:space="preserve">2.88303995132446</t>
   </si>
   <si>
-    <t xml:space="preserve">2.79639959335327</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.87557101249695</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.89797806739807</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.80088067054749</t>
+    <t xml:space="preserve">2.79639935493469</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.87557125091553</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.89797830581665</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.80088114738464</t>
   </si>
   <si>
     <t xml:space="preserve">2.74262261390686</t>
   </si>
   <si>
-    <t xml:space="preserve">2.82179403305054</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.75009155273438</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.76353573799133</t>
+    <t xml:space="preserve">2.82179427146912</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.75009179115295</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2.76353597640991</t>
   </si>
   <si>
     <t xml:space="preserve">2.77847385406494</t>
@@ -203,7 +203,7 @@
     <t xml:space="preserve">2.79341197013855</t>
   </si>
   <si>
-    <t xml:space="preserve">2.69631481170654</t>
+    <t xml:space="preserve">2.69631457328796</t>
   </si>
   <si>
     <t xml:space="preserve">2.6515007019043</t>
@@ -212,52 +212,52 @@
     <t xml:space="preserve">2.62162446975708</t>
   </si>
   <si>
-    <t xml:space="preserve">2.5394651889801</t>
+    <t xml:space="preserve">2.53946542739868</t>
   </si>
   <si>
     <t xml:space="preserve">2.5693416595459</t>
   </si>
   <si>
-    <t xml:space="preserve">2.61415553092957</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.65896987915039</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2.68884563446045</t>
+    <t xml:space="preserve">2.